--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="83">
   <si>
     <t>#</t>
   </si>
@@ -210,6 +210,12 @@
   </si>
   <si>
     <t>法宝自选</t>
+  </si>
+  <si>
+    <t>兑换魂骨自选*1</t>
+  </si>
+  <si>
+    <t>魂骨自选</t>
   </si>
   <si>
     <t>兑换专属之心*5</t>
@@ -1280,7 +1286,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M76"/>
+  <dimension ref="C1:M77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1547,7 +1553,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" ref="L10:L26" si="1">E10*F10</f>
+        <f t="shared" ref="L10:L27" si="1">E10*F10</f>
         <v>24000</v>
       </c>
     </row>
@@ -1727,7 +1733,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>34</v>
@@ -1746,7 +1752,7 @@
       </c>
       <c r="L16" s="1">
         <f t="shared" si="1"/>
-        <v>24000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:12">
@@ -1760,7 +1766,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>36</v>
@@ -1779,7 +1785,7 @@
       </c>
       <c r="L17" s="1">
         <f t="shared" si="1"/>
-        <v>24000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:12">
@@ -1793,7 +1799,7 @@
         <v>12</v>
       </c>
       <c r="F18" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>38</v>
@@ -1812,7 +1818,7 @@
       </c>
       <c r="L18" s="1">
         <f t="shared" si="1"/>
-        <v>24000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:12">
@@ -1826,7 +1832,7 @@
         <v>12</v>
       </c>
       <c r="F19" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>40</v>
@@ -1845,7 +1851,7 @@
       </c>
       <c r="L19" s="1">
         <f t="shared" si="1"/>
-        <v>24000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:12">
@@ -1859,7 +1865,7 @@
         <v>12</v>
       </c>
       <c r="F20" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>42</v>
@@ -1878,7 +1884,7 @@
       </c>
       <c r="L20" s="1">
         <f t="shared" si="1"/>
-        <v>24000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:12">
@@ -2079,56 +2085,52 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="3:13">
-      <c r="C28" s="1">
-        <v>24</v>
-      </c>
-      <c r="D28" s="1">
-        <v>1</v>
-      </c>
-      <c r="E28" s="1">
-        <v>500</v>
-      </c>
-      <c r="F28" s="1">
-        <f>20*M28</f>
-        <v>20</v>
-      </c>
-      <c r="G28" s="1" t="s">
+    <row r="27" customHeight="1" spans="3:12">
+      <c r="C27" s="1">
+        <v>22</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="I28" s="1">
-        <v>5</v>
-      </c>
-      <c r="J28" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K28" s="1">
-        <v>5</v>
-      </c>
-      <c r="L28" s="1">
-        <f t="shared" ref="L28:L36" si="2">E28*F28</f>
-        <v>10000</v>
-      </c>
-      <c r="M28" s="1">
-        <v>1</v>
+      <c r="I27" s="1">
+        <v>4</v>
+      </c>
+      <c r="J27" s="1">
+        <v>28</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1">
+        <f t="shared" si="1"/>
+        <v>200000</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:13">
       <c r="C29" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D29" s="1">
         <v>1</v>
       </c>
       <c r="E29" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F29" s="1">
-        <f>300*M28</f>
-        <v>300</v>
+        <f>20*M29</f>
+        <v>20</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>63</v>
@@ -2140,180 +2142,180 @@
         <v>5</v>
       </c>
       <c r="J29" s="1">
+        <v>4010</v>
+      </c>
+      <c r="K29" s="1">
+        <v>5</v>
+      </c>
+      <c r="L29" s="1">
+        <f t="shared" ref="L29:L37" si="2">E29*F29</f>
+        <v>10000</v>
+      </c>
+      <c r="M29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:13">
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1">
+        <v>100</v>
+      </c>
+      <c r="F30" s="1">
+        <f>300*M29</f>
+        <v>300</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I30" s="1">
+        <v>5</v>
+      </c>
+      <c r="J30" s="1">
         <v>4007</v>
       </c>
-      <c r="K29" s="1">
+      <c r="K30" s="1">
         <v>1000</v>
       </c>
-      <c r="L29" s="1">
+      <c r="L30" s="1">
         <f t="shared" si="2"/>
         <v>30000</v>
       </c>
-      <c r="M29" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:13">
-      <c r="C30" s="1">
+      <c r="M30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:13">
+      <c r="C31" s="1">
         <v>26</v>
       </c>
-      <c r="D30" s="1">
-        <v>1</v>
-      </c>
-      <c r="E30" s="1">
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1">
         <v>100</v>
       </c>
-      <c r="F30" s="1">
-        <f>500*M28</f>
+      <c r="F31" s="1">
+        <f>500*M29</f>
         <v>500</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I30" s="1">
-        <v>5</v>
-      </c>
-      <c r="J30" s="1">
+      <c r="G31" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I31" s="1">
+        <v>5</v>
+      </c>
+      <c r="J31" s="1">
         <v>4101</v>
       </c>
-      <c r="K30" s="1">
+      <c r="K31" s="1">
         <v>1000</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L31" s="1">
         <f t="shared" si="2"/>
         <v>50000</v>
       </c>
-      <c r="M30" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:13">
-      <c r="C31" s="1">
+      <c r="M31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:13">
+      <c r="C32" s="1">
         <v>27</v>
       </c>
-      <c r="D31" s="1">
-        <v>1</v>
-      </c>
-      <c r="E31" s="1">
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
         <v>1000</v>
       </c>
-      <c r="F31" s="1">
-        <f>5*M28</f>
-        <v>5</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I31" s="1">
+      <c r="F32" s="1">
+        <f>5*M29</f>
+        <v>5</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I32" s="1">
         <v>15</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J32" s="1">
         <v>4014</v>
       </c>
-      <c r="K31" s="1">
+      <c r="K32" s="1">
         <v>100</v>
       </c>
-      <c r="L31" s="1">
+      <c r="L32" s="1">
         <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="M31" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:13">
-      <c r="C32" s="1">
+      <c r="M32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:13">
+      <c r="C33" s="1">
         <v>28</v>
       </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1">
         <v>500</v>
       </c>
-      <c r="F32" s="1">
-        <f>20*M28</f>
+      <c r="F33" s="1">
+        <f>20*M29</f>
         <v>20</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I32" s="1">
-        <v>5</v>
-      </c>
-      <c r="J32" s="1">
+      <c r="G33" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I33" s="1">
+        <v>5</v>
+      </c>
+      <c r="J33" s="1">
         <v>4012</v>
       </c>
-      <c r="K32" s="1">
+      <c r="K33" s="1">
         <v>200</v>
       </c>
-      <c r="L32" s="1">
+      <c r="L33" s="1">
         <f t="shared" si="2"/>
         <v>10000</v>
       </c>
-      <c r="M32" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:13">
-      <c r="C33" s="1">
-        <v>29</v>
-      </c>
-      <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1">
-        <v>5000</v>
-      </c>
-      <c r="F33" s="1">
-        <f>3*M28</f>
-        <v>3</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I33" s="1">
-        <v>5</v>
-      </c>
-      <c r="J33" s="1">
-        <v>4011</v>
-      </c>
-      <c r="K33" s="1">
-        <v>1</v>
-      </c>
-      <c r="L33" s="1">
-        <f t="shared" si="2"/>
-        <v>15000</v>
-      </c>
       <c r="M33" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:13">
       <c r="C34" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D34" s="1">
         <v>1</v>
       </c>
       <c r="E34" s="1">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="F34" s="1">
-        <f>10*M28</f>
-        <v>10</v>
+        <f>5*M29</f>
+        <v>5</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>73</v>
@@ -2325,14 +2327,14 @@
         <v>5</v>
       </c>
       <c r="J34" s="1">
-        <v>4102</v>
+        <v>4011</v>
       </c>
       <c r="K34" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L34" s="1">
         <f t="shared" si="2"/>
-        <v>5000</v>
+        <v>25000</v>
       </c>
       <c r="M34" s="1">
         <v>1</v>
@@ -2340,7 +2342,7 @@
     </row>
     <row r="35" customHeight="1" spans="3:13">
       <c r="C35" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D35" s="1">
         <v>1</v>
@@ -2349,8 +2351,8 @@
         <v>500</v>
       </c>
       <c r="F35" s="1">
-        <f>20*M28</f>
-        <v>20</v>
+        <f>10*M29</f>
+        <v>10</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>75</v>
@@ -2362,14 +2364,14 @@
         <v>5</v>
       </c>
       <c r="J35" s="1">
-        <v>4001</v>
+        <v>4102</v>
       </c>
       <c r="K35" s="1">
-        <v>1000000</v>
+        <v>20</v>
       </c>
       <c r="L35" s="1">
         <f t="shared" si="2"/>
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="M35" s="1">
         <v>1</v>
@@ -2377,7 +2379,7 @@
     </row>
     <row r="36" customHeight="1" spans="3:13">
       <c r="C36" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D36" s="1">
         <v>1</v>
@@ -2386,7 +2388,7 @@
         <v>500</v>
       </c>
       <c r="F36" s="1">
-        <f>20*M28</f>
+        <f>20*M29</f>
         <v>20</v>
       </c>
       <c r="G36" s="1" t="s">
@@ -2399,10 +2401,10 @@
         <v>5</v>
       </c>
       <c r="J36" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K36" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L36" s="1">
         <f t="shared" si="2"/>
@@ -2412,56 +2414,56 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="3:13">
-      <c r="C38" s="1">
-        <v>33</v>
-      </c>
-      <c r="D38" s="1">
-        <v>2</v>
-      </c>
-      <c r="E38" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F38" s="1">
-        <f>20*M38</f>
+    <row r="37" customHeight="1" spans="3:13">
+      <c r="C37" s="1">
+        <v>32</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+      <c r="E37" s="1">
+        <v>500</v>
+      </c>
+      <c r="F37" s="1">
+        <f>20*M29</f>
         <v>20</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I38" s="1">
-        <v>5</v>
-      </c>
-      <c r="J38" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K38" s="1">
-        <v>5</v>
-      </c>
-      <c r="L38" s="1">
-        <f t="shared" ref="L38:L73" si="3">E38*F38</f>
-        <v>20000</v>
-      </c>
-      <c r="M38" s="1">
+      <c r="G37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I37" s="1">
+        <v>5</v>
+      </c>
+      <c r="J37" s="1">
+        <v>4002</v>
+      </c>
+      <c r="K37" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="L37" s="1">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="M37" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:13">
       <c r="C39" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
       </c>
       <c r="E39" s="4">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="F39" s="1">
-        <f>300*M38</f>
-        <v>300</v>
+        <f>20*M39</f>
+        <v>20</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>63</v>
@@ -2473,180 +2475,180 @@
         <v>5</v>
       </c>
       <c r="J39" s="1">
+        <v>4010</v>
+      </c>
+      <c r="K39" s="1">
+        <v>5</v>
+      </c>
+      <c r="L39" s="1">
+        <f t="shared" ref="L39:L74" si="3">E39*F39</f>
+        <v>20000</v>
+      </c>
+      <c r="M39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:13">
+      <c r="C40" s="1">
+        <v>34</v>
+      </c>
+      <c r="D40" s="1">
+        <v>2</v>
+      </c>
+      <c r="E40" s="4">
+        <v>200</v>
+      </c>
+      <c r="F40" s="1">
+        <f>300*M39</f>
+        <v>300</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I40" s="1">
+        <v>5</v>
+      </c>
+      <c r="J40" s="1">
         <v>4007</v>
       </c>
-      <c r="K39" s="1">
+      <c r="K40" s="1">
         <v>1000</v>
       </c>
-      <c r="L39" s="1">
+      <c r="L40" s="1">
         <f t="shared" si="3"/>
         <v>60000</v>
       </c>
-      <c r="M39" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:13">
-      <c r="C40" s="1">
+      <c r="M40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:13">
+      <c r="C41" s="1">
         <v>35</v>
       </c>
-      <c r="D40" s="1">
+      <c r="D41" s="1">
         <v>2</v>
       </c>
-      <c r="E40" s="4">
+      <c r="E41" s="4">
         <v>200</v>
       </c>
-      <c r="F40" s="1">
-        <f>500*M38</f>
+      <c r="F41" s="1">
+        <f>500*M39</f>
         <v>500</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I40" s="1">
-        <v>5</v>
-      </c>
-      <c r="J40" s="1">
+      <c r="G41" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I41" s="1">
+        <v>5</v>
+      </c>
+      <c r="J41" s="1">
         <v>4101</v>
       </c>
-      <c r="K40" s="1">
+      <c r="K41" s="1">
         <v>1000</v>
       </c>
-      <c r="L40" s="1">
+      <c r="L41" s="1">
         <f t="shared" si="3"/>
         <v>100000</v>
       </c>
-      <c r="M40" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:13">
-      <c r="C41" s="1">
+      <c r="M41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:13">
+      <c r="C42" s="1">
         <v>36</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D42" s="1">
         <v>2</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E42" s="4">
         <v>2000</v>
       </c>
-      <c r="F41" s="1">
-        <f>5*M38</f>
-        <v>5</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I41" s="1">
+      <c r="F42" s="1">
+        <f>5*M39</f>
+        <v>5</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I42" s="1">
         <v>15</v>
       </c>
-      <c r="J41" s="1">
+      <c r="J42" s="1">
         <v>4014</v>
       </c>
-      <c r="K41" s="1">
+      <c r="K42" s="1">
         <v>100</v>
       </c>
-      <c r="L41" s="1">
+      <c r="L42" s="1">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
-      <c r="M41" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:13">
-      <c r="C42" s="1">
+      <c r="M42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:13">
+      <c r="C43" s="1">
         <v>37</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D43" s="1">
         <v>2</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E43" s="4">
         <v>1000</v>
       </c>
-      <c r="F42" s="1">
-        <f>20*M38</f>
+      <c r="F43" s="1">
+        <f>20*M39</f>
         <v>20</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I42" s="1">
-        <v>5</v>
-      </c>
-      <c r="J42" s="1">
+      <c r="G43" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I43" s="1">
+        <v>5</v>
+      </c>
+      <c r="J43" s="1">
         <v>4012</v>
       </c>
-      <c r="K42" s="1">
+      <c r="K43" s="1">
         <v>200</v>
       </c>
-      <c r="L42" s="1">
+      <c r="L43" s="1">
         <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="M42" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:13">
-      <c r="C43" s="1">
-        <v>38</v>
-      </c>
-      <c r="D43" s="1">
-        <v>2</v>
-      </c>
-      <c r="E43" s="4">
-        <v>10000</v>
-      </c>
-      <c r="F43" s="1">
-        <f>3*M38</f>
-        <v>3</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I43" s="1">
-        <v>5</v>
-      </c>
-      <c r="J43" s="1">
-        <v>4011</v>
-      </c>
-      <c r="K43" s="1">
-        <v>1</v>
-      </c>
-      <c r="L43" s="1">
-        <f t="shared" si="3"/>
-        <v>30000</v>
-      </c>
       <c r="M43" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:13">
       <c r="C44" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D44" s="1">
         <v>2</v>
       </c>
       <c r="E44" s="4">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="F44" s="1">
-        <f>10*M38</f>
-        <v>10</v>
+        <f>5*M39</f>
+        <v>5</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>73</v>
@@ -2658,14 +2660,14 @@
         <v>5</v>
       </c>
       <c r="J44" s="1">
-        <v>4102</v>
+        <v>4011</v>
       </c>
       <c r="K44" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L44" s="1">
         <f t="shared" si="3"/>
-        <v>10000</v>
+        <v>50000</v>
       </c>
       <c r="M44" s="1">
         <v>1</v>
@@ -2673,7 +2675,7 @@
     </row>
     <row r="45" customHeight="1" spans="3:13">
       <c r="C45" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D45" s="1">
         <v>2</v>
@@ -2682,8 +2684,8 @@
         <v>1000</v>
       </c>
       <c r="F45" s="1">
-        <f>20*M38</f>
-        <v>20</v>
+        <f>10*M39</f>
+        <v>10</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>75</v>
@@ -2695,14 +2697,14 @@
         <v>5</v>
       </c>
       <c r="J45" s="1">
-        <v>4001</v>
+        <v>4102</v>
       </c>
       <c r="K45" s="1">
-        <v>1000000</v>
+        <v>20</v>
       </c>
       <c r="L45" s="1">
         <f t="shared" si="3"/>
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="M45" s="1">
         <v>1</v>
@@ -2710,7 +2712,7 @@
     </row>
     <row r="46" customHeight="1" spans="3:13">
       <c r="C46" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D46" s="1">
         <v>2</v>
@@ -2719,7 +2721,7 @@
         <v>1000</v>
       </c>
       <c r="F46" s="1">
-        <f>20*M38</f>
+        <f>20*M39</f>
         <v>20</v>
       </c>
       <c r="G46" s="1" t="s">
@@ -2732,10 +2734,10 @@
         <v>5</v>
       </c>
       <c r="J46" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K46" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L46" s="1">
         <f t="shared" si="3"/>
@@ -2747,36 +2749,36 @@
     </row>
     <row r="47" customHeight="1" spans="3:13">
       <c r="C47" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D47" s="1">
-        <v>3</v>
-      </c>
-      <c r="E47" s="1">
-        <v>2000</v>
+        <v>2</v>
+      </c>
+      <c r="E47" s="4">
+        <v>1000</v>
       </c>
       <c r="F47" s="1">
-        <f>20*M47</f>
+        <f>20*M39</f>
         <v>20</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="I47" s="1">
         <v>5</v>
       </c>
       <c r="J47" s="1">
-        <v>4010</v>
+        <v>4002</v>
       </c>
       <c r="K47" s="1">
-        <v>5</v>
+        <v>6000000</v>
       </c>
       <c r="L47" s="1">
         <f t="shared" si="3"/>
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="M47" s="1">
         <v>1</v>
@@ -2784,17 +2786,17 @@
     </row>
     <row r="48" customHeight="1" spans="3:13">
       <c r="C48" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D48" s="1">
         <v>3</v>
       </c>
       <c r="E48" s="1">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="F48" s="1">
-        <f>300*M47</f>
-        <v>300</v>
+        <f>20*M48</f>
+        <v>20</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>63</v>
@@ -2806,14 +2808,14 @@
         <v>5</v>
       </c>
       <c r="J48" s="1">
-        <v>4007</v>
+        <v>4010</v>
       </c>
       <c r="K48" s="1">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L48" s="1">
         <f t="shared" si="3"/>
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="M48" s="1">
         <v>1</v>
@@ -2821,7 +2823,7 @@
     </row>
     <row r="49" customHeight="1" spans="3:13">
       <c r="C49" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D49" s="1">
         <v>3</v>
@@ -2830,8 +2832,8 @@
         <v>400</v>
       </c>
       <c r="F49" s="1">
-        <f>500*M47</f>
-        <v>500</v>
+        <f>300*M48</f>
+        <v>300</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>65</v>
@@ -2843,14 +2845,14 @@
         <v>5</v>
       </c>
       <c r="J49" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K49" s="1">
         <v>1000</v>
       </c>
       <c r="L49" s="1">
         <f t="shared" si="3"/>
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="M49" s="1">
         <v>1</v>
@@ -2858,17 +2860,17 @@
     </row>
     <row r="50" customHeight="1" spans="3:13">
       <c r="C50" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D50" s="1">
         <v>3</v>
       </c>
       <c r="E50" s="1">
-        <v>4000</v>
+        <v>400</v>
       </c>
       <c r="F50" s="1">
-        <f>5*M47</f>
-        <v>5</v>
+        <f>500*M48</f>
+        <v>500</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>67</v>
@@ -2877,17 +2879,17 @@
         <v>68</v>
       </c>
       <c r="I50" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J50" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="K50" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L50" s="1">
         <f t="shared" si="3"/>
-        <v>20000</v>
+        <v>200000</v>
       </c>
       <c r="M50" s="1">
         <v>1</v>
@@ -2895,17 +2897,17 @@
     </row>
     <row r="51" customHeight="1" spans="3:13">
       <c r="C51" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D51" s="1">
         <v>3</v>
       </c>
       <c r="E51" s="1">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="F51" s="1">
-        <f>20*M47</f>
-        <v>20</v>
+        <f>5*M48</f>
+        <v>5</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>69</v>
@@ -2914,17 +2916,17 @@
         <v>70</v>
       </c>
       <c r="I51" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J51" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="K51" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L51" s="1">
         <f t="shared" si="3"/>
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="M51" s="1">
         <v>1</v>
@@ -2932,17 +2934,17 @@
     </row>
     <row r="52" customHeight="1" spans="3:13">
       <c r="C52" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D52" s="1">
         <v>3</v>
       </c>
       <c r="E52" s="1">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="F52" s="1">
-        <f>3*M47</f>
-        <v>3</v>
+        <f>20*M48</f>
+        <v>20</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>71</v>
@@ -2954,14 +2956,14 @@
         <v>5</v>
       </c>
       <c r="J52" s="1">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="K52" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="L52" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>40000</v>
       </c>
       <c r="M52" s="1">
         <v>1</v>
@@ -2969,17 +2971,17 @@
     </row>
     <row r="53" customHeight="1" spans="3:13">
       <c r="C53" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D53" s="1">
         <v>3</v>
       </c>
       <c r="E53" s="1">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="F53" s="1">
-        <f>10*M47</f>
-        <v>10</v>
+        <f>5*M48</f>
+        <v>5</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>73</v>
@@ -2991,14 +2993,14 @@
         <v>5</v>
       </c>
       <c r="J53" s="1">
-        <v>4102</v>
+        <v>4011</v>
       </c>
       <c r="K53" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L53" s="1">
         <f t="shared" si="3"/>
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="M53" s="1">
         <v>1</v>
@@ -3006,7 +3008,7 @@
     </row>
     <row r="54" customHeight="1" spans="3:13">
       <c r="C54" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D54" s="1">
         <v>3</v>
@@ -3015,8 +3017,8 @@
         <v>2000</v>
       </c>
       <c r="F54" s="1">
-        <f>20*M47</f>
-        <v>20</v>
+        <f>10*M48</f>
+        <v>10</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>75</v>
@@ -3028,14 +3030,14 @@
         <v>5</v>
       </c>
       <c r="J54" s="1">
-        <v>4001</v>
+        <v>4102</v>
       </c>
       <c r="K54" s="1">
-        <v>1000000</v>
+        <v>20</v>
       </c>
       <c r="L54" s="1">
         <f t="shared" si="3"/>
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="M54" s="1">
         <v>1</v>
@@ -3043,7 +3045,7 @@
     </row>
     <row r="55" customHeight="1" spans="3:13">
       <c r="C55" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D55" s="1">
         <v>3</v>
@@ -3052,7 +3054,7 @@
         <v>2000</v>
       </c>
       <c r="F55" s="1">
-        <f>20*M47</f>
+        <f>20*M48</f>
         <v>20</v>
       </c>
       <c r="G55" s="1" t="s">
@@ -3065,10 +3067,10 @@
         <v>5</v>
       </c>
       <c r="J55" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K55" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L55" s="1">
         <f t="shared" si="3"/>
@@ -3080,36 +3082,36 @@
     </row>
     <row r="56" customHeight="1" spans="3:13">
       <c r="C56" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D56" s="1">
-        <v>4</v>
-      </c>
-      <c r="E56" s="4">
-        <v>3000</v>
+        <v>3</v>
+      </c>
+      <c r="E56" s="1">
+        <v>2000</v>
       </c>
       <c r="F56" s="1">
-        <f>20*M56</f>
+        <f>20*M48</f>
         <v>20</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="I56" s="1">
         <v>5</v>
       </c>
       <c r="J56" s="1">
-        <v>4010</v>
+        <v>4002</v>
       </c>
       <c r="K56" s="1">
-        <v>5</v>
+        <v>6000000</v>
       </c>
       <c r="L56" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>40000</v>
       </c>
       <c r="M56" s="1">
         <v>1</v>
@@ -3117,17 +3119,17 @@
     </row>
     <row r="57" customHeight="1" spans="3:13">
       <c r="C57" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D57" s="1">
         <v>4</v>
       </c>
       <c r="E57" s="4">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="F57" s="1">
-        <f>300*M56</f>
-        <v>300</v>
+        <f>20*M57</f>
+        <v>20</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>63</v>
@@ -3139,14 +3141,14 @@
         <v>5</v>
       </c>
       <c r="J57" s="1">
-        <v>4007</v>
+        <v>4010</v>
       </c>
       <c r="K57" s="1">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L57" s="1">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>60000</v>
       </c>
       <c r="M57" s="1">
         <v>1</v>
@@ -3154,7 +3156,7 @@
     </row>
     <row r="58" customHeight="1" spans="3:13">
       <c r="C58" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D58" s="1">
         <v>4</v>
@@ -3163,8 +3165,8 @@
         <v>600</v>
       </c>
       <c r="F58" s="1">
-        <f>500*M56</f>
-        <v>500</v>
+        <f>300*M57</f>
+        <v>300</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>65</v>
@@ -3176,14 +3178,14 @@
         <v>5</v>
       </c>
       <c r="J58" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K58" s="1">
         <v>1000</v>
       </c>
       <c r="L58" s="1">
         <f t="shared" si="3"/>
-        <v>300000</v>
+        <v>180000</v>
       </c>
       <c r="M58" s="1">
         <v>1</v>
@@ -3191,17 +3193,17 @@
     </row>
     <row r="59" customHeight="1" spans="3:13">
       <c r="C59" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D59" s="1">
         <v>4</v>
       </c>
       <c r="E59" s="4">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="F59" s="1">
-        <f>5*M56</f>
-        <v>5</v>
+        <f>500*M57</f>
+        <v>500</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>67</v>
@@ -3210,17 +3212,17 @@
         <v>68</v>
       </c>
       <c r="I59" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J59" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="K59" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L59" s="1">
         <f t="shared" si="3"/>
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="M59" s="1">
         <v>1</v>
@@ -3228,17 +3230,17 @@
     </row>
     <row r="60" customHeight="1" spans="3:13">
       <c r="C60" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D60" s="1">
         <v>4</v>
       </c>
       <c r="E60" s="4">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="F60" s="1">
-        <f>20*M56</f>
-        <v>20</v>
+        <f>5*M57</f>
+        <v>5</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>69</v>
@@ -3247,17 +3249,17 @@
         <v>70</v>
       </c>
       <c r="I60" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J60" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="K60" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L60" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="M60" s="1">
         <v>1</v>
@@ -3265,17 +3267,17 @@
     </row>
     <row r="61" customHeight="1" spans="3:13">
       <c r="C61" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D61" s="1">
         <v>4</v>
       </c>
       <c r="E61" s="4">
-        <v>30000</v>
+        <v>3000</v>
       </c>
       <c r="F61" s="1">
-        <f>3*M56</f>
-        <v>3</v>
+        <f>20*M57</f>
+        <v>20</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>71</v>
@@ -3287,14 +3289,14 @@
         <v>5</v>
       </c>
       <c r="J61" s="1">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="K61" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="L61" s="1">
         <f t="shared" si="3"/>
-        <v>90000</v>
+        <v>60000</v>
       </c>
       <c r="M61" s="1">
         <v>1</v>
@@ -3302,17 +3304,17 @@
     </row>
     <row r="62" customHeight="1" spans="3:13">
       <c r="C62" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D62" s="1">
         <v>4</v>
       </c>
       <c r="E62" s="4">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="F62" s="1">
-        <f>10*M56</f>
-        <v>10</v>
+        <f>5*M57</f>
+        <v>5</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>73</v>
@@ -3324,14 +3326,14 @@
         <v>5</v>
       </c>
       <c r="J62" s="1">
-        <v>4102</v>
+        <v>4011</v>
       </c>
       <c r="K62" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L62" s="1">
         <f t="shared" si="3"/>
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="M62" s="1">
         <v>1</v>
@@ -3339,7 +3341,7 @@
     </row>
     <row r="63" customHeight="1" spans="3:13">
       <c r="C63" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D63" s="1">
         <v>4</v>
@@ -3348,8 +3350,8 @@
         <v>3000</v>
       </c>
       <c r="F63" s="1">
-        <f>20*M56</f>
-        <v>20</v>
+        <f>10*M57</f>
+        <v>10</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>75</v>
@@ -3361,14 +3363,14 @@
         <v>5</v>
       </c>
       <c r="J63" s="1">
-        <v>4001</v>
+        <v>4102</v>
       </c>
       <c r="K63" s="1">
-        <v>1000000</v>
+        <v>20</v>
       </c>
       <c r="L63" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="M63" s="1">
         <v>1</v>
@@ -3376,7 +3378,7 @@
     </row>
     <row r="64" customHeight="1" spans="3:13">
       <c r="C64" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D64" s="1">
         <v>4</v>
@@ -3385,7 +3387,7 @@
         <v>3000</v>
       </c>
       <c r="F64" s="1">
-        <f>20*M56</f>
+        <f>20*M57</f>
         <v>20</v>
       </c>
       <c r="G64" s="1" t="s">
@@ -3398,10 +3400,10 @@
         <v>5</v>
       </c>
       <c r="J64" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K64" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L64" s="1">
         <f t="shared" si="3"/>
@@ -3413,54 +3415,54 @@
     </row>
     <row r="65" customHeight="1" spans="3:13">
       <c r="C65" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D65" s="1">
-        <v>5</v>
-      </c>
-      <c r="E65" s="1">
-        <v>4000</v>
+        <v>4</v>
+      </c>
+      <c r="E65" s="4">
+        <v>3000</v>
       </c>
       <c r="F65" s="1">
-        <f>20*M65</f>
+        <f>20*M57</f>
+        <v>20</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="I65" s="1">
         <v>5</v>
       </c>
       <c r="J65" s="1">
-        <v>4010</v>
+        <v>4002</v>
       </c>
       <c r="K65" s="1">
-        <v>5</v>
+        <v>6000000</v>
       </c>
       <c r="L65" s="1">
         <f t="shared" si="3"/>
-        <v>320000</v>
+        <v>60000</v>
       </c>
       <c r="M65" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:13">
       <c r="C66" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D66" s="1">
         <v>5</v>
       </c>
       <c r="E66" s="1">
-        <v>800</v>
+        <v>4000</v>
       </c>
       <c r="F66" s="1">
-        <f>300*M65</f>
-        <v>1200</v>
+        <f>20*M66</f>
+        <v>80</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>63</v>
@@ -3472,14 +3474,14 @@
         <v>5</v>
       </c>
       <c r="J66" s="1">
-        <v>4007</v>
+        <v>4010</v>
       </c>
       <c r="K66" s="1">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L66" s="1">
         <f t="shared" si="3"/>
-        <v>960000</v>
+        <v>320000</v>
       </c>
       <c r="M66" s="1">
         <v>4</v>
@@ -3487,7 +3489,7 @@
     </row>
     <row r="67" customHeight="1" spans="3:13">
       <c r="C67" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D67" s="1">
         <v>5</v>
@@ -3496,8 +3498,8 @@
         <v>800</v>
       </c>
       <c r="F67" s="1">
-        <f>500*M65</f>
-        <v>2000</v>
+        <f>300*M66</f>
+        <v>1200</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>65</v>
@@ -3509,14 +3511,14 @@
         <v>5</v>
       </c>
       <c r="J67" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K67" s="1">
         <v>1000</v>
       </c>
       <c r="L67" s="1">
         <f t="shared" si="3"/>
-        <v>1600000</v>
+        <v>960000</v>
       </c>
       <c r="M67" s="1">
         <v>4</v>
@@ -3524,17 +3526,17 @@
     </row>
     <row r="68" customHeight="1" spans="3:13">
       <c r="C68" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D68" s="1">
         <v>5</v>
       </c>
       <c r="E68" s="1">
-        <v>8000</v>
+        <v>800</v>
       </c>
       <c r="F68" s="1">
-        <f>5*M65</f>
-        <v>20</v>
+        <f>500*M66</f>
+        <v>2000</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>67</v>
@@ -3543,17 +3545,17 @@
         <v>68</v>
       </c>
       <c r="I68" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J68" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="K68" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L68" s="1">
         <f t="shared" si="3"/>
-        <v>160000</v>
+        <v>1600000</v>
       </c>
       <c r="M68" s="1">
         <v>4</v>
@@ -3561,17 +3563,17 @@
     </row>
     <row r="69" customHeight="1" spans="3:13">
       <c r="C69" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D69" s="1">
         <v>5</v>
       </c>
       <c r="E69" s="1">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="F69" s="1">
-        <f>20*M65</f>
-        <v>80</v>
+        <f>5*M66</f>
+        <v>20</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>69</v>
@@ -3580,17 +3582,17 @@
         <v>70</v>
       </c>
       <c r="I69" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J69" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="K69" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L69" s="1">
         <f t="shared" si="3"/>
-        <v>320000</v>
+        <v>160000</v>
       </c>
       <c r="M69" s="1">
         <v>4</v>
@@ -3598,17 +3600,17 @@
     </row>
     <row r="70" customHeight="1" spans="3:13">
       <c r="C70" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D70" s="1">
         <v>5</v>
       </c>
       <c r="E70" s="1">
-        <v>40000</v>
+        <v>4000</v>
       </c>
       <c r="F70" s="1">
-        <f>3*M65</f>
-        <v>12</v>
+        <f>20*M66</f>
+        <v>80</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>71</v>
@@ -3620,14 +3622,14 @@
         <v>5</v>
       </c>
       <c r="J70" s="1">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="K70" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="L70" s="1">
         <f t="shared" si="3"/>
-        <v>480000</v>
+        <v>320000</v>
       </c>
       <c r="M70" s="1">
         <v>4</v>
@@ -3635,17 +3637,17 @@
     </row>
     <row r="71" customHeight="1" spans="3:13">
       <c r="C71" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D71" s="1">
         <v>5</v>
       </c>
       <c r="E71" s="1">
-        <v>4000</v>
+        <v>40000</v>
       </c>
       <c r="F71" s="1">
-        <f>10*M65</f>
-        <v>40</v>
+        <f>5*M66</f>
+        <v>20</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>73</v>
@@ -3657,14 +3659,14 @@
         <v>5</v>
       </c>
       <c r="J71" s="1">
-        <v>4102</v>
+        <v>4011</v>
       </c>
       <c r="K71" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L71" s="1">
         <f t="shared" si="3"/>
-        <v>160000</v>
+        <v>800000</v>
       </c>
       <c r="M71" s="1">
         <v>4</v>
@@ -3672,7 +3674,7 @@
     </row>
     <row r="72" customHeight="1" spans="3:13">
       <c r="C72" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D72" s="1">
         <v>5</v>
@@ -3681,8 +3683,8 @@
         <v>4000</v>
       </c>
       <c r="F72" s="1">
-        <f>20*M65</f>
-        <v>80</v>
+        <f>10*M66</f>
+        <v>40</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>75</v>
@@ -3694,14 +3696,14 @@
         <v>5</v>
       </c>
       <c r="J72" s="1">
-        <v>4001</v>
+        <v>4102</v>
       </c>
       <c r="K72" s="1">
-        <v>1000000</v>
+        <v>20</v>
       </c>
       <c r="L72" s="1">
         <f t="shared" si="3"/>
-        <v>320000</v>
+        <v>160000</v>
       </c>
       <c r="M72" s="1">
         <v>4</v>
@@ -3709,7 +3711,7 @@
     </row>
     <row r="73" customHeight="1" spans="3:13">
       <c r="C73" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D73" s="1">
         <v>5</v>
@@ -3718,7 +3720,7 @@
         <v>4000</v>
       </c>
       <c r="F73" s="1">
-        <f>20*M65</f>
+        <f>20*M66</f>
         <v>80</v>
       </c>
       <c r="G73" s="1" t="s">
@@ -3731,10 +3733,10 @@
         <v>5</v>
       </c>
       <c r="J73" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K73" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L73" s="1">
         <f t="shared" si="3"/>
@@ -3744,36 +3746,73 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="3:12">
-      <c r="C76" s="1">
+    <row r="74" customHeight="1" spans="3:13">
+      <c r="C74" s="1">
+        <v>68</v>
+      </c>
+      <c r="D74" s="1">
+        <v>5</v>
+      </c>
+      <c r="E74" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F74" s="1">
+        <f>20*M66</f>
+        <v>80</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I74" s="1">
+        <v>5</v>
+      </c>
+      <c r="J74" s="1">
+        <v>4002</v>
+      </c>
+      <c r="K74" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="L74" s="1">
+        <f t="shared" si="3"/>
+        <v>320000</v>
+      </c>
+      <c r="M74" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:12">
+      <c r="C77" s="1">
         <v>99</v>
       </c>
-      <c r="D76" s="1">
+      <c r="D77" s="1">
         <v>0</v>
       </c>
-      <c r="E76" s="6" t="s">
+      <c r="E77" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F77" s="1">
         <v>100</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I76" s="1">
-        <v>5</v>
-      </c>
-      <c r="J76" s="1">
+      <c r="G77" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I77" s="1">
+        <v>5</v>
+      </c>
+      <c r="J77" s="1">
         <v>4006</v>
       </c>
-      <c r="K76" s="1">
+      <c r="K77" s="1">
         <v>1000</v>
       </c>
-      <c r="L76" s="1">
-        <f>E76*F76</f>
+      <c r="L77" s="1">
+        <f>E77*F77</f>
         <v>100000</v>
       </c>
     </row>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="84">
   <si>
     <t>#</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>法宝自选</t>
+  </si>
+  <si>
+    <t>300000</t>
   </si>
   <si>
     <t>兑换魂骨自选*1</t>
@@ -2093,16 +2096,16 @@
         <v>0</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F27" s="1">
         <v>1</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I27" s="1">
         <v>4</v>
@@ -2115,7 +2118,7 @@
       </c>
       <c r="L27" s="1">
         <f t="shared" si="1"/>
-        <v>200000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:13">
@@ -2133,10 +2136,10 @@
         <v>20</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I29" s="1">
         <v>5</v>
@@ -2170,10 +2173,10 @@
         <v>300</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I30" s="1">
         <v>5</v>
@@ -2207,10 +2210,10 @@
         <v>500</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I31" s="1">
         <v>5</v>
@@ -2244,10 +2247,10 @@
         <v>5</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I32" s="1">
         <v>15</v>
@@ -2281,10 +2284,10 @@
         <v>20</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I33" s="1">
         <v>5</v>
@@ -2318,10 +2321,10 @@
         <v>5</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I34" s="1">
         <v>5</v>
@@ -2355,10 +2358,10 @@
         <v>10</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I35" s="1">
         <v>5</v>
@@ -2388,14 +2391,14 @@
         <v>500</v>
       </c>
       <c r="F36" s="1">
-        <f>20*M29</f>
-        <v>20</v>
+        <f>40*M29</f>
+        <v>40</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I36" s="1">
         <v>5</v>
@@ -2408,7 +2411,7 @@
       </c>
       <c r="L36" s="1">
         <f t="shared" si="2"/>
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="M36" s="1">
         <v>1</v>
@@ -2425,14 +2428,14 @@
         <v>500</v>
       </c>
       <c r="F37" s="1">
-        <f>20*M29</f>
-        <v>20</v>
+        <f>40*M29</f>
+        <v>40</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I37" s="1">
         <v>5</v>
@@ -2445,7 +2448,7 @@
       </c>
       <c r="L37" s="1">
         <f t="shared" si="2"/>
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="M37" s="1">
         <v>1</v>
@@ -2466,10 +2469,10 @@
         <v>20</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I39" s="1">
         <v>5</v>
@@ -2503,10 +2506,10 @@
         <v>300</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I40" s="1">
         <v>5</v>
@@ -2540,10 +2543,10 @@
         <v>500</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I41" s="1">
         <v>5</v>
@@ -2577,10 +2580,10 @@
         <v>5</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I42" s="1">
         <v>15</v>
@@ -2614,10 +2617,10 @@
         <v>20</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I43" s="1">
         <v>5</v>
@@ -2651,10 +2654,10 @@
         <v>5</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I44" s="1">
         <v>5</v>
@@ -2688,10 +2691,10 @@
         <v>10</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I45" s="1">
         <v>5</v>
@@ -2721,14 +2724,14 @@
         <v>1000</v>
       </c>
       <c r="F46" s="1">
-        <f>20*M39</f>
-        <v>20</v>
+        <f>40*M39</f>
+        <v>40</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I46" s="1">
         <v>5</v>
@@ -2741,7 +2744,7 @@
       </c>
       <c r="L46" s="1">
         <f t="shared" si="3"/>
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="M46" s="1">
         <v>1</v>
@@ -2758,14 +2761,14 @@
         <v>1000</v>
       </c>
       <c r="F47" s="1">
-        <f>20*M39</f>
-        <v>20</v>
+        <f>40*M39</f>
+        <v>40</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I47" s="1">
         <v>5</v>
@@ -2778,7 +2781,7 @@
       </c>
       <c r="L47" s="1">
         <f t="shared" si="3"/>
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="M47" s="1">
         <v>1</v>
@@ -2799,10 +2802,10 @@
         <v>20</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I48" s="1">
         <v>5</v>
@@ -2836,10 +2839,10 @@
         <v>300</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I49" s="1">
         <v>5</v>
@@ -2873,10 +2876,10 @@
         <v>500</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I50" s="1">
         <v>5</v>
@@ -2910,10 +2913,10 @@
         <v>5</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I51" s="1">
         <v>15</v>
@@ -2947,10 +2950,10 @@
         <v>20</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I52" s="1">
         <v>5</v>
@@ -2984,10 +2987,10 @@
         <v>5</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I53" s="1">
         <v>5</v>
@@ -3021,10 +3024,10 @@
         <v>10</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I54" s="1">
         <v>5</v>
@@ -3054,14 +3057,14 @@
         <v>2000</v>
       </c>
       <c r="F55" s="1">
-        <f>20*M48</f>
-        <v>20</v>
+        <f>40*M48</f>
+        <v>40</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I55" s="1">
         <v>5</v>
@@ -3074,7 +3077,7 @@
       </c>
       <c r="L55" s="1">
         <f t="shared" si="3"/>
-        <v>40000</v>
+        <v>80000</v>
       </c>
       <c r="M55" s="1">
         <v>1</v>
@@ -3091,14 +3094,14 @@
         <v>2000</v>
       </c>
       <c r="F56" s="1">
-        <f>20*M48</f>
-        <v>20</v>
+        <f>40*M48</f>
+        <v>40</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I56" s="1">
         <v>5</v>
@@ -3111,7 +3114,7 @@
       </c>
       <c r="L56" s="1">
         <f t="shared" si="3"/>
-        <v>40000</v>
+        <v>80000</v>
       </c>
       <c r="M56" s="1">
         <v>1</v>
@@ -3132,10 +3135,10 @@
         <v>20</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I57" s="1">
         <v>5</v>
@@ -3169,10 +3172,10 @@
         <v>300</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I58" s="1">
         <v>5</v>
@@ -3206,10 +3209,10 @@
         <v>500</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I59" s="1">
         <v>5</v>
@@ -3243,10 +3246,10 @@
         <v>5</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I60" s="1">
         <v>15</v>
@@ -3280,10 +3283,10 @@
         <v>20</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I61" s="1">
         <v>5</v>
@@ -3317,10 +3320,10 @@
         <v>5</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I62" s="1">
         <v>5</v>
@@ -3354,10 +3357,10 @@
         <v>10</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I63" s="1">
         <v>5</v>
@@ -3387,14 +3390,14 @@
         <v>3000</v>
       </c>
       <c r="F64" s="1">
-        <f>20*M57</f>
-        <v>20</v>
+        <f>40*M57</f>
+        <v>40</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I64" s="1">
         <v>5</v>
@@ -3407,7 +3410,7 @@
       </c>
       <c r="L64" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>120000</v>
       </c>
       <c r="M64" s="1">
         <v>1</v>
@@ -3424,14 +3427,14 @@
         <v>3000</v>
       </c>
       <c r="F65" s="1">
-        <f>20*M57</f>
-        <v>20</v>
+        <f>40*M57</f>
+        <v>40</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I65" s="1">
         <v>5</v>
@@ -3444,7 +3447,7 @@
       </c>
       <c r="L65" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>120000</v>
       </c>
       <c r="M65" s="1">
         <v>1</v>
@@ -3465,10 +3468,10 @@
         <v>80</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I66" s="1">
         <v>5</v>
@@ -3502,10 +3505,10 @@
         <v>1200</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I67" s="1">
         <v>5</v>
@@ -3539,10 +3542,10 @@
         <v>2000</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I68" s="1">
         <v>5</v>
@@ -3576,10 +3579,10 @@
         <v>20</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I69" s="1">
         <v>15</v>
@@ -3613,10 +3616,10 @@
         <v>80</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I70" s="1">
         <v>5</v>
@@ -3650,10 +3653,10 @@
         <v>20</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I71" s="1">
         <v>5</v>
@@ -3687,10 +3690,10 @@
         <v>40</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I72" s="1">
         <v>5</v>
@@ -3720,14 +3723,14 @@
         <v>4000</v>
       </c>
       <c r="F73" s="1">
-        <f>20*M66</f>
-        <v>80</v>
+        <f>40*M66</f>
+        <v>160</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I73" s="1">
         <v>5</v>
@@ -3740,7 +3743,7 @@
       </c>
       <c r="L73" s="1">
         <f t="shared" si="3"/>
-        <v>320000</v>
+        <v>640000</v>
       </c>
       <c r="M73" s="1">
         <v>4</v>
@@ -3757,14 +3760,14 @@
         <v>4000</v>
       </c>
       <c r="F74" s="1">
-        <f>20*M66</f>
+        <f>40*M66</f>
+        <v>160</v>
+      </c>
+      <c r="G74" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G74" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="H74" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I74" s="1">
         <v>5</v>
@@ -3777,7 +3780,7 @@
       </c>
       <c r="L74" s="1">
         <f t="shared" si="3"/>
-        <v>320000</v>
+        <v>640000</v>
       </c>
       <c r="M74" s="1">
         <v>4</v>
@@ -3797,10 +3800,10 @@
         <v>100</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I77" s="1">
         <v>5</v>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="87">
   <si>
     <t>#</t>
   </si>
@@ -219,6 +219,15 @@
   </si>
   <si>
     <t>魂骨自选</t>
+  </si>
+  <si>
+    <t>500000</t>
+  </si>
+  <si>
+    <t>兑换极法宝自选*1</t>
+  </si>
+  <si>
+    <t>极法宝自选</t>
   </si>
   <si>
     <t>兑换专属之心*5</t>
@@ -1289,7 +1298,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M77"/>
+  <dimension ref="C1:M78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1556,7 +1565,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" ref="L10:L27" si="1">E10*F10</f>
+        <f t="shared" ref="L10:L28" si="1">E10*F10</f>
         <v>24000</v>
       </c>
     </row>
@@ -2121,305 +2130,301 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="3:13">
-      <c r="C29" s="1">
-        <v>24</v>
-      </c>
-      <c r="D29" s="1">
-        <v>1</v>
-      </c>
-      <c r="E29" s="1">
-        <v>500</v>
-      </c>
-      <c r="F29" s="1">
-        <f>20*M29</f>
-        <v>20</v>
-      </c>
-      <c r="G29" s="1" t="s">
+    <row r="28" customHeight="1" spans="3:12">
+      <c r="C28" s="1">
+        <v>23</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I29" s="1">
-        <v>5</v>
-      </c>
-      <c r="J29" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K29" s="1">
-        <v>5</v>
-      </c>
-      <c r="L29" s="1">
-        <f t="shared" ref="L29:L37" si="2">E29*F29</f>
-        <v>10000</v>
-      </c>
-      <c r="M29" s="1">
-        <v>1</v>
+      <c r="H28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I28" s="1">
+        <v>4</v>
+      </c>
+      <c r="J28" s="1">
+        <v>30</v>
+      </c>
+      <c r="K28" s="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1">
+        <f t="shared" si="1"/>
+        <v>500000</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:13">
       <c r="C30" s="1">
+        <v>24</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1">
+        <v>500</v>
+      </c>
+      <c r="F30" s="1">
+        <f>20*M30</f>
+        <v>20</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I30" s="1">
+        <v>5</v>
+      </c>
+      <c r="J30" s="1">
+        <v>4010</v>
+      </c>
+      <c r="K30" s="1">
+        <v>5</v>
+      </c>
+      <c r="L30" s="1">
+        <f t="shared" ref="L30:L38" si="2">E30*F30</f>
+        <v>10000</v>
+      </c>
+      <c r="M30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:13">
+      <c r="C31" s="1">
         <v>25</v>
       </c>
-      <c r="D30" s="1">
-        <v>1</v>
-      </c>
-      <c r="E30" s="1">
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1">
         <v>100</v>
       </c>
-      <c r="F30" s="1">
-        <f>300*M29</f>
+      <c r="F31" s="1">
+        <f>300*M30</f>
         <v>300</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I30" s="1">
-        <v>5</v>
-      </c>
-      <c r="J30" s="1">
+      <c r="G31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I31" s="1">
+        <v>5</v>
+      </c>
+      <c r="J31" s="1">
         <v>4007</v>
       </c>
-      <c r="K30" s="1">
+      <c r="K31" s="1">
         <v>1000</v>
       </c>
-      <c r="L30" s="1">
+      <c r="L31" s="1">
         <f t="shared" si="2"/>
         <v>30000</v>
       </c>
-      <c r="M30" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:13">
-      <c r="C31" s="1">
+      <c r="M31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:13">
+      <c r="C32" s="1">
         <v>26</v>
       </c>
-      <c r="D31" s="1">
-        <v>1</v>
-      </c>
-      <c r="E31" s="1">
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
         <v>100</v>
       </c>
-      <c r="F31" s="1">
-        <f>500*M29</f>
+      <c r="F32" s="1">
+        <f>500*M30</f>
         <v>500</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I31" s="1">
-        <v>5</v>
-      </c>
-      <c r="J31" s="1">
+      <c r="G32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I32" s="1">
+        <v>5</v>
+      </c>
+      <c r="J32" s="1">
         <v>4101</v>
       </c>
-      <c r="K31" s="1">
+      <c r="K32" s="1">
         <v>1000</v>
       </c>
-      <c r="L31" s="1">
+      <c r="L32" s="1">
         <f t="shared" si="2"/>
         <v>50000</v>
       </c>
-      <c r="M31" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:13">
-      <c r="C32" s="1">
+      <c r="M32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:13">
+      <c r="C33" s="1">
         <v>27</v>
       </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1">
         <v>1000</v>
       </c>
-      <c r="F32" s="1">
-        <f>5*M29</f>
-        <v>5</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I32" s="1">
+      <c r="F33" s="1">
+        <f>5*M30</f>
+        <v>5</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I33" s="1">
         <v>15</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J33" s="1">
         <v>4014</v>
       </c>
-      <c r="K32" s="1">
+      <c r="K33" s="1">
         <v>100</v>
       </c>
-      <c r="L32" s="1">
+      <c r="L33" s="1">
         <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="M32" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:13">
-      <c r="C33" s="1">
+      <c r="M33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:13">
+      <c r="C34" s="1">
         <v>28</v>
       </c>
-      <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1">
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+      <c r="E34" s="1">
         <v>500</v>
       </c>
-      <c r="F33" s="1">
-        <f>20*M29</f>
+      <c r="F34" s="1">
+        <f>20*M30</f>
         <v>20</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I33" s="1">
-        <v>5</v>
-      </c>
-      <c r="J33" s="1">
+      <c r="G34" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I34" s="1">
+        <v>5</v>
+      </c>
+      <c r="J34" s="1">
         <v>4012</v>
       </c>
-      <c r="K33" s="1">
+      <c r="K34" s="1">
         <v>200</v>
       </c>
-      <c r="L33" s="1">
+      <c r="L34" s="1">
         <f t="shared" si="2"/>
         <v>10000</v>
       </c>
-      <c r="M33" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:13">
-      <c r="C34" s="1">
+      <c r="M34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:13">
+      <c r="C35" s="1">
         <v>29</v>
       </c>
-      <c r="D34" s="1">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1">
+      <c r="D35" s="1">
+        <v>1</v>
+      </c>
+      <c r="E35" s="1">
         <v>5000</v>
       </c>
-      <c r="F34" s="1">
-        <f>5*M29</f>
-        <v>5</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I34" s="1">
-        <v>5</v>
-      </c>
-      <c r="J34" s="1">
+      <c r="F35" s="1">
+        <f>5*M30</f>
+        <v>5</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I35" s="1">
+        <v>5</v>
+      </c>
+      <c r="J35" s="1">
         <v>4011</v>
       </c>
-      <c r="K34" s="1">
-        <v>1</v>
-      </c>
-      <c r="L34" s="1">
+      <c r="K35" s="1">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1">
         <f t="shared" si="2"/>
         <v>25000</v>
       </c>
-      <c r="M34" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:13">
-      <c r="C35" s="1">
+      <c r="M35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:13">
+      <c r="C36" s="1">
         <v>30</v>
       </c>
-      <c r="D35" s="1">
-        <v>1</v>
-      </c>
-      <c r="E35" s="1">
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1">
         <v>500</v>
       </c>
-      <c r="F35" s="1">
-        <f>10*M29</f>
+      <c r="F36" s="1">
+        <f>10*M30</f>
         <v>10</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I35" s="1">
-        <v>5</v>
-      </c>
-      <c r="J35" s="1">
+      <c r="G36" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I36" s="1">
+        <v>5</v>
+      </c>
+      <c r="J36" s="1">
         <v>4102</v>
       </c>
-      <c r="K35" s="1">
+      <c r="K36" s="1">
         <v>20</v>
       </c>
-      <c r="L35" s="1">
+      <c r="L36" s="1">
         <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="M35" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:13">
-      <c r="C36" s="1">
-        <v>31</v>
-      </c>
-      <c r="D36" s="1">
-        <v>1</v>
-      </c>
-      <c r="E36" s="1">
-        <v>500</v>
-      </c>
-      <c r="F36" s="1">
-        <f>40*M29</f>
-        <v>40</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I36" s="1">
-        <v>5</v>
-      </c>
-      <c r="J36" s="1">
-        <v>4001</v>
-      </c>
-      <c r="K36" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="L36" s="1">
-        <f t="shared" si="2"/>
-        <v>20000</v>
-      </c>
       <c r="M36" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:13">
       <c r="C37" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D37" s="1">
         <v>1</v>
@@ -2428,23 +2433,23 @@
         <v>500</v>
       </c>
       <c r="F37" s="1">
-        <f>40*M29</f>
+        <f>40*M30</f>
         <v>40</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I37" s="1">
         <v>5</v>
       </c>
       <c r="J37" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K37" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L37" s="1">
         <f t="shared" si="2"/>
@@ -2454,305 +2459,305 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="3:13">
-      <c r="C39" s="1">
-        <v>33</v>
-      </c>
-      <c r="D39" s="1">
-        <v>2</v>
-      </c>
-      <c r="E39" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F39" s="1">
-        <f>20*M39</f>
-        <v>20</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I39" s="1">
-        <v>5</v>
-      </c>
-      <c r="J39" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K39" s="1">
-        <v>5</v>
-      </c>
-      <c r="L39" s="1">
-        <f t="shared" ref="L39:L74" si="3">E39*F39</f>
+    <row r="38" customHeight="1" spans="3:13">
+      <c r="C38" s="1">
+        <v>32</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
+        <v>500</v>
+      </c>
+      <c r="F38" s="1">
+        <f>40*M30</f>
+        <v>40</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I38" s="1">
+        <v>5</v>
+      </c>
+      <c r="J38" s="1">
+        <v>4002</v>
+      </c>
+      <c r="K38" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="L38" s="1">
+        <f t="shared" si="2"/>
         <v>20000</v>
       </c>
-      <c r="M39" s="1">
+      <c r="M38" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:13">
       <c r="C40" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D40" s="1">
         <v>2</v>
       </c>
       <c r="E40" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F40" s="1">
+        <f>20*M40</f>
+        <v>20</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I40" s="1">
+        <v>5</v>
+      </c>
+      <c r="J40" s="1">
+        <v>4010</v>
+      </c>
+      <c r="K40" s="1">
+        <v>5</v>
+      </c>
+      <c r="L40" s="1">
+        <f t="shared" ref="L40:L75" si="3">E40*F40</f>
+        <v>20000</v>
+      </c>
+      <c r="M40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:13">
+      <c r="C41" s="1">
+        <v>34</v>
+      </c>
+      <c r="D41" s="1">
+        <v>2</v>
+      </c>
+      <c r="E41" s="4">
         <v>200</v>
       </c>
-      <c r="F40" s="1">
-        <f>300*M39</f>
+      <c r="F41" s="1">
+        <f>300*M40</f>
         <v>300</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I40" s="1">
-        <v>5</v>
-      </c>
-      <c r="J40" s="1">
+      <c r="G41" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I41" s="1">
+        <v>5</v>
+      </c>
+      <c r="J41" s="1">
         <v>4007</v>
       </c>
-      <c r="K40" s="1">
+      <c r="K41" s="1">
         <v>1000</v>
       </c>
-      <c r="L40" s="1">
+      <c r="L41" s="1">
         <f t="shared" si="3"/>
         <v>60000</v>
       </c>
-      <c r="M40" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:13">
-      <c r="C41" s="1">
+      <c r="M41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:13">
+      <c r="C42" s="1">
         <v>35</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D42" s="1">
         <v>2</v>
       </c>
-      <c r="E41" s="4">
+      <c r="E42" s="4">
         <v>200</v>
       </c>
-      <c r="F41" s="1">
-        <f>500*M39</f>
+      <c r="F42" s="1">
+        <f>500*M40</f>
         <v>500</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I41" s="1">
-        <v>5</v>
-      </c>
-      <c r="J41" s="1">
+      <c r="G42" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I42" s="1">
+        <v>5</v>
+      </c>
+      <c r="J42" s="1">
         <v>4101</v>
       </c>
-      <c r="K41" s="1">
+      <c r="K42" s="1">
         <v>1000</v>
       </c>
-      <c r="L41" s="1">
+      <c r="L42" s="1">
         <f t="shared" si="3"/>
         <v>100000</v>
       </c>
-      <c r="M41" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:13">
-      <c r="C42" s="1">
+      <c r="M42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:13">
+      <c r="C43" s="1">
         <v>36</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D43" s="1">
         <v>2</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E43" s="4">
         <v>2000</v>
       </c>
-      <c r="F42" s="1">
-        <f>5*M39</f>
-        <v>5</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I42" s="1">
+      <c r="F43" s="1">
+        <f>5*M40</f>
+        <v>5</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I43" s="1">
         <v>15</v>
       </c>
-      <c r="J42" s="1">
+      <c r="J43" s="1">
         <v>4014</v>
       </c>
-      <c r="K42" s="1">
+      <c r="K43" s="1">
         <v>100</v>
       </c>
-      <c r="L42" s="1">
+      <c r="L43" s="1">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
-      <c r="M42" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:13">
-      <c r="C43" s="1">
+      <c r="M43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:13">
+      <c r="C44" s="1">
         <v>37</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D44" s="1">
         <v>2</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E44" s="4">
         <v>1000</v>
       </c>
-      <c r="F43" s="1">
-        <f>20*M39</f>
+      <c r="F44" s="1">
+        <f>20*M40</f>
         <v>20</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I43" s="1">
-        <v>5</v>
-      </c>
-      <c r="J43" s="1">
+      <c r="G44" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I44" s="1">
+        <v>5</v>
+      </c>
+      <c r="J44" s="1">
         <v>4012</v>
       </c>
-      <c r="K43" s="1">
+      <c r="K44" s="1">
         <v>200</v>
       </c>
-      <c r="L43" s="1">
+      <c r="L44" s="1">
         <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="M43" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:13">
-      <c r="C44" s="1">
+      <c r="M44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:13">
+      <c r="C45" s="1">
         <v>38</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D45" s="1">
         <v>2</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E45" s="4">
         <v>10000</v>
       </c>
-      <c r="F44" s="1">
-        <f>5*M39</f>
-        <v>5</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I44" s="1">
-        <v>5</v>
-      </c>
-      <c r="J44" s="1">
+      <c r="F45" s="1">
+        <f>5*M40</f>
+        <v>5</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I45" s="1">
+        <v>5</v>
+      </c>
+      <c r="J45" s="1">
         <v>4011</v>
       </c>
-      <c r="K44" s="1">
-        <v>1</v>
-      </c>
-      <c r="L44" s="1">
+      <c r="K45" s="1">
+        <v>1</v>
+      </c>
+      <c r="L45" s="1">
         <f t="shared" si="3"/>
         <v>50000</v>
       </c>
-      <c r="M44" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:13">
-      <c r="C45" s="1">
+      <c r="M45" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:13">
+      <c r="C46" s="1">
         <v>39</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D46" s="1">
         <v>2</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E46" s="4">
         <v>1000</v>
       </c>
-      <c r="F45" s="1">
-        <f>10*M39</f>
+      <c r="F46" s="1">
+        <f>10*M40</f>
         <v>10</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I45" s="1">
-        <v>5</v>
-      </c>
-      <c r="J45" s="1">
+      <c r="G46" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I46" s="1">
+        <v>5</v>
+      </c>
+      <c r="J46" s="1">
         <v>4102</v>
       </c>
-      <c r="K45" s="1">
+      <c r="K46" s="1">
         <v>20</v>
       </c>
-      <c r="L45" s="1">
+      <c r="L46" s="1">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
-      <c r="M45" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:13">
-      <c r="C46" s="1">
-        <v>40</v>
-      </c>
-      <c r="D46" s="1">
-        <v>2</v>
-      </c>
-      <c r="E46" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F46" s="1">
-        <f>40*M39</f>
-        <v>40</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I46" s="1">
-        <v>5</v>
-      </c>
-      <c r="J46" s="1">
-        <v>4001</v>
-      </c>
-      <c r="K46" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="L46" s="1">
-        <f t="shared" si="3"/>
-        <v>40000</v>
-      </c>
       <c r="M46" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:13">
       <c r="C47" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D47" s="1">
         <v>2</v>
@@ -2761,23 +2766,23 @@
         <v>1000</v>
       </c>
       <c r="F47" s="1">
-        <f>40*M39</f>
+        <f>40*M40</f>
         <v>40</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I47" s="1">
         <v>5</v>
       </c>
       <c r="J47" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K47" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L47" s="1">
         <f t="shared" si="3"/>
@@ -2789,32 +2794,32 @@
     </row>
     <row r="48" customHeight="1" spans="3:13">
       <c r="C48" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D48" s="1">
-        <v>3</v>
-      </c>
-      <c r="E48" s="1">
-        <v>2000</v>
+        <v>2</v>
+      </c>
+      <c r="E48" s="4">
+        <v>1000</v>
       </c>
       <c r="F48" s="1">
-        <f>20*M48</f>
-        <v>20</v>
+        <f>40*M40</f>
+        <v>40</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="I48" s="1">
         <v>5</v>
       </c>
       <c r="J48" s="1">
-        <v>4010</v>
+        <v>4002</v>
       </c>
       <c r="K48" s="1">
-        <v>5</v>
+        <v>6000000</v>
       </c>
       <c r="L48" s="1">
         <f t="shared" si="3"/>
@@ -2826,36 +2831,36 @@
     </row>
     <row r="49" customHeight="1" spans="3:13">
       <c r="C49" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D49" s="1">
         <v>3</v>
       </c>
       <c r="E49" s="1">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="F49" s="1">
-        <f>300*M48</f>
-        <v>300</v>
+        <f>20*M49</f>
+        <v>20</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I49" s="1">
         <v>5</v>
       </c>
       <c r="J49" s="1">
-        <v>4007</v>
+        <v>4010</v>
       </c>
       <c r="K49" s="1">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L49" s="1">
         <f t="shared" si="3"/>
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="M49" s="1">
         <v>1</v>
@@ -2863,7 +2868,7 @@
     </row>
     <row r="50" customHeight="1" spans="3:13">
       <c r="C50" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D50" s="1">
         <v>3</v>
@@ -2872,27 +2877,27 @@
         <v>400</v>
       </c>
       <c r="F50" s="1">
-        <f>500*M48</f>
-        <v>500</v>
+        <f>300*M49</f>
+        <v>300</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I50" s="1">
         <v>5</v>
       </c>
       <c r="J50" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K50" s="1">
         <v>1000</v>
       </c>
       <c r="L50" s="1">
         <f t="shared" si="3"/>
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="M50" s="1">
         <v>1</v>
@@ -2900,36 +2905,36 @@
     </row>
     <row r="51" customHeight="1" spans="3:13">
       <c r="C51" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D51" s="1">
         <v>3</v>
       </c>
       <c r="E51" s="1">
-        <v>4000</v>
+        <v>400</v>
       </c>
       <c r="F51" s="1">
-        <f>5*M48</f>
-        <v>5</v>
+        <f>500*M49</f>
+        <v>500</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I51" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J51" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="K51" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L51" s="1">
         <f t="shared" si="3"/>
-        <v>20000</v>
+        <v>200000</v>
       </c>
       <c r="M51" s="1">
         <v>1</v>
@@ -2937,36 +2942,36 @@
     </row>
     <row r="52" customHeight="1" spans="3:13">
       <c r="C52" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D52" s="1">
         <v>3</v>
       </c>
       <c r="E52" s="1">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="F52" s="1">
-        <f>20*M48</f>
-        <v>20</v>
+        <f>5*M49</f>
+        <v>5</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I52" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J52" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="K52" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L52" s="1">
         <f t="shared" si="3"/>
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="M52" s="1">
         <v>1</v>
@@ -2974,36 +2979,36 @@
     </row>
     <row r="53" customHeight="1" spans="3:13">
       <c r="C53" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D53" s="1">
         <v>3</v>
       </c>
       <c r="E53" s="1">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="F53" s="1">
-        <f>5*M48</f>
-        <v>5</v>
+        <f>20*M49</f>
+        <v>20</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I53" s="1">
         <v>5</v>
       </c>
       <c r="J53" s="1">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="K53" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="L53" s="1">
         <f t="shared" si="3"/>
-        <v>100000</v>
+        <v>40000</v>
       </c>
       <c r="M53" s="1">
         <v>1</v>
@@ -3011,36 +3016,36 @@
     </row>
     <row r="54" customHeight="1" spans="3:13">
       <c r="C54" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D54" s="1">
         <v>3</v>
       </c>
       <c r="E54" s="1">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="F54" s="1">
-        <f>10*M48</f>
-        <v>10</v>
+        <f>5*M49</f>
+        <v>5</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I54" s="1">
         <v>5</v>
       </c>
       <c r="J54" s="1">
-        <v>4102</v>
+        <v>4011</v>
       </c>
       <c r="K54" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L54" s="1">
         <f t="shared" si="3"/>
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="M54" s="1">
         <v>1</v>
@@ -3048,7 +3053,7 @@
     </row>
     <row r="55" customHeight="1" spans="3:13">
       <c r="C55" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D55" s="1">
         <v>3</v>
@@ -3057,27 +3062,27 @@
         <v>2000</v>
       </c>
       <c r="F55" s="1">
-        <f>40*M48</f>
-        <v>40</v>
+        <f>10*M49</f>
+        <v>10</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I55" s="1">
         <v>5</v>
       </c>
       <c r="J55" s="1">
-        <v>4001</v>
+        <v>4102</v>
       </c>
       <c r="K55" s="1">
-        <v>1000000</v>
+        <v>20</v>
       </c>
       <c r="L55" s="1">
         <f t="shared" si="3"/>
-        <v>80000</v>
+        <v>20000</v>
       </c>
       <c r="M55" s="1">
         <v>1</v>
@@ -3085,7 +3090,7 @@
     </row>
     <row r="56" customHeight="1" spans="3:13">
       <c r="C56" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D56" s="1">
         <v>3</v>
@@ -3094,23 +3099,23 @@
         <v>2000</v>
       </c>
       <c r="F56" s="1">
-        <f>40*M48</f>
+        <f>40*M49</f>
         <v>40</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I56" s="1">
         <v>5</v>
       </c>
       <c r="J56" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K56" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L56" s="1">
         <f t="shared" si="3"/>
@@ -3122,36 +3127,36 @@
     </row>
     <row r="57" customHeight="1" spans="3:13">
       <c r="C57" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D57" s="1">
-        <v>4</v>
-      </c>
-      <c r="E57" s="4">
-        <v>3000</v>
+        <v>3</v>
+      </c>
+      <c r="E57" s="1">
+        <v>2000</v>
       </c>
       <c r="F57" s="1">
-        <f>20*M57</f>
-        <v>20</v>
+        <f>40*M49</f>
+        <v>40</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="I57" s="1">
         <v>5</v>
       </c>
       <c r="J57" s="1">
-        <v>4010</v>
+        <v>4002</v>
       </c>
       <c r="K57" s="1">
-        <v>5</v>
+        <v>6000000</v>
       </c>
       <c r="L57" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="M57" s="1">
         <v>1</v>
@@ -3159,36 +3164,36 @@
     </row>
     <row r="58" customHeight="1" spans="3:13">
       <c r="C58" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D58" s="1">
         <v>4</v>
       </c>
       <c r="E58" s="4">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="F58" s="1">
-        <f>300*M57</f>
-        <v>300</v>
+        <f>20*M58</f>
+        <v>20</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I58" s="1">
         <v>5</v>
       </c>
       <c r="J58" s="1">
-        <v>4007</v>
+        <v>4010</v>
       </c>
       <c r="K58" s="1">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L58" s="1">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>60000</v>
       </c>
       <c r="M58" s="1">
         <v>1</v>
@@ -3196,7 +3201,7 @@
     </row>
     <row r="59" customHeight="1" spans="3:13">
       <c r="C59" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D59" s="1">
         <v>4</v>
@@ -3205,27 +3210,27 @@
         <v>600</v>
       </c>
       <c r="F59" s="1">
-        <f>500*M57</f>
-        <v>500</v>
+        <f>300*M58</f>
+        <v>300</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I59" s="1">
         <v>5</v>
       </c>
       <c r="J59" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K59" s="1">
         <v>1000</v>
       </c>
       <c r="L59" s="1">
         <f t="shared" si="3"/>
-        <v>300000</v>
+        <v>180000</v>
       </c>
       <c r="M59" s="1">
         <v>1</v>
@@ -3233,36 +3238,36 @@
     </row>
     <row r="60" customHeight="1" spans="3:13">
       <c r="C60" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D60" s="1">
         <v>4</v>
       </c>
       <c r="E60" s="4">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="F60" s="1">
-        <f>5*M57</f>
-        <v>5</v>
+        <f>500*M58</f>
+        <v>500</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I60" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J60" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="K60" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L60" s="1">
         <f t="shared" si="3"/>
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="M60" s="1">
         <v>1</v>
@@ -3270,36 +3275,36 @@
     </row>
     <row r="61" customHeight="1" spans="3:13">
       <c r="C61" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D61" s="1">
         <v>4</v>
       </c>
       <c r="E61" s="4">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="F61" s="1">
-        <f>20*M57</f>
-        <v>20</v>
+        <f>5*M58</f>
+        <v>5</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I61" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J61" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="K61" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L61" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="M61" s="1">
         <v>1</v>
@@ -3307,36 +3312,36 @@
     </row>
     <row r="62" customHeight="1" spans="3:13">
       <c r="C62" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D62" s="1">
         <v>4</v>
       </c>
       <c r="E62" s="4">
-        <v>30000</v>
+        <v>3000</v>
       </c>
       <c r="F62" s="1">
-        <f>5*M57</f>
-        <v>5</v>
+        <f>20*M58</f>
+        <v>20</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I62" s="1">
         <v>5</v>
       </c>
       <c r="J62" s="1">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="K62" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="L62" s="1">
         <f t="shared" si="3"/>
-        <v>150000</v>
+        <v>60000</v>
       </c>
       <c r="M62" s="1">
         <v>1</v>
@@ -3344,36 +3349,36 @@
     </row>
     <row r="63" customHeight="1" spans="3:13">
       <c r="C63" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D63" s="1">
         <v>4</v>
       </c>
       <c r="E63" s="4">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="F63" s="1">
-        <f>10*M57</f>
-        <v>10</v>
+        <f>5*M58</f>
+        <v>5</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I63" s="1">
         <v>5</v>
       </c>
       <c r="J63" s="1">
-        <v>4102</v>
+        <v>4011</v>
       </c>
       <c r="K63" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L63" s="1">
         <f t="shared" si="3"/>
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="M63" s="1">
         <v>1</v>
@@ -3381,7 +3386,7 @@
     </row>
     <row r="64" customHeight="1" spans="3:13">
       <c r="C64" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D64" s="1">
         <v>4</v>
@@ -3390,27 +3395,27 @@
         <v>3000</v>
       </c>
       <c r="F64" s="1">
-        <f>40*M57</f>
-        <v>40</v>
+        <f>10*M58</f>
+        <v>10</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I64" s="1">
         <v>5</v>
       </c>
       <c r="J64" s="1">
-        <v>4001</v>
+        <v>4102</v>
       </c>
       <c r="K64" s="1">
-        <v>1000000</v>
+        <v>20</v>
       </c>
       <c r="L64" s="1">
         <f t="shared" si="3"/>
-        <v>120000</v>
+        <v>30000</v>
       </c>
       <c r="M64" s="1">
         <v>1</v>
@@ -3418,7 +3423,7 @@
     </row>
     <row r="65" customHeight="1" spans="3:13">
       <c r="C65" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D65" s="1">
         <v>4</v>
@@ -3427,23 +3432,23 @@
         <v>3000</v>
       </c>
       <c r="F65" s="1">
-        <f>40*M57</f>
+        <f>40*M58</f>
         <v>40</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I65" s="1">
         <v>5</v>
       </c>
       <c r="J65" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K65" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L65" s="1">
         <f t="shared" si="3"/>
@@ -3455,73 +3460,73 @@
     </row>
     <row r="66" customHeight="1" spans="3:13">
       <c r="C66" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D66" s="1">
-        <v>5</v>
-      </c>
-      <c r="E66" s="1">
-        <v>4000</v>
+        <v>4</v>
+      </c>
+      <c r="E66" s="4">
+        <v>3000</v>
       </c>
       <c r="F66" s="1">
-        <f>20*M66</f>
-        <v>80</v>
+        <f>40*M58</f>
+        <v>40</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="I66" s="1">
         <v>5</v>
       </c>
       <c r="J66" s="1">
-        <v>4010</v>
+        <v>4002</v>
       </c>
       <c r="K66" s="1">
-        <v>5</v>
+        <v>6000000</v>
       </c>
       <c r="L66" s="1">
         <f t="shared" si="3"/>
-        <v>320000</v>
+        <v>120000</v>
       </c>
       <c r="M66" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:13">
       <c r="C67" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D67" s="1">
         <v>5</v>
       </c>
       <c r="E67" s="1">
-        <v>800</v>
+        <v>4000</v>
       </c>
       <c r="F67" s="1">
-        <f>300*M66</f>
-        <v>1200</v>
+        <f>20*M67</f>
+        <v>80</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I67" s="1">
         <v>5</v>
       </c>
       <c r="J67" s="1">
-        <v>4007</v>
+        <v>4010</v>
       </c>
       <c r="K67" s="1">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L67" s="1">
         <f t="shared" si="3"/>
-        <v>960000</v>
+        <v>320000</v>
       </c>
       <c r="M67" s="1">
         <v>4</v>
@@ -3529,7 +3534,7 @@
     </row>
     <row r="68" customHeight="1" spans="3:13">
       <c r="C68" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D68" s="1">
         <v>5</v>
@@ -3538,27 +3543,27 @@
         <v>800</v>
       </c>
       <c r="F68" s="1">
-        <f>500*M66</f>
-        <v>2000</v>
+        <f>300*M67</f>
+        <v>1200</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I68" s="1">
         <v>5</v>
       </c>
       <c r="J68" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K68" s="1">
         <v>1000</v>
       </c>
       <c r="L68" s="1">
         <f t="shared" si="3"/>
-        <v>1600000</v>
+        <v>960000</v>
       </c>
       <c r="M68" s="1">
         <v>4</v>
@@ -3566,36 +3571,36 @@
     </row>
     <row r="69" customHeight="1" spans="3:13">
       <c r="C69" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D69" s="1">
         <v>5</v>
       </c>
       <c r="E69" s="1">
-        <v>8000</v>
+        <v>800</v>
       </c>
       <c r="F69" s="1">
-        <f>5*M66</f>
-        <v>20</v>
+        <f>500*M67</f>
+        <v>2000</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I69" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J69" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="K69" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L69" s="1">
         <f t="shared" si="3"/>
-        <v>160000</v>
+        <v>1600000</v>
       </c>
       <c r="M69" s="1">
         <v>4</v>
@@ -3603,36 +3608,36 @@
     </row>
     <row r="70" customHeight="1" spans="3:13">
       <c r="C70" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D70" s="1">
         <v>5</v>
       </c>
       <c r="E70" s="1">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="F70" s="1">
-        <f>20*M66</f>
-        <v>80</v>
+        <f>5*M67</f>
+        <v>20</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I70" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J70" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="K70" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L70" s="1">
         <f t="shared" si="3"/>
-        <v>320000</v>
+        <v>160000</v>
       </c>
       <c r="M70" s="1">
         <v>4</v>
@@ -3640,36 +3645,36 @@
     </row>
     <row r="71" customHeight="1" spans="3:13">
       <c r="C71" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D71" s="1">
         <v>5</v>
       </c>
       <c r="E71" s="1">
-        <v>40000</v>
+        <v>4000</v>
       </c>
       <c r="F71" s="1">
-        <f>5*M66</f>
-        <v>20</v>
+        <f>20*M67</f>
+        <v>80</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I71" s="1">
         <v>5</v>
       </c>
       <c r="J71" s="1">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="K71" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="L71" s="1">
         <f t="shared" si="3"/>
-        <v>800000</v>
+        <v>320000</v>
       </c>
       <c r="M71" s="1">
         <v>4</v>
@@ -3677,36 +3682,36 @@
     </row>
     <row r="72" customHeight="1" spans="3:13">
       <c r="C72" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D72" s="1">
         <v>5</v>
       </c>
       <c r="E72" s="1">
-        <v>4000</v>
+        <v>40000</v>
       </c>
       <c r="F72" s="1">
-        <f>10*M66</f>
-        <v>40</v>
+        <f>5*M67</f>
+        <v>20</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I72" s="1">
         <v>5</v>
       </c>
       <c r="J72" s="1">
-        <v>4102</v>
+        <v>4011</v>
       </c>
       <c r="K72" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L72" s="1">
         <f t="shared" si="3"/>
-        <v>160000</v>
+        <v>800000</v>
       </c>
       <c r="M72" s="1">
         <v>4</v>
@@ -3714,7 +3719,7 @@
     </row>
     <row r="73" customHeight="1" spans="3:13">
       <c r="C73" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D73" s="1">
         <v>5</v>
@@ -3723,27 +3728,27 @@
         <v>4000</v>
       </c>
       <c r="F73" s="1">
-        <f>40*M66</f>
-        <v>160</v>
+        <f>10*M67</f>
+        <v>40</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I73" s="1">
         <v>5</v>
       </c>
       <c r="J73" s="1">
-        <v>4001</v>
+        <v>4102</v>
       </c>
       <c r="K73" s="1">
-        <v>1000000</v>
+        <v>20</v>
       </c>
       <c r="L73" s="1">
         <f t="shared" si="3"/>
-        <v>640000</v>
+        <v>160000</v>
       </c>
       <c r="M73" s="1">
         <v>4</v>
@@ -3751,7 +3756,7 @@
     </row>
     <row r="74" customHeight="1" spans="3:13">
       <c r="C74" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D74" s="1">
         <v>5</v>
@@ -3760,23 +3765,23 @@
         <v>4000</v>
       </c>
       <c r="F74" s="1">
-        <f>40*M66</f>
+        <f>40*M67</f>
         <v>160</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I74" s="1">
         <v>5</v>
       </c>
       <c r="J74" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K74" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L74" s="1">
         <f t="shared" si="3"/>
@@ -3786,36 +3791,73 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="3:12">
-      <c r="C77" s="1">
+    <row r="75" customHeight="1" spans="3:13">
+      <c r="C75" s="1">
+        <v>68</v>
+      </c>
+      <c r="D75" s="1">
+        <v>5</v>
+      </c>
+      <c r="E75" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F75" s="1">
+        <f>40*M67</f>
+        <v>160</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I75" s="1">
+        <v>5</v>
+      </c>
+      <c r="J75" s="1">
+        <v>4002</v>
+      </c>
+      <c r="K75" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="L75" s="1">
+        <f t="shared" si="3"/>
+        <v>640000</v>
+      </c>
+      <c r="M75" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:12">
+      <c r="C78" s="1">
         <v>99</v>
       </c>
-      <c r="D77" s="1">
+      <c r="D78" s="1">
         <v>0</v>
       </c>
-      <c r="E77" s="6" t="s">
+      <c r="E78" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F78" s="1">
         <v>100</v>
       </c>
-      <c r="G77" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I77" s="1">
-        <v>5</v>
-      </c>
-      <c r="J77" s="1">
+      <c r="G78" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I78" s="1">
+        <v>5</v>
+      </c>
+      <c r="J78" s="1">
         <v>4006</v>
       </c>
-      <c r="K77" s="1">
+      <c r="K78" s="1">
         <v>1000</v>
       </c>
-      <c r="L77" s="1">
-        <f>E77*F77</f>
+      <c r="L78" s="1">
+        <f>E78*F78</f>
         <v>100000</v>
       </c>
     </row>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -221,7 +221,7 @@
     <t>魂骨自选</t>
   </si>
   <si>
-    <t>500000</t>
+    <t>400000</t>
   </si>
   <si>
     <t>兑换极法宝自选*1</t>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="L28" s="1">
         <f t="shared" si="1"/>
-        <v>500000</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:13">

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -1415,7 +1415,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>13</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="L6" s="1">
         <f t="shared" ref="L6:L9" si="0">E6*F6</f>
-        <v>14400</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:12">
@@ -1448,7 +1448,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="1">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>15</v>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="L7" s="1">
         <f t="shared" si="0"/>
-        <v>14400</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1481,7 +1481,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="1">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>17</v>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="L8" s="1">
         <f t="shared" si="0"/>
-        <v>14400</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:12">

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="90">
   <si>
     <t>#</t>
   </si>
@@ -222,6 +222,15 @@
   </si>
   <si>
     <t>400000</t>
+  </si>
+  <si>
+    <t>兑换极矿工礼包*1</t>
+  </si>
+  <si>
+    <t>极矿工礼包</t>
+  </si>
+  <si>
+    <t>500000</t>
   </si>
   <si>
     <t>兑换极法宝自选*1</t>
@@ -1298,7 +1307,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M78"/>
+  <dimension ref="C1:M79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1565,7 +1574,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" ref="L10:L28" si="1">E10*F10</f>
+        <f t="shared" ref="L10:L29" si="1">E10*F10</f>
         <v>24000</v>
       </c>
     </row>
@@ -2042,7 +2051,7 @@
         <v>55</v>
       </c>
       <c r="F25" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>56</v>
@@ -2061,7 +2070,7 @@
       </c>
       <c r="L25" s="1">
         <f t="shared" si="1"/>
-        <v>50000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:12">
@@ -2108,7 +2117,7 @@
         <v>61</v>
       </c>
       <c r="F27" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>62</v>
@@ -2127,7 +2136,7 @@
       </c>
       <c r="L27" s="1">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:12">
@@ -2163,305 +2172,301 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="3:13">
-      <c r="C30" s="1">
+    <row r="29" customHeight="1" spans="3:12">
+      <c r="C29" s="1">
         <v>24</v>
       </c>
-      <c r="D30" s="1">
-        <v>1</v>
-      </c>
-      <c r="E30" s="1">
-        <v>500</v>
-      </c>
-      <c r="F30" s="1">
-        <f>20*M30</f>
-        <v>20</v>
-      </c>
-      <c r="G30" s="1" t="s">
+      <c r="D29" s="1">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I30" s="1">
-        <v>5</v>
-      </c>
-      <c r="J30" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K30" s="1">
-        <v>5</v>
-      </c>
-      <c r="L30" s="1">
-        <f t="shared" ref="L30:L38" si="2">E30*F30</f>
-        <v>10000</v>
-      </c>
-      <c r="M30" s="1">
-        <v>1</v>
+      <c r="H29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I29" s="1">
+        <v>4</v>
+      </c>
+      <c r="J29" s="1">
+        <v>31</v>
+      </c>
+      <c r="K29" s="1">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1">
+        <f t="shared" si="1"/>
+        <v>500000</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:13">
       <c r="C31" s="1">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="D31" s="1">
         <v>1</v>
       </c>
       <c r="E31" s="1">
+        <v>500</v>
+      </c>
+      <c r="F31" s="1">
+        <f>20*M31</f>
+        <v>20</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I31" s="1">
+        <v>5</v>
+      </c>
+      <c r="J31" s="1">
+        <v>4010</v>
+      </c>
+      <c r="K31" s="1">
+        <v>5</v>
+      </c>
+      <c r="L31" s="1">
+        <f t="shared" ref="L31:L39" si="2">E31*F31</f>
+        <v>10000</v>
+      </c>
+      <c r="M31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:13">
+      <c r="C32" s="1">
+        <v>102</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
         <v>100</v>
       </c>
-      <c r="F31" s="1">
-        <f>300*M30</f>
+      <c r="F32" s="1">
+        <f>300*M31</f>
         <v>300</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I31" s="1">
-        <v>5</v>
-      </c>
-      <c r="J31" s="1">
+      <c r="G32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I32" s="1">
+        <v>5</v>
+      </c>
+      <c r="J32" s="1">
         <v>4007</v>
       </c>
-      <c r="K31" s="1">
+      <c r="K32" s="1">
         <v>1000</v>
       </c>
-      <c r="L31" s="1">
+      <c r="L32" s="1">
         <f t="shared" si="2"/>
         <v>30000</v>
       </c>
-      <c r="M31" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:13">
-      <c r="C32" s="1">
-        <v>26</v>
-      </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="M32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:13">
+      <c r="C33" s="1">
+        <v>103</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1">
         <v>100</v>
       </c>
-      <c r="F32" s="1">
-        <f>500*M30</f>
+      <c r="F33" s="1">
+        <f>500*M31</f>
         <v>500</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I32" s="1">
-        <v>5</v>
-      </c>
-      <c r="J32" s="1">
+      <c r="G33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I33" s="1">
+        <v>5</v>
+      </c>
+      <c r="J33" s="1">
         <v>4101</v>
       </c>
-      <c r="K32" s="1">
+      <c r="K33" s="1">
         <v>1000</v>
       </c>
-      <c r="L32" s="1">
+      <c r="L33" s="1">
         <f t="shared" si="2"/>
         <v>50000</v>
       </c>
-      <c r="M32" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:13">
-      <c r="C33" s="1">
-        <v>27</v>
-      </c>
-      <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1">
+      <c r="M33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:13">
+      <c r="C34" s="1">
+        <v>104</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+      <c r="E34" s="1">
         <v>1000</v>
       </c>
-      <c r="F33" s="1">
-        <f>5*M30</f>
-        <v>5</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I33" s="1">
+      <c r="F34" s="1">
+        <f>5*M31</f>
+        <v>5</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I34" s="1">
         <v>15</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J34" s="1">
         <v>4014</v>
       </c>
-      <c r="K33" s="1">
+      <c r="K34" s="1">
         <v>100</v>
       </c>
-      <c r="L33" s="1">
+      <c r="L34" s="1">
         <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="M33" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:13">
-      <c r="C34" s="1">
-        <v>28</v>
-      </c>
-      <c r="D34" s="1">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1">
+      <c r="M34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:13">
+      <c r="C35" s="1">
+        <v>105</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1</v>
+      </c>
+      <c r="E35" s="1">
         <v>500</v>
       </c>
-      <c r="F34" s="1">
-        <f>20*M30</f>
+      <c r="F35" s="1">
+        <f>20*M31</f>
         <v>20</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I34" s="1">
-        <v>5</v>
-      </c>
-      <c r="J34" s="1">
+      <c r="G35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I35" s="1">
+        <v>5</v>
+      </c>
+      <c r="J35" s="1">
         <v>4012</v>
       </c>
-      <c r="K34" s="1">
+      <c r="K35" s="1">
         <v>200</v>
       </c>
-      <c r="L34" s="1">
+      <c r="L35" s="1">
         <f t="shared" si="2"/>
         <v>10000</v>
       </c>
-      <c r="M34" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:13">
-      <c r="C35" s="1">
-        <v>29</v>
-      </c>
-      <c r="D35" s="1">
-        <v>1</v>
-      </c>
-      <c r="E35" s="1">
+      <c r="M35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:13">
+      <c r="C36" s="1">
+        <v>106</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1">
         <v>5000</v>
       </c>
-      <c r="F35" s="1">
-        <f>5*M30</f>
-        <v>5</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I35" s="1">
-        <v>5</v>
-      </c>
-      <c r="J35" s="1">
+      <c r="F36" s="1">
+        <f>5*M31</f>
+        <v>5</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I36" s="1">
+        <v>5</v>
+      </c>
+      <c r="J36" s="1">
         <v>4011</v>
       </c>
-      <c r="K35" s="1">
-        <v>1</v>
-      </c>
-      <c r="L35" s="1">
+      <c r="K36" s="1">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1">
         <f t="shared" si="2"/>
         <v>25000</v>
       </c>
-      <c r="M35" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:13">
-      <c r="C36" s="1">
-        <v>30</v>
-      </c>
-      <c r="D36" s="1">
-        <v>1</v>
-      </c>
-      <c r="E36" s="1">
+      <c r="M36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:13">
+      <c r="C37" s="1">
+        <v>107</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+      <c r="E37" s="1">
         <v>500</v>
       </c>
-      <c r="F36" s="1">
-        <f>10*M30</f>
+      <c r="F37" s="1">
+        <f>10*M31</f>
         <v>10</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I36" s="1">
-        <v>5</v>
-      </c>
-      <c r="J36" s="1">
+      <c r="G37" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I37" s="1">
+        <v>5</v>
+      </c>
+      <c r="J37" s="1">
         <v>4102</v>
       </c>
-      <c r="K36" s="1">
+      <c r="K37" s="1">
         <v>20</v>
       </c>
-      <c r="L36" s="1">
+      <c r="L37" s="1">
         <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="M36" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:13">
-      <c r="C37" s="1">
-        <v>31</v>
-      </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
-      <c r="E37" s="1">
-        <v>500</v>
-      </c>
-      <c r="F37" s="1">
-        <f>40*M30</f>
-        <v>40</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I37" s="1">
-        <v>5</v>
-      </c>
-      <c r="J37" s="1">
-        <v>4001</v>
-      </c>
-      <c r="K37" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="L37" s="1">
-        <f t="shared" si="2"/>
-        <v>20000</v>
-      </c>
       <c r="M37" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:13">
       <c r="C38" s="1">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
@@ -2470,23 +2475,23 @@
         <v>500</v>
       </c>
       <c r="F38" s="1">
-        <f>40*M30</f>
+        <f>40*M31</f>
         <v>40</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I38" s="1">
         <v>5</v>
       </c>
       <c r="J38" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K38" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L38" s="1">
         <f t="shared" si="2"/>
@@ -2496,305 +2501,305 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="3:13">
-      <c r="C40" s="1">
-        <v>33</v>
-      </c>
-      <c r="D40" s="1">
-        <v>2</v>
-      </c>
-      <c r="E40" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F40" s="1">
-        <f>20*M40</f>
-        <v>20</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I40" s="1">
-        <v>5</v>
-      </c>
-      <c r="J40" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K40" s="1">
-        <v>5</v>
-      </c>
-      <c r="L40" s="1">
-        <f t="shared" ref="L40:L75" si="3">E40*F40</f>
+    <row r="39" customHeight="1" spans="3:13">
+      <c r="C39" s="1">
+        <v>109</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1</v>
+      </c>
+      <c r="E39" s="1">
+        <v>500</v>
+      </c>
+      <c r="F39" s="1">
+        <f>40*M31</f>
+        <v>40</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I39" s="1">
+        <v>5</v>
+      </c>
+      <c r="J39" s="1">
+        <v>4002</v>
+      </c>
+      <c r="K39" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="L39" s="1">
+        <f t="shared" si="2"/>
         <v>20000</v>
       </c>
-      <c r="M40" s="1">
+      <c r="M39" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:13">
       <c r="C41" s="1">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="D41" s="1">
         <v>2</v>
       </c>
       <c r="E41" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F41" s="1">
+        <f>20*M41</f>
+        <v>20</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I41" s="1">
+        <v>5</v>
+      </c>
+      <c r="J41" s="1">
+        <v>4010</v>
+      </c>
+      <c r="K41" s="1">
+        <v>5</v>
+      </c>
+      <c r="L41" s="1">
+        <f t="shared" ref="L41:L76" si="3">E41*F41</f>
+        <v>20000</v>
+      </c>
+      <c r="M41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:13">
+      <c r="C42" s="1">
+        <v>202</v>
+      </c>
+      <c r="D42" s="1">
+        <v>2</v>
+      </c>
+      <c r="E42" s="4">
         <v>200</v>
       </c>
-      <c r="F41" s="1">
-        <f>300*M40</f>
+      <c r="F42" s="1">
+        <f>300*M41</f>
         <v>300</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I41" s="1">
-        <v>5</v>
-      </c>
-      <c r="J41" s="1">
+      <c r="G42" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I42" s="1">
+        <v>5</v>
+      </c>
+      <c r="J42" s="1">
         <v>4007</v>
       </c>
-      <c r="K41" s="1">
+      <c r="K42" s="1">
         <v>1000</v>
       </c>
-      <c r="L41" s="1">
+      <c r="L42" s="1">
         <f t="shared" si="3"/>
         <v>60000</v>
       </c>
-      <c r="M41" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:13">
-      <c r="C42" s="1">
-        <v>35</v>
-      </c>
-      <c r="D42" s="1">
+      <c r="M42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:13">
+      <c r="C43" s="1">
+        <v>203</v>
+      </c>
+      <c r="D43" s="1">
         <v>2</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E43" s="4">
         <v>200</v>
       </c>
-      <c r="F42" s="1">
-        <f>500*M40</f>
+      <c r="F43" s="1">
+        <f>500*M41</f>
         <v>500</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="I42" s="1">
-        <v>5</v>
-      </c>
-      <c r="J42" s="1">
+      <c r="G43" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I43" s="1">
+        <v>5</v>
+      </c>
+      <c r="J43" s="1">
         <v>4101</v>
       </c>
-      <c r="K42" s="1">
+      <c r="K43" s="1">
         <v>1000</v>
       </c>
-      <c r="L42" s="1">
+      <c r="L43" s="1">
         <f t="shared" si="3"/>
         <v>100000</v>
       </c>
-      <c r="M42" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:13">
-      <c r="C43" s="1">
-        <v>36</v>
-      </c>
-      <c r="D43" s="1">
+      <c r="M43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:13">
+      <c r="C44" s="1">
+        <v>204</v>
+      </c>
+      <c r="D44" s="1">
         <v>2</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E44" s="4">
         <v>2000</v>
       </c>
-      <c r="F43" s="1">
-        <f>5*M40</f>
-        <v>5</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I43" s="1">
+      <c r="F44" s="1">
+        <f>5*M41</f>
+        <v>5</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I44" s="1">
         <v>15</v>
       </c>
-      <c r="J43" s="1">
+      <c r="J44" s="1">
         <v>4014</v>
       </c>
-      <c r="K43" s="1">
+      <c r="K44" s="1">
         <v>100</v>
       </c>
-      <c r="L43" s="1">
+      <c r="L44" s="1">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
-      <c r="M43" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:13">
-      <c r="C44" s="1">
-        <v>37</v>
-      </c>
-      <c r="D44" s="1">
+      <c r="M44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:13">
+      <c r="C45" s="1">
+        <v>205</v>
+      </c>
+      <c r="D45" s="1">
         <v>2</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E45" s="4">
         <v>1000</v>
       </c>
-      <c r="F44" s="1">
-        <f>20*M40</f>
+      <c r="F45" s="1">
+        <f>20*M41</f>
         <v>20</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I44" s="1">
-        <v>5</v>
-      </c>
-      <c r="J44" s="1">
+      <c r="G45" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I45" s="1">
+        <v>5</v>
+      </c>
+      <c r="J45" s="1">
         <v>4012</v>
       </c>
-      <c r="K44" s="1">
+      <c r="K45" s="1">
         <v>200</v>
       </c>
-      <c r="L44" s="1">
+      <c r="L45" s="1">
         <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="M44" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:13">
-      <c r="C45" s="1">
-        <v>38</v>
-      </c>
-      <c r="D45" s="1">
+      <c r="M45" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:13">
+      <c r="C46" s="1">
+        <v>206</v>
+      </c>
+      <c r="D46" s="1">
         <v>2</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E46" s="4">
         <v>10000</v>
       </c>
-      <c r="F45" s="1">
-        <f>5*M40</f>
-        <v>5</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I45" s="1">
-        <v>5</v>
-      </c>
-      <c r="J45" s="1">
+      <c r="F46" s="1">
+        <f>5*M41</f>
+        <v>5</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I46" s="1">
+        <v>5</v>
+      </c>
+      <c r="J46" s="1">
         <v>4011</v>
       </c>
-      <c r="K45" s="1">
-        <v>1</v>
-      </c>
-      <c r="L45" s="1">
+      <c r="K46" s="1">
+        <v>1</v>
+      </c>
+      <c r="L46" s="1">
         <f t="shared" si="3"/>
         <v>50000</v>
       </c>
-      <c r="M45" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:13">
-      <c r="C46" s="1">
-        <v>39</v>
-      </c>
-      <c r="D46" s="1">
+      <c r="M46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:13">
+      <c r="C47" s="1">
+        <v>207</v>
+      </c>
+      <c r="D47" s="1">
         <v>2</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E47" s="4">
         <v>1000</v>
       </c>
-      <c r="F46" s="1">
-        <f>10*M40</f>
+      <c r="F47" s="1">
+        <f>10*M41</f>
         <v>10</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I46" s="1">
-        <v>5</v>
-      </c>
-      <c r="J46" s="1">
+      <c r="G47" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I47" s="1">
+        <v>5</v>
+      </c>
+      <c r="J47" s="1">
         <v>4102</v>
       </c>
-      <c r="K46" s="1">
+      <c r="K47" s="1">
         <v>20</v>
       </c>
-      <c r="L46" s="1">
+      <c r="L47" s="1">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
-      <c r="M46" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:13">
-      <c r="C47" s="1">
-        <v>40</v>
-      </c>
-      <c r="D47" s="1">
-        <v>2</v>
-      </c>
-      <c r="E47" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F47" s="1">
-        <f>40*M40</f>
-        <v>40</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I47" s="1">
-        <v>5</v>
-      </c>
-      <c r="J47" s="1">
-        <v>4001</v>
-      </c>
-      <c r="K47" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="L47" s="1">
-        <f t="shared" si="3"/>
-        <v>40000</v>
-      </c>
       <c r="M47" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:13">
       <c r="C48" s="1">
-        <v>41</v>
+        <v>208</v>
       </c>
       <c r="D48" s="1">
         <v>2</v>
@@ -2803,23 +2808,23 @@
         <v>1000</v>
       </c>
       <c r="F48" s="1">
-        <f>40*M40</f>
+        <f>40*M41</f>
         <v>40</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I48" s="1">
         <v>5</v>
       </c>
       <c r="J48" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K48" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L48" s="1">
         <f t="shared" si="3"/>
@@ -2831,32 +2836,32 @@
     </row>
     <row r="49" customHeight="1" spans="3:13">
       <c r="C49" s="1">
-        <v>42</v>
+        <v>209</v>
       </c>
       <c r="D49" s="1">
-        <v>3</v>
-      </c>
-      <c r="E49" s="1">
-        <v>2000</v>
+        <v>2</v>
+      </c>
+      <c r="E49" s="4">
+        <v>1000</v>
       </c>
       <c r="F49" s="1">
-        <f>20*M49</f>
-        <v>20</v>
+        <f>40*M41</f>
+        <v>40</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="I49" s="1">
         <v>5</v>
       </c>
       <c r="J49" s="1">
-        <v>4010</v>
+        <v>4002</v>
       </c>
       <c r="K49" s="1">
-        <v>5</v>
+        <v>6000000</v>
       </c>
       <c r="L49" s="1">
         <f t="shared" si="3"/>
@@ -2868,36 +2873,36 @@
     </row>
     <row r="50" customHeight="1" spans="3:13">
       <c r="C50" s="1">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="D50" s="1">
         <v>3</v>
       </c>
       <c r="E50" s="1">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="F50" s="1">
-        <f>300*M49</f>
-        <v>300</v>
+        <f>20*M50</f>
+        <v>20</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I50" s="1">
         <v>5</v>
       </c>
       <c r="J50" s="1">
-        <v>4007</v>
+        <v>4010</v>
       </c>
       <c r="K50" s="1">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L50" s="1">
         <f t="shared" si="3"/>
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="M50" s="1">
         <v>1</v>
@@ -2905,7 +2910,7 @@
     </row>
     <row r="51" customHeight="1" spans="3:13">
       <c r="C51" s="1">
-        <v>44</v>
+        <v>211</v>
       </c>
       <c r="D51" s="1">
         <v>3</v>
@@ -2914,27 +2919,27 @@
         <v>400</v>
       </c>
       <c r="F51" s="1">
-        <f>500*M49</f>
-        <v>500</v>
+        <f>300*M50</f>
+        <v>300</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I51" s="1">
         <v>5</v>
       </c>
       <c r="J51" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K51" s="1">
         <v>1000</v>
       </c>
       <c r="L51" s="1">
         <f t="shared" si="3"/>
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="M51" s="1">
         <v>1</v>
@@ -2942,36 +2947,36 @@
     </row>
     <row r="52" customHeight="1" spans="3:13">
       <c r="C52" s="1">
-        <v>45</v>
+        <v>212</v>
       </c>
       <c r="D52" s="1">
         <v>3</v>
       </c>
       <c r="E52" s="1">
-        <v>4000</v>
+        <v>400</v>
       </c>
       <c r="F52" s="1">
-        <f>5*M49</f>
-        <v>5</v>
+        <f>500*M50</f>
+        <v>500</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I52" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J52" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="K52" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L52" s="1">
         <f t="shared" si="3"/>
-        <v>20000</v>
+        <v>200000</v>
       </c>
       <c r="M52" s="1">
         <v>1</v>
@@ -2979,36 +2984,36 @@
     </row>
     <row r="53" customHeight="1" spans="3:13">
       <c r="C53" s="1">
-        <v>46</v>
+        <v>213</v>
       </c>
       <c r="D53" s="1">
         <v>3</v>
       </c>
       <c r="E53" s="1">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="F53" s="1">
-        <f>20*M49</f>
-        <v>20</v>
+        <f>5*M50</f>
+        <v>5</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I53" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J53" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="K53" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L53" s="1">
         <f t="shared" si="3"/>
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="M53" s="1">
         <v>1</v>
@@ -3016,36 +3021,36 @@
     </row>
     <row r="54" customHeight="1" spans="3:13">
       <c r="C54" s="1">
-        <v>47</v>
+        <v>214</v>
       </c>
       <c r="D54" s="1">
         <v>3</v>
       </c>
       <c r="E54" s="1">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="F54" s="1">
-        <f>5*M49</f>
-        <v>5</v>
+        <f>20*M50</f>
+        <v>20</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I54" s="1">
         <v>5</v>
       </c>
       <c r="J54" s="1">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="K54" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="L54" s="1">
         <f t="shared" si="3"/>
-        <v>100000</v>
+        <v>40000</v>
       </c>
       <c r="M54" s="1">
         <v>1</v>
@@ -3053,36 +3058,36 @@
     </row>
     <row r="55" customHeight="1" spans="3:13">
       <c r="C55" s="1">
-        <v>48</v>
+        <v>215</v>
       </c>
       <c r="D55" s="1">
         <v>3</v>
       </c>
       <c r="E55" s="1">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="F55" s="1">
-        <f>10*M49</f>
-        <v>10</v>
+        <f>5*M50</f>
+        <v>5</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I55" s="1">
         <v>5</v>
       </c>
       <c r="J55" s="1">
-        <v>4102</v>
+        <v>4011</v>
       </c>
       <c r="K55" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L55" s="1">
         <f t="shared" si="3"/>
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="M55" s="1">
         <v>1</v>
@@ -3090,7 +3095,7 @@
     </row>
     <row r="56" customHeight="1" spans="3:13">
       <c r="C56" s="1">
-        <v>49</v>
+        <v>216</v>
       </c>
       <c r="D56" s="1">
         <v>3</v>
@@ -3099,27 +3104,27 @@
         <v>2000</v>
       </c>
       <c r="F56" s="1">
-        <f>40*M49</f>
-        <v>40</v>
+        <f>10*M50</f>
+        <v>10</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I56" s="1">
         <v>5</v>
       </c>
       <c r="J56" s="1">
-        <v>4001</v>
+        <v>4102</v>
       </c>
       <c r="K56" s="1">
-        <v>1000000</v>
+        <v>20</v>
       </c>
       <c r="L56" s="1">
         <f t="shared" si="3"/>
-        <v>80000</v>
+        <v>20000</v>
       </c>
       <c r="M56" s="1">
         <v>1</v>
@@ -3127,7 +3132,7 @@
     </row>
     <row r="57" customHeight="1" spans="3:13">
       <c r="C57" s="1">
-        <v>50</v>
+        <v>217</v>
       </c>
       <c r="D57" s="1">
         <v>3</v>
@@ -3136,23 +3141,23 @@
         <v>2000</v>
       </c>
       <c r="F57" s="1">
-        <f>40*M49</f>
+        <f>40*M50</f>
         <v>40</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I57" s="1">
         <v>5</v>
       </c>
       <c r="J57" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K57" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L57" s="1">
         <f t="shared" si="3"/>
@@ -3164,36 +3169,36 @@
     </row>
     <row r="58" customHeight="1" spans="3:13">
       <c r="C58" s="1">
-        <v>51</v>
+        <v>218</v>
       </c>
       <c r="D58" s="1">
-        <v>4</v>
-      </c>
-      <c r="E58" s="4">
-        <v>3000</v>
+        <v>3</v>
+      </c>
+      <c r="E58" s="1">
+        <v>2000</v>
       </c>
       <c r="F58" s="1">
-        <f>20*M58</f>
-        <v>20</v>
+        <f>40*M50</f>
+        <v>40</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="I58" s="1">
         <v>5</v>
       </c>
       <c r="J58" s="1">
-        <v>4010</v>
+        <v>4002</v>
       </c>
       <c r="K58" s="1">
-        <v>5</v>
+        <v>6000000</v>
       </c>
       <c r="L58" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="M58" s="1">
         <v>1</v>
@@ -3201,36 +3206,36 @@
     </row>
     <row r="59" customHeight="1" spans="3:13">
       <c r="C59" s="1">
-        <v>52</v>
+        <v>219</v>
       </c>
       <c r="D59" s="1">
         <v>4</v>
       </c>
       <c r="E59" s="4">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="F59" s="1">
-        <f>300*M58</f>
-        <v>300</v>
+        <f>20*M59</f>
+        <v>20</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I59" s="1">
         <v>5</v>
       </c>
       <c r="J59" s="1">
-        <v>4007</v>
+        <v>4010</v>
       </c>
       <c r="K59" s="1">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L59" s="1">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>60000</v>
       </c>
       <c r="M59" s="1">
         <v>1</v>
@@ -3238,7 +3243,7 @@
     </row>
     <row r="60" customHeight="1" spans="3:13">
       <c r="C60" s="1">
-        <v>53</v>
+        <v>220</v>
       </c>
       <c r="D60" s="1">
         <v>4</v>
@@ -3247,27 +3252,27 @@
         <v>600</v>
       </c>
       <c r="F60" s="1">
-        <f>500*M58</f>
-        <v>500</v>
+        <f>300*M59</f>
+        <v>300</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I60" s="1">
         <v>5</v>
       </c>
       <c r="J60" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K60" s="1">
         <v>1000</v>
       </c>
       <c r="L60" s="1">
         <f t="shared" si="3"/>
-        <v>300000</v>
+        <v>180000</v>
       </c>
       <c r="M60" s="1">
         <v>1</v>
@@ -3275,36 +3280,36 @@
     </row>
     <row r="61" customHeight="1" spans="3:13">
       <c r="C61" s="1">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="D61" s="1">
         <v>4</v>
       </c>
       <c r="E61" s="4">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="F61" s="1">
-        <f>5*M58</f>
-        <v>5</v>
+        <f>500*M59</f>
+        <v>500</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I61" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J61" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="K61" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L61" s="1">
         <f t="shared" si="3"/>
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="M61" s="1">
         <v>1</v>
@@ -3312,36 +3317,36 @@
     </row>
     <row r="62" customHeight="1" spans="3:13">
       <c r="C62" s="1">
-        <v>55</v>
+        <v>222</v>
       </c>
       <c r="D62" s="1">
         <v>4</v>
       </c>
       <c r="E62" s="4">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="F62" s="1">
-        <f>20*M58</f>
-        <v>20</v>
+        <f>5*M59</f>
+        <v>5</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I62" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J62" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="K62" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L62" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="M62" s="1">
         <v>1</v>
@@ -3349,36 +3354,36 @@
     </row>
     <row r="63" customHeight="1" spans="3:13">
       <c r="C63" s="1">
-        <v>56</v>
+        <v>223</v>
       </c>
       <c r="D63" s="1">
         <v>4</v>
       </c>
       <c r="E63" s="4">
-        <v>30000</v>
+        <v>3000</v>
       </c>
       <c r="F63" s="1">
-        <f>5*M58</f>
-        <v>5</v>
+        <f>20*M59</f>
+        <v>20</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I63" s="1">
         <v>5</v>
       </c>
       <c r="J63" s="1">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="K63" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="L63" s="1">
         <f t="shared" si="3"/>
-        <v>150000</v>
+        <v>60000</v>
       </c>
       <c r="M63" s="1">
         <v>1</v>
@@ -3386,36 +3391,36 @@
     </row>
     <row r="64" customHeight="1" spans="3:13">
       <c r="C64" s="1">
-        <v>57</v>
+        <v>224</v>
       </c>
       <c r="D64" s="1">
         <v>4</v>
       </c>
       <c r="E64" s="4">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="F64" s="1">
-        <f>10*M58</f>
-        <v>10</v>
+        <f>5*M59</f>
+        <v>5</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I64" s="1">
         <v>5</v>
       </c>
       <c r="J64" s="1">
-        <v>4102</v>
+        <v>4011</v>
       </c>
       <c r="K64" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L64" s="1">
         <f t="shared" si="3"/>
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="M64" s="1">
         <v>1</v>
@@ -3423,7 +3428,7 @@
     </row>
     <row r="65" customHeight="1" spans="3:13">
       <c r="C65" s="1">
-        <v>58</v>
+        <v>225</v>
       </c>
       <c r="D65" s="1">
         <v>4</v>
@@ -3432,27 +3437,27 @@
         <v>3000</v>
       </c>
       <c r="F65" s="1">
-        <f>40*M58</f>
-        <v>40</v>
+        <f>10*M59</f>
+        <v>10</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I65" s="1">
         <v>5</v>
       </c>
       <c r="J65" s="1">
-        <v>4001</v>
+        <v>4102</v>
       </c>
       <c r="K65" s="1">
-        <v>1000000</v>
+        <v>20</v>
       </c>
       <c r="L65" s="1">
         <f t="shared" si="3"/>
-        <v>120000</v>
+        <v>30000</v>
       </c>
       <c r="M65" s="1">
         <v>1</v>
@@ -3460,7 +3465,7 @@
     </row>
     <row r="66" customHeight="1" spans="3:13">
       <c r="C66" s="1">
-        <v>59</v>
+        <v>226</v>
       </c>
       <c r="D66" s="1">
         <v>4</v>
@@ -3469,23 +3474,23 @@
         <v>3000</v>
       </c>
       <c r="F66" s="1">
-        <f>40*M58</f>
+        <f>40*M59</f>
         <v>40</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I66" s="1">
         <v>5</v>
       </c>
       <c r="J66" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K66" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L66" s="1">
         <f t="shared" si="3"/>
@@ -3497,73 +3502,73 @@
     </row>
     <row r="67" customHeight="1" spans="3:13">
       <c r="C67" s="1">
-        <v>60</v>
+        <v>227</v>
       </c>
       <c r="D67" s="1">
-        <v>5</v>
-      </c>
-      <c r="E67" s="1">
-        <v>4000</v>
+        <v>4</v>
+      </c>
+      <c r="E67" s="4">
+        <v>3000</v>
       </c>
       <c r="F67" s="1">
-        <f>20*M67</f>
-        <v>80</v>
+        <f>40*M59</f>
+        <v>40</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="I67" s="1">
         <v>5</v>
       </c>
       <c r="J67" s="1">
-        <v>4010</v>
+        <v>4002</v>
       </c>
       <c r="K67" s="1">
-        <v>5</v>
+        <v>6000000</v>
       </c>
       <c r="L67" s="1">
         <f t="shared" si="3"/>
-        <v>320000</v>
+        <v>120000</v>
       </c>
       <c r="M67" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:13">
       <c r="C68" s="1">
-        <v>61</v>
+        <v>228</v>
       </c>
       <c r="D68" s="1">
         <v>5</v>
       </c>
       <c r="E68" s="1">
-        <v>800</v>
+        <v>4000</v>
       </c>
       <c r="F68" s="1">
-        <f>300*M67</f>
-        <v>1200</v>
+        <f>20*M68</f>
+        <v>80</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I68" s="1">
         <v>5</v>
       </c>
       <c r="J68" s="1">
-        <v>4007</v>
+        <v>4010</v>
       </c>
       <c r="K68" s="1">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L68" s="1">
         <f t="shared" si="3"/>
-        <v>960000</v>
+        <v>320000</v>
       </c>
       <c r="M68" s="1">
         <v>4</v>
@@ -3571,7 +3576,7 @@
     </row>
     <row r="69" customHeight="1" spans="3:13">
       <c r="C69" s="1">
-        <v>62</v>
+        <v>229</v>
       </c>
       <c r="D69" s="1">
         <v>5</v>
@@ -3580,27 +3585,27 @@
         <v>800</v>
       </c>
       <c r="F69" s="1">
-        <f>500*M67</f>
-        <v>2000</v>
+        <f>300*M68</f>
+        <v>1200</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I69" s="1">
         <v>5</v>
       </c>
       <c r="J69" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K69" s="1">
         <v>1000</v>
       </c>
       <c r="L69" s="1">
         <f t="shared" si="3"/>
-        <v>1600000</v>
+        <v>960000</v>
       </c>
       <c r="M69" s="1">
         <v>4</v>
@@ -3608,36 +3613,36 @@
     </row>
     <row r="70" customHeight="1" spans="3:13">
       <c r="C70" s="1">
-        <v>63</v>
+        <v>230</v>
       </c>
       <c r="D70" s="1">
         <v>5</v>
       </c>
       <c r="E70" s="1">
-        <v>8000</v>
+        <v>800</v>
       </c>
       <c r="F70" s="1">
-        <f>5*M67</f>
-        <v>20</v>
+        <f>500*M68</f>
+        <v>2000</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I70" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J70" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="K70" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L70" s="1">
         <f t="shared" si="3"/>
-        <v>160000</v>
+        <v>1600000</v>
       </c>
       <c r="M70" s="1">
         <v>4</v>
@@ -3645,36 +3650,36 @@
     </row>
     <row r="71" customHeight="1" spans="3:13">
       <c r="C71" s="1">
-        <v>64</v>
+        <v>231</v>
       </c>
       <c r="D71" s="1">
         <v>5</v>
       </c>
       <c r="E71" s="1">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="F71" s="1">
-        <f>20*M67</f>
-        <v>80</v>
+        <f>5*M68</f>
+        <v>20</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I71" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J71" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="K71" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L71" s="1">
         <f t="shared" si="3"/>
-        <v>320000</v>
+        <v>160000</v>
       </c>
       <c r="M71" s="1">
         <v>4</v>
@@ -3682,36 +3687,36 @@
     </row>
     <row r="72" customHeight="1" spans="3:13">
       <c r="C72" s="1">
-        <v>65</v>
+        <v>232</v>
       </c>
       <c r="D72" s="1">
         <v>5</v>
       </c>
       <c r="E72" s="1">
-        <v>40000</v>
+        <v>4000</v>
       </c>
       <c r="F72" s="1">
-        <f>5*M67</f>
-        <v>20</v>
+        <f>20*M68</f>
+        <v>80</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I72" s="1">
         <v>5</v>
       </c>
       <c r="J72" s="1">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="K72" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="L72" s="1">
         <f t="shared" si="3"/>
-        <v>800000</v>
+        <v>320000</v>
       </c>
       <c r="M72" s="1">
         <v>4</v>
@@ -3719,36 +3724,36 @@
     </row>
     <row r="73" customHeight="1" spans="3:13">
       <c r="C73" s="1">
-        <v>66</v>
+        <v>233</v>
       </c>
       <c r="D73" s="1">
         <v>5</v>
       </c>
       <c r="E73" s="1">
-        <v>4000</v>
+        <v>40000</v>
       </c>
       <c r="F73" s="1">
-        <f>10*M67</f>
-        <v>40</v>
+        <f>5*M68</f>
+        <v>20</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I73" s="1">
         <v>5</v>
       </c>
       <c r="J73" s="1">
-        <v>4102</v>
+        <v>4011</v>
       </c>
       <c r="K73" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L73" s="1">
         <f t="shared" si="3"/>
-        <v>160000</v>
+        <v>800000</v>
       </c>
       <c r="M73" s="1">
         <v>4</v>
@@ -3756,7 +3761,7 @@
     </row>
     <row r="74" customHeight="1" spans="3:13">
       <c r="C74" s="1">
-        <v>67</v>
+        <v>234</v>
       </c>
       <c r="D74" s="1">
         <v>5</v>
@@ -3765,27 +3770,27 @@
         <v>4000</v>
       </c>
       <c r="F74" s="1">
-        <f>40*M67</f>
-        <v>160</v>
+        <f>10*M68</f>
+        <v>40</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I74" s="1">
         <v>5</v>
       </c>
       <c r="J74" s="1">
-        <v>4001</v>
+        <v>4102</v>
       </c>
       <c r="K74" s="1">
-        <v>1000000</v>
+        <v>20</v>
       </c>
       <c r="L74" s="1">
         <f t="shared" si="3"/>
-        <v>640000</v>
+        <v>160000</v>
       </c>
       <c r="M74" s="1">
         <v>4</v>
@@ -3793,7 +3798,7 @@
     </row>
     <row r="75" customHeight="1" spans="3:13">
       <c r="C75" s="1">
-        <v>68</v>
+        <v>235</v>
       </c>
       <c r="D75" s="1">
         <v>5</v>
@@ -3802,23 +3807,23 @@
         <v>4000</v>
       </c>
       <c r="F75" s="1">
-        <f>40*M67</f>
+        <f>40*M68</f>
         <v>160</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I75" s="1">
         <v>5</v>
       </c>
       <c r="J75" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K75" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L75" s="1">
         <f t="shared" si="3"/>
@@ -3828,36 +3833,73 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="3:12">
-      <c r="C78" s="1">
-        <v>99</v>
-      </c>
-      <c r="D78" s="1">
+    <row r="76" customHeight="1" spans="3:13">
+      <c r="C76" s="1">
+        <v>236</v>
+      </c>
+      <c r="D76" s="1">
+        <v>5</v>
+      </c>
+      <c r="E76" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F76" s="1">
+        <f>40*M68</f>
+        <v>160</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I76" s="1">
+        <v>5</v>
+      </c>
+      <c r="J76" s="1">
+        <v>4002</v>
+      </c>
+      <c r="K76" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="L76" s="1">
+        <f t="shared" si="3"/>
+        <v>640000</v>
+      </c>
+      <c r="M76" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:12">
+      <c r="C79" s="1">
+        <v>999</v>
+      </c>
+      <c r="D79" s="1">
         <v>0</v>
       </c>
-      <c r="E78" s="6" t="s">
+      <c r="E79" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F79" s="1">
         <v>100</v>
       </c>
-      <c r="G78" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I78" s="1">
-        <v>5</v>
-      </c>
-      <c r="J78" s="1">
+      <c r="G79" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I79" s="1">
+        <v>5</v>
+      </c>
+      <c r="J79" s="1">
         <v>4006</v>
       </c>
-      <c r="K78" s="1">
+      <c r="K79" s="1">
         <v>1000</v>
       </c>
-      <c r="L78" s="1">
-        <f>E78*F78</f>
+      <c r="L79" s="1">
+        <f>E79*F79</f>
         <v>100000</v>
       </c>
     </row>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="90">
   <si>
     <t>#</t>
   </si>
@@ -1307,7 +1307,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M79"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1424,7 +1424,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>13</v>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="L6" s="1">
         <f t="shared" ref="L6:L9" si="0">E6*F6</f>
-        <v>20400</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:12">
@@ -1457,7 +1457,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="1">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>15</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="L7" s="1">
         <f t="shared" si="0"/>
-        <v>20400</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1490,7 +1490,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="1">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>17</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="L8" s="1">
         <f t="shared" si="0"/>
-        <v>20400</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:12">
@@ -2172,7 +2172,13 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="3:12">
+    <row r="29" customHeight="1" spans="1:12">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C29" s="1">
         <v>24</v>
       </c>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="93">
   <si>
     <t>#</t>
   </si>
@@ -237,6 +237,15 @@
   </si>
   <si>
     <t>极法宝自选</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>兑换改造石</t>
+  </si>
+  <si>
+    <t>改造石</t>
   </si>
   <si>
     <t>兑换专属之心*5</t>
@@ -1307,7 +1316,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1424,7 +1433,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>13</v>
@@ -1443,7 +1452,7 @@
       </c>
       <c r="L6" s="1">
         <f t="shared" ref="L6:L9" si="0">E6*F6</f>
-        <v>14400</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:12">
@@ -1457,7 +1466,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="1">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>15</v>
@@ -1476,7 +1485,7 @@
       </c>
       <c r="L7" s="1">
         <f t="shared" si="0"/>
-        <v>14400</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1490,7 +1499,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="1">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>17</v>
@@ -1509,7 +1518,7 @@
       </c>
       <c r="L8" s="1">
         <f t="shared" si="0"/>
-        <v>14400</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:12">
@@ -1574,7 +1583,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" ref="L10:L29" si="1">E10*F10</f>
+        <f t="shared" ref="L10:L30" si="1">E10*F10</f>
         <v>24000</v>
       </c>
     </row>
@@ -2211,305 +2220,301 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="3:13">
-      <c r="C31" s="1">
-        <v>101</v>
-      </c>
-      <c r="D31" s="1">
-        <v>1</v>
-      </c>
-      <c r="E31" s="1">
-        <v>500</v>
-      </c>
-      <c r="F31" s="1">
-        <f>20*M31</f>
-        <v>20</v>
-      </c>
-      <c r="G31" s="1" t="s">
+    <row r="30" customHeight="1" spans="3:12">
+      <c r="C30" s="1">
+        <v>23</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="F30" s="1">
+        <v>100</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I31" s="1">
-        <v>5</v>
-      </c>
-      <c r="J31" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K31" s="1">
-        <v>5</v>
-      </c>
-      <c r="L31" s="1">
-        <f t="shared" ref="L31:L39" si="2">E31*F31</f>
-        <v>10000</v>
-      </c>
-      <c r="M31" s="1">
-        <v>1</v>
+      <c r="H30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I30" s="1">
+        <v>5</v>
+      </c>
+      <c r="J30" s="1">
+        <v>4021</v>
+      </c>
+      <c r="K30" s="1">
+        <v>1</v>
+      </c>
+      <c r="L30" s="1">
+        <f t="shared" si="1"/>
+        <v>500000</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:13">
       <c r="C32" s="1">
+        <v>101</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
+        <v>500</v>
+      </c>
+      <c r="F32" s="1">
+        <f>20*M32</f>
+        <v>20</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I32" s="1">
+        <v>5</v>
+      </c>
+      <c r="J32" s="1">
+        <v>4010</v>
+      </c>
+      <c r="K32" s="1">
+        <v>5</v>
+      </c>
+      <c r="L32" s="1">
+        <f t="shared" ref="L32:L40" si="2">E32*F32</f>
+        <v>10000</v>
+      </c>
+      <c r="M32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:13">
+      <c r="C33" s="1">
         <v>102</v>
       </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1">
         <v>100</v>
       </c>
-      <c r="F32" s="1">
-        <f>300*M31</f>
+      <c r="F33" s="1">
+        <f>300*M32</f>
         <v>300</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I32" s="1">
-        <v>5</v>
-      </c>
-      <c r="J32" s="1">
+      <c r="G33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I33" s="1">
+        <v>5</v>
+      </c>
+      <c r="J33" s="1">
         <v>4007</v>
       </c>
-      <c r="K32" s="1">
+      <c r="K33" s="1">
         <v>1000</v>
       </c>
-      <c r="L32" s="1">
+      <c r="L33" s="1">
         <f t="shared" si="2"/>
         <v>30000</v>
       </c>
-      <c r="M32" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:13">
-      <c r="C33" s="1">
+      <c r="M33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:13">
+      <c r="C34" s="1">
         <v>103</v>
       </c>
-      <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1">
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+      <c r="E34" s="1">
         <v>100</v>
       </c>
-      <c r="F33" s="1">
-        <f>500*M31</f>
+      <c r="F34" s="1">
+        <f>500*M32</f>
         <v>500</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I33" s="1">
-        <v>5</v>
-      </c>
-      <c r="J33" s="1">
+      <c r="G34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I34" s="1">
+        <v>5</v>
+      </c>
+      <c r="J34" s="1">
         <v>4101</v>
       </c>
-      <c r="K33" s="1">
+      <c r="K34" s="1">
         <v>1000</v>
       </c>
-      <c r="L33" s="1">
+      <c r="L34" s="1">
         <f t="shared" si="2"/>
         <v>50000</v>
       </c>
-      <c r="M33" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:13">
-      <c r="C34" s="1">
+      <c r="M34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:13">
+      <c r="C35" s="1">
         <v>104</v>
       </c>
-      <c r="D34" s="1">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1">
+      <c r="D35" s="1">
+        <v>1</v>
+      </c>
+      <c r="E35" s="1">
         <v>1000</v>
       </c>
-      <c r="F34" s="1">
-        <f>5*M31</f>
-        <v>5</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I34" s="1">
+      <c r="F35" s="1">
+        <f>5*M32</f>
+        <v>5</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I35" s="1">
         <v>15</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J35" s="1">
         <v>4014</v>
       </c>
-      <c r="K34" s="1">
+      <c r="K35" s="1">
         <v>100</v>
       </c>
-      <c r="L34" s="1">
+      <c r="L35" s="1">
         <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="M34" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:13">
-      <c r="C35" s="1">
+      <c r="M35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:13">
+      <c r="C36" s="1">
         <v>105</v>
       </c>
-      <c r="D35" s="1">
-        <v>1</v>
-      </c>
-      <c r="E35" s="1">
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1">
         <v>500</v>
       </c>
-      <c r="F35" s="1">
-        <f>20*M31</f>
+      <c r="F36" s="1">
+        <f>20*M32</f>
         <v>20</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I35" s="1">
-        <v>5</v>
-      </c>
-      <c r="J35" s="1">
+      <c r="G36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I36" s="1">
+        <v>5</v>
+      </c>
+      <c r="J36" s="1">
         <v>4012</v>
       </c>
-      <c r="K35" s="1">
+      <c r="K36" s="1">
         <v>200</v>
       </c>
-      <c r="L35" s="1">
+      <c r="L36" s="1">
         <f t="shared" si="2"/>
         <v>10000</v>
       </c>
-      <c r="M35" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:13">
-      <c r="C36" s="1">
+      <c r="M36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:13">
+      <c r="C37" s="1">
         <v>106</v>
       </c>
-      <c r="D36" s="1">
-        <v>1</v>
-      </c>
-      <c r="E36" s="1">
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+      <c r="E37" s="1">
         <v>5000</v>
       </c>
-      <c r="F36" s="1">
-        <f>5*M31</f>
-        <v>5</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I36" s="1">
-        <v>5</v>
-      </c>
-      <c r="J36" s="1">
+      <c r="F37" s="1">
+        <f>5*M32</f>
+        <v>5</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I37" s="1">
+        <v>5</v>
+      </c>
+      <c r="J37" s="1">
         <v>4011</v>
       </c>
-      <c r="K36" s="1">
-        <v>1</v>
-      </c>
-      <c r="L36" s="1">
+      <c r="K37" s="1">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1">
         <f t="shared" si="2"/>
         <v>25000</v>
       </c>
-      <c r="M36" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:13">
-      <c r="C37" s="1">
+      <c r="M37" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:13">
+      <c r="C38" s="1">
         <v>107</v>
       </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
-      <c r="E37" s="1">
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
         <v>500</v>
       </c>
-      <c r="F37" s="1">
-        <f>10*M31</f>
+      <c r="F38" s="1">
+        <f>10*M32</f>
         <v>10</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I37" s="1">
-        <v>5</v>
-      </c>
-      <c r="J37" s="1">
+      <c r="G38" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I38" s="1">
+        <v>5</v>
+      </c>
+      <c r="J38" s="1">
         <v>4102</v>
       </c>
-      <c r="K37" s="1">
+      <c r="K38" s="1">
         <v>20</v>
       </c>
-      <c r="L37" s="1">
+      <c r="L38" s="1">
         <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="M37" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:13">
-      <c r="C38" s="1">
-        <v>108</v>
-      </c>
-      <c r="D38" s="1">
-        <v>1</v>
-      </c>
-      <c r="E38" s="1">
-        <v>500</v>
-      </c>
-      <c r="F38" s="1">
-        <f>40*M31</f>
-        <v>40</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I38" s="1">
-        <v>5</v>
-      </c>
-      <c r="J38" s="1">
-        <v>4001</v>
-      </c>
-      <c r="K38" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="L38" s="1">
-        <f t="shared" si="2"/>
-        <v>20000</v>
-      </c>
       <c r="M38" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:13">
       <c r="C39" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D39" s="1">
         <v>1</v>
@@ -2518,23 +2523,23 @@
         <v>500</v>
       </c>
       <c r="F39" s="1">
-        <f>40*M31</f>
+        <f>40*M32</f>
         <v>40</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I39" s="1">
         <v>5</v>
       </c>
       <c r="J39" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K39" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L39" s="1">
         <f t="shared" si="2"/>
@@ -2544,305 +2549,305 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="3:13">
-      <c r="C41" s="1">
-        <v>201</v>
-      </c>
-      <c r="D41" s="1">
-        <v>2</v>
-      </c>
-      <c r="E41" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F41" s="1">
-        <f>20*M41</f>
-        <v>20</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I41" s="1">
-        <v>5</v>
-      </c>
-      <c r="J41" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K41" s="1">
-        <v>5</v>
-      </c>
-      <c r="L41" s="1">
-        <f t="shared" ref="L41:L76" si="3">E41*F41</f>
+    <row r="40" customHeight="1" spans="3:13">
+      <c r="C40" s="1">
+        <v>109</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1">
+        <v>500</v>
+      </c>
+      <c r="F40" s="1">
+        <f>40*M32</f>
+        <v>40</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I40" s="1">
+        <v>5</v>
+      </c>
+      <c r="J40" s="1">
+        <v>4002</v>
+      </c>
+      <c r="K40" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="L40" s="1">
+        <f t="shared" si="2"/>
         <v>20000</v>
       </c>
-      <c r="M41" s="1">
+      <c r="M40" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:13">
       <c r="C42" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
       </c>
       <c r="E42" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F42" s="1">
+        <f>20*M42</f>
+        <v>20</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I42" s="1">
+        <v>5</v>
+      </c>
+      <c r="J42" s="1">
+        <v>4010</v>
+      </c>
+      <c r="K42" s="1">
+        <v>5</v>
+      </c>
+      <c r="L42" s="1">
+        <f t="shared" ref="L42:L77" si="3">E42*F42</f>
+        <v>20000</v>
+      </c>
+      <c r="M42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:13">
+      <c r="C43" s="1">
+        <v>202</v>
+      </c>
+      <c r="D43" s="1">
+        <v>2</v>
+      </c>
+      <c r="E43" s="4">
         <v>200</v>
       </c>
-      <c r="F42" s="1">
-        <f>300*M41</f>
+      <c r="F43" s="1">
+        <f>300*M42</f>
         <v>300</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I42" s="1">
-        <v>5</v>
-      </c>
-      <c r="J42" s="1">
+      <c r="G43" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I43" s="1">
+        <v>5</v>
+      </c>
+      <c r="J43" s="1">
         <v>4007</v>
       </c>
-      <c r="K42" s="1">
+      <c r="K43" s="1">
         <v>1000</v>
       </c>
-      <c r="L42" s="1">
+      <c r="L43" s="1">
         <f t="shared" si="3"/>
         <v>60000</v>
       </c>
-      <c r="M42" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:13">
-      <c r="C43" s="1">
+      <c r="M43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:13">
+      <c r="C44" s="1">
         <v>203</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D44" s="1">
         <v>2</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E44" s="4">
         <v>200</v>
       </c>
-      <c r="F43" s="1">
-        <f>500*M41</f>
+      <c r="F44" s="1">
+        <f>500*M42</f>
         <v>500</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I43" s="1">
-        <v>5</v>
-      </c>
-      <c r="J43" s="1">
+      <c r="G44" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I44" s="1">
+        <v>5</v>
+      </c>
+      <c r="J44" s="1">
         <v>4101</v>
       </c>
-      <c r="K43" s="1">
+      <c r="K44" s="1">
         <v>1000</v>
       </c>
-      <c r="L43" s="1">
+      <c r="L44" s="1">
         <f t="shared" si="3"/>
         <v>100000</v>
       </c>
-      <c r="M43" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:13">
-      <c r="C44" s="1">
+      <c r="M44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:13">
+      <c r="C45" s="1">
         <v>204</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D45" s="1">
         <v>2</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E45" s="4">
         <v>2000</v>
       </c>
-      <c r="F44" s="1">
-        <f>5*M41</f>
-        <v>5</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I44" s="1">
+      <c r="F45" s="1">
+        <f>5*M42</f>
+        <v>5</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I45" s="1">
         <v>15</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J45" s="1">
         <v>4014</v>
       </c>
-      <c r="K44" s="1">
+      <c r="K45" s="1">
         <v>100</v>
       </c>
-      <c r="L44" s="1">
+      <c r="L45" s="1">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
-      <c r="M44" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:13">
-      <c r="C45" s="1">
+      <c r="M45" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:13">
+      <c r="C46" s="1">
         <v>205</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D46" s="1">
         <v>2</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E46" s="4">
         <v>1000</v>
       </c>
-      <c r="F45" s="1">
-        <f>20*M41</f>
+      <c r="F46" s="1">
+        <f>20*M42</f>
         <v>20</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I45" s="1">
-        <v>5</v>
-      </c>
-      <c r="J45" s="1">
+      <c r="G46" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I46" s="1">
+        <v>5</v>
+      </c>
+      <c r="J46" s="1">
         <v>4012</v>
       </c>
-      <c r="K45" s="1">
+      <c r="K46" s="1">
         <v>200</v>
       </c>
-      <c r="L45" s="1">
+      <c r="L46" s="1">
         <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="M45" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:13">
-      <c r="C46" s="1">
+      <c r="M46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:13">
+      <c r="C47" s="1">
         <v>206</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D47" s="1">
         <v>2</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E47" s="4">
         <v>10000</v>
       </c>
-      <c r="F46" s="1">
-        <f>5*M41</f>
-        <v>5</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I46" s="1">
-        <v>5</v>
-      </c>
-      <c r="J46" s="1">
+      <c r="F47" s="1">
+        <f>5*M42</f>
+        <v>5</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I47" s="1">
+        <v>5</v>
+      </c>
+      <c r="J47" s="1">
         <v>4011</v>
       </c>
-      <c r="K46" s="1">
-        <v>1</v>
-      </c>
-      <c r="L46" s="1">
+      <c r="K47" s="1">
+        <v>1</v>
+      </c>
+      <c r="L47" s="1">
         <f t="shared" si="3"/>
         <v>50000</v>
       </c>
-      <c r="M46" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:13">
-      <c r="C47" s="1">
+      <c r="M47" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:13">
+      <c r="C48" s="1">
         <v>207</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D48" s="1">
         <v>2</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E48" s="4">
         <v>1000</v>
       </c>
-      <c r="F47" s="1">
-        <f>10*M41</f>
+      <c r="F48" s="1">
+        <f>10*M42</f>
         <v>10</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I47" s="1">
-        <v>5</v>
-      </c>
-      <c r="J47" s="1">
+      <c r="G48" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I48" s="1">
+        <v>5</v>
+      </c>
+      <c r="J48" s="1">
         <v>4102</v>
       </c>
-      <c r="K47" s="1">
+      <c r="K48" s="1">
         <v>20</v>
       </c>
-      <c r="L47" s="1">
+      <c r="L48" s="1">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
-      <c r="M47" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:13">
-      <c r="C48" s="1">
-        <v>208</v>
-      </c>
-      <c r="D48" s="1">
-        <v>2</v>
-      </c>
-      <c r="E48" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F48" s="1">
-        <f>40*M41</f>
-        <v>40</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I48" s="1">
-        <v>5</v>
-      </c>
-      <c r="J48" s="1">
-        <v>4001</v>
-      </c>
-      <c r="K48" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="L48" s="1">
-        <f t="shared" si="3"/>
-        <v>40000</v>
-      </c>
       <c r="M48" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:13">
       <c r="C49" s="1">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D49" s="1">
         <v>2</v>
@@ -2851,23 +2856,23 @@
         <v>1000</v>
       </c>
       <c r="F49" s="1">
-        <f>40*M41</f>
+        <f>40*M42</f>
         <v>40</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I49" s="1">
         <v>5</v>
       </c>
       <c r="J49" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K49" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L49" s="1">
         <f t="shared" si="3"/>
@@ -2879,32 +2884,32 @@
     </row>
     <row r="50" customHeight="1" spans="3:13">
       <c r="C50" s="1">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D50" s="1">
-        <v>3</v>
-      </c>
-      <c r="E50" s="1">
-        <v>2000</v>
+        <v>2</v>
+      </c>
+      <c r="E50" s="4">
+        <v>1000</v>
       </c>
       <c r="F50" s="1">
-        <f>20*M50</f>
-        <v>20</v>
+        <f>40*M42</f>
+        <v>40</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="I50" s="1">
         <v>5</v>
       </c>
       <c r="J50" s="1">
-        <v>4010</v>
+        <v>4002</v>
       </c>
       <c r="K50" s="1">
-        <v>5</v>
+        <v>6000000</v>
       </c>
       <c r="L50" s="1">
         <f t="shared" si="3"/>
@@ -2916,36 +2921,36 @@
     </row>
     <row r="51" customHeight="1" spans="3:13">
       <c r="C51" s="1">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D51" s="1">
         <v>3</v>
       </c>
       <c r="E51" s="1">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="F51" s="1">
-        <f>300*M50</f>
-        <v>300</v>
+        <f>20*M51</f>
+        <v>20</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I51" s="1">
         <v>5</v>
       </c>
       <c r="J51" s="1">
-        <v>4007</v>
+        <v>4010</v>
       </c>
       <c r="K51" s="1">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L51" s="1">
         <f t="shared" si="3"/>
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="M51" s="1">
         <v>1</v>
@@ -2953,7 +2958,7 @@
     </row>
     <row r="52" customHeight="1" spans="3:13">
       <c r="C52" s="1">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D52" s="1">
         <v>3</v>
@@ -2962,27 +2967,27 @@
         <v>400</v>
       </c>
       <c r="F52" s="1">
-        <f>500*M50</f>
-        <v>500</v>
+        <f>300*M51</f>
+        <v>300</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I52" s="1">
         <v>5</v>
       </c>
       <c r="J52" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K52" s="1">
         <v>1000</v>
       </c>
       <c r="L52" s="1">
         <f t="shared" si="3"/>
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="M52" s="1">
         <v>1</v>
@@ -2990,36 +2995,36 @@
     </row>
     <row r="53" customHeight="1" spans="3:13">
       <c r="C53" s="1">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D53" s="1">
         <v>3</v>
       </c>
       <c r="E53" s="1">
-        <v>4000</v>
+        <v>400</v>
       </c>
       <c r="F53" s="1">
-        <f>5*M50</f>
-        <v>5</v>
+        <f>500*M51</f>
+        <v>500</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I53" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J53" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="K53" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L53" s="1">
         <f t="shared" si="3"/>
-        <v>20000</v>
+        <v>200000</v>
       </c>
       <c r="M53" s="1">
         <v>1</v>
@@ -3027,36 +3032,36 @@
     </row>
     <row r="54" customHeight="1" spans="3:13">
       <c r="C54" s="1">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D54" s="1">
         <v>3</v>
       </c>
       <c r="E54" s="1">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="F54" s="1">
-        <f>20*M50</f>
-        <v>20</v>
+        <f>5*M51</f>
+        <v>5</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I54" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J54" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="K54" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L54" s="1">
         <f t="shared" si="3"/>
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="M54" s="1">
         <v>1</v>
@@ -3064,36 +3069,36 @@
     </row>
     <row r="55" customHeight="1" spans="3:13">
       <c r="C55" s="1">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D55" s="1">
         <v>3</v>
       </c>
       <c r="E55" s="1">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="F55" s="1">
-        <f>5*M50</f>
-        <v>5</v>
+        <f>20*M51</f>
+        <v>20</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I55" s="1">
         <v>5</v>
       </c>
       <c r="J55" s="1">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="K55" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="L55" s="1">
         <f t="shared" si="3"/>
-        <v>100000</v>
+        <v>40000</v>
       </c>
       <c r="M55" s="1">
         <v>1</v>
@@ -3101,36 +3106,36 @@
     </row>
     <row r="56" customHeight="1" spans="3:13">
       <c r="C56" s="1">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D56" s="1">
         <v>3</v>
       </c>
       <c r="E56" s="1">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="F56" s="1">
-        <f>10*M50</f>
-        <v>10</v>
+        <f>5*M51</f>
+        <v>5</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I56" s="1">
         <v>5</v>
       </c>
       <c r="J56" s="1">
-        <v>4102</v>
+        <v>4011</v>
       </c>
       <c r="K56" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L56" s="1">
         <f t="shared" si="3"/>
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="M56" s="1">
         <v>1</v>
@@ -3138,7 +3143,7 @@
     </row>
     <row r="57" customHeight="1" spans="3:13">
       <c r="C57" s="1">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D57" s="1">
         <v>3</v>
@@ -3147,27 +3152,27 @@
         <v>2000</v>
       </c>
       <c r="F57" s="1">
-        <f>40*M50</f>
-        <v>40</v>
+        <f>10*M51</f>
+        <v>10</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I57" s="1">
         <v>5</v>
       </c>
       <c r="J57" s="1">
-        <v>4001</v>
+        <v>4102</v>
       </c>
       <c r="K57" s="1">
-        <v>1000000</v>
+        <v>20</v>
       </c>
       <c r="L57" s="1">
         <f t="shared" si="3"/>
-        <v>80000</v>
+        <v>20000</v>
       </c>
       <c r="M57" s="1">
         <v>1</v>
@@ -3175,7 +3180,7 @@
     </row>
     <row r="58" customHeight="1" spans="3:13">
       <c r="C58" s="1">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D58" s="1">
         <v>3</v>
@@ -3184,23 +3189,23 @@
         <v>2000</v>
       </c>
       <c r="F58" s="1">
-        <f>40*M50</f>
+        <f>40*M51</f>
         <v>40</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I58" s="1">
         <v>5</v>
       </c>
       <c r="J58" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K58" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L58" s="1">
         <f t="shared" si="3"/>
@@ -3212,36 +3217,36 @@
     </row>
     <row r="59" customHeight="1" spans="3:13">
       <c r="C59" s="1">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D59" s="1">
-        <v>4</v>
-      </c>
-      <c r="E59" s="4">
-        <v>3000</v>
+        <v>3</v>
+      </c>
+      <c r="E59" s="1">
+        <v>2000</v>
       </c>
       <c r="F59" s="1">
-        <f>20*M59</f>
-        <v>20</v>
+        <f>40*M51</f>
+        <v>40</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="I59" s="1">
         <v>5</v>
       </c>
       <c r="J59" s="1">
-        <v>4010</v>
+        <v>4002</v>
       </c>
       <c r="K59" s="1">
-        <v>5</v>
+        <v>6000000</v>
       </c>
       <c r="L59" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="M59" s="1">
         <v>1</v>
@@ -3249,36 +3254,36 @@
     </row>
     <row r="60" customHeight="1" spans="3:13">
       <c r="C60" s="1">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D60" s="1">
         <v>4</v>
       </c>
       <c r="E60" s="4">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="F60" s="1">
-        <f>300*M59</f>
-        <v>300</v>
+        <f>20*M60</f>
+        <v>20</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I60" s="1">
         <v>5</v>
       </c>
       <c r="J60" s="1">
-        <v>4007</v>
+        <v>4010</v>
       </c>
       <c r="K60" s="1">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L60" s="1">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>60000</v>
       </c>
       <c r="M60" s="1">
         <v>1</v>
@@ -3286,7 +3291,7 @@
     </row>
     <row r="61" customHeight="1" spans="3:13">
       <c r="C61" s="1">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D61" s="1">
         <v>4</v>
@@ -3295,27 +3300,27 @@
         <v>600</v>
       </c>
       <c r="F61" s="1">
-        <f>500*M59</f>
-        <v>500</v>
+        <f>300*M60</f>
+        <v>300</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I61" s="1">
         <v>5</v>
       </c>
       <c r="J61" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K61" s="1">
         <v>1000</v>
       </c>
       <c r="L61" s="1">
         <f t="shared" si="3"/>
-        <v>300000</v>
+        <v>180000</v>
       </c>
       <c r="M61" s="1">
         <v>1</v>
@@ -3323,36 +3328,36 @@
     </row>
     <row r="62" customHeight="1" spans="3:13">
       <c r="C62" s="1">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D62" s="1">
         <v>4</v>
       </c>
       <c r="E62" s="4">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="F62" s="1">
-        <f>5*M59</f>
-        <v>5</v>
+        <f>500*M60</f>
+        <v>500</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I62" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J62" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="K62" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L62" s="1">
         <f t="shared" si="3"/>
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="M62" s="1">
         <v>1</v>
@@ -3360,36 +3365,36 @@
     </row>
     <row r="63" customHeight="1" spans="3:13">
       <c r="C63" s="1">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D63" s="1">
         <v>4</v>
       </c>
       <c r="E63" s="4">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="F63" s="1">
-        <f>20*M59</f>
-        <v>20</v>
+        <f>5*M60</f>
+        <v>5</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I63" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J63" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="K63" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L63" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="M63" s="1">
         <v>1</v>
@@ -3397,36 +3402,36 @@
     </row>
     <row r="64" customHeight="1" spans="3:13">
       <c r="C64" s="1">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D64" s="1">
         <v>4</v>
       </c>
       <c r="E64" s="4">
-        <v>30000</v>
+        <v>3000</v>
       </c>
       <c r="F64" s="1">
-        <f>5*M59</f>
-        <v>5</v>
+        <f>20*M60</f>
+        <v>20</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I64" s="1">
         <v>5</v>
       </c>
       <c r="J64" s="1">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="K64" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="L64" s="1">
         <f t="shared" si="3"/>
-        <v>150000</v>
+        <v>60000</v>
       </c>
       <c r="M64" s="1">
         <v>1</v>
@@ -3434,36 +3439,36 @@
     </row>
     <row r="65" customHeight="1" spans="3:13">
       <c r="C65" s="1">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D65" s="1">
         <v>4</v>
       </c>
       <c r="E65" s="4">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="F65" s="1">
-        <f>10*M59</f>
-        <v>10</v>
+        <f>5*M60</f>
+        <v>5</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I65" s="1">
         <v>5</v>
       </c>
       <c r="J65" s="1">
-        <v>4102</v>
+        <v>4011</v>
       </c>
       <c r="K65" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L65" s="1">
         <f t="shared" si="3"/>
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="M65" s="1">
         <v>1</v>
@@ -3471,7 +3476,7 @@
     </row>
     <row r="66" customHeight="1" spans="3:13">
       <c r="C66" s="1">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D66" s="1">
         <v>4</v>
@@ -3480,27 +3485,27 @@
         <v>3000</v>
       </c>
       <c r="F66" s="1">
-        <f>40*M59</f>
-        <v>40</v>
+        <f>10*M60</f>
+        <v>10</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I66" s="1">
         <v>5</v>
       </c>
       <c r="J66" s="1">
-        <v>4001</v>
+        <v>4102</v>
       </c>
       <c r="K66" s="1">
-        <v>1000000</v>
+        <v>20</v>
       </c>
       <c r="L66" s="1">
         <f t="shared" si="3"/>
-        <v>120000</v>
+        <v>30000</v>
       </c>
       <c r="M66" s="1">
         <v>1</v>
@@ -3508,7 +3513,7 @@
     </row>
     <row r="67" customHeight="1" spans="3:13">
       <c r="C67" s="1">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D67" s="1">
         <v>4</v>
@@ -3517,23 +3522,23 @@
         <v>3000</v>
       </c>
       <c r="F67" s="1">
-        <f>40*M59</f>
+        <f>40*M60</f>
         <v>40</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I67" s="1">
         <v>5</v>
       </c>
       <c r="J67" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K67" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L67" s="1">
         <f t="shared" si="3"/>
@@ -3545,73 +3550,73 @@
     </row>
     <row r="68" customHeight="1" spans="3:13">
       <c r="C68" s="1">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D68" s="1">
-        <v>5</v>
-      </c>
-      <c r="E68" s="1">
-        <v>4000</v>
+        <v>4</v>
+      </c>
+      <c r="E68" s="4">
+        <v>3000</v>
       </c>
       <c r="F68" s="1">
-        <f>20*M68</f>
-        <v>80</v>
+        <f>40*M60</f>
+        <v>40</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="I68" s="1">
         <v>5</v>
       </c>
       <c r="J68" s="1">
-        <v>4010</v>
+        <v>4002</v>
       </c>
       <c r="K68" s="1">
-        <v>5</v>
+        <v>6000000</v>
       </c>
       <c r="L68" s="1">
         <f t="shared" si="3"/>
-        <v>320000</v>
+        <v>120000</v>
       </c>
       <c r="M68" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:13">
       <c r="C69" s="1">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D69" s="1">
         <v>5</v>
       </c>
       <c r="E69" s="1">
-        <v>800</v>
+        <v>4000</v>
       </c>
       <c r="F69" s="1">
-        <f>300*M68</f>
-        <v>1200</v>
+        <f>20*M69</f>
+        <v>80</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I69" s="1">
         <v>5</v>
       </c>
       <c r="J69" s="1">
-        <v>4007</v>
+        <v>4010</v>
       </c>
       <c r="K69" s="1">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L69" s="1">
         <f t="shared" si="3"/>
-        <v>960000</v>
+        <v>320000</v>
       </c>
       <c r="M69" s="1">
         <v>4</v>
@@ -3619,7 +3624,7 @@
     </row>
     <row r="70" customHeight="1" spans="3:13">
       <c r="C70" s="1">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D70" s="1">
         <v>5</v>
@@ -3628,27 +3633,27 @@
         <v>800</v>
       </c>
       <c r="F70" s="1">
-        <f>500*M68</f>
-        <v>2000</v>
+        <f>300*M69</f>
+        <v>1200</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I70" s="1">
         <v>5</v>
       </c>
       <c r="J70" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K70" s="1">
         <v>1000</v>
       </c>
       <c r="L70" s="1">
         <f t="shared" si="3"/>
-        <v>1600000</v>
+        <v>960000</v>
       </c>
       <c r="M70" s="1">
         <v>4</v>
@@ -3656,36 +3661,36 @@
     </row>
     <row r="71" customHeight="1" spans="3:13">
       <c r="C71" s="1">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D71" s="1">
         <v>5</v>
       </c>
       <c r="E71" s="1">
-        <v>8000</v>
+        <v>800</v>
       </c>
       <c r="F71" s="1">
-        <f>5*M68</f>
-        <v>20</v>
+        <f>500*M69</f>
+        <v>2000</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I71" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J71" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="K71" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="L71" s="1">
         <f t="shared" si="3"/>
-        <v>160000</v>
+        <v>1600000</v>
       </c>
       <c r="M71" s="1">
         <v>4</v>
@@ -3693,36 +3698,36 @@
     </row>
     <row r="72" customHeight="1" spans="3:13">
       <c r="C72" s="1">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D72" s="1">
         <v>5</v>
       </c>
       <c r="E72" s="1">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="F72" s="1">
-        <f>20*M68</f>
+        <f>5*M69</f>
+        <v>20</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H72" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G72" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="I72" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J72" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="K72" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L72" s="1">
         <f t="shared" si="3"/>
-        <v>320000</v>
+        <v>160000</v>
       </c>
       <c r="M72" s="1">
         <v>4</v>
@@ -3730,36 +3735,36 @@
     </row>
     <row r="73" customHeight="1" spans="3:13">
       <c r="C73" s="1">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D73" s="1">
         <v>5</v>
       </c>
       <c r="E73" s="1">
-        <v>40000</v>
+        <v>4000</v>
       </c>
       <c r="F73" s="1">
-        <f>5*M68</f>
-        <v>20</v>
+        <f>20*M69</f>
+        <v>80</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I73" s="1">
         <v>5</v>
       </c>
       <c r="J73" s="1">
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="K73" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="L73" s="1">
         <f t="shared" si="3"/>
-        <v>800000</v>
+        <v>320000</v>
       </c>
       <c r="M73" s="1">
         <v>4</v>
@@ -3767,36 +3772,36 @@
     </row>
     <row r="74" customHeight="1" spans="3:13">
       <c r="C74" s="1">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D74" s="1">
         <v>5</v>
       </c>
       <c r="E74" s="1">
-        <v>4000</v>
+        <v>40000</v>
       </c>
       <c r="F74" s="1">
-        <f>10*M68</f>
-        <v>40</v>
+        <f>5*M69</f>
+        <v>20</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I74" s="1">
         <v>5</v>
       </c>
       <c r="J74" s="1">
-        <v>4102</v>
+        <v>4011</v>
       </c>
       <c r="K74" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L74" s="1">
         <f t="shared" si="3"/>
-        <v>160000</v>
+        <v>800000</v>
       </c>
       <c r="M74" s="1">
         <v>4</v>
@@ -3804,7 +3809,7 @@
     </row>
     <row r="75" customHeight="1" spans="3:13">
       <c r="C75" s="1">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D75" s="1">
         <v>5</v>
@@ -3813,27 +3818,27 @@
         <v>4000</v>
       </c>
       <c r="F75" s="1">
-        <f>40*M68</f>
-        <v>160</v>
+        <f>10*M69</f>
+        <v>40</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I75" s="1">
         <v>5</v>
       </c>
       <c r="J75" s="1">
-        <v>4001</v>
+        <v>4102</v>
       </c>
       <c r="K75" s="1">
-        <v>1000000</v>
+        <v>20</v>
       </c>
       <c r="L75" s="1">
         <f t="shared" si="3"/>
-        <v>640000</v>
+        <v>160000</v>
       </c>
       <c r="M75" s="1">
         <v>4</v>
@@ -3841,7 +3846,7 @@
     </row>
     <row r="76" customHeight="1" spans="3:13">
       <c r="C76" s="1">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D76" s="1">
         <v>5</v>
@@ -3850,23 +3855,23 @@
         <v>4000</v>
       </c>
       <c r="F76" s="1">
-        <f>40*M68</f>
+        <f>40*M69</f>
         <v>160</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I76" s="1">
         <v>5</v>
       </c>
       <c r="J76" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="K76" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="L76" s="1">
         <f t="shared" si="3"/>
@@ -3876,36 +3881,73 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="3:12">
-      <c r="C79" s="1">
+    <row r="77" customHeight="1" spans="3:13">
+      <c r="C77" s="1">
+        <v>236</v>
+      </c>
+      <c r="D77" s="1">
+        <v>5</v>
+      </c>
+      <c r="E77" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F77" s="1">
+        <f>40*M69</f>
+        <v>160</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I77" s="1">
+        <v>5</v>
+      </c>
+      <c r="J77" s="1">
+        <v>4002</v>
+      </c>
+      <c r="K77" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="L77" s="1">
+        <f t="shared" si="3"/>
+        <v>640000</v>
+      </c>
+      <c r="M77" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:12">
+      <c r="C80" s="1">
         <v>999</v>
       </c>
-      <c r="D79" s="1">
+      <c r="D80" s="1">
         <v>0</v>
       </c>
-      <c r="E79" s="6" t="s">
+      <c r="E80" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F80" s="1">
         <v>100</v>
       </c>
-      <c r="G79" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I79" s="1">
-        <v>5</v>
-      </c>
-      <c r="J79" s="1">
+      <c r="G80" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I80" s="1">
+        <v>5</v>
+      </c>
+      <c r="J80" s="1">
         <v>4006</v>
       </c>
-      <c r="K79" s="1">
+      <c r="K80" s="1">
         <v>1000</v>
       </c>
-      <c r="L79" s="1">
-        <f>E79*F79</f>
+      <c r="L80" s="1">
+        <f>E80*F80</f>
         <v>100000</v>
       </c>
     </row>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -2222,7 +2222,7 @@
     </row>
     <row r="30" customHeight="1" spans="3:12">
       <c r="C30" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -95,40 +95,40 @@
     <t>凤凰之羽</t>
   </si>
   <si>
-    <t>兑换战神时装包*1</t>
-  </si>
-  <si>
-    <t>战神时装包</t>
-  </si>
-  <si>
-    <t>兑换恶魔时装包*1</t>
-  </si>
-  <si>
-    <t>恶魔时装包</t>
-  </si>
-  <si>
-    <t>兑换幽灵时装包*1</t>
-  </si>
-  <si>
-    <t>幽灵时装包</t>
-  </si>
-  <si>
-    <t>兑换圣战时装包*1</t>
-  </si>
-  <si>
-    <t>圣战时装包</t>
-  </si>
-  <si>
-    <t>兑换法神时装包*1</t>
-  </si>
-  <si>
-    <t>法神时装包</t>
-  </si>
-  <si>
-    <t>兑换天尊时装包*1</t>
-  </si>
-  <si>
-    <t>天尊时装包</t>
+    <t>兑换斩仙时装包*1</t>
+  </si>
+  <si>
+    <t>斩仙时装包</t>
+  </si>
+  <si>
+    <t>兑换魔尊时装包*1</t>
+  </si>
+  <si>
+    <t>魔尊时装包</t>
+  </si>
+  <si>
+    <t>兑换幽冥时装包*1</t>
+  </si>
+  <si>
+    <t>幽冥时装包</t>
+  </si>
+  <si>
+    <t>兑换战魂时装包*1</t>
+  </si>
+  <si>
+    <t>战魂时装包</t>
+  </si>
+  <si>
+    <t>兑换法魂时装包*1</t>
+  </si>
+  <si>
+    <t>法魂时装包</t>
+  </si>
+  <si>
+    <t>兑换道魂时装包*1</t>
+  </si>
+  <si>
+    <t>道魂时装包</t>
   </si>
   <si>
     <t>兑换图鉴龙之力*1</t>
@@ -1320,11 +1320,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="11.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.2545454545455" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="7" width="22.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1272727272727" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.8727272727273" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.5" style="1" customWidth="1"/>
     <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
@@ -3929,7 +3929,7 @@
         <v>49</v>
       </c>
       <c r="F80" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>91</v>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="L80" s="1">
         <f>E80*F80</f>
-        <v>100000</v>
+        <v>50000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="99">
   <si>
     <t>#</t>
   </si>
@@ -248,6 +248,24 @@
     <t>改造石</t>
   </si>
   <si>
+    <t>兑换宠物口粮*100</t>
+  </si>
+  <si>
+    <t>宠物口粮</t>
+  </si>
+  <si>
+    <t>兑换红装精华*1</t>
+  </si>
+  <si>
+    <t>红装精华</t>
+  </si>
+  <si>
+    <t>兑换天赋秘籍*1</t>
+  </si>
+  <si>
+    <t>天赋秘籍</t>
+  </si>
+  <si>
     <t>兑换专属之心*5</t>
   </si>
   <si>
@@ -278,10 +296,10 @@
     <t>传世精华</t>
   </si>
   <si>
-    <t>兑换红装精华*1</t>
-  </si>
-  <si>
-    <t>红装精华</t>
+    <t>兑换金装精华*1</t>
+  </si>
+  <si>
+    <t>金装精华</t>
   </si>
   <si>
     <t>兑换高级书页*20</t>
@@ -1316,15 +1334,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M80"/>
+  <dimension ref="C1:M86"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="11.2545454545455" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.2583333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="7" width="22.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1272727272727" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.8727272727273" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.875" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.5" style="1" customWidth="1"/>
     <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
@@ -1433,7 +1451,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>13</v>
@@ -1452,7 +1470,7 @@
       </c>
       <c r="L6" s="1">
         <f t="shared" ref="L6:L9" si="0">E6*F6</f>
-        <v>20400</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:12">
@@ -1466,7 +1484,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="1">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>15</v>
@@ -1485,7 +1503,7 @@
       </c>
       <c r="L7" s="1">
         <f t="shared" si="0"/>
-        <v>20400</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1499,7 +1517,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="1">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>17</v>
@@ -1518,7 +1536,7 @@
       </c>
       <c r="L8" s="1">
         <f t="shared" si="0"/>
-        <v>20400</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:12">
@@ -1532,7 +1550,7 @@
         <v>19</v>
       </c>
       <c r="F9" s="1">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>20</v>
@@ -1551,7 +1569,7 @@
       </c>
       <c r="L9" s="1">
         <f t="shared" si="0"/>
-        <v>14000</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:12">
@@ -1565,7 +1583,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="1">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>22</v>
@@ -1583,8 +1601,8 @@
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" ref="L10:L30" si="1">E10*F10</f>
-        <v>24000</v>
+        <f t="shared" ref="L10:L33" si="1">E10*F10</f>
+        <v>60000</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:12">
@@ -1598,7 +1616,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="1">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>24</v>
@@ -1617,7 +1635,7 @@
       </c>
       <c r="L11" s="1">
         <f t="shared" si="1"/>
-        <v>24000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:12">
@@ -1631,7 +1649,7 @@
         <v>12</v>
       </c>
       <c r="F12" s="1">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>26</v>
@@ -1650,7 +1668,7 @@
       </c>
       <c r="L12" s="1">
         <f t="shared" si="1"/>
-        <v>24000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:12">
@@ -1664,7 +1682,7 @@
         <v>19</v>
       </c>
       <c r="F13" s="1">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>28</v>
@@ -1683,7 +1701,7 @@
       </c>
       <c r="L13" s="1">
         <f t="shared" si="1"/>
-        <v>40000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:12">
@@ -1697,7 +1715,7 @@
         <v>19</v>
       </c>
       <c r="F14" s="1">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>30</v>
@@ -1716,7 +1734,7 @@
       </c>
       <c r="L14" s="1">
         <f t="shared" si="1"/>
-        <v>40000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:12">
@@ -1730,7 +1748,7 @@
         <v>19</v>
       </c>
       <c r="F15" s="1">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>32</v>
@@ -1749,7 +1767,7 @@
       </c>
       <c r="L15" s="1">
         <f t="shared" si="1"/>
-        <v>40000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:12">
@@ -1763,7 +1781,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>34</v>
@@ -1782,7 +1800,7 @@
       </c>
       <c r="L16" s="1">
         <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:12">
@@ -1796,7 +1814,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>36</v>
@@ -1815,7 +1833,7 @@
       </c>
       <c r="L17" s="1">
         <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:12">
@@ -1829,7 +1847,7 @@
         <v>12</v>
       </c>
       <c r="F18" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>38</v>
@@ -1848,7 +1866,7 @@
       </c>
       <c r="L18" s="1">
         <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:12">
@@ -1862,7 +1880,7 @@
         <v>12</v>
       </c>
       <c r="F19" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>40</v>
@@ -1881,7 +1899,7 @@
       </c>
       <c r="L19" s="1">
         <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:12">
@@ -1895,7 +1913,7 @@
         <v>12</v>
       </c>
       <c r="F20" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>42</v>
@@ -1914,7 +1932,7 @@
       </c>
       <c r="L20" s="1">
         <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:12">
@@ -2027,7 +2045,7 @@
         <v>52</v>
       </c>
       <c r="F24" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>53</v>
@@ -2046,7 +2064,7 @@
       </c>
       <c r="L24" s="1">
         <f t="shared" si="1"/>
-        <v>150000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:12">
@@ -2060,7 +2078,7 @@
         <v>55</v>
       </c>
       <c r="F25" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>56</v>
@@ -2079,7 +2097,7 @@
       </c>
       <c r="L25" s="1">
         <f t="shared" si="1"/>
-        <v>100000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:12">
@@ -2093,7 +2111,7 @@
         <v>58</v>
       </c>
       <c r="F26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>59</v>
@@ -2112,7 +2130,7 @@
       </c>
       <c r="L26" s="1">
         <f t="shared" si="1"/>
-        <v>200000</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:12">
@@ -2126,7 +2144,7 @@
         <v>61</v>
       </c>
       <c r="F27" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>62</v>
@@ -2145,7 +2163,7 @@
       </c>
       <c r="L27" s="1">
         <f t="shared" si="1"/>
-        <v>600000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:12">
@@ -2159,7 +2177,7 @@
         <v>64</v>
       </c>
       <c r="F28" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>65</v>
@@ -2178,16 +2196,10 @@
       </c>
       <c r="L28" s="1">
         <f t="shared" si="1"/>
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:12">
-      <c r="A29" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:12">
       <c r="C29" s="1">
         <v>24</v>
       </c>
@@ -2231,7 +2243,7 @@
         <v>70</v>
       </c>
       <c r="F30" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>71</v>
@@ -2250,851 +2262,728 @@
       </c>
       <c r="L30" s="1">
         <f t="shared" si="1"/>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:12">
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="1">
+        <v>100</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I31" s="1">
+        <v>5</v>
+      </c>
+      <c r="J31" s="1">
+        <v>4022</v>
+      </c>
+      <c r="K31" s="1">
+        <v>100</v>
+      </c>
+      <c r="L31" s="1">
+        <f t="shared" si="1"/>
         <v>500000</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="3:13">
+    <row r="32" customHeight="1" spans="3:12">
       <c r="C32" s="1">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
+      <c r="E32" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F32" s="1">
+        <v>100</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I32" s="1">
+        <v>5</v>
+      </c>
+      <c r="J32" s="1">
+        <v>4011</v>
+      </c>
+      <c r="K32" s="1">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1">
+        <f t="shared" si="1"/>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:12">
+      <c r="C33" s="1">
+        <v>28</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0</v>
+      </c>
+      <c r="E33" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F33" s="1">
+        <v>40</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I33" s="1">
+        <v>5</v>
+      </c>
+      <c r="J33" s="1">
+        <v>4020</v>
+      </c>
+      <c r="K33" s="1">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1">
+        <f t="shared" si="1"/>
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:13">
+      <c r="C38" s="1">
         <v>101</v>
       </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
         <v>500</v>
       </c>
-      <c r="F32" s="1">
-        <f>20*M32</f>
+      <c r="F38" s="1">
+        <f>20*M38</f>
         <v>20</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I32" s="1">
-        <v>5</v>
-      </c>
-      <c r="J32" s="1">
+      <c r="G38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I38" s="1">
+        <v>5</v>
+      </c>
+      <c r="J38" s="1">
         <v>4010</v>
       </c>
-      <c r="K32" s="1">
-        <v>5</v>
-      </c>
-      <c r="L32" s="1">
-        <f t="shared" ref="L32:L40" si="2">E32*F32</f>
+      <c r="K38" s="1">
+        <v>5</v>
+      </c>
+      <c r="L38" s="1">
+        <f t="shared" ref="L38:L46" si="2">E38*F38</f>
         <v>10000</v>
       </c>
-      <c r="M32" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:13">
-      <c r="C33" s="1">
+      <c r="M38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:13">
+      <c r="C39" s="1">
         <v>102</v>
       </c>
-      <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1">
+      <c r="D39" s="1">
+        <v>1</v>
+      </c>
+      <c r="E39" s="1">
         <v>100</v>
       </c>
-      <c r="F33" s="1">
-        <f>300*M32</f>
+      <c r="F39" s="1">
+        <f>300*M38</f>
         <v>300</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I33" s="1">
-        <v>5</v>
-      </c>
-      <c r="J33" s="1">
+      <c r="G39" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I39" s="1">
+        <v>5</v>
+      </c>
+      <c r="J39" s="1">
         <v>4007</v>
       </c>
-      <c r="K33" s="1">
+      <c r="K39" s="1">
         <v>1000</v>
       </c>
-      <c r="L33" s="1">
+      <c r="L39" s="1">
         <f t="shared" si="2"/>
         <v>30000</v>
       </c>
-      <c r="M33" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:13">
-      <c r="C34" s="1">
+      <c r="M39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:13">
+      <c r="C40" s="1">
         <v>103</v>
       </c>
-      <c r="D34" s="1">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1">
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1">
         <v>100</v>
       </c>
-      <c r="F34" s="1">
-        <f>500*M32</f>
+      <c r="F40" s="1">
+        <f>500*M38</f>
         <v>500</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I34" s="1">
-        <v>5</v>
-      </c>
-      <c r="J34" s="1">
+      <c r="G40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I40" s="1">
+        <v>5</v>
+      </c>
+      <c r="J40" s="1">
         <v>4101</v>
       </c>
-      <c r="K34" s="1">
+      <c r="K40" s="1">
         <v>1000</v>
       </c>
-      <c r="L34" s="1">
+      <c r="L40" s="1">
         <f t="shared" si="2"/>
         <v>50000</v>
       </c>
-      <c r="M34" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:13">
-      <c r="C35" s="1">
+      <c r="M40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:13">
+      <c r="C41" s="1">
         <v>104</v>
       </c>
-      <c r="D35" s="1">
-        <v>1</v>
-      </c>
-      <c r="E35" s="1">
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1">
         <v>1000</v>
       </c>
-      <c r="F35" s="1">
-        <f>5*M32</f>
-        <v>5</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I35" s="1">
+      <c r="F41" s="1">
+        <f>6*M38</f>
+        <v>6</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I41" s="1">
         <v>15</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J41" s="1">
         <v>4014</v>
       </c>
-      <c r="K35" s="1">
+      <c r="K41" s="1">
         <v>100</v>
       </c>
-      <c r="L35" s="1">
+      <c r="L41" s="1">
+        <f t="shared" si="2"/>
+        <v>6000</v>
+      </c>
+      <c r="M41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:13">
+      <c r="C42" s="1">
+        <v>105</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1">
+        <v>500</v>
+      </c>
+      <c r="F42" s="1">
+        <f>20*M38</f>
+        <v>20</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I42" s="1">
+        <v>5</v>
+      </c>
+      <c r="J42" s="1">
+        <v>4012</v>
+      </c>
+      <c r="K42" s="1">
+        <v>200</v>
+      </c>
+      <c r="L42" s="1">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="M42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:13">
+      <c r="C43" s="1">
+        <v>106</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1</v>
+      </c>
+      <c r="E43" s="1">
+        <v>15000</v>
+      </c>
+      <c r="F43" s="1">
+        <f>5*M38</f>
+        <v>5</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I43" s="1">
+        <v>5</v>
+      </c>
+      <c r="J43" s="1">
+        <v>4019</v>
+      </c>
+      <c r="K43" s="1">
+        <v>1</v>
+      </c>
+      <c r="L43" s="1">
+        <f t="shared" si="2"/>
+        <v>75000</v>
+      </c>
+      <c r="M43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:13">
+      <c r="C44" s="1">
+        <v>107</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+      <c r="E44" s="1">
+        <v>500</v>
+      </c>
+      <c r="F44" s="1">
+        <f>10*M38</f>
+        <v>10</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I44" s="1">
+        <v>5</v>
+      </c>
+      <c r="J44" s="1">
+        <v>4102</v>
+      </c>
+      <c r="K44" s="1">
+        <v>20</v>
+      </c>
+      <c r="L44" s="1">
         <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="M35" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:13">
-      <c r="C36" s="1">
-        <v>105</v>
-      </c>
-      <c r="D36" s="1">
-        <v>1</v>
-      </c>
-      <c r="E36" s="1">
+      <c r="M44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:13">
+      <c r="C45" s="1">
+        <v>108</v>
+      </c>
+      <c r="D45" s="1">
+        <v>1</v>
+      </c>
+      <c r="E45" s="1">
         <v>500</v>
       </c>
-      <c r="F36" s="1">
-        <f>20*M32</f>
-        <v>20</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I36" s="1">
-        <v>5</v>
-      </c>
-      <c r="J36" s="1">
-        <v>4012</v>
-      </c>
-      <c r="K36" s="1">
-        <v>200</v>
-      </c>
-      <c r="L36" s="1">
-        <f t="shared" si="2"/>
-        <v>10000</v>
-      </c>
-      <c r="M36" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:13">
-      <c r="C37" s="1">
-        <v>106</v>
-      </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
-      <c r="E37" s="1">
-        <v>5000</v>
-      </c>
-      <c r="F37" s="1">
-        <f>5*M32</f>
-        <v>5</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I37" s="1">
-        <v>5</v>
-      </c>
-      <c r="J37" s="1">
-        <v>4011</v>
-      </c>
-      <c r="K37" s="1">
-        <v>1</v>
-      </c>
-      <c r="L37" s="1">
-        <f t="shared" si="2"/>
-        <v>25000</v>
-      </c>
-      <c r="M37" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:13">
-      <c r="C38" s="1">
-        <v>107</v>
-      </c>
-      <c r="D38" s="1">
-        <v>1</v>
-      </c>
-      <c r="E38" s="1">
-        <v>500</v>
-      </c>
-      <c r="F38" s="1">
-        <f>10*M32</f>
-        <v>10</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I38" s="1">
-        <v>5</v>
-      </c>
-      <c r="J38" s="1">
-        <v>4102</v>
-      </c>
-      <c r="K38" s="1">
-        <v>20</v>
-      </c>
-      <c r="L38" s="1">
-        <f t="shared" si="2"/>
-        <v>5000</v>
-      </c>
-      <c r="M38" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:13">
-      <c r="C39" s="1">
-        <v>108</v>
-      </c>
-      <c r="D39" s="1">
-        <v>1</v>
-      </c>
-      <c r="E39" s="1">
-        <v>500</v>
-      </c>
-      <c r="F39" s="1">
-        <f>40*M32</f>
+      <c r="F45" s="1">
+        <f>40*M38</f>
         <v>40</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I39" s="1">
-        <v>5</v>
-      </c>
-      <c r="J39" s="1">
+      <c r="G45" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I45" s="1">
+        <v>5</v>
+      </c>
+      <c r="J45" s="1">
         <v>4001</v>
       </c>
-      <c r="K39" s="1">
+      <c r="K45" s="1">
         <v>1000000</v>
       </c>
-      <c r="L39" s="1">
+      <c r="L45" s="1">
         <f t="shared" si="2"/>
         <v>20000</v>
       </c>
-      <c r="M39" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:13">
-      <c r="C40" s="1">
+      <c r="M45" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:13">
+      <c r="C46" s="1">
         <v>109</v>
       </c>
-      <c r="D40" s="1">
-        <v>1</v>
-      </c>
-      <c r="E40" s="1">
+      <c r="D46" s="1">
+        <v>1</v>
+      </c>
+      <c r="E46" s="1">
         <v>500</v>
       </c>
-      <c r="F40" s="1">
-        <f>40*M32</f>
+      <c r="F46" s="1">
+        <f>40*M38</f>
         <v>40</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I40" s="1">
-        <v>5</v>
-      </c>
-      <c r="J40" s="1">
+      <c r="G46" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I46" s="1">
+        <v>5</v>
+      </c>
+      <c r="J46" s="1">
         <v>4002</v>
       </c>
-      <c r="K40" s="1">
+      <c r="K46" s="1">
         <v>6000000</v>
       </c>
-      <c r="L40" s="1">
+      <c r="L46" s="1">
         <f t="shared" si="2"/>
         <v>20000</v>
       </c>
-      <c r="M40" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:13">
-      <c r="C42" s="1">
+      <c r="M46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:13">
+      <c r="C48" s="1">
         <v>201</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D48" s="1">
         <v>2</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E48" s="4">
         <v>1000</v>
       </c>
-      <c r="F42" s="1">
-        <f>20*M42</f>
+      <c r="F48" s="1">
+        <f>20*M48</f>
         <v>20</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I42" s="1">
-        <v>5</v>
-      </c>
-      <c r="J42" s="1">
+      <c r="G48" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I48" s="1">
+        <v>5</v>
+      </c>
+      <c r="J48" s="1">
         <v>4010</v>
       </c>
-      <c r="K42" s="1">
-        <v>5</v>
-      </c>
-      <c r="L42" s="1">
-        <f t="shared" ref="L42:L77" si="3">E42*F42</f>
+      <c r="K48" s="1">
+        <v>5</v>
+      </c>
+      <c r="L48" s="1">
+        <f t="shared" ref="L48:L83" si="3">E48*F48</f>
         <v>20000</v>
       </c>
-      <c r="M42" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:13">
-      <c r="C43" s="1">
+      <c r="M48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:13">
+      <c r="C49" s="1">
         <v>202</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D49" s="1">
         <v>2</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E49" s="4">
         <v>200</v>
       </c>
-      <c r="F43" s="1">
-        <f>300*M42</f>
+      <c r="F49" s="1">
+        <f>300*M48</f>
         <v>300</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I43" s="1">
-        <v>5</v>
-      </c>
-      <c r="J43" s="1">
+      <c r="G49" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I49" s="1">
+        <v>5</v>
+      </c>
+      <c r="J49" s="1">
         <v>4007</v>
       </c>
-      <c r="K43" s="1">
+      <c r="K49" s="1">
         <v>1000</v>
       </c>
-      <c r="L43" s="1">
+      <c r="L49" s="1">
         <f t="shared" si="3"/>
         <v>60000</v>
       </c>
-      <c r="M43" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:13">
-      <c r="C44" s="1">
+      <c r="M49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:13">
+      <c r="C50" s="1">
         <v>203</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D50" s="1">
         <v>2</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E50" s="4">
         <v>200</v>
       </c>
-      <c r="F44" s="1">
-        <f>500*M42</f>
+      <c r="F50" s="1">
+        <f>500*M48</f>
         <v>500</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I44" s="1">
-        <v>5</v>
-      </c>
-      <c r="J44" s="1">
+      <c r="G50" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I50" s="1">
+        <v>5</v>
+      </c>
+      <c r="J50" s="1">
         <v>4101</v>
       </c>
-      <c r="K44" s="1">
+      <c r="K50" s="1">
         <v>1000</v>
       </c>
-      <c r="L44" s="1">
+      <c r="L50" s="1">
         <f t="shared" si="3"/>
         <v>100000</v>
       </c>
-      <c r="M44" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:13">
-      <c r="C45" s="1">
+      <c r="M50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:13">
+      <c r="C51" s="1">
         <v>204</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D51" s="1">
         <v>2</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E51" s="4">
         <v>2000</v>
       </c>
-      <c r="F45" s="1">
-        <f>5*M42</f>
-        <v>5</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I45" s="1">
+      <c r="F51" s="1">
+        <f>6*M48</f>
+        <v>6</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I51" s="1">
         <v>15</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J51" s="1">
         <v>4014</v>
       </c>
-      <c r="K45" s="1">
+      <c r="K51" s="1">
         <v>100</v>
       </c>
-      <c r="L45" s="1">
+      <c r="L51" s="1">
+        <f t="shared" si="3"/>
+        <v>12000</v>
+      </c>
+      <c r="M51" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:13">
+      <c r="C52" s="1">
+        <v>205</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2</v>
+      </c>
+      <c r="E52" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F52" s="1">
+        <f>20*M48</f>
+        <v>20</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I52" s="1">
+        <v>5</v>
+      </c>
+      <c r="J52" s="1">
+        <v>4012</v>
+      </c>
+      <c r="K52" s="1">
+        <v>200</v>
+      </c>
+      <c r="L52" s="1">
+        <f t="shared" si="3"/>
+        <v>20000</v>
+      </c>
+      <c r="M52" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:13">
+      <c r="C53" s="1">
+        <v>206</v>
+      </c>
+      <c r="D53" s="1">
+        <v>2</v>
+      </c>
+      <c r="E53" s="4">
+        <v>30000</v>
+      </c>
+      <c r="F53" s="1">
+        <f>5*M48</f>
+        <v>5</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I53" s="1">
+        <v>5</v>
+      </c>
+      <c r="J53" s="1">
+        <v>4019</v>
+      </c>
+      <c r="K53" s="1">
+        <v>1</v>
+      </c>
+      <c r="L53" s="1">
+        <f t="shared" si="3"/>
+        <v>150000</v>
+      </c>
+      <c r="M53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:13">
+      <c r="C54" s="1">
+        <v>207</v>
+      </c>
+      <c r="D54" s="1">
+        <v>2</v>
+      </c>
+      <c r="E54" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F54" s="1">
+        <f>10*M48</f>
+        <v>10</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I54" s="1">
+        <v>5</v>
+      </c>
+      <c r="J54" s="1">
+        <v>4102</v>
+      </c>
+      <c r="K54" s="1">
+        <v>20</v>
+      </c>
+      <c r="L54" s="1">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
-      <c r="M45" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:13">
-      <c r="C46" s="1">
-        <v>205</v>
-      </c>
-      <c r="D46" s="1">
-        <v>2</v>
-      </c>
-      <c r="E46" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F46" s="1">
-        <f>20*M42</f>
-        <v>20</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I46" s="1">
-        <v>5</v>
-      </c>
-      <c r="J46" s="1">
-        <v>4012</v>
-      </c>
-      <c r="K46" s="1">
-        <v>200</v>
-      </c>
-      <c r="L46" s="1">
-        <f t="shared" si="3"/>
-        <v>20000</v>
-      </c>
-      <c r="M46" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:13">
-      <c r="C47" s="1">
-        <v>206</v>
-      </c>
-      <c r="D47" s="1">
-        <v>2</v>
-      </c>
-      <c r="E47" s="4">
-        <v>10000</v>
-      </c>
-      <c r="F47" s="1">
-        <f>5*M42</f>
-        <v>5</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I47" s="1">
-        <v>5</v>
-      </c>
-      <c r="J47" s="1">
-        <v>4011</v>
-      </c>
-      <c r="K47" s="1">
-        <v>1</v>
-      </c>
-      <c r="L47" s="1">
-        <f t="shared" si="3"/>
-        <v>50000</v>
-      </c>
-      <c r="M47" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:13">
-      <c r="C48" s="1">
-        <v>207</v>
-      </c>
-      <c r="D48" s="1">
-        <v>2</v>
-      </c>
-      <c r="E48" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F48" s="1">
-        <f>10*M42</f>
-        <v>10</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I48" s="1">
-        <v>5</v>
-      </c>
-      <c r="J48" s="1">
-        <v>4102</v>
-      </c>
-      <c r="K48" s="1">
-        <v>20</v>
-      </c>
-      <c r="L48" s="1">
-        <f t="shared" si="3"/>
-        <v>10000</v>
-      </c>
-      <c r="M48" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:13">
-      <c r="C49" s="1">
-        <v>208</v>
-      </c>
-      <c r="D49" s="1">
-        <v>2</v>
-      </c>
-      <c r="E49" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F49" s="1">
-        <f>40*M42</f>
-        <v>40</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I49" s="1">
-        <v>5</v>
-      </c>
-      <c r="J49" s="1">
-        <v>4001</v>
-      </c>
-      <c r="K49" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="L49" s="1">
-        <f t="shared" si="3"/>
-        <v>40000</v>
-      </c>
-      <c r="M49" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:13">
-      <c r="C50" s="1">
-        <v>209</v>
-      </c>
-      <c r="D50" s="1">
-        <v>2</v>
-      </c>
-      <c r="E50" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F50" s="1">
-        <f>40*M42</f>
-        <v>40</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I50" s="1">
-        <v>5</v>
-      </c>
-      <c r="J50" s="1">
-        <v>4002</v>
-      </c>
-      <c r="K50" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="L50" s="1">
-        <f t="shared" si="3"/>
-        <v>40000</v>
-      </c>
-      <c r="M50" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:13">
-      <c r="C51" s="1">
-        <v>210</v>
-      </c>
-      <c r="D51" s="1">
-        <v>3</v>
-      </c>
-      <c r="E51" s="1">
-        <v>2000</v>
-      </c>
-      <c r="F51" s="1">
-        <f>20*M51</f>
-        <v>20</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I51" s="1">
-        <v>5</v>
-      </c>
-      <c r="J51" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K51" s="1">
-        <v>5</v>
-      </c>
-      <c r="L51" s="1">
-        <f t="shared" si="3"/>
-        <v>40000</v>
-      </c>
-      <c r="M51" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:13">
-      <c r="C52" s="1">
-        <v>211</v>
-      </c>
-      <c r="D52" s="1">
-        <v>3</v>
-      </c>
-      <c r="E52" s="1">
-        <v>400</v>
-      </c>
-      <c r="F52" s="1">
-        <f>300*M51</f>
-        <v>300</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I52" s="1">
-        <v>5</v>
-      </c>
-      <c r="J52" s="1">
-        <v>4007</v>
-      </c>
-      <c r="K52" s="1">
-        <v>1000</v>
-      </c>
-      <c r="L52" s="1">
-        <f t="shared" si="3"/>
-        <v>120000</v>
-      </c>
-      <c r="M52" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:13">
-      <c r="C53" s="1">
-        <v>212</v>
-      </c>
-      <c r="D53" s="1">
-        <v>3</v>
-      </c>
-      <c r="E53" s="1">
-        <v>400</v>
-      </c>
-      <c r="F53" s="1">
-        <f>500*M51</f>
-        <v>500</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I53" s="1">
-        <v>5</v>
-      </c>
-      <c r="J53" s="1">
-        <v>4101</v>
-      </c>
-      <c r="K53" s="1">
-        <v>1000</v>
-      </c>
-      <c r="L53" s="1">
-        <f t="shared" si="3"/>
-        <v>200000</v>
-      </c>
-      <c r="M53" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:13">
-      <c r="C54" s="1">
-        <v>213</v>
-      </c>
-      <c r="D54" s="1">
-        <v>3</v>
-      </c>
-      <c r="E54" s="1">
-        <v>4000</v>
-      </c>
-      <c r="F54" s="1">
-        <f>5*M51</f>
-        <v>5</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I54" s="1">
-        <v>15</v>
-      </c>
-      <c r="J54" s="1">
-        <v>4014</v>
-      </c>
-      <c r="K54" s="1">
-        <v>100</v>
-      </c>
-      <c r="L54" s="1">
-        <f t="shared" si="3"/>
-        <v>20000</v>
-      </c>
       <c r="M54" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:13">
       <c r="C55" s="1">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D55" s="1">
-        <v>3</v>
-      </c>
-      <c r="E55" s="1">
-        <v>2000</v>
+        <v>2</v>
+      </c>
+      <c r="E55" s="4">
+        <v>1000</v>
       </c>
       <c r="F55" s="1">
-        <f>20*M51</f>
-        <v>20</v>
+        <f>40*M48</f>
+        <v>40</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I55" s="1">
         <v>5</v>
       </c>
       <c r="J55" s="1">
-        <v>4012</v>
+        <v>4001</v>
       </c>
       <c r="K55" s="1">
-        <v>200</v>
+        <v>1000000</v>
       </c>
       <c r="L55" s="1">
         <f t="shared" si="3"/>
@@ -3106,36 +2995,36 @@
     </row>
     <row r="56" customHeight="1" spans="3:13">
       <c r="C56" s="1">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D56" s="1">
-        <v>3</v>
-      </c>
-      <c r="E56" s="1">
-        <v>20000</v>
+        <v>2</v>
+      </c>
+      <c r="E56" s="4">
+        <v>1000</v>
       </c>
       <c r="F56" s="1">
-        <f>5*M51</f>
-        <v>5</v>
+        <f>40*M48</f>
+        <v>40</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I56" s="1">
         <v>5</v>
       </c>
       <c r="J56" s="1">
-        <v>4011</v>
+        <v>4002</v>
       </c>
       <c r="K56" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="L56" s="1">
         <f t="shared" si="3"/>
-        <v>100000</v>
+        <v>40000</v>
       </c>
       <c r="M56" s="1">
         <v>1</v>
@@ -3143,7 +3032,7 @@
     </row>
     <row r="57" customHeight="1" spans="3:13">
       <c r="C57" s="1">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D57" s="1">
         <v>3</v>
@@ -3152,27 +3041,27 @@
         <v>2000</v>
       </c>
       <c r="F57" s="1">
-        <f>10*M51</f>
-        <v>10</v>
+        <f>20*M57</f>
+        <v>20</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I57" s="1">
         <v>5</v>
       </c>
       <c r="J57" s="1">
-        <v>4102</v>
+        <v>4010</v>
       </c>
       <c r="K57" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="L57" s="1">
         <f t="shared" si="3"/>
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="M57" s="1">
         <v>1</v>
@@ -3180,36 +3069,36 @@
     </row>
     <row r="58" customHeight="1" spans="3:13">
       <c r="C58" s="1">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D58" s="1">
         <v>3</v>
       </c>
       <c r="E58" s="1">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="F58" s="1">
-        <f>40*M51</f>
-        <v>40</v>
+        <f>300*M57</f>
+        <v>300</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I58" s="1">
         <v>5</v>
       </c>
       <c r="J58" s="1">
-        <v>4001</v>
+        <v>4007</v>
       </c>
       <c r="K58" s="1">
-        <v>1000000</v>
+        <v>1000</v>
       </c>
       <c r="L58" s="1">
         <f t="shared" si="3"/>
-        <v>80000</v>
+        <v>120000</v>
       </c>
       <c r="M58" s="1">
         <v>1</v>
@@ -3217,36 +3106,36 @@
     </row>
     <row r="59" customHeight="1" spans="3:13">
       <c r="C59" s="1">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D59" s="1">
         <v>3</v>
       </c>
       <c r="E59" s="1">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="F59" s="1">
-        <f>40*M51</f>
-        <v>40</v>
+        <f>500*M57</f>
+        <v>500</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I59" s="1">
         <v>5</v>
       </c>
       <c r="J59" s="1">
-        <v>4002</v>
+        <v>4101</v>
       </c>
       <c r="K59" s="1">
-        <v>6000000</v>
+        <v>1000</v>
       </c>
       <c r="L59" s="1">
         <f t="shared" si="3"/>
-        <v>80000</v>
+        <v>200000</v>
       </c>
       <c r="M59" s="1">
         <v>1</v>
@@ -3254,36 +3143,36 @@
     </row>
     <row r="60" customHeight="1" spans="3:13">
       <c r="C60" s="1">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D60" s="1">
-        <v>4</v>
-      </c>
-      <c r="E60" s="4">
-        <v>3000</v>
+        <v>3</v>
+      </c>
+      <c r="E60" s="1">
+        <v>4000</v>
       </c>
       <c r="F60" s="1">
-        <f>20*M60</f>
-        <v>20</v>
+        <f>6*M57</f>
+        <v>6</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="I60" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J60" s="1">
-        <v>4010</v>
+        <v>4014</v>
       </c>
       <c r="K60" s="1">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L60" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>24000</v>
       </c>
       <c r="M60" s="1">
         <v>1</v>
@@ -3291,36 +3180,36 @@
     </row>
     <row r="61" customHeight="1" spans="3:13">
       <c r="C61" s="1">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D61" s="1">
-        <v>4</v>
-      </c>
-      <c r="E61" s="4">
-        <v>600</v>
+        <v>3</v>
+      </c>
+      <c r="E61" s="1">
+        <v>2000</v>
       </c>
       <c r="F61" s="1">
-        <f>300*M60</f>
-        <v>300</v>
+        <f>20*M57</f>
+        <v>20</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I61" s="1">
         <v>5</v>
       </c>
       <c r="J61" s="1">
-        <v>4007</v>
+        <v>4012</v>
       </c>
       <c r="K61" s="1">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="L61" s="1">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>40000</v>
       </c>
       <c r="M61" s="1">
         <v>1</v>
@@ -3328,36 +3217,36 @@
     </row>
     <row r="62" customHeight="1" spans="3:13">
       <c r="C62" s="1">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D62" s="1">
-        <v>4</v>
-      </c>
-      <c r="E62" s="4">
-        <v>600</v>
+        <v>3</v>
+      </c>
+      <c r="E62" s="1">
+        <v>45000</v>
       </c>
       <c r="F62" s="1">
-        <f>500*M60</f>
-        <v>500</v>
+        <f>5*M57</f>
+        <v>5</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I62" s="1">
         <v>5</v>
       </c>
       <c r="J62" s="1">
-        <v>4101</v>
+        <v>4019</v>
       </c>
       <c r="K62" s="1">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="L62" s="1">
         <f t="shared" si="3"/>
-        <v>300000</v>
+        <v>225000</v>
       </c>
       <c r="M62" s="1">
         <v>1</v>
@@ -3365,36 +3254,36 @@
     </row>
     <row r="63" customHeight="1" spans="3:13">
       <c r="C63" s="1">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D63" s="1">
-        <v>4</v>
-      </c>
-      <c r="E63" s="4">
-        <v>6000</v>
+        <v>3</v>
+      </c>
+      <c r="E63" s="1">
+        <v>2000</v>
       </c>
       <c r="F63" s="1">
-        <f>5*M60</f>
-        <v>5</v>
+        <f>10*M57</f>
+        <v>10</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I63" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J63" s="1">
-        <v>4014</v>
+        <v>4102</v>
       </c>
       <c r="K63" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="L63" s="1">
         <f t="shared" si="3"/>
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="M63" s="1">
         <v>1</v>
@@ -3402,36 +3291,36 @@
     </row>
     <row r="64" customHeight="1" spans="3:13">
       <c r="C64" s="1">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="D64" s="1">
-        <v>4</v>
-      </c>
-      <c r="E64" s="4">
-        <v>3000</v>
+        <v>3</v>
+      </c>
+      <c r="E64" s="1">
+        <v>2000</v>
       </c>
       <c r="F64" s="1">
-        <f>20*M60</f>
-        <v>20</v>
+        <f>40*M57</f>
+        <v>40</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I64" s="1">
         <v>5</v>
       </c>
       <c r="J64" s="1">
-        <v>4012</v>
+        <v>4001</v>
       </c>
       <c r="K64" s="1">
-        <v>200</v>
+        <v>1000000</v>
       </c>
       <c r="L64" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="M64" s="1">
         <v>1</v>
@@ -3439,36 +3328,36 @@
     </row>
     <row r="65" customHeight="1" spans="3:13">
       <c r="C65" s="1">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D65" s="1">
-        <v>4</v>
-      </c>
-      <c r="E65" s="4">
-        <v>30000</v>
+        <v>3</v>
+      </c>
+      <c r="E65" s="1">
+        <v>2000</v>
       </c>
       <c r="F65" s="1">
-        <f>5*M60</f>
-        <v>5</v>
+        <f>40*M57</f>
+        <v>40</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I65" s="1">
         <v>5</v>
       </c>
       <c r="J65" s="1">
-        <v>4011</v>
+        <v>4002</v>
       </c>
       <c r="K65" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="L65" s="1">
         <f t="shared" si="3"/>
-        <v>150000</v>
+        <v>80000</v>
       </c>
       <c r="M65" s="1">
         <v>1</v>
@@ -3476,7 +3365,7 @@
     </row>
     <row r="66" customHeight="1" spans="3:13">
       <c r="C66" s="1">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D66" s="1">
         <v>4</v>
@@ -3485,27 +3374,27 @@
         <v>3000</v>
       </c>
       <c r="F66" s="1">
-        <f>10*M60</f>
-        <v>10</v>
+        <f>20*M66</f>
+        <v>20</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I66" s="1">
         <v>5</v>
       </c>
       <c r="J66" s="1">
-        <v>4102</v>
+        <v>4010</v>
       </c>
       <c r="K66" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="L66" s="1">
         <f t="shared" si="3"/>
-        <v>30000</v>
+        <v>60000</v>
       </c>
       <c r="M66" s="1">
         <v>1</v>
@@ -3513,36 +3402,36 @@
     </row>
     <row r="67" customHeight="1" spans="3:13">
       <c r="C67" s="1">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D67" s="1">
         <v>4</v>
       </c>
       <c r="E67" s="4">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="F67" s="1">
-        <f>40*M60</f>
-        <v>40</v>
+        <f>300*M66</f>
+        <v>300</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I67" s="1">
         <v>5</v>
       </c>
       <c r="J67" s="1">
-        <v>4001</v>
+        <v>4007</v>
       </c>
       <c r="K67" s="1">
-        <v>1000000</v>
+        <v>1000</v>
       </c>
       <c r="L67" s="1">
         <f t="shared" si="3"/>
-        <v>120000</v>
+        <v>180000</v>
       </c>
       <c r="M67" s="1">
         <v>1</v>
@@ -3550,36 +3439,36 @@
     </row>
     <row r="68" customHeight="1" spans="3:13">
       <c r="C68" s="1">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D68" s="1">
         <v>4</v>
       </c>
       <c r="E68" s="4">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="F68" s="1">
-        <f>40*M60</f>
-        <v>40</v>
+        <f>500*M66</f>
+        <v>500</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I68" s="1">
         <v>5</v>
       </c>
       <c r="J68" s="1">
-        <v>4002</v>
+        <v>4101</v>
       </c>
       <c r="K68" s="1">
-        <v>6000000</v>
+        <v>1000</v>
       </c>
       <c r="L68" s="1">
         <f t="shared" si="3"/>
-        <v>120000</v>
+        <v>300000</v>
       </c>
       <c r="M68" s="1">
         <v>1</v>
@@ -3587,229 +3476,229 @@
     </row>
     <row r="69" customHeight="1" spans="3:13">
       <c r="C69" s="1">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D69" s="1">
-        <v>5</v>
-      </c>
-      <c r="E69" s="1">
-        <v>4000</v>
+        <v>4</v>
+      </c>
+      <c r="E69" s="4">
+        <v>6000</v>
       </c>
       <c r="F69" s="1">
-        <f>20*M69</f>
-        <v>80</v>
+        <f>6*M66</f>
+        <v>6</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="I69" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J69" s="1">
-        <v>4010</v>
+        <v>4014</v>
       </c>
       <c r="K69" s="1">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="L69" s="1">
         <f t="shared" si="3"/>
-        <v>320000</v>
+        <v>36000</v>
       </c>
       <c r="M69" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:13">
       <c r="C70" s="1">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D70" s="1">
-        <v>5</v>
-      </c>
-      <c r="E70" s="1">
-        <v>800</v>
+        <v>4</v>
+      </c>
+      <c r="E70" s="4">
+        <v>3000</v>
       </c>
       <c r="F70" s="1">
-        <f>300*M69</f>
-        <v>1200</v>
+        <f>20*M66</f>
+        <v>20</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I70" s="1">
         <v>5</v>
       </c>
       <c r="J70" s="1">
-        <v>4007</v>
+        <v>4012</v>
       </c>
       <c r="K70" s="1">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="L70" s="1">
         <f t="shared" si="3"/>
-        <v>960000</v>
+        <v>60000</v>
       </c>
       <c r="M70" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:13">
       <c r="C71" s="1">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D71" s="1">
-        <v>5</v>
-      </c>
-      <c r="E71" s="1">
-        <v>800</v>
+        <v>4</v>
+      </c>
+      <c r="E71" s="4">
+        <v>60000</v>
       </c>
       <c r="F71" s="1">
-        <f>500*M69</f>
-        <v>2000</v>
+        <f>5*M66</f>
+        <v>5</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I71" s="1">
         <v>5</v>
       </c>
       <c r="J71" s="1">
-        <v>4101</v>
+        <v>4019</v>
       </c>
       <c r="K71" s="1">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="L71" s="1">
         <f t="shared" si="3"/>
-        <v>1600000</v>
+        <v>300000</v>
       </c>
       <c r="M71" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:13">
       <c r="C72" s="1">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D72" s="1">
-        <v>5</v>
-      </c>
-      <c r="E72" s="1">
-        <v>8000</v>
+        <v>4</v>
+      </c>
+      <c r="E72" s="4">
+        <v>3000</v>
       </c>
       <c r="F72" s="1">
-        <f>5*M69</f>
+        <f>10*M66</f>
+        <v>10</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I72" s="1">
+        <v>5</v>
+      </c>
+      <c r="J72" s="1">
+        <v>4102</v>
+      </c>
+      <c r="K72" s="1">
         <v>20</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I72" s="1">
-        <v>15</v>
-      </c>
-      <c r="J72" s="1">
-        <v>4014</v>
-      </c>
-      <c r="K72" s="1">
-        <v>100</v>
       </c>
       <c r="L72" s="1">
         <f t="shared" si="3"/>
-        <v>160000</v>
+        <v>30000</v>
       </c>
       <c r="M72" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:13">
       <c r="C73" s="1">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D73" s="1">
-        <v>5</v>
-      </c>
-      <c r="E73" s="1">
-        <v>4000</v>
+        <v>4</v>
+      </c>
+      <c r="E73" s="4">
+        <v>3000</v>
       </c>
       <c r="F73" s="1">
-        <f>20*M69</f>
-        <v>80</v>
+        <f>40*M66</f>
+        <v>40</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I73" s="1">
         <v>5</v>
       </c>
       <c r="J73" s="1">
-        <v>4012</v>
+        <v>4001</v>
       </c>
       <c r="K73" s="1">
-        <v>200</v>
+        <v>1000000</v>
       </c>
       <c r="L73" s="1">
         <f t="shared" si="3"/>
-        <v>320000</v>
+        <v>120000</v>
       </c>
       <c r="M73" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:13">
       <c r="C74" s="1">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D74" s="1">
-        <v>5</v>
-      </c>
-      <c r="E74" s="1">
-        <v>40000</v>
+        <v>4</v>
+      </c>
+      <c r="E74" s="4">
+        <v>3000</v>
       </c>
       <c r="F74" s="1">
-        <f>5*M69</f>
-        <v>20</v>
+        <f>40*M66</f>
+        <v>40</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I74" s="1">
         <v>5</v>
       </c>
       <c r="J74" s="1">
-        <v>4011</v>
+        <v>4002</v>
       </c>
       <c r="K74" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="L74" s="1">
         <f t="shared" si="3"/>
-        <v>800000</v>
+        <v>120000</v>
       </c>
       <c r="M74" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:13">
       <c r="C75" s="1">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D75" s="1">
         <v>5</v>
@@ -3818,27 +3707,27 @@
         <v>4000</v>
       </c>
       <c r="F75" s="1">
-        <f>10*M69</f>
-        <v>40</v>
+        <f>20*M75</f>
+        <v>80</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I75" s="1">
         <v>5</v>
       </c>
       <c r="J75" s="1">
-        <v>4102</v>
+        <v>4010</v>
       </c>
       <c r="K75" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="L75" s="1">
         <f t="shared" si="3"/>
-        <v>160000</v>
+        <v>320000</v>
       </c>
       <c r="M75" s="1">
         <v>4</v>
@@ -3846,36 +3735,36 @@
     </row>
     <row r="76" customHeight="1" spans="3:13">
       <c r="C76" s="1">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D76" s="1">
         <v>5</v>
       </c>
       <c r="E76" s="1">
-        <v>4000</v>
+        <v>800</v>
       </c>
       <c r="F76" s="1">
-        <f>40*M69</f>
-        <v>160</v>
+        <f>300*M75</f>
+        <v>1200</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I76" s="1">
         <v>5</v>
       </c>
       <c r="J76" s="1">
-        <v>4001</v>
+        <v>4007</v>
       </c>
       <c r="K76" s="1">
-        <v>1000000</v>
+        <v>1000</v>
       </c>
       <c r="L76" s="1">
         <f t="shared" si="3"/>
-        <v>640000</v>
+        <v>960000</v>
       </c>
       <c r="M76" s="1">
         <v>4</v>
@@ -3883,71 +3772,293 @@
     </row>
     <row r="77" customHeight="1" spans="3:13">
       <c r="C77" s="1">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D77" s="1">
         <v>5</v>
       </c>
       <c r="E77" s="1">
-        <v>4000</v>
+        <v>800</v>
       </c>
       <c r="F77" s="1">
-        <f>40*M69</f>
-        <v>160</v>
+        <f>500*M75</f>
+        <v>2000</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I77" s="1">
         <v>5</v>
       </c>
       <c r="J77" s="1">
-        <v>4002</v>
+        <v>4101</v>
       </c>
       <c r="K77" s="1">
-        <v>6000000</v>
+        <v>1000</v>
       </c>
       <c r="L77" s="1">
         <f t="shared" si="3"/>
-        <v>640000</v>
+        <v>1600000</v>
       </c>
       <c r="M77" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="80" customHeight="1" spans="3:12">
+    <row r="78" customHeight="1" spans="3:13">
+      <c r="C78" s="1">
+        <v>231</v>
+      </c>
+      <c r="D78" s="1">
+        <v>5</v>
+      </c>
+      <c r="E78" s="1">
+        <v>8000</v>
+      </c>
+      <c r="F78" s="1">
+        <f>6*M75</f>
+        <v>24</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I78" s="1">
+        <v>15</v>
+      </c>
+      <c r="J78" s="1">
+        <v>4014</v>
+      </c>
+      <c r="K78" s="1">
+        <v>100</v>
+      </c>
+      <c r="L78" s="1">
+        <f t="shared" si="3"/>
+        <v>192000</v>
+      </c>
+      <c r="M78" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:13">
+      <c r="C79" s="1">
+        <v>232</v>
+      </c>
+      <c r="D79" s="1">
+        <v>5</v>
+      </c>
+      <c r="E79" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F79" s="1">
+        <f>20*M75</f>
+        <v>80</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I79" s="1">
+        <v>5</v>
+      </c>
+      <c r="J79" s="1">
+        <v>4012</v>
+      </c>
+      <c r="K79" s="1">
+        <v>200</v>
+      </c>
+      <c r="L79" s="1">
+        <f t="shared" si="3"/>
+        <v>320000</v>
+      </c>
+      <c r="M79" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:13">
       <c r="C80" s="1">
+        <v>233</v>
+      </c>
+      <c r="D80" s="1">
+        <v>5</v>
+      </c>
+      <c r="E80" s="1">
+        <v>75000</v>
+      </c>
+      <c r="F80" s="1">
+        <f>5*M75</f>
+        <v>20</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I80" s="1">
+        <v>5</v>
+      </c>
+      <c r="J80" s="1">
+        <v>4019</v>
+      </c>
+      <c r="K80" s="1">
+        <v>1</v>
+      </c>
+      <c r="L80" s="1">
+        <f t="shared" si="3"/>
+        <v>1500000</v>
+      </c>
+      <c r="M80" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:13">
+      <c r="C81" s="1">
+        <v>234</v>
+      </c>
+      <c r="D81" s="1">
+        <v>5</v>
+      </c>
+      <c r="E81" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F81" s="1">
+        <f>10*M75</f>
+        <v>40</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I81" s="1">
+        <v>5</v>
+      </c>
+      <c r="J81" s="1">
+        <v>4102</v>
+      </c>
+      <c r="K81" s="1">
+        <v>20</v>
+      </c>
+      <c r="L81" s="1">
+        <f t="shared" si="3"/>
+        <v>160000</v>
+      </c>
+      <c r="M81" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:13">
+      <c r="C82" s="1">
+        <v>235</v>
+      </c>
+      <c r="D82" s="1">
+        <v>5</v>
+      </c>
+      <c r="E82" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F82" s="1">
+        <f>40*M75</f>
+        <v>160</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I82" s="1">
+        <v>5</v>
+      </c>
+      <c r="J82" s="1">
+        <v>4001</v>
+      </c>
+      <c r="K82" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="L82" s="1">
+        <f t="shared" si="3"/>
+        <v>640000</v>
+      </c>
+      <c r="M82" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:13">
+      <c r="C83" s="1">
+        <v>236</v>
+      </c>
+      <c r="D83" s="1">
+        <v>5</v>
+      </c>
+      <c r="E83" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F83" s="1">
+        <f>40*M75</f>
+        <v>160</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I83" s="1">
+        <v>5</v>
+      </c>
+      <c r="J83" s="1">
+        <v>4002</v>
+      </c>
+      <c r="K83" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="L83" s="1">
+        <f t="shared" si="3"/>
+        <v>640000</v>
+      </c>
+      <c r="M83" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:12">
+      <c r="C86" s="1">
         <v>999</v>
       </c>
-      <c r="D80" s="1">
+      <c r="D86" s="1">
         <v>0</v>
       </c>
-      <c r="E80" s="6" t="s">
+      <c r="E86" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F86" s="1">
         <v>50</v>
       </c>
-      <c r="G80" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I80" s="1">
-        <v>5</v>
-      </c>
-      <c r="J80" s="1">
+      <c r="G86" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I86" s="1">
+        <v>5</v>
+      </c>
+      <c r="J86" s="1">
         <v>4006</v>
       </c>
-      <c r="K80" s="1">
+      <c r="K86" s="1">
         <v>1000</v>
       </c>
-      <c r="L80" s="1">
-        <f>E80*F80</f>
+      <c r="L86" s="1">
+        <f>E86*F86</f>
         <v>50000</v>
       </c>
     </row>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="93">
   <si>
     <t>#</t>
   </si>
@@ -248,58 +248,40 @@
     <t>改造石</t>
   </si>
   <si>
-    <t>兑换宠物口粮*100</t>
-  </si>
-  <si>
-    <t>宠物口粮</t>
+    <t>兑换专属之心*5</t>
+  </si>
+  <si>
+    <t>专属之心</t>
+  </si>
+  <si>
+    <t>兑换四格碎片*1000</t>
+  </si>
+  <si>
+    <t>四格碎片</t>
+  </si>
+  <si>
+    <t>兑换图鉴碎片*1000</t>
+  </si>
+  <si>
+    <t>图鉴碎片</t>
+  </si>
+  <si>
+    <t>兑换经验丹*100</t>
+  </si>
+  <si>
+    <t>经验丹</t>
+  </si>
+  <si>
+    <t>兑换传世精华*200</t>
+  </si>
+  <si>
+    <t>传世精华</t>
   </si>
   <si>
     <t>兑换红装精华*1</t>
   </si>
   <si>
     <t>红装精华</t>
-  </si>
-  <si>
-    <t>兑换天赋秘籍*1</t>
-  </si>
-  <si>
-    <t>天赋秘籍</t>
-  </si>
-  <si>
-    <t>兑换专属之心*5</t>
-  </si>
-  <si>
-    <t>专属之心</t>
-  </si>
-  <si>
-    <t>兑换四格碎片*1000</t>
-  </si>
-  <si>
-    <t>四格碎片</t>
-  </si>
-  <si>
-    <t>兑换图鉴碎片*1000</t>
-  </si>
-  <si>
-    <t>图鉴碎片</t>
-  </si>
-  <si>
-    <t>兑换经验丹*100</t>
-  </si>
-  <si>
-    <t>经验丹</t>
-  </si>
-  <si>
-    <t>兑换传世精华*200</t>
-  </si>
-  <si>
-    <t>传世精华</t>
-  </si>
-  <si>
-    <t>兑换金装精华*1</t>
-  </si>
-  <si>
-    <t>金装精华</t>
   </si>
   <si>
     <t>兑换高级书页*20</t>
@@ -1334,7 +1316,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M86"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1451,7 +1433,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1">
-        <v>168</v>
+        <v>68</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>13</v>
@@ -1470,7 +1452,7 @@
       </c>
       <c r="L6" s="1">
         <f t="shared" ref="L6:L9" si="0">E6*F6</f>
-        <v>50400</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:12">
@@ -1484,7 +1466,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="1">
-        <v>168</v>
+        <v>68</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>15</v>
@@ -1503,7 +1485,7 @@
       </c>
       <c r="L7" s="1">
         <f t="shared" si="0"/>
-        <v>50400</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1517,7 +1499,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="1">
-        <v>168</v>
+        <v>68</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>17</v>
@@ -1536,7 +1518,7 @@
       </c>
       <c r="L8" s="1">
         <f t="shared" si="0"/>
-        <v>50400</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:12">
@@ -1550,7 +1532,7 @@
         <v>19</v>
       </c>
       <c r="F9" s="1">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>20</v>
@@ -1569,7 +1551,7 @@
       </c>
       <c r="L9" s="1">
         <f t="shared" si="0"/>
-        <v>33000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:12">
@@ -1583,7 +1565,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="1">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>22</v>
@@ -1601,8 +1583,8 @@
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" ref="L10:L33" si="1">E10*F10</f>
-        <v>60000</v>
+        <f t="shared" ref="L10:L30" si="1">E10*F10</f>
+        <v>24000</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:12">
@@ -1616,7 +1598,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="1">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>24</v>
@@ -1635,7 +1617,7 @@
       </c>
       <c r="L11" s="1">
         <f t="shared" si="1"/>
-        <v>60000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:12">
@@ -1649,7 +1631,7 @@
         <v>12</v>
       </c>
       <c r="F12" s="1">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>26</v>
@@ -1668,7 +1650,7 @@
       </c>
       <c r="L12" s="1">
         <f t="shared" si="1"/>
-        <v>60000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:12">
@@ -1682,7 +1664,7 @@
         <v>19</v>
       </c>
       <c r="F13" s="1">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>28</v>
@@ -1701,7 +1683,7 @@
       </c>
       <c r="L13" s="1">
         <f t="shared" si="1"/>
-        <v>100000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:12">
@@ -1715,7 +1697,7 @@
         <v>19</v>
       </c>
       <c r="F14" s="1">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>30</v>
@@ -1734,7 +1716,7 @@
       </c>
       <c r="L14" s="1">
         <f t="shared" si="1"/>
-        <v>100000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:12">
@@ -1748,7 +1730,7 @@
         <v>19</v>
       </c>
       <c r="F15" s="1">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>32</v>
@@ -1767,7 +1749,7 @@
       </c>
       <c r="L15" s="1">
         <f t="shared" si="1"/>
-        <v>100000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:12">
@@ -1781,7 +1763,7 @@
         <v>12</v>
       </c>
       <c r="F16" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>34</v>
@@ -1800,7 +1782,7 @@
       </c>
       <c r="L16" s="1">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:12">
@@ -1814,7 +1796,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>36</v>
@@ -1833,7 +1815,7 @@
       </c>
       <c r="L17" s="1">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:12">
@@ -1847,7 +1829,7 @@
         <v>12</v>
       </c>
       <c r="F18" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>38</v>
@@ -1866,7 +1848,7 @@
       </c>
       <c r="L18" s="1">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:12">
@@ -1880,7 +1862,7 @@
         <v>12</v>
       </c>
       <c r="F19" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>40</v>
@@ -1899,7 +1881,7 @@
       </c>
       <c r="L19" s="1">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:12">
@@ -1913,7 +1895,7 @@
         <v>12</v>
       </c>
       <c r="F20" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>42</v>
@@ -1932,7 +1914,7 @@
       </c>
       <c r="L20" s="1">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:12">
@@ -2045,7 +2027,7 @@
         <v>52</v>
       </c>
       <c r="F24" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>53</v>
@@ -2064,7 +2046,7 @@
       </c>
       <c r="L24" s="1">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:12">
@@ -2078,7 +2060,7 @@
         <v>55</v>
       </c>
       <c r="F25" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>56</v>
@@ -2097,7 +2079,7 @@
       </c>
       <c r="L25" s="1">
         <f t="shared" si="1"/>
-        <v>250000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:12">
@@ -2111,7 +2093,7 @@
         <v>58</v>
       </c>
       <c r="F26" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>59</v>
@@ -2130,7 +2112,7 @@
       </c>
       <c r="L26" s="1">
         <f t="shared" si="1"/>
-        <v>400000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:12">
@@ -2144,7 +2126,7 @@
         <v>61</v>
       </c>
       <c r="F27" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>62</v>
@@ -2163,7 +2145,7 @@
       </c>
       <c r="L27" s="1">
         <f t="shared" si="1"/>
-        <v>1500000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:12">
@@ -2177,7 +2159,7 @@
         <v>64</v>
       </c>
       <c r="F28" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>65</v>
@@ -2196,10 +2178,16 @@
       </c>
       <c r="L28" s="1">
         <f t="shared" si="1"/>
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:12">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:12">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C29" s="1">
         <v>24</v>
       </c>
@@ -2243,7 +2231,7 @@
         <v>70</v>
       </c>
       <c r="F30" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>71</v>
@@ -2262,111 +2250,234 @@
       </c>
       <c r="L30" s="1">
         <f t="shared" si="1"/>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:12">
-      <c r="C31" s="1">
-        <v>26</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F31" s="1">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:13">
+      <c r="C32" s="1">
+        <v>101</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
+        <v>500</v>
+      </c>
+      <c r="F32" s="1">
+        <f>20*M32</f>
+        <v>20</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I32" s="1">
+        <v>5</v>
+      </c>
+      <c r="J32" s="1">
+        <v>4010</v>
+      </c>
+      <c r="K32" s="1">
+        <v>5</v>
+      </c>
+      <c r="L32" s="1">
+        <f t="shared" ref="L32:L40" si="2">E32*F32</f>
+        <v>10000</v>
+      </c>
+      <c r="M32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:13">
+      <c r="C33" s="1">
+        <v>102</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1">
         <v>100</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I31" s="1">
-        <v>5</v>
-      </c>
-      <c r="J31" s="1">
-        <v>4022</v>
-      </c>
-      <c r="K31" s="1">
+      <c r="F33" s="1">
+        <f>300*M32</f>
+        <v>300</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I33" s="1">
+        <v>5</v>
+      </c>
+      <c r="J33" s="1">
+        <v>4007</v>
+      </c>
+      <c r="K33" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L33" s="1">
+        <f t="shared" si="2"/>
+        <v>30000</v>
+      </c>
+      <c r="M33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:13">
+      <c r="C34" s="1">
+        <v>103</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+      <c r="E34" s="1">
         <v>100</v>
       </c>
-      <c r="L31" s="1">
-        <f t="shared" si="1"/>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:12">
-      <c r="C32" s="1">
-        <v>27</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0</v>
-      </c>
-      <c r="E32" s="1">
-        <v>3000</v>
-      </c>
-      <c r="F32" s="1">
+      <c r="F34" s="1">
+        <f>500*M32</f>
+        <v>500</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I34" s="1">
+        <v>5</v>
+      </c>
+      <c r="J34" s="1">
+        <v>4101</v>
+      </c>
+      <c r="K34" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L34" s="1">
+        <f t="shared" si="2"/>
+        <v>50000</v>
+      </c>
+      <c r="M34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:13">
+      <c r="C35" s="1">
+        <v>104</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F35" s="1">
+        <f>5*M32</f>
+        <v>5</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I35" s="1">
+        <v>15</v>
+      </c>
+      <c r="J35" s="1">
+        <v>4014</v>
+      </c>
+      <c r="K35" s="1">
         <v>100</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I32" s="1">
-        <v>5</v>
-      </c>
-      <c r="J32" s="1">
+      <c r="L35" s="1">
+        <f t="shared" si="2"/>
+        <v>5000</v>
+      </c>
+      <c r="M35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:13">
+      <c r="C36" s="1">
+        <v>105</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1">
+        <v>500</v>
+      </c>
+      <c r="F36" s="1">
+        <f>20*M32</f>
+        <v>20</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I36" s="1">
+        <v>5</v>
+      </c>
+      <c r="J36" s="1">
+        <v>4012</v>
+      </c>
+      <c r="K36" s="1">
+        <v>200</v>
+      </c>
+      <c r="L36" s="1">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="M36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:13">
+      <c r="C37" s="1">
+        <v>106</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+      <c r="E37" s="1">
+        <v>5000</v>
+      </c>
+      <c r="F37" s="1">
+        <f>5*M32</f>
+        <v>5</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I37" s="1">
+        <v>5</v>
+      </c>
+      <c r="J37" s="1">
         <v>4011</v>
       </c>
-      <c r="K32" s="1">
-        <v>1</v>
-      </c>
-      <c r="L32" s="1">
-        <f t="shared" si="1"/>
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:12">
-      <c r="C33" s="1">
-        <v>28</v>
-      </c>
-      <c r="D33" s="1">
-        <v>0</v>
-      </c>
-      <c r="E33" s="1">
-        <v>20000</v>
-      </c>
-      <c r="F33" s="1">
-        <v>40</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I33" s="1">
-        <v>5</v>
-      </c>
-      <c r="J33" s="1">
-        <v>4020</v>
-      </c>
-      <c r="K33" s="1">
-        <v>1</v>
-      </c>
-      <c r="L33" s="1">
-        <f t="shared" si="1"/>
-        <v>800000</v>
+      <c r="K37" s="1">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1">
+        <f t="shared" si="2"/>
+        <v>25000</v>
+      </c>
+      <c r="M37" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:13">
       <c r="C38" s="1">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
@@ -2375,27 +2486,27 @@
         <v>500</v>
       </c>
       <c r="F38" s="1">
-        <f>20*M38</f>
+        <f>10*M32</f>
+        <v>10</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I38" s="1">
+        <v>5</v>
+      </c>
+      <c r="J38" s="1">
+        <v>4102</v>
+      </c>
+      <c r="K38" s="1">
         <v>20</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I38" s="1">
-        <v>5</v>
-      </c>
-      <c r="J38" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K38" s="1">
-        <v>5</v>
-      </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L46" si="2">E38*F38</f>
-        <v>10000</v>
+        <f t="shared" si="2"/>
+        <v>5000</v>
       </c>
       <c r="M38" s="1">
         <v>1</v>
@@ -2403,36 +2514,36 @@
     </row>
     <row r="39" customHeight="1" spans="3:13">
       <c r="C39" s="1">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D39" s="1">
         <v>1</v>
       </c>
       <c r="E39" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F39" s="1">
-        <f>300*M38</f>
-        <v>300</v>
+        <f>40*M32</f>
+        <v>40</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I39" s="1">
         <v>5</v>
       </c>
       <c r="J39" s="1">
-        <v>4007</v>
+        <v>4001</v>
       </c>
       <c r="K39" s="1">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="L39" s="1">
         <f t="shared" si="2"/>
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="M39" s="1">
         <v>1</v>
@@ -2440,110 +2551,73 @@
     </row>
     <row r="40" customHeight="1" spans="3:13">
       <c r="C40" s="1">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D40" s="1">
         <v>1</v>
       </c>
       <c r="E40" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F40" s="1">
-        <f>500*M38</f>
-        <v>500</v>
+        <f>40*M32</f>
+        <v>40</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I40" s="1">
         <v>5</v>
       </c>
       <c r="J40" s="1">
-        <v>4101</v>
+        <v>4002</v>
       </c>
       <c r="K40" s="1">
-        <v>1000</v>
+        <v>6000000</v>
       </c>
       <c r="L40" s="1">
         <f t="shared" si="2"/>
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="M40" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:13">
-      <c r="C41" s="1">
-        <v>104</v>
-      </c>
-      <c r="D41" s="1">
-        <v>1</v>
-      </c>
-      <c r="E41" s="1">
-        <v>1000</v>
-      </c>
-      <c r="F41" s="1">
-        <f>6*M38</f>
-        <v>6</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I41" s="1">
-        <v>15</v>
-      </c>
-      <c r="J41" s="1">
-        <v>4014</v>
-      </c>
-      <c r="K41" s="1">
-        <v>100</v>
-      </c>
-      <c r="L41" s="1">
-        <f t="shared" si="2"/>
-        <v>6000</v>
-      </c>
-      <c r="M41" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:13">
       <c r="C42" s="1">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="D42" s="1">
-        <v>1</v>
-      </c>
-      <c r="E42" s="1">
-        <v>500</v>
+        <v>2</v>
+      </c>
+      <c r="E42" s="4">
+        <v>1000</v>
       </c>
       <c r="F42" s="1">
-        <f>20*M38</f>
+        <f>20*M42</f>
         <v>20</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="I42" s="1">
         <v>5</v>
       </c>
       <c r="J42" s="1">
-        <v>4012</v>
+        <v>4010</v>
       </c>
       <c r="K42" s="1">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="2"/>
-        <v>10000</v>
+        <f t="shared" ref="L42:L77" si="3">E42*F42</f>
+        <v>20000</v>
       </c>
       <c r="M42" s="1">
         <v>1</v>
@@ -2551,36 +2625,36 @@
     </row>
     <row r="43" customHeight="1" spans="3:13">
       <c r="C43" s="1">
-        <v>106</v>
+        <v>202</v>
       </c>
       <c r="D43" s="1">
-        <v>1</v>
-      </c>
-      <c r="E43" s="1">
-        <v>15000</v>
+        <v>2</v>
+      </c>
+      <c r="E43" s="4">
+        <v>200</v>
       </c>
       <c r="F43" s="1">
-        <f>5*M38</f>
-        <v>5</v>
+        <f>300*M42</f>
+        <v>300</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="I43" s="1">
         <v>5</v>
       </c>
       <c r="J43" s="1">
-        <v>4019</v>
+        <v>4007</v>
       </c>
       <c r="K43" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="2"/>
-        <v>75000</v>
+        <f t="shared" si="3"/>
+        <v>60000</v>
       </c>
       <c r="M43" s="1">
         <v>1</v>
@@ -2588,36 +2662,36 @@
     </row>
     <row r="44" customHeight="1" spans="3:13">
       <c r="C44" s="1">
-        <v>107</v>
+        <v>203</v>
       </c>
       <c r="D44" s="1">
-        <v>1</v>
-      </c>
-      <c r="E44" s="1">
+        <v>2</v>
+      </c>
+      <c r="E44" s="4">
+        <v>200</v>
+      </c>
+      <c r="F44" s="1">
+        <f>500*M42</f>
         <v>500</v>
       </c>
-      <c r="F44" s="1">
-        <f>10*M38</f>
-        <v>10</v>
-      </c>
       <c r="G44" s="1" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="I44" s="1">
         <v>5</v>
       </c>
       <c r="J44" s="1">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="K44" s="1">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="2"/>
-        <v>5000</v>
+        <f t="shared" si="3"/>
+        <v>100000</v>
       </c>
       <c r="M44" s="1">
         <v>1</v>
@@ -2625,36 +2699,36 @@
     </row>
     <row r="45" customHeight="1" spans="3:13">
       <c r="C45" s="1">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="D45" s="1">
-        <v>1</v>
-      </c>
-      <c r="E45" s="1">
-        <v>500</v>
+        <v>2</v>
+      </c>
+      <c r="E45" s="4">
+        <v>2000</v>
       </c>
       <c r="F45" s="1">
-        <f>40*M38</f>
-        <v>40</v>
+        <f>5*M42</f>
+        <v>5</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I45" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J45" s="1">
-        <v>4001</v>
+        <v>4014</v>
       </c>
       <c r="K45" s="1">
-        <v>1000000</v>
+        <v>100</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="2"/>
-        <v>20000</v>
+        <f t="shared" si="3"/>
+        <v>10000</v>
       </c>
       <c r="M45" s="1">
         <v>1</v>
@@ -2662,44 +2736,81 @@
     </row>
     <row r="46" customHeight="1" spans="3:13">
       <c r="C46" s="1">
-        <v>109</v>
+        <v>205</v>
       </c>
       <c r="D46" s="1">
-        <v>1</v>
-      </c>
-      <c r="E46" s="1">
-        <v>500</v>
+        <v>2</v>
+      </c>
+      <c r="E46" s="4">
+        <v>1000</v>
       </c>
       <c r="F46" s="1">
-        <f>40*M38</f>
-        <v>40</v>
+        <f>20*M42</f>
+        <v>20</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="I46" s="1">
         <v>5</v>
       </c>
       <c r="J46" s="1">
-        <v>4002</v>
+        <v>4012</v>
       </c>
       <c r="K46" s="1">
-        <v>6000000</v>
+        <v>200</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>20000</v>
       </c>
       <c r="M46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:13">
+      <c r="C47" s="1">
+        <v>206</v>
+      </c>
+      <c r="D47" s="1">
+        <v>2</v>
+      </c>
+      <c r="E47" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F47" s="1">
+        <f>5*M42</f>
+        <v>5</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I47" s="1">
+        <v>5</v>
+      </c>
+      <c r="J47" s="1">
+        <v>4011</v>
+      </c>
+      <c r="K47" s="1">
+        <v>1</v>
+      </c>
+      <c r="L47" s="1">
+        <f t="shared" si="3"/>
+        <v>50000</v>
+      </c>
+      <c r="M47" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:13">
       <c r="C48" s="1">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="D48" s="1">
         <v>2</v>
@@ -2708,27 +2819,27 @@
         <v>1000</v>
       </c>
       <c r="F48" s="1">
-        <f>20*M48</f>
+        <f>10*M42</f>
+        <v>10</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I48" s="1">
+        <v>5</v>
+      </c>
+      <c r="J48" s="1">
+        <v>4102</v>
+      </c>
+      <c r="K48" s="1">
         <v>20</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I48" s="1">
-        <v>5</v>
-      </c>
-      <c r="J48" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K48" s="1">
-        <v>5</v>
-      </c>
       <c r="L48" s="1">
-        <f t="shared" ref="L48:L83" si="3">E48*F48</f>
-        <v>20000</v>
+        <f t="shared" si="3"/>
+        <v>10000</v>
       </c>
       <c r="M48" s="1">
         <v>1</v>
@@ -2736,36 +2847,36 @@
     </row>
     <row r="49" customHeight="1" spans="3:13">
       <c r="C49" s="1">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D49" s="1">
         <v>2</v>
       </c>
       <c r="E49" s="4">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="F49" s="1">
-        <f>300*M48</f>
-        <v>300</v>
+        <f>40*M42</f>
+        <v>40</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I49" s="1">
         <v>5</v>
       </c>
       <c r="J49" s="1">
-        <v>4007</v>
+        <v>4001</v>
       </c>
       <c r="K49" s="1">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="L49" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>40000</v>
       </c>
       <c r="M49" s="1">
         <v>1</v>
@@ -2773,36 +2884,36 @@
     </row>
     <row r="50" customHeight="1" spans="3:13">
       <c r="C50" s="1">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="D50" s="1">
         <v>2</v>
       </c>
       <c r="E50" s="4">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="F50" s="1">
-        <f>500*M48</f>
-        <v>500</v>
+        <f>40*M42</f>
+        <v>40</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I50" s="1">
         <v>5</v>
       </c>
       <c r="J50" s="1">
-        <v>4101</v>
+        <v>4002</v>
       </c>
       <c r="K50" s="1">
-        <v>1000</v>
+        <v>6000000</v>
       </c>
       <c r="L50" s="1">
         <f t="shared" si="3"/>
-        <v>100000</v>
+        <v>40000</v>
       </c>
       <c r="M50" s="1">
         <v>1</v>
@@ -2810,36 +2921,36 @@
     </row>
     <row r="51" customHeight="1" spans="3:13">
       <c r="C51" s="1">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D51" s="1">
-        <v>2</v>
-      </c>
-      <c r="E51" s="4">
+        <v>3</v>
+      </c>
+      <c r="E51" s="1">
         <v>2000</v>
       </c>
       <c r="F51" s="1">
-        <f>6*M48</f>
-        <v>6</v>
+        <f>20*M51</f>
+        <v>20</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="I51" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J51" s="1">
-        <v>4014</v>
+        <v>4010</v>
       </c>
       <c r="K51" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L51" s="1">
         <f t="shared" si="3"/>
-        <v>12000</v>
+        <v>40000</v>
       </c>
       <c r="M51" s="1">
         <v>1</v>
@@ -2847,36 +2958,36 @@
     </row>
     <row r="52" customHeight="1" spans="3:13">
       <c r="C52" s="1">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="D52" s="1">
-        <v>2</v>
-      </c>
-      <c r="E52" s="4">
+        <v>3</v>
+      </c>
+      <c r="E52" s="1">
+        <v>400</v>
+      </c>
+      <c r="F52" s="1">
+        <f>300*M51</f>
+        <v>300</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I52" s="1">
+        <v>5</v>
+      </c>
+      <c r="J52" s="1">
+        <v>4007</v>
+      </c>
+      <c r="K52" s="1">
         <v>1000</v>
-      </c>
-      <c r="F52" s="1">
-        <f>20*M48</f>
-        <v>20</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I52" s="1">
-        <v>5</v>
-      </c>
-      <c r="J52" s="1">
-        <v>4012</v>
-      </c>
-      <c r="K52" s="1">
-        <v>200</v>
       </c>
       <c r="L52" s="1">
         <f t="shared" si="3"/>
-        <v>20000</v>
+        <v>120000</v>
       </c>
       <c r="M52" s="1">
         <v>1</v>
@@ -2884,36 +2995,36 @@
     </row>
     <row r="53" customHeight="1" spans="3:13">
       <c r="C53" s="1">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D53" s="1">
-        <v>2</v>
-      </c>
-      <c r="E53" s="4">
-        <v>30000</v>
+        <v>3</v>
+      </c>
+      <c r="E53" s="1">
+        <v>400</v>
       </c>
       <c r="F53" s="1">
-        <f>5*M48</f>
-        <v>5</v>
+        <f>500*M51</f>
+        <v>500</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I53" s="1">
         <v>5</v>
       </c>
       <c r="J53" s="1">
-        <v>4019</v>
+        <v>4101</v>
       </c>
       <c r="K53" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="L53" s="1">
         <f t="shared" si="3"/>
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="M53" s="1">
         <v>1</v>
@@ -2921,36 +3032,36 @@
     </row>
     <row r="54" customHeight="1" spans="3:13">
       <c r="C54" s="1">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D54" s="1">
-        <v>2</v>
-      </c>
-      <c r="E54" s="4">
-        <v>1000</v>
+        <v>3</v>
+      </c>
+      <c r="E54" s="1">
+        <v>4000</v>
       </c>
       <c r="F54" s="1">
-        <f>10*M48</f>
-        <v>10</v>
+        <f>5*M51</f>
+        <v>5</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I54" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J54" s="1">
-        <v>4102</v>
+        <v>4014</v>
       </c>
       <c r="K54" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L54" s="1">
         <f t="shared" si="3"/>
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="M54" s="1">
         <v>1</v>
@@ -2958,32 +3069,32 @@
     </row>
     <row r="55" customHeight="1" spans="3:13">
       <c r="C55" s="1">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D55" s="1">
-        <v>2</v>
-      </c>
-      <c r="E55" s="4">
-        <v>1000</v>
+        <v>3</v>
+      </c>
+      <c r="E55" s="1">
+        <v>2000</v>
       </c>
       <c r="F55" s="1">
-        <f>40*M48</f>
-        <v>40</v>
+        <f>20*M51</f>
+        <v>20</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I55" s="1">
         <v>5</v>
       </c>
       <c r="J55" s="1">
-        <v>4001</v>
+        <v>4012</v>
       </c>
       <c r="K55" s="1">
-        <v>1000000</v>
+        <v>200</v>
       </c>
       <c r="L55" s="1">
         <f t="shared" si="3"/>
@@ -2995,36 +3106,36 @@
     </row>
     <row r="56" customHeight="1" spans="3:13">
       <c r="C56" s="1">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="D56" s="1">
-        <v>2</v>
-      </c>
-      <c r="E56" s="4">
-        <v>1000</v>
+        <v>3</v>
+      </c>
+      <c r="E56" s="1">
+        <v>20000</v>
       </c>
       <c r="F56" s="1">
-        <f>40*M48</f>
-        <v>40</v>
+        <f>5*M51</f>
+        <v>5</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I56" s="1">
         <v>5</v>
       </c>
       <c r="J56" s="1">
-        <v>4002</v>
+        <v>4011</v>
       </c>
       <c r="K56" s="1">
-        <v>6000000</v>
+        <v>1</v>
       </c>
       <c r="L56" s="1">
         <f t="shared" si="3"/>
-        <v>40000</v>
+        <v>100000</v>
       </c>
       <c r="M56" s="1">
         <v>1</v>
@@ -3032,7 +3143,7 @@
     </row>
     <row r="57" customHeight="1" spans="3:13">
       <c r="C57" s="1">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D57" s="1">
         <v>3</v>
@@ -3041,27 +3152,27 @@
         <v>2000</v>
       </c>
       <c r="F57" s="1">
-        <f>20*M57</f>
+        <f>10*M51</f>
+        <v>10</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I57" s="1">
+        <v>5</v>
+      </c>
+      <c r="J57" s="1">
+        <v>4102</v>
+      </c>
+      <c r="K57" s="1">
         <v>20</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I57" s="1">
-        <v>5</v>
-      </c>
-      <c r="J57" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K57" s="1">
-        <v>5</v>
       </c>
       <c r="L57" s="1">
         <f t="shared" si="3"/>
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="M57" s="1">
         <v>1</v>
@@ -3069,36 +3180,36 @@
     </row>
     <row r="58" customHeight="1" spans="3:13">
       <c r="C58" s="1">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D58" s="1">
         <v>3</v>
       </c>
       <c r="E58" s="1">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="F58" s="1">
-        <f>300*M57</f>
-        <v>300</v>
+        <f>40*M51</f>
+        <v>40</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I58" s="1">
         <v>5</v>
       </c>
       <c r="J58" s="1">
-        <v>4007</v>
+        <v>4001</v>
       </c>
       <c r="K58" s="1">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="L58" s="1">
         <f t="shared" si="3"/>
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="M58" s="1">
         <v>1</v>
@@ -3106,36 +3217,36 @@
     </row>
     <row r="59" customHeight="1" spans="3:13">
       <c r="C59" s="1">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D59" s="1">
         <v>3</v>
       </c>
       <c r="E59" s="1">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="F59" s="1">
-        <f>500*M57</f>
-        <v>500</v>
+        <f>40*M51</f>
+        <v>40</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I59" s="1">
         <v>5</v>
       </c>
       <c r="J59" s="1">
-        <v>4101</v>
+        <v>4002</v>
       </c>
       <c r="K59" s="1">
-        <v>1000</v>
+        <v>6000000</v>
       </c>
       <c r="L59" s="1">
         <f t="shared" si="3"/>
-        <v>200000</v>
+        <v>80000</v>
       </c>
       <c r="M59" s="1">
         <v>1</v>
@@ -3143,36 +3254,36 @@
     </row>
     <row r="60" customHeight="1" spans="3:13">
       <c r="C60" s="1">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="D60" s="1">
-        <v>3</v>
-      </c>
-      <c r="E60" s="1">
-        <v>4000</v>
+        <v>4</v>
+      </c>
+      <c r="E60" s="4">
+        <v>3000</v>
       </c>
       <c r="F60" s="1">
-        <f>6*M57</f>
-        <v>6</v>
+        <f>20*M60</f>
+        <v>20</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="I60" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J60" s="1">
-        <v>4014</v>
+        <v>4010</v>
       </c>
       <c r="K60" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L60" s="1">
         <f t="shared" si="3"/>
-        <v>24000</v>
+        <v>60000</v>
       </c>
       <c r="M60" s="1">
         <v>1</v>
@@ -3180,36 +3291,36 @@
     </row>
     <row r="61" customHeight="1" spans="3:13">
       <c r="C61" s="1">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D61" s="1">
-        <v>3</v>
-      </c>
-      <c r="E61" s="1">
-        <v>2000</v>
+        <v>4</v>
+      </c>
+      <c r="E61" s="4">
+        <v>600</v>
       </c>
       <c r="F61" s="1">
-        <f>20*M57</f>
-        <v>20</v>
+        <f>300*M60</f>
+        <v>300</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I61" s="1">
         <v>5</v>
       </c>
       <c r="J61" s="1">
-        <v>4012</v>
+        <v>4007</v>
       </c>
       <c r="K61" s="1">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="L61" s="1">
         <f t="shared" si="3"/>
-        <v>40000</v>
+        <v>180000</v>
       </c>
       <c r="M61" s="1">
         <v>1</v>
@@ -3217,36 +3328,36 @@
     </row>
     <row r="62" customHeight="1" spans="3:13">
       <c r="C62" s="1">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="D62" s="1">
-        <v>3</v>
-      </c>
-      <c r="E62" s="1">
-        <v>45000</v>
+        <v>4</v>
+      </c>
+      <c r="E62" s="4">
+        <v>600</v>
       </c>
       <c r="F62" s="1">
-        <f>5*M57</f>
-        <v>5</v>
+        <f>500*M60</f>
+        <v>500</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I62" s="1">
         <v>5</v>
       </c>
       <c r="J62" s="1">
-        <v>4019</v>
+        <v>4101</v>
       </c>
       <c r="K62" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="L62" s="1">
         <f t="shared" si="3"/>
-        <v>225000</v>
+        <v>300000</v>
       </c>
       <c r="M62" s="1">
         <v>1</v>
@@ -3254,36 +3365,36 @@
     </row>
     <row r="63" customHeight="1" spans="3:13">
       <c r="C63" s="1">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D63" s="1">
-        <v>3</v>
-      </c>
-      <c r="E63" s="1">
-        <v>2000</v>
+        <v>4</v>
+      </c>
+      <c r="E63" s="4">
+        <v>6000</v>
       </c>
       <c r="F63" s="1">
-        <f>10*M57</f>
-        <v>10</v>
+        <f>5*M60</f>
+        <v>5</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I63" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J63" s="1">
-        <v>4102</v>
+        <v>4014</v>
       </c>
       <c r="K63" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L63" s="1">
         <f t="shared" si="3"/>
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="M63" s="1">
         <v>1</v>
@@ -3291,36 +3402,36 @@
     </row>
     <row r="64" customHeight="1" spans="3:13">
       <c r="C64" s="1">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="D64" s="1">
-        <v>3</v>
-      </c>
-      <c r="E64" s="1">
-        <v>2000</v>
+        <v>4</v>
+      </c>
+      <c r="E64" s="4">
+        <v>3000</v>
       </c>
       <c r="F64" s="1">
-        <f>40*M57</f>
-        <v>40</v>
+        <f>20*M60</f>
+        <v>20</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I64" s="1">
         <v>5</v>
       </c>
       <c r="J64" s="1">
-        <v>4001</v>
+        <v>4012</v>
       </c>
       <c r="K64" s="1">
-        <v>1000000</v>
+        <v>200</v>
       </c>
       <c r="L64" s="1">
         <f t="shared" si="3"/>
-        <v>80000</v>
+        <v>60000</v>
       </c>
       <c r="M64" s="1">
         <v>1</v>
@@ -3328,36 +3439,36 @@
     </row>
     <row r="65" customHeight="1" spans="3:13">
       <c r="C65" s="1">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D65" s="1">
-        <v>3</v>
-      </c>
-      <c r="E65" s="1">
-        <v>2000</v>
+        <v>4</v>
+      </c>
+      <c r="E65" s="4">
+        <v>30000</v>
       </c>
       <c r="F65" s="1">
-        <f>40*M57</f>
-        <v>40</v>
+        <f>5*M60</f>
+        <v>5</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I65" s="1">
         <v>5</v>
       </c>
       <c r="J65" s="1">
-        <v>4002</v>
+        <v>4011</v>
       </c>
       <c r="K65" s="1">
-        <v>6000000</v>
+        <v>1</v>
       </c>
       <c r="L65" s="1">
         <f t="shared" si="3"/>
-        <v>80000</v>
+        <v>150000</v>
       </c>
       <c r="M65" s="1">
         <v>1</v>
@@ -3365,7 +3476,7 @@
     </row>
     <row r="66" customHeight="1" spans="3:13">
       <c r="C66" s="1">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D66" s="1">
         <v>4</v>
@@ -3374,27 +3485,27 @@
         <v>3000</v>
       </c>
       <c r="F66" s="1">
-        <f>20*M66</f>
+        <f>10*M60</f>
+        <v>10</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I66" s="1">
+        <v>5</v>
+      </c>
+      <c r="J66" s="1">
+        <v>4102</v>
+      </c>
+      <c r="K66" s="1">
         <v>20</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I66" s="1">
-        <v>5</v>
-      </c>
-      <c r="J66" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K66" s="1">
-        <v>5</v>
       </c>
       <c r="L66" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="M66" s="1">
         <v>1</v>
@@ -3402,36 +3513,36 @@
     </row>
     <row r="67" customHeight="1" spans="3:13">
       <c r="C67" s="1">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D67" s="1">
         <v>4</v>
       </c>
       <c r="E67" s="4">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="F67" s="1">
-        <f>300*M66</f>
-        <v>300</v>
+        <f>40*M60</f>
+        <v>40</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I67" s="1">
         <v>5</v>
       </c>
       <c r="J67" s="1">
-        <v>4007</v>
+        <v>4001</v>
       </c>
       <c r="K67" s="1">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="L67" s="1">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>120000</v>
       </c>
       <c r="M67" s="1">
         <v>1</v>
@@ -3439,36 +3550,36 @@
     </row>
     <row r="68" customHeight="1" spans="3:13">
       <c r="C68" s="1">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D68" s="1">
         <v>4</v>
       </c>
       <c r="E68" s="4">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="F68" s="1">
-        <f>500*M66</f>
-        <v>500</v>
+        <f>40*M60</f>
+        <v>40</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I68" s="1">
         <v>5</v>
       </c>
       <c r="J68" s="1">
-        <v>4101</v>
+        <v>4002</v>
       </c>
       <c r="K68" s="1">
-        <v>1000</v>
+        <v>6000000</v>
       </c>
       <c r="L68" s="1">
         <f t="shared" si="3"/>
-        <v>300000</v>
+        <v>120000</v>
       </c>
       <c r="M68" s="1">
         <v>1</v>
@@ -3476,229 +3587,229 @@
     </row>
     <row r="69" customHeight="1" spans="3:13">
       <c r="C69" s="1">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D69" s="1">
-        <v>4</v>
-      </c>
-      <c r="E69" s="4">
-        <v>6000</v>
+        <v>5</v>
+      </c>
+      <c r="E69" s="1">
+        <v>4000</v>
       </c>
       <c r="F69" s="1">
-        <f>6*M66</f>
-        <v>6</v>
+        <f>20*M69</f>
+        <v>80</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="I69" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J69" s="1">
-        <v>4014</v>
+        <v>4010</v>
       </c>
       <c r="K69" s="1">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="L69" s="1">
         <f t="shared" si="3"/>
-        <v>36000</v>
+        <v>320000</v>
       </c>
       <c r="M69" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:13">
       <c r="C70" s="1">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D70" s="1">
-        <v>4</v>
-      </c>
-      <c r="E70" s="4">
-        <v>3000</v>
+        <v>5</v>
+      </c>
+      <c r="E70" s="1">
+        <v>800</v>
       </c>
       <c r="F70" s="1">
-        <f>20*M66</f>
-        <v>20</v>
+        <f>300*M69</f>
+        <v>1200</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I70" s="1">
         <v>5</v>
       </c>
       <c r="J70" s="1">
-        <v>4012</v>
+        <v>4007</v>
       </c>
       <c r="K70" s="1">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="L70" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>960000</v>
       </c>
       <c r="M70" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:13">
       <c r="C71" s="1">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D71" s="1">
-        <v>4</v>
-      </c>
-      <c r="E71" s="4">
-        <v>60000</v>
+        <v>5</v>
+      </c>
+      <c r="E71" s="1">
+        <v>800</v>
       </c>
       <c r="F71" s="1">
-        <f>5*M66</f>
-        <v>5</v>
+        <f>500*M69</f>
+        <v>2000</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I71" s="1">
         <v>5</v>
       </c>
       <c r="J71" s="1">
-        <v>4019</v>
+        <v>4101</v>
       </c>
       <c r="K71" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="L71" s="1">
         <f t="shared" si="3"/>
-        <v>300000</v>
+        <v>1600000</v>
       </c>
       <c r="M71" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:13">
       <c r="C72" s="1">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="D72" s="1">
-        <v>4</v>
-      </c>
-      <c r="E72" s="4">
-        <v>3000</v>
+        <v>5</v>
+      </c>
+      <c r="E72" s="1">
+        <v>8000</v>
       </c>
       <c r="F72" s="1">
-        <f>10*M66</f>
-        <v>10</v>
+        <f>5*M69</f>
+        <v>20</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I72" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J72" s="1">
-        <v>4102</v>
+        <v>4014</v>
       </c>
       <c r="K72" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L72" s="1">
         <f t="shared" si="3"/>
-        <v>30000</v>
+        <v>160000</v>
       </c>
       <c r="M72" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:13">
       <c r="C73" s="1">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D73" s="1">
-        <v>4</v>
-      </c>
-      <c r="E73" s="4">
-        <v>3000</v>
+        <v>5</v>
+      </c>
+      <c r="E73" s="1">
+        <v>4000</v>
       </c>
       <c r="F73" s="1">
-        <f>40*M66</f>
-        <v>40</v>
+        <f>20*M69</f>
+        <v>80</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I73" s="1">
         <v>5</v>
       </c>
       <c r="J73" s="1">
-        <v>4001</v>
+        <v>4012</v>
       </c>
       <c r="K73" s="1">
-        <v>1000000</v>
+        <v>200</v>
       </c>
       <c r="L73" s="1">
         <f t="shared" si="3"/>
-        <v>120000</v>
+        <v>320000</v>
       </c>
       <c r="M73" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:13">
       <c r="C74" s="1">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D74" s="1">
-        <v>4</v>
-      </c>
-      <c r="E74" s="4">
-        <v>3000</v>
+        <v>5</v>
+      </c>
+      <c r="E74" s="1">
+        <v>40000</v>
       </c>
       <c r="F74" s="1">
-        <f>40*M66</f>
-        <v>40</v>
+        <f>5*M69</f>
+        <v>20</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I74" s="1">
         <v>5</v>
       </c>
       <c r="J74" s="1">
-        <v>4002</v>
+        <v>4011</v>
       </c>
       <c r="K74" s="1">
-        <v>6000000</v>
+        <v>1</v>
       </c>
       <c r="L74" s="1">
         <f t="shared" si="3"/>
-        <v>120000</v>
+        <v>800000</v>
       </c>
       <c r="M74" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:13">
       <c r="C75" s="1">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D75" s="1">
         <v>5</v>
@@ -3707,27 +3818,27 @@
         <v>4000</v>
       </c>
       <c r="F75" s="1">
-        <f>20*M75</f>
-        <v>80</v>
+        <f>10*M69</f>
+        <v>40</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="I75" s="1">
         <v>5</v>
       </c>
       <c r="J75" s="1">
-        <v>4010</v>
+        <v>4102</v>
       </c>
       <c r="K75" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L75" s="1">
         <f t="shared" si="3"/>
-        <v>320000</v>
+        <v>160000</v>
       </c>
       <c r="M75" s="1">
         <v>4</v>
@@ -3735,36 +3846,36 @@
     </row>
     <row r="76" customHeight="1" spans="3:13">
       <c r="C76" s="1">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="D76" s="1">
         <v>5</v>
       </c>
       <c r="E76" s="1">
-        <v>800</v>
+        <v>4000</v>
       </c>
       <c r="F76" s="1">
-        <f>300*M75</f>
-        <v>1200</v>
+        <f>40*M69</f>
+        <v>160</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I76" s="1">
         <v>5</v>
       </c>
       <c r="J76" s="1">
-        <v>4007</v>
+        <v>4001</v>
       </c>
       <c r="K76" s="1">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="L76" s="1">
         <f t="shared" si="3"/>
-        <v>960000</v>
+        <v>640000</v>
       </c>
       <c r="M76" s="1">
         <v>4</v>
@@ -3772,293 +3883,71 @@
     </row>
     <row r="77" customHeight="1" spans="3:13">
       <c r="C77" s="1">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D77" s="1">
         <v>5</v>
       </c>
       <c r="E77" s="1">
-        <v>800</v>
+        <v>4000</v>
       </c>
       <c r="F77" s="1">
-        <f>500*M75</f>
-        <v>2000</v>
+        <f>40*M69</f>
+        <v>160</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I77" s="1">
         <v>5</v>
       </c>
       <c r="J77" s="1">
-        <v>4101</v>
+        <v>4002</v>
       </c>
       <c r="K77" s="1">
-        <v>1000</v>
+        <v>6000000</v>
       </c>
       <c r="L77" s="1">
         <f t="shared" si="3"/>
-        <v>1600000</v>
+        <v>640000</v>
       </c>
       <c r="M77" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="3:13">
-      <c r="C78" s="1">
-        <v>231</v>
-      </c>
-      <c r="D78" s="1">
-        <v>5</v>
-      </c>
-      <c r="E78" s="1">
-        <v>8000</v>
-      </c>
-      <c r="F78" s="1">
-        <f>6*M75</f>
-        <v>24</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I78" s="1">
-        <v>15</v>
-      </c>
-      <c r="J78" s="1">
-        <v>4014</v>
-      </c>
-      <c r="K78" s="1">
-        <v>100</v>
-      </c>
-      <c r="L78" s="1">
-        <f t="shared" si="3"/>
-        <v>192000</v>
-      </c>
-      <c r="M78" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" spans="3:13">
-      <c r="C79" s="1">
-        <v>232</v>
-      </c>
-      <c r="D79" s="1">
-        <v>5</v>
-      </c>
-      <c r="E79" s="1">
-        <v>4000</v>
-      </c>
-      <c r="F79" s="1">
-        <f>20*M75</f>
-        <v>80</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I79" s="1">
-        <v>5</v>
-      </c>
-      <c r="J79" s="1">
-        <v>4012</v>
-      </c>
-      <c r="K79" s="1">
-        <v>200</v>
-      </c>
-      <c r="L79" s="1">
-        <f t="shared" si="3"/>
-        <v>320000</v>
-      </c>
-      <c r="M79" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" customHeight="1" spans="3:13">
+    <row r="80" customHeight="1" spans="3:12">
       <c r="C80" s="1">
-        <v>233</v>
+        <v>999</v>
       </c>
       <c r="D80" s="1">
-        <v>5</v>
-      </c>
-      <c r="E80" s="1">
-        <v>75000</v>
+        <v>0</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="F80" s="1">
-        <f>5*M75</f>
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I80" s="1">
         <v>5</v>
       </c>
       <c r="J80" s="1">
-        <v>4019</v>
+        <v>4006</v>
       </c>
       <c r="K80" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="3"/>
-        <v>1500000</v>
-      </c>
-      <c r="M80" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" customHeight="1" spans="3:13">
-      <c r="C81" s="1">
-        <v>234</v>
-      </c>
-      <c r="D81" s="1">
-        <v>5</v>
-      </c>
-      <c r="E81" s="1">
-        <v>4000</v>
-      </c>
-      <c r="F81" s="1">
-        <f>10*M75</f>
-        <v>40</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I81" s="1">
-        <v>5</v>
-      </c>
-      <c r="J81" s="1">
-        <v>4102</v>
-      </c>
-      <c r="K81" s="1">
-        <v>20</v>
-      </c>
-      <c r="L81" s="1">
-        <f t="shared" si="3"/>
-        <v>160000</v>
-      </c>
-      <c r="M81" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" spans="3:13">
-      <c r="C82" s="1">
-        <v>235</v>
-      </c>
-      <c r="D82" s="1">
-        <v>5</v>
-      </c>
-      <c r="E82" s="1">
-        <v>4000</v>
-      </c>
-      <c r="F82" s="1">
-        <f>40*M75</f>
-        <v>160</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I82" s="1">
-        <v>5</v>
-      </c>
-      <c r="J82" s="1">
-        <v>4001</v>
-      </c>
-      <c r="K82" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="L82" s="1">
-        <f t="shared" si="3"/>
-        <v>640000</v>
-      </c>
-      <c r="M82" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" spans="3:13">
-      <c r="C83" s="1">
-        <v>236</v>
-      </c>
-      <c r="D83" s="1">
-        <v>5</v>
-      </c>
-      <c r="E83" s="1">
-        <v>4000</v>
-      </c>
-      <c r="F83" s="1">
-        <f>40*M75</f>
-        <v>160</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I83" s="1">
-        <v>5</v>
-      </c>
-      <c r="J83" s="1">
-        <v>4002</v>
-      </c>
-      <c r="K83" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="L83" s="1">
-        <f t="shared" si="3"/>
-        <v>640000</v>
-      </c>
-      <c r="M83" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" customHeight="1" spans="3:12">
-      <c r="C86" s="1">
-        <v>999</v>
-      </c>
-      <c r="D86" s="1">
-        <v>0</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F86" s="1">
-        <v>50</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I86" s="1">
-        <v>5</v>
-      </c>
-      <c r="J86" s="1">
-        <v>4006</v>
-      </c>
-      <c r="K86" s="1">
-        <v>1000</v>
-      </c>
-      <c r="L86" s="1">
-        <f>E86*F86</f>
+        <f>E80*F80</f>
         <v>50000</v>
       </c>
     </row>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="101">
   <si>
     <t>#</t>
   </si>
@@ -248,6 +248,30 @@
     <t>改造石</t>
   </si>
   <si>
+    <t>兑换宠物口粮*100</t>
+  </si>
+  <si>
+    <t>宠物口粮</t>
+  </si>
+  <si>
+    <t>兑换红装精华*1</t>
+  </si>
+  <si>
+    <t>红装精华</t>
+  </si>
+  <si>
+    <t>兑换天赋秘籍*1</t>
+  </si>
+  <si>
+    <t>天赋秘籍</t>
+  </si>
+  <si>
+    <t>兑换红宠自选</t>
+  </si>
+  <si>
+    <t>红宠自选</t>
+  </si>
+  <si>
     <t>兑换专属之心*5</t>
   </si>
   <si>
@@ -278,10 +302,10 @@
     <t>传世精华</t>
   </si>
   <si>
-    <t>兑换红装精华*1</t>
-  </si>
-  <si>
-    <t>红装精华</t>
+    <t>兑换金装精华*1</t>
+  </si>
+  <si>
+    <t>金装精华</t>
   </si>
   <si>
     <t>兑换高级书页*20</t>
@@ -1316,7 +1340,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1433,7 +1457,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>13</v>
@@ -1452,7 +1476,7 @@
       </c>
       <c r="L6" s="1">
         <f t="shared" ref="L6:L9" si="0">E6*F6</f>
-        <v>20400</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:12">
@@ -1466,7 +1490,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="1">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>15</v>
@@ -1485,7 +1509,7 @@
       </c>
       <c r="L7" s="1">
         <f t="shared" si="0"/>
-        <v>20400</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1499,7 +1523,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="1">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>17</v>
@@ -1518,7 +1542,7 @@
       </c>
       <c r="L8" s="1">
         <f t="shared" si="0"/>
-        <v>20400</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:12">
@@ -1532,7 +1556,7 @@
         <v>19</v>
       </c>
       <c r="F9" s="1">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>20</v>
@@ -1551,7 +1575,7 @@
       </c>
       <c r="L9" s="1">
         <f t="shared" si="0"/>
-        <v>14000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:12">
@@ -1583,7 +1607,7 @@
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" ref="L10:L30" si="1">E10*F10</f>
+        <f t="shared" ref="L10:L34" si="1">E10*F10</f>
         <v>24000</v>
       </c>
     </row>
@@ -2253,823 +2277,807 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="3:13">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C31" s="1">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="1">
+        <v>100</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I31" s="1">
+        <v>5</v>
+      </c>
+      <c r="J31" s="1">
+        <v>4022</v>
+      </c>
+      <c r="K31" s="1">
+        <v>100</v>
+      </c>
+      <c r="L31" s="1">
+        <f t="shared" si="1"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C32" s="1">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
+      <c r="E32" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F32" s="1">
+        <v>50</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I32" s="1">
+        <v>5</v>
+      </c>
+      <c r="J32" s="1">
+        <v>4011</v>
+      </c>
+      <c r="K32" s="1">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1">
+        <f t="shared" si="1"/>
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C33" s="1">
+        <v>28</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0</v>
+      </c>
+      <c r="E33" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F33" s="1">
+        <v>20</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I33" s="1">
+        <v>5</v>
+      </c>
+      <c r="J33" s="1">
+        <v>4020</v>
+      </c>
+      <c r="K33" s="1">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1">
+        <f t="shared" si="1"/>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C34" s="1">
+        <v>29</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0</v>
+      </c>
+      <c r="E34" s="1">
+        <v>488888</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I34" s="1">
+        <v>4</v>
+      </c>
+      <c r="J34" s="1">
+        <v>204</v>
+      </c>
+      <c r="K34" s="1">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1">
+        <f t="shared" si="1"/>
+        <v>488888</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:13">
+      <c r="C36" s="1">
         <v>101</v>
       </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1">
         <v>500</v>
       </c>
-      <c r="F32" s="1">
-        <f>20*M32</f>
+      <c r="F36" s="1">
+        <f>20*M36</f>
         <v>20</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I32" s="1">
-        <v>5</v>
-      </c>
-      <c r="J32" s="1">
+      <c r="G36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I36" s="1">
+        <v>5</v>
+      </c>
+      <c r="J36" s="1">
         <v>4010</v>
       </c>
-      <c r="K32" s="1">
-        <v>5</v>
-      </c>
-      <c r="L32" s="1">
-        <f t="shared" ref="L32:L40" si="2">E32*F32</f>
+      <c r="K36" s="1">
+        <v>5</v>
+      </c>
+      <c r="L36" s="1">
+        <f t="shared" ref="L36:L44" si="2">E36*F36</f>
         <v>10000</v>
       </c>
-      <c r="M32" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:13">
-      <c r="C33" s="1">
+      <c r="M36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:13">
+      <c r="C37" s="1">
         <v>102</v>
       </c>
-      <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1">
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+      <c r="E37" s="1">
         <v>100</v>
       </c>
-      <c r="F33" s="1">
-        <f>300*M32</f>
+      <c r="F37" s="1">
+        <f>300*M36</f>
         <v>300</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I33" s="1">
-        <v>5</v>
-      </c>
-      <c r="J33" s="1">
+      <c r="G37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I37" s="1">
+        <v>5</v>
+      </c>
+      <c r="J37" s="1">
         <v>4007</v>
       </c>
-      <c r="K33" s="1">
+      <c r="K37" s="1">
         <v>1000</v>
       </c>
-      <c r="L33" s="1">
+      <c r="L37" s="1">
         <f t="shared" si="2"/>
         <v>30000</v>
       </c>
-      <c r="M33" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:13">
-      <c r="C34" s="1">
+      <c r="M37" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:13">
+      <c r="C38" s="1">
         <v>103</v>
       </c>
-      <c r="D34" s="1">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1">
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
         <v>100</v>
       </c>
-      <c r="F34" s="1">
-        <f>500*M32</f>
+      <c r="F38" s="1">
+        <f>500*M36</f>
         <v>500</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I34" s="1">
-        <v>5</v>
-      </c>
-      <c r="J34" s="1">
+      <c r="G38" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I38" s="1">
+        <v>5</v>
+      </c>
+      <c r="J38" s="1">
         <v>4101</v>
       </c>
-      <c r="K34" s="1">
+      <c r="K38" s="1">
         <v>1000</v>
       </c>
-      <c r="L34" s="1">
+      <c r="L38" s="1">
         <f t="shared" si="2"/>
         <v>50000</v>
       </c>
-      <c r="M34" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:13">
-      <c r="C35" s="1">
+      <c r="M38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:13">
+      <c r="C39" s="1">
         <v>104</v>
       </c>
-      <c r="D35" s="1">
-        <v>1</v>
-      </c>
-      <c r="E35" s="1">
+      <c r="D39" s="1">
+        <v>1</v>
+      </c>
+      <c r="E39" s="1">
         <v>1000</v>
       </c>
-      <c r="F35" s="1">
-        <f>5*M32</f>
-        <v>5</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I35" s="1">
+      <c r="F39" s="1">
+        <f>6*M36</f>
+        <v>6</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I39" s="1">
         <v>15</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J39" s="1">
         <v>4014</v>
       </c>
-      <c r="K35" s="1">
+      <c r="K39" s="1">
         <v>100</v>
       </c>
-      <c r="L35" s="1">
+      <c r="L39" s="1">
+        <f t="shared" si="2"/>
+        <v>6000</v>
+      </c>
+      <c r="M39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:13">
+      <c r="C40" s="1">
+        <v>105</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1">
+        <v>500</v>
+      </c>
+      <c r="F40" s="1">
+        <f>20*M36</f>
+        <v>20</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I40" s="1">
+        <v>5</v>
+      </c>
+      <c r="J40" s="1">
+        <v>4012</v>
+      </c>
+      <c r="K40" s="1">
+        <v>200</v>
+      </c>
+      <c r="L40" s="1">
+        <f t="shared" si="2"/>
+        <v>10000</v>
+      </c>
+      <c r="M40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:13">
+      <c r="C41" s="1">
+        <v>106</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1">
+        <v>15000</v>
+      </c>
+      <c r="F41" s="1">
+        <f>5*M36</f>
+        <v>5</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I41" s="1">
+        <v>5</v>
+      </c>
+      <c r="J41" s="1">
+        <v>4019</v>
+      </c>
+      <c r="K41" s="1">
+        <v>1</v>
+      </c>
+      <c r="L41" s="1">
+        <f t="shared" si="2"/>
+        <v>75000</v>
+      </c>
+      <c r="M41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:13">
+      <c r="C42" s="1">
+        <v>107</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1">
+        <v>500</v>
+      </c>
+      <c r="F42" s="1">
+        <f>10*M36</f>
+        <v>10</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I42" s="1">
+        <v>5</v>
+      </c>
+      <c r="J42" s="1">
+        <v>4102</v>
+      </c>
+      <c r="K42" s="1">
+        <v>20</v>
+      </c>
+      <c r="L42" s="1">
         <f t="shared" si="2"/>
         <v>5000</v>
       </c>
-      <c r="M35" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:13">
-      <c r="C36" s="1">
-        <v>105</v>
-      </c>
-      <c r="D36" s="1">
-        <v>1</v>
-      </c>
-      <c r="E36" s="1">
+      <c r="M42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:13">
+      <c r="C43" s="1">
+        <v>108</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1</v>
+      </c>
+      <c r="E43" s="1">
         <v>500</v>
       </c>
-      <c r="F36" s="1">
-        <f>20*M32</f>
-        <v>20</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I36" s="1">
-        <v>5</v>
-      </c>
-      <c r="J36" s="1">
-        <v>4012</v>
-      </c>
-      <c r="K36" s="1">
-        <v>200</v>
-      </c>
-      <c r="L36" s="1">
-        <f t="shared" si="2"/>
-        <v>10000</v>
-      </c>
-      <c r="M36" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:13">
-      <c r="C37" s="1">
-        <v>106</v>
-      </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
-      <c r="E37" s="1">
-        <v>5000</v>
-      </c>
-      <c r="F37" s="1">
-        <f>5*M32</f>
-        <v>5</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I37" s="1">
-        <v>5</v>
-      </c>
-      <c r="J37" s="1">
-        <v>4011</v>
-      </c>
-      <c r="K37" s="1">
-        <v>1</v>
-      </c>
-      <c r="L37" s="1">
-        <f t="shared" si="2"/>
-        <v>25000</v>
-      </c>
-      <c r="M37" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:13">
-      <c r="C38" s="1">
-        <v>107</v>
-      </c>
-      <c r="D38" s="1">
-        <v>1</v>
-      </c>
-      <c r="E38" s="1">
-        <v>500</v>
-      </c>
-      <c r="F38" s="1">
-        <f>10*M32</f>
-        <v>10</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I38" s="1">
-        <v>5</v>
-      </c>
-      <c r="J38" s="1">
-        <v>4102</v>
-      </c>
-      <c r="K38" s="1">
-        <v>20</v>
-      </c>
-      <c r="L38" s="1">
-        <f t="shared" si="2"/>
-        <v>5000</v>
-      </c>
-      <c r="M38" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:13">
-      <c r="C39" s="1">
-        <v>108</v>
-      </c>
-      <c r="D39" s="1">
-        <v>1</v>
-      </c>
-      <c r="E39" s="1">
-        <v>500</v>
-      </c>
-      <c r="F39" s="1">
-        <f>40*M32</f>
+      <c r="F43" s="1">
+        <f>40*M36</f>
         <v>40</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I39" s="1">
-        <v>5</v>
-      </c>
-      <c r="J39" s="1">
+      <c r="G43" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I43" s="1">
+        <v>5</v>
+      </c>
+      <c r="J43" s="1">
         <v>4001</v>
       </c>
-      <c r="K39" s="1">
+      <c r="K43" s="1">
         <v>1000000</v>
       </c>
-      <c r="L39" s="1">
+      <c r="L43" s="1">
         <f t="shared" si="2"/>
         <v>20000</v>
       </c>
-      <c r="M39" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:13">
-      <c r="C40" s="1">
+      <c r="M43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:13">
+      <c r="C44" s="1">
         <v>109</v>
       </c>
-      <c r="D40" s="1">
-        <v>1</v>
-      </c>
-      <c r="E40" s="1">
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+      <c r="E44" s="1">
         <v>500</v>
       </c>
-      <c r="F40" s="1">
-        <f>40*M32</f>
+      <c r="F44" s="1">
+        <f>40*M36</f>
         <v>40</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I40" s="1">
-        <v>5</v>
-      </c>
-      <c r="J40" s="1">
+      <c r="G44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I44" s="1">
+        <v>5</v>
+      </c>
+      <c r="J44" s="1">
         <v>4002</v>
       </c>
-      <c r="K40" s="1">
+      <c r="K44" s="1">
         <v>6000000</v>
       </c>
-      <c r="L40" s="1">
+      <c r="L44" s="1">
         <f t="shared" si="2"/>
         <v>20000</v>
       </c>
-      <c r="M40" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:13">
-      <c r="C42" s="1">
+      <c r="M44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:13">
+      <c r="C46" s="1">
         <v>201</v>
       </c>
-      <c r="D42" s="1">
+      <c r="D46" s="1">
         <v>2</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E46" s="4">
         <v>1000</v>
       </c>
-      <c r="F42" s="1">
-        <f>20*M42</f>
+      <c r="F46" s="1">
+        <f>20*M46</f>
         <v>20</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I42" s="1">
-        <v>5</v>
-      </c>
-      <c r="J42" s="1">
+      <c r="G46" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I46" s="1">
+        <v>5</v>
+      </c>
+      <c r="J46" s="1">
         <v>4010</v>
       </c>
-      <c r="K42" s="1">
-        <v>5</v>
-      </c>
-      <c r="L42" s="1">
-        <f t="shared" ref="L42:L77" si="3">E42*F42</f>
+      <c r="K46" s="1">
+        <v>5</v>
+      </c>
+      <c r="L46" s="1">
+        <f t="shared" ref="L46:L81" si="3">E46*F46</f>
         <v>20000</v>
       </c>
-      <c r="M42" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:13">
-      <c r="C43" s="1">
+      <c r="M46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:13">
+      <c r="C47" s="1">
         <v>202</v>
       </c>
-      <c r="D43" s="1">
+      <c r="D47" s="1">
         <v>2</v>
       </c>
-      <c r="E43" s="4">
+      <c r="E47" s="4">
         <v>200</v>
       </c>
-      <c r="F43" s="1">
-        <f>300*M42</f>
+      <c r="F47" s="1">
+        <f>300*M46</f>
         <v>300</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I43" s="1">
-        <v>5</v>
-      </c>
-      <c r="J43" s="1">
+      <c r="G47" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I47" s="1">
+        <v>5</v>
+      </c>
+      <c r="J47" s="1">
         <v>4007</v>
       </c>
-      <c r="K43" s="1">
+      <c r="K47" s="1">
         <v>1000</v>
       </c>
-      <c r="L43" s="1">
+      <c r="L47" s="1">
         <f t="shared" si="3"/>
         <v>60000</v>
       </c>
-      <c r="M43" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:13">
-      <c r="C44" s="1">
+      <c r="M47" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:13">
+      <c r="C48" s="1">
         <v>203</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D48" s="1">
         <v>2</v>
       </c>
-      <c r="E44" s="4">
+      <c r="E48" s="4">
         <v>200</v>
       </c>
-      <c r="F44" s="1">
-        <f>500*M42</f>
+      <c r="F48" s="1">
+        <f>500*M46</f>
         <v>500</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I44" s="1">
-        <v>5</v>
-      </c>
-      <c r="J44" s="1">
+      <c r="G48" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I48" s="1">
+        <v>5</v>
+      </c>
+      <c r="J48" s="1">
         <v>4101</v>
       </c>
-      <c r="K44" s="1">
+      <c r="K48" s="1">
         <v>1000</v>
       </c>
-      <c r="L44" s="1">
+      <c r="L48" s="1">
         <f t="shared" si="3"/>
         <v>100000</v>
       </c>
-      <c r="M44" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:13">
-      <c r="C45" s="1">
+      <c r="M48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:13">
+      <c r="C49" s="1">
         <v>204</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D49" s="1">
         <v>2</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E49" s="4">
         <v>2000</v>
       </c>
-      <c r="F45" s="1">
-        <f>5*M42</f>
-        <v>5</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I45" s="1">
+      <c r="F49" s="1">
+        <f>6*M46</f>
+        <v>6</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I49" s="1">
         <v>15</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J49" s="1">
         <v>4014</v>
       </c>
-      <c r="K45" s="1">
+      <c r="K49" s="1">
         <v>100</v>
       </c>
-      <c r="L45" s="1">
+      <c r="L49" s="1">
+        <f t="shared" si="3"/>
+        <v>12000</v>
+      </c>
+      <c r="M49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:13">
+      <c r="C50" s="1">
+        <v>205</v>
+      </c>
+      <c r="D50" s="1">
+        <v>2</v>
+      </c>
+      <c r="E50" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F50" s="1">
+        <f>20*M46</f>
+        <v>20</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I50" s="1">
+        <v>5</v>
+      </c>
+      <c r="J50" s="1">
+        <v>4012</v>
+      </c>
+      <c r="K50" s="1">
+        <v>200</v>
+      </c>
+      <c r="L50" s="1">
+        <f t="shared" si="3"/>
+        <v>20000</v>
+      </c>
+      <c r="M50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:13">
+      <c r="C51" s="1">
+        <v>206</v>
+      </c>
+      <c r="D51" s="1">
+        <v>2</v>
+      </c>
+      <c r="E51" s="4">
+        <v>30000</v>
+      </c>
+      <c r="F51" s="1">
+        <f>5*M46</f>
+        <v>5</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I51" s="1">
+        <v>5</v>
+      </c>
+      <c r="J51" s="1">
+        <v>4019</v>
+      </c>
+      <c r="K51" s="1">
+        <v>1</v>
+      </c>
+      <c r="L51" s="1">
+        <f t="shared" si="3"/>
+        <v>150000</v>
+      </c>
+      <c r="M51" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:13">
+      <c r="C52" s="1">
+        <v>207</v>
+      </c>
+      <c r="D52" s="1">
+        <v>2</v>
+      </c>
+      <c r="E52" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F52" s="1">
+        <f>10*M46</f>
+        <v>10</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I52" s="1">
+        <v>5</v>
+      </c>
+      <c r="J52" s="1">
+        <v>4102</v>
+      </c>
+      <c r="K52" s="1">
+        <v>20</v>
+      </c>
+      <c r="L52" s="1">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
-      <c r="M45" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:13">
-      <c r="C46" s="1">
-        <v>205</v>
-      </c>
-      <c r="D46" s="1">
+      <c r="M52" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:13">
+      <c r="C53" s="1">
+        <v>208</v>
+      </c>
+      <c r="D53" s="1">
         <v>2</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E53" s="4">
         <v>1000</v>
       </c>
-      <c r="F46" s="1">
-        <f>20*M42</f>
-        <v>20</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I46" s="1">
-        <v>5</v>
-      </c>
-      <c r="J46" s="1">
-        <v>4012</v>
-      </c>
-      <c r="K46" s="1">
-        <v>200</v>
-      </c>
-      <c r="L46" s="1">
-        <f t="shared" si="3"/>
-        <v>20000</v>
-      </c>
-      <c r="M46" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:13">
-      <c r="C47" s="1">
-        <v>206</v>
-      </c>
-      <c r="D47" s="1">
-        <v>2</v>
-      </c>
-      <c r="E47" s="4">
-        <v>10000</v>
-      </c>
-      <c r="F47" s="1">
-        <f>5*M42</f>
-        <v>5</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I47" s="1">
-        <v>5</v>
-      </c>
-      <c r="J47" s="1">
-        <v>4011</v>
-      </c>
-      <c r="K47" s="1">
-        <v>1</v>
-      </c>
-      <c r="L47" s="1">
-        <f t="shared" si="3"/>
-        <v>50000</v>
-      </c>
-      <c r="M47" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:13">
-      <c r="C48" s="1">
-        <v>207</v>
-      </c>
-      <c r="D48" s="1">
-        <v>2</v>
-      </c>
-      <c r="E48" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F48" s="1">
-        <f>10*M42</f>
-        <v>10</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I48" s="1">
-        <v>5</v>
-      </c>
-      <c r="J48" s="1">
-        <v>4102</v>
-      </c>
-      <c r="K48" s="1">
-        <v>20</v>
-      </c>
-      <c r="L48" s="1">
-        <f t="shared" si="3"/>
-        <v>10000</v>
-      </c>
-      <c r="M48" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:13">
-      <c r="C49" s="1">
-        <v>208</v>
-      </c>
-      <c r="D49" s="1">
-        <v>2</v>
-      </c>
-      <c r="E49" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F49" s="1">
-        <f>40*M42</f>
+      <c r="F53" s="1">
+        <f>40*M46</f>
         <v>40</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I49" s="1">
-        <v>5</v>
-      </c>
-      <c r="J49" s="1">
+      <c r="G53" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I53" s="1">
+        <v>5</v>
+      </c>
+      <c r="J53" s="1">
         <v>4001</v>
       </c>
-      <c r="K49" s="1">
+      <c r="K53" s="1">
         <v>1000000</v>
       </c>
-      <c r="L49" s="1">
+      <c r="L53" s="1">
         <f t="shared" si="3"/>
         <v>40000</v>
       </c>
-      <c r="M49" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:13">
-      <c r="C50" s="1">
+      <c r="M53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:13">
+      <c r="C54" s="1">
         <v>209</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D54" s="1">
         <v>2</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E54" s="4">
         <v>1000</v>
       </c>
-      <c r="F50" s="1">
-        <f>40*M42</f>
+      <c r="F54" s="1">
+        <f>40*M46</f>
         <v>40</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I50" s="1">
-        <v>5</v>
-      </c>
-      <c r="J50" s="1">
+      <c r="G54" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I54" s="1">
+        <v>5</v>
+      </c>
+      <c r="J54" s="1">
         <v>4002</v>
       </c>
-      <c r="K50" s="1">
+      <c r="K54" s="1">
         <v>6000000</v>
       </c>
-      <c r="L50" s="1">
+      <c r="L54" s="1">
         <f t="shared" si="3"/>
         <v>40000</v>
       </c>
-      <c r="M50" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:13">
-      <c r="C51" s="1">
-        <v>210</v>
-      </c>
-      <c r="D51" s="1">
-        <v>3</v>
-      </c>
-      <c r="E51" s="1">
-        <v>2000</v>
-      </c>
-      <c r="F51" s="1">
-        <f>20*M51</f>
-        <v>20</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I51" s="1">
-        <v>5</v>
-      </c>
-      <c r="J51" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K51" s="1">
-        <v>5</v>
-      </c>
-      <c r="L51" s="1">
-        <f t="shared" si="3"/>
-        <v>40000</v>
-      </c>
-      <c r="M51" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:13">
-      <c r="C52" s="1">
-        <v>211</v>
-      </c>
-      <c r="D52" s="1">
-        <v>3</v>
-      </c>
-      <c r="E52" s="1">
-        <v>400</v>
-      </c>
-      <c r="F52" s="1">
-        <f>300*M51</f>
-        <v>300</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I52" s="1">
-        <v>5</v>
-      </c>
-      <c r="J52" s="1">
-        <v>4007</v>
-      </c>
-      <c r="K52" s="1">
-        <v>1000</v>
-      </c>
-      <c r="L52" s="1">
-        <f t="shared" si="3"/>
-        <v>120000</v>
-      </c>
-      <c r="M52" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:13">
-      <c r="C53" s="1">
-        <v>212</v>
-      </c>
-      <c r="D53" s="1">
-        <v>3</v>
-      </c>
-      <c r="E53" s="1">
-        <v>400</v>
-      </c>
-      <c r="F53" s="1">
-        <f>500*M51</f>
-        <v>500</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I53" s="1">
-        <v>5</v>
-      </c>
-      <c r="J53" s="1">
-        <v>4101</v>
-      </c>
-      <c r="K53" s="1">
-        <v>1000</v>
-      </c>
-      <c r="L53" s="1">
-        <f t="shared" si="3"/>
-        <v>200000</v>
-      </c>
-      <c r="M53" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:13">
-      <c r="C54" s="1">
-        <v>213</v>
-      </c>
-      <c r="D54" s="1">
-        <v>3</v>
-      </c>
-      <c r="E54" s="1">
-        <v>4000</v>
-      </c>
-      <c r="F54" s="1">
-        <f>5*M51</f>
-        <v>5</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I54" s="1">
-        <v>15</v>
-      </c>
-      <c r="J54" s="1">
-        <v>4014</v>
-      </c>
-      <c r="K54" s="1">
-        <v>100</v>
-      </c>
-      <c r="L54" s="1">
-        <f t="shared" si="3"/>
-        <v>20000</v>
-      </c>
       <c r="M54" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:13">
       <c r="C55" s="1">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D55" s="1">
         <v>3</v>
@@ -3078,7 +3086,7 @@
         <v>2000</v>
       </c>
       <c r="F55" s="1">
-        <f>20*M51</f>
+        <f>20*M55</f>
         <v>20</v>
       </c>
       <c r="G55" s="1" t="s">
@@ -3091,10 +3099,10 @@
         <v>5</v>
       </c>
       <c r="J55" s="1">
-        <v>4012</v>
+        <v>4010</v>
       </c>
       <c r="K55" s="1">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="L55" s="1">
         <f t="shared" si="3"/>
@@ -3106,17 +3114,17 @@
     </row>
     <row r="56" customHeight="1" spans="3:13">
       <c r="C56" s="1">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D56" s="1">
         <v>3</v>
       </c>
       <c r="E56" s="1">
-        <v>20000</v>
+        <v>400</v>
       </c>
       <c r="F56" s="1">
-        <f>5*M51</f>
-        <v>5</v>
+        <f>300*M55</f>
+        <v>300</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>83</v>
@@ -3128,14 +3136,14 @@
         <v>5</v>
       </c>
       <c r="J56" s="1">
-        <v>4011</v>
+        <v>4007</v>
       </c>
       <c r="K56" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="L56" s="1">
         <f t="shared" si="3"/>
-        <v>100000</v>
+        <v>120000</v>
       </c>
       <c r="M56" s="1">
         <v>1</v>
@@ -3143,17 +3151,17 @@
     </row>
     <row r="57" customHeight="1" spans="3:13">
       <c r="C57" s="1">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D57" s="1">
         <v>3</v>
       </c>
       <c r="E57" s="1">
-        <v>2000</v>
+        <v>400</v>
       </c>
       <c r="F57" s="1">
-        <f>10*M51</f>
-        <v>10</v>
+        <f>500*M55</f>
+        <v>500</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>85</v>
@@ -3165,14 +3173,14 @@
         <v>5</v>
       </c>
       <c r="J57" s="1">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="K57" s="1">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="L57" s="1">
         <f t="shared" si="3"/>
-        <v>20000</v>
+        <v>200000</v>
       </c>
       <c r="M57" s="1">
         <v>1</v>
@@ -3180,17 +3188,17 @@
     </row>
     <row r="58" customHeight="1" spans="3:13">
       <c r="C58" s="1">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D58" s="1">
         <v>3</v>
       </c>
       <c r="E58" s="1">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="F58" s="1">
-        <f>40*M51</f>
-        <v>40</v>
+        <f>6*M55</f>
+        <v>6</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>87</v>
@@ -3199,17 +3207,17 @@
         <v>88</v>
       </c>
       <c r="I58" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J58" s="1">
-        <v>4001</v>
+        <v>4014</v>
       </c>
       <c r="K58" s="1">
-        <v>1000000</v>
+        <v>100</v>
       </c>
       <c r="L58" s="1">
         <f t="shared" si="3"/>
-        <v>80000</v>
+        <v>24000</v>
       </c>
       <c r="M58" s="1">
         <v>1</v>
@@ -3217,7 +3225,7 @@
     </row>
     <row r="59" customHeight="1" spans="3:13">
       <c r="C59" s="1">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D59" s="1">
         <v>3</v>
@@ -3226,8 +3234,8 @@
         <v>2000</v>
       </c>
       <c r="F59" s="1">
-        <f>40*M51</f>
-        <v>40</v>
+        <f>20*M55</f>
+        <v>20</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>89</v>
@@ -3239,14 +3247,14 @@
         <v>5</v>
       </c>
       <c r="J59" s="1">
-        <v>4002</v>
+        <v>4012</v>
       </c>
       <c r="K59" s="1">
-        <v>6000000</v>
+        <v>200</v>
       </c>
       <c r="L59" s="1">
         <f t="shared" si="3"/>
-        <v>80000</v>
+        <v>40000</v>
       </c>
       <c r="M59" s="1">
         <v>1</v>
@@ -3254,36 +3262,36 @@
     </row>
     <row r="60" customHeight="1" spans="3:13">
       <c r="C60" s="1">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D60" s="1">
-        <v>4</v>
-      </c>
-      <c r="E60" s="4">
-        <v>3000</v>
+        <v>3</v>
+      </c>
+      <c r="E60" s="1">
+        <v>45000</v>
       </c>
       <c r="F60" s="1">
-        <f>20*M60</f>
-        <v>20</v>
+        <f>5*M55</f>
+        <v>5</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="I60" s="1">
         <v>5</v>
       </c>
       <c r="J60" s="1">
-        <v>4010</v>
+        <v>4019</v>
       </c>
       <c r="K60" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L60" s="1">
         <f t="shared" si="3"/>
-        <v>60000</v>
+        <v>225000</v>
       </c>
       <c r="M60" s="1">
         <v>1</v>
@@ -3291,36 +3299,36 @@
     </row>
     <row r="61" customHeight="1" spans="3:13">
       <c r="C61" s="1">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D61" s="1">
-        <v>4</v>
-      </c>
-      <c r="E61" s="4">
-        <v>600</v>
+        <v>3</v>
+      </c>
+      <c r="E61" s="1">
+        <v>2000</v>
       </c>
       <c r="F61" s="1">
-        <f>300*M60</f>
-        <v>300</v>
+        <f>10*M55</f>
+        <v>10</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="I61" s="1">
         <v>5</v>
       </c>
       <c r="J61" s="1">
-        <v>4007</v>
+        <v>4102</v>
       </c>
       <c r="K61" s="1">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="L61" s="1">
         <f t="shared" si="3"/>
-        <v>180000</v>
+        <v>20000</v>
       </c>
       <c r="M61" s="1">
         <v>1</v>
@@ -3328,36 +3336,36 @@
     </row>
     <row r="62" customHeight="1" spans="3:13">
       <c r="C62" s="1">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D62" s="1">
-        <v>4</v>
-      </c>
-      <c r="E62" s="4">
-        <v>600</v>
+        <v>3</v>
+      </c>
+      <c r="E62" s="1">
+        <v>2000</v>
       </c>
       <c r="F62" s="1">
-        <f>500*M60</f>
-        <v>500</v>
+        <f>40*M55</f>
+        <v>40</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="I62" s="1">
         <v>5</v>
       </c>
       <c r="J62" s="1">
-        <v>4101</v>
+        <v>4001</v>
       </c>
       <c r="K62" s="1">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="L62" s="1">
         <f t="shared" si="3"/>
-        <v>300000</v>
+        <v>80000</v>
       </c>
       <c r="M62" s="1">
         <v>1</v>
@@ -3365,36 +3373,36 @@
     </row>
     <row r="63" customHeight="1" spans="3:13">
       <c r="C63" s="1">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D63" s="1">
-        <v>4</v>
-      </c>
-      <c r="E63" s="4">
-        <v>6000</v>
+        <v>3</v>
+      </c>
+      <c r="E63" s="1">
+        <v>2000</v>
       </c>
       <c r="F63" s="1">
-        <f>5*M60</f>
-        <v>5</v>
+        <f>40*M55</f>
+        <v>40</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="I63" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J63" s="1">
-        <v>4014</v>
+        <v>4002</v>
       </c>
       <c r="K63" s="1">
-        <v>100</v>
+        <v>6000000</v>
       </c>
       <c r="L63" s="1">
         <f t="shared" si="3"/>
-        <v>30000</v>
+        <v>80000</v>
       </c>
       <c r="M63" s="1">
         <v>1</v>
@@ -3402,7 +3410,7 @@
     </row>
     <row r="64" customHeight="1" spans="3:13">
       <c r="C64" s="1">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D64" s="1">
         <v>4</v>
@@ -3411,7 +3419,7 @@
         <v>3000</v>
       </c>
       <c r="F64" s="1">
-        <f>20*M60</f>
+        <f>20*M64</f>
         <v>20</v>
       </c>
       <c r="G64" s="1" t="s">
@@ -3424,10 +3432,10 @@
         <v>5</v>
       </c>
       <c r="J64" s="1">
-        <v>4012</v>
+        <v>4010</v>
       </c>
       <c r="K64" s="1">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="L64" s="1">
         <f t="shared" si="3"/>
@@ -3439,17 +3447,17 @@
     </row>
     <row r="65" customHeight="1" spans="3:13">
       <c r="C65" s="1">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D65" s="1">
         <v>4</v>
       </c>
       <c r="E65" s="4">
-        <v>30000</v>
+        <v>600</v>
       </c>
       <c r="F65" s="1">
-        <f>5*M60</f>
-        <v>5</v>
+        <f>300*M64</f>
+        <v>300</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>83</v>
@@ -3461,14 +3469,14 @@
         <v>5</v>
       </c>
       <c r="J65" s="1">
-        <v>4011</v>
+        <v>4007</v>
       </c>
       <c r="K65" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="L65" s="1">
         <f t="shared" si="3"/>
-        <v>150000</v>
+        <v>180000</v>
       </c>
       <c r="M65" s="1">
         <v>1</v>
@@ -3476,17 +3484,17 @@
     </row>
     <row r="66" customHeight="1" spans="3:13">
       <c r="C66" s="1">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D66" s="1">
         <v>4</v>
       </c>
       <c r="E66" s="4">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="F66" s="1">
-        <f>10*M60</f>
-        <v>10</v>
+        <f>500*M64</f>
+        <v>500</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>85</v>
@@ -3498,14 +3506,14 @@
         <v>5</v>
       </c>
       <c r="J66" s="1">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="K66" s="1">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="L66" s="1">
         <f t="shared" si="3"/>
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="M66" s="1">
         <v>1</v>
@@ -3513,17 +3521,17 @@
     </row>
     <row r="67" customHeight="1" spans="3:13">
       <c r="C67" s="1">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D67" s="1">
         <v>4</v>
       </c>
       <c r="E67" s="4">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="F67" s="1">
-        <f>40*M60</f>
-        <v>40</v>
+        <f>6*M64</f>
+        <v>6</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>87</v>
@@ -3532,17 +3540,17 @@
         <v>88</v>
       </c>
       <c r="I67" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J67" s="1">
-        <v>4001</v>
+        <v>4014</v>
       </c>
       <c r="K67" s="1">
-        <v>1000000</v>
+        <v>100</v>
       </c>
       <c r="L67" s="1">
         <f t="shared" si="3"/>
-        <v>120000</v>
+        <v>36000</v>
       </c>
       <c r="M67" s="1">
         <v>1</v>
@@ -3550,7 +3558,7 @@
     </row>
     <row r="68" customHeight="1" spans="3:13">
       <c r="C68" s="1">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D68" s="1">
         <v>4</v>
@@ -3559,8 +3567,8 @@
         <v>3000</v>
       </c>
       <c r="F68" s="1">
-        <f>40*M60</f>
-        <v>40</v>
+        <f>20*M64</f>
+        <v>20</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>89</v>
@@ -3572,14 +3580,14 @@
         <v>5</v>
       </c>
       <c r="J68" s="1">
-        <v>4002</v>
+        <v>4012</v>
       </c>
       <c r="K68" s="1">
-        <v>6000000</v>
+        <v>200</v>
       </c>
       <c r="L68" s="1">
         <f t="shared" si="3"/>
-        <v>120000</v>
+        <v>60000</v>
       </c>
       <c r="M68" s="1">
         <v>1</v>
@@ -3587,155 +3595,155 @@
     </row>
     <row r="69" customHeight="1" spans="3:13">
       <c r="C69" s="1">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D69" s="1">
-        <v>5</v>
-      </c>
-      <c r="E69" s="1">
-        <v>4000</v>
+        <v>4</v>
+      </c>
+      <c r="E69" s="4">
+        <v>60000</v>
       </c>
       <c r="F69" s="1">
-        <f>20*M69</f>
-        <v>80</v>
+        <f>5*M64</f>
+        <v>5</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="I69" s="1">
         <v>5</v>
       </c>
       <c r="J69" s="1">
-        <v>4010</v>
+        <v>4019</v>
       </c>
       <c r="K69" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L69" s="1">
         <f t="shared" si="3"/>
-        <v>320000</v>
+        <v>300000</v>
       </c>
       <c r="M69" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:13">
       <c r="C70" s="1">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D70" s="1">
-        <v>5</v>
-      </c>
-      <c r="E70" s="1">
-        <v>800</v>
+        <v>4</v>
+      </c>
+      <c r="E70" s="4">
+        <v>3000</v>
       </c>
       <c r="F70" s="1">
-        <f>300*M69</f>
-        <v>1200</v>
+        <f>10*M64</f>
+        <v>10</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="I70" s="1">
         <v>5</v>
       </c>
       <c r="J70" s="1">
-        <v>4007</v>
+        <v>4102</v>
       </c>
       <c r="K70" s="1">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="L70" s="1">
         <f t="shared" si="3"/>
-        <v>960000</v>
+        <v>30000</v>
       </c>
       <c r="M70" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:13">
       <c r="C71" s="1">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D71" s="1">
-        <v>5</v>
-      </c>
-      <c r="E71" s="1">
-        <v>800</v>
+        <v>4</v>
+      </c>
+      <c r="E71" s="4">
+        <v>3000</v>
       </c>
       <c r="F71" s="1">
-        <f>500*M69</f>
-        <v>2000</v>
+        <f>40*M64</f>
+        <v>40</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="I71" s="1">
         <v>5</v>
       </c>
       <c r="J71" s="1">
-        <v>4101</v>
+        <v>4001</v>
       </c>
       <c r="K71" s="1">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="L71" s="1">
         <f t="shared" si="3"/>
-        <v>1600000</v>
+        <v>120000</v>
       </c>
       <c r="M71" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:13">
       <c r="C72" s="1">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D72" s="1">
-        <v>5</v>
-      </c>
-      <c r="E72" s="1">
-        <v>8000</v>
+        <v>4</v>
+      </c>
+      <c r="E72" s="4">
+        <v>3000</v>
       </c>
       <c r="F72" s="1">
-        <f>5*M69</f>
-        <v>20</v>
+        <f>40*M64</f>
+        <v>40</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="I72" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J72" s="1">
-        <v>4014</v>
+        <v>4002</v>
       </c>
       <c r="K72" s="1">
-        <v>100</v>
+        <v>6000000</v>
       </c>
       <c r="L72" s="1">
         <f t="shared" si="3"/>
-        <v>160000</v>
+        <v>120000</v>
       </c>
       <c r="M72" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:13">
       <c r="C73" s="1">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D73" s="1">
         <v>5</v>
@@ -3744,7 +3752,7 @@
         <v>4000</v>
       </c>
       <c r="F73" s="1">
-        <f>20*M69</f>
+        <f>20*M73</f>
         <v>80</v>
       </c>
       <c r="G73" s="1" t="s">
@@ -3757,10 +3765,10 @@
         <v>5</v>
       </c>
       <c r="J73" s="1">
-        <v>4012</v>
+        <v>4010</v>
       </c>
       <c r="K73" s="1">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="L73" s="1">
         <f t="shared" si="3"/>
@@ -3772,17 +3780,17 @@
     </row>
     <row r="74" customHeight="1" spans="3:13">
       <c r="C74" s="1">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D74" s="1">
         <v>5</v>
       </c>
       <c r="E74" s="1">
-        <v>40000</v>
+        <v>800</v>
       </c>
       <c r="F74" s="1">
-        <f>5*M69</f>
-        <v>20</v>
+        <f>300*M73</f>
+        <v>1200</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>83</v>
@@ -3794,14 +3802,14 @@
         <v>5</v>
       </c>
       <c r="J74" s="1">
-        <v>4011</v>
+        <v>4007</v>
       </c>
       <c r="K74" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="L74" s="1">
         <f t="shared" si="3"/>
-        <v>800000</v>
+        <v>960000</v>
       </c>
       <c r="M74" s="1">
         <v>4</v>
@@ -3809,17 +3817,17 @@
     </row>
     <row r="75" customHeight="1" spans="3:13">
       <c r="C75" s="1">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D75" s="1">
         <v>5</v>
       </c>
       <c r="E75" s="1">
-        <v>4000</v>
+        <v>800</v>
       </c>
       <c r="F75" s="1">
-        <f>10*M69</f>
-        <v>40</v>
+        <f>500*M73</f>
+        <v>2000</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>85</v>
@@ -3831,14 +3839,14 @@
         <v>5</v>
       </c>
       <c r="J75" s="1">
-        <v>4102</v>
+        <v>4101</v>
       </c>
       <c r="K75" s="1">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="L75" s="1">
         <f t="shared" si="3"/>
-        <v>160000</v>
+        <v>1600000</v>
       </c>
       <c r="M75" s="1">
         <v>4</v>
@@ -3846,17 +3854,17 @@
     </row>
     <row r="76" customHeight="1" spans="3:13">
       <c r="C76" s="1">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D76" s="1">
         <v>5</v>
       </c>
       <c r="E76" s="1">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="F76" s="1">
-        <f>40*M69</f>
-        <v>160</v>
+        <f>6*M73</f>
+        <v>24</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>87</v>
@@ -3865,17 +3873,17 @@
         <v>88</v>
       </c>
       <c r="I76" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J76" s="1">
-        <v>4001</v>
+        <v>4014</v>
       </c>
       <c r="K76" s="1">
-        <v>1000000</v>
+        <v>100</v>
       </c>
       <c r="L76" s="1">
         <f t="shared" si="3"/>
-        <v>640000</v>
+        <v>192000</v>
       </c>
       <c r="M76" s="1">
         <v>4</v>
@@ -3883,7 +3891,7 @@
     </row>
     <row r="77" customHeight="1" spans="3:13">
       <c r="C77" s="1">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D77" s="1">
         <v>5</v>
@@ -3892,8 +3900,8 @@
         <v>4000</v>
       </c>
       <c r="F77" s="1">
-        <f>40*M69</f>
-        <v>160</v>
+        <f>20*M73</f>
+        <v>80</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>89</v>
@@ -3905,49 +3913,197 @@
         <v>5</v>
       </c>
       <c r="J77" s="1">
-        <v>4002</v>
+        <v>4012</v>
       </c>
       <c r="K77" s="1">
-        <v>6000000</v>
+        <v>200</v>
       </c>
       <c r="L77" s="1">
         <f t="shared" si="3"/>
-        <v>640000</v>
+        <v>320000</v>
       </c>
       <c r="M77" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="80" customHeight="1" spans="3:12">
+    <row r="78" customHeight="1" spans="3:13">
+      <c r="C78" s="1">
+        <v>233</v>
+      </c>
+      <c r="D78" s="1">
+        <v>5</v>
+      </c>
+      <c r="E78" s="1">
+        <v>75000</v>
+      </c>
+      <c r="F78" s="1">
+        <f>5*M73</f>
+        <v>20</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I78" s="1">
+        <v>5</v>
+      </c>
+      <c r="J78" s="1">
+        <v>4019</v>
+      </c>
+      <c r="K78" s="1">
+        <v>1</v>
+      </c>
+      <c r="L78" s="1">
+        <f t="shared" si="3"/>
+        <v>1500000</v>
+      </c>
+      <c r="M78" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:13">
+      <c r="C79" s="1">
+        <v>234</v>
+      </c>
+      <c r="D79" s="1">
+        <v>5</v>
+      </c>
+      <c r="E79" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F79" s="1">
+        <f>10*M73</f>
+        <v>40</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I79" s="1">
+        <v>5</v>
+      </c>
+      <c r="J79" s="1">
+        <v>4102</v>
+      </c>
+      <c r="K79" s="1">
+        <v>20</v>
+      </c>
+      <c r="L79" s="1">
+        <f t="shared" si="3"/>
+        <v>160000</v>
+      </c>
+      <c r="M79" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:13">
       <c r="C80" s="1">
+        <v>235</v>
+      </c>
+      <c r="D80" s="1">
+        <v>5</v>
+      </c>
+      <c r="E80" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F80" s="1">
+        <f>40*M73</f>
+        <v>160</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I80" s="1">
+        <v>5</v>
+      </c>
+      <c r="J80" s="1">
+        <v>4001</v>
+      </c>
+      <c r="K80" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="L80" s="1">
+        <f t="shared" si="3"/>
+        <v>640000</v>
+      </c>
+      <c r="M80" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:13">
+      <c r="C81" s="1">
+        <v>236</v>
+      </c>
+      <c r="D81" s="1">
+        <v>5</v>
+      </c>
+      <c r="E81" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F81" s="1">
+        <f>40*M73</f>
+        <v>160</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I81" s="1">
+        <v>5</v>
+      </c>
+      <c r="J81" s="1">
+        <v>4002</v>
+      </c>
+      <c r="K81" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="L81" s="1">
+        <f t="shared" si="3"/>
+        <v>640000</v>
+      </c>
+      <c r="M81" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:12">
+      <c r="C84" s="1">
         <v>999</v>
       </c>
-      <c r="D80" s="1">
+      <c r="D84" s="1">
         <v>0</v>
       </c>
-      <c r="E80" s="6" t="s">
+      <c r="E84" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F84" s="1">
         <v>50</v>
       </c>
-      <c r="G80" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I80" s="1">
-        <v>5</v>
-      </c>
-      <c r="J80" s="1">
+      <c r="G84" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I84" s="1">
+        <v>5</v>
+      </c>
+      <c r="J84" s="1">
         <v>4006</v>
       </c>
-      <c r="K80" s="1">
+      <c r="K84" s="1">
         <v>1000</v>
       </c>
-      <c r="L80" s="1">
-        <f>E80*F80</f>
+      <c r="L84" s="1">
+        <f>E84*F84</f>
         <v>50000</v>
       </c>
     </row>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="103">
   <si>
     <t>#</t>
   </si>
@@ -212,6 +212,12 @@
     <t>法宝自选</t>
   </si>
   <si>
+    <t>兑换低级法宝自选*1</t>
+  </si>
+  <si>
+    <t>低级法宝自选</t>
+  </si>
+  <si>
     <t>300000</t>
   </si>
   <si>
@@ -272,64 +278,64 @@
     <t>红宠自选</t>
   </si>
   <si>
+    <t>兑换四格碎片*1000</t>
+  </si>
+  <si>
+    <t>四格碎片</t>
+  </si>
+  <si>
+    <t>兑换图鉴碎片*1000</t>
+  </si>
+  <si>
+    <t>图鉴碎片</t>
+  </si>
+  <si>
+    <t>兑换经验丹*100</t>
+  </si>
+  <si>
+    <t>经验丹</t>
+  </si>
+  <si>
+    <t>兑换传世精华*200</t>
+  </si>
+  <si>
+    <t>传世精华</t>
+  </si>
+  <si>
+    <t>兑换金装精华*1</t>
+  </si>
+  <si>
+    <t>金装精华</t>
+  </si>
+  <si>
+    <t>兑换魂环碎片*100w</t>
+  </si>
+  <si>
+    <t>魂环碎片</t>
+  </si>
+  <si>
+    <t>兑换精炼石*600w</t>
+  </si>
+  <si>
+    <t>精炼石</t>
+  </si>
+  <si>
+    <t>兑换书页1000个</t>
+  </si>
+  <si>
+    <t>书页</t>
+  </si>
+  <si>
     <t>兑换专属之心*5</t>
   </si>
   <si>
     <t>专属之心</t>
   </si>
   <si>
-    <t>兑换四格碎片*1000</t>
-  </si>
-  <si>
-    <t>四格碎片</t>
-  </si>
-  <si>
-    <t>兑换图鉴碎片*1000</t>
-  </si>
-  <si>
-    <t>图鉴碎片</t>
-  </si>
-  <si>
-    <t>兑换经验丹*100</t>
-  </si>
-  <si>
-    <t>经验丹</t>
-  </si>
-  <si>
-    <t>兑换传世精华*200</t>
-  </si>
-  <si>
-    <t>传世精华</t>
-  </si>
-  <si>
-    <t>兑换金装精华*1</t>
-  </si>
-  <si>
-    <t>金装精华</t>
-  </si>
-  <si>
     <t>兑换高级书页*20</t>
   </si>
   <si>
     <t>高级书页</t>
-  </si>
-  <si>
-    <t>兑换魂环碎片*100w</t>
-  </si>
-  <si>
-    <t>魂环碎片</t>
-  </si>
-  <si>
-    <t>兑换精炼石*600w</t>
-  </si>
-  <si>
-    <t>精炼石</t>
-  </si>
-  <si>
-    <t>兑换书页1000个</t>
-  </si>
-  <si>
-    <t>书页</t>
   </si>
 </sst>
 </file>
@@ -1340,7 +1346,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1457,7 +1463,7 @@
         <v>12</v>
       </c>
       <c r="F6" s="1">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>13</v>
@@ -1476,7 +1482,7 @@
       </c>
       <c r="L6" s="1">
         <f t="shared" ref="L6:L9" si="0">E6*F6</f>
-        <v>14400</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:12">
@@ -1490,7 +1496,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="1">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>15</v>
@@ -1509,7 +1515,7 @@
       </c>
       <c r="L7" s="1">
         <f t="shared" si="0"/>
-        <v>14400</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1523,7 +1529,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="1">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>17</v>
@@ -1542,7 +1548,7 @@
       </c>
       <c r="L8" s="1">
         <f t="shared" si="0"/>
-        <v>14400</v>
+        <v>20400</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:12">
@@ -1556,7 +1562,7 @@
         <v>19</v>
       </c>
       <c r="F9" s="1">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>20</v>
@@ -1575,7 +1581,7 @@
       </c>
       <c r="L9" s="1">
         <f t="shared" si="0"/>
-        <v>9000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:12">
@@ -1589,7 +1595,7 @@
         <v>12</v>
       </c>
       <c r="F10" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>22</v>
@@ -1607,8 +1613,8 @@
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" ref="L10:L34" si="1">E10*F10</f>
-        <v>24000</v>
+        <f t="shared" ref="L10:L35" si="1">E10*F10</f>
+        <v>30000</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:12">
@@ -1622,7 +1628,7 @@
         <v>12</v>
       </c>
       <c r="F11" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>24</v>
@@ -1641,7 +1647,7 @@
       </c>
       <c r="L11" s="1">
         <f t="shared" si="1"/>
-        <v>24000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:12">
@@ -1655,7 +1661,7 @@
         <v>12</v>
       </c>
       <c r="F12" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>26</v>
@@ -1674,7 +1680,7 @@
       </c>
       <c r="L12" s="1">
         <f t="shared" si="1"/>
-        <v>24000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:12">
@@ -1688,7 +1694,7 @@
         <v>19</v>
       </c>
       <c r="F13" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>28</v>
@@ -1707,7 +1713,7 @@
       </c>
       <c r="L13" s="1">
         <f t="shared" si="1"/>
-        <v>40000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:12">
@@ -1721,7 +1727,7 @@
         <v>19</v>
       </c>
       <c r="F14" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>30</v>
@@ -1740,7 +1746,7 @@
       </c>
       <c r="L14" s="1">
         <f t="shared" si="1"/>
-        <v>40000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:12">
@@ -1754,7 +1760,7 @@
         <v>19</v>
       </c>
       <c r="F15" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>32</v>
@@ -1773,7 +1779,7 @@
       </c>
       <c r="L15" s="1">
         <f t="shared" si="1"/>
-        <v>40000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:12">
@@ -2051,7 +2057,7 @@
         <v>52</v>
       </c>
       <c r="F24" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>53</v>
@@ -2070,7 +2076,7 @@
       </c>
       <c r="L24" s="1">
         <f t="shared" si="1"/>
-        <v>150000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:12">
@@ -2084,7 +2090,7 @@
         <v>55</v>
       </c>
       <c r="F25" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>56</v>
@@ -2103,7 +2109,7 @@
       </c>
       <c r="L25" s="1">
         <f t="shared" si="1"/>
-        <v>100000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:12">
@@ -2141,133 +2147,133 @@
     </row>
     <row r="27" customHeight="1" spans="3:12">
       <c r="C27" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" s="1">
+        <v>50</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="1">
-        <v>2</v>
-      </c>
-      <c r="G27" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="I27" s="1">
         <v>4</v>
       </c>
       <c r="J27" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K27" s="1">
         <v>1</v>
       </c>
       <c r="L27" s="1">
         <f t="shared" si="1"/>
-        <v>600000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:12">
       <c r="C28" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
       <c r="E28" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F28" s="1">
+        <v>3</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="F28" s="1">
-        <v>1</v>
-      </c>
-      <c r="G28" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="I28" s="1">
         <v>4</v>
       </c>
       <c r="J28" s="1">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K28" s="1">
         <v>1</v>
       </c>
       <c r="L28" s="1">
         <f t="shared" si="1"/>
-        <v>400000</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:12">
-      <c r="A29" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:12">
       <c r="C29" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F29" s="1">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1" t="s">
+      <c r="H29" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="I29" s="1">
         <v>4</v>
       </c>
       <c r="J29" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K29" s="1">
         <v>1</v>
       </c>
       <c r="L29" s="1">
         <f t="shared" si="1"/>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:12">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:12">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C30" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F30" s="1">
-        <v>100</v>
-      </c>
-      <c r="G30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="I30" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J30" s="1">
-        <v>4021</v>
+        <v>31</v>
       </c>
       <c r="K30" s="1">
         <v>1</v>
@@ -2277,15 +2283,15 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="31" customHeight="1" spans="3:12">
       <c r="C31" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F31" s="1">
         <v>100</v>
@@ -2300,10 +2306,10 @@
         <v>5</v>
       </c>
       <c r="J31" s="1">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="L31" s="1">
         <f t="shared" si="1"/>
@@ -2312,16 +2318,16 @@
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C32" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
-      <c r="E32" s="1">
-        <v>3000</v>
+      <c r="E32" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="F32" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>75</v>
@@ -2333,28 +2339,28 @@
         <v>5</v>
       </c>
       <c r="J32" s="1">
-        <v>4011</v>
+        <v>4022</v>
       </c>
       <c r="K32" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L32" s="1">
         <f t="shared" si="1"/>
-        <v>150000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C33" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="F33" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>77</v>
@@ -2366,28 +2372,28 @@
         <v>5</v>
       </c>
       <c r="J33" s="1">
-        <v>4020</v>
+        <v>4011</v>
       </c>
       <c r="K33" s="1">
         <v>1</v>
       </c>
       <c r="L33" s="1">
         <f t="shared" si="1"/>
-        <v>400000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C34" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>488888</v>
+        <v>20000</v>
       </c>
       <c r="F34" s="1">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>79</v>
@@ -2396,96 +2402,55 @@
         <v>80</v>
       </c>
       <c r="I34" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J34" s="1">
-        <v>204</v>
+        <v>4020</v>
       </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
       <c r="L34" s="1">
         <f t="shared" si="1"/>
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C35" s="1">
+        <v>29</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0</v>
+      </c>
+      <c r="E35" s="1">
         <v>488888</v>
       </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:13">
-      <c r="C36" s="1">
-        <v>101</v>
-      </c>
-      <c r="D36" s="1">
-        <v>1</v>
-      </c>
-      <c r="E36" s="1">
-        <v>500</v>
-      </c>
-      <c r="F36" s="1">
-        <f>20*M36</f>
-        <v>20</v>
-      </c>
-      <c r="G36" s="1" t="s">
+      <c r="F35" s="1">
+        <v>1</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H35" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I36" s="1">
-        <v>5</v>
-      </c>
-      <c r="J36" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K36" s="1">
-        <v>5</v>
-      </c>
-      <c r="L36" s="1">
-        <f t="shared" ref="L36:L44" si="2">E36*F36</f>
-        <v>10000</v>
-      </c>
-      <c r="M36" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:13">
-      <c r="C37" s="1">
+      <c r="I35" s="1">
+        <v>4</v>
+      </c>
+      <c r="J35" s="1">
+        <v>204</v>
+      </c>
+      <c r="K35" s="1">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1">
+        <f t="shared" si="1"/>
+        <v>488888</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:14">
+      <c r="C38" s="1">
         <v>102</v>
-      </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
-      <c r="E37" s="1">
-        <v>100</v>
-      </c>
-      <c r="F37" s="1">
-        <f>300*M36</f>
-        <v>300</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I37" s="1">
-        <v>5</v>
-      </c>
-      <c r="J37" s="1">
-        <v>4007</v>
-      </c>
-      <c r="K37" s="1">
-        <v>1000</v>
-      </c>
-      <c r="L37" s="1">
-        <f t="shared" si="2"/>
-        <v>30000</v>
-      </c>
-      <c r="M37" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:13">
-      <c r="C38" s="1">
-        <v>103</v>
       </c>
       <c r="D38" s="1">
         <v>1</v>
@@ -2494,183 +2459,198 @@
         <v>100</v>
       </c>
       <c r="F38" s="1">
-        <f>500*M36</f>
-        <v>500</v>
+        <f t="shared" ref="F38:F44" si="2">M38*N38</f>
+        <v>300</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I38" s="1">
         <v>5</v>
       </c>
       <c r="J38" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K38" s="1">
         <v>1000</v>
       </c>
       <c r="L38" s="1">
+        <f t="shared" ref="L38:L44" si="3">E38*F38</f>
+        <v>30000</v>
+      </c>
+      <c r="M38" s="1">
+        <v>1</v>
+      </c>
+      <c r="N38" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:14">
+      <c r="C39" s="1">
+        <v>103</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1</v>
+      </c>
+      <c r="E39" s="1">
+        <v>100</v>
+      </c>
+      <c r="F39" s="1">
         <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I39" s="1">
+        <v>5</v>
+      </c>
+      <c r="J39" s="1">
+        <v>4101</v>
+      </c>
+      <c r="K39" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L39" s="1">
+        <f t="shared" si="3"/>
         <v>50000</v>
       </c>
-      <c r="M38" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:13">
-      <c r="C39" s="1">
+      <c r="M39" s="1">
+        <v>1</v>
+      </c>
+      <c r="N39" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:14">
+      <c r="C40" s="1">
         <v>104</v>
       </c>
-      <c r="D39" s="1">
-        <v>1</v>
-      </c>
-      <c r="E39" s="1">
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1">
         <v>1000</v>
       </c>
-      <c r="F39" s="1">
-        <f>6*M36</f>
+      <c r="F40" s="1">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G40" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H40" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I39" s="1">
+      <c r="I40" s="1">
         <v>15</v>
       </c>
-      <c r="J39" s="1">
+      <c r="J40" s="1">
         <v>4014</v>
       </c>
-      <c r="K39" s="1">
+      <c r="K40" s="1">
         <v>100</v>
       </c>
-      <c r="L39" s="1">
+      <c r="L40" s="1">
+        <f t="shared" si="3"/>
+        <v>6000</v>
+      </c>
+      <c r="M40" s="1">
+        <v>1</v>
+      </c>
+      <c r="N40" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:14">
+      <c r="C41" s="1">
+        <v>105</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1">
+        <v>500</v>
+      </c>
+      <c r="F41" s="1">
         <f t="shared" si="2"/>
-        <v>6000</v>
-      </c>
-      <c r="M39" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:13">
-      <c r="C40" s="1">
-        <v>105</v>
-      </c>
-      <c r="D40" s="1">
-        <v>1</v>
-      </c>
-      <c r="E40" s="1">
-        <v>500</v>
-      </c>
-      <c r="F40" s="1">
-        <f>20*M36</f>
         <v>20</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G41" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H41" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I40" s="1">
-        <v>5</v>
-      </c>
-      <c r="J40" s="1">
+      <c r="I41" s="1">
+        <v>5</v>
+      </c>
+      <c r="J41" s="1">
         <v>4012</v>
       </c>
-      <c r="K40" s="1">
+      <c r="K41" s="1">
         <v>200</v>
       </c>
-      <c r="L40" s="1">
+      <c r="L41" s="1">
+        <f t="shared" si="3"/>
+        <v>10000</v>
+      </c>
+      <c r="M41" s="1">
+        <v>1</v>
+      </c>
+      <c r="N41" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:14">
+      <c r="C42" s="1">
+        <v>106</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1">
+        <v>15000</v>
+      </c>
+      <c r="F42" s="1">
         <f t="shared" si="2"/>
-        <v>10000</v>
-      </c>
-      <c r="M40" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:13">
-      <c r="C41" s="1">
-        <v>106</v>
-      </c>
-      <c r="D41" s="1">
-        <v>1</v>
-      </c>
-      <c r="E41" s="1">
-        <v>15000</v>
-      </c>
-      <c r="F41" s="1">
-        <f>5*M36</f>
-        <v>5</v>
-      </c>
-      <c r="G41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I41" s="1">
-        <v>5</v>
-      </c>
-      <c r="J41" s="1">
+      <c r="I42" s="1">
+        <v>5</v>
+      </c>
+      <c r="J42" s="1">
         <v>4019</v>
       </c>
-      <c r="K41" s="1">
-        <v>1</v>
-      </c>
-      <c r="L41" s="1">
-        <f t="shared" si="2"/>
+      <c r="K42" s="1">
+        <v>1</v>
+      </c>
+      <c r="L42" s="1">
+        <f t="shared" si="3"/>
         <v>75000</v>
       </c>
-      <c r="M41" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:13">
-      <c r="C42" s="1">
+      <c r="M42" s="1">
+        <v>1</v>
+      </c>
+      <c r="N42" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:14">
+      <c r="C43" s="1">
         <v>107</v>
-      </c>
-      <c r="D42" s="1">
-        <v>1</v>
-      </c>
-      <c r="E42" s="1">
-        <v>500</v>
-      </c>
-      <c r="F42" s="1">
-        <f>10*M36</f>
-        <v>10</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I42" s="1">
-        <v>5</v>
-      </c>
-      <c r="J42" s="1">
-        <v>4102</v>
-      </c>
-      <c r="K42" s="1">
-        <v>20</v>
-      </c>
-      <c r="L42" s="1">
-        <f t="shared" si="2"/>
-        <v>5000</v>
-      </c>
-      <c r="M42" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:13">
-      <c r="C43" s="1">
-        <v>108</v>
       </c>
       <c r="D43" s="1">
         <v>1</v>
@@ -2679,14 +2659,14 @@
         <v>500</v>
       </c>
       <c r="F43" s="1">
-        <f>40*M36</f>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I43" s="1">
         <v>5</v>
@@ -2698,16 +2678,19 @@
         <v>1000000</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>20000</v>
       </c>
       <c r="M43" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:13">
+      <c r="N43" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:14">
       <c r="C44" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
@@ -2716,14 +2699,14 @@
         <v>500</v>
       </c>
       <c r="F44" s="1">
-        <f>40*M36</f>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I44" s="1">
         <v>5</v>
@@ -2735,51 +2718,17 @@
         <v>6000000</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>20000</v>
       </c>
       <c r="M44" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:13">
-      <c r="C46" s="1">
-        <v>201</v>
-      </c>
-      <c r="D46" s="1">
-        <v>2</v>
-      </c>
-      <c r="E46" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F46" s="1">
-        <f>20*M46</f>
-        <v>20</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I46" s="1">
-        <v>5</v>
-      </c>
-      <c r="J46" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K46" s="1">
-        <v>5</v>
-      </c>
-      <c r="L46" s="1">
-        <f t="shared" ref="L46:L81" si="3">E46*F46</f>
-        <v>20000</v>
-      </c>
-      <c r="M46" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:13">
+      <c r="N44" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:14">
       <c r="C47" s="1">
         <v>202</v>
       </c>
@@ -2790,7 +2739,7 @@
         <v>200</v>
       </c>
       <c r="F47" s="1">
-        <f>300*M46</f>
+        <f t="shared" ref="F47:F53" si="4">M47*N47</f>
         <v>300</v>
       </c>
       <c r="G47" s="1" t="s">
@@ -2809,14 +2758,17 @@
         <v>1000</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="L47:L53" si="5">E47*F47</f>
         <v>60000</v>
       </c>
       <c r="M47" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:13">
+      <c r="N47" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:14">
       <c r="C48" s="1">
         <v>203</v>
       </c>
@@ -2827,7 +2779,7 @@
         <v>200</v>
       </c>
       <c r="F48" s="1">
-        <f>500*M46</f>
+        <f t="shared" si="4"/>
         <v>500</v>
       </c>
       <c r="G48" s="1" t="s">
@@ -2846,14 +2798,17 @@
         <v>1000</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>100000</v>
       </c>
       <c r="M48" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:13">
+      <c r="N48" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:14">
       <c r="C49" s="1">
         <v>204</v>
       </c>
@@ -2864,7 +2819,7 @@
         <v>2000</v>
       </c>
       <c r="F49" s="1">
-        <f>6*M46</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="G49" s="1" t="s">
@@ -2883,14 +2838,17 @@
         <v>100</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>12000</v>
       </c>
       <c r="M49" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:13">
+      <c r="N49" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:14">
       <c r="C50" s="1">
         <v>205</v>
       </c>
@@ -2901,7 +2859,7 @@
         <v>1000</v>
       </c>
       <c r="F50" s="1">
-        <f>20*M46</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="G50" s="1" t="s">
@@ -2920,14 +2878,17 @@
         <v>200</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20000</v>
       </c>
       <c r="M50" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:13">
+      <c r="N50" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:14">
       <c r="C51" s="1">
         <v>206</v>
       </c>
@@ -2938,7 +2899,7 @@
         <v>30000</v>
       </c>
       <c r="F51" s="1">
-        <f>5*M46</f>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="G51" s="1" t="s">
@@ -2957,14 +2918,17 @@
         <v>1</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>150000</v>
       </c>
       <c r="M51" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:13">
+      <c r="N51" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:14">
       <c r="C52" s="1">
         <v>207</v>
       </c>
@@ -2975,8 +2939,8 @@
         <v>1000</v>
       </c>
       <c r="F52" s="1">
-        <f>10*M46</f>
-        <v>10</v>
+        <f t="shared" si="4"/>
+        <v>40</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>93</v>
@@ -2988,20 +2952,23 @@
         <v>5</v>
       </c>
       <c r="J52" s="1">
-        <v>4102</v>
+        <v>4001</v>
       </c>
       <c r="K52" s="1">
-        <v>20</v>
+        <v>1000000</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="3"/>
-        <v>10000</v>
+        <f t="shared" si="5"/>
+        <v>40000</v>
       </c>
       <c r="M52" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:13">
+      <c r="N52" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:14">
       <c r="C53" s="1">
         <v>208</v>
       </c>
@@ -3012,7 +2979,7 @@
         <v>1000</v>
       </c>
       <c r="F53" s="1">
-        <f>40*M46</f>
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="G53" s="1" t="s">
@@ -3025,94 +2992,23 @@
         <v>5</v>
       </c>
       <c r="J53" s="1">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="K53" s="1">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>40000</v>
       </c>
       <c r="M53" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:13">
-      <c r="C54" s="1">
-        <v>209</v>
-      </c>
-      <c r="D54" s="1">
-        <v>2</v>
-      </c>
-      <c r="E54" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F54" s="1">
-        <f>40*M46</f>
+      <c r="N53" s="1">
         <v>40</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I54" s="1">
-        <v>5</v>
-      </c>
-      <c r="J54" s="1">
-        <v>4002</v>
-      </c>
-      <c r="K54" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="L54" s="1">
-        <f t="shared" si="3"/>
-        <v>40000</v>
-      </c>
-      <c r="M54" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:13">
-      <c r="C55" s="1">
-        <v>210</v>
-      </c>
-      <c r="D55" s="1">
-        <v>3</v>
-      </c>
-      <c r="E55" s="1">
-        <v>2000</v>
-      </c>
-      <c r="F55" s="1">
-        <f>20*M55</f>
-        <v>20</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I55" s="1">
-        <v>5</v>
-      </c>
-      <c r="J55" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K55" s="1">
-        <v>5</v>
-      </c>
-      <c r="L55" s="1">
-        <f t="shared" si="3"/>
-        <v>40000</v>
-      </c>
-      <c r="M55" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:13">
+    </row>
+    <row r="56" customHeight="1" spans="3:14">
       <c r="C56" s="1">
         <v>211</v>
       </c>
@@ -3123,7 +3019,7 @@
         <v>400</v>
       </c>
       <c r="F56" s="1">
-        <f>300*M55</f>
+        <f t="shared" ref="F56:F62" si="6">M56*N56</f>
         <v>300</v>
       </c>
       <c r="G56" s="1" t="s">
@@ -3142,14 +3038,17 @@
         <v>1000</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="L56:L62" si="7">E56*F56</f>
         <v>120000</v>
       </c>
       <c r="M56" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:13">
+      <c r="N56" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:14">
       <c r="C57" s="1">
         <v>212</v>
       </c>
@@ -3160,7 +3059,7 @@
         <v>400</v>
       </c>
       <c r="F57" s="1">
-        <f>500*M55</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="G57" s="1" t="s">
@@ -3179,14 +3078,17 @@
         <v>1000</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>200000</v>
       </c>
       <c r="M57" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:13">
+      <c r="N57" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:14">
       <c r="C58" s="1">
         <v>213</v>
       </c>
@@ -3197,7 +3099,7 @@
         <v>4000</v>
       </c>
       <c r="F58" s="1">
-        <f>6*M55</f>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="G58" s="1" t="s">
@@ -3216,14 +3118,17 @@
         <v>100</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>24000</v>
       </c>
       <c r="M58" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:13">
+      <c r="N58" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:14">
       <c r="C59" s="1">
         <v>214</v>
       </c>
@@ -3234,7 +3139,7 @@
         <v>2000</v>
       </c>
       <c r="F59" s="1">
-        <f>20*M55</f>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="G59" s="1" t="s">
@@ -3253,14 +3158,17 @@
         <v>200</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>40000</v>
       </c>
       <c r="M59" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:13">
+      <c r="N59" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:14">
       <c r="C60" s="1">
         <v>215</v>
       </c>
@@ -3271,7 +3179,7 @@
         <v>45000</v>
       </c>
       <c r="F60" s="1">
-        <f>5*M55</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="G60" s="1" t="s">
@@ -3290,14 +3198,17 @@
         <v>1</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>225000</v>
       </c>
       <c r="M60" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:13">
+      <c r="N60" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:14">
       <c r="C61" s="1">
         <v>216</v>
       </c>
@@ -3308,8 +3219,8 @@
         <v>2000</v>
       </c>
       <c r="F61" s="1">
-        <f>10*M55</f>
-        <v>10</v>
+        <f t="shared" si="6"/>
+        <v>40</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>93</v>
@@ -3321,20 +3232,23 @@
         <v>5</v>
       </c>
       <c r="J61" s="1">
-        <v>4102</v>
+        <v>4001</v>
       </c>
       <c r="K61" s="1">
-        <v>20</v>
+        <v>1000000</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="3"/>
-        <v>20000</v>
+        <f t="shared" si="7"/>
+        <v>80000</v>
       </c>
       <c r="M61" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:13">
+      <c r="N61" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:14">
       <c r="C62" s="1">
         <v>217</v>
       </c>
@@ -3345,7 +3259,7 @@
         <v>2000</v>
       </c>
       <c r="F62" s="1">
-        <f>40*M55</f>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
       <c r="G62" s="1" t="s">
@@ -3358,94 +3272,23 @@
         <v>5</v>
       </c>
       <c r="J62" s="1">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="K62" s="1">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>80000</v>
       </c>
       <c r="M62" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:13">
-      <c r="C63" s="1">
-        <v>218</v>
-      </c>
-      <c r="D63" s="1">
-        <v>3</v>
-      </c>
-      <c r="E63" s="1">
-        <v>2000</v>
-      </c>
-      <c r="F63" s="1">
-        <f>40*M55</f>
+      <c r="N62" s="1">
         <v>40</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I63" s="1">
-        <v>5</v>
-      </c>
-      <c r="J63" s="1">
-        <v>4002</v>
-      </c>
-      <c r="K63" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="L63" s="1">
-        <f t="shared" si="3"/>
-        <v>80000</v>
-      </c>
-      <c r="M63" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:13">
-      <c r="C64" s="1">
-        <v>219</v>
-      </c>
-      <c r="D64" s="1">
-        <v>4</v>
-      </c>
-      <c r="E64" s="4">
-        <v>3000</v>
-      </c>
-      <c r="F64" s="1">
-        <f>20*M64</f>
-        <v>20</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I64" s="1">
-        <v>5</v>
-      </c>
-      <c r="J64" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K64" s="1">
-        <v>5</v>
-      </c>
-      <c r="L64" s="1">
-        <f t="shared" si="3"/>
-        <v>60000</v>
-      </c>
-      <c r="M64" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:13">
+    </row>
+    <row r="65" customHeight="1" spans="3:14">
       <c r="C65" s="1">
         <v>220</v>
       </c>
@@ -3456,7 +3299,7 @@
         <v>600</v>
       </c>
       <c r="F65" s="1">
-        <f>300*M64</f>
+        <f t="shared" ref="F65:F71" si="8">M65*N65</f>
         <v>300</v>
       </c>
       <c r="G65" s="1" t="s">
@@ -3475,14 +3318,17 @@
         <v>1000</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="L65:L71" si="9">E65*F65</f>
         <v>180000</v>
       </c>
       <c r="M65" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:13">
+      <c r="N65" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:14">
       <c r="C66" s="1">
         <v>221</v>
       </c>
@@ -3493,7 +3339,7 @@
         <v>600</v>
       </c>
       <c r="F66" s="1">
-        <f>500*M64</f>
+        <f t="shared" si="8"/>
         <v>500</v>
       </c>
       <c r="G66" s="1" t="s">
@@ -3512,14 +3358,17 @@
         <v>1000</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>300000</v>
       </c>
       <c r="M66" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:13">
+      <c r="N66" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:14">
       <c r="C67" s="1">
         <v>222</v>
       </c>
@@ -3530,7 +3379,7 @@
         <v>6000</v>
       </c>
       <c r="F67" s="1">
-        <f>6*M64</f>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
       <c r="G67" s="1" t="s">
@@ -3549,14 +3398,17 @@
         <v>100</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>36000</v>
       </c>
       <c r="M67" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" customHeight="1" spans="3:13">
+      <c r="N67" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:14">
       <c r="C68" s="1">
         <v>223</v>
       </c>
@@ -3567,7 +3419,7 @@
         <v>3000</v>
       </c>
       <c r="F68" s="1">
-        <f>20*M64</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="G68" s="1" t="s">
@@ -3586,14 +3438,17 @@
         <v>200</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>60000</v>
       </c>
       <c r="M68" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:13">
+      <c r="N68" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:14">
       <c r="C69" s="1">
         <v>224</v>
       </c>
@@ -3604,7 +3459,7 @@
         <v>60000</v>
       </c>
       <c r="F69" s="1">
-        <f>5*M64</f>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
       <c r="G69" s="1" t="s">
@@ -3623,14 +3478,17 @@
         <v>1</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>300000</v>
       </c>
       <c r="M69" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:13">
+      <c r="N69" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:14">
       <c r="C70" s="1">
         <v>225</v>
       </c>
@@ -3641,8 +3499,8 @@
         <v>3000</v>
       </c>
       <c r="F70" s="1">
-        <f>10*M64</f>
-        <v>10</v>
+        <f t="shared" si="8"/>
+        <v>40</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>93</v>
@@ -3654,20 +3512,23 @@
         <v>5</v>
       </c>
       <c r="J70" s="1">
-        <v>4102</v>
+        <v>4001</v>
       </c>
       <c r="K70" s="1">
-        <v>20</v>
+        <v>1000000</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" si="3"/>
-        <v>30000</v>
+        <f t="shared" si="9"/>
+        <v>120000</v>
       </c>
       <c r="M70" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" customHeight="1" spans="3:13">
+      <c r="N70" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:14">
       <c r="C71" s="1">
         <v>226</v>
       </c>
@@ -3678,7 +3539,7 @@
         <v>3000</v>
       </c>
       <c r="F71" s="1">
-        <f>40*M64</f>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
       <c r="G71" s="1" t="s">
@@ -3691,94 +3552,23 @@
         <v>5</v>
       </c>
       <c r="J71" s="1">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="K71" s="1">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>120000</v>
       </c>
       <c r="M71" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" customHeight="1" spans="3:13">
-      <c r="C72" s="1">
-        <v>227</v>
-      </c>
-      <c r="D72" s="1">
-        <v>4</v>
-      </c>
-      <c r="E72" s="4">
-        <v>3000</v>
-      </c>
-      <c r="F72" s="1">
-        <f>40*M64</f>
+      <c r="N71" s="1">
         <v>40</v>
       </c>
-      <c r="G72" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I72" s="1">
-        <v>5</v>
-      </c>
-      <c r="J72" s="1">
-        <v>4002</v>
-      </c>
-      <c r="K72" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="L72" s="1">
-        <f t="shared" si="3"/>
-        <v>120000</v>
-      </c>
-      <c r="M72" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="3:13">
-      <c r="C73" s="1">
-        <v>228</v>
-      </c>
-      <c r="D73" s="1">
-        <v>5</v>
-      </c>
-      <c r="E73" s="1">
-        <v>4000</v>
-      </c>
-      <c r="F73" s="1">
-        <f>20*M73</f>
-        <v>80</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I73" s="1">
-        <v>5</v>
-      </c>
-      <c r="J73" s="1">
-        <v>4010</v>
-      </c>
-      <c r="K73" s="1">
-        <v>5</v>
-      </c>
-      <c r="L73" s="1">
-        <f t="shared" si="3"/>
-        <v>320000</v>
-      </c>
-      <c r="M73" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:13">
+    </row>
+    <row r="74" customHeight="1" spans="3:14">
       <c r="C74" s="1">
         <v>229</v>
       </c>
@@ -3789,7 +3579,7 @@
         <v>800</v>
       </c>
       <c r="F74" s="1">
-        <f>300*M73</f>
+        <f t="shared" ref="F74:F80" si="10">M74*N74</f>
         <v>1200</v>
       </c>
       <c r="G74" s="1" t="s">
@@ -3808,14 +3598,17 @@
         <v>1000</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="L74:L80" si="11">E74*F74</f>
         <v>960000</v>
       </c>
       <c r="M74" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="75" customHeight="1" spans="3:13">
+      <c r="N74" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:14">
       <c r="C75" s="1">
         <v>230</v>
       </c>
@@ -3826,7 +3619,7 @@
         <v>800</v>
       </c>
       <c r="F75" s="1">
-        <f>500*M73</f>
+        <f t="shared" si="10"/>
         <v>2000</v>
       </c>
       <c r="G75" s="1" t="s">
@@ -3845,14 +3638,17 @@
         <v>1000</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>1600000</v>
       </c>
       <c r="M75" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:13">
+      <c r="N75" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:14">
       <c r="C76" s="1">
         <v>231</v>
       </c>
@@ -3863,7 +3659,7 @@
         <v>8000</v>
       </c>
       <c r="F76" s="1">
-        <f>6*M73</f>
+        <f t="shared" si="10"/>
         <v>24</v>
       </c>
       <c r="G76" s="1" t="s">
@@ -3882,14 +3678,17 @@
         <v>100</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>192000</v>
       </c>
       <c r="M76" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:13">
+      <c r="N76" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:14">
       <c r="C77" s="1">
         <v>232</v>
       </c>
@@ -3900,7 +3699,7 @@
         <v>4000</v>
       </c>
       <c r="F77" s="1">
-        <f>20*M73</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="G77" s="1" t="s">
@@ -3919,14 +3718,17 @@
         <v>200</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>320000</v>
       </c>
       <c r="M77" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="78" customHeight="1" spans="3:13">
+      <c r="N77" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:14">
       <c r="C78" s="1">
         <v>233</v>
       </c>
@@ -3937,7 +3739,7 @@
         <v>75000</v>
       </c>
       <c r="F78" s="1">
-        <f>5*M73</f>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="G78" s="1" t="s">
@@ -3956,14 +3758,17 @@
         <v>1</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>1500000</v>
       </c>
       <c r="M78" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="79" customHeight="1" spans="3:13">
+      <c r="N78" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:14">
       <c r="C79" s="1">
         <v>234</v>
       </c>
@@ -3974,8 +3779,8 @@
         <v>4000</v>
       </c>
       <c r="F79" s="1">
-        <f>10*M73</f>
-        <v>40</v>
+        <f t="shared" si="10"/>
+        <v>160</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>93</v>
@@ -3987,20 +3792,23 @@
         <v>5</v>
       </c>
       <c r="J79" s="1">
-        <v>4102</v>
+        <v>4001</v>
       </c>
       <c r="K79" s="1">
-        <v>20</v>
+        <v>1000000</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="3"/>
-        <v>160000</v>
+        <f t="shared" si="11"/>
+        <v>640000</v>
       </c>
       <c r="M79" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="80" customHeight="1" spans="3:13">
+      <c r="N79" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:14">
       <c r="C80" s="1">
         <v>235</v>
       </c>
@@ -4011,7 +3819,7 @@
         <v>4000</v>
       </c>
       <c r="F80" s="1">
-        <f>40*M73</f>
+        <f t="shared" si="10"/>
         <v>160</v>
       </c>
       <c r="G80" s="1" t="s">
@@ -4024,68 +3832,67 @@
         <v>5</v>
       </c>
       <c r="J80" s="1">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="K80" s="1">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="11"/>
         <v>640000</v>
       </c>
       <c r="M80" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="81" customHeight="1" spans="3:13">
-      <c r="C81" s="1">
-        <v>236</v>
-      </c>
-      <c r="D81" s="1">
-        <v>5</v>
-      </c>
-      <c r="E81" s="1">
-        <v>4000</v>
-      </c>
-      <c r="F81" s="1">
-        <f>40*M73</f>
-        <v>160</v>
-      </c>
-      <c r="G81" s="1" t="s">
+      <c r="N80" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:12">
+      <c r="C83" s="1">
+        <v>999</v>
+      </c>
+      <c r="D83" s="1">
+        <v>0</v>
+      </c>
+      <c r="E83" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F83" s="1">
+        <v>50</v>
+      </c>
+      <c r="G83" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="H81" s="1" t="s">
+      <c r="H83" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I81" s="1">
-        <v>5</v>
-      </c>
-      <c r="J81" s="1">
-        <v>4002</v>
-      </c>
-      <c r="K81" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="L81" s="1">
-        <f t="shared" si="3"/>
-        <v>640000</v>
-      </c>
-      <c r="M81" s="1">
-        <v>4</v>
+      <c r="I83" s="1">
+        <v>5</v>
+      </c>
+      <c r="J83" s="1">
+        <v>4006</v>
+      </c>
+      <c r="K83" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L83" s="1">
+        <f>E83*F83</f>
+        <v>50000</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:12">
       <c r="C84" s="1">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D84" s="1">
         <v>0</v>
       </c>
-      <c r="E84" s="6" t="s">
-        <v>49</v>
+      <c r="E84" s="1">
+        <v>2000</v>
       </c>
       <c r="F84" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>99</v>
@@ -4097,14 +3904,47 @@
         <v>5</v>
       </c>
       <c r="J84" s="1">
-        <v>4006</v>
+        <v>4010</v>
       </c>
       <c r="K84" s="1">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L84" s="1">
         <f>E84*F84</f>
-        <v>50000</v>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:12">
+      <c r="C85" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D85" s="1">
+        <v>0</v>
+      </c>
+      <c r="E85" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F85" s="1">
+        <v>50</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I85" s="1">
+        <v>5</v>
+      </c>
+      <c r="J85" s="1">
+        <v>4102</v>
+      </c>
+      <c r="K85" s="1">
+        <v>20</v>
+      </c>
+      <c r="L85" s="1">
+        <f>E85*F85</f>
+        <v>100000</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -2147,7 +2147,7 @@
     </row>
     <row r="27" customHeight="1" spans="3:12">
       <c r="C27" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -2156,7 +2156,7 @@
         <v>55</v>
       </c>
       <c r="F27" s="1">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>61</v>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="L27" s="1">
         <f t="shared" si="1"/>
-        <v>2500000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:12">
       <c r="C28" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -2213,7 +2213,7 @@
     </row>
     <row r="29" customHeight="1" spans="3:12">
       <c r="C29" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
@@ -2252,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="C30" s="1">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="31" customHeight="1" spans="3:12">
       <c r="C31" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
@@ -2318,7 +2318,7 @@
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C32" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
@@ -2351,7 +2351,7 @@
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C33" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
@@ -2384,7 +2384,7 @@
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C34" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C35" s="1">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -1350,11 +1350,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="11.2583333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.2545454545455" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="7" width="22.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1272727272727" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.8727272727273" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.5" style="1" customWidth="1"/>
     <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
@@ -2222,7 +2222,7 @@
         <v>66</v>
       </c>
       <c r="F29" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>67</v>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="L29" s="1">
         <f t="shared" si="1"/>
-        <v>400000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:12">

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="124">
   <si>
     <t>#</t>
   </si>
@@ -212,12 +212,6 @@
     <t>法宝自选</t>
   </si>
   <si>
-    <t>兑换低级法宝自选*1</t>
-  </si>
-  <si>
-    <t>低级法宝自选</t>
-  </si>
-  <si>
     <t>300000</t>
   </si>
   <si>
@@ -278,6 +272,72 @@
     <t>红宠自选</t>
   </si>
   <si>
+    <t>兑换开孔石</t>
+  </si>
+  <si>
+    <t>开孔石</t>
+  </si>
+  <si>
+    <t>兑换攻击宝石</t>
+  </si>
+  <si>
+    <t>攻击宝石</t>
+  </si>
+  <si>
+    <t>兑换防御宝石</t>
+  </si>
+  <si>
+    <t>防御宝石</t>
+  </si>
+  <si>
+    <t>兑换生命宝石</t>
+  </si>
+  <si>
+    <t>生命宝石</t>
+  </si>
+  <si>
+    <t>兑换命中宝石</t>
+  </si>
+  <si>
+    <t>命中宝石</t>
+  </si>
+  <si>
+    <t>兑换闪避宝石</t>
+  </si>
+  <si>
+    <t>闪避宝石</t>
+  </si>
+  <si>
+    <t>兑换物理宝石</t>
+  </si>
+  <si>
+    <t>物理宝石</t>
+  </si>
+  <si>
+    <t>兑换魔法宝石</t>
+  </si>
+  <si>
+    <t>魔法宝石</t>
+  </si>
+  <si>
+    <t>兑换道术宝石</t>
+  </si>
+  <si>
+    <t>道术宝石</t>
+  </si>
+  <si>
+    <t>兑换增伤宝石</t>
+  </si>
+  <si>
+    <t>增伤宝石</t>
+  </si>
+  <si>
+    <t>兑换韧性宝石</t>
+  </si>
+  <si>
+    <t>韧性宝石</t>
+  </si>
+  <si>
     <t>兑换四格碎片*1000</t>
   </si>
   <si>
@@ -318,6 +378,9 @@
   </si>
   <si>
     <t>精炼石</t>
+  </si>
+  <si>
+    <t>兑换暗金精华*1</t>
   </si>
   <si>
     <t>兑换书页1000个</t>
@@ -348,7 +411,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -366,6 +429,11 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -843,160 +911,161 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1346,7 +1415,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N85"/>
+  <dimension ref="C1:N95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1459,11 +1528,11 @@
       <c r="D6" s="1">
         <v>0</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="1">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>13</v>
@@ -1482,7 +1551,7 @@
       </c>
       <c r="L6" s="1">
         <f t="shared" ref="L6:L9" si="0">E6*F6</f>
-        <v>20400</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:12">
@@ -1492,11 +1561,11 @@
       <c r="D7" s="1">
         <v>0</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F7" s="1">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>15</v>
@@ -1515,7 +1584,7 @@
       </c>
       <c r="L7" s="1">
         <f t="shared" si="0"/>
-        <v>20400</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1525,11 +1594,11 @@
       <c r="D8" s="1">
         <v>0</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F8" s="1">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>17</v>
@@ -1548,7 +1617,7 @@
       </c>
       <c r="L8" s="1">
         <f t="shared" si="0"/>
-        <v>20400</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:12">
@@ -1558,11 +1627,11 @@
       <c r="D9" s="1">
         <v>0</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="7" t="s">
         <v>19</v>
       </c>
       <c r="F9" s="1">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>20</v>
@@ -1581,7 +1650,7 @@
       </c>
       <c r="L9" s="1">
         <f t="shared" si="0"/>
-        <v>14000</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:12">
@@ -1591,11 +1660,11 @@
       <c r="D10" s="1">
         <v>0</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F10" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>22</v>
@@ -1613,8 +1682,8 @@
         <v>1</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" ref="L10:L35" si="1">E10*F10</f>
-        <v>30000</v>
+        <f t="shared" ref="L10:L45" si="1">E10*F10</f>
+        <v>60000</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:12">
@@ -1624,11 +1693,11 @@
       <c r="D11" s="1">
         <v>0</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>24</v>
@@ -1647,7 +1716,7 @@
       </c>
       <c r="L11" s="1">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:12">
@@ -1657,11 +1726,11 @@
       <c r="D12" s="1">
         <v>0</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F12" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>26</v>
@@ -1680,7 +1749,7 @@
       </c>
       <c r="L12" s="1">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:12">
@@ -1690,11 +1759,11 @@
       <c r="D13" s="1">
         <v>0</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="7" t="s">
         <v>19</v>
       </c>
       <c r="F13" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>28</v>
@@ -1705,7 +1774,7 @@
       <c r="I13" s="1">
         <v>4</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="6">
         <v>15</v>
       </c>
       <c r="K13" s="1">
@@ -1713,7 +1782,7 @@
       </c>
       <c r="L13" s="1">
         <f t="shared" si="1"/>
-        <v>50000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:12">
@@ -1723,11 +1792,11 @@
       <c r="D14" s="1">
         <v>0</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="7" t="s">
         <v>19</v>
       </c>
       <c r="F14" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>30</v>
@@ -1738,7 +1807,7 @@
       <c r="I14" s="1">
         <v>4</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="6">
         <v>16</v>
       </c>
       <c r="K14" s="1">
@@ -1746,7 +1815,7 @@
       </c>
       <c r="L14" s="1">
         <f t="shared" si="1"/>
-        <v>50000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:12">
@@ -1756,11 +1825,11 @@
       <c r="D15" s="1">
         <v>0</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="7" t="s">
         <v>19</v>
       </c>
       <c r="F15" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>32</v>
@@ -1771,7 +1840,7 @@
       <c r="I15" s="1">
         <v>4</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15" s="6">
         <v>17</v>
       </c>
       <c r="K15" s="1">
@@ -1779,7 +1848,7 @@
       </c>
       <c r="L15" s="1">
         <f t="shared" si="1"/>
-        <v>50000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:12">
@@ -1789,11 +1858,11 @@
       <c r="D16" s="1">
         <v>0</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F16" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>34</v>
@@ -1812,7 +1881,7 @@
       </c>
       <c r="L16" s="1">
         <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:12">
@@ -1822,11 +1891,11 @@
       <c r="D17" s="1">
         <v>0</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F17" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>36</v>
@@ -1845,7 +1914,7 @@
       </c>
       <c r="L17" s="1">
         <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:12">
@@ -1855,11 +1924,11 @@
       <c r="D18" s="1">
         <v>0</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F18" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>38</v>
@@ -1878,7 +1947,7 @@
       </c>
       <c r="L18" s="1">
         <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:12">
@@ -1888,11 +1957,11 @@
       <c r="D19" s="1">
         <v>0</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F19" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>40</v>
@@ -1911,7 +1980,7 @@
       </c>
       <c r="L19" s="1">
         <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:12">
@@ -1921,11 +1990,11 @@
       <c r="D20" s="1">
         <v>0</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F20" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>42</v>
@@ -1944,7 +2013,7 @@
       </c>
       <c r="L20" s="1">
         <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:12">
@@ -1954,7 +2023,7 @@
       <c r="D21" s="1">
         <v>0</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="7" t="s">
         <v>44</v>
       </c>
       <c r="F21" s="1">
@@ -1987,7 +2056,7 @@
       <c r="D22" s="1">
         <v>0</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="7" t="s">
         <v>19</v>
       </c>
       <c r="F22" s="1">
@@ -2020,7 +2089,7 @@
       <c r="D23" s="1">
         <v>0</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="7" t="s">
         <v>49</v>
       </c>
       <c r="F23" s="1">
@@ -2053,11 +2122,11 @@
       <c r="D24" s="1">
         <v>0</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="7" t="s">
         <v>52</v>
       </c>
       <c r="F24" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>53</v>
@@ -2076,7 +2145,7 @@
       </c>
       <c r="L24" s="1">
         <f t="shared" si="1"/>
-        <v>180000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:12">
@@ -2086,11 +2155,11 @@
       <c r="D25" s="1">
         <v>0</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="7" t="s">
         <v>55</v>
       </c>
       <c r="F25" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>56</v>
@@ -2109,7 +2178,7 @@
       </c>
       <c r="L25" s="1">
         <f t="shared" si="1"/>
-        <v>150000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:12">
@@ -2119,11 +2188,11 @@
       <c r="D26" s="1">
         <v>0</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="7" t="s">
         <v>58</v>
       </c>
       <c r="F26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>59</v>
@@ -2142,7 +2211,7 @@
       </c>
       <c r="L26" s="1">
         <f t="shared" si="1"/>
-        <v>200000</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:12">
@@ -2152,30 +2221,30 @@
       <c r="D27" s="1">
         <v>0</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>55</v>
+      <c r="E27" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="F27" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I27" s="1">
         <v>4</v>
       </c>
       <c r="J27" s="1">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K27" s="1">
         <v>1</v>
       </c>
       <c r="L27" s="1">
         <f t="shared" si="1"/>
-        <v>1000000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:12">
@@ -2185,30 +2254,30 @@
       <c r="D28" s="1">
         <v>0</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>63</v>
+      <c r="E28" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="F28" s="1">
         <v>3</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I28" s="1">
         <v>4</v>
       </c>
       <c r="J28" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K28" s="1">
         <v>1</v>
       </c>
       <c r="L28" s="1">
         <f t="shared" si="1"/>
-        <v>900000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:12">
@@ -2218,69 +2287,63 @@
       <c r="D29" s="1">
         <v>0</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>66</v>
+      <c r="E29" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="F29" s="1">
         <v>2</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I29" s="1">
         <v>4</v>
       </c>
       <c r="J29" s="1">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K29" s="1">
         <v>1</v>
       </c>
       <c r="L29" s="1">
         <f t="shared" si="1"/>
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:12">
-      <c r="A30" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:12">
       <c r="C30" s="1">
         <v>25</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>69</v>
+      <c r="E30" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="F30" s="1">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I30" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="1">
-        <v>31</v>
+        <v>4021</v>
       </c>
       <c r="K30" s="1">
         <v>1</v>
       </c>
       <c r="L30" s="1">
         <f t="shared" si="1"/>
-        <v>500000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:12">
@@ -2290,11 +2353,11 @@
       <c r="D31" s="1">
         <v>0</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>72</v>
+      <c r="E31" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="F31" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>73</v>
@@ -2306,25 +2369,25 @@
         <v>5</v>
       </c>
       <c r="J31" s="1">
-        <v>4021</v>
+        <v>4022</v>
       </c>
       <c r="K31" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L31" s="1">
         <f t="shared" si="1"/>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:12">
       <c r="C32" s="1">
         <v>27</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>72</v>
+      <c r="E32" s="1">
+        <v>3000</v>
       </c>
       <c r="F32" s="1">
         <v>100</v>
@@ -2339,17 +2402,17 @@
         <v>5</v>
       </c>
       <c r="J32" s="1">
-        <v>4022</v>
+        <v>4011</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="L32" s="1">
         <f t="shared" si="1"/>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:12">
       <c r="C33" s="1">
         <v>28</v>
       </c>
@@ -2357,10 +2420,10 @@
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="F33" s="1">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>77</v>
@@ -2372,14 +2435,14 @@
         <v>5</v>
       </c>
       <c r="J33" s="1">
-        <v>4011</v>
+        <v>4020</v>
       </c>
       <c r="K33" s="1">
         <v>1</v>
       </c>
       <c r="L33" s="1">
         <f t="shared" si="1"/>
-        <v>180000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2390,10 +2453,10 @@
         <v>0</v>
       </c>
       <c r="E34" s="1">
-        <v>20000</v>
+        <v>488888</v>
       </c>
       <c r="F34" s="1">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>79</v>
@@ -2402,17 +2465,17 @@
         <v>80</v>
       </c>
       <c r="I34" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J34" s="1">
-        <v>4020</v>
+        <v>204</v>
       </c>
       <c r="K34" s="1">
         <v>1</v>
       </c>
       <c r="L34" s="1">
         <f t="shared" si="1"/>
-        <v>600000</v>
+        <v>488888</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -2423,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>488888</v>
+        <v>600000</v>
       </c>
       <c r="F35" s="1">
         <v>1</v>
@@ -2435,1515 +2498,2089 @@
         <v>82</v>
       </c>
       <c r="I35" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J35" s="1">
-        <v>204</v>
+        <v>4027</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
       </c>
       <c r="L35" s="1">
         <f t="shared" si="1"/>
-        <v>488888</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:14">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:12">
+      <c r="C36" s="1">
+        <v>31</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0</v>
+      </c>
+      <c r="E36" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F36" s="1">
+        <v>15</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I36" s="1">
+        <v>5</v>
+      </c>
+      <c r="J36" s="6">
+        <v>60000001</v>
+      </c>
+      <c r="K36" s="1">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1">
+        <f t="shared" si="1"/>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:12">
+      <c r="C37" s="1">
+        <v>32</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0</v>
+      </c>
+      <c r="E37" s="1">
+        <v>15000</v>
+      </c>
+      <c r="F37" s="1">
+        <v>20</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I37" s="1">
+        <v>5</v>
+      </c>
+      <c r="J37" s="6">
+        <v>60000002</v>
+      </c>
+      <c r="K37" s="1">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1">
+        <f t="shared" si="1"/>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" customHeight="1" spans="3:14">
       <c r="C38" s="1">
+        <v>33</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0</v>
+      </c>
+      <c r="E38" s="1">
+        <v>15000</v>
+      </c>
+      <c r="F38" s="1">
+        <v>20</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I38" s="1">
+        <v>5</v>
+      </c>
+      <c r="J38" s="6">
+        <v>60000003</v>
+      </c>
+      <c r="K38" s="1">
+        <v>1</v>
+      </c>
+      <c r="L38" s="1">
+        <f t="shared" si="1"/>
+        <v>300000</v>
+      </c>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+    </row>
+    <row r="39" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C39" s="1">
+        <v>34</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1">
+        <v>25000</v>
+      </c>
+      <c r="F39" s="1">
+        <v>10</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I39" s="1">
+        <v>5</v>
+      </c>
+      <c r="J39" s="6">
+        <v>60000004</v>
+      </c>
+      <c r="K39" s="1">
+        <v>1</v>
+      </c>
+      <c r="L39" s="1">
+        <f t="shared" si="1"/>
+        <v>250000</v>
+      </c>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+    </row>
+    <row r="40" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C40" s="1">
+        <v>35</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0</v>
+      </c>
+      <c r="E40" s="1">
+        <v>25000</v>
+      </c>
+      <c r="F40" s="1">
+        <v>10</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I40" s="1">
+        <v>5</v>
+      </c>
+      <c r="J40" s="6">
+        <v>60000005</v>
+      </c>
+      <c r="K40" s="1">
+        <v>1</v>
+      </c>
+      <c r="L40" s="1">
+        <f t="shared" si="1"/>
+        <v>250000</v>
+      </c>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+    </row>
+    <row r="41" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C41" s="1">
+        <v>36</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
+      <c r="E41" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F41" s="1">
+        <v>15</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I41" s="1">
+        <v>5</v>
+      </c>
+      <c r="J41" s="6">
+        <v>60000006</v>
+      </c>
+      <c r="K41" s="1">
+        <v>1</v>
+      </c>
+      <c r="L41" s="1">
+        <f t="shared" si="1"/>
+        <v>300000</v>
+      </c>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+    </row>
+    <row r="42" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C42" s="1">
+        <v>37</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0</v>
+      </c>
+      <c r="E42" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F42" s="1">
+        <v>15</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I42" s="1">
+        <v>5</v>
+      </c>
+      <c r="J42" s="6">
+        <v>60000007</v>
+      </c>
+      <c r="K42" s="1">
+        <v>1</v>
+      </c>
+      <c r="L42" s="1">
+        <f t="shared" si="1"/>
+        <v>300000</v>
+      </c>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+    </row>
+    <row r="43" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C43" s="1">
+        <v>38</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0</v>
+      </c>
+      <c r="E43" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F43" s="1">
+        <v>15</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I43" s="1">
+        <v>5</v>
+      </c>
+      <c r="J43" s="6">
+        <v>60000008</v>
+      </c>
+      <c r="K43" s="1">
+        <v>1</v>
+      </c>
+      <c r="L43" s="1">
+        <f t="shared" si="1"/>
+        <v>300000</v>
+      </c>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+    </row>
+    <row r="44" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C44" s="1">
+        <v>39</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F44" s="1">
+        <v>15</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I44" s="1">
+        <v>5</v>
+      </c>
+      <c r="J44" s="6">
+        <v>60000009</v>
+      </c>
+      <c r="K44" s="1">
+        <v>1</v>
+      </c>
+      <c r="L44" s="1">
+        <f t="shared" si="1"/>
+        <v>300000</v>
+      </c>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+    </row>
+    <row r="45" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C45" s="1">
+        <v>40</v>
+      </c>
+      <c r="D45" s="1">
+        <v>0</v>
+      </c>
+      <c r="E45" s="1">
+        <v>20000</v>
+      </c>
+      <c r="F45" s="1">
+        <v>20</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D38" s="1">
-        <v>1</v>
-      </c>
-      <c r="E38" s="1">
+      <c r="I45" s="1">
+        <v>5</v>
+      </c>
+      <c r="J45" s="6">
+        <v>60000010</v>
+      </c>
+      <c r="K45" s="1">
+        <v>1</v>
+      </c>
+      <c r="L45" s="1">
+        <f t="shared" si="1"/>
+        <v>400000</v>
+      </c>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+    </row>
+    <row r="46" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+    </row>
+    <row r="47" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C48" s="1">
+        <v>102</v>
+      </c>
+      <c r="D48" s="1">
+        <v>1</v>
+      </c>
+      <c r="E48" s="1">
         <v>100</v>
       </c>
-      <c r="F38" s="1">
-        <f t="shared" ref="F38:F44" si="2">M38*N38</f>
+      <c r="F48" s="1">
+        <f t="shared" ref="F48:F55" si="2">M48*N48</f>
         <v>300</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I38" s="1">
-        <v>5</v>
-      </c>
-      <c r="J38" s="1">
+      <c r="G48" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I48" s="1">
+        <v>5</v>
+      </c>
+      <c r="J48" s="1">
         <v>4007</v>
       </c>
-      <c r="K38" s="1">
+      <c r="K48" s="1">
         <v>1000</v>
       </c>
-      <c r="L38" s="1">
-        <f t="shared" ref="L38:L44" si="3">E38*F38</f>
+      <c r="L48" s="1">
+        <f t="shared" ref="L48:L55" si="3">E48*F48</f>
         <v>30000</v>
       </c>
-      <c r="M38" s="1">
-        <v>1</v>
-      </c>
-      <c r="N38" s="1">
+      <c r="M48" s="1">
+        <v>1</v>
+      </c>
+      <c r="N48" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="3:14">
-      <c r="C39" s="1">
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C49" s="1">
         <v>103</v>
       </c>
-      <c r="D39" s="1">
-        <v>1</v>
-      </c>
-      <c r="E39" s="1">
+      <c r="D49" s="1">
+        <v>1</v>
+      </c>
+      <c r="E49" s="1">
         <v>100</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F49" s="1">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I39" s="1">
-        <v>5</v>
-      </c>
-      <c r="J39" s="1">
+      <c r="G49" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I49" s="1">
+        <v>5</v>
+      </c>
+      <c r="J49" s="1">
         <v>4101</v>
       </c>
-      <c r="K39" s="1">
+      <c r="K49" s="1">
         <v>1000</v>
       </c>
-      <c r="L39" s="1">
+      <c r="L49" s="1">
         <f t="shared" si="3"/>
         <v>50000</v>
       </c>
-      <c r="M39" s="1">
-        <v>1</v>
-      </c>
-      <c r="N39" s="1">
+      <c r="M49" s="1">
+        <v>1</v>
+      </c>
+      <c r="N49" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="3:14">
-      <c r="C40" s="1">
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C50" s="1">
         <v>104</v>
       </c>
-      <c r="D40" s="1">
-        <v>1</v>
-      </c>
-      <c r="E40" s="1">
+      <c r="D50" s="1">
+        <v>1</v>
+      </c>
+      <c r="E50" s="1">
         <v>1000</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F50" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I40" s="1">
+      <c r="G50" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I50" s="1">
         <v>15</v>
       </c>
-      <c r="J40" s="1">
+      <c r="J50" s="1">
         <v>4014</v>
       </c>
-      <c r="K40" s="1">
+      <c r="K50" s="1">
         <v>100</v>
       </c>
-      <c r="L40" s="1">
+      <c r="L50" s="1">
         <f t="shared" si="3"/>
         <v>6000</v>
       </c>
-      <c r="M40" s="1">
-        <v>1</v>
-      </c>
-      <c r="N40" s="1">
+      <c r="M50" s="1">
+        <v>1</v>
+      </c>
+      <c r="N50" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="3:14">
-      <c r="C41" s="1">
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C51" s="1">
         <v>105</v>
       </c>
-      <c r="D41" s="1">
-        <v>1</v>
-      </c>
-      <c r="E41" s="1">
+      <c r="D51" s="1">
+        <v>1</v>
+      </c>
+      <c r="E51" s="1">
         <v>500</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F51" s="1">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="G41" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I41" s="1">
-        <v>5</v>
-      </c>
-      <c r="J41" s="1">
+      <c r="G51" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I51" s="1">
+        <v>5</v>
+      </c>
+      <c r="J51" s="1">
         <v>4012</v>
       </c>
-      <c r="K41" s="1">
+      <c r="K51" s="1">
         <v>200</v>
       </c>
-      <c r="L41" s="1">
+      <c r="L51" s="1">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
-      <c r="M41" s="1">
-        <v>1</v>
-      </c>
-      <c r="N41" s="1">
+      <c r="M51" s="1">
+        <v>1</v>
+      </c>
+      <c r="N51" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="3:14">
-      <c r="C42" s="1">
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C52" s="1">
         <v>106</v>
       </c>
-      <c r="D42" s="1">
-        <v>1</v>
-      </c>
-      <c r="E42" s="1">
+      <c r="D52" s="1">
+        <v>1</v>
+      </c>
+      <c r="E52" s="1">
         <v>15000</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F52" s="1">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I42" s="1">
-        <v>5</v>
-      </c>
-      <c r="J42" s="1">
+        <v>8</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I52" s="1">
+        <v>5</v>
+      </c>
+      <c r="J52" s="1">
         <v>4019</v>
       </c>
-      <c r="K42" s="1">
-        <v>1</v>
-      </c>
-      <c r="L42" s="1">
+      <c r="K52" s="1">
+        <v>1</v>
+      </c>
+      <c r="L52" s="1">
         <f t="shared" si="3"/>
-        <v>75000</v>
-      </c>
-      <c r="M42" s="1">
-        <v>1</v>
-      </c>
-      <c r="N42" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:14">
-      <c r="C43" s="1">
+        <v>120000</v>
+      </c>
+      <c r="M52" s="1">
+        <v>1</v>
+      </c>
+      <c r="N52" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C53" s="1">
         <v>107</v>
       </c>
-      <c r="D43" s="1">
-        <v>1</v>
-      </c>
-      <c r="E43" s="1">
+      <c r="D53" s="1">
+        <v>1</v>
+      </c>
+      <c r="E53" s="1">
         <v>500</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F53" s="1">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I43" s="1">
-        <v>5</v>
-      </c>
-      <c r="J43" s="1">
+      <c r="G53" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I53" s="1">
+        <v>5</v>
+      </c>
+      <c r="J53" s="1">
         <v>4001</v>
       </c>
-      <c r="K43" s="1">
+      <c r="K53" s="1">
         <v>1000000</v>
       </c>
-      <c r="L43" s="1">
+      <c r="L53" s="1">
         <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="M43" s="1">
-        <v>1</v>
-      </c>
-      <c r="N43" s="1">
+      <c r="M53" s="1">
+        <v>1</v>
+      </c>
+      <c r="N53" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="3:14">
-      <c r="C44" s="1">
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C54" s="1">
         <v>108</v>
       </c>
-      <c r="D44" s="1">
-        <v>1</v>
-      </c>
-      <c r="E44" s="1">
+      <c r="D54" s="1">
+        <v>1</v>
+      </c>
+      <c r="E54" s="1">
         <v>500</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F54" s="1">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I44" s="1">
-        <v>5</v>
-      </c>
-      <c r="J44" s="1">
+      <c r="G54" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I54" s="1">
+        <v>5</v>
+      </c>
+      <c r="J54" s="1">
         <v>4002</v>
       </c>
-      <c r="K44" s="1">
+      <c r="K54" s="1">
         <v>6000000</v>
       </c>
-      <c r="L44" s="1">
+      <c r="L54" s="1">
         <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="M44" s="1">
-        <v>1</v>
-      </c>
-      <c r="N44" s="1">
+      <c r="M54" s="1">
+        <v>1</v>
+      </c>
+      <c r="N54" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="3:14">
-      <c r="C47" s="1">
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C55" s="1">
+        <v>109</v>
+      </c>
+      <c r="D55" s="1">
+        <v>1</v>
+      </c>
+      <c r="E55" s="1">
+        <v>30000</v>
+      </c>
+      <c r="F55" s="1">
+        <f>M55*N55</f>
+        <v>5</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I55" s="1">
+        <v>5</v>
+      </c>
+      <c r="J55" s="1">
+        <v>4026</v>
+      </c>
+      <c r="K55" s="1">
+        <v>1</v>
+      </c>
+      <c r="L55" s="1">
+        <f t="shared" si="3"/>
+        <v>150000</v>
+      </c>
+      <c r="M55" s="1">
+        <v>1</v>
+      </c>
+      <c r="N55" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C57" s="1">
+        <v>201</v>
+      </c>
+      <c r="D57" s="1">
+        <v>2</v>
+      </c>
+      <c r="E57" s="5">
+        <v>200</v>
+      </c>
+      <c r="F57" s="1">
+        <f t="shared" ref="F57:F64" si="4">M57*N57</f>
+        <v>300</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I57" s="1">
+        <v>5</v>
+      </c>
+      <c r="J57" s="1">
+        <v>4007</v>
+      </c>
+      <c r="K57" s="1">
+        <v>1000</v>
+      </c>
+      <c r="L57" s="1">
+        <f t="shared" ref="L57:L64" si="5">E57*F57</f>
+        <v>60000</v>
+      </c>
+      <c r="M57" s="1">
+        <v>1</v>
+      </c>
+      <c r="N57" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C58" s="1">
         <v>202</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D58" s="1">
         <v>2</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E58" s="5">
         <v>200</v>
       </c>
-      <c r="F47" s="1">
-        <f t="shared" ref="F47:F53" si="4">M47*N47</f>
-        <v>300</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I47" s="1">
-        <v>5</v>
-      </c>
-      <c r="J47" s="1">
-        <v>4007</v>
-      </c>
-      <c r="K47" s="1">
-        <v>1000</v>
-      </c>
-      <c r="L47" s="1">
-        <f t="shared" ref="L47:L53" si="5">E47*F47</f>
-        <v>60000</v>
-      </c>
-      <c r="M47" s="1">
-        <v>1</v>
-      </c>
-      <c r="N47" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:14">
-      <c r="C48" s="1">
-        <v>203</v>
-      </c>
-      <c r="D48" s="1">
-        <v>2</v>
-      </c>
-      <c r="E48" s="4">
-        <v>200</v>
-      </c>
-      <c r="F48" s="1">
+      <c r="F58" s="1">
         <f t="shared" si="4"/>
         <v>500</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I48" s="1">
-        <v>5</v>
-      </c>
-      <c r="J48" s="1">
+      <c r="G58" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I58" s="1">
+        <v>5</v>
+      </c>
+      <c r="J58" s="1">
         <v>4101</v>
       </c>
-      <c r="K48" s="1">
+      <c r="K58" s="1">
         <v>1000</v>
       </c>
-      <c r="L48" s="1">
+      <c r="L58" s="1">
         <f t="shared" si="5"/>
         <v>100000</v>
       </c>
-      <c r="M48" s="1">
-        <v>1</v>
-      </c>
-      <c r="N48" s="1">
+      <c r="M58" s="1">
+        <v>1</v>
+      </c>
+      <c r="N58" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="3:14">
-      <c r="C49" s="1">
-        <v>204</v>
-      </c>
-      <c r="D49" s="1">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C59" s="1">
+        <v>203</v>
+      </c>
+      <c r="D59" s="1">
         <v>2</v>
       </c>
-      <c r="E49" s="4">
+      <c r="E59" s="5">
         <v>2000</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F59" s="1">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I49" s="1">
+      <c r="G59" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I59" s="1">
         <v>15</v>
       </c>
-      <c r="J49" s="1">
+      <c r="J59" s="1">
         <v>4014</v>
       </c>
-      <c r="K49" s="1">
+      <c r="K59" s="1">
         <v>100</v>
       </c>
-      <c r="L49" s="1">
+      <c r="L59" s="1">
         <f t="shared" si="5"/>
         <v>12000</v>
       </c>
-      <c r="M49" s="1">
-        <v>1</v>
-      </c>
-      <c r="N49" s="1">
+      <c r="M59" s="1">
+        <v>1</v>
+      </c>
+      <c r="N59" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="3:14">
-      <c r="C50" s="1">
-        <v>205</v>
-      </c>
-      <c r="D50" s="1">
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C60" s="1">
+        <v>204</v>
+      </c>
+      <c r="D60" s="1">
         <v>2</v>
       </c>
-      <c r="E50" s="4">
+      <c r="E60" s="5">
         <v>1000</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F60" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I50" s="1">
-        <v>5</v>
-      </c>
-      <c r="J50" s="1">
+      <c r="G60" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I60" s="1">
+        <v>5</v>
+      </c>
+      <c r="J60" s="1">
         <v>4012</v>
       </c>
-      <c r="K50" s="1">
+      <c r="K60" s="1">
         <v>200</v>
       </c>
-      <c r="L50" s="1">
+      <c r="L60" s="1">
         <f t="shared" si="5"/>
         <v>20000</v>
       </c>
-      <c r="M50" s="1">
-        <v>1</v>
-      </c>
-      <c r="N50" s="1">
+      <c r="M60" s="1">
+        <v>1</v>
+      </c>
+      <c r="N60" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="3:14">
-      <c r="C51" s="1">
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C61" s="1">
+        <v>205</v>
+      </c>
+      <c r="D61" s="1">
+        <v>2</v>
+      </c>
+      <c r="E61" s="5">
+        <v>30000</v>
+      </c>
+      <c r="F61" s="1">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I61" s="1">
+        <v>5</v>
+      </c>
+      <c r="J61" s="1">
+        <v>4019</v>
+      </c>
+      <c r="K61" s="1">
+        <v>1</v>
+      </c>
+      <c r="L61" s="1">
+        <f t="shared" si="5"/>
+        <v>240000</v>
+      </c>
+      <c r="M61" s="1">
+        <v>1</v>
+      </c>
+      <c r="N61" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C62" s="1">
         <v>206</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D62" s="1">
         <v>2</v>
       </c>
-      <c r="E51" s="4">
+      <c r="E62" s="5">
+        <v>1000</v>
+      </c>
+      <c r="F62" s="1">
+        <f t="shared" si="4"/>
+        <v>40</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I62" s="1">
+        <v>5</v>
+      </c>
+      <c r="J62" s="1">
+        <v>4001</v>
+      </c>
+      <c r="K62" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="L62" s="1">
+        <f t="shared" si="5"/>
+        <v>40000</v>
+      </c>
+      <c r="M62" s="1">
+        <v>1</v>
+      </c>
+      <c r="N62" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C63" s="1">
+        <v>207</v>
+      </c>
+      <c r="D63" s="1">
+        <v>2</v>
+      </c>
+      <c r="E63" s="5">
+        <v>1000</v>
+      </c>
+      <c r="F63" s="1">
+        <f t="shared" si="4"/>
+        <v>40</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I63" s="1">
+        <v>5</v>
+      </c>
+      <c r="J63" s="1">
+        <v>4002</v>
+      </c>
+      <c r="K63" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="L63" s="1">
+        <f t="shared" si="5"/>
+        <v>40000</v>
+      </c>
+      <c r="M63" s="1">
+        <v>1</v>
+      </c>
+      <c r="N63" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C64" s="1">
+        <v>208</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1</v>
+      </c>
+      <c r="E64" s="1">
         <v>30000</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F64" s="1">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I51" s="1">
-        <v>5</v>
-      </c>
-      <c r="J51" s="1">
-        <v>4019</v>
-      </c>
-      <c r="K51" s="1">
-        <v>1</v>
-      </c>
-      <c r="L51" s="1">
+      <c r="G64" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I64" s="1">
+        <v>5</v>
+      </c>
+      <c r="J64" s="1">
+        <v>4026</v>
+      </c>
+      <c r="K64" s="1">
+        <v>1</v>
+      </c>
+      <c r="L64" s="1">
         <f t="shared" si="5"/>
         <v>150000</v>
       </c>
-      <c r="M51" s="1">
-        <v>1</v>
-      </c>
-      <c r="N51" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:14">
-      <c r="C52" s="1">
-        <v>207</v>
-      </c>
-      <c r="D52" s="1">
-        <v>2</v>
-      </c>
-      <c r="E52" s="4">
+      <c r="M64" s="1">
+        <v>1</v>
+      </c>
+      <c r="N64" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C66" s="1">
+        <v>211</v>
+      </c>
+      <c r="D66" s="1">
+        <v>3</v>
+      </c>
+      <c r="E66" s="1">
+        <v>400</v>
+      </c>
+      <c r="F66" s="1">
+        <f t="shared" ref="F66:F73" si="6">M66*N66</f>
+        <v>300</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I66" s="1">
+        <v>5</v>
+      </c>
+      <c r="J66" s="1">
+        <v>4007</v>
+      </c>
+      <c r="K66" s="1">
         <v>1000</v>
       </c>
-      <c r="F52" s="1">
-        <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I52" s="1">
-        <v>5</v>
-      </c>
-      <c r="J52" s="1">
-        <v>4001</v>
-      </c>
-      <c r="K52" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="L52" s="1">
-        <f t="shared" si="5"/>
-        <v>40000</v>
-      </c>
-      <c r="M52" s="1">
-        <v>1</v>
-      </c>
-      <c r="N52" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:14">
-      <c r="C53" s="1">
-        <v>208</v>
-      </c>
-      <c r="D53" s="1">
-        <v>2</v>
-      </c>
-      <c r="E53" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F53" s="1">
-        <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I53" s="1">
-        <v>5</v>
-      </c>
-      <c r="J53" s="1">
-        <v>4002</v>
-      </c>
-      <c r="K53" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="L53" s="1">
-        <f t="shared" si="5"/>
-        <v>40000</v>
-      </c>
-      <c r="M53" s="1">
-        <v>1</v>
-      </c>
-      <c r="N53" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:14">
-      <c r="C56" s="1">
-        <v>211</v>
-      </c>
-      <c r="D56" s="1">
+      <c r="L66" s="1">
+        <f t="shared" ref="L66:L73" si="7">E66*F66</f>
+        <v>120000</v>
+      </c>
+      <c r="M66" s="1">
+        <v>1</v>
+      </c>
+      <c r="N66" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C67" s="1">
+        <v>212</v>
+      </c>
+      <c r="D67" s="1">
         <v>3</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E67" s="1">
         <v>400</v>
       </c>
-      <c r="F56" s="1">
-        <f t="shared" ref="F56:F62" si="6">M56*N56</f>
-        <v>300</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I56" s="1">
-        <v>5</v>
-      </c>
-      <c r="J56" s="1">
-        <v>4007</v>
-      </c>
-      <c r="K56" s="1">
-        <v>1000</v>
-      </c>
-      <c r="L56" s="1">
-        <f t="shared" ref="L56:L62" si="7">E56*F56</f>
-        <v>120000</v>
-      </c>
-      <c r="M56" s="1">
-        <v>1</v>
-      </c>
-      <c r="N56" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:14">
-      <c r="C57" s="1">
-        <v>212</v>
-      </c>
-      <c r="D57" s="1">
-        <v>3</v>
-      </c>
-      <c r="E57" s="1">
-        <v>400</v>
-      </c>
-      <c r="F57" s="1">
+      <c r="F67" s="1">
         <f t="shared" si="6"/>
         <v>500</v>
       </c>
-      <c r="G57" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I57" s="1">
-        <v>5</v>
-      </c>
-      <c r="J57" s="1">
+      <c r="G67" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I67" s="1">
+        <v>5</v>
+      </c>
+      <c r="J67" s="1">
         <v>4101</v>
       </c>
-      <c r="K57" s="1">
+      <c r="K67" s="1">
         <v>1000</v>
       </c>
-      <c r="L57" s="1">
+      <c r="L67" s="1">
         <f t="shared" si="7"/>
         <v>200000</v>
       </c>
-      <c r="M57" s="1">
-        <v>1</v>
-      </c>
-      <c r="N57" s="1">
+      <c r="M67" s="1">
+        <v>1</v>
+      </c>
+      <c r="N67" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="3:14">
-      <c r="C58" s="1">
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C68" s="1">
         <v>213</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D68" s="1">
         <v>3</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E68" s="1">
         <v>4000</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F68" s="1">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I58" s="1">
+      <c r="G68" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I68" s="1">
         <v>15</v>
       </c>
-      <c r="J58" s="1">
+      <c r="J68" s="1">
         <v>4014</v>
       </c>
-      <c r="K58" s="1">
+      <c r="K68" s="1">
         <v>100</v>
       </c>
-      <c r="L58" s="1">
+      <c r="L68" s="1">
         <f t="shared" si="7"/>
         <v>24000</v>
       </c>
-      <c r="M58" s="1">
-        <v>1</v>
-      </c>
-      <c r="N58" s="1">
+      <c r="M68" s="1">
+        <v>1</v>
+      </c>
+      <c r="N68" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="3:14">
-      <c r="C59" s="1">
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C69" s="1">
         <v>214</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D69" s="1">
         <v>3</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E69" s="1">
         <v>2000</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F69" s="1">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="G59" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I59" s="1">
-        <v>5</v>
-      </c>
-      <c r="J59" s="1">
+      <c r="G69" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I69" s="1">
+        <v>5</v>
+      </c>
+      <c r="J69" s="1">
         <v>4012</v>
       </c>
-      <c r="K59" s="1">
+      <c r="K69" s="1">
         <v>200</v>
       </c>
-      <c r="L59" s="1">
+      <c r="L69" s="1">
         <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="M59" s="1">
-        <v>1</v>
-      </c>
-      <c r="N59" s="1">
+      <c r="M69" s="1">
+        <v>1</v>
+      </c>
+      <c r="N69" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="3:14">
-      <c r="C60" s="1">
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C70" s="1">
         <v>215</v>
       </c>
-      <c r="D60" s="1">
+      <c r="D70" s="1">
         <v>3</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E70" s="1">
         <v>45000</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F70" s="1">
         <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I60" s="1">
-        <v>5</v>
-      </c>
-      <c r="J60" s="1">
+        <v>8</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I70" s="1">
+        <v>5</v>
+      </c>
+      <c r="J70" s="1">
         <v>4019</v>
       </c>
-      <c r="K60" s="1">
-        <v>1</v>
-      </c>
-      <c r="L60" s="1">
+      <c r="K70" s="1">
+        <v>1</v>
+      </c>
+      <c r="L70" s="1">
         <f t="shared" si="7"/>
-        <v>225000</v>
-      </c>
-      <c r="M60" s="1">
-        <v>1</v>
-      </c>
-      <c r="N60" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:14">
-      <c r="C61" s="1">
+        <v>360000</v>
+      </c>
+      <c r="M70" s="1">
+        <v>1</v>
+      </c>
+      <c r="N70" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C71" s="1">
         <v>216</v>
       </c>
-      <c r="D61" s="1">
+      <c r="D71" s="1">
         <v>3</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E71" s="1">
         <v>2000</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F71" s="1">
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I61" s="1">
-        <v>5</v>
-      </c>
-      <c r="J61" s="1">
+      <c r="G71" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I71" s="1">
+        <v>5</v>
+      </c>
+      <c r="J71" s="1">
         <v>4001</v>
       </c>
-      <c r="K61" s="1">
+      <c r="K71" s="1">
         <v>1000000</v>
       </c>
-      <c r="L61" s="1">
+      <c r="L71" s="1">
         <f t="shared" si="7"/>
         <v>80000</v>
       </c>
-      <c r="M61" s="1">
-        <v>1</v>
-      </c>
-      <c r="N61" s="1">
+      <c r="M71" s="1">
+        <v>1</v>
+      </c>
+      <c r="N71" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="3:14">
-      <c r="C62" s="1">
+    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C72" s="1">
         <v>217</v>
       </c>
-      <c r="D62" s="1">
+      <c r="D72" s="1">
         <v>3</v>
       </c>
-      <c r="E62" s="1">
+      <c r="E72" s="1">
         <v>2000</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F72" s="1">
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I62" s="1">
-        <v>5</v>
-      </c>
-      <c r="J62" s="1">
+      <c r="G72" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I72" s="1">
+        <v>5</v>
+      </c>
+      <c r="J72" s="1">
         <v>4002</v>
       </c>
-      <c r="K62" s="1">
+      <c r="K72" s="1">
         <v>6000000</v>
       </c>
-      <c r="L62" s="1">
+      <c r="L72" s="1">
         <f t="shared" si="7"/>
         <v>80000</v>
       </c>
-      <c r="M62" s="1">
-        <v>1</v>
-      </c>
-      <c r="N62" s="1">
+      <c r="M72" s="1">
+        <v>1</v>
+      </c>
+      <c r="N72" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="3:14">
-      <c r="C65" s="1">
-        <v>220</v>
-      </c>
-      <c r="D65" s="1">
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C73" s="1">
+        <v>218</v>
+      </c>
+      <c r="D73" s="1">
+        <v>1</v>
+      </c>
+      <c r="E73" s="1">
+        <v>30000</v>
+      </c>
+      <c r="F73" s="1">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I73" s="1">
+        <v>5</v>
+      </c>
+      <c r="J73" s="1">
+        <v>4026</v>
+      </c>
+      <c r="K73" s="1">
+        <v>1</v>
+      </c>
+      <c r="L73" s="1">
+        <f t="shared" si="7"/>
+        <v>150000</v>
+      </c>
+      <c r="M73" s="1">
+        <v>1</v>
+      </c>
+      <c r="N73" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C75" s="1">
+        <v>221</v>
+      </c>
+      <c r="D75" s="1">
         <v>4</v>
       </c>
-      <c r="E65" s="4">
+      <c r="E75" s="5">
         <v>600</v>
       </c>
-      <c r="F65" s="1">
-        <f t="shared" ref="F65:F71" si="8">M65*N65</f>
+      <c r="F75" s="1">
+        <f t="shared" ref="F75:F82" si="8">M75*N75</f>
         <v>300</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I65" s="1">
-        <v>5</v>
-      </c>
-      <c r="J65" s="1">
+      <c r="G75" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I75" s="1">
+        <v>5</v>
+      </c>
+      <c r="J75" s="1">
         <v>4007</v>
       </c>
-      <c r="K65" s="1">
+      <c r="K75" s="1">
         <v>1000</v>
       </c>
-      <c r="L65" s="1">
-        <f t="shared" ref="L65:L71" si="9">E65*F65</f>
+      <c r="L75" s="1">
+        <f t="shared" ref="L75:L82" si="9">E75*F75</f>
         <v>180000</v>
       </c>
-      <c r="M65" s="1">
-        <v>1</v>
-      </c>
-      <c r="N65" s="1">
+      <c r="M75" s="1">
+        <v>1</v>
+      </c>
+      <c r="N75" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="3:14">
-      <c r="C66" s="1">
-        <v>221</v>
-      </c>
-      <c r="D66" s="1">
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C76" s="1">
+        <v>222</v>
+      </c>
+      <c r="D76" s="1">
         <v>4</v>
       </c>
-      <c r="E66" s="4">
+      <c r="E76" s="5">
         <v>600</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F76" s="1">
         <f t="shared" si="8"/>
         <v>500</v>
       </c>
-      <c r="G66" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I66" s="1">
-        <v>5</v>
-      </c>
-      <c r="J66" s="1">
+      <c r="G76" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I76" s="1">
+        <v>5</v>
+      </c>
+      <c r="J76" s="1">
         <v>4101</v>
       </c>
-      <c r="K66" s="1">
+      <c r="K76" s="1">
         <v>1000</v>
       </c>
-      <c r="L66" s="1">
+      <c r="L76" s="1">
         <f t="shared" si="9"/>
         <v>300000</v>
       </c>
-      <c r="M66" s="1">
-        <v>1</v>
-      </c>
-      <c r="N66" s="1">
+      <c r="M76" s="1">
+        <v>1</v>
+      </c>
+      <c r="N76" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="3:14">
-      <c r="C67" s="1">
-        <v>222</v>
-      </c>
-      <c r="D67" s="1">
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C77" s="1">
+        <v>223</v>
+      </c>
+      <c r="D77" s="1">
         <v>4</v>
       </c>
-      <c r="E67" s="4">
+      <c r="E77" s="5">
         <v>6000</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F77" s="1">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I67" s="1">
+      <c r="G77" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I77" s="1">
         <v>15</v>
       </c>
-      <c r="J67" s="1">
+      <c r="J77" s="1">
         <v>4014</v>
       </c>
-      <c r="K67" s="1">
+      <c r="K77" s="1">
         <v>100</v>
       </c>
-      <c r="L67" s="1">
+      <c r="L77" s="1">
         <f t="shared" si="9"/>
         <v>36000</v>
       </c>
-      <c r="M67" s="1">
-        <v>1</v>
-      </c>
-      <c r="N67" s="1">
+      <c r="M77" s="1">
+        <v>1</v>
+      </c>
+      <c r="N77" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="3:14">
-      <c r="C68" s="1">
-        <v>223</v>
-      </c>
-      <c r="D68" s="1">
+    <row r="78" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C78" s="1">
+        <v>224</v>
+      </c>
+      <c r="D78" s="1">
         <v>4</v>
       </c>
-      <c r="E68" s="4">
+      <c r="E78" s="5">
         <v>3000</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F78" s="1">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="G68" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I68" s="1">
-        <v>5</v>
-      </c>
-      <c r="J68" s="1">
+      <c r="G78" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I78" s="1">
+        <v>5</v>
+      </c>
+      <c r="J78" s="1">
         <v>4012</v>
       </c>
-      <c r="K68" s="1">
+      <c r="K78" s="1">
         <v>200</v>
       </c>
-      <c r="L68" s="1">
+      <c r="L78" s="1">
         <f t="shared" si="9"/>
         <v>60000</v>
       </c>
-      <c r="M68" s="1">
-        <v>1</v>
-      </c>
-      <c r="N68" s="1">
+      <c r="M78" s="1">
+        <v>1</v>
+      </c>
+      <c r="N78" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="3:14">
-      <c r="C69" s="1">
-        <v>224</v>
-      </c>
-      <c r="D69" s="1">
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C79" s="1">
+        <v>225</v>
+      </c>
+      <c r="D79" s="1">
         <v>4</v>
       </c>
-      <c r="E69" s="4">
+      <c r="E79" s="5">
         <v>60000</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F79" s="1">
         <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I69" s="1">
-        <v>5</v>
-      </c>
-      <c r="J69" s="1">
+        <v>8</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I79" s="1">
+        <v>5</v>
+      </c>
+      <c r="J79" s="1">
         <v>4019</v>
       </c>
-      <c r="K69" s="1">
-        <v>1</v>
-      </c>
-      <c r="L69" s="1">
+      <c r="K79" s="1">
+        <v>1</v>
+      </c>
+      <c r="L79" s="1">
         <f t="shared" si="9"/>
-        <v>300000</v>
-      </c>
-      <c r="M69" s="1">
-        <v>1</v>
-      </c>
-      <c r="N69" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:14">
-      <c r="C70" s="1">
-        <v>225</v>
-      </c>
-      <c r="D70" s="1">
+        <v>480000</v>
+      </c>
+      <c r="M79" s="1">
+        <v>1</v>
+      </c>
+      <c r="N79" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C80" s="1">
+        <v>226</v>
+      </c>
+      <c r="D80" s="1">
         <v>4</v>
       </c>
-      <c r="E70" s="4">
+      <c r="E80" s="5">
         <v>3000</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F80" s="1">
         <f t="shared" si="8"/>
         <v>40</v>
       </c>
-      <c r="G70" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I70" s="1">
-        <v>5</v>
-      </c>
-      <c r="J70" s="1">
+      <c r="G80" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I80" s="1">
+        <v>5</v>
+      </c>
+      <c r="J80" s="1">
         <v>4001</v>
       </c>
-      <c r="K70" s="1">
+      <c r="K80" s="1">
         <v>1000000</v>
       </c>
-      <c r="L70" s="1">
+      <c r="L80" s="1">
         <f t="shared" si="9"/>
         <v>120000</v>
       </c>
-      <c r="M70" s="1">
-        <v>1</v>
-      </c>
-      <c r="N70" s="1">
+      <c r="M80" s="1">
+        <v>1</v>
+      </c>
+      <c r="N80" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="71" customHeight="1" spans="3:14">
-      <c r="C71" s="1">
-        <v>226</v>
-      </c>
-      <c r="D71" s="1">
+    <row r="81" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C81" s="1">
+        <v>227</v>
+      </c>
+      <c r="D81" s="1">
         <v>4</v>
       </c>
-      <c r="E71" s="4">
+      <c r="E81" s="5">
         <v>3000</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F81" s="1">
         <f t="shared" si="8"/>
         <v>40</v>
       </c>
-      <c r="G71" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I71" s="1">
-        <v>5</v>
-      </c>
-      <c r="J71" s="1">
+      <c r="G81" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I81" s="1">
+        <v>5</v>
+      </c>
+      <c r="J81" s="1">
         <v>4002</v>
       </c>
-      <c r="K71" s="1">
+      <c r="K81" s="1">
         <v>6000000</v>
       </c>
-      <c r="L71" s="1">
+      <c r="L81" s="1">
         <f t="shared" si="9"/>
         <v>120000</v>
       </c>
-      <c r="M71" s="1">
-        <v>1</v>
-      </c>
-      <c r="N71" s="1">
+      <c r="M81" s="1">
+        <v>1</v>
+      </c>
+      <c r="N81" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="74" customHeight="1" spans="3:14">
-      <c r="C74" s="1">
-        <v>229</v>
-      </c>
-      <c r="D74" s="1">
-        <v>5</v>
-      </c>
-      <c r="E74" s="1">
+    <row r="82" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C82" s="1">
+        <v>228</v>
+      </c>
+      <c r="D82" s="1">
+        <v>1</v>
+      </c>
+      <c r="E82" s="1">
+        <v>30000</v>
+      </c>
+      <c r="F82" s="1">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I82" s="1">
+        <v>5</v>
+      </c>
+      <c r="J82" s="1">
+        <v>4026</v>
+      </c>
+      <c r="K82" s="1">
+        <v>1</v>
+      </c>
+      <c r="L82" s="1">
+        <f t="shared" si="9"/>
+        <v>150000</v>
+      </c>
+      <c r="M82" s="1">
+        <v>1</v>
+      </c>
+      <c r="N82" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C84" s="1">
+        <v>231</v>
+      </c>
+      <c r="D84" s="1">
+        <v>5</v>
+      </c>
+      <c r="E84" s="1">
         <v>800</v>
       </c>
-      <c r="F74" s="1">
-        <f t="shared" ref="F74:F80" si="10">M74*N74</f>
+      <c r="F84" s="1">
+        <f t="shared" ref="F84:F91" si="10">M84*N84</f>
         <v>1200</v>
       </c>
-      <c r="G74" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I74" s="1">
-        <v>5</v>
-      </c>
-      <c r="J74" s="1">
+      <c r="G84" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I84" s="1">
+        <v>5</v>
+      </c>
+      <c r="J84" s="1">
         <v>4007</v>
       </c>
-      <c r="K74" s="1">
+      <c r="K84" s="1">
         <v>1000</v>
       </c>
-      <c r="L74" s="1">
-        <f t="shared" ref="L74:L80" si="11">E74*F74</f>
+      <c r="L84" s="1">
+        <f t="shared" ref="L84:L91" si="11">E84*F84</f>
         <v>960000</v>
       </c>
-      <c r="M74" s="1">
+      <c r="M84" s="1">
         <v>4</v>
       </c>
-      <c r="N74" s="1">
+      <c r="N84" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="3:14">
-      <c r="C75" s="1">
-        <v>230</v>
-      </c>
-      <c r="D75" s="1">
-        <v>5</v>
-      </c>
-      <c r="E75" s="1">
+    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C85" s="1">
+        <v>232</v>
+      </c>
+      <c r="D85" s="1">
+        <v>5</v>
+      </c>
+      <c r="E85" s="1">
         <v>800</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F85" s="1">
         <f t="shared" si="10"/>
         <v>2000</v>
       </c>
-      <c r="G75" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I75" s="1">
-        <v>5</v>
-      </c>
-      <c r="J75" s="1">
+      <c r="G85" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I85" s="1">
+        <v>5</v>
+      </c>
+      <c r="J85" s="1">
         <v>4101</v>
       </c>
-      <c r="K75" s="1">
+      <c r="K85" s="1">
         <v>1000</v>
       </c>
-      <c r="L75" s="1">
+      <c r="L85" s="1">
         <f t="shared" si="11"/>
         <v>1600000</v>
       </c>
-      <c r="M75" s="1">
+      <c r="M85" s="1">
         <v>4</v>
       </c>
-      <c r="N75" s="1">
+      <c r="N85" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="3:14">
-      <c r="C76" s="1">
-        <v>231</v>
-      </c>
-      <c r="D76" s="1">
-        <v>5</v>
-      </c>
-      <c r="E76" s="1">
+    <row r="86" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C86" s="1">
+        <v>233</v>
+      </c>
+      <c r="D86" s="1">
+        <v>5</v>
+      </c>
+      <c r="E86" s="1">
         <v>8000</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F86" s="1">
         <f t="shared" si="10"/>
         <v>24</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I76" s="1">
+      <c r="G86" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I86" s="1">
         <v>15</v>
       </c>
-      <c r="J76" s="1">
+      <c r="J86" s="1">
         <v>4014</v>
       </c>
-      <c r="K76" s="1">
+      <c r="K86" s="1">
         <v>100</v>
       </c>
-      <c r="L76" s="1">
+      <c r="L86" s="1">
         <f t="shared" si="11"/>
         <v>192000</v>
       </c>
-      <c r="M76" s="1">
+      <c r="M86" s="1">
         <v>4</v>
       </c>
-      <c r="N76" s="1">
+      <c r="N86" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="3:14">
-      <c r="C77" s="1">
-        <v>232</v>
-      </c>
-      <c r="D77" s="1">
-        <v>5</v>
-      </c>
-      <c r="E77" s="1">
+    <row r="87" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C87" s="1">
+        <v>234</v>
+      </c>
+      <c r="D87" s="1">
+        <v>5</v>
+      </c>
+      <c r="E87" s="1">
         <v>4000</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F87" s="1">
         <f t="shared" si="10"/>
         <v>80</v>
       </c>
-      <c r="G77" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I77" s="1">
-        <v>5</v>
-      </c>
-      <c r="J77" s="1">
+      <c r="G87" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I87" s="1">
+        <v>5</v>
+      </c>
+      <c r="J87" s="1">
         <v>4012</v>
       </c>
-      <c r="K77" s="1">
+      <c r="K87" s="1">
         <v>200</v>
       </c>
-      <c r="L77" s="1">
+      <c r="L87" s="1">
         <f t="shared" si="11"/>
         <v>320000</v>
       </c>
-      <c r="M77" s="1">
+      <c r="M87" s="1">
         <v>4</v>
       </c>
-      <c r="N77" s="1">
+      <c r="N87" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="3:14">
-      <c r="C78" s="1">
-        <v>233</v>
-      </c>
-      <c r="D78" s="1">
-        <v>5</v>
-      </c>
-      <c r="E78" s="1">
+    <row r="88" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C88" s="1">
+        <v>235</v>
+      </c>
+      <c r="D88" s="1">
+        <v>5</v>
+      </c>
+      <c r="E88" s="1">
         <v>75000</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F88" s="1">
         <f t="shared" si="10"/>
-        <v>20</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I78" s="1">
-        <v>5</v>
-      </c>
-      <c r="J78" s="1">
+        <v>32</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I88" s="1">
+        <v>5</v>
+      </c>
+      <c r="J88" s="1">
         <v>4019</v>
       </c>
-      <c r="K78" s="1">
-        <v>1</v>
-      </c>
-      <c r="L78" s="1">
+      <c r="K88" s="1">
+        <v>1</v>
+      </c>
+      <c r="L88" s="1">
         <f t="shared" si="11"/>
-        <v>1500000</v>
-      </c>
-      <c r="M78" s="1">
+        <v>2400000</v>
+      </c>
+      <c r="M88" s="1">
         <v>4</v>
       </c>
-      <c r="N78" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79" customHeight="1" spans="3:14">
-      <c r="C79" s="1">
-        <v>234</v>
-      </c>
-      <c r="D79" s="1">
-        <v>5</v>
-      </c>
-      <c r="E79" s="1">
+      <c r="N88" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C89" s="1">
+        <v>236</v>
+      </c>
+      <c r="D89" s="1">
+        <v>5</v>
+      </c>
+      <c r="E89" s="1">
         <v>4000</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F89" s="1">
         <f t="shared" si="10"/>
         <v>160</v>
       </c>
-      <c r="G79" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I79" s="1">
-        <v>5</v>
-      </c>
-      <c r="J79" s="1">
+      <c r="G89" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I89" s="1">
+        <v>5</v>
+      </c>
+      <c r="J89" s="1">
         <v>4001</v>
       </c>
-      <c r="K79" s="1">
+      <c r="K89" s="1">
         <v>1000000</v>
       </c>
-      <c r="L79" s="1">
+      <c r="L89" s="1">
         <f t="shared" si="11"/>
         <v>640000</v>
       </c>
-      <c r="M79" s="1">
+      <c r="M89" s="1">
         <v>4</v>
       </c>
-      <c r="N79" s="1">
+      <c r="N89" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="80" customHeight="1" spans="3:14">
-      <c r="C80" s="1">
-        <v>235</v>
-      </c>
-      <c r="D80" s="1">
-        <v>5</v>
-      </c>
-      <c r="E80" s="1">
+    <row r="90" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C90" s="1">
+        <v>237</v>
+      </c>
+      <c r="D90" s="1">
+        <v>5</v>
+      </c>
+      <c r="E90" s="1">
         <v>4000</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F90" s="1">
         <f t="shared" si="10"/>
         <v>160</v>
       </c>
-      <c r="G80" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I80" s="1">
-        <v>5</v>
-      </c>
-      <c r="J80" s="1">
+      <c r="G90" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I90" s="1">
+        <v>5</v>
+      </c>
+      <c r="J90" s="1">
         <v>4002</v>
       </c>
-      <c r="K80" s="1">
+      <c r="K90" s="1">
         <v>6000000</v>
       </c>
-      <c r="L80" s="1">
+      <c r="L90" s="1">
         <f t="shared" si="11"/>
         <v>640000</v>
       </c>
-      <c r="M80" s="1">
+      <c r="M90" s="1">
         <v>4</v>
       </c>
-      <c r="N80" s="1">
+      <c r="N90" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="83" customHeight="1" spans="3:12">
-      <c r="C83" s="1">
+    <row r="91" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C91" s="1">
+        <v>238</v>
+      </c>
+      <c r="D91" s="1">
+        <v>1</v>
+      </c>
+      <c r="E91" s="1">
+        <v>30000</v>
+      </c>
+      <c r="F91" s="1">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I91" s="1">
+        <v>5</v>
+      </c>
+      <c r="J91" s="1">
+        <v>4026</v>
+      </c>
+      <c r="K91" s="1">
+        <v>1</v>
+      </c>
+      <c r="L91" s="1">
+        <f t="shared" si="11"/>
+        <v>150000</v>
+      </c>
+      <c r="M91" s="1">
+        <v>1</v>
+      </c>
+      <c r="N91" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C93" s="1">
         <v>999</v>
       </c>
-      <c r="D83" s="1">
+      <c r="D93" s="1">
         <v>0</v>
       </c>
-      <c r="E83" s="1">
+      <c r="E93" s="1">
         <v>1000</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F93" s="1">
         <v>50</v>
       </c>
-      <c r="G83" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I83" s="1">
-        <v>5</v>
-      </c>
-      <c r="J83" s="1">
+      <c r="G93" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I93" s="1">
+        <v>5</v>
+      </c>
+      <c r="J93" s="1">
         <v>4006</v>
       </c>
-      <c r="K83" s="1">
+      <c r="K93" s="1">
         <v>1000</v>
       </c>
-      <c r="L83" s="1">
-        <f>E83*F83</f>
+      <c r="L93" s="1">
+        <f t="shared" ref="L93:L95" si="12">E93*F93</f>
         <v>50000</v>
       </c>
     </row>
-    <row r="84" customHeight="1" spans="3:12">
-      <c r="C84" s="1">
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C94" s="1">
         <v>1000</v>
       </c>
-      <c r="D84" s="1">
+      <c r="D94" s="1">
         <v>0</v>
       </c>
-      <c r="E84" s="1">
+      <c r="E94" s="1">
         <v>2000</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F94" s="1">
         <v>100</v>
       </c>
-      <c r="G84" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I84" s="1">
-        <v>5</v>
-      </c>
-      <c r="J84" s="1">
+      <c r="G94" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I94" s="1">
+        <v>5</v>
+      </c>
+      <c r="J94" s="1">
         <v>4010</v>
       </c>
-      <c r="K84" s="1">
-        <v>5</v>
-      </c>
-      <c r="L84" s="1">
-        <f>E84*F84</f>
+      <c r="K94" s="1">
+        <v>5</v>
+      </c>
+      <c r="L94" s="1">
+        <f t="shared" si="12"/>
         <v>200000</v>
       </c>
     </row>
-    <row r="85" customHeight="1" spans="3:12">
-      <c r="C85" s="1">
+    <row r="95" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C95" s="1">
         <v>1001</v>
       </c>
-      <c r="D85" s="1">
+      <c r="D95" s="1">
         <v>0</v>
       </c>
-      <c r="E85" s="1">
+      <c r="E95" s="1">
         <v>2000</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F95" s="1">
         <v>50</v>
       </c>
-      <c r="G85" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I85" s="1">
-        <v>5</v>
-      </c>
-      <c r="J85" s="1">
+      <c r="G95" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I95" s="1">
+        <v>5</v>
+      </c>
+      <c r="J95" s="1">
         <v>4102</v>
       </c>
-      <c r="K85" s="1">
+      <c r="K95" s="1">
         <v>20</v>
       </c>
-      <c r="L85" s="1">
-        <f>E85*F85</f>
+      <c r="L95" s="1">
+        <f t="shared" si="12"/>
         <v>100000</v>
       </c>
     </row>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="125">
   <si>
     <t>#</t>
   </si>
@@ -381,6 +381,9 @@
   </si>
   <si>
     <t>兑换暗金精华*1</t>
+  </si>
+  <si>
+    <t>暗金精华</t>
   </si>
   <si>
     <t>兑换书页1000个</t>
@@ -1419,11 +1422,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="11.2545454545455" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.2583333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="7" width="22.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1272727272727" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.8727272727273" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.875" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.5" style="1" customWidth="1"/>
     <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
@@ -3176,14 +3179,14 @@
         <v>30000</v>
       </c>
       <c r="F55" s="1">
-        <f>M55*N55</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>117</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I55" s="1">
         <v>5</v>
@@ -3490,7 +3493,7 @@
         <v>208</v>
       </c>
       <c r="D64" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" s="1">
         <v>30000</v>
@@ -3503,7 +3506,7 @@
         <v>117</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I64" s="1">
         <v>5</v>
@@ -3810,7 +3813,7 @@
         <v>218</v>
       </c>
       <c r="D73" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E73" s="1">
         <v>30000</v>
@@ -3823,7 +3826,7 @@
         <v>117</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I73" s="1">
         <v>5</v>
@@ -4130,7 +4133,7 @@
         <v>228</v>
       </c>
       <c r="D82" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82" s="1">
         <v>30000</v>
@@ -4143,7 +4146,7 @@
         <v>117</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I82" s="1">
         <v>5</v>
@@ -4450,7 +4453,7 @@
         <v>238</v>
       </c>
       <c r="D91" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E91" s="1">
         <v>30000</v>
@@ -4463,7 +4466,7 @@
         <v>117</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I91" s="1">
         <v>5</v>
@@ -4499,10 +4502,10 @@
         <v>50</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I93" s="1">
         <v>5</v>
@@ -4532,10 +4535,10 @@
         <v>100</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I94" s="1">
         <v>5</v>
@@ -4565,10 +4568,10 @@
         <v>50</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I95" s="1">
         <v>5</v>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="126">
   <si>
     <t>#</t>
   </si>
@@ -36,6 +36,9 @@
   </si>
   <si>
     <t>Step</t>
+  </si>
+  <si>
+    <t>RequireCycle</t>
   </si>
   <si>
     <t>Cost</t>
@@ -1418,33 +1421,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N95"/>
+  <dimension ref="C1:O95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="11.2583333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="15.3636363636364" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.2545454545455" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1272727272727" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.8727272727273" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="12:12">
-      <c r="L1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="1" customHeight="1" spans="13:13">
+      <c r="M1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
@@ -1453,7 +1457,7 @@
       <c r="G3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -1465,15 +1469,18 @@
       <c r="K3" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -1482,7 +1489,7 @@
       <c r="G4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -1494,895 +1501,979 @@
       <c r="K4" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="K5" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:12">
+        <v>11</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:13">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="1">
         <v>168</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="1">
         <v>9</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>4003</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>100</v>
       </c>
-      <c r="L6" s="1">
-        <f t="shared" ref="L6:L9" si="0">E6*F6</f>
+      <c r="M6" s="1">
+        <f t="shared" ref="M6:M9" si="0">F6*G6</f>
         <v>50400</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:12">
+    <row r="7" customHeight="1" spans="3:13">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="1">
         <v>168</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="1">
-        <v>5</v>
+      <c r="I7" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="J7" s="1">
+        <v>5</v>
+      </c>
+      <c r="K7" s="1">
         <v>4004</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>10</v>
       </c>
-      <c r="L7" s="1">
+      <c r="M7" s="1">
         <f t="shared" si="0"/>
         <v>50400</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="1">
         <v>168</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="1">
         <v>9</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>4013</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>4</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <f t="shared" si="0"/>
         <v>50400</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="3:12">
+    <row r="9" customHeight="1" spans="3:13">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="1">
         <v>66</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="1">
-        <v>5</v>
+      <c r="I9" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="J9" s="1">
+        <v>5</v>
+      </c>
+      <c r="K9" s="1">
         <v>4008</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>10</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="1">
         <f t="shared" si="0"/>
         <v>33000</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="3:12">
+    <row r="10" customHeight="1" spans="3:13">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="1">
         <v>200</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="1">
         <v>4</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>10</v>
       </c>
-      <c r="K10" s="1">
-        <v>1</v>
-      </c>
       <c r="L10" s="1">
-        <f t="shared" ref="L10:L45" si="1">E10*F10</f>
+        <v>1</v>
+      </c>
+      <c r="M10" s="1">
+        <f t="shared" ref="M10:M45" si="1">F10*G10</f>
         <v>60000</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:12">
+    <row r="11" customHeight="1" spans="3:13">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="1">
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="1">
         <v>200</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="1">
         <v>4</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>11</v>
       </c>
-      <c r="K11" s="1">
-        <v>1</v>
-      </c>
       <c r="L11" s="1">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1">
         <f t="shared" si="1"/>
         <v>60000</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:12">
+    <row r="12" customHeight="1" spans="3:13">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="1">
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="1">
         <v>200</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="1">
         <v>4</v>
       </c>
-      <c r="J12" s="1">
+      <c r="K12" s="1">
         <v>12</v>
       </c>
-      <c r="K12" s="1">
-        <v>1</v>
-      </c>
       <c r="L12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1">
         <f t="shared" si="1"/>
         <v>60000</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:12">
+    <row r="13" customHeight="1" spans="3:13">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="1">
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="1">
         <v>200</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="1">
         <v>4</v>
       </c>
-      <c r="J13" s="6">
+      <c r="K13" s="6">
         <v>15</v>
       </c>
-      <c r="K13" s="1">
-        <v>1</v>
-      </c>
       <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
         <f t="shared" si="1"/>
         <v>100000</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:12">
+    <row r="14" customHeight="1" spans="3:13">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="1">
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="1">
         <v>200</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I14" s="1">
+      <c r="I14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" s="1">
         <v>4</v>
       </c>
-      <c r="J14" s="6">
+      <c r="K14" s="6">
         <v>16</v>
       </c>
-      <c r="K14" s="1">
-        <v>1</v>
-      </c>
       <c r="L14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1">
         <f t="shared" si="1"/>
         <v>100000</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:12">
+    <row r="15" customHeight="1" spans="3:13">
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="1">
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="1">
         <v>200</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I15" s="1">
+      <c r="I15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J15" s="1">
         <v>4</v>
       </c>
-      <c r="J15" s="6">
+      <c r="K15" s="6">
         <v>17</v>
       </c>
-      <c r="K15" s="1">
-        <v>1</v>
-      </c>
       <c r="L15" s="1">
+        <v>1</v>
+      </c>
+      <c r="M15" s="1">
         <f t="shared" si="1"/>
         <v>100000</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:12">
+    <row r="16" customHeight="1" spans="3:13">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="1">
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="1">
         <v>100</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J16" s="1">
         <v>11</v>
       </c>
-      <c r="J16" s="1">
+      <c r="K16" s="1">
         <v>1999995</v>
       </c>
-      <c r="K16" s="1">
-        <v>1</v>
-      </c>
       <c r="L16" s="1">
+        <v>1</v>
+      </c>
+      <c r="M16" s="1">
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="3:12">
+    <row r="17" customHeight="1" spans="3:13">
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="1">
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="1">
         <v>100</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J17" s="1">
         <v>11</v>
       </c>
-      <c r="J17" s="1">
+      <c r="K17" s="1">
         <v>1999996</v>
       </c>
-      <c r="K17" s="1">
-        <v>1</v>
-      </c>
       <c r="L17" s="1">
+        <v>1</v>
+      </c>
+      <c r="M17" s="1">
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="3:12">
+    <row r="18" customHeight="1" spans="3:13">
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="1">
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="1">
         <v>100</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J18" s="1">
         <v>11</v>
       </c>
-      <c r="J18" s="1">
+      <c r="K18" s="1">
         <v>1999997</v>
       </c>
-      <c r="K18" s="1">
-        <v>1</v>
-      </c>
       <c r="L18" s="1">
+        <v>1</v>
+      </c>
+      <c r="M18" s="1">
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="3:12">
+    <row r="19" customHeight="1" spans="3:13">
       <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="1">
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="1">
         <v>100</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I19" s="1">
+      <c r="I19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J19" s="1">
         <v>11</v>
       </c>
-      <c r="J19" s="1">
+      <c r="K19" s="1">
         <v>1999994</v>
       </c>
-      <c r="K19" s="1">
-        <v>1</v>
-      </c>
       <c r="L19" s="1">
+        <v>1</v>
+      </c>
+      <c r="M19" s="1">
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="3:12">
+    <row r="20" customHeight="1" spans="3:13">
       <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="1">
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="1">
         <v>100</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" s="1">
         <v>11</v>
       </c>
-      <c r="J20" s="1">
+      <c r="K20" s="1">
         <v>1999993</v>
       </c>
-      <c r="K20" s="1">
-        <v>1</v>
-      </c>
       <c r="L20" s="1">
+        <v>1</v>
+      </c>
+      <c r="M20" s="1">
         <f t="shared" si="1"/>
         <v>30000</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="3:12">
+    <row r="21" customHeight="1" spans="3:13">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1</v>
-      </c>
-      <c r="G21" s="1" t="s">
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>45</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J21" s="1">
         <v>4</v>
       </c>
-      <c r="J21" s="1">
+      <c r="K21" s="1">
         <v>13</v>
       </c>
-      <c r="K21" s="1">
-        <v>1</v>
-      </c>
       <c r="L21" s="1">
+        <v>1</v>
+      </c>
+      <c r="M21" s="1">
         <f t="shared" si="1"/>
         <v>2000</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="3:12">
+    <row r="22" customHeight="1" spans="3:13">
       <c r="C22" s="1">
         <v>17</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>47</v>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I22" s="1">
+      <c r="I22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J22" s="1">
         <v>4</v>
       </c>
-      <c r="J22" s="1">
+      <c r="K22" s="1">
         <v>8</v>
       </c>
-      <c r="K22" s="1">
-        <v>1</v>
-      </c>
       <c r="L22" s="1">
+        <v>1</v>
+      </c>
+      <c r="M22" s="1">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="3:12">
+    <row r="23" customHeight="1" spans="3:13">
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1" t="s">
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>50</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="1">
+      <c r="I23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J23" s="1">
         <v>4</v>
       </c>
-      <c r="J23" s="1">
+      <c r="K23" s="1">
         <v>9</v>
       </c>
-      <c r="K23" s="1">
-        <v>1</v>
-      </c>
       <c r="L23" s="1">
+        <v>1</v>
+      </c>
+      <c r="M23" s="1">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="3:12">
+    <row r="24" customHeight="1" spans="3:13">
       <c r="C24" s="1">
         <v>19</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="F24" s="1">
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="1">
         <v>10</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I24" s="1">
+      <c r="I24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J24" s="1">
         <v>4</v>
       </c>
-      <c r="J24" s="1">
+      <c r="K24" s="1">
         <v>22</v>
       </c>
-      <c r="K24" s="1">
-        <v>1</v>
-      </c>
       <c r="L24" s="1">
+        <v>1</v>
+      </c>
+      <c r="M24" s="1">
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="3:12">
+    <row r="25" customHeight="1" spans="3:13">
       <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="F25" s="1">
-        <v>5</v>
-      </c>
-      <c r="G25" s="1" t="s">
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>56</v>
+      </c>
+      <c r="G25" s="1">
+        <v>5</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J25" s="1">
         <v>4</v>
       </c>
-      <c r="J25" s="1">
+      <c r="K25" s="1">
         <v>26</v>
       </c>
-      <c r="K25" s="1">
-        <v>1</v>
-      </c>
       <c r="L25" s="1">
+        <v>1</v>
+      </c>
+      <c r="M25" s="1">
         <f t="shared" si="1"/>
         <v>250000</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="3:12">
+    <row r="26" customHeight="1" spans="3:13">
       <c r="C26" s="1">
         <v>21</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="F26" s="1">
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" s="1">
         <v>2</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I26" s="1">
+      <c r="I26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J26" s="1">
         <v>4</v>
       </c>
-      <c r="J26" s="1">
+      <c r="K26" s="1">
         <v>25</v>
       </c>
-      <c r="K26" s="1">
-        <v>1</v>
-      </c>
       <c r="L26" s="1">
+        <v>1</v>
+      </c>
+      <c r="M26" s="1">
         <f t="shared" si="1"/>
         <v>400000</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="3:12">
+    <row r="27" customHeight="1" spans="3:13">
       <c r="C27" s="1">
         <v>22</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F27" s="1">
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G27" s="1">
         <v>6</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I27" s="1">
+      <c r="I27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J27" s="1">
         <v>4</v>
       </c>
-      <c r="J27" s="1">
+      <c r="K27" s="1">
         <v>28</v>
       </c>
-      <c r="K27" s="1">
-        <v>1</v>
-      </c>
       <c r="L27" s="1">
+        <v>1</v>
+      </c>
+      <c r="M27" s="1">
         <f t="shared" si="1"/>
         <v>1800000</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="3:12">
+    <row r="28" customHeight="1" spans="3:13">
       <c r="C28" s="1">
         <v>23</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F28" s="1">
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" s="1">
         <v>3</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I28" s="1">
+      <c r="I28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J28" s="1">
         <v>4</v>
       </c>
-      <c r="J28" s="1">
+      <c r="K28" s="1">
         <v>30</v>
       </c>
-      <c r="K28" s="1">
-        <v>1</v>
-      </c>
       <c r="L28" s="1">
+        <v>1</v>
+      </c>
+      <c r="M28" s="1">
         <f t="shared" si="1"/>
         <v>1200000</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="3:12">
+    <row r="29" customHeight="1" spans="3:13">
       <c r="C29" s="1">
         <v>24</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
-      <c r="E29" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F29" s="1">
+      <c r="E29" s="1">
+        <v>0</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="1">
         <v>2</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="I29" s="1">
+      <c r="I29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J29" s="1">
         <v>4</v>
       </c>
-      <c r="J29" s="1">
+      <c r="K29" s="1">
         <v>31</v>
       </c>
-      <c r="K29" s="1">
-        <v>1</v>
-      </c>
       <c r="L29" s="1">
+        <v>1</v>
+      </c>
+      <c r="M29" s="1">
         <f t="shared" si="1"/>
         <v>1000000</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="3:12">
+    <row r="30" customHeight="1" spans="3:13">
       <c r="C30" s="1">
         <v>25</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F30" s="1">
+      <c r="E30" s="1">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="1">
         <v>400</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I30" s="1">
-        <v>5</v>
+      <c r="I30" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="J30" s="1">
+        <v>5</v>
+      </c>
+      <c r="K30" s="1">
         <v>4021</v>
       </c>
-      <c r="K30" s="1">
-        <v>1</v>
-      </c>
       <c r="L30" s="1">
+        <v>1</v>
+      </c>
+      <c r="M30" s="1">
         <f t="shared" si="1"/>
         <v>2000000</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="3:12">
+    <row r="31" customHeight="1" spans="3:13">
       <c r="C31" s="1">
         <v>26</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F31" s="1">
+      <c r="E31" s="1">
+        <v>0</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="1">
         <v>200</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I31" s="1">
-        <v>5</v>
+      <c r="I31" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="J31" s="1">
+        <v>5</v>
+      </c>
+      <c r="K31" s="1">
         <v>4022</v>
       </c>
-      <c r="K31" s="1">
+      <c r="L31" s="1">
         <v>100</v>
       </c>
-      <c r="L31" s="1">
+      <c r="M31" s="1">
         <f t="shared" si="1"/>
         <v>1000000</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="3:12">
+    <row r="32" customHeight="1" spans="3:13">
       <c r="C32" s="1">
         <v>27</v>
       </c>
@@ -2390,32 +2481,35 @@
         <v>0</v>
       </c>
       <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="F32" s="1">
         <v>3000</v>
       </c>
-      <c r="F32" s="1">
+      <c r="G32" s="1">
         <v>100</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="I32" s="1">
-        <v>5</v>
+      <c r="I32" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="J32" s="1">
+        <v>5</v>
+      </c>
+      <c r="K32" s="1">
         <v>4011</v>
       </c>
-      <c r="K32" s="1">
-        <v>1</v>
-      </c>
       <c r="L32" s="1">
+        <v>1</v>
+      </c>
+      <c r="M32" s="1">
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="3:12">
+    <row r="33" customHeight="1" spans="3:13">
       <c r="C33" s="1">
         <v>28</v>
       </c>
@@ -2423,32 +2517,35 @@
         <v>0</v>
       </c>
       <c r="E33" s="1">
+        <v>0</v>
+      </c>
+      <c r="F33" s="1">
         <v>20000</v>
       </c>
-      <c r="F33" s="1">
+      <c r="G33" s="1">
         <v>40</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I33" s="1">
-        <v>5</v>
+      <c r="I33" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="J33" s="1">
+        <v>5</v>
+      </c>
+      <c r="K33" s="1">
         <v>4020</v>
       </c>
-      <c r="K33" s="1">
-        <v>1</v>
-      </c>
       <c r="L33" s="1">
+        <v>1</v>
+      </c>
+      <c r="M33" s="1">
         <f t="shared" si="1"/>
         <v>800000</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C34" s="1">
         <v>29</v>
       </c>
@@ -2456,32 +2553,35 @@
         <v>0</v>
       </c>
       <c r="E34" s="1">
+        <v>0</v>
+      </c>
+      <c r="F34" s="1">
         <v>488888</v>
       </c>
-      <c r="F34" s="1">
-        <v>1</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>79</v>
+      <c r="G34" s="1">
+        <v>1</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I34" s="1">
+      <c r="I34" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="J34" s="1">
         <v>4</v>
       </c>
-      <c r="J34" s="1">
+      <c r="K34" s="1">
         <v>204</v>
       </c>
-      <c r="K34" s="1">
-        <v>1</v>
-      </c>
       <c r="L34" s="1">
+        <v>1</v>
+      </c>
+      <c r="M34" s="1">
         <f t="shared" si="1"/>
         <v>488888</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C35" s="1">
         <v>30</v>
       </c>
@@ -2489,32 +2589,35 @@
         <v>0</v>
       </c>
       <c r="E35" s="1">
+        <v>4</v>
+      </c>
+      <c r="F35" s="1">
         <v>600000</v>
       </c>
-      <c r="F35" s="1">
-        <v>1</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>81</v>
+      <c r="G35" s="1">
+        <v>1</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I35" s="1">
-        <v>5</v>
+      <c r="I35" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="J35" s="1">
+        <v>5</v>
+      </c>
+      <c r="K35" s="1">
         <v>4027</v>
       </c>
-      <c r="K35" s="1">
-        <v>1</v>
-      </c>
       <c r="L35" s="1">
+        <v>1</v>
+      </c>
+      <c r="M35" s="1">
         <f t="shared" si="1"/>
         <v>600000</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="3:12">
+    <row r="36" customHeight="1" spans="3:13">
       <c r="C36" s="1">
         <v>31</v>
       </c>
@@ -2522,32 +2625,35 @@
         <v>0</v>
       </c>
       <c r="E36" s="1">
+        <v>4</v>
+      </c>
+      <c r="F36" s="1">
         <v>20000</v>
       </c>
-      <c r="F36" s="1">
+      <c r="G36" s="1">
         <v>15</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="I36" s="1">
-        <v>5</v>
-      </c>
-      <c r="J36" s="6">
+      <c r="I36" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J36" s="1">
+        <v>5</v>
+      </c>
+      <c r="K36" s="6">
         <v>60000001</v>
       </c>
-      <c r="K36" s="1">
-        <v>1</v>
-      </c>
       <c r="L36" s="1">
+        <v>1</v>
+      </c>
+      <c r="M36" s="1">
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="3:12">
+    <row r="37" customHeight="1" spans="3:13">
       <c r="C37" s="1">
         <v>32</v>
       </c>
@@ -2555,32 +2661,35 @@
         <v>0</v>
       </c>
       <c r="E37" s="1">
+        <v>4</v>
+      </c>
+      <c r="F37" s="1">
         <v>15000</v>
       </c>
-      <c r="F37" s="1">
+      <c r="G37" s="1">
         <v>20</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I37" s="1">
-        <v>5</v>
-      </c>
-      <c r="J37" s="6">
+      <c r="I37" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J37" s="1">
+        <v>5</v>
+      </c>
+      <c r="K37" s="6">
         <v>60000002</v>
       </c>
-      <c r="K37" s="1">
-        <v>1</v>
-      </c>
       <c r="L37" s="1">
+        <v>1</v>
+      </c>
+      <c r="M37" s="1">
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
     </row>
-    <row r="38" customFormat="1" customHeight="1" spans="3:14">
+    <row r="38" customFormat="1" customHeight="1" spans="3:15">
       <c r="C38" s="1">
         <v>33</v>
       </c>
@@ -2588,34 +2697,37 @@
         <v>0</v>
       </c>
       <c r="E38" s="1">
+        <v>4</v>
+      </c>
+      <c r="F38" s="1">
         <v>15000</v>
       </c>
-      <c r="F38" s="1">
+      <c r="G38" s="1">
         <v>20</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I38" s="1">
-        <v>5</v>
-      </c>
-      <c r="J38" s="6">
+      <c r="I38" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J38" s="1">
+        <v>5</v>
+      </c>
+      <c r="K38" s="6">
         <v>60000003</v>
       </c>
-      <c r="K38" s="1">
-        <v>1</v>
-      </c>
       <c r="L38" s="1">
+        <v>1</v>
+      </c>
+      <c r="M38" s="1">
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="M38" s="1"/>
       <c r="N38" s="1"/>
-    </row>
-    <row r="39" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O38" s="1"/>
+    </row>
+    <row r="39" customFormat="1" customHeight="1" spans="3:15">
       <c r="C39" s="1">
         <v>34</v>
       </c>
@@ -2623,34 +2735,37 @@
         <v>0</v>
       </c>
       <c r="E39" s="1">
+        <v>4</v>
+      </c>
+      <c r="F39" s="1">
         <v>25000</v>
       </c>
-      <c r="F39" s="1">
+      <c r="G39" s="1">
         <v>10</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I39" s="1">
-        <v>5</v>
-      </c>
-      <c r="J39" s="6">
+      <c r="I39" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J39" s="1">
+        <v>5</v>
+      </c>
+      <c r="K39" s="6">
         <v>60000004</v>
       </c>
-      <c r="K39" s="1">
-        <v>1</v>
-      </c>
       <c r="L39" s="1">
+        <v>1</v>
+      </c>
+      <c r="M39" s="1">
         <f t="shared" si="1"/>
         <v>250000</v>
       </c>
-      <c r="M39" s="1"/>
       <c r="N39" s="1"/>
-    </row>
-    <row r="40" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O39" s="1"/>
+    </row>
+    <row r="40" customFormat="1" customHeight="1" spans="3:15">
       <c r="C40" s="1">
         <v>35</v>
       </c>
@@ -2658,34 +2773,37 @@
         <v>0</v>
       </c>
       <c r="E40" s="1">
+        <v>4</v>
+      </c>
+      <c r="F40" s="1">
         <v>25000</v>
       </c>
-      <c r="F40" s="1">
+      <c r="G40" s="1">
         <v>10</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I40" s="1">
-        <v>5</v>
-      </c>
-      <c r="J40" s="6">
+      <c r="I40" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J40" s="1">
+        <v>5</v>
+      </c>
+      <c r="K40" s="6">
         <v>60000005</v>
       </c>
-      <c r="K40" s="1">
-        <v>1</v>
-      </c>
       <c r="L40" s="1">
+        <v>1</v>
+      </c>
+      <c r="M40" s="1">
         <f t="shared" si="1"/>
         <v>250000</v>
       </c>
-      <c r="M40" s="1"/>
       <c r="N40" s="1"/>
-    </row>
-    <row r="41" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O40" s="1"/>
+    </row>
+    <row r="41" customFormat="1" customHeight="1" spans="3:15">
       <c r="C41" s="1">
         <v>36</v>
       </c>
@@ -2693,34 +2811,37 @@
         <v>0</v>
       </c>
       <c r="E41" s="1">
+        <v>4</v>
+      </c>
+      <c r="F41" s="1">
         <v>20000</v>
       </c>
-      <c r="F41" s="1">
+      <c r="G41" s="1">
         <v>15</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I41" s="1">
-        <v>5</v>
-      </c>
-      <c r="J41" s="6">
+      <c r="I41" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J41" s="1">
+        <v>5</v>
+      </c>
+      <c r="K41" s="6">
         <v>60000006</v>
       </c>
-      <c r="K41" s="1">
-        <v>1</v>
-      </c>
       <c r="L41" s="1">
+        <v>1</v>
+      </c>
+      <c r="M41" s="1">
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="M41" s="1"/>
       <c r="N41" s="1"/>
-    </row>
-    <row r="42" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O41" s="1"/>
+    </row>
+    <row r="42" customFormat="1" customHeight="1" spans="3:15">
       <c r="C42" s="1">
         <v>37</v>
       </c>
@@ -2728,34 +2849,37 @@
         <v>0</v>
       </c>
       <c r="E42" s="1">
+        <v>4</v>
+      </c>
+      <c r="F42" s="1">
         <v>20000</v>
       </c>
-      <c r="F42" s="1">
+      <c r="G42" s="1">
         <v>15</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I42" s="1">
-        <v>5</v>
-      </c>
-      <c r="J42" s="6">
+      <c r="I42" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J42" s="1">
+        <v>5</v>
+      </c>
+      <c r="K42" s="6">
         <v>60000007</v>
       </c>
-      <c r="K42" s="1">
-        <v>1</v>
-      </c>
       <c r="L42" s="1">
+        <v>1</v>
+      </c>
+      <c r="M42" s="1">
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="M42" s="1"/>
       <c r="N42" s="1"/>
-    </row>
-    <row r="43" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O42" s="1"/>
+    </row>
+    <row r="43" customFormat="1" customHeight="1" spans="3:15">
       <c r="C43" s="1">
         <v>38</v>
       </c>
@@ -2763,34 +2887,37 @@
         <v>0</v>
       </c>
       <c r="E43" s="1">
+        <v>4</v>
+      </c>
+      <c r="F43" s="1">
         <v>20000</v>
       </c>
-      <c r="F43" s="1">
+      <c r="G43" s="1">
         <v>15</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="I43" s="1">
-        <v>5</v>
-      </c>
-      <c r="J43" s="6">
+      <c r="I43" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="J43" s="1">
+        <v>5</v>
+      </c>
+      <c r="K43" s="6">
         <v>60000008</v>
       </c>
-      <c r="K43" s="1">
-        <v>1</v>
-      </c>
       <c r="L43" s="1">
+        <v>1</v>
+      </c>
+      <c r="M43" s="1">
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="M43" s="1"/>
       <c r="N43" s="1"/>
-    </row>
-    <row r="44" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O43" s="1"/>
+    </row>
+    <row r="44" customFormat="1" customHeight="1" spans="3:15">
       <c r="C44" s="1">
         <v>39</v>
       </c>
@@ -2798,34 +2925,37 @@
         <v>0</v>
       </c>
       <c r="E44" s="1">
+        <v>4</v>
+      </c>
+      <c r="F44" s="1">
         <v>20000</v>
       </c>
-      <c r="F44" s="1">
+      <c r="G44" s="1">
         <v>15</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I44" s="1">
-        <v>5</v>
-      </c>
-      <c r="J44" s="6">
+      <c r="I44" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J44" s="1">
+        <v>5</v>
+      </c>
+      <c r="K44" s="6">
         <v>60000009</v>
       </c>
-      <c r="K44" s="1">
-        <v>1</v>
-      </c>
       <c r="L44" s="1">
+        <v>1</v>
+      </c>
+      <c r="M44" s="1">
         <f t="shared" si="1"/>
         <v>300000</v>
       </c>
-      <c r="M44" s="1"/>
       <c r="N44" s="1"/>
-    </row>
-    <row r="45" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O44" s="1"/>
+    </row>
+    <row r="45" customFormat="1" customHeight="1" spans="3:15">
       <c r="C45" s="1">
         <v>40</v>
       </c>
@@ -2833,34 +2963,37 @@
         <v>0</v>
       </c>
       <c r="E45" s="1">
+        <v>4</v>
+      </c>
+      <c r="F45" s="1">
         <v>20000</v>
       </c>
-      <c r="F45" s="1">
+      <c r="G45" s="1">
         <v>20</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="I45" s="1">
-        <v>5</v>
-      </c>
-      <c r="J45" s="6">
+      <c r="I45" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J45" s="1">
+        <v>5</v>
+      </c>
+      <c r="K45" s="6">
         <v>60000010</v>
       </c>
-      <c r="K45" s="1">
-        <v>1</v>
-      </c>
       <c r="L45" s="1">
+        <v>1</v>
+      </c>
+      <c r="M45" s="1">
         <f t="shared" si="1"/>
         <v>400000</v>
       </c>
-      <c r="M45" s="1"/>
       <c r="N45" s="1"/>
-    </row>
-    <row r="46" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O45" s="1"/>
+    </row>
+    <row r="46" customFormat="1" customHeight="1" spans="3:15">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -2873,8 +3006,9 @@
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
-    </row>
-    <row r="47" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O46" s="1"/>
+    </row>
+    <row r="47" customFormat="1" customHeight="1" spans="3:15">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -2887,8 +3021,9 @@
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
-    </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="O47" s="1"/>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C48" s="1">
         <v>102</v>
       </c>
@@ -2896,39 +3031,42 @@
         <v>1</v>
       </c>
       <c r="E48" s="1">
+        <v>0</v>
+      </c>
+      <c r="F48" s="1">
         <v>100</v>
       </c>
-      <c r="F48" s="1">
-        <f t="shared" ref="F48:F55" si="2">M48*N48</f>
+      <c r="G48" s="1">
+        <f t="shared" ref="G48:G55" si="2">N48*O48</f>
         <v>300</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I48" s="1">
-        <v>5</v>
+      <c r="I48" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="J48" s="1">
+        <v>5</v>
+      </c>
+      <c r="K48" s="1">
         <v>4007</v>
       </c>
-      <c r="K48" s="1">
+      <c r="L48" s="1">
         <v>1000</v>
       </c>
-      <c r="L48" s="1">
-        <f t="shared" ref="L48:L55" si="3">E48*F48</f>
+      <c r="M48" s="1">
+        <f t="shared" ref="M48:M55" si="3">F48*G48</f>
         <v>30000</v>
       </c>
-      <c r="M48" s="1">
-        <v>1</v>
-      </c>
       <c r="N48" s="1">
+        <v>1</v>
+      </c>
+      <c r="O48" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C49" s="1">
         <v>103</v>
       </c>
@@ -2936,39 +3074,42 @@
         <v>1</v>
       </c>
       <c r="E49" s="1">
+        <v>0</v>
+      </c>
+      <c r="F49" s="1">
         <v>100</v>
       </c>
-      <c r="F49" s="1">
+      <c r="G49" s="1">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="H49" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="I49" s="1">
-        <v>5</v>
+      <c r="I49" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="J49" s="1">
+        <v>5</v>
+      </c>
+      <c r="K49" s="1">
         <v>4101</v>
       </c>
-      <c r="K49" s="1">
+      <c r="L49" s="1">
         <v>1000</v>
       </c>
-      <c r="L49" s="1">
+      <c r="M49" s="1">
         <f t="shared" si="3"/>
         <v>50000</v>
       </c>
-      <c r="M49" s="1">
-        <v>1</v>
-      </c>
       <c r="N49" s="1">
+        <v>1</v>
+      </c>
+      <c r="O49" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C50" s="1">
         <v>104</v>
       </c>
@@ -2976,39 +3117,42 @@
         <v>1</v>
       </c>
       <c r="E50" s="1">
+        <v>0</v>
+      </c>
+      <c r="F50" s="1">
         <v>1000</v>
       </c>
-      <c r="F50" s="1">
+      <c r="G50" s="1">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="H50" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I50" s="1">
+      <c r="I50" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J50" s="1">
         <v>15</v>
       </c>
-      <c r="J50" s="1">
+      <c r="K50" s="1">
         <v>4014</v>
       </c>
-      <c r="K50" s="1">
+      <c r="L50" s="1">
         <v>100</v>
       </c>
-      <c r="L50" s="1">
+      <c r="M50" s="1">
         <f t="shared" si="3"/>
         <v>6000</v>
       </c>
-      <c r="M50" s="1">
-        <v>1</v>
-      </c>
       <c r="N50" s="1">
+        <v>1</v>
+      </c>
+      <c r="O50" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C51" s="1">
         <v>105</v>
       </c>
@@ -3016,39 +3160,42 @@
         <v>1</v>
       </c>
       <c r="E51" s="1">
+        <v>0</v>
+      </c>
+      <c r="F51" s="1">
         <v>500</v>
       </c>
-      <c r="F51" s="1">
+      <c r="G51" s="1">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="H51" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="I51" s="1">
-        <v>5</v>
+      <c r="I51" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="J51" s="1">
+        <v>5</v>
+      </c>
+      <c r="K51" s="1">
         <v>4012</v>
       </c>
-      <c r="K51" s="1">
+      <c r="L51" s="1">
         <v>200</v>
       </c>
-      <c r="L51" s="1">
+      <c r="M51" s="1">
         <f t="shared" si="3"/>
         <v>10000</v>
       </c>
-      <c r="M51" s="1">
-        <v>1</v>
-      </c>
       <c r="N51" s="1">
+        <v>1</v>
+      </c>
+      <c r="O51" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C52" s="1">
         <v>106</v>
       </c>
@@ -3056,39 +3203,42 @@
         <v>1</v>
       </c>
       <c r="E52" s="1">
+        <v>1</v>
+      </c>
+      <c r="F52" s="1">
         <v>15000</v>
       </c>
-      <c r="F52" s="1">
+      <c r="G52" s="1">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="H52" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I52" s="1">
-        <v>5</v>
+      <c r="I52" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="J52" s="1">
+        <v>5</v>
+      </c>
+      <c r="K52" s="1">
         <v>4019</v>
       </c>
-      <c r="K52" s="1">
-        <v>1</v>
-      </c>
       <c r="L52" s="1">
+        <v>1</v>
+      </c>
+      <c r="M52" s="1">
         <f t="shared" si="3"/>
         <v>120000</v>
       </c>
-      <c r="M52" s="1">
-        <v>1</v>
-      </c>
       <c r="N52" s="1">
+        <v>1</v>
+      </c>
+      <c r="O52" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C53" s="1">
         <v>107</v>
       </c>
@@ -3096,39 +3246,42 @@
         <v>1</v>
       </c>
       <c r="E53" s="1">
+        <v>0</v>
+      </c>
+      <c r="F53" s="1">
         <v>500</v>
       </c>
-      <c r="F53" s="1">
+      <c r="G53" s="1">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="H53" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I53" s="1">
-        <v>5</v>
+      <c r="I53" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="J53" s="1">
+        <v>5</v>
+      </c>
+      <c r="K53" s="1">
         <v>4001</v>
       </c>
-      <c r="K53" s="1">
+      <c r="L53" s="1">
         <v>1000000</v>
       </c>
-      <c r="L53" s="1">
+      <c r="M53" s="1">
         <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="M53" s="1">
-        <v>1</v>
-      </c>
       <c r="N53" s="1">
+        <v>1</v>
+      </c>
+      <c r="O53" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C54" s="1">
         <v>108</v>
       </c>
@@ -3136,39 +3289,42 @@
         <v>1</v>
       </c>
       <c r="E54" s="1">
+        <v>0</v>
+      </c>
+      <c r="F54" s="1">
         <v>500</v>
       </c>
-      <c r="F54" s="1">
+      <c r="G54" s="1">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="H54" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="I54" s="1">
-        <v>5</v>
+      <c r="I54" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="J54" s="1">
+        <v>5</v>
+      </c>
+      <c r="K54" s="1">
         <v>4002</v>
       </c>
-      <c r="K54" s="1">
+      <c r="L54" s="1">
         <v>6000000</v>
       </c>
-      <c r="L54" s="1">
+      <c r="M54" s="1">
         <f t="shared" si="3"/>
         <v>20000</v>
       </c>
-      <c r="M54" s="1">
-        <v>1</v>
-      </c>
       <c r="N54" s="1">
+        <v>1</v>
+      </c>
+      <c r="O54" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C55" s="1">
         <v>109</v>
       </c>
@@ -3176,319 +3332,343 @@
         <v>1</v>
       </c>
       <c r="E55" s="1">
+        <v>6</v>
+      </c>
+      <c r="F55" s="1">
         <v>30000</v>
       </c>
-      <c r="F55" s="1">
+      <c r="G55" s="1">
         <f t="shared" si="2"/>
         <v>5</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I55" s="1">
-        <v>5</v>
+      <c r="I55" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="J55" s="1">
+        <v>5</v>
+      </c>
+      <c r="K55" s="1">
         <v>4026</v>
       </c>
-      <c r="K55" s="1">
-        <v>1</v>
-      </c>
       <c r="L55" s="1">
+        <v>1</v>
+      </c>
+      <c r="M55" s="1">
         <f t="shared" si="3"/>
         <v>150000</v>
       </c>
-      <c r="M55" s="1">
-        <v>1</v>
-      </c>
       <c r="N55" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="O55" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C57" s="1">
         <v>201</v>
       </c>
       <c r="D57" s="1">
         <v>2</v>
       </c>
-      <c r="E57" s="5">
+      <c r="E57" s="1">
+        <v>0</v>
+      </c>
+      <c r="F57" s="5">
         <v>200</v>
       </c>
-      <c r="F57" s="1">
-        <f t="shared" ref="F57:F64" si="4">M57*N57</f>
+      <c r="G57" s="1">
+        <f t="shared" ref="G57:G64" si="4">N57*O57</f>
         <v>300</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I57" s="1">
-        <v>5</v>
+      <c r="I57" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="J57" s="1">
+        <v>5</v>
+      </c>
+      <c r="K57" s="1">
         <v>4007</v>
       </c>
-      <c r="K57" s="1">
+      <c r="L57" s="1">
         <v>1000</v>
       </c>
-      <c r="L57" s="1">
-        <f t="shared" ref="L57:L64" si="5">E57*F57</f>
+      <c r="M57" s="1">
+        <f t="shared" ref="M57:M64" si="5">F57*G57</f>
         <v>60000</v>
       </c>
-      <c r="M57" s="1">
-        <v>1</v>
-      </c>
       <c r="N57" s="1">
+        <v>1</v>
+      </c>
+      <c r="O57" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C58" s="1">
         <v>202</v>
       </c>
       <c r="D58" s="1">
         <v>2</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E58" s="1">
+        <v>0</v>
+      </c>
+      <c r="F58" s="5">
         <v>200</v>
       </c>
-      <c r="F58" s="1">
+      <c r="G58" s="1">
         <f t="shared" si="4"/>
         <v>500</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="H58" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="I58" s="1">
-        <v>5</v>
+      <c r="I58" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="J58" s="1">
+        <v>5</v>
+      </c>
+      <c r="K58" s="1">
         <v>4101</v>
       </c>
-      <c r="K58" s="1">
+      <c r="L58" s="1">
         <v>1000</v>
       </c>
-      <c r="L58" s="1">
+      <c r="M58" s="1">
         <f t="shared" si="5"/>
         <v>100000</v>
       </c>
-      <c r="M58" s="1">
-        <v>1</v>
-      </c>
       <c r="N58" s="1">
+        <v>1</v>
+      </c>
+      <c r="O58" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C59" s="1">
         <v>203</v>
       </c>
       <c r="D59" s="1">
         <v>2</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E59" s="1">
+        <v>0</v>
+      </c>
+      <c r="F59" s="5">
         <v>2000</v>
       </c>
-      <c r="F59" s="1">
+      <c r="G59" s="1">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="G59" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="H59" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I59" s="1">
+      <c r="I59" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J59" s="1">
         <v>15</v>
       </c>
-      <c r="J59" s="1">
+      <c r="K59" s="1">
         <v>4014</v>
       </c>
-      <c r="K59" s="1">
+      <c r="L59" s="1">
         <v>100</v>
       </c>
-      <c r="L59" s="1">
+      <c r="M59" s="1">
         <f t="shared" si="5"/>
         <v>12000</v>
       </c>
-      <c r="M59" s="1">
-        <v>1</v>
-      </c>
       <c r="N59" s="1">
+        <v>1</v>
+      </c>
+      <c r="O59" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C60" s="1">
         <v>204</v>
       </c>
       <c r="D60" s="1">
         <v>2</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="1">
+        <v>0</v>
+      </c>
+      <c r="F60" s="5">
         <v>1000</v>
       </c>
-      <c r="F60" s="1">
+      <c r="G60" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="H60" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="I60" s="1">
-        <v>5</v>
+      <c r="I60" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="J60" s="1">
+        <v>5</v>
+      </c>
+      <c r="K60" s="1">
         <v>4012</v>
       </c>
-      <c r="K60" s="1">
+      <c r="L60" s="1">
         <v>200</v>
       </c>
-      <c r="L60" s="1">
+      <c r="M60" s="1">
         <f t="shared" si="5"/>
         <v>20000</v>
       </c>
-      <c r="M60" s="1">
-        <v>1</v>
-      </c>
       <c r="N60" s="1">
+        <v>1</v>
+      </c>
+      <c r="O60" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C61" s="1">
         <v>205</v>
       </c>
       <c r="D61" s="1">
         <v>2</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+      <c r="F61" s="5">
         <v>30000</v>
       </c>
-      <c r="F61" s="1">
+      <c r="G61" s="1">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="H61" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I61" s="1">
-        <v>5</v>
+      <c r="I61" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="J61" s="1">
+        <v>5</v>
+      </c>
+      <c r="K61" s="1">
         <v>4019</v>
       </c>
-      <c r="K61" s="1">
-        <v>1</v>
-      </c>
       <c r="L61" s="1">
+        <v>1</v>
+      </c>
+      <c r="M61" s="1">
         <f t="shared" si="5"/>
         <v>240000</v>
       </c>
-      <c r="M61" s="1">
-        <v>1</v>
-      </c>
       <c r="N61" s="1">
+        <v>1</v>
+      </c>
+      <c r="O61" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C62" s="1">
         <v>206</v>
       </c>
       <c r="D62" s="1">
         <v>2</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E62" s="1">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5">
         <v>1000</v>
       </c>
-      <c r="F62" s="1">
+      <c r="G62" s="1">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="G62" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="H62" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I62" s="1">
-        <v>5</v>
+      <c r="I62" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="J62" s="1">
+        <v>5</v>
+      </c>
+      <c r="K62" s="1">
         <v>4001</v>
       </c>
-      <c r="K62" s="1">
+      <c r="L62" s="1">
         <v>1000000</v>
       </c>
-      <c r="L62" s="1">
+      <c r="M62" s="1">
         <f t="shared" si="5"/>
         <v>40000</v>
       </c>
-      <c r="M62" s="1">
-        <v>1</v>
-      </c>
       <c r="N62" s="1">
+        <v>1</v>
+      </c>
+      <c r="O62" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C63" s="1">
         <v>207</v>
       </c>
       <c r="D63" s="1">
         <v>2</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E63" s="1">
+        <v>0</v>
+      </c>
+      <c r="F63" s="5">
         <v>1000</v>
       </c>
-      <c r="F63" s="1">
+      <c r="G63" s="1">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="G63" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="H63" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="I63" s="1">
-        <v>5</v>
+      <c r="I63" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="J63" s="1">
+        <v>5</v>
+      </c>
+      <c r="K63" s="1">
         <v>4002</v>
       </c>
-      <c r="K63" s="1">
+      <c r="L63" s="1">
         <v>6000000</v>
       </c>
-      <c r="L63" s="1">
+      <c r="M63" s="1">
         <f t="shared" si="5"/>
         <v>40000</v>
       </c>
-      <c r="M63" s="1">
-        <v>1</v>
-      </c>
       <c r="N63" s="1">
+        <v>1</v>
+      </c>
+      <c r="O63" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C64" s="1">
         <v>208</v>
       </c>
@@ -3496,39 +3676,42 @@
         <v>2</v>
       </c>
       <c r="E64" s="1">
+        <v>6</v>
+      </c>
+      <c r="F64" s="1">
         <v>30000</v>
       </c>
-      <c r="F64" s="1">
+      <c r="G64" s="1">
         <f t="shared" si="4"/>
         <v>5</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I64" s="1">
-        <v>5</v>
+      <c r="I64" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="J64" s="1">
+        <v>5</v>
+      </c>
+      <c r="K64" s="1">
         <v>4026</v>
       </c>
-      <c r="K64" s="1">
-        <v>1</v>
-      </c>
       <c r="L64" s="1">
+        <v>1</v>
+      </c>
+      <c r="M64" s="1">
         <f t="shared" si="5"/>
         <v>150000</v>
       </c>
-      <c r="M64" s="1">
-        <v>1</v>
-      </c>
       <c r="N64" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="O64" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C66" s="1">
         <v>211</v>
       </c>
@@ -3536,39 +3719,42 @@
         <v>3</v>
       </c>
       <c r="E66" s="1">
+        <v>0</v>
+      </c>
+      <c r="F66" s="1">
         <v>400</v>
       </c>
-      <c r="F66" s="1">
-        <f t="shared" ref="F66:F73" si="6">M66*N66</f>
+      <c r="G66" s="1">
+        <f t="shared" ref="G66:G73" si="6">N66*O66</f>
         <v>300</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I66" s="1">
-        <v>5</v>
+      <c r="I66" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="J66" s="1">
+        <v>5</v>
+      </c>
+      <c r="K66" s="1">
         <v>4007</v>
       </c>
-      <c r="K66" s="1">
+      <c r="L66" s="1">
         <v>1000</v>
       </c>
-      <c r="L66" s="1">
-        <f t="shared" ref="L66:L73" si="7">E66*F66</f>
+      <c r="M66" s="1">
+        <f t="shared" ref="M66:M73" si="7">F66*G66</f>
         <v>120000</v>
       </c>
-      <c r="M66" s="1">
-        <v>1</v>
-      </c>
       <c r="N66" s="1">
+        <v>1</v>
+      </c>
+      <c r="O66" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C67" s="1">
         <v>212</v>
       </c>
@@ -3576,39 +3762,42 @@
         <v>3</v>
       </c>
       <c r="E67" s="1">
+        <v>0</v>
+      </c>
+      <c r="F67" s="1">
         <v>400</v>
       </c>
-      <c r="F67" s="1">
+      <c r="G67" s="1">
         <f t="shared" si="6"/>
         <v>500</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="H67" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="I67" s="1">
-        <v>5</v>
+      <c r="I67" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="J67" s="1">
+        <v>5</v>
+      </c>
+      <c r="K67" s="1">
         <v>4101</v>
       </c>
-      <c r="K67" s="1">
+      <c r="L67" s="1">
         <v>1000</v>
       </c>
-      <c r="L67" s="1">
+      <c r="M67" s="1">
         <f t="shared" si="7"/>
         <v>200000</v>
       </c>
-      <c r="M67" s="1">
-        <v>1</v>
-      </c>
       <c r="N67" s="1">
+        <v>1</v>
+      </c>
+      <c r="O67" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C68" s="1">
         <v>213</v>
       </c>
@@ -3616,39 +3805,42 @@
         <v>3</v>
       </c>
       <c r="E68" s="1">
+        <v>0</v>
+      </c>
+      <c r="F68" s="1">
         <v>4000</v>
       </c>
-      <c r="F68" s="1">
+      <c r="G68" s="1">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="G68" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="H68" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I68" s="1">
+      <c r="I68" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J68" s="1">
         <v>15</v>
       </c>
-      <c r="J68" s="1">
+      <c r="K68" s="1">
         <v>4014</v>
       </c>
-      <c r="K68" s="1">
+      <c r="L68" s="1">
         <v>100</v>
       </c>
-      <c r="L68" s="1">
+      <c r="M68" s="1">
         <f t="shared" si="7"/>
         <v>24000</v>
       </c>
-      <c r="M68" s="1">
-        <v>1</v>
-      </c>
       <c r="N68" s="1">
+        <v>1</v>
+      </c>
+      <c r="O68" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C69" s="1">
         <v>214</v>
       </c>
@@ -3656,39 +3848,42 @@
         <v>3</v>
       </c>
       <c r="E69" s="1">
+        <v>0</v>
+      </c>
+      <c r="F69" s="1">
         <v>2000</v>
       </c>
-      <c r="F69" s="1">
+      <c r="G69" s="1">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="G69" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="H69" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="I69" s="1">
-        <v>5</v>
+      <c r="I69" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="J69" s="1">
+        <v>5</v>
+      </c>
+      <c r="K69" s="1">
         <v>4012</v>
       </c>
-      <c r="K69" s="1">
+      <c r="L69" s="1">
         <v>200</v>
       </c>
-      <c r="L69" s="1">
+      <c r="M69" s="1">
         <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="M69" s="1">
-        <v>1</v>
-      </c>
       <c r="N69" s="1">
+        <v>1</v>
+      </c>
+      <c r="O69" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C70" s="1">
         <v>215</v>
       </c>
@@ -3696,39 +3891,42 @@
         <v>3</v>
       </c>
       <c r="E70" s="1">
+        <v>1</v>
+      </c>
+      <c r="F70" s="1">
         <v>45000</v>
       </c>
-      <c r="F70" s="1">
+      <c r="G70" s="1">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="G70" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="H70" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I70" s="1">
-        <v>5</v>
+      <c r="I70" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="J70" s="1">
+        <v>5</v>
+      </c>
+      <c r="K70" s="1">
         <v>4019</v>
       </c>
-      <c r="K70" s="1">
-        <v>1</v>
-      </c>
       <c r="L70" s="1">
+        <v>1</v>
+      </c>
+      <c r="M70" s="1">
         <f t="shared" si="7"/>
         <v>360000</v>
       </c>
-      <c r="M70" s="1">
-        <v>1</v>
-      </c>
       <c r="N70" s="1">
+        <v>1</v>
+      </c>
+      <c r="O70" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C71" s="1">
         <v>216</v>
       </c>
@@ -3736,39 +3934,42 @@
         <v>3</v>
       </c>
       <c r="E71" s="1">
+        <v>0</v>
+      </c>
+      <c r="F71" s="1">
         <v>2000</v>
       </c>
-      <c r="F71" s="1">
+      <c r="G71" s="1">
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="G71" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="H71" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I71" s="1">
-        <v>5</v>
+      <c r="I71" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="J71" s="1">
+        <v>5</v>
+      </c>
+      <c r="K71" s="1">
         <v>4001</v>
       </c>
-      <c r="K71" s="1">
+      <c r="L71" s="1">
         <v>1000000</v>
       </c>
-      <c r="L71" s="1">
+      <c r="M71" s="1">
         <f t="shared" si="7"/>
         <v>80000</v>
       </c>
-      <c r="M71" s="1">
-        <v>1</v>
-      </c>
       <c r="N71" s="1">
+        <v>1</v>
+      </c>
+      <c r="O71" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C72" s="1">
         <v>217</v>
       </c>
@@ -3776,39 +3977,42 @@
         <v>3</v>
       </c>
       <c r="E72" s="1">
+        <v>0</v>
+      </c>
+      <c r="F72" s="1">
         <v>2000</v>
       </c>
-      <c r="F72" s="1">
+      <c r="G72" s="1">
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="G72" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="H72" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="I72" s="1">
-        <v>5</v>
+      <c r="I72" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="J72" s="1">
+        <v>5</v>
+      </c>
+      <c r="K72" s="1">
         <v>4002</v>
       </c>
-      <c r="K72" s="1">
+      <c r="L72" s="1">
         <v>6000000</v>
       </c>
-      <c r="L72" s="1">
+      <c r="M72" s="1">
         <f t="shared" si="7"/>
         <v>80000</v>
       </c>
-      <c r="M72" s="1">
-        <v>1</v>
-      </c>
       <c r="N72" s="1">
+        <v>1</v>
+      </c>
+      <c r="O72" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C73" s="1">
         <v>218</v>
       </c>
@@ -3816,319 +4020,343 @@
         <v>3</v>
       </c>
       <c r="E73" s="1">
+        <v>6</v>
+      </c>
+      <c r="F73" s="1">
         <v>30000</v>
       </c>
-      <c r="F73" s="1">
+      <c r="G73" s="1">
         <f t="shared" si="6"/>
         <v>5</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I73" s="1">
-        <v>5</v>
+      <c r="I73" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="J73" s="1">
+        <v>5</v>
+      </c>
+      <c r="K73" s="1">
         <v>4026</v>
       </c>
-      <c r="K73" s="1">
-        <v>1</v>
-      </c>
       <c r="L73" s="1">
+        <v>1</v>
+      </c>
+      <c r="M73" s="1">
         <f t="shared" si="7"/>
         <v>150000</v>
       </c>
-      <c r="M73" s="1">
-        <v>1</v>
-      </c>
       <c r="N73" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="O73" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C75" s="1">
         <v>221</v>
       </c>
       <c r="D75" s="1">
         <v>4</v>
       </c>
-      <c r="E75" s="5">
+      <c r="E75" s="1">
+        <v>0</v>
+      </c>
+      <c r="F75" s="5">
         <v>600</v>
       </c>
-      <c r="F75" s="1">
-        <f t="shared" ref="F75:F82" si="8">M75*N75</f>
+      <c r="G75" s="1">
+        <f t="shared" ref="G75:G82" si="8">N75*O75</f>
         <v>300</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I75" s="1">
-        <v>5</v>
+      <c r="I75" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="J75" s="1">
+        <v>5</v>
+      </c>
+      <c r="K75" s="1">
         <v>4007</v>
       </c>
-      <c r="K75" s="1">
+      <c r="L75" s="1">
         <v>1000</v>
       </c>
-      <c r="L75" s="1">
-        <f t="shared" ref="L75:L82" si="9">E75*F75</f>
+      <c r="M75" s="1">
+        <f t="shared" ref="M75:M82" si="9">F75*G75</f>
         <v>180000</v>
       </c>
-      <c r="M75" s="1">
-        <v>1</v>
-      </c>
       <c r="N75" s="1">
+        <v>1</v>
+      </c>
+      <c r="O75" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C76" s="1">
         <v>222</v>
       </c>
       <c r="D76" s="1">
         <v>4</v>
       </c>
-      <c r="E76" s="5">
+      <c r="E76" s="1">
+        <v>0</v>
+      </c>
+      <c r="F76" s="5">
         <v>600</v>
       </c>
-      <c r="F76" s="1">
+      <c r="G76" s="1">
         <f t="shared" si="8"/>
         <v>500</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="H76" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="I76" s="1">
-        <v>5</v>
+      <c r="I76" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="J76" s="1">
+        <v>5</v>
+      </c>
+      <c r="K76" s="1">
         <v>4101</v>
       </c>
-      <c r="K76" s="1">
+      <c r="L76" s="1">
         <v>1000</v>
       </c>
-      <c r="L76" s="1">
+      <c r="M76" s="1">
         <f t="shared" si="9"/>
         <v>300000</v>
       </c>
-      <c r="M76" s="1">
-        <v>1</v>
-      </c>
       <c r="N76" s="1">
+        <v>1</v>
+      </c>
+      <c r="O76" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C77" s="1">
         <v>223</v>
       </c>
       <c r="D77" s="1">
         <v>4</v>
       </c>
-      <c r="E77" s="5">
+      <c r="E77" s="1">
+        <v>0</v>
+      </c>
+      <c r="F77" s="5">
         <v>6000</v>
       </c>
-      <c r="F77" s="1">
+      <c r="G77" s="1">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="G77" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="H77" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I77" s="1">
+      <c r="I77" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J77" s="1">
         <v>15</v>
       </c>
-      <c r="J77" s="1">
+      <c r="K77" s="1">
         <v>4014</v>
       </c>
-      <c r="K77" s="1">
+      <c r="L77" s="1">
         <v>100</v>
       </c>
-      <c r="L77" s="1">
+      <c r="M77" s="1">
         <f t="shared" si="9"/>
         <v>36000</v>
       </c>
-      <c r="M77" s="1">
-        <v>1</v>
-      </c>
       <c r="N77" s="1">
+        <v>1</v>
+      </c>
+      <c r="O77" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="78" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C78" s="1">
         <v>224</v>
       </c>
       <c r="D78" s="1">
         <v>4</v>
       </c>
-      <c r="E78" s="5">
+      <c r="E78" s="1">
+        <v>0</v>
+      </c>
+      <c r="F78" s="5">
         <v>3000</v>
       </c>
-      <c r="F78" s="1">
+      <c r="G78" s="1">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="G78" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="H78" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="I78" s="1">
-        <v>5</v>
+      <c r="I78" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="J78" s="1">
+        <v>5</v>
+      </c>
+      <c r="K78" s="1">
         <v>4012</v>
       </c>
-      <c r="K78" s="1">
+      <c r="L78" s="1">
         <v>200</v>
       </c>
-      <c r="L78" s="1">
+      <c r="M78" s="1">
         <f t="shared" si="9"/>
         <v>60000</v>
       </c>
-      <c r="M78" s="1">
-        <v>1</v>
-      </c>
       <c r="N78" s="1">
+        <v>1</v>
+      </c>
+      <c r="O78" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C79" s="1">
         <v>225</v>
       </c>
       <c r="D79" s="1">
         <v>4</v>
       </c>
-      <c r="E79" s="5">
+      <c r="E79" s="1">
+        <v>1</v>
+      </c>
+      <c r="F79" s="5">
         <v>60000</v>
       </c>
-      <c r="F79" s="1">
+      <c r="G79" s="1">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="G79" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="H79" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I79" s="1">
-        <v>5</v>
+      <c r="I79" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="J79" s="1">
+        <v>5</v>
+      </c>
+      <c r="K79" s="1">
         <v>4019</v>
       </c>
-      <c r="K79" s="1">
-        <v>1</v>
-      </c>
       <c r="L79" s="1">
+        <v>1</v>
+      </c>
+      <c r="M79" s="1">
         <f t="shared" si="9"/>
         <v>480000</v>
       </c>
-      <c r="M79" s="1">
-        <v>1</v>
-      </c>
       <c r="N79" s="1">
+        <v>1</v>
+      </c>
+      <c r="O79" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="80" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="80" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C80" s="1">
         <v>226</v>
       </c>
       <c r="D80" s="1">
         <v>4</v>
       </c>
-      <c r="E80" s="5">
+      <c r="E80" s="1">
+        <v>0</v>
+      </c>
+      <c r="F80" s="5">
         <v>3000</v>
       </c>
-      <c r="F80" s="1">
+      <c r="G80" s="1">
         <f t="shared" si="8"/>
         <v>40</v>
       </c>
-      <c r="G80" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="H80" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I80" s="1">
-        <v>5</v>
+      <c r="I80" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="J80" s="1">
+        <v>5</v>
+      </c>
+      <c r="K80" s="1">
         <v>4001</v>
       </c>
-      <c r="K80" s="1">
+      <c r="L80" s="1">
         <v>1000000</v>
       </c>
-      <c r="L80" s="1">
+      <c r="M80" s="1">
         <f t="shared" si="9"/>
         <v>120000</v>
       </c>
-      <c r="M80" s="1">
-        <v>1</v>
-      </c>
       <c r="N80" s="1">
+        <v>1</v>
+      </c>
+      <c r="O80" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="81" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="81" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C81" s="1">
         <v>227</v>
       </c>
       <c r="D81" s="1">
         <v>4</v>
       </c>
-      <c r="E81" s="5">
+      <c r="E81" s="1">
+        <v>0</v>
+      </c>
+      <c r="F81" s="5">
         <v>3000</v>
       </c>
-      <c r="F81" s="1">
+      <c r="G81" s="1">
         <f t="shared" si="8"/>
         <v>40</v>
       </c>
-      <c r="G81" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="H81" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="I81" s="1">
-        <v>5</v>
+      <c r="I81" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="J81" s="1">
+        <v>5</v>
+      </c>
+      <c r="K81" s="1">
         <v>4002</v>
       </c>
-      <c r="K81" s="1">
+      <c r="L81" s="1">
         <v>6000000</v>
       </c>
-      <c r="L81" s="1">
+      <c r="M81" s="1">
         <f t="shared" si="9"/>
         <v>120000</v>
       </c>
-      <c r="M81" s="1">
-        <v>1</v>
-      </c>
       <c r="N81" s="1">
+        <v>1</v>
+      </c>
+      <c r="O81" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="82" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="82" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C82" s="1">
         <v>228</v>
       </c>
@@ -4136,39 +4364,42 @@
         <v>4</v>
       </c>
       <c r="E82" s="1">
+        <v>6</v>
+      </c>
+      <c r="F82" s="1">
         <v>30000</v>
       </c>
-      <c r="F82" s="1">
+      <c r="G82" s="1">
         <f t="shared" si="8"/>
         <v>5</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I82" s="1">
-        <v>5</v>
+      <c r="I82" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="J82" s="1">
+        <v>5</v>
+      </c>
+      <c r="K82" s="1">
         <v>4026</v>
       </c>
-      <c r="K82" s="1">
-        <v>1</v>
-      </c>
       <c r="L82" s="1">
+        <v>1</v>
+      </c>
+      <c r="M82" s="1">
         <f t="shared" si="9"/>
         <v>150000</v>
       </c>
-      <c r="M82" s="1">
-        <v>1</v>
-      </c>
       <c r="N82" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>1</v>
+      </c>
+      <c r="O82" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C84" s="1">
         <v>231</v>
       </c>
@@ -4176,39 +4407,42 @@
         <v>5</v>
       </c>
       <c r="E84" s="1">
+        <v>0</v>
+      </c>
+      <c r="F84" s="1">
         <v>800</v>
       </c>
-      <c r="F84" s="1">
-        <f t="shared" ref="F84:F91" si="10">M84*N84</f>
+      <c r="G84" s="1">
+        <f t="shared" ref="G84:G91" si="10">N84*O84</f>
         <v>1200</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I84" s="1">
-        <v>5</v>
+      <c r="I84" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="J84" s="1">
+        <v>5</v>
+      </c>
+      <c r="K84" s="1">
         <v>4007</v>
       </c>
-      <c r="K84" s="1">
+      <c r="L84" s="1">
         <v>1000</v>
       </c>
-      <c r="L84" s="1">
-        <f t="shared" ref="L84:L91" si="11">E84*F84</f>
+      <c r="M84" s="1">
+        <f t="shared" ref="M84:M91" si="11">F84*G84</f>
         <v>960000</v>
       </c>
-      <c r="M84" s="1">
+      <c r="N84" s="1">
         <v>4</v>
       </c>
-      <c r="N84" s="1">
+      <c r="O84" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C85" s="1">
         <v>232</v>
       </c>
@@ -4216,39 +4450,42 @@
         <v>5</v>
       </c>
       <c r="E85" s="1">
+        <v>0</v>
+      </c>
+      <c r="F85" s="1">
         <v>800</v>
       </c>
-      <c r="F85" s="1">
+      <c r="G85" s="1">
         <f t="shared" si="10"/>
         <v>2000</v>
       </c>
-      <c r="G85" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="H85" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="I85" s="1">
-        <v>5</v>
+      <c r="I85" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="J85" s="1">
+        <v>5</v>
+      </c>
+      <c r="K85" s="1">
         <v>4101</v>
       </c>
-      <c r="K85" s="1">
+      <c r="L85" s="1">
         <v>1000</v>
       </c>
-      <c r="L85" s="1">
+      <c r="M85" s="1">
         <f t="shared" si="11"/>
         <v>1600000</v>
       </c>
-      <c r="M85" s="1">
+      <c r="N85" s="1">
         <v>4</v>
       </c>
-      <c r="N85" s="1">
+      <c r="O85" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="86" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="86" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C86" s="1">
         <v>233</v>
       </c>
@@ -4256,39 +4493,42 @@
         <v>5</v>
       </c>
       <c r="E86" s="1">
+        <v>0</v>
+      </c>
+      <c r="F86" s="1">
         <v>8000</v>
       </c>
-      <c r="F86" s="1">
+      <c r="G86" s="1">
         <f t="shared" si="10"/>
         <v>24</v>
       </c>
-      <c r="G86" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="H86" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I86" s="1">
+      <c r="I86" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J86" s="1">
         <v>15</v>
       </c>
-      <c r="J86" s="1">
+      <c r="K86" s="1">
         <v>4014</v>
       </c>
-      <c r="K86" s="1">
+      <c r="L86" s="1">
         <v>100</v>
       </c>
-      <c r="L86" s="1">
+      <c r="M86" s="1">
         <f t="shared" si="11"/>
         <v>192000</v>
       </c>
-      <c r="M86" s="1">
+      <c r="N86" s="1">
         <v>4</v>
       </c>
-      <c r="N86" s="1">
+      <c r="O86" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="87" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="87" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C87" s="1">
         <v>234</v>
       </c>
@@ -4296,39 +4536,42 @@
         <v>5</v>
       </c>
       <c r="E87" s="1">
+        <v>0</v>
+      </c>
+      <c r="F87" s="1">
         <v>4000</v>
       </c>
-      <c r="F87" s="1">
+      <c r="G87" s="1">
         <f t="shared" si="10"/>
         <v>80</v>
       </c>
-      <c r="G87" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="H87" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="I87" s="1">
-        <v>5</v>
+      <c r="I87" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="J87" s="1">
+        <v>5</v>
+      </c>
+      <c r="K87" s="1">
         <v>4012</v>
       </c>
-      <c r="K87" s="1">
+      <c r="L87" s="1">
         <v>200</v>
       </c>
-      <c r="L87" s="1">
+      <c r="M87" s="1">
         <f t="shared" si="11"/>
         <v>320000</v>
       </c>
-      <c r="M87" s="1">
+      <c r="N87" s="1">
         <v>4</v>
       </c>
-      <c r="N87" s="1">
+      <c r="O87" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="88" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="88" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C88" s="1">
         <v>235</v>
       </c>
@@ -4336,39 +4579,42 @@
         <v>5</v>
       </c>
       <c r="E88" s="1">
+        <v>1</v>
+      </c>
+      <c r="F88" s="1">
         <v>75000</v>
       </c>
-      <c r="F88" s="1">
+      <c r="G88" s="1">
         <f t="shared" si="10"/>
         <v>32</v>
       </c>
-      <c r="G88" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="H88" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="I88" s="1">
-        <v>5</v>
+      <c r="I88" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="J88" s="1">
+        <v>5</v>
+      </c>
+      <c r="K88" s="1">
         <v>4019</v>
       </c>
-      <c r="K88" s="1">
-        <v>1</v>
-      </c>
       <c r="L88" s="1">
+        <v>1</v>
+      </c>
+      <c r="M88" s="1">
         <f t="shared" si="11"/>
         <v>2400000</v>
       </c>
-      <c r="M88" s="1">
+      <c r="N88" s="1">
         <v>4</v>
       </c>
-      <c r="N88" s="1">
+      <c r="O88" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="89" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="89" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C89" s="1">
         <v>236</v>
       </c>
@@ -4376,39 +4622,42 @@
         <v>5</v>
       </c>
       <c r="E89" s="1">
+        <v>0</v>
+      </c>
+      <c r="F89" s="1">
         <v>4000</v>
       </c>
-      <c r="F89" s="1">
+      <c r="G89" s="1">
         <f t="shared" si="10"/>
         <v>160</v>
       </c>
-      <c r="G89" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="H89" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I89" s="1">
-        <v>5</v>
+      <c r="I89" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="J89" s="1">
+        <v>5</v>
+      </c>
+      <c r="K89" s="1">
         <v>4001</v>
       </c>
-      <c r="K89" s="1">
+      <c r="L89" s="1">
         <v>1000000</v>
       </c>
-      <c r="L89" s="1">
+      <c r="M89" s="1">
         <f t="shared" si="11"/>
         <v>640000</v>
       </c>
-      <c r="M89" s="1">
+      <c r="N89" s="1">
         <v>4</v>
       </c>
-      <c r="N89" s="1">
+      <c r="O89" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="90" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="90" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C90" s="1">
         <v>237</v>
       </c>
@@ -4416,39 +4665,42 @@
         <v>5</v>
       </c>
       <c r="E90" s="1">
+        <v>0</v>
+      </c>
+      <c r="F90" s="1">
         <v>4000</v>
       </c>
-      <c r="F90" s="1">
+      <c r="G90" s="1">
         <f t="shared" si="10"/>
         <v>160</v>
       </c>
-      <c r="G90" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="H90" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="I90" s="1">
-        <v>5</v>
+      <c r="I90" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="J90" s="1">
+        <v>5</v>
+      </c>
+      <c r="K90" s="1">
         <v>4002</v>
       </c>
-      <c r="K90" s="1">
+      <c r="L90" s="1">
         <v>6000000</v>
       </c>
-      <c r="L90" s="1">
+      <c r="M90" s="1">
         <f t="shared" si="11"/>
         <v>640000</v>
       </c>
-      <c r="M90" s="1">
+      <c r="N90" s="1">
         <v>4</v>
       </c>
-      <c r="N90" s="1">
+      <c r="O90" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="91" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="91" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C91" s="1">
         <v>238</v>
       </c>
@@ -4456,39 +4708,42 @@
         <v>5</v>
       </c>
       <c r="E91" s="1">
+        <v>6</v>
+      </c>
+      <c r="F91" s="1">
         <v>30000</v>
       </c>
-      <c r="F91" s="1">
+      <c r="G91" s="1">
         <f t="shared" si="10"/>
         <v>5</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I91" s="1">
-        <v>5</v>
+      <c r="I91" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="J91" s="1">
+        <v>5</v>
+      </c>
+      <c r="K91" s="1">
         <v>4026</v>
       </c>
-      <c r="K91" s="1">
-        <v>1</v>
-      </c>
       <c r="L91" s="1">
+        <v>1</v>
+      </c>
+      <c r="M91" s="1">
         <f t="shared" si="11"/>
         <v>150000</v>
       </c>
-      <c r="M91" s="1">
-        <v>1</v>
-      </c>
       <c r="N91" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="93" s="1" customFormat="1" customHeight="1" spans="3:12">
+        <v>1</v>
+      </c>
+      <c r="O91" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C93" s="1">
         <v>999</v>
       </c>
@@ -4496,32 +4751,35 @@
         <v>0</v>
       </c>
       <c r="E93" s="1">
+        <v>0</v>
+      </c>
+      <c r="F93" s="1">
         <v>1000</v>
       </c>
-      <c r="F93" s="1">
+      <c r="G93" s="1">
         <v>50</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="I93" s="1">
-        <v>5</v>
+      <c r="I93" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="J93" s="1">
+        <v>5</v>
+      </c>
+      <c r="K93" s="1">
         <v>4006</v>
       </c>
-      <c r="K93" s="1">
+      <c r="L93" s="1">
         <v>1000</v>
       </c>
-      <c r="L93" s="1">
-        <f t="shared" ref="L93:L95" si="12">E93*F93</f>
+      <c r="M93" s="1">
+        <f t="shared" ref="M93:M95" si="12">F93*G93</f>
         <v>50000</v>
       </c>
     </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C94" s="1">
         <v>1000</v>
       </c>
@@ -4529,32 +4787,35 @@
         <v>0</v>
       </c>
       <c r="E94" s="1">
+        <v>0</v>
+      </c>
+      <c r="F94" s="1">
         <v>2000</v>
       </c>
-      <c r="F94" s="1">
+      <c r="G94" s="1">
         <v>100</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="I94" s="1">
-        <v>5</v>
+      <c r="I94" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="J94" s="1">
+        <v>5</v>
+      </c>
+      <c r="K94" s="1">
         <v>4010</v>
       </c>
-      <c r="K94" s="1">
-        <v>5</v>
-      </c>
       <c r="L94" s="1">
+        <v>5</v>
+      </c>
+      <c r="M94" s="1">
         <f t="shared" si="12"/>
         <v>200000</v>
       </c>
     </row>
-    <row r="95" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="95" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C95" s="1">
         <v>1001</v>
       </c>
@@ -4562,35 +4823,38 @@
         <v>0</v>
       </c>
       <c r="E95" s="1">
+        <v>0</v>
+      </c>
+      <c r="F95" s="1">
         <v>2000</v>
       </c>
-      <c r="F95" s="1">
+      <c r="G95" s="1">
         <v>50</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="I95" s="1">
-        <v>5</v>
+      <c r="I95" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="J95" s="1">
+        <v>5</v>
+      </c>
+      <c r="K95" s="1">
         <v>4102</v>
       </c>
-      <c r="K95" s="1">
+      <c r="L95" s="1">
         <v>20</v>
       </c>
-      <c r="L95" s="1">
+      <c r="M95" s="1">
         <f t="shared" si="12"/>
         <v>100000</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:G5" errorStyle="warning">
-      <formula1>COUNTIF($C:$C,E3)&lt;2</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:H5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,F3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -1425,12 +1425,12 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="15.3636363636364" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.2545454545455" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.3666666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.2583333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="12" style="1" customWidth="1"/>
     <col min="8" max="8" width="22.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.1272727272727" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.8727272727273" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.875" style="1" customWidth="1"/>
     <col min="11" max="11" width="8.5" style="1" customWidth="1"/>
     <col min="12" max="12" width="11.5" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
@@ -2592,10 +2592,10 @@
         <v>4</v>
       </c>
       <c r="F35" s="1">
-        <v>600000</v>
+        <v>300000</v>
       </c>
       <c r="G35" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>82</v>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="128">
   <si>
     <t>#</t>
   </si>
@@ -339,6 +339,12 @@
   </si>
   <si>
     <t>韧性宝石</t>
+  </si>
+  <si>
+    <t>兑换低级法宝自选*1</t>
+  </si>
+  <si>
+    <t>低级法宝自选</t>
   </si>
   <si>
     <t>兑换四格碎片*1000</t>
@@ -2993,20 +2999,41 @@
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
     </row>
-    <row r="46" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C46" s="1">
+        <v>41</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0</v>
+      </c>
+      <c r="E46" s="1">
+        <v>0</v>
+      </c>
+      <c r="F46" s="1">
+        <v>50000</v>
+      </c>
+      <c r="G46" s="1">
+        <v>30</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J46" s="1">
+        <v>4</v>
+      </c>
+      <c r="K46" s="1">
+        <v>24</v>
+      </c>
+      <c r="L46" s="1">
+        <v>1</v>
+      </c>
+      <c r="M46" s="1">
+        <f>F46*G46</f>
+        <v>1500000</v>
+      </c>
     </row>
     <row r="47" customFormat="1" customHeight="1" spans="3:15">
       <c r="C47" s="1"/>
@@ -3041,10 +3068,10 @@
         <v>300</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J48" s="1">
         <v>5</v>
@@ -3084,10 +3111,10 @@
         <v>500</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J49" s="1">
         <v>5</v>
@@ -3127,10 +3154,10 @@
         <v>6</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J50" s="1">
         <v>15</v>
@@ -3170,10 +3197,10 @@
         <v>20</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J51" s="1">
         <v>5</v>
@@ -3213,10 +3240,10 @@
         <v>8</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J52" s="1">
         <v>5</v>
@@ -3256,10 +3283,10 @@
         <v>40</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J53" s="1">
         <v>5</v>
@@ -3299,10 +3326,10 @@
         <v>40</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J54" s="1">
         <v>5</v>
@@ -3342,10 +3369,10 @@
         <v>5</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J55" s="1">
         <v>5</v>
@@ -3385,10 +3412,10 @@
         <v>300</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J57" s="1">
         <v>5</v>
@@ -3428,10 +3455,10 @@
         <v>500</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J58" s="1">
         <v>5</v>
@@ -3471,10 +3498,10 @@
         <v>6</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J59" s="1">
         <v>15</v>
@@ -3514,10 +3541,10 @@
         <v>20</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J60" s="1">
         <v>5</v>
@@ -3557,10 +3584,10 @@
         <v>8</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J61" s="1">
         <v>5</v>
@@ -3600,10 +3627,10 @@
         <v>40</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J62" s="1">
         <v>5</v>
@@ -3643,10 +3670,10 @@
         <v>40</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J63" s="1">
         <v>5</v>
@@ -3686,10 +3713,10 @@
         <v>5</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J64" s="1">
         <v>5</v>
@@ -3729,10 +3756,10 @@
         <v>300</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J66" s="1">
         <v>5</v>
@@ -3772,10 +3799,10 @@
         <v>500</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J67" s="1">
         <v>5</v>
@@ -3815,10 +3842,10 @@
         <v>6</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J68" s="1">
         <v>15</v>
@@ -3858,10 +3885,10 @@
         <v>20</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J69" s="1">
         <v>5</v>
@@ -3901,10 +3928,10 @@
         <v>8</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J70" s="1">
         <v>5</v>
@@ -3944,10 +3971,10 @@
         <v>40</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J71" s="1">
         <v>5</v>
@@ -3987,10 +4014,10 @@
         <v>40</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J72" s="1">
         <v>5</v>
@@ -4030,10 +4057,10 @@
         <v>5</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J73" s="1">
         <v>5</v>
@@ -4073,10 +4100,10 @@
         <v>300</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J75" s="1">
         <v>5</v>
@@ -4116,10 +4143,10 @@
         <v>500</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J76" s="1">
         <v>5</v>
@@ -4159,10 +4186,10 @@
         <v>6</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J77" s="1">
         <v>15</v>
@@ -4202,10 +4229,10 @@
         <v>20</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J78" s="1">
         <v>5</v>
@@ -4245,10 +4272,10 @@
         <v>8</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J79" s="1">
         <v>5</v>
@@ -4288,10 +4315,10 @@
         <v>40</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J80" s="1">
         <v>5</v>
@@ -4331,10 +4358,10 @@
         <v>40</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J81" s="1">
         <v>5</v>
@@ -4374,10 +4401,10 @@
         <v>5</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J82" s="1">
         <v>5</v>
@@ -4417,10 +4444,10 @@
         <v>1200</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J84" s="1">
         <v>5</v>
@@ -4460,10 +4487,10 @@
         <v>2000</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J85" s="1">
         <v>5</v>
@@ -4503,10 +4530,10 @@
         <v>24</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J86" s="1">
         <v>15</v>
@@ -4546,10 +4573,10 @@
         <v>80</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J87" s="1">
         <v>5</v>
@@ -4589,10 +4616,10 @@
         <v>32</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J88" s="1">
         <v>5</v>
@@ -4632,10 +4659,10 @@
         <v>160</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J89" s="1">
         <v>5</v>
@@ -4675,10 +4702,10 @@
         <v>160</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J90" s="1">
         <v>5</v>
@@ -4718,10 +4745,10 @@
         <v>5</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J91" s="1">
         <v>5</v>
@@ -4760,10 +4787,10 @@
         <v>50</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J93" s="1">
         <v>5</v>
@@ -4796,10 +4823,10 @@
         <v>100</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J94" s="1">
         <v>5</v>
@@ -4832,10 +4859,10 @@
         <v>50</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J95" s="1">
         <v>5</v>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="149">
   <si>
     <t>#</t>
   </si>
@@ -162,6 +162,69 @@
   </si>
   <si>
     <t>龙之血</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>兑换图鉴龙之怒*1</t>
+  </si>
+  <si>
+    <t>龙之怒</t>
+  </si>
+  <si>
+    <t>兑换图鉴龙之刀*1</t>
+  </si>
+  <si>
+    <t>龙之刀</t>
+  </si>
+  <si>
+    <t>兑换图鉴龙之杖*1</t>
+  </si>
+  <si>
+    <t>龙之杖</t>
+  </si>
+  <si>
+    <t>兑换图鉴龙之剑*1</t>
+  </si>
+  <si>
+    <t>龙之剑</t>
+  </si>
+  <si>
+    <t>兑换图鉴神鉴·白*1</t>
+  </si>
+  <si>
+    <t>神鉴·白</t>
+  </si>
+  <si>
+    <t>兑换图鉴神鉴·绿*1</t>
+  </si>
+  <si>
+    <t>神鉴·绿</t>
+  </si>
+  <si>
+    <t>兑换图鉴神鉴·蓝*1</t>
+  </si>
+  <si>
+    <t>神鉴·蓝</t>
+  </si>
+  <si>
+    <t>兑换图鉴神鉴·紫*1</t>
+  </si>
+  <si>
+    <t>神鉴·紫</t>
+  </si>
+  <si>
+    <t>兑换图鉴神鉴·橙*1</t>
+  </si>
+  <si>
+    <t>神鉴·橙</t>
+  </si>
+  <si>
+    <t>兑换图鉴神鉴·红*1</t>
+  </si>
+  <si>
+    <t>神鉴·红</t>
   </si>
   <si>
     <t>2000</t>
@@ -1076,8 +1139,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1427,18 +1490,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O95"/>
+  <dimension ref="C1:O105"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="15.3666666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.2583333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.3628318584071" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.2566371681416" style="1" customWidth="1"/>
     <col min="7" max="7" width="12" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5044247787611" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1238938053097" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.8761061946903" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.50442477876106" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5044247787611" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1575,7 +1638,7 @@
         <v>100</v>
       </c>
       <c r="M6" s="1">
-        <f t="shared" ref="M6:M9" si="0">F6*G6</f>
+        <f t="shared" ref="M6:M14" si="0">F6*G6</f>
         <v>50400</v>
       </c>
     </row>
@@ -1719,7 +1782,7 @@
         <v>1</v>
       </c>
       <c r="M10" s="1">
-        <f t="shared" ref="M10:M45" si="1">F10*G10</f>
+        <f t="shared" si="0"/>
         <v>60000</v>
       </c>
     </row>
@@ -1755,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>60000</v>
       </c>
     </row>
@@ -1791,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="M12" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>60000</v>
       </c>
     </row>
@@ -1820,14 +1883,14 @@
       <c r="J13" s="1">
         <v>4</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <v>15</v>
       </c>
       <c r="L13" s="1">
         <v>1</v>
       </c>
       <c r="M13" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
     </row>
@@ -1856,14 +1919,14 @@
       <c r="J14" s="1">
         <v>4</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <v>16</v>
       </c>
       <c r="L14" s="1">
         <v>1</v>
       </c>
       <c r="M14" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
     </row>
@@ -1892,14 +1955,14 @@
       <c r="J15" s="1">
         <v>4</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <v>17</v>
       </c>
       <c r="L15" s="1">
         <v>1</v>
       </c>
       <c r="M15" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="M15:M30" si="1">F15*G15</f>
         <v>100000</v>
       </c>
     </row>
@@ -2097,7 +2160,7 @@
         <v>45</v>
       </c>
       <c r="G21" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>46</v>
@@ -2106,17 +2169,17 @@
         <v>47</v>
       </c>
       <c r="J21" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K21" s="1">
-        <v>13</v>
+        <v>1999989</v>
       </c>
       <c r="L21" s="1">
         <v>1</v>
       </c>
       <c r="M21" s="1">
         <f t="shared" si="1"/>
-        <v>2000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:13">
@@ -2130,10 +2193,10 @@
         <v>0</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="G22" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>48</v>
@@ -2142,17 +2205,17 @@
         <v>49</v>
       </c>
       <c r="J22" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K22" s="1">
-        <v>8</v>
+        <v>1999990</v>
       </c>
       <c r="L22" s="1">
         <v>1</v>
       </c>
       <c r="M22" s="1">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:13">
@@ -2166,29 +2229,29 @@
         <v>0</v>
       </c>
       <c r="F23" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" s="1">
+        <v>100</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G23" s="1">
-        <v>1</v>
-      </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="J23" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K23" s="1">
-        <v>9</v>
+        <v>1999991</v>
       </c>
       <c r="L23" s="1">
         <v>1</v>
       </c>
       <c r="M23" s="1">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:13">
@@ -2202,29 +2265,29 @@
         <v>0</v>
       </c>
       <c r="F24" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="1">
+        <v>100</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G24" s="1">
-        <v>10</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="J24" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K24" s="1">
-        <v>22</v>
+        <v>1999992</v>
       </c>
       <c r="L24" s="1">
         <v>1</v>
       </c>
       <c r="M24" s="1">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:13">
@@ -2237,30 +2300,30 @@
       <c r="E25" s="1">
         <v>0</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>56</v>
+      <c r="F25" s="1">
+        <v>1000</v>
       </c>
       <c r="G25" s="1">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J25" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K25" s="1">
-        <v>26</v>
+        <v>1999001</v>
       </c>
       <c r="L25" s="1">
         <v>1</v>
       </c>
       <c r="M25" s="1">
         <f t="shared" si="1"/>
-        <v>250000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:13">
@@ -2273,30 +2336,30 @@
       <c r="E26" s="1">
         <v>0</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>59</v>
+      <c r="F26" s="1">
+        <v>2000</v>
       </c>
       <c r="G26" s="1">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J26" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K26" s="1">
-        <v>25</v>
+        <v>1999002</v>
       </c>
       <c r="L26" s="1">
         <v>1</v>
       </c>
       <c r="M26" s="1">
         <f t="shared" si="1"/>
-        <v>400000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:13">
@@ -2309,30 +2372,30 @@
       <c r="E27" s="1">
         <v>0</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>62</v>
+      <c r="F27" s="1">
+        <v>3000</v>
       </c>
       <c r="G27" s="1">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="J27" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K27" s="1">
-        <v>28</v>
+        <v>1999003</v>
       </c>
       <c r="L27" s="1">
         <v>1</v>
       </c>
       <c r="M27" s="1">
         <f t="shared" si="1"/>
-        <v>1800000</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:13">
@@ -2345,30 +2408,30 @@
       <c r="E28" s="1">
         <v>0</v>
       </c>
-      <c r="F28" s="7" t="s">
-        <v>65</v>
+      <c r="F28" s="1">
+        <v>4000</v>
       </c>
       <c r="G28" s="1">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="J28" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K28" s="1">
-        <v>30</v>
+        <v>1999004</v>
       </c>
       <c r="L28" s="1">
         <v>1</v>
       </c>
       <c r="M28" s="1">
         <f t="shared" si="1"/>
-        <v>1200000</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:13">
@@ -2381,30 +2444,30 @@
       <c r="E29" s="1">
         <v>0</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>68</v>
+      <c r="F29" s="1">
+        <v>5000</v>
       </c>
       <c r="G29" s="1">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="J29" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K29" s="1">
-        <v>31</v>
+        <v>1999005</v>
       </c>
       <c r="L29" s="1">
         <v>1</v>
       </c>
       <c r="M29" s="1">
         <f t="shared" si="1"/>
-        <v>1000000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:13">
@@ -2417,30 +2480,30 @@
       <c r="E30" s="1">
         <v>0</v>
       </c>
-      <c r="F30" s="7" t="s">
-        <v>71</v>
+      <c r="F30" s="1">
+        <v>6000</v>
       </c>
       <c r="G30" s="1">
-        <v>400</v>
+        <v>11</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="J30" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K30" s="1">
-        <v>4021</v>
+        <v>1999006</v>
       </c>
       <c r="L30" s="1">
         <v>1</v>
       </c>
       <c r="M30" s="1">
         <f t="shared" si="1"/>
-        <v>2000000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:13">
@@ -2454,29 +2517,29 @@
         <v>0</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G31" s="1">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="J31" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K31" s="1">
-        <v>4022</v>
+        <v>13</v>
       </c>
       <c r="L31" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M31" s="1">
-        <f t="shared" si="1"/>
-        <v>1000000</v>
+        <f t="shared" ref="M31:M56" si="2">F31*G31</f>
+        <v>2000</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:13">
@@ -2489,30 +2552,30 @@
       <c r="E32" s="1">
         <v>0</v>
       </c>
-      <c r="F32" s="1">
-        <v>3000</v>
+      <c r="F32" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="G32" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="J32" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K32" s="1">
-        <v>4011</v>
+        <v>8</v>
       </c>
       <c r="L32" s="1">
         <v>1</v>
       </c>
       <c r="M32" s="1">
-        <f t="shared" si="1"/>
-        <v>300000</v>
+        <f t="shared" si="2"/>
+        <v>500</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:13">
@@ -2525,33 +2588,33 @@
       <c r="E33" s="1">
         <v>0</v>
       </c>
-      <c r="F33" s="1">
-        <v>20000</v>
+      <c r="F33" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="G33" s="1">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="J33" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K33" s="1">
-        <v>4020</v>
+        <v>9</v>
       </c>
       <c r="L33" s="1">
         <v>1</v>
       </c>
       <c r="M33" s="1">
-        <f t="shared" si="1"/>
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:13">
       <c r="C34" s="1">
         <v>29</v>
       </c>
@@ -2561,33 +2624,33 @@
       <c r="E34" s="1">
         <v>0</v>
       </c>
-      <c r="F34" s="1">
-        <v>488888</v>
+      <c r="F34" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="G34" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J34" s="1">
         <v>4</v>
       </c>
       <c r="K34" s="1">
-        <v>204</v>
+        <v>22</v>
       </c>
       <c r="L34" s="1">
         <v>1</v>
       </c>
       <c r="M34" s="1">
-        <f t="shared" si="1"/>
-        <v>488888</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <f t="shared" si="2"/>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:13">
       <c r="C35" s="1">
         <v>30</v>
       </c>
@@ -2595,32 +2658,32 @@
         <v>0</v>
       </c>
       <c r="E35" s="1">
+        <v>0</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G35" s="1">
+        <v>5</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J35" s="1">
         <v>4</v>
       </c>
-      <c r="F35" s="1">
-        <v>300000</v>
-      </c>
-      <c r="G35" s="1">
-        <v>2</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J35" s="1">
-        <v>5</v>
-      </c>
       <c r="K35" s="1">
-        <v>4027</v>
+        <v>26</v>
       </c>
       <c r="L35" s="1">
         <v>1</v>
       </c>
       <c r="M35" s="1">
-        <f t="shared" si="1"/>
-        <v>600000</v>
+        <f t="shared" si="2"/>
+        <v>250000</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:13">
@@ -2631,32 +2694,32 @@
         <v>0</v>
       </c>
       <c r="E36" s="1">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J36" s="1">
         <v>4</v>
       </c>
-      <c r="F36" s="1">
-        <v>20000</v>
-      </c>
-      <c r="G36" s="1">
-        <v>15</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J36" s="1">
-        <v>5</v>
-      </c>
-      <c r="K36" s="6">
-        <v>60000001</v>
+      <c r="K36" s="1">
+        <v>25</v>
       </c>
       <c r="L36" s="1">
         <v>1</v>
       </c>
       <c r="M36" s="1">
-        <f t="shared" si="1"/>
-        <v>300000</v>
+        <f t="shared" si="2"/>
+        <v>400000</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:13">
@@ -2667,35 +2730,35 @@
         <v>0</v>
       </c>
       <c r="E37" s="1">
+        <v>0</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G37" s="1">
+        <v>6</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="J37" s="1">
         <v>4</v>
       </c>
-      <c r="F37" s="1">
-        <v>15000</v>
-      </c>
-      <c r="G37" s="1">
-        <v>20</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J37" s="1">
-        <v>5</v>
-      </c>
-      <c r="K37" s="6">
-        <v>60000002</v>
+      <c r="K37" s="1">
+        <v>28</v>
       </c>
       <c r="L37" s="1">
         <v>1</v>
       </c>
       <c r="M37" s="1">
-        <f t="shared" si="1"/>
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="38" customFormat="1" customHeight="1" spans="3:15">
+        <f t="shared" si="2"/>
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:13">
       <c r="C38" s="1">
         <v>33</v>
       </c>
@@ -2703,37 +2766,35 @@
         <v>0</v>
       </c>
       <c r="E38" s="1">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G38" s="1">
+        <v>3</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J38" s="1">
         <v>4</v>
       </c>
-      <c r="F38" s="1">
-        <v>15000</v>
-      </c>
-      <c r="G38" s="1">
-        <v>20</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="J38" s="1">
-        <v>5</v>
-      </c>
-      <c r="K38" s="6">
-        <v>60000003</v>
+      <c r="K38" s="1">
+        <v>30</v>
       </c>
       <c r="L38" s="1">
         <v>1</v>
       </c>
       <c r="M38" s="1">
-        <f t="shared" si="1"/>
-        <v>300000</v>
-      </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-    </row>
-    <row r="39" customFormat="1" customHeight="1" spans="3:15">
+        <f t="shared" si="2"/>
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:13">
       <c r="C39" s="1">
         <v>34</v>
       </c>
@@ -2741,13 +2802,13 @@
         <v>0</v>
       </c>
       <c r="E39" s="1">
-        <v>4</v>
-      </c>
-      <c r="F39" s="1">
-        <v>25000</v>
+        <v>0</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="G39" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>90</v>
@@ -2756,22 +2817,20 @@
         <v>91</v>
       </c>
       <c r="J39" s="1">
-        <v>5</v>
-      </c>
-      <c r="K39" s="6">
-        <v>60000004</v>
+        <v>4</v>
+      </c>
+      <c r="K39" s="1">
+        <v>31</v>
       </c>
       <c r="L39" s="1">
         <v>1</v>
       </c>
       <c r="M39" s="1">
-        <f t="shared" si="1"/>
-        <v>250000</v>
-      </c>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-    </row>
-    <row r="40" customFormat="1" customHeight="1" spans="3:15">
+        <f t="shared" si="2"/>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:13">
       <c r="C40" s="1">
         <v>35</v>
       </c>
@@ -2779,37 +2838,35 @@
         <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>4</v>
-      </c>
-      <c r="F40" s="1">
-        <v>25000</v>
+        <v>0</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="G40" s="1">
-        <v>10</v>
+        <v>400</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J40" s="1">
         <v>5</v>
       </c>
-      <c r="K40" s="6">
-        <v>60000005</v>
+      <c r="K40" s="1">
+        <v>4021</v>
       </c>
       <c r="L40" s="1">
         <v>1</v>
       </c>
       <c r="M40" s="1">
-        <f t="shared" si="1"/>
-        <v>250000</v>
-      </c>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-    </row>
-    <row r="41" customFormat="1" customHeight="1" spans="3:15">
+        <f t="shared" si="2"/>
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:13">
       <c r="C41" s="1">
         <v>36</v>
       </c>
@@ -2817,37 +2874,35 @@
         <v>0</v>
       </c>
       <c r="E41" s="1">
-        <v>4</v>
-      </c>
-      <c r="F41" s="1">
-        <v>20000</v>
+        <v>0</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="G41" s="1">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J41" s="1">
         <v>5</v>
       </c>
-      <c r="K41" s="6">
-        <v>60000006</v>
+      <c r="K41" s="1">
+        <v>4022</v>
       </c>
       <c r="L41" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M41" s="1">
-        <f t="shared" si="1"/>
-        <v>300000</v>
-      </c>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-    </row>
-    <row r="42" customFormat="1" customHeight="1" spans="3:15">
+        <f t="shared" si="2"/>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:13">
       <c r="C42" s="1">
         <v>37</v>
       </c>
@@ -2855,37 +2910,35 @@
         <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F42" s="1">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="G42" s="1">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J42" s="1">
         <v>5</v>
       </c>
-      <c r="K42" s="6">
-        <v>60000007</v>
+      <c r="K42" s="1">
+        <v>4011</v>
       </c>
       <c r="L42" s="1">
         <v>1</v>
       </c>
       <c r="M42" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>300000</v>
       </c>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-    </row>
-    <row r="43" customFormat="1" customHeight="1" spans="3:15">
+    </row>
+    <row r="43" customHeight="1" spans="3:13">
       <c r="C43" s="1">
         <v>38</v>
       </c>
@@ -2893,37 +2946,35 @@
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F43" s="1">
         <v>20000</v>
       </c>
       <c r="G43" s="1">
-        <v>15</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="I43" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H43" s="1" t="s">
         <v>99</v>
       </c>
+      <c r="I43" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="J43" s="1">
         <v>5</v>
       </c>
-      <c r="K43" s="6">
-        <v>60000008</v>
+      <c r="K43" s="1">
+        <v>4020</v>
       </c>
       <c r="L43" s="1">
         <v>1</v>
       </c>
       <c r="M43" s="1">
-        <f t="shared" si="1"/>
-        <v>300000</v>
-      </c>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-    </row>
-    <row r="44" customFormat="1" customHeight="1" spans="3:15">
+        <f t="shared" si="2"/>
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C44" s="1">
         <v>39</v>
       </c>
@@ -2931,37 +2982,35 @@
         <v>0</v>
       </c>
       <c r="E44" s="1">
+        <v>0</v>
+      </c>
+      <c r="F44" s="1">
+        <v>488888</v>
+      </c>
+      <c r="G44" s="1">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="J44" s="1">
         <v>4</v>
       </c>
-      <c r="F44" s="1">
-        <v>20000</v>
-      </c>
-      <c r="G44" s="1">
-        <v>15</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J44" s="1">
-        <v>5</v>
-      </c>
-      <c r="K44" s="6">
-        <v>60000009</v>
+      <c r="K44" s="1">
+        <v>204</v>
       </c>
       <c r="L44" s="1">
         <v>1</v>
       </c>
       <c r="M44" s="1">
-        <f t="shared" si="1"/>
-        <v>300000</v>
-      </c>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-    </row>
-    <row r="45" customFormat="1" customHeight="1" spans="3:15">
+        <f t="shared" si="2"/>
+        <v>488888</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C45" s="1">
         <v>40</v>
       </c>
@@ -2972,34 +3021,32 @@
         <v>4</v>
       </c>
       <c r="F45" s="1">
-        <v>20000</v>
+        <v>300000</v>
       </c>
       <c r="G45" s="1">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J45" s="1">
         <v>5</v>
       </c>
-      <c r="K45" s="6">
-        <v>60000010</v>
+      <c r="K45" s="1">
+        <v>4027</v>
       </c>
       <c r="L45" s="1">
         <v>1</v>
       </c>
       <c r="M45" s="1">
-        <f t="shared" si="1"/>
-        <v>400000</v>
-      </c>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-    </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <f t="shared" si="2"/>
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:13">
       <c r="C46" s="1">
         <v>41</v>
       </c>
@@ -3007,686 +3054,675 @@
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F46" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G46" s="1">
+        <v>15</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J46" s="1">
+        <v>5</v>
+      </c>
+      <c r="K46" s="5">
+        <v>60000001</v>
+      </c>
+      <c r="L46" s="1">
+        <v>1</v>
+      </c>
+      <c r="M46" s="1">
+        <f t="shared" si="2"/>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:13">
+      <c r="C47" s="1">
+        <v>42</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0</v>
+      </c>
+      <c r="E47" s="1">
+        <v>4</v>
+      </c>
+      <c r="F47" s="1">
+        <v>15000</v>
+      </c>
+      <c r="G47" s="1">
+        <v>20</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J47" s="1">
+        <v>5</v>
+      </c>
+      <c r="K47" s="5">
+        <v>60000002</v>
+      </c>
+      <c r="L47" s="1">
+        <v>1</v>
+      </c>
+      <c r="M47" s="1">
+        <f t="shared" si="2"/>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C48" s="1">
+        <v>43</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0</v>
+      </c>
+      <c r="E48" s="1">
+        <v>4</v>
+      </c>
+      <c r="F48" s="1">
+        <v>15000</v>
+      </c>
+      <c r="G48" s="1">
+        <v>20</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J48" s="1">
+        <v>5</v>
+      </c>
+      <c r="K48" s="5">
+        <v>60000003</v>
+      </c>
+      <c r="L48" s="1">
+        <v>1</v>
+      </c>
+      <c r="M48" s="1">
+        <f t="shared" si="2"/>
+        <v>300000</v>
+      </c>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C49" s="1">
+        <v>44</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0</v>
+      </c>
+      <c r="E49" s="1">
+        <v>4</v>
+      </c>
+      <c r="F49" s="1">
+        <v>25000</v>
+      </c>
+      <c r="G49" s="1">
+        <v>10</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J49" s="1">
+        <v>5</v>
+      </c>
+      <c r="K49" s="5">
+        <v>60000004</v>
+      </c>
+      <c r="L49" s="1">
+        <v>1</v>
+      </c>
+      <c r="M49" s="1">
+        <f t="shared" si="2"/>
+        <v>250000</v>
+      </c>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C50" s="1">
+        <v>45</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0</v>
+      </c>
+      <c r="E50" s="1">
+        <v>4</v>
+      </c>
+      <c r="F50" s="1">
+        <v>25000</v>
+      </c>
+      <c r="G50" s="1">
+        <v>10</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J50" s="1">
+        <v>5</v>
+      </c>
+      <c r="K50" s="5">
+        <v>60000005</v>
+      </c>
+      <c r="L50" s="1">
+        <v>1</v>
+      </c>
+      <c r="M50" s="1">
+        <f t="shared" si="2"/>
+        <v>250000</v>
+      </c>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C51" s="1">
+        <v>46</v>
+      </c>
+      <c r="D51" s="1">
+        <v>0</v>
+      </c>
+      <c r="E51" s="1">
+        <v>4</v>
+      </c>
+      <c r="F51" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G51" s="1">
+        <v>15</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J51" s="1">
+        <v>5</v>
+      </c>
+      <c r="K51" s="5">
+        <v>60000006</v>
+      </c>
+      <c r="L51" s="1">
+        <v>1</v>
+      </c>
+      <c r="M51" s="1">
+        <f t="shared" si="2"/>
+        <v>300000</v>
+      </c>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C52" s="1">
+        <v>47</v>
+      </c>
+      <c r="D52" s="1">
+        <v>0</v>
+      </c>
+      <c r="E52" s="1">
+        <v>4</v>
+      </c>
+      <c r="F52" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G52" s="1">
+        <v>15</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J52" s="1">
+        <v>5</v>
+      </c>
+      <c r="K52" s="5">
+        <v>60000007</v>
+      </c>
+      <c r="L52" s="1">
+        <v>1</v>
+      </c>
+      <c r="M52" s="1">
+        <f t="shared" si="2"/>
+        <v>300000</v>
+      </c>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+    </row>
+    <row r="53" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C53" s="1">
+        <v>48</v>
+      </c>
+      <c r="D53" s="1">
+        <v>0</v>
+      </c>
+      <c r="E53" s="1">
+        <v>4</v>
+      </c>
+      <c r="F53" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G53" s="1">
+        <v>15</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J53" s="1">
+        <v>5</v>
+      </c>
+      <c r="K53" s="5">
+        <v>60000008</v>
+      </c>
+      <c r="L53" s="1">
+        <v>1</v>
+      </c>
+      <c r="M53" s="1">
+        <f t="shared" si="2"/>
+        <v>300000</v>
+      </c>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+    </row>
+    <row r="54" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C54" s="1">
+        <v>49</v>
+      </c>
+      <c r="D54" s="1">
+        <v>0</v>
+      </c>
+      <c r="E54" s="1">
+        <v>4</v>
+      </c>
+      <c r="F54" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G54" s="1">
+        <v>15</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J54" s="1">
+        <v>5</v>
+      </c>
+      <c r="K54" s="5">
+        <v>60000009</v>
+      </c>
+      <c r="L54" s="1">
+        <v>1</v>
+      </c>
+      <c r="M54" s="1">
+        <f t="shared" si="2"/>
+        <v>300000</v>
+      </c>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
+    </row>
+    <row r="55" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C55" s="1">
+        <v>50</v>
+      </c>
+      <c r="D55" s="1">
+        <v>0</v>
+      </c>
+      <c r="E55" s="1">
+        <v>4</v>
+      </c>
+      <c r="F55" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G55" s="1">
+        <v>20</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J55" s="1">
+        <v>5</v>
+      </c>
+      <c r="K55" s="5">
+        <v>60000010</v>
+      </c>
+      <c r="L55" s="1">
+        <v>1</v>
+      </c>
+      <c r="M55" s="1">
+        <f t="shared" si="2"/>
+        <v>400000</v>
+      </c>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+    </row>
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C56" s="1">
+        <v>51</v>
+      </c>
+      <c r="D56" s="1">
+        <v>0</v>
+      </c>
+      <c r="E56" s="1">
+        <v>0</v>
+      </c>
+      <c r="F56" s="1">
         <v>50000</v>
       </c>
-      <c r="G46" s="1">
+      <c r="G56" s="1">
         <v>30</v>
       </c>
-      <c r="H46" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="J46" s="1">
+      <c r="H56" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J56" s="1">
         <v>4</v>
       </c>
-      <c r="K46" s="1">
+      <c r="K56" s="1">
         <v>24</v>
       </c>
-      <c r="L46" s="1">
-        <v>1</v>
-      </c>
-      <c r="M46" s="1">
-        <f>F46*G46</f>
+      <c r="L56" s="1">
+        <v>1</v>
+      </c>
+      <c r="M56" s="1">
+        <f t="shared" si="2"/>
         <v>1500000</v>
       </c>
     </row>
-    <row r="47" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-    </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C48" s="1">
-        <v>102</v>
-      </c>
-      <c r="D48" s="1">
-        <v>1</v>
-      </c>
-      <c r="E48" s="1">
-        <v>0</v>
-      </c>
-      <c r="F48" s="1">
-        <v>100</v>
-      </c>
-      <c r="G48" s="1">
-        <f t="shared" ref="G48:G55" si="2">N48*O48</f>
-        <v>300</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J48" s="1">
-        <v>5</v>
-      </c>
-      <c r="K48" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L48" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M48" s="1">
-        <f t="shared" ref="M48:M55" si="3">F48*G48</f>
-        <v>30000</v>
-      </c>
-      <c r="N48" s="1">
-        <v>1</v>
-      </c>
-      <c r="O48" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C49" s="1">
-        <v>103</v>
-      </c>
-      <c r="D49" s="1">
-        <v>1</v>
-      </c>
-      <c r="E49" s="1">
-        <v>0</v>
-      </c>
-      <c r="F49" s="1">
-        <v>100</v>
-      </c>
-      <c r="G49" s="1">
-        <f t="shared" si="2"/>
-        <v>500</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="J49" s="1">
-        <v>5</v>
-      </c>
-      <c r="K49" s="1">
-        <v>4101</v>
-      </c>
-      <c r="L49" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M49" s="1">
-        <f t="shared" si="3"/>
-        <v>50000</v>
-      </c>
-      <c r="N49" s="1">
-        <v>1</v>
-      </c>
-      <c r="O49" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C50" s="1">
-        <v>104</v>
-      </c>
-      <c r="D50" s="1">
-        <v>1</v>
-      </c>
-      <c r="E50" s="1">
-        <v>0</v>
-      </c>
-      <c r="F50" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G50" s="1">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J50" s="1">
-        <v>15</v>
-      </c>
-      <c r="K50" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L50" s="1">
-        <v>100</v>
-      </c>
-      <c r="M50" s="1">
-        <f t="shared" si="3"/>
-        <v>6000</v>
-      </c>
-      <c r="N50" s="1">
-        <v>1</v>
-      </c>
-      <c r="O50" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C51" s="1">
-        <v>105</v>
-      </c>
-      <c r="D51" s="1">
-        <v>1</v>
-      </c>
-      <c r="E51" s="1">
-        <v>0</v>
-      </c>
-      <c r="F51" s="1">
-        <v>500</v>
-      </c>
-      <c r="G51" s="1">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J51" s="1">
-        <v>5</v>
-      </c>
-      <c r="K51" s="1">
-        <v>4012</v>
-      </c>
-      <c r="L51" s="1">
-        <v>200</v>
-      </c>
-      <c r="M51" s="1">
-        <f t="shared" si="3"/>
-        <v>10000</v>
-      </c>
-      <c r="N51" s="1">
-        <v>1</v>
-      </c>
-      <c r="O51" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C52" s="1">
-        <v>106</v>
-      </c>
-      <c r="D52" s="1">
-        <v>1</v>
-      </c>
-      <c r="E52" s="1">
-        <v>1</v>
-      </c>
-      <c r="F52" s="1">
-        <v>15000</v>
-      </c>
-      <c r="G52" s="1">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="J52" s="1">
-        <v>5</v>
-      </c>
-      <c r="K52" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L52" s="1">
-        <v>1</v>
-      </c>
-      <c r="M52" s="1">
-        <f t="shared" si="3"/>
-        <v>120000</v>
-      </c>
-      <c r="N52" s="1">
-        <v>1</v>
-      </c>
-      <c r="O52" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C53" s="1">
-        <v>107</v>
-      </c>
-      <c r="D53" s="1">
-        <v>1</v>
-      </c>
-      <c r="E53" s="1">
-        <v>0</v>
-      </c>
-      <c r="F53" s="1">
-        <v>500</v>
-      </c>
-      <c r="G53" s="1">
-        <f t="shared" si="2"/>
-        <v>40</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J53" s="1">
-        <v>5</v>
-      </c>
-      <c r="K53" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L53" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M53" s="1">
-        <f t="shared" si="3"/>
-        <v>20000</v>
-      </c>
-      <c r="N53" s="1">
-        <v>1</v>
-      </c>
-      <c r="O53" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C54" s="1">
-        <v>108</v>
-      </c>
-      <c r="D54" s="1">
-        <v>1</v>
-      </c>
-      <c r="E54" s="1">
-        <v>0</v>
-      </c>
-      <c r="F54" s="1">
-        <v>500</v>
-      </c>
-      <c r="G54" s="1">
-        <f t="shared" si="2"/>
-        <v>40</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J54" s="1">
-        <v>5</v>
-      </c>
-      <c r="K54" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L54" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M54" s="1">
-        <f t="shared" si="3"/>
-        <v>20000</v>
-      </c>
-      <c r="N54" s="1">
-        <v>1</v>
-      </c>
-      <c r="O54" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C55" s="1">
-        <v>109</v>
-      </c>
-      <c r="D55" s="1">
-        <v>1</v>
-      </c>
-      <c r="E55" s="1">
-        <v>6</v>
-      </c>
-      <c r="F55" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G55" s="1">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J55" s="1">
-        <v>5</v>
-      </c>
-      <c r="K55" s="1">
-        <v>4026</v>
-      </c>
-      <c r="L55" s="1">
-        <v>1</v>
-      </c>
-      <c r="M55" s="1">
-        <f t="shared" si="3"/>
-        <v>150000</v>
-      </c>
-      <c r="N55" s="1">
-        <v>1</v>
-      </c>
-      <c r="O55" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C57" s="1">
-        <v>201</v>
-      </c>
-      <c r="D57" s="1">
-        <v>2</v>
-      </c>
-      <c r="E57" s="1">
-        <v>0</v>
-      </c>
-      <c r="F57" s="5">
-        <v>200</v>
-      </c>
-      <c r="G57" s="1">
-        <f t="shared" ref="G57:G64" si="4">N57*O57</f>
-        <v>300</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J57" s="1">
-        <v>5</v>
-      </c>
-      <c r="K57" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L57" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M57" s="1">
-        <f t="shared" ref="M57:M64" si="5">F57*G57</f>
-        <v>60000</v>
-      </c>
-      <c r="N57" s="1">
-        <v>1</v>
-      </c>
-      <c r="O57" s="1">
-        <v>300</v>
-      </c>
+    <row r="57" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C58" s="1">
-        <v>202</v>
+        <v>102</v>
       </c>
       <c r="D58" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
       </c>
-      <c r="F58" s="5">
-        <v>200</v>
+      <c r="F58" s="1">
+        <v>100</v>
       </c>
       <c r="G58" s="1">
-        <f t="shared" si="4"/>
-        <v>500</v>
+        <f t="shared" ref="G58:G65" si="3">N58*O58</f>
+        <v>300</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="J58" s="1">
         <v>5</v>
       </c>
       <c r="K58" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="L58" s="1">
         <v>1000</v>
       </c>
       <c r="M58" s="1">
-        <f t="shared" si="5"/>
-        <v>100000</v>
+        <f t="shared" ref="M58:M65" si="4">F58*G58</f>
+        <v>30000</v>
       </c>
       <c r="N58" s="1">
         <v>1</v>
       </c>
       <c r="O58" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C59" s="1">
-        <v>203</v>
+        <v>103</v>
       </c>
       <c r="D59" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
       </c>
-      <c r="F59" s="5">
-        <v>2000</v>
+      <c r="F59" s="1">
+        <v>100</v>
       </c>
       <c r="G59" s="1">
+        <f t="shared" si="3"/>
+        <v>500</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J59" s="1">
+        <v>5</v>
+      </c>
+      <c r="K59" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L59" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M59" s="1">
         <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J59" s="1">
-        <v>15</v>
-      </c>
-      <c r="K59" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L59" s="1">
-        <v>100</v>
-      </c>
-      <c r="M59" s="1">
-        <f t="shared" si="5"/>
-        <v>12000</v>
+        <v>50000</v>
       </c>
       <c r="N59" s="1">
         <v>1</v>
       </c>
       <c r="O59" s="1">
-        <v>6</v>
+        <v>500</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C60" s="1">
-        <v>204</v>
+        <v>104</v>
       </c>
       <c r="D60" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
       </c>
-      <c r="F60" s="5">
+      <c r="F60" s="1">
         <v>1000</v>
       </c>
       <c r="G60" s="1">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J60" s="1">
+        <v>15</v>
+      </c>
+      <c r="K60" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L60" s="1">
+        <v>100</v>
+      </c>
+      <c r="M60" s="1">
         <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J60" s="1">
-        <v>5</v>
-      </c>
-      <c r="K60" s="1">
-        <v>4012</v>
-      </c>
-      <c r="L60" s="1">
-        <v>200</v>
-      </c>
-      <c r="M60" s="1">
-        <f t="shared" si="5"/>
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="N60" s="1">
         <v>1</v>
       </c>
       <c r="O60" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C61" s="1">
-        <v>205</v>
+        <v>105</v>
       </c>
       <c r="D61" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="1">
-        <v>1</v>
-      </c>
-      <c r="F61" s="5">
-        <v>30000</v>
+        <v>0</v>
+      </c>
+      <c r="F61" s="1">
+        <v>500</v>
       </c>
       <c r="G61" s="1">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J61" s="1">
+        <v>5</v>
+      </c>
+      <c r="K61" s="1">
+        <v>4012</v>
+      </c>
+      <c r="L61" s="1">
+        <v>200</v>
+      </c>
+      <c r="M61" s="1">
         <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="J61" s="1">
-        <v>5</v>
-      </c>
-      <c r="K61" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L61" s="1">
-        <v>1</v>
-      </c>
-      <c r="M61" s="1">
-        <f t="shared" si="5"/>
-        <v>240000</v>
+        <v>10000</v>
       </c>
       <c r="N61" s="1">
         <v>1</v>
       </c>
       <c r="O61" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C62" s="1">
-        <v>206</v>
+        <v>106</v>
       </c>
       <c r="D62" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="1">
-        <v>0</v>
-      </c>
-      <c r="F62" s="5">
-        <v>1000</v>
+        <v>1</v>
+      </c>
+      <c r="F62" s="1">
+        <v>15000</v>
       </c>
       <c r="G62" s="1">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J62" s="1">
+        <v>5</v>
+      </c>
+      <c r="K62" s="1">
+        <v>4019</v>
+      </c>
+      <c r="L62" s="1">
+        <v>1</v>
+      </c>
+      <c r="M62" s="1">
         <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J62" s="1">
-        <v>5</v>
-      </c>
-      <c r="K62" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L62" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M62" s="1">
-        <f t="shared" si="5"/>
-        <v>40000</v>
+        <v>120000</v>
       </c>
       <c r="N62" s="1">
         <v>1</v>
       </c>
       <c r="O62" s="1">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C63" s="1">
-        <v>207</v>
+        <v>107</v>
       </c>
       <c r="D63" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
       </c>
-      <c r="F63" s="5">
-        <v>1000</v>
+      <c r="F63" s="1">
+        <v>500</v>
       </c>
       <c r="G63" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J63" s="1">
+        <v>5</v>
+      </c>
+      <c r="K63" s="1">
+        <v>4001</v>
+      </c>
+      <c r="L63" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="M63" s="1">
         <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J63" s="1">
-        <v>5</v>
-      </c>
-      <c r="K63" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L63" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M63" s="1">
-        <f t="shared" si="5"/>
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="N63" s="1">
         <v>1</v>
@@ -3697,340 +3733,340 @@
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C64" s="1">
-        <v>208</v>
+        <v>108</v>
       </c>
       <c r="D64" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" s="1">
+        <v>0</v>
+      </c>
+      <c r="F64" s="1">
+        <v>500</v>
+      </c>
+      <c r="G64" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J64" s="1">
+        <v>5</v>
+      </c>
+      <c r="K64" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L64" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M64" s="1">
+        <f t="shared" si="4"/>
+        <v>20000</v>
+      </c>
+      <c r="N64" s="1">
+        <v>1</v>
+      </c>
+      <c r="O64" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C65" s="1">
+        <v>109</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1</v>
+      </c>
+      <c r="E65" s="1">
         <v>6</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F65" s="1">
         <v>30000</v>
       </c>
-      <c r="G64" s="1">
+      <c r="G65" s="1">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J65" s="1">
+        <v>5</v>
+      </c>
+      <c r="K65" s="1">
+        <v>4026</v>
+      </c>
+      <c r="L65" s="1">
+        <v>1</v>
+      </c>
+      <c r="M65" s="1">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J64" s="1">
-        <v>5</v>
-      </c>
-      <c r="K64" s="1">
-        <v>4026</v>
-      </c>
-      <c r="L64" s="1">
-        <v>1</v>
-      </c>
-      <c r="M64" s="1">
-        <f t="shared" si="5"/>
         <v>150000</v>
       </c>
-      <c r="N64" s="1">
-        <v>1</v>
-      </c>
-      <c r="O64" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C66" s="1">
-        <v>211</v>
-      </c>
-      <c r="D66" s="1">
-        <v>3</v>
-      </c>
-      <c r="E66" s="1">
-        <v>0</v>
-      </c>
-      <c r="F66" s="1">
-        <v>400</v>
-      </c>
-      <c r="G66" s="1">
-        <f t="shared" ref="G66:G73" si="6">N66*O66</f>
-        <v>300</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J66" s="1">
-        <v>5</v>
-      </c>
-      <c r="K66" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L66" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M66" s="1">
-        <f t="shared" ref="M66:M73" si="7">F66*G66</f>
-        <v>120000</v>
-      </c>
-      <c r="N66" s="1">
-        <v>1</v>
-      </c>
-      <c r="O66" s="1">
-        <v>300</v>
+      <c r="N65" s="1">
+        <v>1</v>
+      </c>
+      <c r="O65" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C67" s="1">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="D67" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E67" s="1">
         <v>0</v>
       </c>
-      <c r="F67" s="1">
-        <v>400</v>
+      <c r="F67" s="6">
+        <v>200</v>
       </c>
       <c r="G67" s="1">
-        <f t="shared" si="6"/>
-        <v>500</v>
+        <f t="shared" ref="G67:G74" si="5">N67*O67</f>
+        <v>300</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="J67" s="1">
         <v>5</v>
       </c>
       <c r="K67" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="L67" s="1">
         <v>1000</v>
       </c>
       <c r="M67" s="1">
-        <f t="shared" si="7"/>
-        <v>200000</v>
+        <f t="shared" ref="M67:M74" si="6">F67*G67</f>
+        <v>60000</v>
       </c>
       <c r="N67" s="1">
         <v>1</v>
       </c>
       <c r="O67" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C68" s="1">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="D68" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E68" s="1">
         <v>0</v>
       </c>
-      <c r="F68" s="1">
-        <v>4000</v>
+      <c r="F68" s="6">
+        <v>200</v>
       </c>
       <c r="G68" s="1">
+        <f t="shared" si="5"/>
+        <v>500</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J68" s="1">
+        <v>5</v>
+      </c>
+      <c r="K68" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L68" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M68" s="1">
         <f t="shared" si="6"/>
-        <v>6</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J68" s="1">
-        <v>15</v>
-      </c>
-      <c r="K68" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L68" s="1">
-        <v>100</v>
-      </c>
-      <c r="M68" s="1">
-        <f t="shared" si="7"/>
-        <v>24000</v>
+        <v>100000</v>
       </c>
       <c r="N68" s="1">
         <v>1</v>
       </c>
       <c r="O68" s="1">
-        <v>6</v>
+        <v>500</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C69" s="1">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="D69" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69" s="1">
         <v>0</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69" s="6">
         <v>2000</v>
       </c>
       <c r="G69" s="1">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J69" s="1">
+        <v>15</v>
+      </c>
+      <c r="K69" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L69" s="1">
+        <v>100</v>
+      </c>
+      <c r="M69" s="1">
         <f t="shared" si="6"/>
-        <v>20</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J69" s="1">
-        <v>5</v>
-      </c>
-      <c r="K69" s="1">
-        <v>4012</v>
-      </c>
-      <c r="L69" s="1">
-        <v>200</v>
-      </c>
-      <c r="M69" s="1">
-        <f t="shared" si="7"/>
-        <v>40000</v>
+        <v>12000</v>
       </c>
       <c r="N69" s="1">
         <v>1</v>
       </c>
       <c r="O69" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C70" s="1">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="D70" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70" s="1">
-        <v>1</v>
-      </c>
-      <c r="F70" s="1">
-        <v>45000</v>
+        <v>0</v>
+      </c>
+      <c r="F70" s="6">
+        <v>1000</v>
       </c>
       <c r="G70" s="1">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J70" s="1">
+        <v>5</v>
+      </c>
+      <c r="K70" s="1">
+        <v>4012</v>
+      </c>
+      <c r="L70" s="1">
+        <v>200</v>
+      </c>
+      <c r="M70" s="1">
         <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="J70" s="1">
-        <v>5</v>
-      </c>
-      <c r="K70" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L70" s="1">
-        <v>1</v>
-      </c>
-      <c r="M70" s="1">
-        <f t="shared" si="7"/>
-        <v>360000</v>
+        <v>20000</v>
       </c>
       <c r="N70" s="1">
         <v>1</v>
       </c>
       <c r="O70" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C71" s="1">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D71" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71" s="1">
-        <v>0</v>
-      </c>
-      <c r="F71" s="1">
-        <v>2000</v>
+        <v>1</v>
+      </c>
+      <c r="F71" s="6">
+        <v>30000</v>
       </c>
       <c r="G71" s="1">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J71" s="1">
+        <v>5</v>
+      </c>
+      <c r="K71" s="1">
+        <v>4019</v>
+      </c>
+      <c r="L71" s="1">
+        <v>1</v>
+      </c>
+      <c r="M71" s="1">
         <f t="shared" si="6"/>
-        <v>40</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J71" s="1">
-        <v>5</v>
-      </c>
-      <c r="K71" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L71" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M71" s="1">
-        <f t="shared" si="7"/>
-        <v>80000</v>
+        <v>240000</v>
       </c>
       <c r="N71" s="1">
         <v>1</v>
       </c>
       <c r="O71" s="1">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C72" s="1">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D72" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E72" s="1">
         <v>0</v>
       </c>
-      <c r="F72" s="1">
-        <v>2000</v>
+      <c r="F72" s="6">
+        <v>1000</v>
       </c>
       <c r="G72" s="1">
+        <f t="shared" si="5"/>
+        <v>40</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J72" s="1">
+        <v>5</v>
+      </c>
+      <c r="K72" s="1">
+        <v>4001</v>
+      </c>
+      <c r="L72" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="M72" s="1">
         <f t="shared" si="6"/>
-        <v>40</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J72" s="1">
-        <v>5</v>
-      </c>
-      <c r="K72" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L72" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M72" s="1">
-        <f t="shared" si="7"/>
-        <v>80000</v>
+        <v>40000</v>
       </c>
       <c r="N72" s="1">
         <v>1</v>
@@ -4041,340 +4077,340 @@
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C73" s="1">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="D73" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E73" s="1">
+        <v>0</v>
+      </c>
+      <c r="F73" s="6">
+        <v>1000</v>
+      </c>
+      <c r="G73" s="1">
+        <f t="shared" si="5"/>
+        <v>40</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J73" s="1">
+        <v>5</v>
+      </c>
+      <c r="K73" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L73" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M73" s="1">
+        <f t="shared" si="6"/>
+        <v>40000</v>
+      </c>
+      <c r="N73" s="1">
+        <v>1</v>
+      </c>
+      <c r="O73" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="74" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C74" s="1">
+        <v>208</v>
+      </c>
+      <c r="D74" s="1">
+        <v>2</v>
+      </c>
+      <c r="E74" s="1">
         <v>6</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F74" s="1">
         <v>30000</v>
       </c>
-      <c r="G73" s="1">
+      <c r="G74" s="1">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J74" s="1">
+        <v>5</v>
+      </c>
+      <c r="K74" s="1">
+        <v>4026</v>
+      </c>
+      <c r="L74" s="1">
+        <v>1</v>
+      </c>
+      <c r="M74" s="1">
         <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J73" s="1">
-        <v>5</v>
-      </c>
-      <c r="K73" s="1">
-        <v>4026</v>
-      </c>
-      <c r="L73" s="1">
-        <v>1</v>
-      </c>
-      <c r="M73" s="1">
-        <f t="shared" si="7"/>
         <v>150000</v>
       </c>
-      <c r="N73" s="1">
-        <v>1</v>
-      </c>
-      <c r="O73" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C75" s="1">
-        <v>221</v>
-      </c>
-      <c r="D75" s="1">
-        <v>4</v>
-      </c>
-      <c r="E75" s="1">
-        <v>0</v>
-      </c>
-      <c r="F75" s="5">
-        <v>600</v>
-      </c>
-      <c r="G75" s="1">
-        <f t="shared" ref="G75:G82" si="8">N75*O75</f>
-        <v>300</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J75" s="1">
-        <v>5</v>
-      </c>
-      <c r="K75" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L75" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M75" s="1">
-        <f t="shared" ref="M75:M82" si="9">F75*G75</f>
-        <v>180000</v>
-      </c>
-      <c r="N75" s="1">
-        <v>1</v>
-      </c>
-      <c r="O75" s="1">
-        <v>300</v>
+      <c r="N74" s="1">
+        <v>1</v>
+      </c>
+      <c r="O74" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C76" s="1">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="D76" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E76" s="1">
         <v>0</v>
       </c>
-      <c r="F76" s="5">
-        <v>600</v>
+      <c r="F76" s="1">
+        <v>400</v>
       </c>
       <c r="G76" s="1">
-        <f t="shared" si="8"/>
-        <v>500</v>
+        <f t="shared" ref="G76:G83" si="7">N76*O76</f>
+        <v>300</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="J76" s="1">
         <v>5</v>
       </c>
       <c r="K76" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="L76" s="1">
         <v>1000</v>
       </c>
       <c r="M76" s="1">
-        <f t="shared" si="9"/>
-        <v>300000</v>
+        <f t="shared" ref="M76:M83" si="8">F76*G76</f>
+        <v>120000</v>
       </c>
       <c r="N76" s="1">
         <v>1</v>
       </c>
       <c r="O76" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C77" s="1">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D77" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E77" s="1">
         <v>0</v>
       </c>
-      <c r="F77" s="5">
-        <v>6000</v>
+      <c r="F77" s="1">
+        <v>400</v>
       </c>
       <c r="G77" s="1">
+        <f t="shared" si="7"/>
+        <v>500</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J77" s="1">
+        <v>5</v>
+      </c>
+      <c r="K77" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L77" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M77" s="1">
         <f t="shared" si="8"/>
-        <v>6</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J77" s="1">
-        <v>15</v>
-      </c>
-      <c r="K77" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L77" s="1">
-        <v>100</v>
-      </c>
-      <c r="M77" s="1">
-        <f t="shared" si="9"/>
-        <v>36000</v>
+        <v>200000</v>
       </c>
       <c r="N77" s="1">
         <v>1</v>
       </c>
       <c r="O77" s="1">
-        <v>6</v>
+        <v>500</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C78" s="1">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="D78" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E78" s="1">
         <v>0</v>
       </c>
-      <c r="F78" s="5">
-        <v>3000</v>
+      <c r="F78" s="1">
+        <v>4000</v>
       </c>
       <c r="G78" s="1">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J78" s="1">
+        <v>15</v>
+      </c>
+      <c r="K78" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L78" s="1">
+        <v>100</v>
+      </c>
+      <c r="M78" s="1">
         <f t="shared" si="8"/>
-        <v>20</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J78" s="1">
-        <v>5</v>
-      </c>
-      <c r="K78" s="1">
-        <v>4012</v>
-      </c>
-      <c r="L78" s="1">
-        <v>200</v>
-      </c>
-      <c r="M78" s="1">
-        <f t="shared" si="9"/>
-        <v>60000</v>
+        <v>24000</v>
       </c>
       <c r="N78" s="1">
         <v>1</v>
       </c>
       <c r="O78" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C79" s="1">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="D79" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E79" s="1">
-        <v>1</v>
-      </c>
-      <c r="F79" s="5">
-        <v>60000</v>
+        <v>0</v>
+      </c>
+      <c r="F79" s="1">
+        <v>2000</v>
       </c>
       <c r="G79" s="1">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J79" s="1">
+        <v>5</v>
+      </c>
+      <c r="K79" s="1">
+        <v>4012</v>
+      </c>
+      <c r="L79" s="1">
+        <v>200</v>
+      </c>
+      <c r="M79" s="1">
         <f t="shared" si="8"/>
-        <v>8</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="J79" s="1">
-        <v>5</v>
-      </c>
-      <c r="K79" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L79" s="1">
-        <v>1</v>
-      </c>
-      <c r="M79" s="1">
-        <f t="shared" si="9"/>
-        <v>480000</v>
+        <v>40000</v>
       </c>
       <c r="N79" s="1">
         <v>1</v>
       </c>
       <c r="O79" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C80" s="1">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="D80" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E80" s="1">
-        <v>0</v>
-      </c>
-      <c r="F80" s="5">
-        <v>3000</v>
+        <v>1</v>
+      </c>
+      <c r="F80" s="1">
+        <v>45000</v>
       </c>
       <c r="G80" s="1">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J80" s="1">
+        <v>5</v>
+      </c>
+      <c r="K80" s="1">
+        <v>4019</v>
+      </c>
+      <c r="L80" s="1">
+        <v>1</v>
+      </c>
+      <c r="M80" s="1">
         <f t="shared" si="8"/>
-        <v>40</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J80" s="1">
-        <v>5</v>
-      </c>
-      <c r="K80" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L80" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M80" s="1">
-        <f t="shared" si="9"/>
-        <v>120000</v>
+        <v>360000</v>
       </c>
       <c r="N80" s="1">
         <v>1</v>
       </c>
       <c r="O80" s="1">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C81" s="1">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D81" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E81" s="1">
         <v>0</v>
       </c>
-      <c r="F81" s="5">
-        <v>3000</v>
+      <c r="F81" s="1">
+        <v>2000</v>
       </c>
       <c r="G81" s="1">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J81" s="1">
+        <v>5</v>
+      </c>
+      <c r="K81" s="1">
+        <v>4001</v>
+      </c>
+      <c r="L81" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="M81" s="1">
         <f t="shared" si="8"/>
-        <v>40</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J81" s="1">
-        <v>5</v>
-      </c>
-      <c r="K81" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L81" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M81" s="1">
-        <f t="shared" si="9"/>
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="N81" s="1">
         <v>1</v>
@@ -4385,343 +4421,343 @@
     </row>
     <row r="82" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C82" s="1">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D82" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E82" s="1">
+        <v>0</v>
+      </c>
+      <c r="F82" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G82" s="1">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J82" s="1">
+        <v>5</v>
+      </c>
+      <c r="K82" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L82" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M82" s="1">
+        <f t="shared" si="8"/>
+        <v>80000</v>
+      </c>
+      <c r="N82" s="1">
+        <v>1</v>
+      </c>
+      <c r="O82" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="83" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C83" s="1">
+        <v>218</v>
+      </c>
+      <c r="D83" s="1">
+        <v>3</v>
+      </c>
+      <c r="E83" s="1">
         <v>6</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F83" s="1">
         <v>30000</v>
       </c>
-      <c r="G82" s="1">
+      <c r="G83" s="1">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J83" s="1">
+        <v>5</v>
+      </c>
+      <c r="K83" s="1">
+        <v>4026</v>
+      </c>
+      <c r="L83" s="1">
+        <v>1</v>
+      </c>
+      <c r="M83" s="1">
         <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J82" s="1">
-        <v>5</v>
-      </c>
-      <c r="K82" s="1">
-        <v>4026</v>
-      </c>
-      <c r="L82" s="1">
-        <v>1</v>
-      </c>
-      <c r="M82" s="1">
-        <f t="shared" si="9"/>
         <v>150000</v>
       </c>
-      <c r="N82" s="1">
-        <v>1</v>
-      </c>
-      <c r="O82" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C84" s="1">
-        <v>231</v>
-      </c>
-      <c r="D84" s="1">
-        <v>5</v>
-      </c>
-      <c r="E84" s="1">
-        <v>0</v>
-      </c>
-      <c r="F84" s="1">
-        <v>800</v>
-      </c>
-      <c r="G84" s="1">
-        <f t="shared" ref="G84:G91" si="10">N84*O84</f>
-        <v>1200</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J84" s="1">
-        <v>5</v>
-      </c>
-      <c r="K84" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L84" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M84" s="1">
-        <f t="shared" ref="M84:M91" si="11">F84*G84</f>
-        <v>960000</v>
-      </c>
-      <c r="N84" s="1">
-        <v>4</v>
-      </c>
-      <c r="O84" s="1">
-        <v>300</v>
+      <c r="N83" s="1">
+        <v>1</v>
+      </c>
+      <c r="O83" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="85" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C85" s="1">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="D85" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E85" s="1">
         <v>0</v>
       </c>
-      <c r="F85" s="1">
-        <v>800</v>
+      <c r="F85" s="6">
+        <v>600</v>
       </c>
       <c r="G85" s="1">
-        <f t="shared" si="10"/>
-        <v>2000</v>
+        <f t="shared" ref="G85:G92" si="9">N85*O85</f>
+        <v>300</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="J85" s="1">
         <v>5</v>
       </c>
       <c r="K85" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="L85" s="1">
         <v>1000</v>
       </c>
       <c r="M85" s="1">
-        <f t="shared" si="11"/>
-        <v>1600000</v>
+        <f t="shared" ref="M85:M92" si="10">F85*G85</f>
+        <v>180000</v>
       </c>
       <c r="N85" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O85" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="86" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C86" s="1">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="D86" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E86" s="1">
         <v>0</v>
       </c>
-      <c r="F86" s="1">
-        <v>8000</v>
+      <c r="F86" s="6">
+        <v>600</v>
       </c>
       <c r="G86" s="1">
+        <f t="shared" si="9"/>
+        <v>500</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J86" s="1">
+        <v>5</v>
+      </c>
+      <c r="K86" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L86" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M86" s="1">
         <f t="shared" si="10"/>
-        <v>24</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J86" s="1">
-        <v>15</v>
-      </c>
-      <c r="K86" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L86" s="1">
-        <v>100</v>
-      </c>
-      <c r="M86" s="1">
-        <f t="shared" si="11"/>
-        <v>192000</v>
+        <v>300000</v>
       </c>
       <c r="N86" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O86" s="1">
-        <v>6</v>
+        <v>500</v>
       </c>
     </row>
     <row r="87" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C87" s="1">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="D87" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E87" s="1">
         <v>0</v>
       </c>
-      <c r="F87" s="1">
-        <v>4000</v>
+      <c r="F87" s="6">
+        <v>6000</v>
       </c>
       <c r="G87" s="1">
+        <f t="shared" si="9"/>
+        <v>6</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J87" s="1">
+        <v>15</v>
+      </c>
+      <c r="K87" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L87" s="1">
+        <v>100</v>
+      </c>
+      <c r="M87" s="1">
         <f t="shared" si="10"/>
-        <v>80</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J87" s="1">
-        <v>5</v>
-      </c>
-      <c r="K87" s="1">
-        <v>4012</v>
-      </c>
-      <c r="L87" s="1">
-        <v>200</v>
-      </c>
-      <c r="M87" s="1">
-        <f t="shared" si="11"/>
-        <v>320000</v>
+        <v>36000</v>
       </c>
       <c r="N87" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O87" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C88" s="1">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="D88" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E88" s="1">
-        <v>1</v>
-      </c>
-      <c r="F88" s="1">
-        <v>75000</v>
+        <v>0</v>
+      </c>
+      <c r="F88" s="6">
+        <v>3000</v>
       </c>
       <c r="G88" s="1">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J88" s="1">
+        <v>5</v>
+      </c>
+      <c r="K88" s="1">
+        <v>4012</v>
+      </c>
+      <c r="L88" s="1">
+        <v>200</v>
+      </c>
+      <c r="M88" s="1">
         <f t="shared" si="10"/>
-        <v>32</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="J88" s="1">
-        <v>5</v>
-      </c>
-      <c r="K88" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L88" s="1">
-        <v>1</v>
-      </c>
-      <c r="M88" s="1">
-        <f t="shared" si="11"/>
-        <v>2400000</v>
+        <v>60000</v>
       </c>
       <c r="N88" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O88" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C89" s="1">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="D89" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E89" s="1">
-        <v>0</v>
-      </c>
-      <c r="F89" s="1">
-        <v>4000</v>
+        <v>1</v>
+      </c>
+      <c r="F89" s="6">
+        <v>60000</v>
       </c>
       <c r="G89" s="1">
+        <f t="shared" si="9"/>
+        <v>8</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J89" s="1">
+        <v>5</v>
+      </c>
+      <c r="K89" s="1">
+        <v>4019</v>
+      </c>
+      <c r="L89" s="1">
+        <v>1</v>
+      </c>
+      <c r="M89" s="1">
         <f t="shared" si="10"/>
-        <v>160</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J89" s="1">
-        <v>5</v>
-      </c>
-      <c r="K89" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L89" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M89" s="1">
-        <f t="shared" si="11"/>
-        <v>640000</v>
+        <v>480000</v>
       </c>
       <c r="N89" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O89" s="1">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C90" s="1">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="D90" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E90" s="1">
         <v>0</v>
       </c>
-      <c r="F90" s="1">
-        <v>4000</v>
+      <c r="F90" s="6">
+        <v>3000</v>
       </c>
       <c r="G90" s="1">
+        <f t="shared" si="9"/>
+        <v>40</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J90" s="1">
+        <v>5</v>
+      </c>
+      <c r="K90" s="1">
+        <v>4001</v>
+      </c>
+      <c r="L90" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="M90" s="1">
         <f t="shared" si="10"/>
-        <v>160</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="J90" s="1">
-        <v>5</v>
-      </c>
-      <c r="K90" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L90" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M90" s="1">
-        <f t="shared" si="11"/>
-        <v>640000</v>
+        <v>120000</v>
       </c>
       <c r="N90" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O90" s="1">
         <v>40</v>
@@ -4729,152 +4765,539 @@
     </row>
     <row r="91" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C91" s="1">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="D91" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E91" s="1">
+        <v>0</v>
+      </c>
+      <c r="F91" s="6">
+        <v>3000</v>
+      </c>
+      <c r="G91" s="1">
+        <f t="shared" si="9"/>
+        <v>40</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J91" s="1">
+        <v>5</v>
+      </c>
+      <c r="K91" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L91" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M91" s="1">
+        <f t="shared" si="10"/>
+        <v>120000</v>
+      </c>
+      <c r="N91" s="1">
+        <v>1</v>
+      </c>
+      <c r="O91" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="92" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C92" s="1">
+        <v>228</v>
+      </c>
+      <c r="D92" s="1">
+        <v>4</v>
+      </c>
+      <c r="E92" s="1">
         <v>6</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F92" s="1">
         <v>30000</v>
       </c>
-      <c r="G91" s="1">
+      <c r="G92" s="1">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J92" s="1">
+        <v>5</v>
+      </c>
+      <c r="K92" s="1">
+        <v>4026</v>
+      </c>
+      <c r="L92" s="1">
+        <v>1</v>
+      </c>
+      <c r="M92" s="1">
         <f t="shared" si="10"/>
-        <v>5</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J91" s="1">
-        <v>5</v>
-      </c>
-      <c r="K91" s="1">
-        <v>4026</v>
-      </c>
-      <c r="L91" s="1">
-        <v>1</v>
-      </c>
-      <c r="M91" s="1">
+        <v>150000</v>
+      </c>
+      <c r="N92" s="1">
+        <v>1</v>
+      </c>
+      <c r="O92" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C94" s="1">
+        <v>231</v>
+      </c>
+      <c r="D94" s="1">
+        <v>5</v>
+      </c>
+      <c r="E94" s="1">
+        <v>0</v>
+      </c>
+      <c r="F94" s="1">
+        <v>800</v>
+      </c>
+      <c r="G94" s="1">
+        <f t="shared" ref="G94:G101" si="11">N94*O94</f>
+        <v>1200</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J94" s="1">
+        <v>5</v>
+      </c>
+      <c r="K94" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L94" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M94" s="1">
+        <f t="shared" ref="M94:M101" si="12">F94*G94</f>
+        <v>960000</v>
+      </c>
+      <c r="N94" s="1">
+        <v>4</v>
+      </c>
+      <c r="O94" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="95" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C95" s="1">
+        <v>232</v>
+      </c>
+      <c r="D95" s="1">
+        <v>5</v>
+      </c>
+      <c r="E95" s="1">
+        <v>0</v>
+      </c>
+      <c r="F95" s="1">
+        <v>800</v>
+      </c>
+      <c r="G95" s="1">
         <f t="shared" si="11"/>
-        <v>150000</v>
-      </c>
-      <c r="N91" s="1">
-        <v>1</v>
-      </c>
-      <c r="O91" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="93" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C93" s="1">
-        <v>999</v>
-      </c>
-      <c r="D93" s="1">
-        <v>0</v>
-      </c>
-      <c r="E93" s="1">
-        <v>0</v>
-      </c>
-      <c r="F93" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J95" s="1">
+        <v>5</v>
+      </c>
+      <c r="K95" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L95" s="1">
         <v>1000</v>
-      </c>
-      <c r="G93" s="1">
-        <v>50</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J93" s="1">
-        <v>5</v>
-      </c>
-      <c r="K93" s="1">
-        <v>4006</v>
-      </c>
-      <c r="L93" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M93" s="1">
-        <f t="shared" ref="M93:M95" si="12">F93*G93</f>
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C94" s="1">
-        <v>1000</v>
-      </c>
-      <c r="D94" s="1">
-        <v>0</v>
-      </c>
-      <c r="E94" s="1">
-        <v>0</v>
-      </c>
-      <c r="F94" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G94" s="1">
-        <v>100</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J94" s="1">
-        <v>5</v>
-      </c>
-      <c r="K94" s="1">
-        <v>4010</v>
-      </c>
-      <c r="L94" s="1">
-        <v>5</v>
-      </c>
-      <c r="M94" s="1">
-        <f t="shared" si="12"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="95" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C95" s="1">
-        <v>1001</v>
-      </c>
-      <c r="D95" s="1">
-        <v>0</v>
-      </c>
-      <c r="E95" s="1">
-        <v>0</v>
-      </c>
-      <c r="F95" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G95" s="1">
-        <v>50</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="J95" s="1">
-        <v>5</v>
-      </c>
-      <c r="K95" s="1">
-        <v>4102</v>
-      </c>
-      <c r="L95" s="1">
-        <v>20</v>
       </c>
       <c r="M95" s="1">
         <f t="shared" si="12"/>
+        <v>1600000</v>
+      </c>
+      <c r="N95" s="1">
+        <v>4</v>
+      </c>
+      <c r="O95" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="96" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C96" s="1">
+        <v>233</v>
+      </c>
+      <c r="D96" s="1">
+        <v>5</v>
+      </c>
+      <c r="E96" s="1">
+        <v>0</v>
+      </c>
+      <c r="F96" s="1">
+        <v>8000</v>
+      </c>
+      <c r="G96" s="1">
+        <f t="shared" si="11"/>
+        <v>24</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J96" s="1">
+        <v>15</v>
+      </c>
+      <c r="K96" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L96" s="1">
+        <v>100</v>
+      </c>
+      <c r="M96" s="1">
+        <f t="shared" si="12"/>
+        <v>192000</v>
+      </c>
+      <c r="N96" s="1">
+        <v>4</v>
+      </c>
+      <c r="O96" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C97" s="1">
+        <v>234</v>
+      </c>
+      <c r="D97" s="1">
+        <v>5</v>
+      </c>
+      <c r="E97" s="1">
+        <v>0</v>
+      </c>
+      <c r="F97" s="1">
+        <v>4000</v>
+      </c>
+      <c r="G97" s="1">
+        <f t="shared" si="11"/>
+        <v>80</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J97" s="1">
+        <v>5</v>
+      </c>
+      <c r="K97" s="1">
+        <v>4012</v>
+      </c>
+      <c r="L97" s="1">
+        <v>200</v>
+      </c>
+      <c r="M97" s="1">
+        <f t="shared" si="12"/>
+        <v>320000</v>
+      </c>
+      <c r="N97" s="1">
+        <v>4</v>
+      </c>
+      <c r="O97" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="98" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C98" s="1">
+        <v>235</v>
+      </c>
+      <c r="D98" s="1">
+        <v>5</v>
+      </c>
+      <c r="E98" s="1">
+        <v>1</v>
+      </c>
+      <c r="F98" s="1">
+        <v>75000</v>
+      </c>
+      <c r="G98" s="1">
+        <f t="shared" si="11"/>
+        <v>32</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J98" s="1">
+        <v>5</v>
+      </c>
+      <c r="K98" s="1">
+        <v>4019</v>
+      </c>
+      <c r="L98" s="1">
+        <v>1</v>
+      </c>
+      <c r="M98" s="1">
+        <f t="shared" si="12"/>
+        <v>2400000</v>
+      </c>
+      <c r="N98" s="1">
+        <v>4</v>
+      </c>
+      <c r="O98" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C99" s="1">
+        <v>236</v>
+      </c>
+      <c r="D99" s="1">
+        <v>5</v>
+      </c>
+      <c r="E99" s="1">
+        <v>0</v>
+      </c>
+      <c r="F99" s="1">
+        <v>4000</v>
+      </c>
+      <c r="G99" s="1">
+        <f t="shared" si="11"/>
+        <v>160</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J99" s="1">
+        <v>5</v>
+      </c>
+      <c r="K99" s="1">
+        <v>4001</v>
+      </c>
+      <c r="L99" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="M99" s="1">
+        <f t="shared" si="12"/>
+        <v>640000</v>
+      </c>
+      <c r="N99" s="1">
+        <v>4</v>
+      </c>
+      <c r="O99" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="100" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C100" s="1">
+        <v>237</v>
+      </c>
+      <c r="D100" s="1">
+        <v>5</v>
+      </c>
+      <c r="E100" s="1">
+        <v>0</v>
+      </c>
+      <c r="F100" s="1">
+        <v>4000</v>
+      </c>
+      <c r="G100" s="1">
+        <f t="shared" si="11"/>
+        <v>160</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J100" s="1">
+        <v>5</v>
+      </c>
+      <c r="K100" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L100" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M100" s="1">
+        <f t="shared" si="12"/>
+        <v>640000</v>
+      </c>
+      <c r="N100" s="1">
+        <v>4</v>
+      </c>
+      <c r="O100" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="101" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C101" s="1">
+        <v>238</v>
+      </c>
+      <c r="D101" s="1">
+        <v>5</v>
+      </c>
+      <c r="E101" s="1">
+        <v>6</v>
+      </c>
+      <c r="F101" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G101" s="1">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J101" s="1">
+        <v>5</v>
+      </c>
+      <c r="K101" s="1">
+        <v>4026</v>
+      </c>
+      <c r="L101" s="1">
+        <v>1</v>
+      </c>
+      <c r="M101" s="1">
+        <f t="shared" si="12"/>
+        <v>150000</v>
+      </c>
+      <c r="N101" s="1">
+        <v>1</v>
+      </c>
+      <c r="O101" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C103" s="1">
+        <v>999</v>
+      </c>
+      <c r="D103" s="1">
+        <v>0</v>
+      </c>
+      <c r="E103" s="1">
+        <v>0</v>
+      </c>
+      <c r="F103" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G103" s="1">
+        <v>50</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J103" s="1">
+        <v>5</v>
+      </c>
+      <c r="K103" s="1">
+        <v>4006</v>
+      </c>
+      <c r="L103" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M103" s="1">
+        <f t="shared" ref="M103:M105" si="13">F103*G103</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="104" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C104" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D104" s="1">
+        <v>0</v>
+      </c>
+      <c r="E104" s="1">
+        <v>0</v>
+      </c>
+      <c r="F104" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G104" s="1">
+        <v>100</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J104" s="1">
+        <v>5</v>
+      </c>
+      <c r="K104" s="1">
+        <v>4010</v>
+      </c>
+      <c r="L104" s="1">
+        <v>5</v>
+      </c>
+      <c r="M104" s="1">
+        <f t="shared" si="13"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="105" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C105" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D105" s="1">
+        <v>0</v>
+      </c>
+      <c r="E105" s="1">
+        <v>0</v>
+      </c>
+      <c r="F105" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G105" s="1">
+        <v>50</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J105" s="1">
+        <v>5</v>
+      </c>
+      <c r="K105" s="1">
+        <v>4102</v>
+      </c>
+      <c r="L105" s="1">
+        <v>20</v>
+      </c>
+      <c r="M105" s="1">
+        <f t="shared" si="13"/>
         <v>100000</v>
       </c>
     </row>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -2304,7 +2304,7 @@
         <v>1000</v>
       </c>
       <c r="G25" s="1">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>54</v>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="M25" s="1">
         <f t="shared" si="1"/>
-        <v>66000</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:13">
@@ -2340,7 +2340,7 @@
         <v>2000</v>
       </c>
       <c r="G26" s="1">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>56</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="M26" s="1">
         <f t="shared" si="1"/>
-        <v>110000</v>
+        <v>154000</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:13">
@@ -2376,7 +2376,7 @@
         <v>3000</v>
       </c>
       <c r="G27" s="1">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>58</v>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="M27" s="1">
         <f t="shared" si="1"/>
-        <v>132000</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:13">
@@ -2412,7 +2412,7 @@
         <v>4000</v>
       </c>
       <c r="G28" s="1">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>60</v>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="M28" s="1">
         <f t="shared" si="1"/>
-        <v>132000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:13">
@@ -2448,7 +2448,7 @@
         <v>5000</v>
       </c>
       <c r="G29" s="1">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>62</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="M29" s="1">
         <f t="shared" si="1"/>
-        <v>110000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:13">
@@ -2484,7 +2484,7 @@
         <v>6000</v>
       </c>
       <c r="G30" s="1">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>64</v>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="M30" s="1">
         <f t="shared" si="1"/>
-        <v>66000</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:13">
@@ -2736,7 +2736,7 @@
         <v>83</v>
       </c>
       <c r="G37" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>84</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="M37" s="1">
         <f t="shared" si="2"/>
-        <v>1800000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:13">
@@ -2772,7 +2772,7 @@
         <v>86</v>
       </c>
       <c r="G38" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>87</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="M38" s="1">
         <f t="shared" si="2"/>
-        <v>1200000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:13">
@@ -2808,7 +2808,7 @@
         <v>89</v>
       </c>
       <c r="G39" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>90</v>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="M39" s="1">
         <f t="shared" si="2"/>
-        <v>1000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:13">
@@ -3057,7 +3057,7 @@
         <v>4</v>
       </c>
       <c r="F46" s="1">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="G46" s="1">
         <v>15</v>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M46" s="1">
         <f t="shared" si="2"/>
-        <v>300000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:13">
@@ -3093,7 +3093,7 @@
         <v>4</v>
       </c>
       <c r="F47" s="1">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="G47" s="1">
         <v>20</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="M47" s="1">
         <f t="shared" si="2"/>
-        <v>300000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="48" customFormat="1" customHeight="1" spans="3:15">
@@ -3129,7 +3129,7 @@
         <v>4</v>
       </c>
       <c r="F48" s="1">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="G48" s="1">
         <v>20</v>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="M48" s="1">
         <f t="shared" si="2"/>
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
@@ -3167,7 +3167,7 @@
         <v>4</v>
       </c>
       <c r="F49" s="1">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="G49" s="1">
         <v>10</v>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="M49" s="1">
         <f t="shared" si="2"/>
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
@@ -3205,7 +3205,7 @@
         <v>4</v>
       </c>
       <c r="F50" s="1">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="G50" s="1">
         <v>10</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="M50" s="1">
         <f t="shared" si="2"/>
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
@@ -3243,7 +3243,7 @@
         <v>4</v>
       </c>
       <c r="F51" s="1">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="G51" s="1">
         <v>15</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="M51" s="1">
         <f t="shared" si="2"/>
-        <v>300000</v>
+        <v>225000</v>
       </c>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
@@ -3281,7 +3281,7 @@
         <v>4</v>
       </c>
       <c r="F52" s="1">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="G52" s="1">
         <v>15</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="M52" s="1">
         <f t="shared" si="2"/>
-        <v>300000</v>
+        <v>225000</v>
       </c>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
@@ -3319,7 +3319,7 @@
         <v>4</v>
       </c>
       <c r="F53" s="1">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="G53" s="1">
         <v>15</v>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="M53" s="1">
         <f t="shared" si="2"/>
-        <v>300000</v>
+        <v>225000</v>
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
@@ -3357,7 +3357,7 @@
         <v>4</v>
       </c>
       <c r="F54" s="1">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="G54" s="1">
         <v>15</v>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="M54" s="1">
         <f t="shared" si="2"/>
-        <v>300000</v>
+        <v>225000</v>
       </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
@@ -3395,7 +3395,7 @@
         <v>4</v>
       </c>
       <c r="F55" s="1">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="G55" s="1">
         <v>20</v>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="M55" s="1">
         <f t="shared" si="2"/>
-        <v>400000</v>
+        <v>300000</v>
       </c>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="151">
   <si>
     <t>#</t>
   </si>
@@ -324,6 +324,12 @@
   </si>
   <si>
     <t>红装精华</t>
+  </si>
+  <si>
+    <t>兑换遗物粉尘*10</t>
+  </si>
+  <si>
+    <t>遗物粉尘</t>
   </si>
   <si>
     <t>兑换天赋秘籍*1</t>
@@ -1490,7 +1496,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O105"/>
+  <dimension ref="C1:O106"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -2538,7 +2544,7 @@
         <v>1</v>
       </c>
       <c r="M31" s="1">
-        <f t="shared" ref="M31:M56" si="2">F31*G31</f>
+        <f>F31*G31</f>
         <v>2000</v>
       </c>
     </row>
@@ -2574,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="M32" s="1">
-        <f t="shared" si="2"/>
+        <f>F32*G32</f>
         <v>500</v>
       </c>
     </row>
@@ -2610,7 +2616,7 @@
         <v>1</v>
       </c>
       <c r="M33" s="1">
-        <f t="shared" si="2"/>
+        <f>F33*G33</f>
         <v>1000</v>
       </c>
     </row>
@@ -2646,7 +2652,7 @@
         <v>1</v>
       </c>
       <c r="M34" s="1">
-        <f t="shared" si="2"/>
+        <f>F34*G34</f>
         <v>300000</v>
       </c>
     </row>
@@ -2682,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="M35" s="1">
-        <f t="shared" si="2"/>
+        <f>F35*G35</f>
         <v>250000</v>
       </c>
     </row>
@@ -2718,7 +2724,7 @@
         <v>1</v>
       </c>
       <c r="M36" s="1">
-        <f t="shared" si="2"/>
+        <f>F36*G36</f>
         <v>400000</v>
       </c>
     </row>
@@ -2736,7 +2742,7 @@
         <v>83</v>
       </c>
       <c r="G37" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>84</v>
@@ -2754,8 +2760,8 @@
         <v>1</v>
       </c>
       <c r="M37" s="1">
-        <f t="shared" si="2"/>
-        <v>1200000</v>
+        <f>F37*G37</f>
+        <v>2400000</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:13">
@@ -2790,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="M38" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="M38:M43" si="2">F38*G38</f>
         <v>800000</v>
       </c>
     </row>
@@ -2916,7 +2922,7 @@
         <v>3000</v>
       </c>
       <c r="G42" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>97</v>
@@ -2935,7 +2941,7 @@
       </c>
       <c r="M42" s="1">
         <f t="shared" si="2"/>
-        <v>300000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:13">
@@ -2952,7 +2958,7 @@
         <v>20000</v>
       </c>
       <c r="G43" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>99</v>
@@ -2964,17 +2970,17 @@
         <v>5</v>
       </c>
       <c r="K43" s="1">
-        <v>4020</v>
+        <v>4018</v>
       </c>
       <c r="L43" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M43" s="1">
         <f t="shared" si="2"/>
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:13">
       <c r="C44" s="1">
         <v>39</v>
       </c>
@@ -2985,10 +2991,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="1">
-        <v>488888</v>
+        <v>20000</v>
       </c>
       <c r="G44" s="1">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>101</v>
@@ -2997,17 +3003,17 @@
         <v>102</v>
       </c>
       <c r="J44" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K44" s="1">
-        <v>204</v>
+        <v>4020</v>
       </c>
       <c r="L44" s="1">
         <v>1</v>
       </c>
       <c r="M44" s="1">
-        <f t="shared" si="2"/>
-        <v>488888</v>
+        <f t="shared" ref="M44:M57" si="3">F44*G44</f>
+        <v>800000</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -3018,13 +3024,13 @@
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F45" s="1">
-        <v>300000</v>
+        <v>388888</v>
       </c>
       <c r="G45" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>103</v>
@@ -3033,20 +3039,20 @@
         <v>104</v>
       </c>
       <c r="J45" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K45" s="1">
-        <v>4027</v>
+        <v>204</v>
       </c>
       <c r="L45" s="1">
         <v>1</v>
       </c>
       <c r="M45" s="1">
-        <f t="shared" si="2"/>
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:13">
+        <f t="shared" si="3"/>
+        <v>388888</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C46" s="1">
         <v>41</v>
       </c>
@@ -3057,10 +3063,10 @@
         <v>4</v>
       </c>
       <c r="F46" s="1">
-        <v>15000</v>
+        <v>300000</v>
       </c>
       <c r="G46" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>105</v>
@@ -3071,15 +3077,15 @@
       <c r="J46" s="1">
         <v>5</v>
       </c>
-      <c r="K46" s="5">
-        <v>60000001</v>
+      <c r="K46" s="1">
+        <v>4027</v>
       </c>
       <c r="L46" s="1">
         <v>1</v>
       </c>
       <c r="M46" s="1">
-        <f t="shared" si="2"/>
-        <v>225000</v>
+        <f t="shared" si="3"/>
+        <v>600000</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:13">
@@ -3096,7 +3102,7 @@
         <v>10000</v>
       </c>
       <c r="G47" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>107</v>
@@ -3108,17 +3114,17 @@
         <v>5</v>
       </c>
       <c r="K47" s="5">
-        <v>60000002</v>
+        <v>60000001</v>
       </c>
       <c r="L47" s="1">
         <v>1</v>
       </c>
       <c r="M47" s="1">
-        <f t="shared" si="2"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" customHeight="1" spans="3:15">
+        <f t="shared" si="3"/>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:13">
       <c r="C48" s="1">
         <v>43</v>
       </c>
@@ -3129,10 +3135,10 @@
         <v>4</v>
       </c>
       <c r="F48" s="1">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="G48" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>109</v>
@@ -3144,17 +3150,15 @@
         <v>5</v>
       </c>
       <c r="K48" s="5">
-        <v>60000003</v>
+        <v>60000002</v>
       </c>
       <c r="L48" s="1">
         <v>1</v>
       </c>
       <c r="M48" s="1">
-        <f t="shared" si="2"/>
-        <v>200000</v>
-      </c>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
+        <f t="shared" si="3"/>
+        <v>320000</v>
+      </c>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="3:15">
       <c r="C49" s="1">
@@ -3167,10 +3171,10 @@
         <v>4</v>
       </c>
       <c r="F49" s="1">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="G49" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>111</v>
@@ -3182,14 +3186,14 @@
         <v>5</v>
       </c>
       <c r="K49" s="5">
-        <v>60000004</v>
+        <v>60000003</v>
       </c>
       <c r="L49" s="1">
         <v>1</v>
       </c>
       <c r="M49" s="1">
-        <f t="shared" si="2"/>
-        <v>200000</v>
+        <f t="shared" si="3"/>
+        <v>320000</v>
       </c>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
@@ -3205,10 +3209,10 @@
         <v>4</v>
       </c>
       <c r="F50" s="1">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="G50" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>113</v>
@@ -3220,14 +3224,14 @@
         <v>5</v>
       </c>
       <c r="K50" s="5">
-        <v>60000005</v>
+        <v>60000004</v>
       </c>
       <c r="L50" s="1">
         <v>1</v>
       </c>
       <c r="M50" s="1">
-        <f t="shared" si="2"/>
-        <v>200000</v>
+        <f t="shared" si="3"/>
+        <v>300000</v>
       </c>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
@@ -3246,7 +3250,7 @@
         <v>15000</v>
       </c>
       <c r="G51" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>115</v>
@@ -3258,14 +3262,14 @@
         <v>5</v>
       </c>
       <c r="K51" s="5">
-        <v>60000006</v>
+        <v>60000005</v>
       </c>
       <c r="L51" s="1">
         <v>1</v>
       </c>
       <c r="M51" s="1">
-        <f t="shared" si="2"/>
-        <v>225000</v>
+        <f t="shared" si="3"/>
+        <v>300000</v>
       </c>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
@@ -3281,10 +3285,10 @@
         <v>4</v>
       </c>
       <c r="F52" s="1">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="G52" s="1">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>117</v>
@@ -3296,14 +3300,14 @@
         <v>5</v>
       </c>
       <c r="K52" s="5">
-        <v>60000007</v>
+        <v>60000006</v>
       </c>
       <c r="L52" s="1">
         <v>1</v>
       </c>
       <c r="M52" s="1">
-        <f t="shared" si="2"/>
-        <v>225000</v>
+        <f t="shared" si="3"/>
+        <v>300000</v>
       </c>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
@@ -3319,29 +3323,29 @@
         <v>4</v>
       </c>
       <c r="F53" s="1">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="G53" s="1">
-        <v>15</v>
-      </c>
-      <c r="H53" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H53" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="I53" s="4" t="s">
+      <c r="I53" s="1" t="s">
         <v>120</v>
       </c>
       <c r="J53" s="1">
         <v>5</v>
       </c>
       <c r="K53" s="5">
-        <v>60000008</v>
+        <v>60000007</v>
       </c>
       <c r="L53" s="1">
         <v>1</v>
       </c>
       <c r="M53" s="1">
-        <f t="shared" si="2"/>
-        <v>225000</v>
+        <f t="shared" si="3"/>
+        <v>300000</v>
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
@@ -3357,29 +3361,29 @@
         <v>4</v>
       </c>
       <c r="F54" s="1">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="G54" s="1">
-        <v>15</v>
-      </c>
-      <c r="H54" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H54" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="I54" s="4" t="s">
         <v>122</v>
       </c>
       <c r="J54" s="1">
         <v>5</v>
       </c>
       <c r="K54" s="5">
-        <v>60000009</v>
+        <v>60000008</v>
       </c>
       <c r="L54" s="1">
         <v>1</v>
       </c>
       <c r="M54" s="1">
-        <f t="shared" si="2"/>
-        <v>225000</v>
+        <f t="shared" si="3"/>
+        <v>300000</v>
       </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
@@ -3395,10 +3399,10 @@
         <v>4</v>
       </c>
       <c r="F55" s="1">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="G55" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>123</v>
@@ -3410,19 +3414,19 @@
         <v>5</v>
       </c>
       <c r="K55" s="5">
-        <v>60000010</v>
+        <v>60000009</v>
       </c>
       <c r="L55" s="1">
         <v>1</v>
       </c>
       <c r="M55" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>300000</v>
       </c>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
     </row>
-    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:13">
+    <row r="56" customFormat="1" customHeight="1" spans="3:15">
       <c r="C56" s="1">
         <v>51</v>
       </c>
@@ -3430,13 +3434,13 @@
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="G56" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>125</v>
@@ -3445,80 +3449,75 @@
         <v>126</v>
       </c>
       <c r="J56" s="1">
+        <v>5</v>
+      </c>
+      <c r="K56" s="5">
+        <v>60000010</v>
+      </c>
+      <c r="L56" s="1">
+        <v>1</v>
+      </c>
+      <c r="M56" s="1">
+        <f t="shared" si="3"/>
+        <v>400000</v>
+      </c>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C57" s="1">
+        <v>52</v>
+      </c>
+      <c r="D57" s="1">
+        <v>0</v>
+      </c>
+      <c r="E57" s="1">
+        <v>0</v>
+      </c>
+      <c r="F57" s="1">
+        <v>50000</v>
+      </c>
+      <c r="G57" s="1">
+        <v>30</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J57" s="1">
         <v>4</v>
       </c>
-      <c r="K56" s="1">
+      <c r="K57" s="1">
         <v>24</v>
       </c>
-      <c r="L56" s="1">
-        <v>1</v>
-      </c>
-      <c r="M56" s="1">
-        <f t="shared" si="2"/>
+      <c r="L57" s="1">
+        <v>1</v>
+      </c>
+      <c r="M57" s="1">
+        <f t="shared" si="3"/>
         <v>1500000</v>
       </c>
     </row>
-    <row r="57" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-    </row>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C58" s="1">
-        <v>102</v>
-      </c>
-      <c r="D58" s="1">
-        <v>1</v>
-      </c>
-      <c r="E58" s="1">
-        <v>0</v>
-      </c>
-      <c r="F58" s="1">
-        <v>100</v>
-      </c>
-      <c r="G58" s="1">
-        <f t="shared" ref="G58:G65" si="3">N58*O58</f>
-        <v>300</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J58" s="1">
-        <v>5</v>
-      </c>
-      <c r="K58" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L58" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M58" s="1">
-        <f t="shared" ref="M58:M65" si="4">F58*G58</f>
-        <v>30000</v>
-      </c>
-      <c r="N58" s="1">
-        <v>1</v>
-      </c>
-      <c r="O58" s="1">
-        <v>300</v>
-      </c>
+    <row r="58" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C59" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D59" s="1">
         <v>1</v>
@@ -3530,8 +3529,8 @@
         <v>100</v>
       </c>
       <c r="G59" s="1">
-        <f t="shared" si="3"/>
-        <v>500</v>
+        <f t="shared" ref="G59:G66" si="4">N59*O59</f>
+        <v>300</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>129</v>
@@ -3543,25 +3542,25 @@
         <v>5</v>
       </c>
       <c r="K59" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="L59" s="1">
         <v>1000</v>
       </c>
       <c r="M59" s="1">
-        <f t="shared" si="4"/>
-        <v>50000</v>
+        <f t="shared" ref="M59:M66" si="5">F59*G59</f>
+        <v>30000</v>
       </c>
       <c r="N59" s="1">
         <v>1</v>
       </c>
       <c r="O59" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C60" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D60" s="1">
         <v>1</v>
@@ -3570,11 +3569,11 @@
         <v>0</v>
       </c>
       <c r="F60" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="G60" s="1">
-        <f t="shared" si="3"/>
-        <v>6</v>
+        <f t="shared" si="4"/>
+        <v>500</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>131</v>
@@ -3583,28 +3582,28 @@
         <v>132</v>
       </c>
       <c r="J60" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K60" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="L60" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="M60" s="1">
-        <f t="shared" si="4"/>
-        <v>6000</v>
+        <f t="shared" si="5"/>
+        <v>50000</v>
       </c>
       <c r="N60" s="1">
         <v>1</v>
       </c>
       <c r="O60" s="1">
-        <v>6</v>
+        <v>500</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C61" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D61" s="1">
         <v>1</v>
@@ -3613,11 +3612,11 @@
         <v>0</v>
       </c>
       <c r="F61" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G61" s="1">
-        <f t="shared" si="3"/>
-        <v>20</v>
+        <f t="shared" si="4"/>
+        <v>6</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>133</v>
@@ -3626,41 +3625,41 @@
         <v>134</v>
       </c>
       <c r="J61" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K61" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="L61" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M61" s="1">
-        <f t="shared" si="4"/>
-        <v>10000</v>
+        <f t="shared" si="5"/>
+        <v>6000</v>
       </c>
       <c r="N61" s="1">
         <v>1</v>
       </c>
       <c r="O61" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C62" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D62" s="1">
         <v>1</v>
       </c>
       <c r="E62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" s="1">
-        <v>15000</v>
+        <v>500</v>
       </c>
       <c r="G62" s="1">
-        <f t="shared" si="3"/>
-        <v>8</v>
+        <f t="shared" si="4"/>
+        <v>20</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>135</v>
@@ -3672,38 +3671,38 @@
         <v>5</v>
       </c>
       <c r="K62" s="1">
-        <v>4019</v>
+        <v>4012</v>
       </c>
       <c r="L62" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="M62" s="1">
-        <f t="shared" si="4"/>
-        <v>120000</v>
+        <f t="shared" si="5"/>
+        <v>10000</v>
       </c>
       <c r="N62" s="1">
         <v>1</v>
       </c>
       <c r="O62" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C63" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D63" s="1">
         <v>1</v>
       </c>
       <c r="E63" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="1">
-        <v>500</v>
+        <v>15000</v>
       </c>
       <c r="G63" s="1">
-        <f t="shared" si="3"/>
-        <v>40</v>
+        <f t="shared" si="4"/>
+        <v>8</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>137</v>
@@ -3715,25 +3714,25 @@
         <v>5</v>
       </c>
       <c r="K63" s="1">
-        <v>4001</v>
+        <v>4019</v>
       </c>
       <c r="L63" s="1">
-        <v>1000000</v>
+        <v>1</v>
       </c>
       <c r="M63" s="1">
-        <f t="shared" si="4"/>
-        <v>20000</v>
+        <f t="shared" si="5"/>
+        <v>120000</v>
       </c>
       <c r="N63" s="1">
         <v>1</v>
       </c>
       <c r="O63" s="1">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C64" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D64" s="1">
         <v>1</v>
@@ -3745,7 +3744,7 @@
         <v>500</v>
       </c>
       <c r="G64" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="H64" s="1" t="s">
@@ -3758,13 +3757,13 @@
         <v>5</v>
       </c>
       <c r="K64" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L64" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M64" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20000</v>
       </c>
       <c r="N64" s="1">
@@ -3776,20 +3775,20 @@
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C65" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D65" s="1">
         <v>1</v>
       </c>
       <c r="E65" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F65" s="1">
-        <v>30000</v>
+        <v>500</v>
       </c>
       <c r="G65" s="1">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <f t="shared" si="4"/>
+        <v>40</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>141</v>
@@ -3801,68 +3800,68 @@
         <v>5</v>
       </c>
       <c r="K65" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L65" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M65" s="1">
+        <f t="shared" si="5"/>
+        <v>20000</v>
+      </c>
+      <c r="N65" s="1">
+        <v>1</v>
+      </c>
+      <c r="O65" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C66" s="1">
+        <v>109</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1</v>
+      </c>
+      <c r="E66" s="1">
+        <v>6</v>
+      </c>
+      <c r="F66" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G66" s="1">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J66" s="1">
+        <v>5</v>
+      </c>
+      <c r="K66" s="1">
         <v>4026</v>
       </c>
-      <c r="L65" s="1">
-        <v>1</v>
-      </c>
-      <c r="M65" s="1">
-        <f t="shared" si="4"/>
+      <c r="L66" s="1">
+        <v>1</v>
+      </c>
+      <c r="M66" s="1">
+        <f t="shared" si="5"/>
         <v>150000</v>
       </c>
-      <c r="N65" s="1">
-        <v>1</v>
-      </c>
-      <c r="O65" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C67" s="1">
-        <v>201</v>
-      </c>
-      <c r="D67" s="1">
-        <v>2</v>
-      </c>
-      <c r="E67" s="1">
-        <v>0</v>
-      </c>
-      <c r="F67" s="6">
-        <v>200</v>
-      </c>
-      <c r="G67" s="1">
-        <f t="shared" ref="G67:G74" si="5">N67*O67</f>
-        <v>300</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J67" s="1">
-        <v>5</v>
-      </c>
-      <c r="K67" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L67" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M67" s="1">
-        <f t="shared" ref="M67:M74" si="6">F67*G67</f>
-        <v>60000</v>
-      </c>
-      <c r="N67" s="1">
-        <v>1</v>
-      </c>
-      <c r="O67" s="1">
-        <v>300</v>
+      <c r="N66" s="1">
+        <v>1</v>
+      </c>
+      <c r="O66" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C68" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D68" s="1">
         <v>2</v>
@@ -3874,8 +3873,8 @@
         <v>200</v>
       </c>
       <c r="G68" s="1">
-        <f t="shared" si="5"/>
-        <v>500</v>
+        <f t="shared" ref="G68:G75" si="6">N68*O68</f>
+        <v>300</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>129</v>
@@ -3887,25 +3886,25 @@
         <v>5</v>
       </c>
       <c r="K68" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="L68" s="1">
         <v>1000</v>
       </c>
       <c r="M68" s="1">
-        <f t="shared" si="6"/>
-        <v>100000</v>
+        <f t="shared" ref="M68:M75" si="7">F68*G68</f>
+        <v>60000</v>
       </c>
       <c r="N68" s="1">
         <v>1</v>
       </c>
       <c r="O68" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C69" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D69" s="1">
         <v>2</v>
@@ -3914,11 +3913,11 @@
         <v>0</v>
       </c>
       <c r="F69" s="6">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="G69" s="1">
-        <f t="shared" si="5"/>
-        <v>6</v>
+        <f t="shared" si="6"/>
+        <v>500</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>131</v>
@@ -3927,28 +3926,28 @@
         <v>132</v>
       </c>
       <c r="J69" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K69" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="L69" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="M69" s="1">
-        <f t="shared" si="6"/>
-        <v>12000</v>
+        <f t="shared" si="7"/>
+        <v>100000</v>
       </c>
       <c r="N69" s="1">
         <v>1</v>
       </c>
       <c r="O69" s="1">
-        <v>6</v>
+        <v>500</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C70" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D70" s="1">
         <v>2</v>
@@ -3957,11 +3956,11 @@
         <v>0</v>
       </c>
       <c r="F70" s="6">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G70" s="1">
-        <f t="shared" si="5"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>6</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>133</v>
@@ -3970,41 +3969,41 @@
         <v>134</v>
       </c>
       <c r="J70" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K70" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="L70" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M70" s="1">
-        <f t="shared" si="6"/>
-        <v>20000</v>
+        <f t="shared" si="7"/>
+        <v>12000</v>
       </c>
       <c r="N70" s="1">
         <v>1</v>
       </c>
       <c r="O70" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C71" s="1">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D71" s="1">
         <v>2</v>
       </c>
       <c r="E71" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" s="6">
-        <v>30000</v>
+        <v>1000</v>
       </c>
       <c r="G71" s="1">
-        <f t="shared" si="5"/>
-        <v>8</v>
+        <f t="shared" si="6"/>
+        <v>20</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>135</v>
@@ -4016,38 +4015,38 @@
         <v>5</v>
       </c>
       <c r="K71" s="1">
-        <v>4019</v>
+        <v>4012</v>
       </c>
       <c r="L71" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="M71" s="1">
-        <f t="shared" si="6"/>
-        <v>240000</v>
+        <f t="shared" si="7"/>
+        <v>20000</v>
       </c>
       <c r="N71" s="1">
         <v>1</v>
       </c>
       <c r="O71" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C72" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D72" s="1">
         <v>2</v>
       </c>
       <c r="E72" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6">
-        <v>1000</v>
+        <v>30000</v>
       </c>
       <c r="G72" s="1">
-        <f t="shared" si="5"/>
-        <v>40</v>
+        <f t="shared" si="6"/>
+        <v>8</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>137</v>
@@ -4059,25 +4058,25 @@
         <v>5</v>
       </c>
       <c r="K72" s="1">
-        <v>4001</v>
+        <v>4019</v>
       </c>
       <c r="L72" s="1">
-        <v>1000000</v>
+        <v>1</v>
       </c>
       <c r="M72" s="1">
-        <f t="shared" si="6"/>
-        <v>40000</v>
+        <f t="shared" si="7"/>
+        <v>240000</v>
       </c>
       <c r="N72" s="1">
         <v>1</v>
       </c>
       <c r="O72" s="1">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C73" s="1">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D73" s="1">
         <v>2</v>
@@ -4089,7 +4088,7 @@
         <v>1000</v>
       </c>
       <c r="G73" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
       <c r="H73" s="1" t="s">
@@ -4102,13 +4101,13 @@
         <v>5</v>
       </c>
       <c r="K73" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L73" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M73" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>40000</v>
       </c>
       <c r="N73" s="1">
@@ -4120,20 +4119,20 @@
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C74" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D74" s="1">
         <v>2</v>
       </c>
       <c r="E74" s="1">
-        <v>6</v>
-      </c>
-      <c r="F74" s="1">
-        <v>30000</v>
+        <v>0</v>
+      </c>
+      <c r="F74" s="6">
+        <v>1000</v>
       </c>
       <c r="G74" s="1">
-        <f t="shared" si="5"/>
-        <v>5</v>
+        <f t="shared" si="6"/>
+        <v>40</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>141</v>
@@ -4145,68 +4144,68 @@
         <v>5</v>
       </c>
       <c r="K74" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L74" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M74" s="1">
+        <f t="shared" si="7"/>
+        <v>40000</v>
+      </c>
+      <c r="N74" s="1">
+        <v>1</v>
+      </c>
+      <c r="O74" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C75" s="1">
+        <v>208</v>
+      </c>
+      <c r="D75" s="1">
+        <v>2</v>
+      </c>
+      <c r="E75" s="1">
+        <v>6</v>
+      </c>
+      <c r="F75" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G75" s="1">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J75" s="1">
+        <v>5</v>
+      </c>
+      <c r="K75" s="1">
         <v>4026</v>
       </c>
-      <c r="L74" s="1">
-        <v>1</v>
-      </c>
-      <c r="M74" s="1">
-        <f t="shared" si="6"/>
+      <c r="L75" s="1">
+        <v>1</v>
+      </c>
+      <c r="M75" s="1">
+        <f t="shared" si="7"/>
         <v>150000</v>
       </c>
-      <c r="N74" s="1">
-        <v>1</v>
-      </c>
-      <c r="O74" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C76" s="1">
-        <v>211</v>
-      </c>
-      <c r="D76" s="1">
-        <v>3</v>
-      </c>
-      <c r="E76" s="1">
-        <v>0</v>
-      </c>
-      <c r="F76" s="1">
-        <v>400</v>
-      </c>
-      <c r="G76" s="1">
-        <f t="shared" ref="G76:G83" si="7">N76*O76</f>
-        <v>300</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J76" s="1">
-        <v>5</v>
-      </c>
-      <c r="K76" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L76" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M76" s="1">
-        <f t="shared" ref="M76:M83" si="8">F76*G76</f>
-        <v>120000</v>
-      </c>
-      <c r="N76" s="1">
-        <v>1</v>
-      </c>
-      <c r="O76" s="1">
-        <v>300</v>
+      <c r="N75" s="1">
+        <v>1</v>
+      </c>
+      <c r="O75" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C77" s="1">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D77" s="1">
         <v>3</v>
@@ -4218,8 +4217,8 @@
         <v>400</v>
       </c>
       <c r="G77" s="1">
-        <f t="shared" si="7"/>
-        <v>500</v>
+        <f t="shared" ref="G77:G84" si="8">N77*O77</f>
+        <v>300</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>129</v>
@@ -4231,25 +4230,25 @@
         <v>5</v>
       </c>
       <c r="K77" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="L77" s="1">
         <v>1000</v>
       </c>
       <c r="M77" s="1">
-        <f t="shared" si="8"/>
-        <v>200000</v>
+        <f t="shared" ref="M77:M84" si="9">F77*G77</f>
+        <v>120000</v>
       </c>
       <c r="N77" s="1">
         <v>1</v>
       </c>
       <c r="O77" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C78" s="1">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D78" s="1">
         <v>3</v>
@@ -4258,11 +4257,11 @@
         <v>0</v>
       </c>
       <c r="F78" s="1">
-        <v>4000</v>
+        <v>400</v>
       </c>
       <c r="G78" s="1">
-        <f t="shared" si="7"/>
-        <v>6</v>
+        <f t="shared" si="8"/>
+        <v>500</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>131</v>
@@ -4271,28 +4270,28 @@
         <v>132</v>
       </c>
       <c r="J78" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K78" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="L78" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="M78" s="1">
-        <f t="shared" si="8"/>
-        <v>24000</v>
+        <f t="shared" si="9"/>
+        <v>200000</v>
       </c>
       <c r="N78" s="1">
         <v>1</v>
       </c>
       <c r="O78" s="1">
-        <v>6</v>
+        <v>500</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C79" s="1">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D79" s="1">
         <v>3</v>
@@ -4301,11 +4300,11 @@
         <v>0</v>
       </c>
       <c r="F79" s="1">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="G79" s="1">
-        <f t="shared" si="7"/>
-        <v>20</v>
+        <f t="shared" si="8"/>
+        <v>6</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>133</v>
@@ -4314,41 +4313,41 @@
         <v>134</v>
       </c>
       <c r="J79" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K79" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="L79" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M79" s="1">
-        <f t="shared" si="8"/>
-        <v>40000</v>
+        <f t="shared" si="9"/>
+        <v>24000</v>
       </c>
       <c r="N79" s="1">
         <v>1</v>
       </c>
       <c r="O79" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C80" s="1">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D80" s="1">
         <v>3</v>
       </c>
       <c r="E80" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" s="1">
-        <v>45000</v>
+        <v>2000</v>
       </c>
       <c r="G80" s="1">
-        <f t="shared" si="7"/>
-        <v>8</v>
+        <f t="shared" si="8"/>
+        <v>20</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>135</v>
@@ -4360,38 +4359,38 @@
         <v>5</v>
       </c>
       <c r="K80" s="1">
-        <v>4019</v>
+        <v>4012</v>
       </c>
       <c r="L80" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="M80" s="1">
-        <f t="shared" si="8"/>
-        <v>360000</v>
+        <f t="shared" si="9"/>
+        <v>40000</v>
       </c>
       <c r="N80" s="1">
         <v>1</v>
       </c>
       <c r="O80" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C81" s="1">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D81" s="1">
         <v>3</v>
       </c>
       <c r="E81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" s="1">
-        <v>2000</v>
+        <v>45000</v>
       </c>
       <c r="G81" s="1">
-        <f t="shared" si="7"/>
-        <v>40</v>
+        <f t="shared" si="8"/>
+        <v>8</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>137</v>
@@ -4403,25 +4402,25 @@
         <v>5</v>
       </c>
       <c r="K81" s="1">
-        <v>4001</v>
+        <v>4019</v>
       </c>
       <c r="L81" s="1">
-        <v>1000000</v>
+        <v>1</v>
       </c>
       <c r="M81" s="1">
-        <f t="shared" si="8"/>
-        <v>80000</v>
+        <f t="shared" si="9"/>
+        <v>360000</v>
       </c>
       <c r="N81" s="1">
         <v>1</v>
       </c>
       <c r="O81" s="1">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C82" s="1">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D82" s="1">
         <v>3</v>
@@ -4433,7 +4432,7 @@
         <v>2000</v>
       </c>
       <c r="G82" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
       <c r="H82" s="1" t="s">
@@ -4446,13 +4445,13 @@
         <v>5</v>
       </c>
       <c r="K82" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L82" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M82" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>80000</v>
       </c>
       <c r="N82" s="1">
@@ -4464,20 +4463,20 @@
     </row>
     <row r="83" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C83" s="1">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D83" s="1">
         <v>3</v>
       </c>
       <c r="E83" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F83" s="1">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="G83" s="1">
-        <f t="shared" si="7"/>
-        <v>5</v>
+        <f t="shared" si="8"/>
+        <v>40</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>141</v>
@@ -4489,68 +4488,68 @@
         <v>5</v>
       </c>
       <c r="K83" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L83" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M83" s="1">
+        <f t="shared" si="9"/>
+        <v>80000</v>
+      </c>
+      <c r="N83" s="1">
+        <v>1</v>
+      </c>
+      <c r="O83" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C84" s="1">
+        <v>218</v>
+      </c>
+      <c r="D84" s="1">
+        <v>3</v>
+      </c>
+      <c r="E84" s="1">
+        <v>6</v>
+      </c>
+      <c r="F84" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G84" s="1">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J84" s="1">
+        <v>5</v>
+      </c>
+      <c r="K84" s="1">
         <v>4026</v>
       </c>
-      <c r="L83" s="1">
-        <v>1</v>
-      </c>
-      <c r="M83" s="1">
-        <f t="shared" si="8"/>
+      <c r="L84" s="1">
+        <v>1</v>
+      </c>
+      <c r="M84" s="1">
+        <f t="shared" si="9"/>
         <v>150000</v>
       </c>
-      <c r="N83" s="1">
-        <v>1</v>
-      </c>
-      <c r="O83" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C85" s="1">
-        <v>221</v>
-      </c>
-      <c r="D85" s="1">
-        <v>4</v>
-      </c>
-      <c r="E85" s="1">
-        <v>0</v>
-      </c>
-      <c r="F85" s="6">
-        <v>600</v>
-      </c>
-      <c r="G85" s="1">
-        <f t="shared" ref="G85:G92" si="9">N85*O85</f>
-        <v>300</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J85" s="1">
-        <v>5</v>
-      </c>
-      <c r="K85" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L85" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M85" s="1">
-        <f t="shared" ref="M85:M92" si="10">F85*G85</f>
-        <v>180000</v>
-      </c>
-      <c r="N85" s="1">
-        <v>1</v>
-      </c>
-      <c r="O85" s="1">
-        <v>300</v>
+      <c r="N84" s="1">
+        <v>1</v>
+      </c>
+      <c r="O84" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="86" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C86" s="1">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D86" s="1">
         <v>4</v>
@@ -4562,8 +4561,8 @@
         <v>600</v>
       </c>
       <c r="G86" s="1">
-        <f t="shared" si="9"/>
-        <v>500</v>
+        <f t="shared" ref="G86:G93" si="10">N86*O86</f>
+        <v>300</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>129</v>
@@ -4575,25 +4574,25 @@
         <v>5</v>
       </c>
       <c r="K86" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="L86" s="1">
         <v>1000</v>
       </c>
       <c r="M86" s="1">
-        <f t="shared" si="10"/>
-        <v>300000</v>
+        <f t="shared" ref="M86:M93" si="11">F86*G86</f>
+        <v>180000</v>
       </c>
       <c r="N86" s="1">
         <v>1</v>
       </c>
       <c r="O86" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="87" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C87" s="1">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D87" s="1">
         <v>4</v>
@@ -4602,11 +4601,11 @@
         <v>0</v>
       </c>
       <c r="F87" s="6">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="G87" s="1">
-        <f t="shared" si="9"/>
-        <v>6</v>
+        <f t="shared" si="10"/>
+        <v>500</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>131</v>
@@ -4615,28 +4614,28 @@
         <v>132</v>
       </c>
       <c r="J87" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K87" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="L87" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="M87" s="1">
-        <f t="shared" si="10"/>
-        <v>36000</v>
+        <f t="shared" si="11"/>
+        <v>300000</v>
       </c>
       <c r="N87" s="1">
         <v>1</v>
       </c>
       <c r="O87" s="1">
-        <v>6</v>
+        <v>500</v>
       </c>
     </row>
     <row r="88" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C88" s="1">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D88" s="1">
         <v>4</v>
@@ -4645,11 +4644,11 @@
         <v>0</v>
       </c>
       <c r="F88" s="6">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="G88" s="1">
-        <f t="shared" si="9"/>
-        <v>20</v>
+        <f t="shared" si="10"/>
+        <v>6</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>133</v>
@@ -4658,41 +4657,41 @@
         <v>134</v>
       </c>
       <c r="J88" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K88" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="L88" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M88" s="1">
-        <f t="shared" si="10"/>
-        <v>60000</v>
+        <f t="shared" si="11"/>
+        <v>36000</v>
       </c>
       <c r="N88" s="1">
         <v>1</v>
       </c>
       <c r="O88" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C89" s="1">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D89" s="1">
         <v>4</v>
       </c>
       <c r="E89" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" s="6">
-        <v>60000</v>
+        <v>3000</v>
       </c>
       <c r="G89" s="1">
-        <f t="shared" si="9"/>
-        <v>8</v>
+        <f t="shared" si="10"/>
+        <v>20</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>135</v>
@@ -4704,38 +4703,38 @@
         <v>5</v>
       </c>
       <c r="K89" s="1">
-        <v>4019</v>
+        <v>4012</v>
       </c>
       <c r="L89" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="M89" s="1">
-        <f t="shared" si="10"/>
-        <v>480000</v>
+        <f t="shared" si="11"/>
+        <v>60000</v>
       </c>
       <c r="N89" s="1">
         <v>1</v>
       </c>
       <c r="O89" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C90" s="1">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D90" s="1">
         <v>4</v>
       </c>
       <c r="E90" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="6">
-        <v>3000</v>
+        <v>60000</v>
       </c>
       <c r="G90" s="1">
-        <f t="shared" si="9"/>
-        <v>40</v>
+        <f t="shared" si="10"/>
+        <v>8</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>137</v>
@@ -4747,25 +4746,25 @@
         <v>5</v>
       </c>
       <c r="K90" s="1">
-        <v>4001</v>
+        <v>4019</v>
       </c>
       <c r="L90" s="1">
-        <v>1000000</v>
+        <v>1</v>
       </c>
       <c r="M90" s="1">
-        <f t="shared" si="10"/>
-        <v>120000</v>
+        <f t="shared" si="11"/>
+        <v>480000</v>
       </c>
       <c r="N90" s="1">
         <v>1</v>
       </c>
       <c r="O90" s="1">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C91" s="1">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D91" s="1">
         <v>4</v>
@@ -4777,7 +4776,7 @@
         <v>3000</v>
       </c>
       <c r="G91" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>40</v>
       </c>
       <c r="H91" s="1" t="s">
@@ -4790,13 +4789,13 @@
         <v>5</v>
       </c>
       <c r="K91" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L91" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M91" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>120000</v>
       </c>
       <c r="N91" s="1">
@@ -4808,20 +4807,20 @@
     </row>
     <row r="92" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C92" s="1">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D92" s="1">
         <v>4</v>
       </c>
       <c r="E92" s="1">
-        <v>6</v>
-      </c>
-      <c r="F92" s="1">
-        <v>30000</v>
+        <v>0</v>
+      </c>
+      <c r="F92" s="6">
+        <v>3000</v>
       </c>
       <c r="G92" s="1">
-        <f t="shared" si="9"/>
-        <v>5</v>
+        <f t="shared" si="10"/>
+        <v>40</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>141</v>
@@ -4833,68 +4832,68 @@
         <v>5</v>
       </c>
       <c r="K92" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L92" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M92" s="1">
+        <f t="shared" si="11"/>
+        <v>120000</v>
+      </c>
+      <c r="N92" s="1">
+        <v>1</v>
+      </c>
+      <c r="O92" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C93" s="1">
+        <v>228</v>
+      </c>
+      <c r="D93" s="1">
+        <v>4</v>
+      </c>
+      <c r="E93" s="1">
+        <v>6</v>
+      </c>
+      <c r="F93" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G93" s="1">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J93" s="1">
+        <v>5</v>
+      </c>
+      <c r="K93" s="1">
         <v>4026</v>
       </c>
-      <c r="L92" s="1">
-        <v>1</v>
-      </c>
-      <c r="M92" s="1">
-        <f t="shared" si="10"/>
+      <c r="L93" s="1">
+        <v>1</v>
+      </c>
+      <c r="M93" s="1">
+        <f t="shared" si="11"/>
         <v>150000</v>
       </c>
-      <c r="N92" s="1">
-        <v>1</v>
-      </c>
-      <c r="O92" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C94" s="1">
-        <v>231</v>
-      </c>
-      <c r="D94" s="1">
-        <v>5</v>
-      </c>
-      <c r="E94" s="1">
-        <v>0</v>
-      </c>
-      <c r="F94" s="1">
-        <v>800</v>
-      </c>
-      <c r="G94" s="1">
-        <f t="shared" ref="G94:G101" si="11">N94*O94</f>
-        <v>1200</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J94" s="1">
-        <v>5</v>
-      </c>
-      <c r="K94" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L94" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M94" s="1">
-        <f t="shared" ref="M94:M101" si="12">F94*G94</f>
-        <v>960000</v>
-      </c>
-      <c r="N94" s="1">
-        <v>4</v>
-      </c>
-      <c r="O94" s="1">
-        <v>300</v>
+      <c r="N93" s="1">
+        <v>1</v>
+      </c>
+      <c r="O93" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C95" s="1">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D95" s="1">
         <v>5</v>
@@ -4906,8 +4905,8 @@
         <v>800</v>
       </c>
       <c r="G95" s="1">
-        <f t="shared" si="11"/>
-        <v>2000</v>
+        <f t="shared" ref="G95:G102" si="12">N95*O95</f>
+        <v>1200</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>129</v>
@@ -4919,25 +4918,25 @@
         <v>5</v>
       </c>
       <c r="K95" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="L95" s="1">
         <v>1000</v>
       </c>
       <c r="M95" s="1">
-        <f t="shared" si="12"/>
-        <v>1600000</v>
+        <f t="shared" ref="M95:M102" si="13">F95*G95</f>
+        <v>960000</v>
       </c>
       <c r="N95" s="1">
         <v>4</v>
       </c>
       <c r="O95" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="96" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C96" s="1">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D96" s="1">
         <v>5</v>
@@ -4946,11 +4945,11 @@
         <v>0</v>
       </c>
       <c r="F96" s="1">
-        <v>8000</v>
+        <v>800</v>
       </c>
       <c r="G96" s="1">
-        <f t="shared" si="11"/>
-        <v>24</v>
+        <f t="shared" si="12"/>
+        <v>2000</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>131</v>
@@ -4959,28 +4958,28 @@
         <v>132</v>
       </c>
       <c r="J96" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K96" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="L96" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="M96" s="1">
-        <f t="shared" si="12"/>
-        <v>192000</v>
+        <f t="shared" si="13"/>
+        <v>1600000</v>
       </c>
       <c r="N96" s="1">
         <v>4</v>
       </c>
       <c r="O96" s="1">
-        <v>6</v>
+        <v>500</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C97" s="1">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D97" s="1">
         <v>5</v>
@@ -4989,11 +4988,11 @@
         <v>0</v>
       </c>
       <c r="F97" s="1">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="G97" s="1">
-        <f t="shared" si="11"/>
-        <v>80</v>
+        <f t="shared" si="12"/>
+        <v>24</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>133</v>
@@ -5002,41 +5001,41 @@
         <v>134</v>
       </c>
       <c r="J97" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K97" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="L97" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M97" s="1">
-        <f t="shared" si="12"/>
-        <v>320000</v>
+        <f t="shared" si="13"/>
+        <v>192000</v>
       </c>
       <c r="N97" s="1">
         <v>4</v>
       </c>
       <c r="O97" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C98" s="1">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D98" s="1">
         <v>5</v>
       </c>
       <c r="E98" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F98" s="1">
-        <v>75000</v>
+        <v>4000</v>
       </c>
       <c r="G98" s="1">
-        <f t="shared" si="11"/>
-        <v>32</v>
+        <f t="shared" si="12"/>
+        <v>80</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>135</v>
@@ -5048,38 +5047,38 @@
         <v>5</v>
       </c>
       <c r="K98" s="1">
-        <v>4019</v>
+        <v>4012</v>
       </c>
       <c r="L98" s="1">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="M98" s="1">
-        <f t="shared" si="12"/>
-        <v>2400000</v>
+        <f t="shared" si="13"/>
+        <v>320000</v>
       </c>
       <c r="N98" s="1">
         <v>4</v>
       </c>
       <c r="O98" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C99" s="1">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D99" s="1">
         <v>5</v>
       </c>
       <c r="E99" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="1">
-        <v>4000</v>
+        <v>75000</v>
       </c>
       <c r="G99" s="1">
-        <f t="shared" si="11"/>
-        <v>160</v>
+        <f t="shared" si="12"/>
+        <v>32</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>137</v>
@@ -5091,25 +5090,25 @@
         <v>5</v>
       </c>
       <c r="K99" s="1">
-        <v>4001</v>
+        <v>4019</v>
       </c>
       <c r="L99" s="1">
-        <v>1000000</v>
+        <v>1</v>
       </c>
       <c r="M99" s="1">
-        <f t="shared" si="12"/>
-        <v>640000</v>
+        <f t="shared" si="13"/>
+        <v>2400000</v>
       </c>
       <c r="N99" s="1">
         <v>4</v>
       </c>
       <c r="O99" s="1">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C100" s="1">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D100" s="1">
         <v>5</v>
@@ -5121,7 +5120,7 @@
         <v>4000</v>
       </c>
       <c r="G100" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>160</v>
       </c>
       <c r="H100" s="1" t="s">
@@ -5134,13 +5133,13 @@
         <v>5</v>
       </c>
       <c r="K100" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L100" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M100" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>640000</v>
       </c>
       <c r="N100" s="1">
@@ -5152,20 +5151,20 @@
     </row>
     <row r="101" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C101" s="1">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D101" s="1">
         <v>5</v>
       </c>
       <c r="E101" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F101" s="1">
-        <v>30000</v>
+        <v>4000</v>
       </c>
       <c r="G101" s="1">
-        <f t="shared" si="11"/>
-        <v>5</v>
+        <f t="shared" si="12"/>
+        <v>160</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>141</v>
@@ -5177,73 +5176,80 @@
         <v>5</v>
       </c>
       <c r="K101" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L101" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M101" s="1">
+        <f t="shared" si="13"/>
+        <v>640000</v>
+      </c>
+      <c r="N101" s="1">
+        <v>4</v>
+      </c>
+      <c r="O101" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="102" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C102" s="1">
+        <v>238</v>
+      </c>
+      <c r="D102" s="1">
+        <v>5</v>
+      </c>
+      <c r="E102" s="1">
+        <v>6</v>
+      </c>
+      <c r="F102" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G102" s="1">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J102" s="1">
+        <v>5</v>
+      </c>
+      <c r="K102" s="1">
         <v>4026</v>
       </c>
-      <c r="L101" s="1">
-        <v>1</v>
-      </c>
-      <c r="M101" s="1">
-        <f t="shared" si="12"/>
+      <c r="L102" s="1">
+        <v>1</v>
+      </c>
+      <c r="M102" s="1">
+        <f t="shared" si="13"/>
         <v>150000</v>
       </c>
-      <c r="N101" s="1">
-        <v>1</v>
-      </c>
-      <c r="O101" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="103" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C103" s="1">
-        <v>999</v>
-      </c>
-      <c r="D103" s="1">
-        <v>0</v>
-      </c>
-      <c r="E103" s="1">
-        <v>0</v>
-      </c>
-      <c r="F103" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G103" s="1">
-        <v>50</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I103" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J103" s="1">
-        <v>5</v>
-      </c>
-      <c r="K103" s="1">
-        <v>4006</v>
-      </c>
-      <c r="L103" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M103" s="1">
-        <f t="shared" ref="M103:M105" si="13">F103*G103</f>
-        <v>50000</v>
+      <c r="N102" s="1">
+        <v>1</v>
+      </c>
+      <c r="O102" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C104" s="1">
+        <v>999</v>
+      </c>
+      <c r="D104" s="1">
+        <v>0</v>
+      </c>
+      <c r="E104" s="1">
+        <v>0</v>
+      </c>
+      <c r="F104" s="1">
         <v>1000</v>
       </c>
-      <c r="D104" s="1">
-        <v>0</v>
-      </c>
-      <c r="E104" s="1">
-        <v>0</v>
-      </c>
-      <c r="F104" s="1">
-        <v>2000</v>
-      </c>
       <c r="G104" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>145</v>
@@ -5255,19 +5261,19 @@
         <v>5</v>
       </c>
       <c r="K104" s="1">
-        <v>4010</v>
+        <v>4006</v>
       </c>
       <c r="L104" s="1">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="M104" s="1">
-        <f t="shared" si="13"/>
-        <v>200000</v>
+        <f t="shared" ref="M104:M106" si="14">F104*G104</f>
+        <v>50000</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C105" s="1">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="D105" s="1">
         <v>0</v>
@@ -5279,7 +5285,7 @@
         <v>2000</v>
       </c>
       <c r="G105" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>147</v>
@@ -5291,13 +5297,49 @@
         <v>5</v>
       </c>
       <c r="K105" s="1">
+        <v>4010</v>
+      </c>
+      <c r="L105" s="1">
+        <v>5</v>
+      </c>
+      <c r="M105" s="1">
+        <f t="shared" si="14"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="106" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C106" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D106" s="1">
+        <v>0</v>
+      </c>
+      <c r="E106" s="1">
+        <v>0</v>
+      </c>
+      <c r="F106" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G106" s="1">
+        <v>50</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J106" s="1">
+        <v>5</v>
+      </c>
+      <c r="K106" s="1">
         <v>4102</v>
       </c>
-      <c r="L105" s="1">
+      <c r="L106" s="1">
         <v>20</v>
       </c>
-      <c r="M105" s="1">
-        <f t="shared" si="13"/>
+      <c r="M106" s="1">
+        <f t="shared" si="14"/>
         <v>100000</v>
       </c>
     </row>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -1968,7 +1968,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="1">
-        <f t="shared" ref="M15:M30" si="1">F15*G15</f>
+        <f t="shared" ref="M15:M37" si="1">F15*G15</f>
         <v>100000</v>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
         <v>1</v>
       </c>
       <c r="M31" s="1">
-        <f>F31*G31</f>
+        <f t="shared" si="1"/>
         <v>2000</v>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="M32" s="1">
-        <f>F32*G32</f>
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
         <v>1</v>
       </c>
       <c r="M33" s="1">
-        <f>F33*G33</f>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
         <v>1</v>
       </c>
       <c r="M34" s="1">
-        <f>F34*G34</f>
+        <f t="shared" si="1"/>
         <v>300000</v>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="M35" s="1">
-        <f>F35*G35</f>
+        <f t="shared" si="1"/>
         <v>250000</v>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
         <v>1</v>
       </c>
       <c r="M36" s="1">
-        <f>F36*G36</f>
+        <f t="shared" si="1"/>
         <v>400000</v>
       </c>
     </row>
@@ -2742,7 +2742,7 @@
         <v>83</v>
       </c>
       <c r="G37" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>84</v>
@@ -2760,8 +2760,8 @@
         <v>1</v>
       </c>
       <c r="M37" s="1">
-        <f>F37*G37</f>
-        <v>2400000</v>
+        <f t="shared" si="1"/>
+        <v>1500000</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:13">

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="159">
   <si>
     <t>#</t>
   </si>
@@ -416,6 +416,36 @@
     <t>低级法宝自选</t>
   </si>
   <si>
+    <t>兑换时装精华</t>
+  </si>
+  <si>
+    <t>时装精华</t>
+  </si>
+  <si>
+    <t>兑换10介技能自选包*1</t>
+  </si>
+  <si>
+    <t>10介技能</t>
+  </si>
+  <si>
+    <t>青龙自选</t>
+  </si>
+  <si>
+    <t>白虎自选</t>
+  </si>
+  <si>
+    <t>朱雀自选</t>
+  </si>
+  <si>
+    <t>行气丹</t>
+  </si>
+  <si>
+    <t>兑换经验丹*100</t>
+  </si>
+  <si>
+    <t>经验丹</t>
+  </si>
+  <si>
     <t>兑换四格碎片*1000</t>
   </si>
   <si>
@@ -426,12 +456,6 @@
   </si>
   <si>
     <t>图鉴碎片</t>
-  </si>
-  <si>
-    <t>兑换经验丹*100</t>
-  </si>
-  <si>
-    <t>经验丹</t>
   </si>
   <si>
     <t>兑换传世精华*200</t>
@@ -1496,18 +1520,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O106"/>
+  <dimension ref="C1:O118"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="15.3628318584071" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.2566371681416" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.3636363636364" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.2545454545455" style="1" customWidth="1"/>
     <col min="7" max="7" width="12" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5044247787611" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.1238938053097" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.8761061946903" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.50442477876106" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5044247787611" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1272727272727" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.8727272727273" style="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1626,7 +1650,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="1">
-        <v>168</v>
+        <v>388</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>14</v>
@@ -1645,7 +1669,7 @@
       </c>
       <c r="M6" s="1">
         <f t="shared" ref="M6:M14" si="0">F6*G6</f>
-        <v>50400</v>
+        <v>116400</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:13">
@@ -1662,7 +1686,7 @@
         <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>168</v>
+        <v>388</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>16</v>
@@ -1681,7 +1705,7 @@
       </c>
       <c r="M7" s="1">
         <f t="shared" si="0"/>
-        <v>50400</v>
+        <v>116400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1698,7 +1722,7 @@
         <v>13</v>
       </c>
       <c r="G8" s="1">
-        <v>168</v>
+        <v>388</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>18</v>
@@ -1717,7 +1741,7 @@
       </c>
       <c r="M8" s="1">
         <f t="shared" si="0"/>
-        <v>50400</v>
+        <v>116400</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:13">
@@ -1734,7 +1758,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="1">
-        <v>66</v>
+        <v>188</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>21</v>
@@ -1753,7 +1777,7 @@
       </c>
       <c r="M9" s="1">
         <f t="shared" si="0"/>
-        <v>33000</v>
+        <v>94000</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:13">
@@ -1770,7 +1794,7 @@
         <v>13</v>
       </c>
       <c r="G10" s="1">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>23</v>
@@ -1789,7 +1813,7 @@
       </c>
       <c r="M10" s="1">
         <f t="shared" si="0"/>
-        <v>60000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:13">
@@ -1806,7 +1830,7 @@
         <v>13</v>
       </c>
       <c r="G11" s="1">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>25</v>
@@ -1825,7 +1849,7 @@
       </c>
       <c r="M11" s="1">
         <f t="shared" si="0"/>
-        <v>60000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:13">
@@ -1842,7 +1866,7 @@
         <v>13</v>
       </c>
       <c r="G12" s="1">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>27</v>
@@ -1861,7 +1885,7 @@
       </c>
       <c r="M12" s="1">
         <f t="shared" si="0"/>
-        <v>60000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:13">
@@ -1878,7 +1902,7 @@
         <v>20</v>
       </c>
       <c r="G13" s="1">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>29</v>
@@ -1897,7 +1921,7 @@
       </c>
       <c r="M13" s="1">
         <f t="shared" si="0"/>
-        <v>100000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:13">
@@ -1914,7 +1938,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="1">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>31</v>
@@ -1933,7 +1957,7 @@
       </c>
       <c r="M14" s="1">
         <f t="shared" si="0"/>
-        <v>100000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:13">
@@ -1950,7 +1974,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="1">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>33</v>
@@ -1969,7 +1993,7 @@
       </c>
       <c r="M15" s="1">
         <f t="shared" ref="M15:M37" si="1">F15*G15</f>
-        <v>100000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:13">
@@ -1986,7 +2010,7 @@
         <v>13</v>
       </c>
       <c r="G16" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>35</v>
@@ -2005,7 +2029,7 @@
       </c>
       <c r="M16" s="1">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:13">
@@ -2022,7 +2046,7 @@
         <v>13</v>
       </c>
       <c r="G17" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>37</v>
@@ -2041,7 +2065,7 @@
       </c>
       <c r="M17" s="1">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:13">
@@ -2058,7 +2082,7 @@
         <v>13</v>
       </c>
       <c r="G18" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>39</v>
@@ -2077,7 +2101,7 @@
       </c>
       <c r="M18" s="1">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:13">
@@ -2094,7 +2118,7 @@
         <v>13</v>
       </c>
       <c r="G19" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>41</v>
@@ -2113,7 +2137,7 @@
       </c>
       <c r="M19" s="1">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:13">
@@ -2130,7 +2154,7 @@
         <v>13</v>
       </c>
       <c r="G20" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>43</v>
@@ -2149,7 +2173,7 @@
       </c>
       <c r="M20" s="1">
         <f t="shared" si="1"/>
-        <v>30000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:13">
@@ -2166,7 +2190,7 @@
         <v>45</v>
       </c>
       <c r="G21" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>46</v>
@@ -2185,7 +2209,7 @@
       </c>
       <c r="M21" s="1">
         <f t="shared" si="1"/>
-        <v>60000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:13">
@@ -2202,7 +2226,7 @@
         <v>45</v>
       </c>
       <c r="G22" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>48</v>
@@ -2221,7 +2245,7 @@
       </c>
       <c r="M22" s="1">
         <f t="shared" si="1"/>
-        <v>60000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:13">
@@ -2238,7 +2262,7 @@
         <v>45</v>
       </c>
       <c r="G23" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>50</v>
@@ -2257,7 +2281,7 @@
       </c>
       <c r="M23" s="1">
         <f t="shared" si="1"/>
-        <v>60000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:13">
@@ -2274,7 +2298,7 @@
         <v>45</v>
       </c>
       <c r="G24" s="1">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>52</v>
@@ -2293,7 +2317,7 @@
       </c>
       <c r="M24" s="1">
         <f t="shared" si="1"/>
-        <v>60000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:13">
@@ -2310,7 +2334,7 @@
         <v>1000</v>
       </c>
       <c r="G25" s="1">
-        <v>88</v>
+        <v>264</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>54</v>
@@ -2329,7 +2353,7 @@
       </c>
       <c r="M25" s="1">
         <f t="shared" si="1"/>
-        <v>88000</v>
+        <v>264000</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:13">
@@ -2346,7 +2370,7 @@
         <v>2000</v>
       </c>
       <c r="G26" s="1">
-        <v>77</v>
+        <v>231</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>56</v>
@@ -2365,7 +2389,7 @@
       </c>
       <c r="M26" s="1">
         <f t="shared" si="1"/>
-        <v>154000</v>
+        <v>462000</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:13">
@@ -2382,7 +2406,7 @@
         <v>3000</v>
       </c>
       <c r="G27" s="1">
-        <v>66</v>
+        <v>198</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>58</v>
@@ -2401,7 +2425,7 @@
       </c>
       <c r="M27" s="1">
         <f t="shared" si="1"/>
-        <v>198000</v>
+        <v>594000</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:13">
@@ -2418,7 +2442,7 @@
         <v>4000</v>
       </c>
       <c r="G28" s="1">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>60</v>
@@ -2437,7 +2461,7 @@
       </c>
       <c r="M28" s="1">
         <f t="shared" si="1"/>
-        <v>220000</v>
+        <v>660000</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:13">
@@ -2454,7 +2478,7 @@
         <v>5000</v>
       </c>
       <c r="G29" s="1">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>62</v>
@@ -2473,7 +2497,7 @@
       </c>
       <c r="M29" s="1">
         <f t="shared" si="1"/>
-        <v>220000</v>
+        <v>660000</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:13">
@@ -2490,7 +2514,7 @@
         <v>6000</v>
       </c>
       <c r="G30" s="1">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>64</v>
@@ -2509,7 +2533,7 @@
       </c>
       <c r="M30" s="1">
         <f t="shared" si="1"/>
-        <v>198000</v>
+        <v>594000</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:13">
@@ -2634,7 +2658,7 @@
         <v>74</v>
       </c>
       <c r="G34" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>75</v>
@@ -2653,7 +2677,7 @@
       </c>
       <c r="M34" s="1">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:13">
@@ -2670,7 +2694,7 @@
         <v>77</v>
       </c>
       <c r="G35" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>78</v>
@@ -2689,7 +2713,7 @@
       </c>
       <c r="M35" s="1">
         <f t="shared" si="1"/>
-        <v>250000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:13">
@@ -2742,7 +2766,7 @@
         <v>83</v>
       </c>
       <c r="G37" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>84</v>
@@ -2761,7 +2785,7 @@
       </c>
       <c r="M37" s="1">
         <f t="shared" si="1"/>
-        <v>1500000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:13">
@@ -2778,7 +2802,7 @@
         <v>86</v>
       </c>
       <c r="G38" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>87</v>
@@ -2797,7 +2821,7 @@
       </c>
       <c r="M38" s="1">
         <f t="shared" ref="M38:M43" si="2">F38*G38</f>
-        <v>800000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:13">
@@ -2814,7 +2838,7 @@
         <v>89</v>
       </c>
       <c r="G39" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>90</v>
@@ -2833,7 +2857,7 @@
       </c>
       <c r="M39" s="1">
         <f t="shared" si="2"/>
-        <v>500000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:13">
@@ -2850,7 +2874,7 @@
         <v>92</v>
       </c>
       <c r="G40" s="1">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>93</v>
@@ -2869,7 +2893,7 @@
       </c>
       <c r="M40" s="1">
         <f t="shared" si="2"/>
-        <v>2000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:13">
@@ -2886,7 +2910,7 @@
         <v>92</v>
       </c>
       <c r="G41" s="1">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>95</v>
@@ -2905,7 +2929,7 @@
       </c>
       <c r="M41" s="1">
         <f t="shared" si="2"/>
-        <v>1000000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:13">
@@ -2922,7 +2946,7 @@
         <v>3000</v>
       </c>
       <c r="G42" s="1">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>97</v>
@@ -2941,7 +2965,7 @@
       </c>
       <c r="M42" s="1">
         <f t="shared" si="2"/>
-        <v>600000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:13">
@@ -2958,7 +2982,7 @@
         <v>20000</v>
       </c>
       <c r="G43" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>99</v>
@@ -2977,7 +3001,7 @@
       </c>
       <c r="M43" s="1">
         <f t="shared" si="2"/>
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:13">
@@ -2994,7 +3018,7 @@
         <v>20000</v>
       </c>
       <c r="G44" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>101</v>
@@ -3013,7 +3037,7 @@
       </c>
       <c r="M44" s="1">
         <f t="shared" ref="M44:M57" si="3">F44*G44</f>
-        <v>800000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -3027,10 +3051,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="1">
-        <v>388888</v>
+        <v>288888</v>
       </c>
       <c r="G45" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>103</v>
@@ -3049,7 +3073,7 @@
       </c>
       <c r="M45" s="1">
         <f t="shared" si="3"/>
-        <v>388888</v>
+        <v>577776</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -3066,7 +3090,7 @@
         <v>300000</v>
       </c>
       <c r="G46" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>105</v>
@@ -3085,7 +3109,7 @@
       </c>
       <c r="M46" s="1">
         <f t="shared" si="3"/>
-        <v>600000</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:13">
@@ -3478,7 +3502,7 @@
         <v>50000</v>
       </c>
       <c r="G57" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>127</v>
@@ -3497,7 +3521,7 @@
       </c>
       <c r="M57" s="1">
         <f t="shared" si="3"/>
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:15">
@@ -3515,22 +3539,21 @@
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C59" s="1">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="D59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
       </c>
       <c r="F59" s="1">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="G59" s="1">
-        <f t="shared" ref="G59:G66" si="4">N59*O59</f>
-        <v>300</v>
+        <v>5</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>129</v>
@@ -3542,38 +3565,31 @@
         <v>5</v>
       </c>
       <c r="K59" s="1">
-        <v>4007</v>
+        <v>4034</v>
       </c>
       <c r="L59" s="1">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="M59" s="1">
-        <f t="shared" ref="M59:M66" si="5">F59*G59</f>
-        <v>30000</v>
-      </c>
-      <c r="N59" s="1">
-        <v>1</v>
-      </c>
-      <c r="O59" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:15">
+        <f t="shared" ref="M59:M63" si="4">F59*G59</f>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C60" s="1">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="D60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
       </c>
       <c r="F60" s="1">
-        <v>100</v>
+        <v>50000</v>
       </c>
       <c r="G60" s="1">
-        <f t="shared" si="4"/>
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>131</v>
@@ -3582,1764 +3598,2099 @@
         <v>132</v>
       </c>
       <c r="J60" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K60" s="1">
-        <v>4101</v>
+        <v>27</v>
       </c>
       <c r="L60" s="1">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="M60" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>50000</v>
       </c>
-      <c r="N60" s="1">
-        <v>1</v>
-      </c>
-      <c r="O60" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:15">
+    </row>
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C61" s="1">
-        <v>104</v>
+        <v>55</v>
       </c>
       <c r="D61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>0</v>
-      </c>
-      <c r="F61" s="1">
-        <v>1000</v>
+        <v>4</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="G61" s="1">
-        <f t="shared" si="4"/>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>133</v>
       </c>
       <c r="I61" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J61" s="1">
+        <v>4</v>
+      </c>
+      <c r="K61" s="1">
+        <v>35</v>
+      </c>
+      <c r="L61" s="1">
+        <v>1</v>
+      </c>
+      <c r="M61" s="1">
+        <f t="shared" si="4"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C62" s="1">
+        <v>56</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0</v>
+      </c>
+      <c r="E62" s="1">
+        <v>6</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="G62" s="1">
+        <v>1</v>
+      </c>
+      <c r="H62" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="J61" s="1">
+      <c r="I62" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J62" s="1">
+        <v>4</v>
+      </c>
+      <c r="K62" s="1">
+        <v>37</v>
+      </c>
+      <c r="L62" s="1">
+        <v>1</v>
+      </c>
+      <c r="M62" s="1">
+        <f t="shared" si="4"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C63" s="1">
+        <v>57</v>
+      </c>
+      <c r="D63" s="1">
+        <v>0</v>
+      </c>
+      <c r="E63" s="1">
+        <v>8</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="G63" s="1">
+        <v>1</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J63" s="1">
+        <v>4</v>
+      </c>
+      <c r="K63" s="1">
+        <v>38</v>
+      </c>
+      <c r="L63" s="1">
+        <v>1</v>
+      </c>
+      <c r="M63" s="1">
+        <f t="shared" si="4"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C64" s="1">
+        <v>58</v>
+      </c>
+      <c r="D64" s="1">
+        <v>0</v>
+      </c>
+      <c r="E64" s="1">
+        <v>10</v>
+      </c>
+      <c r="F64" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G64" s="1">
+        <v>20</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J64" s="1">
+        <v>5</v>
+      </c>
+      <c r="K64" s="1">
+        <v>4033</v>
+      </c>
+      <c r="L64" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M64" s="1">
+        <f>F64*G64</f>
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C65" s="1">
+        <v>59</v>
+      </c>
+      <c r="D65" s="1">
+        <v>2</v>
+      </c>
+      <c r="E65" s="1">
+        <v>0</v>
+      </c>
+      <c r="F65" s="6">
+        <v>5000</v>
+      </c>
+      <c r="G65" s="1">
+        <v>200</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J65" s="1">
         <v>15</v>
       </c>
-      <c r="K61" s="1">
+      <c r="K65" s="1">
         <v>4014</v>
       </c>
-      <c r="L61" s="1">
+      <c r="L65" s="1">
         <v>100</v>
       </c>
-      <c r="M61" s="1">
-        <f t="shared" si="5"/>
-        <v>6000</v>
-      </c>
-      <c r="N61" s="1">
-        <v>1</v>
-      </c>
-      <c r="O61" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C62" s="1">
-        <v>105</v>
-      </c>
-      <c r="D62" s="1">
-        <v>1</v>
-      </c>
-      <c r="E62" s="1">
-        <v>0</v>
-      </c>
-      <c r="F62" s="1">
-        <v>500</v>
-      </c>
-      <c r="G62" s="1">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J62" s="1">
-        <v>5</v>
-      </c>
-      <c r="K62" s="1">
-        <v>4012</v>
-      </c>
-      <c r="L62" s="1">
-        <v>200</v>
-      </c>
-      <c r="M62" s="1">
-        <f t="shared" si="5"/>
-        <v>10000</v>
-      </c>
-      <c r="N62" s="1">
-        <v>1</v>
-      </c>
-      <c r="O62" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C63" s="1">
-        <v>106</v>
-      </c>
-      <c r="D63" s="1">
-        <v>1</v>
-      </c>
-      <c r="E63" s="1">
-        <v>1</v>
-      </c>
-      <c r="F63" s="1">
-        <v>15000</v>
-      </c>
-      <c r="G63" s="1">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J63" s="1">
-        <v>5</v>
-      </c>
-      <c r="K63" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L63" s="1">
-        <v>1</v>
-      </c>
-      <c r="M63" s="1">
-        <f t="shared" si="5"/>
-        <v>120000</v>
-      </c>
-      <c r="N63" s="1">
-        <v>1</v>
-      </c>
-      <c r="O63" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C64" s="1">
-        <v>107</v>
-      </c>
-      <c r="D64" s="1">
-        <v>1</v>
-      </c>
-      <c r="E64" s="1">
-        <v>0</v>
-      </c>
-      <c r="F64" s="1">
-        <v>500</v>
-      </c>
-      <c r="G64" s="1">
-        <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J64" s="1">
-        <v>5</v>
-      </c>
-      <c r="K64" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L64" s="1">
+      <c r="M65" s="1">
+        <f>F65*G65</f>
         <v>1000000</v>
       </c>
-      <c r="M64" s="1">
-        <f t="shared" si="5"/>
-        <v>20000</v>
-      </c>
-      <c r="N64" s="1">
-        <v>1</v>
-      </c>
-      <c r="O64" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C65" s="1">
-        <v>108</v>
-      </c>
-      <c r="D65" s="1">
-        <v>1</v>
-      </c>
-      <c r="E65" s="1">
-        <v>0</v>
-      </c>
-      <c r="F65" s="1">
-        <v>500</v>
-      </c>
-      <c r="G65" s="1">
-        <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J65" s="1">
-        <v>5</v>
-      </c>
-      <c r="K65" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L65" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M65" s="1">
-        <f t="shared" si="5"/>
-        <v>20000</v>
-      </c>
-      <c r="N65" s="1">
-        <v>1</v>
-      </c>
-      <c r="O65" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C66" s="1">
-        <v>109</v>
-      </c>
-      <c r="D66" s="1">
-        <v>1</v>
-      </c>
-      <c r="E66" s="1">
-        <v>6</v>
-      </c>
-      <c r="F66" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G66" s="1">
-        <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J66" s="1">
-        <v>5</v>
-      </c>
-      <c r="K66" s="1">
-        <v>4026</v>
-      </c>
-      <c r="L66" s="1">
-        <v>1</v>
-      </c>
-      <c r="M66" s="1">
-        <f t="shared" si="5"/>
-        <v>150000</v>
-      </c>
-      <c r="N66" s="1">
-        <v>1</v>
-      </c>
-      <c r="O66" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C68" s="1">
-        <v>201</v>
-      </c>
-      <c r="D68" s="1">
-        <v>2</v>
-      </c>
-      <c r="E68" s="1">
-        <v>0</v>
-      </c>
-      <c r="F68" s="6">
-        <v>200</v>
-      </c>
-      <c r="G68" s="1">
-        <f t="shared" ref="G68:G75" si="6">N68*O68</f>
-        <v>300</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J68" s="1">
-        <v>5</v>
-      </c>
-      <c r="K68" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L68" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M68" s="1">
-        <f t="shared" ref="M68:M75" si="7">F68*G68</f>
-        <v>60000</v>
-      </c>
-      <c r="N68" s="1">
-        <v>1</v>
-      </c>
-      <c r="O68" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C69" s="1">
-        <v>202</v>
-      </c>
-      <c r="D69" s="1">
-        <v>2</v>
-      </c>
-      <c r="E69" s="1">
-        <v>0</v>
-      </c>
-      <c r="F69" s="6">
-        <v>200</v>
-      </c>
-      <c r="G69" s="1">
-        <f t="shared" si="6"/>
-        <v>500</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J69" s="1">
-        <v>5</v>
-      </c>
-      <c r="K69" s="1">
-        <v>4101</v>
-      </c>
-      <c r="L69" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M69" s="1">
-        <f t="shared" si="7"/>
-        <v>100000</v>
-      </c>
-      <c r="N69" s="1">
-        <v>1</v>
-      </c>
-      <c r="O69" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C70" s="1">
-        <v>203</v>
-      </c>
-      <c r="D70" s="1">
-        <v>2</v>
-      </c>
-      <c r="E70" s="1">
-        <v>0</v>
-      </c>
-      <c r="F70" s="6">
-        <v>2000</v>
-      </c>
-      <c r="G70" s="1">
-        <f t="shared" si="6"/>
-        <v>6</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J70" s="1">
-        <v>15</v>
-      </c>
-      <c r="K70" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L70" s="1">
-        <v>100</v>
-      </c>
-      <c r="M70" s="1">
-        <f t="shared" si="7"/>
-        <v>12000</v>
-      </c>
-      <c r="N70" s="1">
-        <v>1</v>
-      </c>
-      <c r="O70" s="1">
-        <v>6</v>
-      </c>
+    </row>
+    <row r="66" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
+    </row>
+    <row r="67" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
+    </row>
+    <row r="68" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+    </row>
+    <row r="69" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
+    </row>
+    <row r="70" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
     </row>
     <row r="71" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C71" s="1">
-        <v>204</v>
+        <v>102</v>
       </c>
       <c r="D71" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" s="1">
         <v>0</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F71" s="1">
+        <v>100</v>
+      </c>
+      <c r="G71" s="1">
+        <f t="shared" ref="G71:G78" si="5">N71*O71</f>
+        <v>300</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J71" s="1">
+        <v>5</v>
+      </c>
+      <c r="K71" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L71" s="1">
         <v>1000</v>
       </c>
-      <c r="G71" s="1">
-        <f t="shared" si="6"/>
-        <v>20</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J71" s="1">
-        <v>5</v>
-      </c>
-      <c r="K71" s="1">
-        <v>4012</v>
-      </c>
-      <c r="L71" s="1">
-        <v>200</v>
-      </c>
       <c r="M71" s="1">
-        <f t="shared" si="7"/>
-        <v>20000</v>
+        <f t="shared" ref="M71:M78" si="6">F71*G71</f>
+        <v>30000</v>
       </c>
       <c r="N71" s="1">
         <v>1</v>
       </c>
       <c r="O71" s="1">
-        <v>20</v>
+        <v>300</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C72" s="1">
-        <v>205</v>
+        <v>103</v>
       </c>
       <c r="D72" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" s="1">
-        <v>1</v>
-      </c>
-      <c r="F72" s="6">
-        <v>30000</v>
+        <v>0</v>
+      </c>
+      <c r="F72" s="1">
+        <v>100</v>
       </c>
       <c r="G72" s="1">
+        <f t="shared" si="5"/>
+        <v>500</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J72" s="1">
+        <v>5</v>
+      </c>
+      <c r="K72" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L72" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M72" s="1">
         <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J72" s="1">
-        <v>5</v>
-      </c>
-      <c r="K72" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L72" s="1">
-        <v>1</v>
-      </c>
-      <c r="M72" s="1">
-        <f t="shared" si="7"/>
-        <v>240000</v>
+        <v>50000</v>
       </c>
       <c r="N72" s="1">
         <v>1</v>
       </c>
       <c r="O72" s="1">
-        <v>8</v>
+        <v>500</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C73" s="1">
-        <v>206</v>
+        <v>104</v>
       </c>
       <c r="D73" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
       </c>
-      <c r="F73" s="6">
+      <c r="F73" s="1">
         <v>1000</v>
       </c>
       <c r="G73" s="1">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J73" s="1">
+        <v>15</v>
+      </c>
+      <c r="K73" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L73" s="1">
+        <v>100</v>
+      </c>
+      <c r="M73" s="1">
         <f t="shared" si="6"/>
-        <v>40</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J73" s="1">
-        <v>5</v>
-      </c>
-      <c r="K73" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L73" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M73" s="1">
-        <f t="shared" si="7"/>
-        <v>40000</v>
+        <v>6000</v>
       </c>
       <c r="N73" s="1">
         <v>1</v>
       </c>
       <c r="O73" s="1">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C74" s="1">
-        <v>207</v>
+        <v>105</v>
       </c>
       <c r="D74" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
       </c>
-      <c r="F74" s="6">
-        <v>1000</v>
+      <c r="F74" s="1">
+        <v>500</v>
       </c>
       <c r="G74" s="1">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J74" s="1">
+        <v>5</v>
+      </c>
+      <c r="K74" s="1">
+        <v>4012</v>
+      </c>
+      <c r="L74" s="1">
+        <v>200</v>
+      </c>
+      <c r="M74" s="1">
         <f t="shared" si="6"/>
-        <v>40</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J74" s="1">
-        <v>5</v>
-      </c>
-      <c r="K74" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L74" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M74" s="1">
-        <f t="shared" si="7"/>
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="N74" s="1">
         <v>1</v>
       </c>
       <c r="O74" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C75" s="1">
-        <v>208</v>
+        <v>106</v>
       </c>
       <c r="D75" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F75" s="1">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="G75" s="1">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J75" s="1">
+        <v>5</v>
+      </c>
+      <c r="K75" s="1">
+        <v>4019</v>
+      </c>
+      <c r="L75" s="1">
+        <v>1</v>
+      </c>
+      <c r="M75" s="1">
         <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J75" s="1">
-        <v>5</v>
-      </c>
-      <c r="K75" s="1">
-        <v>4026</v>
-      </c>
-      <c r="L75" s="1">
-        <v>1</v>
-      </c>
-      <c r="M75" s="1">
-        <f t="shared" si="7"/>
-        <v>150000</v>
+        <v>120000</v>
       </c>
       <c r="N75" s="1">
         <v>1</v>
       </c>
       <c r="O75" s="1">
-        <v>5</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C76" s="1">
+        <v>107</v>
+      </c>
+      <c r="D76" s="1">
+        <v>1</v>
+      </c>
+      <c r="E76" s="1">
+        <v>0</v>
+      </c>
+      <c r="F76" s="1">
+        <v>500</v>
+      </c>
+      <c r="G76" s="1">
+        <f t="shared" si="5"/>
+        <v>40</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J76" s="1">
+        <v>5</v>
+      </c>
+      <c r="K76" s="1">
+        <v>4001</v>
+      </c>
+      <c r="L76" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="M76" s="1">
+        <f t="shared" si="6"/>
+        <v>20000</v>
+      </c>
+      <c r="N76" s="1">
+        <v>1</v>
+      </c>
+      <c r="O76" s="1">
+        <v>40</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C77" s="1">
-        <v>211</v>
+        <v>108</v>
       </c>
       <c r="D77" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E77" s="1">
         <v>0</v>
       </c>
       <c r="F77" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G77" s="1">
-        <f t="shared" ref="G77:G84" si="8">N77*O77</f>
-        <v>300</v>
+        <f t="shared" si="5"/>
+        <v>40</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="J77" s="1">
         <v>5</v>
       </c>
       <c r="K77" s="1">
-        <v>4007</v>
+        <v>4002</v>
       </c>
       <c r="L77" s="1">
-        <v>1000</v>
+        <v>6000000</v>
       </c>
       <c r="M77" s="1">
-        <f t="shared" ref="M77:M84" si="9">F77*G77</f>
-        <v>120000</v>
+        <f t="shared" si="6"/>
+        <v>20000</v>
       </c>
       <c r="N77" s="1">
         <v>1</v>
       </c>
       <c r="O77" s="1">
-        <v>300</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C78" s="1">
-        <v>212</v>
+        <v>109</v>
       </c>
       <c r="D78" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F78" s="1">
-        <v>400</v>
+        <v>30000</v>
       </c>
       <c r="G78" s="1">
-        <f t="shared" si="8"/>
-        <v>500</v>
+        <f t="shared" si="5"/>
+        <v>5</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="J78" s="1">
         <v>5</v>
       </c>
       <c r="K78" s="1">
-        <v>4101</v>
+        <v>4026</v>
       </c>
       <c r="L78" s="1">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="M78" s="1">
-        <f t="shared" si="9"/>
-        <v>200000</v>
+        <f t="shared" si="6"/>
+        <v>150000</v>
       </c>
       <c r="N78" s="1">
         <v>1</v>
       </c>
       <c r="O78" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C79" s="1">
-        <v>213</v>
-      </c>
-      <c r="D79" s="1">
-        <v>3</v>
-      </c>
-      <c r="E79" s="1">
-        <v>0</v>
-      </c>
-      <c r="F79" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G79" s="1">
-        <f t="shared" si="8"/>
-        <v>6</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J79" s="1">
-        <v>15</v>
-      </c>
-      <c r="K79" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L79" s="1">
-        <v>100</v>
-      </c>
-      <c r="M79" s="1">
-        <f t="shared" si="9"/>
-        <v>24000</v>
-      </c>
-      <c r="N79" s="1">
-        <v>1</v>
-      </c>
-      <c r="O79" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C80" s="1">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="D80" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E80" s="1">
         <v>0</v>
       </c>
-      <c r="F80" s="1">
-        <v>2000</v>
+      <c r="F80" s="6">
+        <v>200</v>
       </c>
       <c r="G80" s="1">
-        <f t="shared" si="8"/>
-        <v>20</v>
+        <f t="shared" ref="G80:G87" si="7">N80*O80</f>
+        <v>300</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="J80" s="1">
         <v>5</v>
       </c>
       <c r="K80" s="1">
-        <v>4012</v>
+        <v>4007</v>
       </c>
       <c r="L80" s="1">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="M80" s="1">
-        <f t="shared" si="9"/>
-        <v>40000</v>
+        <f t="shared" ref="M80:M87" si="8">F80*G80</f>
+        <v>60000</v>
       </c>
       <c r="N80" s="1">
         <v>1</v>
       </c>
       <c r="O80" s="1">
-        <v>20</v>
+        <v>300</v>
       </c>
     </row>
     <row r="81" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C81" s="1">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="D81" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E81" s="1">
-        <v>1</v>
-      </c>
-      <c r="F81" s="1">
-        <v>45000</v>
+        <v>0</v>
+      </c>
+      <c r="F81" s="6">
+        <v>200</v>
       </c>
       <c r="G81" s="1">
+        <f t="shared" si="7"/>
+        <v>500</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J81" s="1">
+        <v>5</v>
+      </c>
+      <c r="K81" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L81" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M81" s="1">
         <f t="shared" si="8"/>
-        <v>8</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J81" s="1">
-        <v>5</v>
-      </c>
-      <c r="K81" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L81" s="1">
-        <v>1</v>
-      </c>
-      <c r="M81" s="1">
-        <f t="shared" si="9"/>
-        <v>360000</v>
+        <v>100000</v>
       </c>
       <c r="N81" s="1">
         <v>1</v>
       </c>
       <c r="O81" s="1">
-        <v>8</v>
+        <v>500</v>
       </c>
     </row>
     <row r="82" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C82" s="1">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="D82" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E82" s="1">
         <v>0</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82" s="6">
         <v>2000</v>
       </c>
       <c r="G82" s="1">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J82" s="1">
+        <v>15</v>
+      </c>
+      <c r="K82" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L82" s="1">
+        <v>100</v>
+      </c>
+      <c r="M82" s="1">
         <f t="shared" si="8"/>
-        <v>40</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J82" s="1">
-        <v>5</v>
-      </c>
-      <c r="K82" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L82" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M82" s="1">
-        <f t="shared" si="9"/>
-        <v>80000</v>
+        <v>12000</v>
       </c>
       <c r="N82" s="1">
         <v>1</v>
       </c>
       <c r="O82" s="1">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C83" s="1">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="D83" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83" s="1">
         <v>0</v>
       </c>
-      <c r="F83" s="1">
-        <v>2000</v>
+      <c r="F83" s="6">
+        <v>1000</v>
       </c>
       <c r="G83" s="1">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J83" s="1">
+        <v>5</v>
+      </c>
+      <c r="K83" s="1">
+        <v>4012</v>
+      </c>
+      <c r="L83" s="1">
+        <v>200</v>
+      </c>
+      <c r="M83" s="1">
         <f t="shared" si="8"/>
-        <v>40</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J83" s="1">
-        <v>5</v>
-      </c>
-      <c r="K83" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L83" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M83" s="1">
-        <f t="shared" si="9"/>
-        <v>80000</v>
+        <v>20000</v>
       </c>
       <c r="N83" s="1">
         <v>1</v>
       </c>
       <c r="O83" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C84" s="1">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D84" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84" s="1">
-        <v>6</v>
-      </c>
-      <c r="F84" s="1">
+        <v>1</v>
+      </c>
+      <c r="F84" s="6">
         <v>30000</v>
       </c>
       <c r="G84" s="1">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J84" s="1">
+        <v>5</v>
+      </c>
+      <c r="K84" s="1">
+        <v>4019</v>
+      </c>
+      <c r="L84" s="1">
+        <v>1</v>
+      </c>
+      <c r="M84" s="1">
         <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J84" s="1">
-        <v>5</v>
-      </c>
-      <c r="K84" s="1">
-        <v>4026</v>
-      </c>
-      <c r="L84" s="1">
-        <v>1</v>
-      </c>
-      <c r="M84" s="1">
-        <f t="shared" si="9"/>
-        <v>150000</v>
+        <v>240000</v>
       </c>
       <c r="N84" s="1">
         <v>1</v>
       </c>
       <c r="O84" s="1">
-        <v>5</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C85" s="1">
+        <v>206</v>
+      </c>
+      <c r="D85" s="1">
+        <v>2</v>
+      </c>
+      <c r="E85" s="1">
+        <v>0</v>
+      </c>
+      <c r="F85" s="6">
+        <v>1000</v>
+      </c>
+      <c r="G85" s="1">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J85" s="1">
+        <v>5</v>
+      </c>
+      <c r="K85" s="1">
+        <v>4001</v>
+      </c>
+      <c r="L85" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="M85" s="1">
+        <f t="shared" si="8"/>
+        <v>40000</v>
+      </c>
+      <c r="N85" s="1">
+        <v>1</v>
+      </c>
+      <c r="O85" s="1">
+        <v>40</v>
       </c>
     </row>
     <row r="86" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C86" s="1">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="D86" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E86" s="1">
         <v>0</v>
       </c>
       <c r="F86" s="6">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="G86" s="1">
-        <f t="shared" ref="G86:G93" si="10">N86*O86</f>
-        <v>300</v>
+        <f t="shared" si="7"/>
+        <v>40</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="J86" s="1">
         <v>5</v>
       </c>
       <c r="K86" s="1">
-        <v>4007</v>
+        <v>4002</v>
       </c>
       <c r="L86" s="1">
-        <v>1000</v>
+        <v>6000000</v>
       </c>
       <c r="M86" s="1">
-        <f t="shared" ref="M86:M93" si="11">F86*G86</f>
-        <v>180000</v>
+        <f t="shared" si="8"/>
+        <v>40000</v>
       </c>
       <c r="N86" s="1">
         <v>1</v>
       </c>
       <c r="O86" s="1">
-        <v>300</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C87" s="1">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="D87" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E87" s="1">
-        <v>0</v>
-      </c>
-      <c r="F87" s="6">
-        <v>600</v>
+        <v>6</v>
+      </c>
+      <c r="F87" s="1">
+        <v>30000</v>
       </c>
       <c r="G87" s="1">
-        <f t="shared" si="10"/>
-        <v>500</v>
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="J87" s="1">
         <v>5</v>
       </c>
       <c r="K87" s="1">
-        <v>4101</v>
+        <v>4026</v>
       </c>
       <c r="L87" s="1">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="M87" s="1">
-        <f t="shared" si="11"/>
-        <v>300000</v>
+        <f t="shared" si="8"/>
+        <v>150000</v>
       </c>
       <c r="N87" s="1">
         <v>1</v>
       </c>
       <c r="O87" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="88" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C88" s="1">
-        <v>223</v>
-      </c>
-      <c r="D88" s="1">
-        <v>4</v>
-      </c>
-      <c r="E88" s="1">
-        <v>0</v>
-      </c>
-      <c r="F88" s="6">
-        <v>6000</v>
-      </c>
-      <c r="G88" s="1">
-        <f t="shared" si="10"/>
-        <v>6</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J88" s="1">
-        <v>15</v>
-      </c>
-      <c r="K88" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L88" s="1">
-        <v>100</v>
-      </c>
-      <c r="M88" s="1">
-        <f t="shared" si="11"/>
-        <v>36000</v>
-      </c>
-      <c r="N88" s="1">
-        <v>1</v>
-      </c>
-      <c r="O88" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C89" s="1">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="D89" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E89" s="1">
         <v>0</v>
       </c>
-      <c r="F89" s="6">
-        <v>3000</v>
+      <c r="F89" s="1">
+        <v>400</v>
       </c>
       <c r="G89" s="1">
-        <f t="shared" si="10"/>
-        <v>20</v>
+        <f t="shared" ref="G89:G96" si="9">N89*O89</f>
+        <v>300</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="J89" s="1">
         <v>5</v>
       </c>
       <c r="K89" s="1">
-        <v>4012</v>
+        <v>4007</v>
       </c>
       <c r="L89" s="1">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="M89" s="1">
-        <f t="shared" si="11"/>
-        <v>60000</v>
+        <f t="shared" ref="M89:M96" si="10">F89*G89</f>
+        <v>120000</v>
       </c>
       <c r="N89" s="1">
         <v>1</v>
       </c>
       <c r="O89" s="1">
-        <v>20</v>
+        <v>300</v>
       </c>
     </row>
     <row r="90" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C90" s="1">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="D90" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E90" s="1">
-        <v>1</v>
-      </c>
-      <c r="F90" s="6">
-        <v>60000</v>
+        <v>0</v>
+      </c>
+      <c r="F90" s="1">
+        <v>400</v>
       </c>
       <c r="G90" s="1">
+        <f t="shared" si="9"/>
+        <v>500</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J90" s="1">
+        <v>5</v>
+      </c>
+      <c r="K90" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L90" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M90" s="1">
         <f t="shared" si="10"/>
-        <v>8</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J90" s="1">
-        <v>5</v>
-      </c>
-      <c r="K90" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L90" s="1">
-        <v>1</v>
-      </c>
-      <c r="M90" s="1">
-        <f t="shared" si="11"/>
-        <v>480000</v>
+        <v>200000</v>
       </c>
       <c r="N90" s="1">
         <v>1</v>
       </c>
       <c r="O90" s="1">
-        <v>8</v>
+        <v>500</v>
       </c>
     </row>
     <row r="91" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C91" s="1">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="D91" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
       </c>
-      <c r="F91" s="6">
-        <v>3000</v>
+      <c r="F91" s="1">
+        <v>4000</v>
       </c>
       <c r="G91" s="1">
+        <f t="shared" si="9"/>
+        <v>6</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J91" s="1">
+        <v>15</v>
+      </c>
+      <c r="K91" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L91" s="1">
+        <v>100</v>
+      </c>
+      <c r="M91" s="1">
         <f t="shared" si="10"/>
-        <v>40</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J91" s="1">
-        <v>5</v>
-      </c>
-      <c r="K91" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L91" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M91" s="1">
-        <f t="shared" si="11"/>
-        <v>120000</v>
+        <v>24000</v>
       </c>
       <c r="N91" s="1">
         <v>1</v>
       </c>
       <c r="O91" s="1">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C92" s="1">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="D92" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E92" s="1">
         <v>0</v>
       </c>
-      <c r="F92" s="6">
-        <v>3000</v>
+      <c r="F92" s="1">
+        <v>2000</v>
       </c>
       <c r="G92" s="1">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J92" s="1">
+        <v>5</v>
+      </c>
+      <c r="K92" s="1">
+        <v>4012</v>
+      </c>
+      <c r="L92" s="1">
+        <v>200</v>
+      </c>
+      <c r="M92" s="1">
         <f t="shared" si="10"/>
-        <v>40</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J92" s="1">
-        <v>5</v>
-      </c>
-      <c r="K92" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L92" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M92" s="1">
-        <f t="shared" si="11"/>
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="N92" s="1">
         <v>1</v>
       </c>
       <c r="O92" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C93" s="1">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D93" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E93" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F93" s="1">
-        <v>30000</v>
+        <v>45000</v>
       </c>
       <c r="G93" s="1">
+        <f t="shared" si="9"/>
+        <v>8</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J93" s="1">
+        <v>5</v>
+      </c>
+      <c r="K93" s="1">
+        <v>4019</v>
+      </c>
+      <c r="L93" s="1">
+        <v>1</v>
+      </c>
+      <c r="M93" s="1">
         <f t="shared" si="10"/>
-        <v>5</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J93" s="1">
-        <v>5</v>
-      </c>
-      <c r="K93" s="1">
-        <v>4026</v>
-      </c>
-      <c r="L93" s="1">
-        <v>1</v>
-      </c>
-      <c r="M93" s="1">
-        <f t="shared" si="11"/>
-        <v>150000</v>
+        <v>360000</v>
       </c>
       <c r="N93" s="1">
         <v>1</v>
       </c>
       <c r="O93" s="1">
-        <v>5</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C94" s="1">
+        <v>216</v>
+      </c>
+      <c r="D94" s="1">
+        <v>3</v>
+      </c>
+      <c r="E94" s="1">
+        <v>0</v>
+      </c>
+      <c r="F94" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G94" s="1">
+        <f t="shared" si="9"/>
+        <v>40</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J94" s="1">
+        <v>5</v>
+      </c>
+      <c r="K94" s="1">
+        <v>4001</v>
+      </c>
+      <c r="L94" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="M94" s="1">
+        <f t="shared" si="10"/>
+        <v>80000</v>
+      </c>
+      <c r="N94" s="1">
+        <v>1</v>
+      </c>
+      <c r="O94" s="1">
+        <v>40</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C95" s="1">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="D95" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E95" s="1">
         <v>0</v>
       </c>
       <c r="F95" s="1">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="G95" s="1">
-        <f t="shared" ref="G95:G102" si="12">N95*O95</f>
-        <v>1200</v>
+        <f t="shared" si="9"/>
+        <v>40</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="J95" s="1">
         <v>5</v>
       </c>
       <c r="K95" s="1">
-        <v>4007</v>
+        <v>4002</v>
       </c>
       <c r="L95" s="1">
-        <v>1000</v>
+        <v>6000000</v>
       </c>
       <c r="M95" s="1">
-        <f t="shared" ref="M95:M102" si="13">F95*G95</f>
-        <v>960000</v>
+        <f t="shared" si="10"/>
+        <v>80000</v>
       </c>
       <c r="N95" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O95" s="1">
-        <v>300</v>
+        <v>40</v>
       </c>
     </row>
     <row r="96" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C96" s="1">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="D96" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E96" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F96" s="1">
-        <v>800</v>
+        <v>30000</v>
       </c>
       <c r="G96" s="1">
-        <f t="shared" si="12"/>
-        <v>2000</v>
+        <f t="shared" si="9"/>
+        <v>5</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="J96" s="1">
         <v>5</v>
       </c>
       <c r="K96" s="1">
-        <v>4101</v>
+        <v>4026</v>
       </c>
       <c r="L96" s="1">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="M96" s="1">
-        <f t="shared" si="13"/>
-        <v>1600000</v>
+        <f t="shared" si="10"/>
+        <v>150000</v>
       </c>
       <c r="N96" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O96" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="97" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C97" s="1">
-        <v>233</v>
-      </c>
-      <c r="D97" s="1">
-        <v>5</v>
-      </c>
-      <c r="E97" s="1">
-        <v>0</v>
-      </c>
-      <c r="F97" s="1">
-        <v>8000</v>
-      </c>
-      <c r="G97" s="1">
-        <f t="shared" si="12"/>
-        <v>24</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J97" s="1">
-        <v>15</v>
-      </c>
-      <c r="K97" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L97" s="1">
-        <v>100</v>
-      </c>
-      <c r="M97" s="1">
-        <f t="shared" si="13"/>
-        <v>192000</v>
-      </c>
-      <c r="N97" s="1">
-        <v>4</v>
-      </c>
-      <c r="O97" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C98" s="1">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="D98" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E98" s="1">
         <v>0</v>
       </c>
-      <c r="F98" s="1">
-        <v>4000</v>
+      <c r="F98" s="6">
+        <v>600</v>
       </c>
       <c r="G98" s="1">
-        <f t="shared" si="12"/>
-        <v>80</v>
+        <f t="shared" ref="G98:G105" si="11">N98*O98</f>
+        <v>300</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="J98" s="1">
         <v>5</v>
       </c>
       <c r="K98" s="1">
-        <v>4012</v>
+        <v>4007</v>
       </c>
       <c r="L98" s="1">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="M98" s="1">
-        <f t="shared" si="13"/>
-        <v>320000</v>
+        <f t="shared" ref="M98:M105" si="12">F98*G98</f>
+        <v>180000</v>
       </c>
       <c r="N98" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O98" s="1">
-        <v>20</v>
+        <v>300</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C99" s="1">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="D99" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E99" s="1">
-        <v>1</v>
-      </c>
-      <c r="F99" s="1">
-        <v>75000</v>
+        <v>0</v>
+      </c>
+      <c r="F99" s="6">
+        <v>600</v>
       </c>
       <c r="G99" s="1">
+        <f t="shared" si="11"/>
+        <v>500</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J99" s="1">
+        <v>5</v>
+      </c>
+      <c r="K99" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L99" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M99" s="1">
         <f t="shared" si="12"/>
-        <v>32</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J99" s="1">
-        <v>5</v>
-      </c>
-      <c r="K99" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L99" s="1">
-        <v>1</v>
-      </c>
-      <c r="M99" s="1">
-        <f t="shared" si="13"/>
-        <v>2400000</v>
+        <v>300000</v>
       </c>
       <c r="N99" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O99" s="1">
-        <v>8</v>
+        <v>500</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C100" s="1">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="D100" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E100" s="1">
         <v>0</v>
       </c>
-      <c r="F100" s="1">
-        <v>4000</v>
+      <c r="F100" s="6">
+        <v>6000</v>
       </c>
       <c r="G100" s="1">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J100" s="1">
+        <v>15</v>
+      </c>
+      <c r="K100" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L100" s="1">
+        <v>100</v>
+      </c>
+      <c r="M100" s="1">
         <f t="shared" si="12"/>
-        <v>160</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J100" s="1">
-        <v>5</v>
-      </c>
-      <c r="K100" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L100" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M100" s="1">
-        <f t="shared" si="13"/>
-        <v>640000</v>
+        <v>36000</v>
       </c>
       <c r="N100" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O100" s="1">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C101" s="1">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="D101" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E101" s="1">
         <v>0</v>
       </c>
-      <c r="F101" s="1">
-        <v>4000</v>
+      <c r="F101" s="6">
+        <v>3000</v>
       </c>
       <c r="G101" s="1">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J101" s="1">
+        <v>5</v>
+      </c>
+      <c r="K101" s="1">
+        <v>4012</v>
+      </c>
+      <c r="L101" s="1">
+        <v>200</v>
+      </c>
+      <c r="M101" s="1">
         <f t="shared" si="12"/>
-        <v>160</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J101" s="1">
-        <v>5</v>
-      </c>
-      <c r="K101" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L101" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M101" s="1">
-        <f t="shared" si="13"/>
-        <v>640000</v>
+        <v>60000</v>
       </c>
       <c r="N101" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O101" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C102" s="1">
+        <v>225</v>
+      </c>
+      <c r="D102" s="1">
+        <v>4</v>
+      </c>
+      <c r="E102" s="1">
+        <v>1</v>
+      </c>
+      <c r="F102" s="6">
+        <v>60000</v>
+      </c>
+      <c r="G102" s="1">
+        <f t="shared" si="11"/>
+        <v>8</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J102" s="1">
+        <v>5</v>
+      </c>
+      <c r="K102" s="1">
+        <v>4019</v>
+      </c>
+      <c r="L102" s="1">
+        <v>1</v>
+      </c>
+      <c r="M102" s="1">
+        <f t="shared" si="12"/>
+        <v>480000</v>
+      </c>
+      <c r="N102" s="1">
+        <v>1</v>
+      </c>
+      <c r="O102" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C103" s="1">
+        <v>226</v>
+      </c>
+      <c r="D103" s="1">
+        <v>4</v>
+      </c>
+      <c r="E103" s="1">
+        <v>0</v>
+      </c>
+      <c r="F103" s="6">
+        <v>3000</v>
+      </c>
+      <c r="G103" s="1">
+        <f t="shared" si="11"/>
+        <v>40</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J103" s="1">
+        <v>5</v>
+      </c>
+      <c r="K103" s="1">
+        <v>4001</v>
+      </c>
+      <c r="L103" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="M103" s="1">
+        <f t="shared" si="12"/>
+        <v>120000</v>
+      </c>
+      <c r="N103" s="1">
+        <v>1</v>
+      </c>
+      <c r="O103" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="104" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C104" s="1">
+        <v>227</v>
+      </c>
+      <c r="D104" s="1">
+        <v>4</v>
+      </c>
+      <c r="E104" s="1">
+        <v>0</v>
+      </c>
+      <c r="F104" s="6">
+        <v>3000</v>
+      </c>
+      <c r="G104" s="1">
+        <f t="shared" si="11"/>
+        <v>40</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J104" s="1">
+        <v>5</v>
+      </c>
+      <c r="K104" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L104" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M104" s="1">
+        <f t="shared" si="12"/>
+        <v>120000</v>
+      </c>
+      <c r="N104" s="1">
+        <v>1</v>
+      </c>
+      <c r="O104" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="105" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C105" s="1">
+        <v>228</v>
+      </c>
+      <c r="D105" s="1">
+        <v>4</v>
+      </c>
+      <c r="E105" s="1">
+        <v>6</v>
+      </c>
+      <c r="F105" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G105" s="1">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J105" s="1">
+        <v>5</v>
+      </c>
+      <c r="K105" s="1">
+        <v>4026</v>
+      </c>
+      <c r="L105" s="1">
+        <v>1</v>
+      </c>
+      <c r="M105" s="1">
+        <f t="shared" si="12"/>
+        <v>150000</v>
+      </c>
+      <c r="N105" s="1">
+        <v>1</v>
+      </c>
+      <c r="O105" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C107" s="1">
+        <v>231</v>
+      </c>
+      <c r="D107" s="1">
+        <v>5</v>
+      </c>
+      <c r="E107" s="1">
+        <v>0</v>
+      </c>
+      <c r="F107" s="1">
+        <v>800</v>
+      </c>
+      <c r="G107" s="1">
+        <f t="shared" ref="G107:G114" si="13">N107*O107</f>
+        <v>1200</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J107" s="1">
+        <v>5</v>
+      </c>
+      <c r="K107" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L107" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M107" s="1">
+        <f t="shared" ref="M107:M114" si="14">F107*G107</f>
+        <v>960000</v>
+      </c>
+      <c r="N107" s="1">
+        <v>4</v>
+      </c>
+      <c r="O107" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="108" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C108" s="1">
+        <v>232</v>
+      </c>
+      <c r="D108" s="1">
+        <v>5</v>
+      </c>
+      <c r="E108" s="1">
+        <v>0</v>
+      </c>
+      <c r="F108" s="1">
+        <v>800</v>
+      </c>
+      <c r="G108" s="1">
+        <f t="shared" si="13"/>
+        <v>2000</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J108" s="1">
+        <v>5</v>
+      </c>
+      <c r="K108" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L108" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M108" s="1">
+        <f t="shared" si="14"/>
+        <v>1600000</v>
+      </c>
+      <c r="N108" s="1">
+        <v>4</v>
+      </c>
+      <c r="O108" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="109" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C109" s="1">
+        <v>233</v>
+      </c>
+      <c r="D109" s="1">
+        <v>5</v>
+      </c>
+      <c r="E109" s="1">
+        <v>0</v>
+      </c>
+      <c r="F109" s="1">
+        <v>8000</v>
+      </c>
+      <c r="G109" s="1">
+        <f t="shared" si="13"/>
+        <v>24</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J109" s="1">
+        <v>15</v>
+      </c>
+      <c r="K109" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L109" s="1">
+        <v>100</v>
+      </c>
+      <c r="M109" s="1">
+        <f t="shared" si="14"/>
+        <v>192000</v>
+      </c>
+      <c r="N109" s="1">
+        <v>4</v>
+      </c>
+      <c r="O109" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C110" s="1">
+        <v>234</v>
+      </c>
+      <c r="D110" s="1">
+        <v>5</v>
+      </c>
+      <c r="E110" s="1">
+        <v>0</v>
+      </c>
+      <c r="F110" s="1">
+        <v>4000</v>
+      </c>
+      <c r="G110" s="1">
+        <f t="shared" si="13"/>
+        <v>80</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J110" s="1">
+        <v>5</v>
+      </c>
+      <c r="K110" s="1">
+        <v>4012</v>
+      </c>
+      <c r="L110" s="1">
+        <v>200</v>
+      </c>
+      <c r="M110" s="1">
+        <f t="shared" si="14"/>
+        <v>320000</v>
+      </c>
+      <c r="N110" s="1">
+        <v>4</v>
+      </c>
+      <c r="O110" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C111" s="1">
+        <v>235</v>
+      </c>
+      <c r="D111" s="1">
+        <v>5</v>
+      </c>
+      <c r="E111" s="1">
+        <v>1</v>
+      </c>
+      <c r="F111" s="1">
+        <v>75000</v>
+      </c>
+      <c r="G111" s="1">
+        <f t="shared" si="13"/>
+        <v>32</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J111" s="1">
+        <v>5</v>
+      </c>
+      <c r="K111" s="1">
+        <v>4019</v>
+      </c>
+      <c r="L111" s="1">
+        <v>1</v>
+      </c>
+      <c r="M111" s="1">
+        <f t="shared" si="14"/>
+        <v>2400000</v>
+      </c>
+      <c r="N111" s="1">
+        <v>4</v>
+      </c>
+      <c r="O111" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C112" s="1">
+        <v>236</v>
+      </c>
+      <c r="D112" s="1">
+        <v>5</v>
+      </c>
+      <c r="E112" s="1">
+        <v>0</v>
+      </c>
+      <c r="F112" s="1">
+        <v>4000</v>
+      </c>
+      <c r="G112" s="1">
+        <f t="shared" si="13"/>
+        <v>160</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J112" s="1">
+        <v>5</v>
+      </c>
+      <c r="K112" s="1">
+        <v>4001</v>
+      </c>
+      <c r="L112" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="M112" s="1">
+        <f t="shared" si="14"/>
+        <v>640000</v>
+      </c>
+      <c r="N112" s="1">
+        <v>4</v>
+      </c>
+      <c r="O112" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="113" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C113" s="1">
+        <v>237</v>
+      </c>
+      <c r="D113" s="1">
+        <v>5</v>
+      </c>
+      <c r="E113" s="1">
+        <v>0</v>
+      </c>
+      <c r="F113" s="1">
+        <v>4000</v>
+      </c>
+      <c r="G113" s="1">
+        <f t="shared" si="13"/>
+        <v>160</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J113" s="1">
+        <v>5</v>
+      </c>
+      <c r="K113" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L113" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M113" s="1">
+        <f t="shared" si="14"/>
+        <v>640000</v>
+      </c>
+      <c r="N113" s="1">
+        <v>4</v>
+      </c>
+      <c r="O113" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="114" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C114" s="1">
         <v>238</v>
       </c>
-      <c r="D102" s="1">
-        <v>5</v>
-      </c>
-      <c r="E102" s="1">
+      <c r="D114" s="1">
+        <v>5</v>
+      </c>
+      <c r="E114" s="1">
         <v>6</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F114" s="1">
         <v>30000</v>
       </c>
-      <c r="G102" s="1">
-        <f t="shared" si="12"/>
-        <v>5</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J102" s="1">
-        <v>5</v>
-      </c>
-      <c r="K102" s="1">
+      <c r="G114" s="1">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J114" s="1">
+        <v>5</v>
+      </c>
+      <c r="K114" s="1">
         <v>4026</v>
       </c>
-      <c r="L102" s="1">
-        <v>1</v>
-      </c>
-      <c r="M102" s="1">
-        <f t="shared" si="13"/>
+      <c r="L114" s="1">
+        <v>1</v>
+      </c>
+      <c r="M114" s="1">
+        <f t="shared" si="14"/>
         <v>150000</v>
       </c>
-      <c r="N102" s="1">
-        <v>1</v>
-      </c>
-      <c r="O102" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="104" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C104" s="1">
+      <c r="N114" s="1">
+        <v>1</v>
+      </c>
+      <c r="O114" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C116" s="1">
         <v>999</v>
       </c>
-      <c r="D104" s="1">
-        <v>0</v>
-      </c>
-      <c r="E104" s="1">
-        <v>0</v>
-      </c>
-      <c r="F104" s="1">
+      <c r="D116" s="1">
+        <v>0</v>
+      </c>
+      <c r="E116" s="1">
+        <v>0</v>
+      </c>
+      <c r="F116" s="1">
         <v>1000</v>
       </c>
-      <c r="G104" s="1">
+      <c r="G116" s="1">
         <v>50</v>
       </c>
-      <c r="H104" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J104" s="1">
-        <v>5</v>
-      </c>
-      <c r="K104" s="1">
+      <c r="H116" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J116" s="1">
+        <v>5</v>
+      </c>
+      <c r="K116" s="1">
         <v>4006</v>
       </c>
-      <c r="L104" s="1">
+      <c r="L116" s="1">
         <v>1000</v>
       </c>
-      <c r="M104" s="1">
-        <f t="shared" ref="M104:M106" si="14">F104*G104</f>
+      <c r="M116" s="1">
+        <f t="shared" ref="M116:M118" si="15">F116*G116</f>
         <v>50000</v>
       </c>
     </row>
-    <row r="105" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C105" s="1">
+    <row r="117" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C117" s="1">
         <v>1000</v>
       </c>
-      <c r="D105" s="1">
-        <v>0</v>
-      </c>
-      <c r="E105" s="1">
-        <v>0</v>
-      </c>
-      <c r="F105" s="1">
+      <c r="D117" s="1">
+        <v>0</v>
+      </c>
+      <c r="E117" s="1">
+        <v>0</v>
+      </c>
+      <c r="F117" s="1">
         <v>2000</v>
       </c>
-      <c r="G105" s="1">
+      <c r="G117" s="1">
         <v>100</v>
       </c>
-      <c r="H105" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J105" s="1">
-        <v>5</v>
-      </c>
-      <c r="K105" s="1">
+      <c r="H117" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J117" s="1">
+        <v>5</v>
+      </c>
+      <c r="K117" s="1">
         <v>4010</v>
       </c>
-      <c r="L105" s="1">
-        <v>5</v>
-      </c>
-      <c r="M105" s="1">
-        <f t="shared" si="14"/>
+      <c r="L117" s="1">
+        <v>5</v>
+      </c>
+      <c r="M117" s="1">
+        <f t="shared" si="15"/>
         <v>200000</v>
       </c>
     </row>
-    <row r="106" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C106" s="1">
+    <row r="118" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C118" s="1">
         <v>1001</v>
       </c>
-      <c r="D106" s="1">
-        <v>0</v>
-      </c>
-      <c r="E106" s="1">
-        <v>0</v>
-      </c>
-      <c r="F106" s="1">
+      <c r="D118" s="1">
+        <v>0</v>
+      </c>
+      <c r="E118" s="1">
+        <v>0</v>
+      </c>
+      <c r="F118" s="1">
         <v>2000</v>
       </c>
-      <c r="G106" s="1">
+      <c r="G118" s="1">
         <v>50</v>
       </c>
-      <c r="H106" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J106" s="1">
-        <v>5</v>
-      </c>
-      <c r="K106" s="1">
+      <c r="H118" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J118" s="1">
+        <v>5</v>
+      </c>
+      <c r="K118" s="1">
         <v>4102</v>
       </c>
-      <c r="L106" s="1">
+      <c r="L118" s="1">
         <v>20</v>
       </c>
-      <c r="M106" s="1">
-        <f t="shared" si="14"/>
+      <c r="M118" s="1">
+        <f t="shared" si="15"/>
         <v>100000</v>
       </c>
     </row>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="160">
   <si>
     <t>#</t>
   </si>
@@ -435,6 +435,9 @@
   </si>
   <si>
     <t>朱雀自选</t>
+  </si>
+  <si>
+    <t>行气丹*500</t>
   </si>
   <si>
     <t>行气丹</t>
@@ -3571,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="M59" s="1">
-        <f t="shared" ref="M59:M63" si="4">F59*G59</f>
+        <f t="shared" ref="M59:M65" si="4">F59*G59</f>
         <v>500000</v>
       </c>
     </row>
@@ -3739,7 +3742,7 @@
         <v>136</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J64" s="1">
         <v>5</v>
@@ -3748,10 +3751,10 @@
         <v>4033</v>
       </c>
       <c r="L64" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="M64" s="1">
-        <f>F64*G64</f>
+        <f t="shared" si="4"/>
         <v>2000000</v>
       </c>
     </row>
@@ -3772,10 +3775,10 @@
         <v>200</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J65" s="1">
         <v>15</v>
@@ -3787,7 +3790,7 @@
         <v>100</v>
       </c>
       <c r="M65" s="1">
-        <f>F65*G65</f>
+        <f t="shared" si="4"/>
         <v>1000000</v>
       </c>
     </row>
@@ -3884,10 +3887,10 @@
         <v>300</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J71" s="1">
         <v>5</v>
@@ -3927,10 +3930,10 @@
         <v>500</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J72" s="1">
         <v>5</v>
@@ -3970,10 +3973,10 @@
         <v>6</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J73" s="1">
         <v>15</v>
@@ -4013,10 +4016,10 @@
         <v>20</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J74" s="1">
         <v>5</v>
@@ -4056,10 +4059,10 @@
         <v>8</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J75" s="1">
         <v>5</v>
@@ -4099,10 +4102,10 @@
         <v>40</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J76" s="1">
         <v>5</v>
@@ -4142,10 +4145,10 @@
         <v>40</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J77" s="1">
         <v>5</v>
@@ -4185,10 +4188,10 @@
         <v>5</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J78" s="1">
         <v>5</v>
@@ -4228,10 +4231,10 @@
         <v>300</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J80" s="1">
         <v>5</v>
@@ -4271,10 +4274,10 @@
         <v>500</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J81" s="1">
         <v>5</v>
@@ -4314,10 +4317,10 @@
         <v>6</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J82" s="1">
         <v>15</v>
@@ -4357,10 +4360,10 @@
         <v>20</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J83" s="1">
         <v>5</v>
@@ -4400,10 +4403,10 @@
         <v>8</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J84" s="1">
         <v>5</v>
@@ -4443,10 +4446,10 @@
         <v>40</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J85" s="1">
         <v>5</v>
@@ -4486,10 +4489,10 @@
         <v>40</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J86" s="1">
         <v>5</v>
@@ -4529,10 +4532,10 @@
         <v>5</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J87" s="1">
         <v>5</v>
@@ -4572,10 +4575,10 @@
         <v>300</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J89" s="1">
         <v>5</v>
@@ -4615,10 +4618,10 @@
         <v>500</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J90" s="1">
         <v>5</v>
@@ -4658,10 +4661,10 @@
         <v>6</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J91" s="1">
         <v>15</v>
@@ -4701,10 +4704,10 @@
         <v>20</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J92" s="1">
         <v>5</v>
@@ -4744,10 +4747,10 @@
         <v>8</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J93" s="1">
         <v>5</v>
@@ -4787,10 +4790,10 @@
         <v>40</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J94" s="1">
         <v>5</v>
@@ -4830,10 +4833,10 @@
         <v>40</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J95" s="1">
         <v>5</v>
@@ -4873,10 +4876,10 @@
         <v>5</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J96" s="1">
         <v>5</v>
@@ -4916,10 +4919,10 @@
         <v>300</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J98" s="1">
         <v>5</v>
@@ -4959,10 +4962,10 @@
         <v>500</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J99" s="1">
         <v>5</v>
@@ -5002,10 +5005,10 @@
         <v>6</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J100" s="1">
         <v>15</v>
@@ -5045,10 +5048,10 @@
         <v>20</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J101" s="1">
         <v>5</v>
@@ -5088,10 +5091,10 @@
         <v>8</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J102" s="1">
         <v>5</v>
@@ -5131,10 +5134,10 @@
         <v>40</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J103" s="1">
         <v>5</v>
@@ -5174,10 +5177,10 @@
         <v>40</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J104" s="1">
         <v>5</v>
@@ -5217,10 +5220,10 @@
         <v>5</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J105" s="1">
         <v>5</v>
@@ -5260,10 +5263,10 @@
         <v>1200</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J107" s="1">
         <v>5</v>
@@ -5303,10 +5306,10 @@
         <v>2000</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J108" s="1">
         <v>5</v>
@@ -5346,10 +5349,10 @@
         <v>24</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J109" s="1">
         <v>15</v>
@@ -5389,10 +5392,10 @@
         <v>80</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J110" s="1">
         <v>5</v>
@@ -5432,10 +5435,10 @@
         <v>32</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J111" s="1">
         <v>5</v>
@@ -5475,10 +5478,10 @@
         <v>160</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J112" s="1">
         <v>5</v>
@@ -5518,10 +5521,10 @@
         <v>160</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J113" s="1">
         <v>5</v>
@@ -5561,10 +5564,10 @@
         <v>5</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J114" s="1">
         <v>5</v>
@@ -5603,10 +5606,10 @@
         <v>50</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J116" s="1">
         <v>5</v>
@@ -5639,10 +5642,10 @@
         <v>100</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J117" s="1">
         <v>5</v>
@@ -5675,10 +5678,10 @@
         <v>50</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J118" s="1">
         <v>5</v>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -3763,10 +3763,10 @@
         <v>59</v>
       </c>
       <c r="D65" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F65" s="6">
         <v>5000</v>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="151">
   <si>
     <t>#</t>
   </si>
@@ -416,49 +416,22 @@
     <t>低级法宝自选</t>
   </si>
   <si>
-    <t>兑换时装精华</t>
-  </si>
-  <si>
-    <t>时装精华</t>
-  </si>
-  <si>
-    <t>兑换10介技能自选包*1</t>
-  </si>
-  <si>
-    <t>10介技能</t>
-  </si>
-  <si>
-    <t>青龙自选</t>
-  </si>
-  <si>
-    <t>白虎自选</t>
-  </si>
-  <si>
-    <t>朱雀自选</t>
-  </si>
-  <si>
-    <t>行气丹*500</t>
-  </si>
-  <si>
-    <t>行气丹</t>
+    <t>兑换四格碎片*1000</t>
+  </si>
+  <si>
+    <t>四格碎片</t>
+  </si>
+  <si>
+    <t>兑换图鉴碎片*1000</t>
+  </si>
+  <si>
+    <t>图鉴碎片</t>
   </si>
   <si>
     <t>兑换经验丹*100</t>
   </si>
   <si>
     <t>经验丹</t>
-  </si>
-  <si>
-    <t>兑换四格碎片*1000</t>
-  </si>
-  <si>
-    <t>四格碎片</t>
-  </si>
-  <si>
-    <t>兑换图鉴碎片*1000</t>
-  </si>
-  <si>
-    <t>图鉴碎片</t>
   </si>
   <si>
     <t>兑换传世精华*200</t>
@@ -1523,7 +1496,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O118"/>
+  <dimension ref="C1:O106"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1653,7 +1626,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="1">
-        <v>388</v>
+        <v>168</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>14</v>
@@ -1672,7 +1645,7 @@
       </c>
       <c r="M6" s="1">
         <f t="shared" ref="M6:M14" si="0">F6*G6</f>
-        <v>116400</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:13">
@@ -1689,7 +1662,7 @@
         <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>388</v>
+        <v>168</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>16</v>
@@ -1708,7 +1681,7 @@
       </c>
       <c r="M7" s="1">
         <f t="shared" si="0"/>
-        <v>116400</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1725,7 +1698,7 @@
         <v>13</v>
       </c>
       <c r="G8" s="1">
-        <v>388</v>
+        <v>168</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>18</v>
@@ -1744,7 +1717,7 @@
       </c>
       <c r="M8" s="1">
         <f t="shared" si="0"/>
-        <v>116400</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:13">
@@ -1761,7 +1734,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="1">
-        <v>188</v>
+        <v>66</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>21</v>
@@ -1780,7 +1753,7 @@
       </c>
       <c r="M9" s="1">
         <f t="shared" si="0"/>
-        <v>94000</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:13">
@@ -1797,7 +1770,7 @@
         <v>13</v>
       </c>
       <c r="G10" s="1">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>23</v>
@@ -1816,7 +1789,7 @@
       </c>
       <c r="M10" s="1">
         <f t="shared" si="0"/>
-        <v>180000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:13">
@@ -1833,7 +1806,7 @@
         <v>13</v>
       </c>
       <c r="G11" s="1">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>25</v>
@@ -1852,7 +1825,7 @@
       </c>
       <c r="M11" s="1">
         <f t="shared" si="0"/>
-        <v>180000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:13">
@@ -1869,7 +1842,7 @@
         <v>13</v>
       </c>
       <c r="G12" s="1">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>27</v>
@@ -1888,7 +1861,7 @@
       </c>
       <c r="M12" s="1">
         <f t="shared" si="0"/>
-        <v>180000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:13">
@@ -1905,7 +1878,7 @@
         <v>20</v>
       </c>
       <c r="G13" s="1">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>29</v>
@@ -1924,7 +1897,7 @@
       </c>
       <c r="M13" s="1">
         <f t="shared" si="0"/>
-        <v>300000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:13">
@@ -1941,7 +1914,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="1">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>31</v>
@@ -1960,7 +1933,7 @@
       </c>
       <c r="M14" s="1">
         <f t="shared" si="0"/>
-        <v>300000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:13">
@@ -1977,7 +1950,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="1">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>33</v>
@@ -1996,7 +1969,7 @@
       </c>
       <c r="M15" s="1">
         <f t="shared" ref="M15:M37" si="1">F15*G15</f>
-        <v>300000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:13">
@@ -2013,7 +1986,7 @@
         <v>13</v>
       </c>
       <c r="G16" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>35</v>
@@ -2032,7 +2005,7 @@
       </c>
       <c r="M16" s="1">
         <f t="shared" si="1"/>
-        <v>90000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:13">
@@ -2049,7 +2022,7 @@
         <v>13</v>
       </c>
       <c r="G17" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>37</v>
@@ -2068,7 +2041,7 @@
       </c>
       <c r="M17" s="1">
         <f t="shared" si="1"/>
-        <v>90000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:13">
@@ -2085,7 +2058,7 @@
         <v>13</v>
       </c>
       <c r="G18" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>39</v>
@@ -2104,7 +2077,7 @@
       </c>
       <c r="M18" s="1">
         <f t="shared" si="1"/>
-        <v>90000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:13">
@@ -2121,7 +2094,7 @@
         <v>13</v>
       </c>
       <c r="G19" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>41</v>
@@ -2140,7 +2113,7 @@
       </c>
       <c r="M19" s="1">
         <f t="shared" si="1"/>
-        <v>90000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:13">
@@ -2157,7 +2130,7 @@
         <v>13</v>
       </c>
       <c r="G20" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>43</v>
@@ -2176,7 +2149,7 @@
       </c>
       <c r="M20" s="1">
         <f t="shared" si="1"/>
-        <v>90000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:13">
@@ -2193,7 +2166,7 @@
         <v>45</v>
       </c>
       <c r="G21" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>46</v>
@@ -2212,7 +2185,7 @@
       </c>
       <c r="M21" s="1">
         <f t="shared" si="1"/>
-        <v>180000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:13">
@@ -2229,7 +2202,7 @@
         <v>45</v>
       </c>
       <c r="G22" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>48</v>
@@ -2248,7 +2221,7 @@
       </c>
       <c r="M22" s="1">
         <f t="shared" si="1"/>
-        <v>180000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:13">
@@ -2265,7 +2238,7 @@
         <v>45</v>
       </c>
       <c r="G23" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>50</v>
@@ -2284,7 +2257,7 @@
       </c>
       <c r="M23" s="1">
         <f t="shared" si="1"/>
-        <v>180000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:13">
@@ -2301,7 +2274,7 @@
         <v>45</v>
       </c>
       <c r="G24" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>52</v>
@@ -2320,7 +2293,7 @@
       </c>
       <c r="M24" s="1">
         <f t="shared" si="1"/>
-        <v>180000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:13">
@@ -2337,7 +2310,7 @@
         <v>1000</v>
       </c>
       <c r="G25" s="1">
-        <v>264</v>
+        <v>88</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>54</v>
@@ -2356,7 +2329,7 @@
       </c>
       <c r="M25" s="1">
         <f t="shared" si="1"/>
-        <v>264000</v>
+        <v>88000</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:13">
@@ -2373,7 +2346,7 @@
         <v>2000</v>
       </c>
       <c r="G26" s="1">
-        <v>231</v>
+        <v>77</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>56</v>
@@ -2392,7 +2365,7 @@
       </c>
       <c r="M26" s="1">
         <f t="shared" si="1"/>
-        <v>462000</v>
+        <v>154000</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:13">
@@ -2409,7 +2382,7 @@
         <v>3000</v>
       </c>
       <c r="G27" s="1">
-        <v>198</v>
+        <v>66</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>58</v>
@@ -2428,7 +2401,7 @@
       </c>
       <c r="M27" s="1">
         <f t="shared" si="1"/>
-        <v>594000</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:13">
@@ -2445,7 +2418,7 @@
         <v>4000</v>
       </c>
       <c r="G28" s="1">
-        <v>165</v>
+        <v>55</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>60</v>
@@ -2464,7 +2437,7 @@
       </c>
       <c r="M28" s="1">
         <f t="shared" si="1"/>
-        <v>660000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:13">
@@ -2481,7 +2454,7 @@
         <v>5000</v>
       </c>
       <c r="G29" s="1">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>62</v>
@@ -2500,7 +2473,7 @@
       </c>
       <c r="M29" s="1">
         <f t="shared" si="1"/>
-        <v>660000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:13">
@@ -2517,7 +2490,7 @@
         <v>6000</v>
       </c>
       <c r="G30" s="1">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>64</v>
@@ -2536,7 +2509,7 @@
       </c>
       <c r="M30" s="1">
         <f t="shared" si="1"/>
-        <v>594000</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:13">
@@ -2661,7 +2634,7 @@
         <v>74</v>
       </c>
       <c r="G34" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>75</v>
@@ -2680,7 +2653,7 @@
       </c>
       <c r="M34" s="1">
         <f t="shared" si="1"/>
-        <v>600000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:13">
@@ -2697,7 +2670,7 @@
         <v>77</v>
       </c>
       <c r="G35" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>78</v>
@@ -2716,7 +2689,7 @@
       </c>
       <c r="M35" s="1">
         <f t="shared" si="1"/>
-        <v>500000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:13">
@@ -2769,7 +2742,7 @@
         <v>83</v>
       </c>
       <c r="G37" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>84</v>
@@ -2788,7 +2761,7 @@
       </c>
       <c r="M37" s="1">
         <f t="shared" si="1"/>
-        <v>4500000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:13">
@@ -2805,7 +2778,7 @@
         <v>86</v>
       </c>
       <c r="G38" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>87</v>
@@ -2824,7 +2797,7 @@
       </c>
       <c r="M38" s="1">
         <f t="shared" ref="M38:M43" si="2">F38*G38</f>
-        <v>2000000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:13">
@@ -2841,7 +2814,7 @@
         <v>89</v>
       </c>
       <c r="G39" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>90</v>
@@ -2860,7 +2833,7 @@
       </c>
       <c r="M39" s="1">
         <f t="shared" si="2"/>
-        <v>1000000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:13">
@@ -2877,7 +2850,7 @@
         <v>92</v>
       </c>
       <c r="G40" s="1">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>93</v>
@@ -2896,7 +2869,7 @@
       </c>
       <c r="M40" s="1">
         <f t="shared" si="2"/>
-        <v>5000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:13">
@@ -2913,7 +2886,7 @@
         <v>92</v>
       </c>
       <c r="G41" s="1">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>95</v>
@@ -2932,7 +2905,7 @@
       </c>
       <c r="M41" s="1">
         <f t="shared" si="2"/>
-        <v>2500000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:13">
@@ -2949,7 +2922,7 @@
         <v>3000</v>
       </c>
       <c r="G42" s="1">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>97</v>
@@ -2968,7 +2941,7 @@
       </c>
       <c r="M42" s="1">
         <f t="shared" si="2"/>
-        <v>1500000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:13">
@@ -2985,7 +2958,7 @@
         <v>20000</v>
       </c>
       <c r="G43" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>99</v>
@@ -3004,7 +2977,7 @@
       </c>
       <c r="M43" s="1">
         <f t="shared" si="2"/>
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:13">
@@ -3021,7 +2994,7 @@
         <v>20000</v>
       </c>
       <c r="G44" s="1">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>101</v>
@@ -3040,7 +3013,7 @@
       </c>
       <c r="M44" s="1">
         <f t="shared" ref="M44:M57" si="3">F44*G44</f>
-        <v>2000000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -3054,10 +3027,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="1">
-        <v>288888</v>
+        <v>388888</v>
       </c>
       <c r="G45" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>103</v>
@@ -3076,7 +3049,7 @@
       </c>
       <c r="M45" s="1">
         <f t="shared" si="3"/>
-        <v>577776</v>
+        <v>388888</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -3093,7 +3066,7 @@
         <v>300000</v>
       </c>
       <c r="G46" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>105</v>
@@ -3112,7 +3085,7 @@
       </c>
       <c r="M46" s="1">
         <f t="shared" si="3"/>
-        <v>900000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:13">
@@ -3505,7 +3478,7 @@
         <v>50000</v>
       </c>
       <c r="G57" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>127</v>
@@ -3524,7 +3497,7 @@
       </c>
       <c r="M57" s="1">
         <f t="shared" si="3"/>
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:15">
@@ -3542,21 +3515,22 @@
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:13">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C59" s="1">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="D59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
       </c>
       <c r="F59" s="1">
-        <v>100000</v>
+        <v>100</v>
       </c>
       <c r="G59" s="1">
-        <v>5</v>
+        <f t="shared" ref="G59:G66" si="4">N59*O59</f>
+        <v>300</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>129</v>
@@ -3568,31 +3542,38 @@
         <v>5</v>
       </c>
       <c r="K59" s="1">
-        <v>4034</v>
+        <v>4007</v>
       </c>
       <c r="L59" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="M59" s="1">
-        <f t="shared" ref="M59:M65" si="4">F59*G59</f>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <f t="shared" ref="M59:M66" si="5">F59*G59</f>
+        <v>30000</v>
+      </c>
+      <c r="N59" s="1">
+        <v>1</v>
+      </c>
+      <c r="O59" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C60" s="1">
-        <v>54</v>
+        <v>103</v>
       </c>
       <c r="D60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
       </c>
       <c r="F60" s="1">
-        <v>50000</v>
+        <v>100</v>
       </c>
       <c r="G60" s="1">
-        <v>1</v>
+        <f t="shared" si="4"/>
+        <v>500</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>131</v>
@@ -3601,2099 +3582,1764 @@
         <v>132</v>
       </c>
       <c r="J60" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K60" s="1">
-        <v>27</v>
+        <v>4101</v>
       </c>
       <c r="L60" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="M60" s="1">
+        <f t="shared" si="5"/>
+        <v>50000</v>
+      </c>
+      <c r="N60" s="1">
+        <v>1</v>
+      </c>
+      <c r="O60" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C61" s="1">
+        <v>104</v>
+      </c>
+      <c r="D61" s="1">
+        <v>1</v>
+      </c>
+      <c r="E61" s="1">
+        <v>0</v>
+      </c>
+      <c r="F61" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G61" s="1">
         <f t="shared" si="4"/>
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C61" s="1">
-        <v>55</v>
-      </c>
-      <c r="D61" s="1">
-        <v>0</v>
-      </c>
-      <c r="E61" s="1">
-        <v>4</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G61" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>133</v>
       </c>
       <c r="I61" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J61" s="1">
+        <v>15</v>
+      </c>
+      <c r="K61" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L61" s="1">
+        <v>100</v>
+      </c>
+      <c r="M61" s="1">
+        <f t="shared" si="5"/>
+        <v>6000</v>
+      </c>
+      <c r="N61" s="1">
+        <v>1</v>
+      </c>
+      <c r="O61" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C62" s="1">
+        <v>105</v>
+      </c>
+      <c r="D62" s="1">
+        <v>1</v>
+      </c>
+      <c r="E62" s="1">
+        <v>0</v>
+      </c>
+      <c r="F62" s="1">
+        <v>500</v>
+      </c>
+      <c r="G62" s="1">
+        <f t="shared" si="4"/>
+        <v>20</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J62" s="1">
+        <v>5</v>
+      </c>
+      <c r="K62" s="1">
+        <v>4012</v>
+      </c>
+      <c r="L62" s="1">
+        <v>200</v>
+      </c>
+      <c r="M62" s="1">
+        <f t="shared" si="5"/>
+        <v>10000</v>
+      </c>
+      <c r="N62" s="1">
+        <v>1</v>
+      </c>
+      <c r="O62" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C63" s="1">
+        <v>106</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+      <c r="F63" s="1">
+        <v>15000</v>
+      </c>
+      <c r="G63" s="1">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J63" s="1">
+        <v>5</v>
+      </c>
+      <c r="K63" s="1">
+        <v>4019</v>
+      </c>
+      <c r="L63" s="1">
+        <v>1</v>
+      </c>
+      <c r="M63" s="1">
+        <f t="shared" si="5"/>
+        <v>120000</v>
+      </c>
+      <c r="N63" s="1">
+        <v>1</v>
+      </c>
+      <c r="O63" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C64" s="1">
+        <v>107</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1</v>
+      </c>
+      <c r="E64" s="1">
+        <v>0</v>
+      </c>
+      <c r="F64" s="1">
+        <v>500</v>
+      </c>
+      <c r="G64" s="1">
+        <f t="shared" si="4"/>
+        <v>40</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J64" s="1">
+        <v>5</v>
+      </c>
+      <c r="K64" s="1">
+        <v>4001</v>
+      </c>
+      <c r="L64" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="M64" s="1">
+        <f t="shared" si="5"/>
+        <v>20000</v>
+      </c>
+      <c r="N64" s="1">
+        <v>1</v>
+      </c>
+      <c r="O64" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C65" s="1">
+        <v>108</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1</v>
+      </c>
+      <c r="E65" s="1">
+        <v>0</v>
+      </c>
+      <c r="F65" s="1">
+        <v>500</v>
+      </c>
+      <c r="G65" s="1">
+        <f t="shared" si="4"/>
+        <v>40</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J65" s="1">
+        <v>5</v>
+      </c>
+      <c r="K65" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L65" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M65" s="1">
+        <f t="shared" si="5"/>
+        <v>20000</v>
+      </c>
+      <c r="N65" s="1">
+        <v>1</v>
+      </c>
+      <c r="O65" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C66" s="1">
+        <v>109</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1</v>
+      </c>
+      <c r="E66" s="1">
+        <v>6</v>
+      </c>
+      <c r="F66" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G66" s="1">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J66" s="1">
+        <v>5</v>
+      </c>
+      <c r="K66" s="1">
+        <v>4026</v>
+      </c>
+      <c r="L66" s="1">
+        <v>1</v>
+      </c>
+      <c r="M66" s="1">
+        <f t="shared" si="5"/>
+        <v>150000</v>
+      </c>
+      <c r="N66" s="1">
+        <v>1</v>
+      </c>
+      <c r="O66" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C68" s="1">
+        <v>201</v>
+      </c>
+      <c r="D68" s="1">
+        <v>2</v>
+      </c>
+      <c r="E68" s="1">
+        <v>0</v>
+      </c>
+      <c r="F68" s="6">
+        <v>200</v>
+      </c>
+      <c r="G68" s="1">
+        <f t="shared" ref="G68:G75" si="6">N68*O68</f>
+        <v>300</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J68" s="1">
+        <v>5</v>
+      </c>
+      <c r="K68" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L68" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M68" s="1">
+        <f t="shared" ref="M68:M75" si="7">F68*G68</f>
+        <v>60000</v>
+      </c>
+      <c r="N68" s="1">
+        <v>1</v>
+      </c>
+      <c r="O68" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C69" s="1">
+        <v>202</v>
+      </c>
+      <c r="D69" s="1">
+        <v>2</v>
+      </c>
+      <c r="E69" s="1">
+        <v>0</v>
+      </c>
+      <c r="F69" s="6">
+        <v>200</v>
+      </c>
+      <c r="G69" s="1">
+        <f t="shared" si="6"/>
+        <v>500</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J69" s="1">
+        <v>5</v>
+      </c>
+      <c r="K69" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L69" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M69" s="1">
+        <f t="shared" si="7"/>
+        <v>100000</v>
+      </c>
+      <c r="N69" s="1">
+        <v>1</v>
+      </c>
+      <c r="O69" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C70" s="1">
+        <v>203</v>
+      </c>
+      <c r="D70" s="1">
+        <v>2</v>
+      </c>
+      <c r="E70" s="1">
+        <v>0</v>
+      </c>
+      <c r="F70" s="6">
+        <v>2000</v>
+      </c>
+      <c r="G70" s="1">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="H70" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="J61" s="1">
-        <v>4</v>
-      </c>
-      <c r="K61" s="1">
-        <v>35</v>
-      </c>
-      <c r="L61" s="1">
-        <v>1</v>
-      </c>
-      <c r="M61" s="1">
-        <f t="shared" si="4"/>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C62" s="1">
-        <v>56</v>
-      </c>
-      <c r="D62" s="1">
-        <v>0</v>
-      </c>
-      <c r="E62" s="1">
+      <c r="I70" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J70" s="1">
+        <v>15</v>
+      </c>
+      <c r="K70" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L70" s="1">
+        <v>100</v>
+      </c>
+      <c r="M70" s="1">
+        <f t="shared" si="7"/>
+        <v>12000</v>
+      </c>
+      <c r="N70" s="1">
+        <v>1</v>
+      </c>
+      <c r="O70" s="1">
         <v>6</v>
       </c>
-      <c r="F62" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G62" s="1">
-        <v>1</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J62" s="1">
-        <v>4</v>
-      </c>
-      <c r="K62" s="1">
-        <v>37</v>
-      </c>
-      <c r="L62" s="1">
-        <v>1</v>
-      </c>
-      <c r="M62" s="1">
-        <f t="shared" si="4"/>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C63" s="1">
-        <v>57</v>
-      </c>
-      <c r="D63" s="1">
-        <v>0</v>
-      </c>
-      <c r="E63" s="1">
-        <v>8</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G63" s="1">
-        <v>1</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="J63" s="1">
-        <v>4</v>
-      </c>
-      <c r="K63" s="1">
-        <v>38</v>
-      </c>
-      <c r="L63" s="1">
-        <v>1</v>
-      </c>
-      <c r="M63" s="1">
-        <f t="shared" si="4"/>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C64" s="1">
-        <v>58</v>
-      </c>
-      <c r="D64" s="1">
-        <v>0</v>
-      </c>
-      <c r="E64" s="1">
-        <v>10</v>
-      </c>
-      <c r="F64" s="1">
-        <v>100000</v>
-      </c>
-      <c r="G64" s="1">
-        <v>20</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="J64" s="1">
-        <v>5</v>
-      </c>
-      <c r="K64" s="1">
-        <v>4033</v>
-      </c>
-      <c r="L64" s="1">
-        <v>500</v>
-      </c>
-      <c r="M64" s="1">
-        <f t="shared" si="4"/>
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C65" s="1">
-        <v>59</v>
-      </c>
-      <c r="D65" s="1">
-        <v>0</v>
-      </c>
-      <c r="E65" s="1">
-        <v>4</v>
-      </c>
-      <c r="F65" s="6">
-        <v>5000</v>
-      </c>
-      <c r="G65" s="1">
-        <v>200</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J65" s="1">
-        <v>15</v>
-      </c>
-      <c r="K65" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L65" s="1">
-        <v>100</v>
-      </c>
-      <c r="M65" s="1">
-        <f t="shared" si="4"/>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="66" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-    </row>
-    <row r="67" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
-    </row>
-    <row r="68" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-    </row>
-    <row r="69" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
-    </row>
-    <row r="70" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-      <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
     </row>
     <row r="71" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C71" s="1">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="D71" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" s="1">
         <v>0</v>
       </c>
-      <c r="F71" s="1">
-        <v>100</v>
+      <c r="F71" s="6">
+        <v>1000</v>
       </c>
       <c r="G71" s="1">
-        <f t="shared" ref="G71:G78" si="5">N71*O71</f>
-        <v>300</v>
+        <f t="shared" si="6"/>
+        <v>20</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J71" s="1">
         <v>5</v>
       </c>
       <c r="K71" s="1">
-        <v>4007</v>
+        <v>4012</v>
       </c>
       <c r="L71" s="1">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="M71" s="1">
-        <f t="shared" ref="M71:M78" si="6">F71*G71</f>
-        <v>30000</v>
+        <f t="shared" si="7"/>
+        <v>20000</v>
       </c>
       <c r="N71" s="1">
         <v>1</v>
       </c>
       <c r="O71" s="1">
-        <v>300</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C72" s="1">
-        <v>103</v>
+        <v>205</v>
       </c>
       <c r="D72" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" s="1">
-        <v>0</v>
-      </c>
-      <c r="F72" s="1">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="F72" s="6">
+        <v>30000</v>
       </c>
       <c r="G72" s="1">
-        <f t="shared" si="5"/>
-        <v>500</v>
+        <f t="shared" si="6"/>
+        <v>8</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J72" s="1">
         <v>5</v>
       </c>
       <c r="K72" s="1">
-        <v>4101</v>
+        <v>4019</v>
       </c>
       <c r="L72" s="1">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="M72" s="1">
-        <f t="shared" si="6"/>
-        <v>50000</v>
+        <f t="shared" si="7"/>
+        <v>240000</v>
       </c>
       <c r="N72" s="1">
         <v>1</v>
       </c>
       <c r="O72" s="1">
-        <v>500</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C73" s="1">
-        <v>104</v>
+        <v>206</v>
       </c>
       <c r="D73" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73" s="6">
         <v>1000</v>
       </c>
       <c r="G73" s="1">
-        <f t="shared" si="5"/>
-        <v>6</v>
+        <f t="shared" si="6"/>
+        <v>40</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J73" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K73" s="1">
-        <v>4014</v>
+        <v>4001</v>
       </c>
       <c r="L73" s="1">
-        <v>100</v>
+        <v>1000000</v>
       </c>
       <c r="M73" s="1">
-        <f t="shared" si="6"/>
-        <v>6000</v>
+        <f t="shared" si="7"/>
+        <v>40000</v>
       </c>
       <c r="N73" s="1">
         <v>1</v>
       </c>
       <c r="O73" s="1">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C74" s="1">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="D74" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
       </c>
-      <c r="F74" s="1">
-        <v>500</v>
+      <c r="F74" s="6">
+        <v>1000</v>
       </c>
       <c r="G74" s="1">
-        <f t="shared" si="5"/>
-        <v>20</v>
+        <f t="shared" si="6"/>
+        <v>40</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J74" s="1">
         <v>5</v>
       </c>
       <c r="K74" s="1">
-        <v>4012</v>
+        <v>4002</v>
       </c>
       <c r="L74" s="1">
-        <v>200</v>
+        <v>6000000</v>
       </c>
       <c r="M74" s="1">
-        <f t="shared" si="6"/>
-        <v>10000</v>
+        <f t="shared" si="7"/>
+        <v>40000</v>
       </c>
       <c r="N74" s="1">
         <v>1</v>
       </c>
       <c r="O74" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C75" s="1">
-        <v>106</v>
+        <v>208</v>
       </c>
       <c r="D75" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F75" s="1">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="G75" s="1">
-        <f t="shared" si="5"/>
-        <v>8</v>
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J75" s="1">
         <v>5</v>
       </c>
       <c r="K75" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="L75" s="1">
         <v>1</v>
       </c>
       <c r="M75" s="1">
-        <f t="shared" si="6"/>
-        <v>120000</v>
+        <f t="shared" si="7"/>
+        <v>150000</v>
       </c>
       <c r="N75" s="1">
         <v>1</v>
       </c>
       <c r="O75" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C76" s="1">
-        <v>107</v>
-      </c>
-      <c r="D76" s="1">
-        <v>1</v>
-      </c>
-      <c r="E76" s="1">
-        <v>0</v>
-      </c>
-      <c r="F76" s="1">
-        <v>500</v>
-      </c>
-      <c r="G76" s="1">
-        <f t="shared" si="5"/>
-        <v>40</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J76" s="1">
-        <v>5</v>
-      </c>
-      <c r="K76" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L76" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M76" s="1">
-        <f t="shared" si="6"/>
-        <v>20000</v>
-      </c>
-      <c r="N76" s="1">
-        <v>1</v>
-      </c>
-      <c r="O76" s="1">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C77" s="1">
-        <v>108</v>
+        <v>211</v>
       </c>
       <c r="D77" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E77" s="1">
         <v>0</v>
       </c>
       <c r="F77" s="1">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G77" s="1">
-        <f t="shared" si="5"/>
-        <v>40</v>
+        <f t="shared" ref="G77:G84" si="8">N77*O77</f>
+        <v>300</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="J77" s="1">
         <v>5</v>
       </c>
       <c r="K77" s="1">
-        <v>4002</v>
+        <v>4007</v>
       </c>
       <c r="L77" s="1">
-        <v>6000000</v>
+        <v>1000</v>
       </c>
       <c r="M77" s="1">
-        <f t="shared" si="6"/>
-        <v>20000</v>
+        <f t="shared" ref="M77:M84" si="9">F77*G77</f>
+        <v>120000</v>
       </c>
       <c r="N77" s="1">
         <v>1</v>
       </c>
       <c r="O77" s="1">
-        <v>40</v>
+        <v>300</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C78" s="1">
-        <v>109</v>
+        <v>212</v>
       </c>
       <c r="D78" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E78" s="1">
+        <v>0</v>
+      </c>
+      <c r="F78" s="1">
+        <v>400</v>
+      </c>
+      <c r="G78" s="1">
+        <f t="shared" si="8"/>
+        <v>500</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J78" s="1">
+        <v>5</v>
+      </c>
+      <c r="K78" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L78" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M78" s="1">
+        <f t="shared" si="9"/>
+        <v>200000</v>
+      </c>
+      <c r="N78" s="1">
+        <v>1</v>
+      </c>
+      <c r="O78" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C79" s="1">
+        <v>213</v>
+      </c>
+      <c r="D79" s="1">
+        <v>3</v>
+      </c>
+      <c r="E79" s="1">
+        <v>0</v>
+      </c>
+      <c r="F79" s="1">
+        <v>4000</v>
+      </c>
+      <c r="G79" s="1">
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="F78" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G78" s="1">
-        <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J78" s="1">
-        <v>5</v>
-      </c>
-      <c r="K78" s="1">
-        <v>4026</v>
-      </c>
-      <c r="L78" s="1">
-        <v>1</v>
-      </c>
-      <c r="M78" s="1">
-        <f t="shared" si="6"/>
-        <v>150000</v>
-      </c>
-      <c r="N78" s="1">
-        <v>1</v>
-      </c>
-      <c r="O78" s="1">
-        <v>5</v>
+      <c r="H79" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J79" s="1">
+        <v>15</v>
+      </c>
+      <c r="K79" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L79" s="1">
+        <v>100</v>
+      </c>
+      <c r="M79" s="1">
+        <f t="shared" si="9"/>
+        <v>24000</v>
+      </c>
+      <c r="N79" s="1">
+        <v>1</v>
+      </c>
+      <c r="O79" s="1">
+        <v>6</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C80" s="1">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="D80" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80" s="1">
         <v>0</v>
       </c>
-      <c r="F80" s="6">
+      <c r="F80" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G80" s="1">
+        <f t="shared" si="8"/>
+        <v>20</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J80" s="1">
+        <v>5</v>
+      </c>
+      <c r="K80" s="1">
+        <v>4012</v>
+      </c>
+      <c r="L80" s="1">
         <v>200</v>
       </c>
-      <c r="G80" s="1">
-        <f t="shared" ref="G80:G87" si="7">N80*O80</f>
-        <v>300</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="J80" s="1">
-        <v>5</v>
-      </c>
-      <c r="K80" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L80" s="1">
-        <v>1000</v>
-      </c>
       <c r="M80" s="1">
-        <f t="shared" ref="M80:M87" si="8">F80*G80</f>
-        <v>60000</v>
+        <f t="shared" si="9"/>
+        <v>40000</v>
       </c>
       <c r="N80" s="1">
         <v>1</v>
       </c>
       <c r="O80" s="1">
-        <v>300</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C81" s="1">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D81" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81" s="1">
-        <v>0</v>
-      </c>
-      <c r="F81" s="6">
-        <v>200</v>
+        <v>1</v>
+      </c>
+      <c r="F81" s="1">
+        <v>45000</v>
       </c>
       <c r="G81" s="1">
-        <f t="shared" si="7"/>
-        <v>500</v>
+        <f t="shared" si="8"/>
+        <v>8</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J81" s="1">
         <v>5</v>
       </c>
       <c r="K81" s="1">
-        <v>4101</v>
+        <v>4019</v>
       </c>
       <c r="L81" s="1">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="M81" s="1">
-        <f t="shared" si="8"/>
-        <v>100000</v>
+        <f t="shared" si="9"/>
+        <v>360000</v>
       </c>
       <c r="N81" s="1">
         <v>1</v>
       </c>
       <c r="O81" s="1">
-        <v>500</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C82" s="1">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="D82" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82" s="1">
         <v>0</v>
       </c>
-      <c r="F82" s="6">
+      <c r="F82" s="1">
         <v>2000</v>
       </c>
       <c r="G82" s="1">
-        <f t="shared" si="7"/>
-        <v>6</v>
+        <f t="shared" si="8"/>
+        <v>40</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J82" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K82" s="1">
-        <v>4014</v>
+        <v>4001</v>
       </c>
       <c r="L82" s="1">
-        <v>100</v>
+        <v>1000000</v>
       </c>
       <c r="M82" s="1">
-        <f t="shared" si="8"/>
-        <v>12000</v>
+        <f t="shared" si="9"/>
+        <v>80000</v>
       </c>
       <c r="N82" s="1">
         <v>1</v>
       </c>
       <c r="O82" s="1">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="83" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C83" s="1">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="D83" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83" s="1">
         <v>0</v>
       </c>
-      <c r="F83" s="6">
-        <v>1000</v>
+      <c r="F83" s="1">
+        <v>2000</v>
       </c>
       <c r="G83" s="1">
-        <f t="shared" si="7"/>
-        <v>20</v>
+        <f t="shared" si="8"/>
+        <v>40</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J83" s="1">
         <v>5</v>
       </c>
       <c r="K83" s="1">
-        <v>4012</v>
+        <v>4002</v>
       </c>
       <c r="L83" s="1">
-        <v>200</v>
+        <v>6000000</v>
       </c>
       <c r="M83" s="1">
-        <f t="shared" si="8"/>
-        <v>20000</v>
+        <f t="shared" si="9"/>
+        <v>80000</v>
       </c>
       <c r="N83" s="1">
         <v>1</v>
       </c>
       <c r="O83" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="84" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C84" s="1">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D84" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E84" s="1">
-        <v>1</v>
-      </c>
-      <c r="F84" s="6">
+        <v>6</v>
+      </c>
+      <c r="F84" s="1">
         <v>30000</v>
       </c>
       <c r="G84" s="1">
-        <f t="shared" si="7"/>
-        <v>8</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J84" s="1">
         <v>5</v>
       </c>
       <c r="K84" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="L84" s="1">
         <v>1</v>
       </c>
       <c r="M84" s="1">
-        <f t="shared" si="8"/>
-        <v>240000</v>
+        <f t="shared" si="9"/>
+        <v>150000</v>
       </c>
       <c r="N84" s="1">
         <v>1</v>
       </c>
       <c r="O84" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C85" s="1">
-        <v>206</v>
-      </c>
-      <c r="D85" s="1">
-        <v>2</v>
-      </c>
-      <c r="E85" s="1">
-        <v>0</v>
-      </c>
-      <c r="F85" s="6">
-        <v>1000</v>
-      </c>
-      <c r="G85" s="1">
-        <f t="shared" si="7"/>
-        <v>40</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J85" s="1">
-        <v>5</v>
-      </c>
-      <c r="K85" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L85" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M85" s="1">
-        <f t="shared" si="8"/>
-        <v>40000</v>
-      </c>
-      <c r="N85" s="1">
-        <v>1</v>
-      </c>
-      <c r="O85" s="1">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C86" s="1">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="D86" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E86" s="1">
         <v>0</v>
       </c>
       <c r="F86" s="6">
+        <v>600</v>
+      </c>
+      <c r="G86" s="1">
+        <f t="shared" ref="G86:G93" si="10">N86*O86</f>
+        <v>300</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J86" s="1">
+        <v>5</v>
+      </c>
+      <c r="K86" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L86" s="1">
         <v>1000</v>
       </c>
-      <c r="G86" s="1">
-        <f t="shared" si="7"/>
-        <v>40</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="J86" s="1">
-        <v>5</v>
-      </c>
-      <c r="K86" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L86" s="1">
-        <v>6000000</v>
-      </c>
       <c r="M86" s="1">
-        <f t="shared" si="8"/>
-        <v>40000</v>
+        <f t="shared" ref="M86:M93" si="11">F86*G86</f>
+        <v>180000</v>
       </c>
       <c r="N86" s="1">
         <v>1</v>
       </c>
       <c r="O86" s="1">
-        <v>40</v>
+        <v>300</v>
       </c>
     </row>
     <row r="87" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C87" s="1">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="D87" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E87" s="1">
+        <v>0</v>
+      </c>
+      <c r="F87" s="6">
+        <v>600</v>
+      </c>
+      <c r="G87" s="1">
+        <f t="shared" si="10"/>
+        <v>500</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J87" s="1">
+        <v>5</v>
+      </c>
+      <c r="K87" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L87" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M87" s="1">
+        <f t="shared" si="11"/>
+        <v>300000</v>
+      </c>
+      <c r="N87" s="1">
+        <v>1</v>
+      </c>
+      <c r="O87" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="88" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C88" s="1">
+        <v>223</v>
+      </c>
+      <c r="D88" s="1">
+        <v>4</v>
+      </c>
+      <c r="E88" s="1">
+        <v>0</v>
+      </c>
+      <c r="F88" s="6">
+        <v>6000</v>
+      </c>
+      <c r="G88" s="1">
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="F87" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G87" s="1">
-        <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J87" s="1">
-        <v>5</v>
-      </c>
-      <c r="K87" s="1">
-        <v>4026</v>
-      </c>
-      <c r="L87" s="1">
-        <v>1</v>
-      </c>
-      <c r="M87" s="1">
-        <f t="shared" si="8"/>
-        <v>150000</v>
-      </c>
-      <c r="N87" s="1">
-        <v>1</v>
-      </c>
-      <c r="O87" s="1">
-        <v>5</v>
+      <c r="H88" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J88" s="1">
+        <v>15</v>
+      </c>
+      <c r="K88" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L88" s="1">
+        <v>100</v>
+      </c>
+      <c r="M88" s="1">
+        <f t="shared" si="11"/>
+        <v>36000</v>
+      </c>
+      <c r="N88" s="1">
+        <v>1</v>
+      </c>
+      <c r="O88" s="1">
+        <v>6</v>
       </c>
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C89" s="1">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="D89" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E89" s="1">
         <v>0</v>
       </c>
-      <c r="F89" s="1">
-        <v>400</v>
+      <c r="F89" s="6">
+        <v>3000</v>
       </c>
       <c r="G89" s="1">
-        <f t="shared" ref="G89:G96" si="9">N89*O89</f>
-        <v>300</v>
+        <f t="shared" si="10"/>
+        <v>20</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J89" s="1">
         <v>5</v>
       </c>
       <c r="K89" s="1">
-        <v>4007</v>
+        <v>4012</v>
       </c>
       <c r="L89" s="1">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="M89" s="1">
-        <f t="shared" ref="M89:M96" si="10">F89*G89</f>
-        <v>120000</v>
+        <f t="shared" si="11"/>
+        <v>60000</v>
       </c>
       <c r="N89" s="1">
         <v>1</v>
       </c>
       <c r="O89" s="1">
-        <v>300</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C90" s="1">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="D90" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E90" s="1">
-        <v>0</v>
-      </c>
-      <c r="F90" s="1">
-        <v>400</v>
+        <v>1</v>
+      </c>
+      <c r="F90" s="6">
+        <v>60000</v>
       </c>
       <c r="G90" s="1">
-        <f t="shared" si="9"/>
-        <v>500</v>
+        <f t="shared" si="10"/>
+        <v>8</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J90" s="1">
         <v>5</v>
       </c>
       <c r="K90" s="1">
-        <v>4101</v>
+        <v>4019</v>
       </c>
       <c r="L90" s="1">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="M90" s="1">
-        <f t="shared" si="10"/>
-        <v>200000</v>
+        <f t="shared" si="11"/>
+        <v>480000</v>
       </c>
       <c r="N90" s="1">
         <v>1</v>
       </c>
       <c r="O90" s="1">
-        <v>500</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C91" s="1">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="D91" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
       </c>
-      <c r="F91" s="1">
-        <v>4000</v>
+      <c r="F91" s="6">
+        <v>3000</v>
       </c>
       <c r="G91" s="1">
-        <f t="shared" si="9"/>
-        <v>6</v>
+        <f t="shared" si="10"/>
+        <v>40</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J91" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K91" s="1">
-        <v>4014</v>
+        <v>4001</v>
       </c>
       <c r="L91" s="1">
-        <v>100</v>
+        <v>1000000</v>
       </c>
       <c r="M91" s="1">
-        <f t="shared" si="10"/>
-        <v>24000</v>
+        <f t="shared" si="11"/>
+        <v>120000</v>
       </c>
       <c r="N91" s="1">
         <v>1</v>
       </c>
       <c r="O91" s="1">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C92" s="1">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="D92" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E92" s="1">
         <v>0</v>
       </c>
-      <c r="F92" s="1">
-        <v>2000</v>
+      <c r="F92" s="6">
+        <v>3000</v>
       </c>
       <c r="G92" s="1">
-        <f t="shared" si="9"/>
-        <v>20</v>
+        <f t="shared" si="10"/>
+        <v>40</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J92" s="1">
         <v>5</v>
       </c>
       <c r="K92" s="1">
-        <v>4012</v>
+        <v>4002</v>
       </c>
       <c r="L92" s="1">
-        <v>200</v>
+        <v>6000000</v>
       </c>
       <c r="M92" s="1">
-        <f t="shared" si="10"/>
-        <v>40000</v>
+        <f t="shared" si="11"/>
+        <v>120000</v>
       </c>
       <c r="N92" s="1">
         <v>1</v>
       </c>
       <c r="O92" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C93" s="1">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="D93" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E93" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F93" s="1">
-        <v>45000</v>
+        <v>30000</v>
       </c>
       <c r="G93" s="1">
-        <f t="shared" si="9"/>
-        <v>8</v>
+        <f t="shared" si="10"/>
+        <v>5</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J93" s="1">
         <v>5</v>
       </c>
       <c r="K93" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="L93" s="1">
         <v>1</v>
       </c>
       <c r="M93" s="1">
-        <f t="shared" si="10"/>
-        <v>360000</v>
+        <f t="shared" si="11"/>
+        <v>150000</v>
       </c>
       <c r="N93" s="1">
         <v>1</v>
       </c>
       <c r="O93" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C94" s="1">
-        <v>216</v>
-      </c>
-      <c r="D94" s="1">
-        <v>3</v>
-      </c>
-      <c r="E94" s="1">
-        <v>0</v>
-      </c>
-      <c r="F94" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G94" s="1">
-        <f t="shared" si="9"/>
-        <v>40</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J94" s="1">
-        <v>5</v>
-      </c>
-      <c r="K94" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L94" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M94" s="1">
-        <f t="shared" si="10"/>
-        <v>80000</v>
-      </c>
-      <c r="N94" s="1">
-        <v>1</v>
-      </c>
-      <c r="O94" s="1">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C95" s="1">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="D95" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E95" s="1">
         <v>0</v>
       </c>
       <c r="F95" s="1">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="G95" s="1">
-        <f t="shared" si="9"/>
-        <v>40</v>
+        <f t="shared" ref="G95:G102" si="12">N95*O95</f>
+        <v>1200</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="J95" s="1">
         <v>5</v>
       </c>
       <c r="K95" s="1">
-        <v>4002</v>
+        <v>4007</v>
       </c>
       <c r="L95" s="1">
-        <v>6000000</v>
+        <v>1000</v>
       </c>
       <c r="M95" s="1">
-        <f t="shared" si="10"/>
-        <v>80000</v>
+        <f t="shared" ref="M95:M102" si="13">F95*G95</f>
+        <v>960000</v>
       </c>
       <c r="N95" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O95" s="1">
-        <v>40</v>
+        <v>300</v>
       </c>
     </row>
     <row r="96" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C96" s="1">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="D96" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E96" s="1">
+        <v>0</v>
+      </c>
+      <c r="F96" s="1">
+        <v>800</v>
+      </c>
+      <c r="G96" s="1">
+        <f t="shared" si="12"/>
+        <v>2000</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J96" s="1">
+        <v>5</v>
+      </c>
+      <c r="K96" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L96" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M96" s="1">
+        <f t="shared" si="13"/>
+        <v>1600000</v>
+      </c>
+      <c r="N96" s="1">
+        <v>4</v>
+      </c>
+      <c r="O96" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="97" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C97" s="1">
+        <v>233</v>
+      </c>
+      <c r="D97" s="1">
+        <v>5</v>
+      </c>
+      <c r="E97" s="1">
+        <v>0</v>
+      </c>
+      <c r="F97" s="1">
+        <v>8000</v>
+      </c>
+      <c r="G97" s="1">
+        <f t="shared" si="12"/>
+        <v>24</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J97" s="1">
+        <v>15</v>
+      </c>
+      <c r="K97" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L97" s="1">
+        <v>100</v>
+      </c>
+      <c r="M97" s="1">
+        <f t="shared" si="13"/>
+        <v>192000</v>
+      </c>
+      <c r="N97" s="1">
+        <v>4</v>
+      </c>
+      <c r="O97" s="1">
         <v>6</v>
-      </c>
-      <c r="F96" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G96" s="1">
-        <f t="shared" si="9"/>
-        <v>5</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J96" s="1">
-        <v>5</v>
-      </c>
-      <c r="K96" s="1">
-        <v>4026</v>
-      </c>
-      <c r="L96" s="1">
-        <v>1</v>
-      </c>
-      <c r="M96" s="1">
-        <f t="shared" si="10"/>
-        <v>150000</v>
-      </c>
-      <c r="N96" s="1">
-        <v>1</v>
-      </c>
-      <c r="O96" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C98" s="1">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="D98" s="1">
+        <v>5</v>
+      </c>
+      <c r="E98" s="1">
+        <v>0</v>
+      </c>
+      <c r="F98" s="1">
+        <v>4000</v>
+      </c>
+      <c r="G98" s="1">
+        <f t="shared" si="12"/>
+        <v>80</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J98" s="1">
+        <v>5</v>
+      </c>
+      <c r="K98" s="1">
+        <v>4012</v>
+      </c>
+      <c r="L98" s="1">
+        <v>200</v>
+      </c>
+      <c r="M98" s="1">
+        <f t="shared" si="13"/>
+        <v>320000</v>
+      </c>
+      <c r="N98" s="1">
         <v>4</v>
       </c>
-      <c r="E98" s="1">
-        <v>0</v>
-      </c>
-      <c r="F98" s="6">
-        <v>600</v>
-      </c>
-      <c r="G98" s="1">
-        <f t="shared" ref="G98:G105" si="11">N98*O98</f>
-        <v>300</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="J98" s="1">
-        <v>5</v>
-      </c>
-      <c r="K98" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L98" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M98" s="1">
-        <f t="shared" ref="M98:M105" si="12">F98*G98</f>
-        <v>180000</v>
-      </c>
-      <c r="N98" s="1">
-        <v>1</v>
-      </c>
       <c r="O98" s="1">
-        <v>300</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C99" s="1">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="D99" s="1">
+        <v>5</v>
+      </c>
+      <c r="E99" s="1">
+        <v>1</v>
+      </c>
+      <c r="F99" s="1">
+        <v>75000</v>
+      </c>
+      <c r="G99" s="1">
+        <f t="shared" si="12"/>
+        <v>32</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J99" s="1">
+        <v>5</v>
+      </c>
+      <c r="K99" s="1">
+        <v>4019</v>
+      </c>
+      <c r="L99" s="1">
+        <v>1</v>
+      </c>
+      <c r="M99" s="1">
+        <f t="shared" si="13"/>
+        <v>2400000</v>
+      </c>
+      <c r="N99" s="1">
         <v>4</v>
       </c>
-      <c r="E99" s="1">
-        <v>0</v>
-      </c>
-      <c r="F99" s="6">
-        <v>600</v>
-      </c>
-      <c r="G99" s="1">
-        <f t="shared" si="11"/>
-        <v>500</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="J99" s="1">
-        <v>5</v>
-      </c>
-      <c r="K99" s="1">
-        <v>4101</v>
-      </c>
-      <c r="L99" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M99" s="1">
-        <f t="shared" si="12"/>
-        <v>300000</v>
-      </c>
-      <c r="N99" s="1">
-        <v>1</v>
-      </c>
       <c r="O99" s="1">
-        <v>500</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C100" s="1">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="D100" s="1">
+        <v>5</v>
+      </c>
+      <c r="E100" s="1">
+        <v>0</v>
+      </c>
+      <c r="F100" s="1">
+        <v>4000</v>
+      </c>
+      <c r="G100" s="1">
+        <f t="shared" si="12"/>
+        <v>160</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J100" s="1">
+        <v>5</v>
+      </c>
+      <c r="K100" s="1">
+        <v>4001</v>
+      </c>
+      <c r="L100" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="M100" s="1">
+        <f t="shared" si="13"/>
+        <v>640000</v>
+      </c>
+      <c r="N100" s="1">
         <v>4</v>
       </c>
-      <c r="E100" s="1">
-        <v>0</v>
-      </c>
-      <c r="F100" s="6">
-        <v>6000</v>
-      </c>
-      <c r="G100" s="1">
-        <f t="shared" si="11"/>
-        <v>6</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J100" s="1">
-        <v>15</v>
-      </c>
-      <c r="K100" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L100" s="1">
-        <v>100</v>
-      </c>
-      <c r="M100" s="1">
-        <f t="shared" si="12"/>
-        <v>36000</v>
-      </c>
-      <c r="N100" s="1">
-        <v>1</v>
-      </c>
       <c r="O100" s="1">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C101" s="1">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="D101" s="1">
+        <v>5</v>
+      </c>
+      <c r="E101" s="1">
+        <v>0</v>
+      </c>
+      <c r="F101" s="1">
+        <v>4000</v>
+      </c>
+      <c r="G101" s="1">
+        <f t="shared" si="12"/>
+        <v>160</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J101" s="1">
+        <v>5</v>
+      </c>
+      <c r="K101" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L101" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M101" s="1">
+        <f t="shared" si="13"/>
+        <v>640000</v>
+      </c>
+      <c r="N101" s="1">
         <v>4</v>
       </c>
-      <c r="E101" s="1">
-        <v>0</v>
-      </c>
-      <c r="F101" s="6">
-        <v>3000</v>
-      </c>
-      <c r="G101" s="1">
-        <f t="shared" si="11"/>
-        <v>20</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="J101" s="1">
-        <v>5</v>
-      </c>
-      <c r="K101" s="1">
-        <v>4012</v>
-      </c>
-      <c r="L101" s="1">
-        <v>200</v>
-      </c>
-      <c r="M101" s="1">
-        <f t="shared" si="12"/>
-        <v>60000</v>
-      </c>
-      <c r="N101" s="1">
-        <v>1</v>
-      </c>
       <c r="O101" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C102" s="1">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="D102" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E102" s="1">
-        <v>1</v>
-      </c>
-      <c r="F102" s="6">
-        <v>60000</v>
+        <v>6</v>
+      </c>
+      <c r="F102" s="1">
+        <v>30000</v>
       </c>
       <c r="G102" s="1">
-        <f t="shared" si="11"/>
-        <v>8</v>
+        <f t="shared" si="12"/>
+        <v>5</v>
       </c>
       <c r="H102" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J102" s="1">
+        <v>5</v>
+      </c>
+      <c r="K102" s="1">
+        <v>4026</v>
+      </c>
+      <c r="L102" s="1">
+        <v>1</v>
+      </c>
+      <c r="M102" s="1">
+        <f t="shared" si="13"/>
+        <v>150000</v>
+      </c>
+      <c r="N102" s="1">
+        <v>1</v>
+      </c>
+      <c r="O102" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C104" s="1">
+        <v>999</v>
+      </c>
+      <c r="D104" s="1">
+        <v>0</v>
+      </c>
+      <c r="E104" s="1">
+        <v>0</v>
+      </c>
+      <c r="F104" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G104" s="1">
+        <v>50</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I104" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="I102" s="1" t="s">
+      <c r="J104" s="1">
+        <v>5</v>
+      </c>
+      <c r="K104" s="1">
+        <v>4006</v>
+      </c>
+      <c r="L104" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M104" s="1">
+        <f t="shared" ref="M104:M106" si="14">F104*G104</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="105" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C105" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D105" s="1">
+        <v>0</v>
+      </c>
+      <c r="E105" s="1">
+        <v>0</v>
+      </c>
+      <c r="F105" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G105" s="1">
+        <v>100</v>
+      </c>
+      <c r="H105" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="J102" s="1">
-        <v>5</v>
-      </c>
-      <c r="K102" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L102" s="1">
-        <v>1</v>
-      </c>
-      <c r="M102" s="1">
-        <f t="shared" si="12"/>
-        <v>480000</v>
-      </c>
-      <c r="N102" s="1">
-        <v>1</v>
-      </c>
-      <c r="O102" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="103" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C103" s="1">
-        <v>226</v>
-      </c>
-      <c r="D103" s="1">
-        <v>4</v>
-      </c>
-      <c r="E103" s="1">
-        <v>0</v>
-      </c>
-      <c r="F103" s="6">
-        <v>3000</v>
-      </c>
-      <c r="G103" s="1">
-        <f t="shared" si="11"/>
-        <v>40</v>
-      </c>
-      <c r="H103" s="1" t="s">
+      <c r="I105" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I103" s="1" t="s">
+      <c r="J105" s="1">
+        <v>5</v>
+      </c>
+      <c r="K105" s="1">
+        <v>4010</v>
+      </c>
+      <c r="L105" s="1">
+        <v>5</v>
+      </c>
+      <c r="M105" s="1">
+        <f t="shared" si="14"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="106" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C106" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D106" s="1">
+        <v>0</v>
+      </c>
+      <c r="E106" s="1">
+        <v>0</v>
+      </c>
+      <c r="F106" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G106" s="1">
+        <v>50</v>
+      </c>
+      <c r="H106" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="J103" s="1">
-        <v>5</v>
-      </c>
-      <c r="K103" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L103" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M103" s="1">
-        <f t="shared" si="12"/>
-        <v>120000</v>
-      </c>
-      <c r="N103" s="1">
-        <v>1</v>
-      </c>
-      <c r="O103" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="104" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C104" s="1">
-        <v>227</v>
-      </c>
-      <c r="D104" s="1">
-        <v>4</v>
-      </c>
-      <c r="E104" s="1">
-        <v>0</v>
-      </c>
-      <c r="F104" s="6">
-        <v>3000</v>
-      </c>
-      <c r="G104" s="1">
-        <f t="shared" si="11"/>
-        <v>40</v>
-      </c>
-      <c r="H104" s="1" t="s">
+      <c r="I106" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="I104" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="J104" s="1">
-        <v>5</v>
-      </c>
-      <c r="K104" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L104" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M104" s="1">
-        <f t="shared" si="12"/>
-        <v>120000</v>
-      </c>
-      <c r="N104" s="1">
-        <v>1</v>
-      </c>
-      <c r="O104" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="105" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C105" s="1">
-        <v>228</v>
-      </c>
-      <c r="D105" s="1">
-        <v>4</v>
-      </c>
-      <c r="E105" s="1">
-        <v>6</v>
-      </c>
-      <c r="F105" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G105" s="1">
-        <f t="shared" si="11"/>
-        <v>5</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J105" s="1">
-        <v>5</v>
-      </c>
-      <c r="K105" s="1">
-        <v>4026</v>
-      </c>
-      <c r="L105" s="1">
-        <v>1</v>
-      </c>
-      <c r="M105" s="1">
-        <f t="shared" si="12"/>
-        <v>150000</v>
-      </c>
-      <c r="N105" s="1">
-        <v>1</v>
-      </c>
-      <c r="O105" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="107" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C107" s="1">
-        <v>231</v>
-      </c>
-      <c r="D107" s="1">
-        <v>5</v>
-      </c>
-      <c r="E107" s="1">
-        <v>0</v>
-      </c>
-      <c r="F107" s="1">
-        <v>800</v>
-      </c>
-      <c r="G107" s="1">
-        <f t="shared" ref="G107:G114" si="13">N107*O107</f>
-        <v>1200</v>
-      </c>
-      <c r="H107" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="J107" s="1">
-        <v>5</v>
-      </c>
-      <c r="K107" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L107" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M107" s="1">
-        <f t="shared" ref="M107:M114" si="14">F107*G107</f>
-        <v>960000</v>
-      </c>
-      <c r="N107" s="1">
-        <v>4</v>
-      </c>
-      <c r="O107" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="108" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C108" s="1">
-        <v>232</v>
-      </c>
-      <c r="D108" s="1">
-        <v>5</v>
-      </c>
-      <c r="E108" s="1">
-        <v>0</v>
-      </c>
-      <c r="F108" s="1">
-        <v>800</v>
-      </c>
-      <c r="G108" s="1">
-        <f t="shared" si="13"/>
-        <v>2000</v>
-      </c>
-      <c r="H108" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I108" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="J108" s="1">
-        <v>5</v>
-      </c>
-      <c r="K108" s="1">
-        <v>4101</v>
-      </c>
-      <c r="L108" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M108" s="1">
+      <c r="J106" s="1">
+        <v>5</v>
+      </c>
+      <c r="K106" s="1">
+        <v>4102</v>
+      </c>
+      <c r="L106" s="1">
+        <v>20</v>
+      </c>
+      <c r="M106" s="1">
         <f t="shared" si="14"/>
-        <v>1600000</v>
-      </c>
-      <c r="N108" s="1">
-        <v>4</v>
-      </c>
-      <c r="O108" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="109" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C109" s="1">
-        <v>233</v>
-      </c>
-      <c r="D109" s="1">
-        <v>5</v>
-      </c>
-      <c r="E109" s="1">
-        <v>0</v>
-      </c>
-      <c r="F109" s="1">
-        <v>8000</v>
-      </c>
-      <c r="G109" s="1">
-        <f t="shared" si="13"/>
-        <v>24</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J109" s="1">
-        <v>15</v>
-      </c>
-      <c r="K109" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L109" s="1">
-        <v>100</v>
-      </c>
-      <c r="M109" s="1">
-        <f t="shared" si="14"/>
-        <v>192000</v>
-      </c>
-      <c r="N109" s="1">
-        <v>4</v>
-      </c>
-      <c r="O109" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="110" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C110" s="1">
-        <v>234</v>
-      </c>
-      <c r="D110" s="1">
-        <v>5</v>
-      </c>
-      <c r="E110" s="1">
-        <v>0</v>
-      </c>
-      <c r="F110" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G110" s="1">
-        <f t="shared" si="13"/>
-        <v>80</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="J110" s="1">
-        <v>5</v>
-      </c>
-      <c r="K110" s="1">
-        <v>4012</v>
-      </c>
-      <c r="L110" s="1">
-        <v>200</v>
-      </c>
-      <c r="M110" s="1">
-        <f t="shared" si="14"/>
-        <v>320000</v>
-      </c>
-      <c r="N110" s="1">
-        <v>4</v>
-      </c>
-      <c r="O110" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="111" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C111" s="1">
-        <v>235</v>
-      </c>
-      <c r="D111" s="1">
-        <v>5</v>
-      </c>
-      <c r="E111" s="1">
-        <v>1</v>
-      </c>
-      <c r="F111" s="1">
-        <v>75000</v>
-      </c>
-      <c r="G111" s="1">
-        <f t="shared" si="13"/>
-        <v>32</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="J111" s="1">
-        <v>5</v>
-      </c>
-      <c r="K111" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L111" s="1">
-        <v>1</v>
-      </c>
-      <c r="M111" s="1">
-        <f t="shared" si="14"/>
-        <v>2400000</v>
-      </c>
-      <c r="N111" s="1">
-        <v>4</v>
-      </c>
-      <c r="O111" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="112" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C112" s="1">
-        <v>236</v>
-      </c>
-      <c r="D112" s="1">
-        <v>5</v>
-      </c>
-      <c r="E112" s="1">
-        <v>0</v>
-      </c>
-      <c r="F112" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G112" s="1">
-        <f t="shared" si="13"/>
-        <v>160</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="I112" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J112" s="1">
-        <v>5</v>
-      </c>
-      <c r="K112" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L112" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M112" s="1">
-        <f t="shared" si="14"/>
-        <v>640000</v>
-      </c>
-      <c r="N112" s="1">
-        <v>4</v>
-      </c>
-      <c r="O112" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="113" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C113" s="1">
-        <v>237</v>
-      </c>
-      <c r="D113" s="1">
-        <v>5</v>
-      </c>
-      <c r="E113" s="1">
-        <v>0</v>
-      </c>
-      <c r="F113" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G113" s="1">
-        <f t="shared" si="13"/>
-        <v>160</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="J113" s="1">
-        <v>5</v>
-      </c>
-      <c r="K113" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L113" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M113" s="1">
-        <f t="shared" si="14"/>
-        <v>640000</v>
-      </c>
-      <c r="N113" s="1">
-        <v>4</v>
-      </c>
-      <c r="O113" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="114" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C114" s="1">
-        <v>238</v>
-      </c>
-      <c r="D114" s="1">
-        <v>5</v>
-      </c>
-      <c r="E114" s="1">
-        <v>6</v>
-      </c>
-      <c r="F114" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G114" s="1">
-        <f t="shared" si="13"/>
-        <v>5</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J114" s="1">
-        <v>5</v>
-      </c>
-      <c r="K114" s="1">
-        <v>4026</v>
-      </c>
-      <c r="L114" s="1">
-        <v>1</v>
-      </c>
-      <c r="M114" s="1">
-        <f t="shared" si="14"/>
-        <v>150000</v>
-      </c>
-      <c r="N114" s="1">
-        <v>1</v>
-      </c>
-      <c r="O114" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="116" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C116" s="1">
-        <v>999</v>
-      </c>
-      <c r="D116" s="1">
-        <v>0</v>
-      </c>
-      <c r="E116" s="1">
-        <v>0</v>
-      </c>
-      <c r="F116" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G116" s="1">
-        <v>50</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J116" s="1">
-        <v>5</v>
-      </c>
-      <c r="K116" s="1">
-        <v>4006</v>
-      </c>
-      <c r="L116" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M116" s="1">
-        <f t="shared" ref="M116:M118" si="15">F116*G116</f>
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="117" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C117" s="1">
-        <v>1000</v>
-      </c>
-      <c r="D117" s="1">
-        <v>0</v>
-      </c>
-      <c r="E117" s="1">
-        <v>0</v>
-      </c>
-      <c r="F117" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G117" s="1">
-        <v>100</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="I117" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="J117" s="1">
-        <v>5</v>
-      </c>
-      <c r="K117" s="1">
-        <v>4010</v>
-      </c>
-      <c r="L117" s="1">
-        <v>5</v>
-      </c>
-      <c r="M117" s="1">
-        <f t="shared" si="15"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="118" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C118" s="1">
-        <v>1001</v>
-      </c>
-      <c r="D118" s="1">
-        <v>0</v>
-      </c>
-      <c r="E118" s="1">
-        <v>0</v>
-      </c>
-      <c r="F118" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G118" s="1">
-        <v>50</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="I118" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="J118" s="1">
-        <v>5</v>
-      </c>
-      <c r="K118" s="1">
-        <v>4102</v>
-      </c>
-      <c r="L118" s="1">
-        <v>20</v>
-      </c>
-      <c r="M118" s="1">
-        <f t="shared" si="15"/>
         <v>100000</v>
       </c>
     </row>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="154">
   <si>
     <t>#</t>
   </si>
@@ -414,6 +414,15 @@
   </si>
   <si>
     <t>低级法宝自选</t>
+  </si>
+  <si>
+    <t>兑换时装精华</t>
+  </si>
+  <si>
+    <t>时装精华</t>
+  </si>
+  <si>
+    <t>超级书页</t>
   </si>
   <si>
     <t>兑换四格碎片*1000</t>
@@ -1496,7 +1505,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O106"/>
+  <dimension ref="C1:O112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -3478,7 +3487,7 @@
         <v>50000</v>
       </c>
       <c r="G57" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>127</v>
@@ -3497,7 +3506,7 @@
       </c>
       <c r="M57" s="1">
         <f t="shared" si="3"/>
-        <v>1500000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="3:15">
@@ -3515,22 +3524,21 @@
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C59" s="1">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="D59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
       </c>
       <c r="F59" s="1">
-        <v>100</v>
+        <v>100000</v>
       </c>
       <c r="G59" s="1">
-        <f t="shared" ref="G59:G66" si="4">N59*O59</f>
-        <v>300</v>
+        <v>4</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>129</v>
@@ -3542,1803 +3550,1936 @@
         <v>5</v>
       </c>
       <c r="K59" s="1">
+        <v>4034</v>
+      </c>
+      <c r="L59" s="1">
+        <v>1</v>
+      </c>
+      <c r="M59" s="1">
+        <f>F59*G59</f>
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C60" s="1">
+        <v>54</v>
+      </c>
+      <c r="D60" s="1">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0</v>
+      </c>
+      <c r="F60" s="1">
+        <v>150000</v>
+      </c>
+      <c r="G60" s="1">
+        <v>1</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J60" s="1">
+        <v>5</v>
+      </c>
+      <c r="K60" s="1">
+        <v>4112</v>
+      </c>
+      <c r="L60" s="1">
+        <v>1</v>
+      </c>
+      <c r="M60" s="1">
+        <f>F60*G60</f>
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
+    </row>
+    <row r="62" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1"/>
+      <c r="O62" s="1"/>
+    </row>
+    <row r="63" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
+    </row>
+    <row r="64" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1"/>
+      <c r="O64" s="1"/>
+    </row>
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C65" s="1">
+        <v>102</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1</v>
+      </c>
+      <c r="E65" s="1">
+        <v>0</v>
+      </c>
+      <c r="F65" s="1">
+        <v>100</v>
+      </c>
+      <c r="G65" s="1">
+        <f t="shared" ref="G65:G72" si="4">N65*O65</f>
+        <v>300</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J65" s="1">
+        <v>5</v>
+      </c>
+      <c r="K65" s="1">
         <v>4007</v>
       </c>
-      <c r="L59" s="1">
+      <c r="L65" s="1">
         <v>1000</v>
       </c>
-      <c r="M59" s="1">
-        <f t="shared" ref="M59:M66" si="5">F59*G59</f>
+      <c r="M65" s="1">
+        <f t="shared" ref="M65:M72" si="5">F65*G65</f>
         <v>30000</v>
       </c>
-      <c r="N59" s="1">
-        <v>1</v>
-      </c>
-      <c r="O59" s="1">
+      <c r="N65" s="1">
+        <v>1</v>
+      </c>
+      <c r="O65" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C60" s="1">
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C66" s="1">
         <v>103</v>
       </c>
-      <c r="D60" s="1">
-        <v>1</v>
-      </c>
-      <c r="E60" s="1">
-        <v>0</v>
-      </c>
-      <c r="F60" s="1">
+      <c r="D66" s="1">
+        <v>1</v>
+      </c>
+      <c r="E66" s="1">
+        <v>0</v>
+      </c>
+      <c r="F66" s="1">
         <v>100</v>
       </c>
-      <c r="G60" s="1">
+      <c r="G66" s="1">
         <f t="shared" si="4"/>
         <v>500</v>
       </c>
-      <c r="H60" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J60" s="1">
-        <v>5</v>
-      </c>
-      <c r="K60" s="1">
+      <c r="H66" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J66" s="1">
+        <v>5</v>
+      </c>
+      <c r="K66" s="1">
         <v>4101</v>
       </c>
-      <c r="L60" s="1">
+      <c r="L66" s="1">
         <v>1000</v>
       </c>
-      <c r="M60" s="1">
+      <c r="M66" s="1">
         <f t="shared" si="5"/>
         <v>50000</v>
       </c>
-      <c r="N60" s="1">
-        <v>1</v>
-      </c>
-      <c r="O60" s="1">
+      <c r="N66" s="1">
+        <v>1</v>
+      </c>
+      <c r="O66" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C61" s="1">
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C67" s="1">
         <v>104</v>
       </c>
-      <c r="D61" s="1">
-        <v>1</v>
-      </c>
-      <c r="E61" s="1">
-        <v>0</v>
-      </c>
-      <c r="F61" s="1">
+      <c r="D67" s="1">
+        <v>1</v>
+      </c>
+      <c r="E67" s="1">
+        <v>0</v>
+      </c>
+      <c r="F67" s="1">
         <v>1000</v>
       </c>
-      <c r="G61" s="1">
+      <c r="G67" s="1">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="H61" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J61" s="1">
+      <c r="H67" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J67" s="1">
         <v>15</v>
       </c>
-      <c r="K61" s="1">
+      <c r="K67" s="1">
         <v>4014</v>
       </c>
-      <c r="L61" s="1">
+      <c r="L67" s="1">
         <v>100</v>
       </c>
-      <c r="M61" s="1">
+      <c r="M67" s="1">
         <f t="shared" si="5"/>
         <v>6000</v>
       </c>
-      <c r="N61" s="1">
-        <v>1</v>
-      </c>
-      <c r="O61" s="1">
+      <c r="N67" s="1">
+        <v>1</v>
+      </c>
+      <c r="O67" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C62" s="1">
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C68" s="1">
         <v>105</v>
       </c>
-      <c r="D62" s="1">
-        <v>1</v>
-      </c>
-      <c r="E62" s="1">
-        <v>0</v>
-      </c>
-      <c r="F62" s="1">
+      <c r="D68" s="1">
+        <v>1</v>
+      </c>
+      <c r="E68" s="1">
+        <v>0</v>
+      </c>
+      <c r="F68" s="1">
         <v>500</v>
       </c>
-      <c r="G62" s="1">
+      <c r="G68" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="H62" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J62" s="1">
-        <v>5</v>
-      </c>
-      <c r="K62" s="1">
+      <c r="H68" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J68" s="1">
+        <v>5</v>
+      </c>
+      <c r="K68" s="1">
         <v>4012</v>
       </c>
-      <c r="L62" s="1">
+      <c r="L68" s="1">
         <v>200</v>
       </c>
-      <c r="M62" s="1">
+      <c r="M68" s="1">
         <f t="shared" si="5"/>
         <v>10000</v>
       </c>
-      <c r="N62" s="1">
-        <v>1</v>
-      </c>
-      <c r="O62" s="1">
+      <c r="N68" s="1">
+        <v>1</v>
+      </c>
+      <c r="O68" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C63" s="1">
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C69" s="1">
         <v>106</v>
       </c>
-      <c r="D63" s="1">
-        <v>1</v>
-      </c>
-      <c r="E63" s="1">
-        <v>1</v>
-      </c>
-      <c r="F63" s="1">
+      <c r="D69" s="1">
+        <v>1</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1</v>
+      </c>
+      <c r="F69" s="1">
         <v>15000</v>
       </c>
-      <c r="G63" s="1">
+      <c r="G69" s="1">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="H63" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J63" s="1">
-        <v>5</v>
-      </c>
-      <c r="K63" s="1">
+      <c r="H69" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J69" s="1">
+        <v>5</v>
+      </c>
+      <c r="K69" s="1">
         <v>4019</v>
       </c>
-      <c r="L63" s="1">
-        <v>1</v>
-      </c>
-      <c r="M63" s="1">
+      <c r="L69" s="1">
+        <v>1</v>
+      </c>
+      <c r="M69" s="1">
         <f t="shared" si="5"/>
         <v>120000</v>
       </c>
-      <c r="N63" s="1">
-        <v>1</v>
-      </c>
-      <c r="O63" s="1">
+      <c r="N69" s="1">
+        <v>1</v>
+      </c>
+      <c r="O69" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C64" s="1">
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C70" s="1">
         <v>107</v>
       </c>
-      <c r="D64" s="1">
-        <v>1</v>
-      </c>
-      <c r="E64" s="1">
-        <v>0</v>
-      </c>
-      <c r="F64" s="1">
+      <c r="D70" s="1">
+        <v>1</v>
+      </c>
+      <c r="E70" s="1">
+        <v>0</v>
+      </c>
+      <c r="F70" s="1">
         <v>500</v>
       </c>
-      <c r="G64" s="1">
+      <c r="G70" s="1">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="H64" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J64" s="1">
-        <v>5</v>
-      </c>
-      <c r="K64" s="1">
+      <c r="H70" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J70" s="1">
+        <v>5</v>
+      </c>
+      <c r="K70" s="1">
         <v>4001</v>
       </c>
-      <c r="L64" s="1">
+      <c r="L70" s="1">
         <v>1000000</v>
       </c>
-      <c r="M64" s="1">
+      <c r="M70" s="1">
         <f t="shared" si="5"/>
         <v>20000</v>
       </c>
-      <c r="N64" s="1">
-        <v>1</v>
-      </c>
-      <c r="O64" s="1">
+      <c r="N70" s="1">
+        <v>1</v>
+      </c>
+      <c r="O70" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C65" s="1">
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C71" s="1">
         <v>108</v>
       </c>
-      <c r="D65" s="1">
-        <v>1</v>
-      </c>
-      <c r="E65" s="1">
-        <v>0</v>
-      </c>
-      <c r="F65" s="1">
+      <c r="D71" s="1">
+        <v>1</v>
+      </c>
+      <c r="E71" s="1">
+        <v>0</v>
+      </c>
+      <c r="F71" s="1">
         <v>500</v>
       </c>
-      <c r="G65" s="1">
+      <c r="G71" s="1">
         <f t="shared" si="4"/>
         <v>40</v>
       </c>
-      <c r="H65" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J65" s="1">
-        <v>5</v>
-      </c>
-      <c r="K65" s="1">
+      <c r="H71" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J71" s="1">
+        <v>5</v>
+      </c>
+      <c r="K71" s="1">
         <v>4002</v>
       </c>
-      <c r="L65" s="1">
+      <c r="L71" s="1">
         <v>6000000</v>
       </c>
-      <c r="M65" s="1">
+      <c r="M71" s="1">
         <f t="shared" si="5"/>
         <v>20000</v>
       </c>
-      <c r="N65" s="1">
-        <v>1</v>
-      </c>
-      <c r="O65" s="1">
+      <c r="N71" s="1">
+        <v>1</v>
+      </c>
+      <c r="O71" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C66" s="1">
+    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C72" s="1">
         <v>109</v>
       </c>
-      <c r="D66" s="1">
-        <v>1</v>
-      </c>
-      <c r="E66" s="1">
+      <c r="D72" s="1">
+        <v>1</v>
+      </c>
+      <c r="E72" s="1">
         <v>6</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F72" s="1">
         <v>30000</v>
       </c>
-      <c r="G66" s="1">
+      <c r="G72" s="1">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="H66" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J66" s="1">
-        <v>5</v>
-      </c>
-      <c r="K66" s="1">
+      <c r="H72" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J72" s="1">
+        <v>5</v>
+      </c>
+      <c r="K72" s="1">
         <v>4026</v>
       </c>
-      <c r="L66" s="1">
-        <v>1</v>
-      </c>
-      <c r="M66" s="1">
+      <c r="L72" s="1">
+        <v>1</v>
+      </c>
+      <c r="M72" s="1">
         <f t="shared" si="5"/>
         <v>150000</v>
       </c>
-      <c r="N66" s="1">
-        <v>1</v>
-      </c>
-      <c r="O66" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C68" s="1">
+      <c r="N72" s="1">
+        <v>1</v>
+      </c>
+      <c r="O72" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C74" s="1">
         <v>201</v>
       </c>
-      <c r="D68" s="1">
+      <c r="D74" s="1">
         <v>2</v>
       </c>
-      <c r="E68" s="1">
-        <v>0</v>
-      </c>
-      <c r="F68" s="6">
+      <c r="E74" s="1">
+        <v>0</v>
+      </c>
+      <c r="F74" s="6">
         <v>200</v>
       </c>
-      <c r="G68" s="1">
-        <f t="shared" ref="G68:G75" si="6">N68*O68</f>
+      <c r="G74" s="1">
+        <f t="shared" ref="G74:G81" si="6">N74*O74</f>
         <v>300</v>
       </c>
-      <c r="H68" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J68" s="1">
-        <v>5</v>
-      </c>
-      <c r="K68" s="1">
+      <c r="H74" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J74" s="1">
+        <v>5</v>
+      </c>
+      <c r="K74" s="1">
         <v>4007</v>
       </c>
-      <c r="L68" s="1">
+      <c r="L74" s="1">
         <v>1000</v>
       </c>
-      <c r="M68" s="1">
-        <f t="shared" ref="M68:M75" si="7">F68*G68</f>
+      <c r="M74" s="1">
+        <f t="shared" ref="M74:M81" si="7">F74*G74</f>
         <v>60000</v>
       </c>
-      <c r="N68" s="1">
-        <v>1</v>
-      </c>
-      <c r="O68" s="1">
+      <c r="N74" s="1">
+        <v>1</v>
+      </c>
+      <c r="O74" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C69" s="1">
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C75" s="1">
         <v>202</v>
       </c>
-      <c r="D69" s="1">
+      <c r="D75" s="1">
         <v>2</v>
       </c>
-      <c r="E69" s="1">
-        <v>0</v>
-      </c>
-      <c r="F69" s="6">
+      <c r="E75" s="1">
+        <v>0</v>
+      </c>
+      <c r="F75" s="6">
         <v>200</v>
       </c>
-      <c r="G69" s="1">
+      <c r="G75" s="1">
         <f t="shared" si="6"/>
         <v>500</v>
       </c>
-      <c r="H69" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J69" s="1">
-        <v>5</v>
-      </c>
-      <c r="K69" s="1">
+      <c r="H75" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J75" s="1">
+        <v>5</v>
+      </c>
+      <c r="K75" s="1">
         <v>4101</v>
       </c>
-      <c r="L69" s="1">
+      <c r="L75" s="1">
         <v>1000</v>
       </c>
-      <c r="M69" s="1">
+      <c r="M75" s="1">
         <f t="shared" si="7"/>
         <v>100000</v>
       </c>
-      <c r="N69" s="1">
-        <v>1</v>
-      </c>
-      <c r="O69" s="1">
+      <c r="N75" s="1">
+        <v>1</v>
+      </c>
+      <c r="O75" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C70" s="1">
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C76" s="1">
         <v>203</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D76" s="1">
         <v>2</v>
       </c>
-      <c r="E70" s="1">
-        <v>0</v>
-      </c>
-      <c r="F70" s="6">
+      <c r="E76" s="1">
+        <v>0</v>
+      </c>
+      <c r="F76" s="6">
         <v>2000</v>
       </c>
-      <c r="G70" s="1">
+      <c r="G76" s="1">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="H70" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J70" s="1">
+      <c r="H76" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J76" s="1">
         <v>15</v>
       </c>
-      <c r="K70" s="1">
+      <c r="K76" s="1">
         <v>4014</v>
       </c>
-      <c r="L70" s="1">
+      <c r="L76" s="1">
         <v>100</v>
       </c>
-      <c r="M70" s="1">
+      <c r="M76" s="1">
         <f t="shared" si="7"/>
         <v>12000</v>
       </c>
-      <c r="N70" s="1">
-        <v>1</v>
-      </c>
-      <c r="O70" s="1">
+      <c r="N76" s="1">
+        <v>1</v>
+      </c>
+      <c r="O76" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C71" s="1">
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C77" s="1">
         <v>204</v>
       </c>
-      <c r="D71" s="1">
+      <c r="D77" s="1">
         <v>2</v>
       </c>
-      <c r="E71" s="1">
-        <v>0</v>
-      </c>
-      <c r="F71" s="6">
+      <c r="E77" s="1">
+        <v>0</v>
+      </c>
+      <c r="F77" s="6">
         <v>1000</v>
       </c>
-      <c r="G71" s="1">
+      <c r="G77" s="1">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="H71" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J71" s="1">
-        <v>5</v>
-      </c>
-      <c r="K71" s="1">
+      <c r="H77" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J77" s="1">
+        <v>5</v>
+      </c>
+      <c r="K77" s="1">
         <v>4012</v>
       </c>
-      <c r="L71" s="1">
+      <c r="L77" s="1">
         <v>200</v>
       </c>
-      <c r="M71" s="1">
+      <c r="M77" s="1">
         <f t="shared" si="7"/>
         <v>20000</v>
       </c>
-      <c r="N71" s="1">
-        <v>1</v>
-      </c>
-      <c r="O71" s="1">
+      <c r="N77" s="1">
+        <v>1</v>
+      </c>
+      <c r="O77" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C72" s="1">
+    <row r="78" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C78" s="1">
         <v>205</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D78" s="1">
         <v>2</v>
       </c>
-      <c r="E72" s="1">
-        <v>1</v>
-      </c>
-      <c r="F72" s="6">
+      <c r="E78" s="1">
+        <v>1</v>
+      </c>
+      <c r="F78" s="6">
         <v>30000</v>
       </c>
-      <c r="G72" s="1">
+      <c r="G78" s="1">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="H72" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J72" s="1">
-        <v>5</v>
-      </c>
-      <c r="K72" s="1">
+      <c r="H78" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J78" s="1">
+        <v>5</v>
+      </c>
+      <c r="K78" s="1">
         <v>4019</v>
       </c>
-      <c r="L72" s="1">
-        <v>1</v>
-      </c>
-      <c r="M72" s="1">
+      <c r="L78" s="1">
+        <v>1</v>
+      </c>
+      <c r="M78" s="1">
         <f t="shared" si="7"/>
         <v>240000</v>
       </c>
-      <c r="N72" s="1">
-        <v>1</v>
-      </c>
-      <c r="O72" s="1">
+      <c r="N78" s="1">
+        <v>1</v>
+      </c>
+      <c r="O78" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C73" s="1">
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C79" s="1">
         <v>206</v>
       </c>
-      <c r="D73" s="1">
+      <c r="D79" s="1">
         <v>2</v>
       </c>
-      <c r="E73" s="1">
-        <v>0</v>
-      </c>
-      <c r="F73" s="6">
+      <c r="E79" s="1">
+        <v>0</v>
+      </c>
+      <c r="F79" s="6">
         <v>1000</v>
       </c>
-      <c r="G73" s="1">
+      <c r="G79" s="1">
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="H73" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J73" s="1">
-        <v>5</v>
-      </c>
-      <c r="K73" s="1">
+      <c r="H79" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J79" s="1">
+        <v>5</v>
+      </c>
+      <c r="K79" s="1">
         <v>4001</v>
       </c>
-      <c r="L73" s="1">
+      <c r="L79" s="1">
         <v>1000000</v>
       </c>
-      <c r="M73" s="1">
+      <c r="M79" s="1">
         <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="N73" s="1">
-        <v>1</v>
-      </c>
-      <c r="O73" s="1">
+      <c r="N79" s="1">
+        <v>1</v>
+      </c>
+      <c r="O79" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="74" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C74" s="1">
+    <row r="80" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C80" s="1">
         <v>207</v>
       </c>
-      <c r="D74" s="1">
+      <c r="D80" s="1">
         <v>2</v>
       </c>
-      <c r="E74" s="1">
-        <v>0</v>
-      </c>
-      <c r="F74" s="6">
+      <c r="E80" s="1">
+        <v>0</v>
+      </c>
+      <c r="F80" s="6">
         <v>1000</v>
       </c>
-      <c r="G74" s="1">
+      <c r="G80" s="1">
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="H74" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J74" s="1">
-        <v>5</v>
-      </c>
-      <c r="K74" s="1">
+      <c r="H80" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J80" s="1">
+        <v>5</v>
+      </c>
+      <c r="K80" s="1">
         <v>4002</v>
       </c>
-      <c r="L74" s="1">
+      <c r="L80" s="1">
         <v>6000000</v>
       </c>
-      <c r="M74" s="1">
+      <c r="M80" s="1">
         <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="N74" s="1">
-        <v>1</v>
-      </c>
-      <c r="O74" s="1">
+      <c r="N80" s="1">
+        <v>1</v>
+      </c>
+      <c r="O80" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C75" s="1">
+    <row r="81" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C81" s="1">
         <v>208</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D81" s="1">
         <v>2</v>
       </c>
-      <c r="E75" s="1">
+      <c r="E81" s="1">
         <v>6</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F81" s="1">
         <v>30000</v>
       </c>
-      <c r="G75" s="1">
+      <c r="G81" s="1">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="H75" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J75" s="1">
-        <v>5</v>
-      </c>
-      <c r="K75" s="1">
+      <c r="H81" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J81" s="1">
+        <v>5</v>
+      </c>
+      <c r="K81" s="1">
         <v>4026</v>
       </c>
-      <c r="L75" s="1">
-        <v>1</v>
-      </c>
-      <c r="M75" s="1">
+      <c r="L81" s="1">
+        <v>1</v>
+      </c>
+      <c r="M81" s="1">
         <f t="shared" si="7"/>
         <v>150000</v>
       </c>
-      <c r="N75" s="1">
-        <v>1</v>
-      </c>
-      <c r="O75" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C77" s="1">
+      <c r="N81" s="1">
+        <v>1</v>
+      </c>
+      <c r="O81" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C83" s="1">
         <v>211</v>
       </c>
-      <c r="D77" s="1">
+      <c r="D83" s="1">
         <v>3</v>
       </c>
-      <c r="E77" s="1">
-        <v>0</v>
-      </c>
-      <c r="F77" s="1">
+      <c r="E83" s="1">
+        <v>0</v>
+      </c>
+      <c r="F83" s="1">
         <v>400</v>
       </c>
-      <c r="G77" s="1">
-        <f t="shared" ref="G77:G84" si="8">N77*O77</f>
+      <c r="G83" s="1">
+        <f t="shared" ref="G83:G90" si="8">N83*O83</f>
         <v>300</v>
       </c>
-      <c r="H77" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J77" s="1">
-        <v>5</v>
-      </c>
-      <c r="K77" s="1">
+      <c r="H83" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J83" s="1">
+        <v>5</v>
+      </c>
+      <c r="K83" s="1">
         <v>4007</v>
       </c>
-      <c r="L77" s="1">
+      <c r="L83" s="1">
         <v>1000</v>
       </c>
-      <c r="M77" s="1">
-        <f t="shared" ref="M77:M84" si="9">F77*G77</f>
+      <c r="M83" s="1">
+        <f t="shared" ref="M83:M90" si="9">F83*G83</f>
         <v>120000</v>
       </c>
-      <c r="N77" s="1">
-        <v>1</v>
-      </c>
-      <c r="O77" s="1">
+      <c r="N83" s="1">
+        <v>1</v>
+      </c>
+      <c r="O83" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C78" s="1">
+    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C84" s="1">
         <v>212</v>
       </c>
-      <c r="D78" s="1">
+      <c r="D84" s="1">
         <v>3</v>
       </c>
-      <c r="E78" s="1">
-        <v>0</v>
-      </c>
-      <c r="F78" s="1">
+      <c r="E84" s="1">
+        <v>0</v>
+      </c>
+      <c r="F84" s="1">
         <v>400</v>
       </c>
-      <c r="G78" s="1">
+      <c r="G84" s="1">
         <f t="shared" si="8"/>
         <v>500</v>
       </c>
-      <c r="H78" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J78" s="1">
-        <v>5</v>
-      </c>
-      <c r="K78" s="1">
+      <c r="H84" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J84" s="1">
+        <v>5</v>
+      </c>
+      <c r="K84" s="1">
         <v>4101</v>
       </c>
-      <c r="L78" s="1">
+      <c r="L84" s="1">
         <v>1000</v>
       </c>
-      <c r="M78" s="1">
+      <c r="M84" s="1">
         <f t="shared" si="9"/>
         <v>200000</v>
       </c>
-      <c r="N78" s="1">
-        <v>1</v>
-      </c>
-      <c r="O78" s="1">
+      <c r="N84" s="1">
+        <v>1</v>
+      </c>
+      <c r="O84" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C79" s="1">
+    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C85" s="1">
         <v>213</v>
       </c>
-      <c r="D79" s="1">
+      <c r="D85" s="1">
         <v>3</v>
       </c>
-      <c r="E79" s="1">
-        <v>0</v>
-      </c>
-      <c r="F79" s="1">
+      <c r="E85" s="1">
+        <v>0</v>
+      </c>
+      <c r="F85" s="1">
         <v>4000</v>
       </c>
-      <c r="G79" s="1">
+      <c r="G85" s="1">
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="H79" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J79" s="1">
+      <c r="H85" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J85" s="1">
         <v>15</v>
       </c>
-      <c r="K79" s="1">
+      <c r="K85" s="1">
         <v>4014</v>
       </c>
-      <c r="L79" s="1">
+      <c r="L85" s="1">
         <v>100</v>
       </c>
-      <c r="M79" s="1">
+      <c r="M85" s="1">
         <f t="shared" si="9"/>
         <v>24000</v>
       </c>
-      <c r="N79" s="1">
-        <v>1</v>
-      </c>
-      <c r="O79" s="1">
+      <c r="N85" s="1">
+        <v>1</v>
+      </c>
+      <c r="O85" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="80" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C80" s="1">
+    <row r="86" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C86" s="1">
         <v>214</v>
       </c>
-      <c r="D80" s="1">
+      <c r="D86" s="1">
         <v>3</v>
       </c>
-      <c r="E80" s="1">
-        <v>0</v>
-      </c>
-      <c r="F80" s="1">
+      <c r="E86" s="1">
+        <v>0</v>
+      </c>
+      <c r="F86" s="1">
         <v>2000</v>
       </c>
-      <c r="G80" s="1">
+      <c r="G86" s="1">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="H80" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J80" s="1">
-        <v>5</v>
-      </c>
-      <c r="K80" s="1">
+      <c r="H86" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J86" s="1">
+        <v>5</v>
+      </c>
+      <c r="K86" s="1">
         <v>4012</v>
       </c>
-      <c r="L80" s="1">
+      <c r="L86" s="1">
         <v>200</v>
       </c>
-      <c r="M80" s="1">
+      <c r="M86" s="1">
         <f t="shared" si="9"/>
         <v>40000</v>
       </c>
-      <c r="N80" s="1">
-        <v>1</v>
-      </c>
-      <c r="O80" s="1">
+      <c r="N86" s="1">
+        <v>1</v>
+      </c>
+      <c r="O86" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="81" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C81" s="1">
+    <row r="87" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C87" s="1">
         <v>215</v>
       </c>
-      <c r="D81" s="1">
+      <c r="D87" s="1">
         <v>3</v>
       </c>
-      <c r="E81" s="1">
-        <v>1</v>
-      </c>
-      <c r="F81" s="1">
+      <c r="E87" s="1">
+        <v>1</v>
+      </c>
+      <c r="F87" s="1">
         <v>45000</v>
       </c>
-      <c r="G81" s="1">
+      <c r="G87" s="1">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="H81" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J81" s="1">
-        <v>5</v>
-      </c>
-      <c r="K81" s="1">
+      <c r="H87" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J87" s="1">
+        <v>5</v>
+      </c>
+      <c r="K87" s="1">
         <v>4019</v>
       </c>
-      <c r="L81" s="1">
-        <v>1</v>
-      </c>
-      <c r="M81" s="1">
+      <c r="L87" s="1">
+        <v>1</v>
+      </c>
+      <c r="M87" s="1">
         <f t="shared" si="9"/>
         <v>360000</v>
       </c>
-      <c r="N81" s="1">
-        <v>1</v>
-      </c>
-      <c r="O81" s="1">
+      <c r="N87" s="1">
+        <v>1</v>
+      </c>
+      <c r="O87" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="82" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C82" s="1">
+    <row r="88" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C88" s="1">
         <v>216</v>
       </c>
-      <c r="D82" s="1">
+      <c r="D88" s="1">
         <v>3</v>
       </c>
-      <c r="E82" s="1">
-        <v>0</v>
-      </c>
-      <c r="F82" s="1">
+      <c r="E88" s="1">
+        <v>0</v>
+      </c>
+      <c r="F88" s="1">
         <v>2000</v>
       </c>
-      <c r="G82" s="1">
+      <c r="G88" s="1">
         <f t="shared" si="8"/>
         <v>40</v>
       </c>
-      <c r="H82" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J82" s="1">
-        <v>5</v>
-      </c>
-      <c r="K82" s="1">
+      <c r="H88" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J88" s="1">
+        <v>5</v>
+      </c>
+      <c r="K88" s="1">
         <v>4001</v>
       </c>
-      <c r="L82" s="1">
+      <c r="L88" s="1">
         <v>1000000</v>
       </c>
-      <c r="M82" s="1">
+      <c r="M88" s="1">
         <f t="shared" si="9"/>
         <v>80000</v>
       </c>
-      <c r="N82" s="1">
-        <v>1</v>
-      </c>
-      <c r="O82" s="1">
+      <c r="N88" s="1">
+        <v>1</v>
+      </c>
+      <c r="O88" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="83" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C83" s="1">
+    <row r="89" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C89" s="1">
         <v>217</v>
       </c>
-      <c r="D83" s="1">
+      <c r="D89" s="1">
         <v>3</v>
       </c>
-      <c r="E83" s="1">
-        <v>0</v>
-      </c>
-      <c r="F83" s="1">
+      <c r="E89" s="1">
+        <v>0</v>
+      </c>
+      <c r="F89" s="1">
         <v>2000</v>
       </c>
-      <c r="G83" s="1">
+      <c r="G89" s="1">
         <f t="shared" si="8"/>
         <v>40</v>
       </c>
-      <c r="H83" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J83" s="1">
-        <v>5</v>
-      </c>
-      <c r="K83" s="1">
+      <c r="H89" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J89" s="1">
+        <v>5</v>
+      </c>
+      <c r="K89" s="1">
         <v>4002</v>
       </c>
-      <c r="L83" s="1">
+      <c r="L89" s="1">
         <v>6000000</v>
       </c>
-      <c r="M83" s="1">
+      <c r="M89" s="1">
         <f t="shared" si="9"/>
         <v>80000</v>
       </c>
-      <c r="N83" s="1">
-        <v>1</v>
-      </c>
-      <c r="O83" s="1">
+      <c r="N89" s="1">
+        <v>1</v>
+      </c>
+      <c r="O89" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C84" s="1">
+    <row r="90" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C90" s="1">
         <v>218</v>
       </c>
-      <c r="D84" s="1">
+      <c r="D90" s="1">
         <v>3</v>
       </c>
-      <c r="E84" s="1">
+      <c r="E90" s="1">
         <v>6</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F90" s="1">
         <v>30000</v>
       </c>
-      <c r="G84" s="1">
+      <c r="G90" s="1">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
-      <c r="H84" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J84" s="1">
-        <v>5</v>
-      </c>
-      <c r="K84" s="1">
+      <c r="H90" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J90" s="1">
+        <v>5</v>
+      </c>
+      <c r="K90" s="1">
         <v>4026</v>
       </c>
-      <c r="L84" s="1">
-        <v>1</v>
-      </c>
-      <c r="M84" s="1">
+      <c r="L90" s="1">
+        <v>1</v>
+      </c>
+      <c r="M90" s="1">
         <f t="shared" si="9"/>
         <v>150000</v>
       </c>
-      <c r="N84" s="1">
-        <v>1</v>
-      </c>
-      <c r="O84" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C86" s="1">
+      <c r="N90" s="1">
+        <v>1</v>
+      </c>
+      <c r="O90" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C92" s="1">
         <v>221</v>
       </c>
-      <c r="D86" s="1">
+      <c r="D92" s="1">
         <v>4</v>
       </c>
-      <c r="E86" s="1">
-        <v>0</v>
-      </c>
-      <c r="F86" s="6">
+      <c r="E92" s="1">
+        <v>0</v>
+      </c>
+      <c r="F92" s="6">
         <v>600</v>
       </c>
-      <c r="G86" s="1">
-        <f t="shared" ref="G86:G93" si="10">N86*O86</f>
+      <c r="G92" s="1">
+        <f t="shared" ref="G92:G99" si="10">N92*O92</f>
         <v>300</v>
       </c>
-      <c r="H86" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J86" s="1">
-        <v>5</v>
-      </c>
-      <c r="K86" s="1">
+      <c r="H92" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J92" s="1">
+        <v>5</v>
+      </c>
+      <c r="K92" s="1">
         <v>4007</v>
       </c>
-      <c r="L86" s="1">
+      <c r="L92" s="1">
         <v>1000</v>
       </c>
-      <c r="M86" s="1">
-        <f t="shared" ref="M86:M93" si="11">F86*G86</f>
+      <c r="M92" s="1">
+        <f t="shared" ref="M92:M99" si="11">F92*G92</f>
         <v>180000</v>
       </c>
-      <c r="N86" s="1">
-        <v>1</v>
-      </c>
-      <c r="O86" s="1">
+      <c r="N92" s="1">
+        <v>1</v>
+      </c>
+      <c r="O92" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="87" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C87" s="1">
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C93" s="1">
         <v>222</v>
       </c>
-      <c r="D87" s="1">
+      <c r="D93" s="1">
         <v>4</v>
       </c>
-      <c r="E87" s="1">
-        <v>0</v>
-      </c>
-      <c r="F87" s="6">
+      <c r="E93" s="1">
+        <v>0</v>
+      </c>
+      <c r="F93" s="6">
         <v>600</v>
       </c>
-      <c r="G87" s="1">
+      <c r="G93" s="1">
         <f t="shared" si="10"/>
         <v>500</v>
       </c>
-      <c r="H87" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J87" s="1">
-        <v>5</v>
-      </c>
-      <c r="K87" s="1">
+      <c r="H93" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J93" s="1">
+        <v>5</v>
+      </c>
+      <c r="K93" s="1">
         <v>4101</v>
       </c>
-      <c r="L87" s="1">
+      <c r="L93" s="1">
         <v>1000</v>
       </c>
-      <c r="M87" s="1">
+      <c r="M93" s="1">
         <f t="shared" si="11"/>
         <v>300000</v>
       </c>
-      <c r="N87" s="1">
-        <v>1</v>
-      </c>
-      <c r="O87" s="1">
+      <c r="N93" s="1">
+        <v>1</v>
+      </c>
+      <c r="O93" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="88" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C88" s="1">
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C94" s="1">
         <v>223</v>
       </c>
-      <c r="D88" s="1">
+      <c r="D94" s="1">
         <v>4</v>
       </c>
-      <c r="E88" s="1">
-        <v>0</v>
-      </c>
-      <c r="F88" s="6">
+      <c r="E94" s="1">
+        <v>0</v>
+      </c>
+      <c r="F94" s="6">
         <v>6000</v>
       </c>
-      <c r="G88" s="1">
+      <c r="G94" s="1">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="H88" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J88" s="1">
+      <c r="H94" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J94" s="1">
         <v>15</v>
       </c>
-      <c r="K88" s="1">
+      <c r="K94" s="1">
         <v>4014</v>
       </c>
-      <c r="L88" s="1">
+      <c r="L94" s="1">
         <v>100</v>
       </c>
-      <c r="M88" s="1">
+      <c r="M94" s="1">
         <f t="shared" si="11"/>
         <v>36000</v>
       </c>
-      <c r="N88" s="1">
-        <v>1</v>
-      </c>
-      <c r="O88" s="1">
+      <c r="N94" s="1">
+        <v>1</v>
+      </c>
+      <c r="O94" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="89" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C89" s="1">
+    <row r="95" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C95" s="1">
         <v>224</v>
       </c>
-      <c r="D89" s="1">
+      <c r="D95" s="1">
         <v>4</v>
       </c>
-      <c r="E89" s="1">
-        <v>0</v>
-      </c>
-      <c r="F89" s="6">
+      <c r="E95" s="1">
+        <v>0</v>
+      </c>
+      <c r="F95" s="6">
         <v>3000</v>
       </c>
-      <c r="G89" s="1">
+      <c r="G95" s="1">
         <f t="shared" si="10"/>
         <v>20</v>
       </c>
-      <c r="H89" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J89" s="1">
-        <v>5</v>
-      </c>
-      <c r="K89" s="1">
+      <c r="H95" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J95" s="1">
+        <v>5</v>
+      </c>
+      <c r="K95" s="1">
         <v>4012</v>
       </c>
-      <c r="L89" s="1">
+      <c r="L95" s="1">
         <v>200</v>
       </c>
-      <c r="M89" s="1">
+      <c r="M95" s="1">
         <f t="shared" si="11"/>
         <v>60000</v>
       </c>
-      <c r="N89" s="1">
-        <v>1</v>
-      </c>
-      <c r="O89" s="1">
+      <c r="N95" s="1">
+        <v>1</v>
+      </c>
+      <c r="O95" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="90" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C90" s="1">
+    <row r="96" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C96" s="1">
         <v>225</v>
       </c>
-      <c r="D90" s="1">
+      <c r="D96" s="1">
         <v>4</v>
       </c>
-      <c r="E90" s="1">
-        <v>1</v>
-      </c>
-      <c r="F90" s="6">
+      <c r="E96" s="1">
+        <v>1</v>
+      </c>
+      <c r="F96" s="6">
         <v>60000</v>
       </c>
-      <c r="G90" s="1">
+      <c r="G96" s="1">
         <f t="shared" si="10"/>
         <v>8</v>
       </c>
-      <c r="H90" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J90" s="1">
-        <v>5</v>
-      </c>
-      <c r="K90" s="1">
+      <c r="H96" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J96" s="1">
+        <v>5</v>
+      </c>
+      <c r="K96" s="1">
         <v>4019</v>
       </c>
-      <c r="L90" s="1">
-        <v>1</v>
-      </c>
-      <c r="M90" s="1">
+      <c r="L96" s="1">
+        <v>1</v>
+      </c>
+      <c r="M96" s="1">
         <f t="shared" si="11"/>
         <v>480000</v>
       </c>
-      <c r="N90" s="1">
-        <v>1</v>
-      </c>
-      <c r="O90" s="1">
+      <c r="N96" s="1">
+        <v>1</v>
+      </c>
+      <c r="O96" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="91" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C91" s="1">
+    <row r="97" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C97" s="1">
         <v>226</v>
       </c>
-      <c r="D91" s="1">
+      <c r="D97" s="1">
         <v>4</v>
       </c>
-      <c r="E91" s="1">
-        <v>0</v>
-      </c>
-      <c r="F91" s="6">
+      <c r="E97" s="1">
+        <v>0</v>
+      </c>
+      <c r="F97" s="6">
         <v>3000</v>
       </c>
-      <c r="G91" s="1">
+      <c r="G97" s="1">
         <f t="shared" si="10"/>
         <v>40</v>
       </c>
-      <c r="H91" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J91" s="1">
-        <v>5</v>
-      </c>
-      <c r="K91" s="1">
+      <c r="H97" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J97" s="1">
+        <v>5</v>
+      </c>
+      <c r="K97" s="1">
         <v>4001</v>
       </c>
-      <c r="L91" s="1">
+      <c r="L97" s="1">
         <v>1000000</v>
       </c>
-      <c r="M91" s="1">
+      <c r="M97" s="1">
         <f t="shared" si="11"/>
         <v>120000</v>
       </c>
-      <c r="N91" s="1">
-        <v>1</v>
-      </c>
-      <c r="O91" s="1">
+      <c r="N97" s="1">
+        <v>1</v>
+      </c>
+      <c r="O97" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="92" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C92" s="1">
+    <row r="98" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C98" s="1">
         <v>227</v>
       </c>
-      <c r="D92" s="1">
+      <c r="D98" s="1">
         <v>4</v>
       </c>
-      <c r="E92" s="1">
-        <v>0</v>
-      </c>
-      <c r="F92" s="6">
+      <c r="E98" s="1">
+        <v>0</v>
+      </c>
+      <c r="F98" s="6">
         <v>3000</v>
       </c>
-      <c r="G92" s="1">
+      <c r="G98" s="1">
         <f t="shared" si="10"/>
         <v>40</v>
       </c>
-      <c r="H92" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J92" s="1">
-        <v>5</v>
-      </c>
-      <c r="K92" s="1">
+      <c r="H98" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J98" s="1">
+        <v>5</v>
+      </c>
+      <c r="K98" s="1">
         <v>4002</v>
       </c>
-      <c r="L92" s="1">
+      <c r="L98" s="1">
         <v>6000000</v>
       </c>
-      <c r="M92" s="1">
+      <c r="M98" s="1">
         <f t="shared" si="11"/>
         <v>120000</v>
       </c>
-      <c r="N92" s="1">
-        <v>1</v>
-      </c>
-      <c r="O92" s="1">
+      <c r="N98" s="1">
+        <v>1</v>
+      </c>
+      <c r="O98" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="93" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C93" s="1">
+    <row r="99" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C99" s="1">
         <v>228</v>
       </c>
-      <c r="D93" s="1">
+      <c r="D99" s="1">
         <v>4</v>
       </c>
-      <c r="E93" s="1">
+      <c r="E99" s="1">
         <v>6</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F99" s="1">
         <v>30000</v>
       </c>
-      <c r="G93" s="1">
+      <c r="G99" s="1">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="H93" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J93" s="1">
-        <v>5</v>
-      </c>
-      <c r="K93" s="1">
+      <c r="H99" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J99" s="1">
+        <v>5</v>
+      </c>
+      <c r="K99" s="1">
         <v>4026</v>
       </c>
-      <c r="L93" s="1">
-        <v>1</v>
-      </c>
-      <c r="M93" s="1">
+      <c r="L99" s="1">
+        <v>1</v>
+      </c>
+      <c r="M99" s="1">
         <f t="shared" si="11"/>
         <v>150000</v>
       </c>
-      <c r="N93" s="1">
-        <v>1</v>
-      </c>
-      <c r="O93" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C95" s="1">
+      <c r="N99" s="1">
+        <v>1</v>
+      </c>
+      <c r="O99" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C101" s="1">
         <v>231</v>
       </c>
-      <c r="D95" s="1">
-        <v>5</v>
-      </c>
-      <c r="E95" s="1">
-        <v>0</v>
-      </c>
-      <c r="F95" s="1">
+      <c r="D101" s="1">
+        <v>5</v>
+      </c>
+      <c r="E101" s="1">
+        <v>0</v>
+      </c>
+      <c r="F101" s="1">
         <v>800</v>
       </c>
-      <c r="G95" s="1">
-        <f t="shared" ref="G95:G102" si="12">N95*O95</f>
+      <c r="G101" s="1">
+        <f t="shared" ref="G101:G108" si="12">N101*O101</f>
         <v>1200</v>
       </c>
-      <c r="H95" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J95" s="1">
-        <v>5</v>
-      </c>
-      <c r="K95" s="1">
+      <c r="H101" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J101" s="1">
+        <v>5</v>
+      </c>
+      <c r="K101" s="1">
         <v>4007</v>
       </c>
-      <c r="L95" s="1">
+      <c r="L101" s="1">
         <v>1000</v>
       </c>
-      <c r="M95" s="1">
-        <f t="shared" ref="M95:M102" si="13">F95*G95</f>
+      <c r="M101" s="1">
+        <f t="shared" ref="M101:M108" si="13">F101*G101</f>
         <v>960000</v>
       </c>
-      <c r="N95" s="1">
+      <c r="N101" s="1">
         <v>4</v>
       </c>
-      <c r="O95" s="1">
+      <c r="O101" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="96" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C96" s="1">
+    <row r="102" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C102" s="1">
         <v>232</v>
       </c>
-      <c r="D96" s="1">
-        <v>5</v>
-      </c>
-      <c r="E96" s="1">
-        <v>0</v>
-      </c>
-      <c r="F96" s="1">
+      <c r="D102" s="1">
+        <v>5</v>
+      </c>
+      <c r="E102" s="1">
+        <v>0</v>
+      </c>
+      <c r="F102" s="1">
         <v>800</v>
       </c>
-      <c r="G96" s="1">
+      <c r="G102" s="1">
         <f t="shared" si="12"/>
         <v>2000</v>
       </c>
-      <c r="H96" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J96" s="1">
-        <v>5</v>
-      </c>
-      <c r="K96" s="1">
+      <c r="H102" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J102" s="1">
+        <v>5</v>
+      </c>
+      <c r="K102" s="1">
         <v>4101</v>
       </c>
-      <c r="L96" s="1">
+      <c r="L102" s="1">
         <v>1000</v>
       </c>
-      <c r="M96" s="1">
+      <c r="M102" s="1">
         <f t="shared" si="13"/>
         <v>1600000</v>
       </c>
-      <c r="N96" s="1">
+      <c r="N102" s="1">
         <v>4</v>
       </c>
-      <c r="O96" s="1">
+      <c r="O102" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="97" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C97" s="1">
+    <row r="103" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C103" s="1">
         <v>233</v>
       </c>
-      <c r="D97" s="1">
-        <v>5</v>
-      </c>
-      <c r="E97" s="1">
-        <v>0</v>
-      </c>
-      <c r="F97" s="1">
+      <c r="D103" s="1">
+        <v>5</v>
+      </c>
+      <c r="E103" s="1">
+        <v>0</v>
+      </c>
+      <c r="F103" s="1">
         <v>8000</v>
       </c>
-      <c r="G97" s="1">
+      <c r="G103" s="1">
         <f t="shared" si="12"/>
         <v>24</v>
       </c>
-      <c r="H97" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J97" s="1">
+      <c r="H103" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J103" s="1">
         <v>15</v>
       </c>
-      <c r="K97" s="1">
+      <c r="K103" s="1">
         <v>4014</v>
       </c>
-      <c r="L97" s="1">
+      <c r="L103" s="1">
         <v>100</v>
       </c>
-      <c r="M97" s="1">
+      <c r="M103" s="1">
         <f t="shared" si="13"/>
         <v>192000</v>
       </c>
-      <c r="N97" s="1">
+      <c r="N103" s="1">
         <v>4</v>
       </c>
-      <c r="O97" s="1">
+      <c r="O103" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="98" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C98" s="1">
+    <row r="104" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C104" s="1">
         <v>234</v>
       </c>
-      <c r="D98" s="1">
-        <v>5</v>
-      </c>
-      <c r="E98" s="1">
-        <v>0</v>
-      </c>
-      <c r="F98" s="1">
+      <c r="D104" s="1">
+        <v>5</v>
+      </c>
+      <c r="E104" s="1">
+        <v>0</v>
+      </c>
+      <c r="F104" s="1">
         <v>4000</v>
       </c>
-      <c r="G98" s="1">
+      <c r="G104" s="1">
         <f t="shared" si="12"/>
         <v>80</v>
       </c>
-      <c r="H98" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J98" s="1">
-        <v>5</v>
-      </c>
-      <c r="K98" s="1">
+      <c r="H104" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J104" s="1">
+        <v>5</v>
+      </c>
+      <c r="K104" s="1">
         <v>4012</v>
       </c>
-      <c r="L98" s="1">
+      <c r="L104" s="1">
         <v>200</v>
       </c>
-      <c r="M98" s="1">
+      <c r="M104" s="1">
         <f t="shared" si="13"/>
         <v>320000</v>
       </c>
-      <c r="N98" s="1">
+      <c r="N104" s="1">
         <v>4</v>
       </c>
-      <c r="O98" s="1">
+      <c r="O104" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="99" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C99" s="1">
+    <row r="105" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C105" s="1">
         <v>235</v>
       </c>
-      <c r="D99" s="1">
-        <v>5</v>
-      </c>
-      <c r="E99" s="1">
-        <v>1</v>
-      </c>
-      <c r="F99" s="1">
+      <c r="D105" s="1">
+        <v>5</v>
+      </c>
+      <c r="E105" s="1">
+        <v>1</v>
+      </c>
+      <c r="F105" s="1">
         <v>75000</v>
       </c>
-      <c r="G99" s="1">
+      <c r="G105" s="1">
         <f t="shared" si="12"/>
         <v>32</v>
       </c>
-      <c r="H99" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J99" s="1">
-        <v>5</v>
-      </c>
-      <c r="K99" s="1">
+      <c r="H105" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J105" s="1">
+        <v>5</v>
+      </c>
+      <c r="K105" s="1">
         <v>4019</v>
       </c>
-      <c r="L99" s="1">
-        <v>1</v>
-      </c>
-      <c r="M99" s="1">
+      <c r="L105" s="1">
+        <v>1</v>
+      </c>
+      <c r="M105" s="1">
         <f t="shared" si="13"/>
         <v>2400000</v>
       </c>
-      <c r="N99" s="1">
+      <c r="N105" s="1">
         <v>4</v>
       </c>
-      <c r="O99" s="1">
+      <c r="O105" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="100" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C100" s="1">
+    <row r="106" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C106" s="1">
         <v>236</v>
       </c>
-      <c r="D100" s="1">
-        <v>5</v>
-      </c>
-      <c r="E100" s="1">
-        <v>0</v>
-      </c>
-      <c r="F100" s="1">
+      <c r="D106" s="1">
+        <v>5</v>
+      </c>
+      <c r="E106" s="1">
+        <v>0</v>
+      </c>
+      <c r="F106" s="1">
         <v>4000</v>
       </c>
-      <c r="G100" s="1">
+      <c r="G106" s="1">
         <f t="shared" si="12"/>
         <v>160</v>
       </c>
-      <c r="H100" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J100" s="1">
-        <v>5</v>
-      </c>
-      <c r="K100" s="1">
+      <c r="H106" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J106" s="1">
+        <v>5</v>
+      </c>
+      <c r="K106" s="1">
         <v>4001</v>
       </c>
-      <c r="L100" s="1">
+      <c r="L106" s="1">
         <v>1000000</v>
       </c>
-      <c r="M100" s="1">
+      <c r="M106" s="1">
         <f t="shared" si="13"/>
         <v>640000</v>
       </c>
-      <c r="N100" s="1">
+      <c r="N106" s="1">
         <v>4</v>
       </c>
-      <c r="O100" s="1">
+      <c r="O106" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="101" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C101" s="1">
+    <row r="107" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C107" s="1">
         <v>237</v>
       </c>
-      <c r="D101" s="1">
-        <v>5</v>
-      </c>
-      <c r="E101" s="1">
-        <v>0</v>
-      </c>
-      <c r="F101" s="1">
+      <c r="D107" s="1">
+        <v>5</v>
+      </c>
+      <c r="E107" s="1">
+        <v>0</v>
+      </c>
+      <c r="F107" s="1">
         <v>4000</v>
       </c>
-      <c r="G101" s="1">
+      <c r="G107" s="1">
         <f t="shared" si="12"/>
         <v>160</v>
       </c>
-      <c r="H101" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J101" s="1">
-        <v>5</v>
-      </c>
-      <c r="K101" s="1">
+      <c r="H107" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J107" s="1">
+        <v>5</v>
+      </c>
+      <c r="K107" s="1">
         <v>4002</v>
       </c>
-      <c r="L101" s="1">
+      <c r="L107" s="1">
         <v>6000000</v>
       </c>
-      <c r="M101" s="1">
+      <c r="M107" s="1">
         <f t="shared" si="13"/>
         <v>640000</v>
       </c>
-      <c r="N101" s="1">
+      <c r="N107" s="1">
         <v>4</v>
       </c>
-      <c r="O101" s="1">
+      <c r="O107" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="102" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C102" s="1">
+    <row r="108" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C108" s="1">
         <v>238</v>
       </c>
-      <c r="D102" s="1">
-        <v>5</v>
-      </c>
-      <c r="E102" s="1">
+      <c r="D108" s="1">
+        <v>5</v>
+      </c>
+      <c r="E108" s="1">
         <v>6</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F108" s="1">
         <v>30000</v>
       </c>
-      <c r="G102" s="1">
+      <c r="G108" s="1">
         <f t="shared" si="12"/>
         <v>5</v>
       </c>
-      <c r="H102" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J102" s="1">
-        <v>5</v>
-      </c>
-      <c r="K102" s="1">
+      <c r="H108" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="J108" s="1">
+        <v>5</v>
+      </c>
+      <c r="K108" s="1">
         <v>4026</v>
       </c>
-      <c r="L102" s="1">
-        <v>1</v>
-      </c>
-      <c r="M102" s="1">
+      <c r="L108" s="1">
+        <v>1</v>
+      </c>
+      <c r="M108" s="1">
         <f t="shared" si="13"/>
         <v>150000</v>
       </c>
-      <c r="N102" s="1">
-        <v>1</v>
-      </c>
-      <c r="O102" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="104" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C104" s="1">
+      <c r="N108" s="1">
+        <v>1</v>
+      </c>
+      <c r="O108" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C110" s="1">
         <v>999</v>
       </c>
-      <c r="D104" s="1">
-        <v>0</v>
-      </c>
-      <c r="E104" s="1">
-        <v>0</v>
-      </c>
-      <c r="F104" s="1">
+      <c r="D110" s="1">
+        <v>0</v>
+      </c>
+      <c r="E110" s="1">
+        <v>0</v>
+      </c>
+      <c r="F110" s="1">
         <v>1000</v>
       </c>
-      <c r="G104" s="1">
+      <c r="G110" s="1">
         <v>50</v>
       </c>
-      <c r="H104" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J104" s="1">
-        <v>5</v>
-      </c>
-      <c r="K104" s="1">
+      <c r="H110" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J110" s="1">
+        <v>5</v>
+      </c>
+      <c r="K110" s="1">
         <v>4006</v>
       </c>
-      <c r="L104" s="1">
+      <c r="L110" s="1">
         <v>1000</v>
       </c>
-      <c r="M104" s="1">
-        <f t="shared" ref="M104:M106" si="14">F104*G104</f>
+      <c r="M110" s="1">
+        <f t="shared" ref="M110:M112" si="14">F110*G110</f>
         <v>50000</v>
       </c>
     </row>
-    <row r="105" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C105" s="1">
+    <row r="111" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C111" s="1">
         <v>1000</v>
       </c>
-      <c r="D105" s="1">
-        <v>0</v>
-      </c>
-      <c r="E105" s="1">
-        <v>0</v>
-      </c>
-      <c r="F105" s="1">
+      <c r="D111" s="1">
+        <v>0</v>
+      </c>
+      <c r="E111" s="1">
+        <v>0</v>
+      </c>
+      <c r="F111" s="1">
         <v>2000</v>
       </c>
-      <c r="G105" s="1">
+      <c r="G111" s="1">
         <v>100</v>
       </c>
-      <c r="H105" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J105" s="1">
-        <v>5</v>
-      </c>
-      <c r="K105" s="1">
+      <c r="H111" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J111" s="1">
+        <v>5</v>
+      </c>
+      <c r="K111" s="1">
         <v>4010</v>
       </c>
-      <c r="L105" s="1">
-        <v>5</v>
-      </c>
-      <c r="M105" s="1">
+      <c r="L111" s="1">
+        <v>5</v>
+      </c>
+      <c r="M111" s="1">
         <f t="shared" si="14"/>
         <v>200000</v>
       </c>
     </row>
-    <row r="106" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C106" s="1">
+    <row r="112" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C112" s="1">
         <v>1001</v>
       </c>
-      <c r="D106" s="1">
-        <v>0</v>
-      </c>
-      <c r="E106" s="1">
-        <v>0</v>
-      </c>
-      <c r="F106" s="1">
+      <c r="D112" s="1">
+        <v>0</v>
+      </c>
+      <c r="E112" s="1">
+        <v>0</v>
+      </c>
+      <c r="F112" s="1">
         <v>2000</v>
       </c>
-      <c r="G106" s="1">
+      <c r="G112" s="1">
         <v>50</v>
       </c>
-      <c r="H106" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J106" s="1">
-        <v>5</v>
-      </c>
-      <c r="K106" s="1">
+      <c r="H112" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J112" s="1">
+        <v>5</v>
+      </c>
+      <c r="K112" s="1">
         <v>4102</v>
       </c>
-      <c r="L106" s="1">
+      <c r="L112" s="1">
         <v>20</v>
       </c>
-      <c r="M106" s="1">
+      <c r="M112" s="1">
         <f t="shared" si="14"/>
         <v>100000</v>
       </c>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -1635,7 +1635,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="1">
-        <v>168</v>
+        <v>268</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>14</v>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="M6" s="1">
         <f t="shared" ref="M6:M14" si="0">F6*G6</f>
-        <v>50400</v>
+        <v>80400</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:13">
@@ -1671,7 +1671,7 @@
         <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>168</v>
+        <v>268</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>16</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="M7" s="1">
         <f t="shared" si="0"/>
-        <v>50400</v>
+        <v>80400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1707,7 +1707,7 @@
         <v>13</v>
       </c>
       <c r="G8" s="1">
-        <v>168</v>
+        <v>268</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>18</v>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="M8" s="1">
         <f t="shared" si="0"/>
-        <v>50400</v>
+        <v>80400</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:13">
@@ -1743,7 +1743,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="1">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>21</v>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="M9" s="1">
         <f t="shared" si="0"/>
-        <v>33000</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:13">
@@ -3108,10 +3108,10 @@
         <v>4</v>
       </c>
       <c r="F47" s="1">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G47" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>107</v>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="M47" s="1">
         <f t="shared" si="3"/>
-        <v>300000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:13">
@@ -3144,10 +3144,10 @@
         <v>4</v>
       </c>
       <c r="F48" s="1">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="G48" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>109</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="M48" s="1">
         <f t="shared" si="3"/>
-        <v>320000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="49" customFormat="1" customHeight="1" spans="3:15">
@@ -3180,10 +3180,10 @@
         <v>4</v>
       </c>
       <c r="F49" s="1">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="G49" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>111</v>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="M49" s="1">
         <f t="shared" si="3"/>
-        <v>320000</v>
+        <v>500000</v>
       </c>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
@@ -3218,10 +3218,10 @@
         <v>4</v>
       </c>
       <c r="F50" s="1">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="G50" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>113</v>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="M50" s="1">
         <f t="shared" si="3"/>
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
@@ -3256,10 +3256,10 @@
         <v>4</v>
       </c>
       <c r="F51" s="1">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="G51" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>115</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="M51" s="1">
         <f t="shared" si="3"/>
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
@@ -3294,10 +3294,10 @@
         <v>4</v>
       </c>
       <c r="F52" s="1">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G52" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>117</v>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="M52" s="1">
         <f t="shared" si="3"/>
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
@@ -3332,10 +3332,10 @@
         <v>4</v>
       </c>
       <c r="F53" s="1">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G53" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>119</v>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="M53" s="1">
         <f t="shared" si="3"/>
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
@@ -3370,10 +3370,10 @@
         <v>4</v>
       </c>
       <c r="F54" s="1">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G54" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="H54" s="4" t="s">
         <v>121</v>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="M54" s="1">
         <f t="shared" si="3"/>
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
@@ -3408,10 +3408,10 @@
         <v>4</v>
       </c>
       <c r="F55" s="1">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G55" s="1">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>123</v>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="M55" s="1">
         <f t="shared" si="3"/>
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
@@ -3446,10 +3446,10 @@
         <v>4</v>
       </c>
       <c r="F56" s="1">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G56" s="1">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>125</v>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="M56" s="1">
         <f t="shared" si="3"/>
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
@@ -3538,7 +3538,7 @@
         <v>100000</v>
       </c>
       <c r="G59" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>129</v>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="M59" s="1">
         <f>F59*G59</f>
-        <v>400000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -5426,7 +5426,7 @@
         <v>2000</v>
       </c>
       <c r="G111" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>150</v>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="M111" s="1">
         <f t="shared" si="14"/>
-        <v>200000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" customHeight="1" spans="3:13">

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="156">
   <si>
     <t>#</t>
   </si>
@@ -423,6 +423,12 @@
   </si>
   <si>
     <t>超级书页</t>
+  </si>
+  <si>
+    <t>行气丹*500</t>
+  </si>
+  <si>
+    <t>行气丹</t>
   </si>
   <si>
     <t>兑换四格碎片*1000</t>
@@ -3556,7 +3562,7 @@
         <v>1</v>
       </c>
       <c r="M59" s="1">
-        <f>F59*G59</f>
+        <f t="shared" ref="M59:M61" si="4">F59*G59</f>
         <v>600000</v>
       </c>
     </row>
@@ -3592,24 +3598,45 @@
         <v>1</v>
       </c>
       <c r="M60" s="1">
-        <f>F60*G60</f>
+        <f t="shared" si="4"/>
         <v>150000</v>
       </c>
     </row>
-    <row r="61" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
-      <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C61" s="1">
+        <v>55</v>
+      </c>
+      <c r="D61" s="1">
+        <v>0</v>
+      </c>
+      <c r="E61" s="1">
+        <v>10</v>
+      </c>
+      <c r="F61" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G61" s="1">
+        <v>20</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J61" s="1">
+        <v>5</v>
+      </c>
+      <c r="K61" s="1">
+        <v>4033</v>
+      </c>
+      <c r="L61" s="1">
+        <v>500</v>
+      </c>
+      <c r="M61" s="1">
+        <f t="shared" si="4"/>
+        <v>2000000</v>
+      </c>
     </row>
     <row r="62" customFormat="1" customHeight="1" spans="3:15">
       <c r="C62" s="1"/>
@@ -3670,14 +3697,14 @@
         <v>100</v>
       </c>
       <c r="G65" s="1">
-        <f t="shared" ref="G65:G72" si="4">N65*O65</f>
+        <f t="shared" ref="G65:G72" si="5">N65*O65</f>
         <v>300</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J65" s="1">
         <v>5</v>
@@ -3689,7 +3716,7 @@
         <v>1000</v>
       </c>
       <c r="M65" s="1">
-        <f t="shared" ref="M65:M72" si="5">F65*G65</f>
+        <f t="shared" ref="M65:M72" si="6">F65*G65</f>
         <v>30000</v>
       </c>
       <c r="N65" s="1">
@@ -3713,14 +3740,14 @@
         <v>100</v>
       </c>
       <c r="G66" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>500</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J66" s="1">
         <v>5</v>
@@ -3732,7 +3759,7 @@
         <v>1000</v>
       </c>
       <c r="M66" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>50000</v>
       </c>
       <c r="N66" s="1">
@@ -3756,14 +3783,14 @@
         <v>1000</v>
       </c>
       <c r="G67" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J67" s="1">
         <v>15</v>
@@ -3775,7 +3802,7 @@
         <v>100</v>
       </c>
       <c r="M67" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6000</v>
       </c>
       <c r="N67" s="1">
@@ -3799,14 +3826,14 @@
         <v>500</v>
       </c>
       <c r="G68" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J68" s="1">
         <v>5</v>
@@ -3818,7 +3845,7 @@
         <v>200</v>
       </c>
       <c r="M68" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10000</v>
       </c>
       <c r="N68" s="1">
@@ -3842,14 +3869,14 @@
         <v>15000</v>
       </c>
       <c r="G69" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J69" s="1">
         <v>5</v>
@@ -3861,7 +3888,7 @@
         <v>1</v>
       </c>
       <c r="M69" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>120000</v>
       </c>
       <c r="N69" s="1">
@@ -3885,14 +3912,14 @@
         <v>500</v>
       </c>
       <c r="G70" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J70" s="1">
         <v>5</v>
@@ -3904,7 +3931,7 @@
         <v>1000000</v>
       </c>
       <c r="M70" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>20000</v>
       </c>
       <c r="N70" s="1">
@@ -3928,14 +3955,14 @@
         <v>500</v>
       </c>
       <c r="G71" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J71" s="1">
         <v>5</v>
@@ -3947,7 +3974,7 @@
         <v>6000000</v>
       </c>
       <c r="M71" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>20000</v>
       </c>
       <c r="N71" s="1">
@@ -3971,14 +3998,14 @@
         <v>30000</v>
       </c>
       <c r="G72" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J72" s="1">
         <v>5</v>
@@ -3990,7 +4017,7 @@
         <v>1</v>
       </c>
       <c r="M72" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>150000</v>
       </c>
       <c r="N72" s="1">
@@ -4014,14 +4041,14 @@
         <v>200</v>
       </c>
       <c r="G74" s="1">
-        <f t="shared" ref="G74:G81" si="6">N74*O74</f>
+        <f t="shared" ref="G74:G81" si="7">N74*O74</f>
         <v>300</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J74" s="1">
         <v>5</v>
@@ -4033,7 +4060,7 @@
         <v>1000</v>
       </c>
       <c r="M74" s="1">
-        <f t="shared" ref="M74:M81" si="7">F74*G74</f>
+        <f t="shared" ref="M74:M81" si="8">F74*G74</f>
         <v>60000</v>
       </c>
       <c r="N74" s="1">
@@ -4057,14 +4084,14 @@
         <v>200</v>
       </c>
       <c r="G75" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>500</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J75" s="1">
         <v>5</v>
@@ -4076,7 +4103,7 @@
         <v>1000</v>
       </c>
       <c r="M75" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>100000</v>
       </c>
       <c r="N75" s="1">
@@ -4100,14 +4127,14 @@
         <v>2000</v>
       </c>
       <c r="G76" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J76" s="1">
         <v>15</v>
@@ -4119,7 +4146,7 @@
         <v>100</v>
       </c>
       <c r="M76" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>12000</v>
       </c>
       <c r="N76" s="1">
@@ -4143,14 +4170,14 @@
         <v>1000</v>
       </c>
       <c r="G77" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J77" s="1">
         <v>5</v>
@@ -4162,7 +4189,7 @@
         <v>200</v>
       </c>
       <c r="M77" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>20000</v>
       </c>
       <c r="N77" s="1">
@@ -4186,14 +4213,14 @@
         <v>30000</v>
       </c>
       <c r="G78" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J78" s="1">
         <v>5</v>
@@ -4205,7 +4232,7 @@
         <v>1</v>
       </c>
       <c r="M78" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>240000</v>
       </c>
       <c r="N78" s="1">
@@ -4229,14 +4256,14 @@
         <v>1000</v>
       </c>
       <c r="G79" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>40</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J79" s="1">
         <v>5</v>
@@ -4248,7 +4275,7 @@
         <v>1000000</v>
       </c>
       <c r="M79" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>40000</v>
       </c>
       <c r="N79" s="1">
@@ -4272,14 +4299,14 @@
         <v>1000</v>
       </c>
       <c r="G80" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>40</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J80" s="1">
         <v>5</v>
@@ -4291,7 +4318,7 @@
         <v>6000000</v>
       </c>
       <c r="M80" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>40000</v>
       </c>
       <c r="N80" s="1">
@@ -4315,14 +4342,14 @@
         <v>30000</v>
       </c>
       <c r="G81" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J81" s="1">
         <v>5</v>
@@ -4334,7 +4361,7 @@
         <v>1</v>
       </c>
       <c r="M81" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>150000</v>
       </c>
       <c r="N81" s="1">
@@ -4358,14 +4385,14 @@
         <v>400</v>
       </c>
       <c r="G83" s="1">
-        <f t="shared" ref="G83:G90" si="8">N83*O83</f>
+        <f t="shared" ref="G83:G90" si="9">N83*O83</f>
         <v>300</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J83" s="1">
         <v>5</v>
@@ -4377,7 +4404,7 @@
         <v>1000</v>
       </c>
       <c r="M83" s="1">
-        <f t="shared" ref="M83:M90" si="9">F83*G83</f>
+        <f t="shared" ref="M83:M90" si="10">F83*G83</f>
         <v>120000</v>
       </c>
       <c r="N83" s="1">
@@ -4401,14 +4428,14 @@
         <v>400</v>
       </c>
       <c r="G84" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>500</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J84" s="1">
         <v>5</v>
@@ -4420,7 +4447,7 @@
         <v>1000</v>
       </c>
       <c r="M84" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>200000</v>
       </c>
       <c r="N84" s="1">
@@ -4444,14 +4471,14 @@
         <v>4000</v>
       </c>
       <c r="G85" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J85" s="1">
         <v>15</v>
@@ -4463,7 +4490,7 @@
         <v>100</v>
       </c>
       <c r="M85" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>24000</v>
       </c>
       <c r="N85" s="1">
@@ -4487,14 +4514,14 @@
         <v>2000</v>
       </c>
       <c r="G86" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J86" s="1">
         <v>5</v>
@@ -4506,7 +4533,7 @@
         <v>200</v>
       </c>
       <c r="M86" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>40000</v>
       </c>
       <c r="N86" s="1">
@@ -4530,14 +4557,14 @@
         <v>45000</v>
       </c>
       <c r="G87" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J87" s="1">
         <v>5</v>
@@ -4549,7 +4576,7 @@
         <v>1</v>
       </c>
       <c r="M87" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>360000</v>
       </c>
       <c r="N87" s="1">
@@ -4573,14 +4600,14 @@
         <v>2000</v>
       </c>
       <c r="G88" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J88" s="1">
         <v>5</v>
@@ -4592,7 +4619,7 @@
         <v>1000000</v>
       </c>
       <c r="M88" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>80000</v>
       </c>
       <c r="N88" s="1">
@@ -4616,14 +4643,14 @@
         <v>2000</v>
       </c>
       <c r="G89" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>40</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J89" s="1">
         <v>5</v>
@@ -4635,7 +4662,7 @@
         <v>6000000</v>
       </c>
       <c r="M89" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>80000</v>
       </c>
       <c r="N89" s="1">
@@ -4659,14 +4686,14 @@
         <v>30000</v>
       </c>
       <c r="G90" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J90" s="1">
         <v>5</v>
@@ -4678,7 +4705,7 @@
         <v>1</v>
       </c>
       <c r="M90" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>150000</v>
       </c>
       <c r="N90" s="1">
@@ -4702,14 +4729,14 @@
         <v>600</v>
       </c>
       <c r="G92" s="1">
-        <f t="shared" ref="G92:G99" si="10">N92*O92</f>
+        <f t="shared" ref="G92:G99" si="11">N92*O92</f>
         <v>300</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J92" s="1">
         <v>5</v>
@@ -4721,7 +4748,7 @@
         <v>1000</v>
       </c>
       <c r="M92" s="1">
-        <f t="shared" ref="M92:M99" si="11">F92*G92</f>
+        <f t="shared" ref="M92:M99" si="12">F92*G92</f>
         <v>180000</v>
       </c>
       <c r="N92" s="1">
@@ -4745,14 +4772,14 @@
         <v>600</v>
       </c>
       <c r="G93" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>500</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J93" s="1">
         <v>5</v>
@@ -4764,7 +4791,7 @@
         <v>1000</v>
       </c>
       <c r="M93" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>300000</v>
       </c>
       <c r="N93" s="1">
@@ -4788,14 +4815,14 @@
         <v>6000</v>
       </c>
       <c r="G94" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J94" s="1">
         <v>15</v>
@@ -4807,7 +4834,7 @@
         <v>100</v>
       </c>
       <c r="M94" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>36000</v>
       </c>
       <c r="N94" s="1">
@@ -4831,14 +4858,14 @@
         <v>3000</v>
       </c>
       <c r="G95" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>20</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J95" s="1">
         <v>5</v>
@@ -4850,7 +4877,7 @@
         <v>200</v>
       </c>
       <c r="M95" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>60000</v>
       </c>
       <c r="N95" s="1">
@@ -4874,14 +4901,14 @@
         <v>60000</v>
       </c>
       <c r="G96" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J96" s="1">
         <v>5</v>
@@ -4893,7 +4920,7 @@
         <v>1</v>
       </c>
       <c r="M96" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>480000</v>
       </c>
       <c r="N96" s="1">
@@ -4917,14 +4944,14 @@
         <v>3000</v>
       </c>
       <c r="G97" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J97" s="1">
         <v>5</v>
@@ -4936,7 +4963,7 @@
         <v>1000000</v>
       </c>
       <c r="M97" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>120000</v>
       </c>
       <c r="N97" s="1">
@@ -4960,14 +4987,14 @@
         <v>3000</v>
       </c>
       <c r="G98" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J98" s="1">
         <v>5</v>
@@ -4979,7 +5006,7 @@
         <v>6000000</v>
       </c>
       <c r="M98" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>120000</v>
       </c>
       <c r="N98" s="1">
@@ -5003,14 +5030,14 @@
         <v>30000</v>
       </c>
       <c r="G99" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J99" s="1">
         <v>5</v>
@@ -5022,7 +5049,7 @@
         <v>1</v>
       </c>
       <c r="M99" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>150000</v>
       </c>
       <c r="N99" s="1">
@@ -5046,14 +5073,14 @@
         <v>800</v>
       </c>
       <c r="G101" s="1">
-        <f t="shared" ref="G101:G108" si="12">N101*O101</f>
+        <f t="shared" ref="G101:G108" si="13">N101*O101</f>
         <v>1200</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J101" s="1">
         <v>5</v>
@@ -5065,7 +5092,7 @@
         <v>1000</v>
       </c>
       <c r="M101" s="1">
-        <f t="shared" ref="M101:M108" si="13">F101*G101</f>
+        <f t="shared" ref="M101:M108" si="14">F101*G101</f>
         <v>960000</v>
       </c>
       <c r="N101" s="1">
@@ -5089,14 +5116,14 @@
         <v>800</v>
       </c>
       <c r="G102" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2000</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J102" s="1">
         <v>5</v>
@@ -5108,7 +5135,7 @@
         <v>1000</v>
       </c>
       <c r="M102" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1600000</v>
       </c>
       <c r="N102" s="1">
@@ -5132,14 +5159,14 @@
         <v>8000</v>
       </c>
       <c r="G103" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>24</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J103" s="1">
         <v>15</v>
@@ -5151,7 +5178,7 @@
         <v>100</v>
       </c>
       <c r="M103" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>192000</v>
       </c>
       <c r="N103" s="1">
@@ -5175,14 +5202,14 @@
         <v>4000</v>
       </c>
       <c r="G104" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>80</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J104" s="1">
         <v>5</v>
@@ -5194,7 +5221,7 @@
         <v>200</v>
       </c>
       <c r="M104" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>320000</v>
       </c>
       <c r="N104" s="1">
@@ -5218,14 +5245,14 @@
         <v>75000</v>
       </c>
       <c r="G105" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>32</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J105" s="1">
         <v>5</v>
@@ -5237,7 +5264,7 @@
         <v>1</v>
       </c>
       <c r="M105" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2400000</v>
       </c>
       <c r="N105" s="1">
@@ -5261,14 +5288,14 @@
         <v>4000</v>
       </c>
       <c r="G106" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>160</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J106" s="1">
         <v>5</v>
@@ -5280,7 +5307,7 @@
         <v>1000000</v>
       </c>
       <c r="M106" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>640000</v>
       </c>
       <c r="N106" s="1">
@@ -5304,14 +5331,14 @@
         <v>4000</v>
       </c>
       <c r="G107" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>160</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J107" s="1">
         <v>5</v>
@@ -5323,7 +5350,7 @@
         <v>6000000</v>
       </c>
       <c r="M107" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>640000</v>
       </c>
       <c r="N107" s="1">
@@ -5347,14 +5374,14 @@
         <v>30000</v>
       </c>
       <c r="G108" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J108" s="1">
         <v>5</v>
@@ -5366,7 +5393,7 @@
         <v>1</v>
       </c>
       <c r="M108" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>150000</v>
       </c>
       <c r="N108" s="1">
@@ -5393,10 +5420,10 @@
         <v>50</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J110" s="1">
         <v>5</v>
@@ -5408,7 +5435,7 @@
         <v>1000</v>
       </c>
       <c r="M110" s="1">
-        <f t="shared" ref="M110:M112" si="14">F110*G110</f>
+        <f t="shared" ref="M110:M112" si="15">F110*G110</f>
         <v>50000</v>
       </c>
     </row>
@@ -5429,10 +5456,10 @@
         <v>1000</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J111" s="1">
         <v>5</v>
@@ -5444,7 +5471,7 @@
         <v>5</v>
       </c>
       <c r="M111" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2000000</v>
       </c>
     </row>
@@ -5465,10 +5492,10 @@
         <v>50</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J112" s="1">
         <v>5</v>
@@ -5480,7 +5507,7 @@
         <v>20</v>
       </c>
       <c r="M112" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>100000</v>
       </c>
     </row>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="157">
   <si>
     <t>#</t>
   </si>
@@ -429,6 +429,9 @@
   </si>
   <si>
     <t>行气丹</t>
+  </si>
+  <si>
+    <t>11技能自选</t>
   </si>
   <si>
     <t>兑换四格碎片*1000</t>
@@ -530,15 +533,15 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1526,12 +1529,12 @@
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="13:13">
+    <row r="1" customHeight="1" spans="3:13">
       <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1563,7 +1566,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1595,7 +1598,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
@@ -1904,7 +1907,7 @@
       <c r="J13" s="1">
         <v>4</v>
       </c>
-      <c r="K13" s="5">
+      <c r="K13" s="4">
         <v>15</v>
       </c>
       <c r="L13" s="1">
@@ -1940,7 +1943,7 @@
       <c r="J14" s="1">
         <v>4</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="4">
         <v>16</v>
       </c>
       <c r="L14" s="1">
@@ -1976,7 +1979,7 @@
       <c r="J15" s="1">
         <v>4</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15" s="4">
         <v>17</v>
       </c>
       <c r="L15" s="1">
@@ -3128,7 +3131,7 @@
       <c r="J47" s="1">
         <v>5</v>
       </c>
-      <c r="K47" s="5">
+      <c r="K47" s="4">
         <v>60000001</v>
       </c>
       <c r="L47" s="1">
@@ -3164,7 +3167,7 @@
       <c r="J48" s="1">
         <v>5</v>
       </c>
-      <c r="K48" s="5">
+      <c r="K48" s="4">
         <v>60000002</v>
       </c>
       <c r="L48" s="1">
@@ -3200,7 +3203,7 @@
       <c r="J49" s="1">
         <v>5</v>
       </c>
-      <c r="K49" s="5">
+      <c r="K49" s="4">
         <v>60000003</v>
       </c>
       <c r="L49" s="1">
@@ -3238,7 +3241,7 @@
       <c r="J50" s="1">
         <v>5</v>
       </c>
-      <c r="K50" s="5">
+      <c r="K50" s="4">
         <v>60000004</v>
       </c>
       <c r="L50" s="1">
@@ -3276,7 +3279,7 @@
       <c r="J51" s="1">
         <v>5</v>
       </c>
-      <c r="K51" s="5">
+      <c r="K51" s="4">
         <v>60000005</v>
       </c>
       <c r="L51" s="1">
@@ -3314,7 +3317,7 @@
       <c r="J52" s="1">
         <v>5</v>
       </c>
-      <c r="K52" s="5">
+      <c r="K52" s="4">
         <v>60000006</v>
       </c>
       <c r="L52" s="1">
@@ -3352,7 +3355,7 @@
       <c r="J53" s="1">
         <v>5</v>
       </c>
-      <c r="K53" s="5">
+      <c r="K53" s="4">
         <v>60000007</v>
       </c>
       <c r="L53" s="1">
@@ -3381,16 +3384,16 @@
       <c r="G54" s="1">
         <v>100</v>
       </c>
-      <c r="H54" s="4" t="s">
+      <c r="H54" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="I54" s="4" t="s">
+      <c r="I54" s="5" t="s">
         <v>122</v>
       </c>
       <c r="J54" s="1">
         <v>5</v>
       </c>
-      <c r="K54" s="5">
+      <c r="K54" s="4">
         <v>60000008</v>
       </c>
       <c r="L54" s="1">
@@ -3428,7 +3431,7 @@
       <c r="J55" s="1">
         <v>5</v>
       </c>
-      <c r="K55" s="5">
+      <c r="K55" s="4">
         <v>60000009</v>
       </c>
       <c r="L55" s="1">
@@ -3466,7 +3469,7 @@
       <c r="J56" s="1">
         <v>5</v>
       </c>
-      <c r="K56" s="5">
+      <c r="K56" s="4">
         <v>60000010</v>
       </c>
       <c r="L56" s="1">
@@ -3479,7 +3482,7 @@
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
     </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:13">
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C57" s="1">
         <v>52</v>
       </c>
@@ -3530,7 +3533,7 @@
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:13">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C59" s="1">
         <v>53</v>
       </c>
@@ -3562,11 +3565,11 @@
         <v>1</v>
       </c>
       <c r="M59" s="1">
-        <f t="shared" ref="M59:M61" si="4">F59*G59</f>
+        <f t="shared" ref="M59:M62" si="4">F59*G59</f>
         <v>600000</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:13">
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C60" s="1">
         <v>54</v>
       </c>
@@ -3580,7 +3583,7 @@
         <v>150000</v>
       </c>
       <c r="G60" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>131</v>
@@ -3599,10 +3602,10 @@
       </c>
       <c r="M60" s="1">
         <f t="shared" si="4"/>
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C61" s="1">
         <v>55</v>
       </c>
@@ -3638,20 +3641,41 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="62" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C62" s="1">
+        <v>56</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0</v>
+      </c>
+      <c r="E62" s="1">
+        <v>15</v>
+      </c>
+      <c r="F62" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="G62" s="1">
+        <v>3</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J62" s="1">
+        <v>4</v>
+      </c>
+      <c r="K62" s="1">
+        <v>29</v>
+      </c>
+      <c r="L62" s="1">
+        <v>1</v>
+      </c>
+      <c r="M62" s="1">
+        <f t="shared" si="4"/>
+        <v>3000000</v>
+      </c>
     </row>
     <row r="63" customFormat="1" customHeight="1" spans="3:15">
       <c r="C63" s="1"/>
@@ -3701,10 +3725,10 @@
         <v>300</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J65" s="1">
         <v>5</v>
@@ -3744,10 +3768,10 @@
         <v>500</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J66" s="1">
         <v>5</v>
@@ -3787,10 +3811,10 @@
         <v>6</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J67" s="1">
         <v>15</v>
@@ -3830,10 +3854,10 @@
         <v>20</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J68" s="1">
         <v>5</v>
@@ -3873,10 +3897,10 @@
         <v>8</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J69" s="1">
         <v>5</v>
@@ -3916,10 +3940,10 @@
         <v>40</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J70" s="1">
         <v>5</v>
@@ -3959,10 +3983,10 @@
         <v>40</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J71" s="1">
         <v>5</v>
@@ -4002,10 +4026,10 @@
         <v>5</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J72" s="1">
         <v>5</v>
@@ -4045,10 +4069,10 @@
         <v>300</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J74" s="1">
         <v>5</v>
@@ -4088,10 +4112,10 @@
         <v>500</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J75" s="1">
         <v>5</v>
@@ -4131,10 +4155,10 @@
         <v>6</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J76" s="1">
         <v>15</v>
@@ -4174,10 +4198,10 @@
         <v>20</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J77" s="1">
         <v>5</v>
@@ -4217,10 +4241,10 @@
         <v>8</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J78" s="1">
         <v>5</v>
@@ -4260,10 +4284,10 @@
         <v>40</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J79" s="1">
         <v>5</v>
@@ -4303,10 +4327,10 @@
         <v>40</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J80" s="1">
         <v>5</v>
@@ -4346,10 +4370,10 @@
         <v>5</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J81" s="1">
         <v>5</v>
@@ -4389,10 +4413,10 @@
         <v>300</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J83" s="1">
         <v>5</v>
@@ -4432,10 +4456,10 @@
         <v>500</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J84" s="1">
         <v>5</v>
@@ -4475,10 +4499,10 @@
         <v>6</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J85" s="1">
         <v>15</v>
@@ -4518,10 +4542,10 @@
         <v>20</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J86" s="1">
         <v>5</v>
@@ -4561,10 +4585,10 @@
         <v>8</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J87" s="1">
         <v>5</v>
@@ -4604,10 +4628,10 @@
         <v>40</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J88" s="1">
         <v>5</v>
@@ -4647,10 +4671,10 @@
         <v>40</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J89" s="1">
         <v>5</v>
@@ -4690,10 +4714,10 @@
         <v>5</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J90" s="1">
         <v>5</v>
@@ -4733,10 +4757,10 @@
         <v>300</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J92" s="1">
         <v>5</v>
@@ -4776,10 +4800,10 @@
         <v>500</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J93" s="1">
         <v>5</v>
@@ -4819,10 +4843,10 @@
         <v>6</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J94" s="1">
         <v>15</v>
@@ -4862,10 +4886,10 @@
         <v>20</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J95" s="1">
         <v>5</v>
@@ -4905,10 +4929,10 @@
         <v>8</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J96" s="1">
         <v>5</v>
@@ -4948,10 +4972,10 @@
         <v>40</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J97" s="1">
         <v>5</v>
@@ -4991,10 +5015,10 @@
         <v>40</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J98" s="1">
         <v>5</v>
@@ -5034,10 +5058,10 @@
         <v>5</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J99" s="1">
         <v>5</v>
@@ -5077,10 +5101,10 @@
         <v>1200</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J101" s="1">
         <v>5</v>
@@ -5120,10 +5144,10 @@
         <v>2000</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J102" s="1">
         <v>5</v>
@@ -5163,10 +5187,10 @@
         <v>24</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J103" s="1">
         <v>15</v>
@@ -5206,10 +5230,10 @@
         <v>80</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J104" s="1">
         <v>5</v>
@@ -5249,10 +5273,10 @@
         <v>32</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J105" s="1">
         <v>5</v>
@@ -5292,10 +5316,10 @@
         <v>160</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J106" s="1">
         <v>5</v>
@@ -5335,10 +5359,10 @@
         <v>160</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J107" s="1">
         <v>5</v>
@@ -5378,10 +5402,10 @@
         <v>5</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J108" s="1">
         <v>5</v>
@@ -5403,7 +5427,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" s="1" customFormat="1" customHeight="1" spans="3:13">
+    <row r="110" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C110" s="1">
         <v>999</v>
       </c>
@@ -5420,10 +5444,10 @@
         <v>50</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J110" s="1">
         <v>5</v>
@@ -5439,7 +5463,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="111" s="1" customFormat="1" customHeight="1" spans="3:13">
+    <row r="111" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C111" s="1">
         <v>1000</v>
       </c>
@@ -5456,10 +5480,10 @@
         <v>1000</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J111" s="1">
         <v>5</v>
@@ -5475,7 +5499,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="112" s="1" customFormat="1" customHeight="1" spans="3:13">
+    <row r="112" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C112" s="1">
         <v>1001</v>
       </c>
@@ -5492,10 +5516,10 @@
         <v>50</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J112" s="1">
         <v>5</v>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -452,12 +452,6 @@
     <t>经验丹</t>
   </si>
   <si>
-    <t>兑换传世精华*200</t>
-  </si>
-  <si>
-    <t>传世精华</t>
-  </si>
-  <si>
     <t>兑换金装精华*1</t>
   </si>
   <si>
@@ -480,6 +474,12 @@
   </si>
   <si>
     <t>暗金精华</t>
+  </si>
+  <si>
+    <t>兑换传奇精华</t>
+  </si>
+  <si>
+    <t>传奇精华</t>
   </si>
   <si>
     <t>兑换书页1000个</t>
@@ -1514,7 +1514,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O112"/>
+  <dimension ref="C1:O113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -3117,10 +3117,10 @@
         <v>4</v>
       </c>
       <c r="F47" s="1">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="G47" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>107</v>
@@ -3153,10 +3153,10 @@
         <v>4</v>
       </c>
       <c r="F48" s="1">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="G48" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>109</v>
@@ -3189,10 +3189,10 @@
         <v>4</v>
       </c>
       <c r="F49" s="1">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="G49" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>111</v>
@@ -3227,10 +3227,10 @@
         <v>4</v>
       </c>
       <c r="F50" s="1">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="G50" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>113</v>
@@ -3265,10 +3265,10 @@
         <v>4</v>
       </c>
       <c r="F51" s="1">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="G51" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>115</v>
@@ -3303,10 +3303,10 @@
         <v>4</v>
       </c>
       <c r="F52" s="1">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="G52" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>117</v>
@@ -3341,10 +3341,10 @@
         <v>4</v>
       </c>
       <c r="F53" s="1">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="G53" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>119</v>
@@ -3379,10 +3379,10 @@
         <v>4</v>
       </c>
       <c r="F54" s="1">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="G54" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H54" s="5" t="s">
         <v>121</v>
@@ -3417,10 +3417,10 @@
         <v>4</v>
       </c>
       <c r="F55" s="1">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="G55" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>123</v>
@@ -3455,10 +3455,10 @@
         <v>4</v>
       </c>
       <c r="F56" s="1">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="G56" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>125</v>
@@ -3547,7 +3547,7 @@
         <v>100000</v>
       </c>
       <c r="G59" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>129</v>
@@ -3565,8 +3565,8 @@
         <v>1</v>
       </c>
       <c r="M59" s="1">
-        <f t="shared" ref="M59:M62" si="4">F59*G59</f>
-        <v>600000</v>
+        <f>F59*G59</f>
+        <v>1000000</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -3601,7 +3601,7 @@
         <v>1</v>
       </c>
       <c r="M60" s="1">
-        <f t="shared" si="4"/>
+        <f>F60*G60</f>
         <v>300000</v>
       </c>
     </row>
@@ -3637,7 +3637,7 @@
         <v>500</v>
       </c>
       <c r="M61" s="1">
-        <f t="shared" si="4"/>
+        <f>F61*G61</f>
         <v>2000000</v>
       </c>
     </row>
@@ -3673,24 +3673,9 @@
         <v>1</v>
       </c>
       <c r="M62" s="1">
-        <f t="shared" si="4"/>
+        <f>F62*G62</f>
         <v>3000000</v>
       </c>
-    </row>
-    <row r="63" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="1"/>
-      <c r="M63" s="1"/>
-      <c r="N63" s="1"/>
-      <c r="O63" s="1"/>
     </row>
     <row r="64" customFormat="1" customHeight="1" spans="3:15">
       <c r="C64" s="1"/>
@@ -3707,52 +3692,24 @@
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
     </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C65" s="1">
-        <v>102</v>
-      </c>
-      <c r="D65" s="1">
-        <v>1</v>
-      </c>
-      <c r="E65" s="1">
-        <v>0</v>
-      </c>
-      <c r="F65" s="1">
-        <v>100</v>
-      </c>
-      <c r="G65" s="1">
-        <f t="shared" ref="G65:G72" si="5">N65*O65</f>
-        <v>300</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J65" s="1">
-        <v>5</v>
-      </c>
-      <c r="K65" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L65" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M65" s="1">
-        <f t="shared" ref="M65:M72" si="6">F65*G65</f>
-        <v>30000</v>
-      </c>
-      <c r="N65" s="1">
-        <v>1</v>
-      </c>
-      <c r="O65" s="1">
-        <v>300</v>
-      </c>
+    <row r="65" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C66" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D66" s="1">
         <v>1</v>
@@ -3764,38 +3721,38 @@
         <v>100</v>
       </c>
       <c r="G66" s="1">
-        <f t="shared" si="5"/>
-        <v>500</v>
+        <f>N66*O66</f>
+        <v>300</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J66" s="1">
         <v>5</v>
       </c>
       <c r="K66" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="L66" s="1">
         <v>1000</v>
       </c>
       <c r="M66" s="1">
-        <f t="shared" si="6"/>
-        <v>50000</v>
+        <f>F66*G66</f>
+        <v>30000</v>
       </c>
       <c r="N66" s="1">
         <v>1</v>
       </c>
       <c r="O66" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C67" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D67" s="1">
         <v>1</v>
@@ -3804,41 +3761,41 @@
         <v>0</v>
       </c>
       <c r="F67" s="1">
+        <v>100</v>
+      </c>
+      <c r="G67" s="1">
+        <f>N67*O67</f>
+        <v>500</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J67" s="1">
+        <v>5</v>
+      </c>
+      <c r="K67" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L67" s="1">
         <v>1000</v>
       </c>
-      <c r="G67" s="1">
-        <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J67" s="1">
-        <v>15</v>
-      </c>
-      <c r="K67" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L67" s="1">
-        <v>100</v>
-      </c>
       <c r="M67" s="1">
-        <f t="shared" si="6"/>
-        <v>6000</v>
+        <f>F67*G67</f>
+        <v>50000</v>
       </c>
       <c r="N67" s="1">
         <v>1</v>
       </c>
       <c r="O67" s="1">
-        <v>6</v>
+        <v>500</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C68" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D68" s="1">
         <v>1</v>
@@ -3847,30 +3804,30 @@
         <v>0</v>
       </c>
       <c r="F68" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G68" s="1">
-        <f t="shared" si="5"/>
+        <f>N68*O68</f>
         <v>20</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J68" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K68" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="L68" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M68" s="1">
-        <f t="shared" si="6"/>
-        <v>10000</v>
+        <f>F68*G68</f>
+        <v>20000</v>
       </c>
       <c r="N68" s="1">
         <v>1</v>
@@ -3881,7 +3838,7 @@
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C69" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D69" s="1">
         <v>1</v>
@@ -3893,14 +3850,14 @@
         <v>15000</v>
       </c>
       <c r="G69" s="1">
-        <f t="shared" si="5"/>
+        <f>N69*O69</f>
         <v>8</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J69" s="1">
         <v>5</v>
@@ -3912,7 +3869,7 @@
         <v>1</v>
       </c>
       <c r="M69" s="1">
-        <f t="shared" si="6"/>
+        <f>F69*G69</f>
         <v>120000</v>
       </c>
       <c r="N69" s="1">
@@ -3924,7 +3881,7 @@
     </row>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C70" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D70" s="1">
         <v>1</v>
@@ -3936,14 +3893,14 @@
         <v>500</v>
       </c>
       <c r="G70" s="1">
-        <f t="shared" si="5"/>
+        <f>N70*O70</f>
         <v>40</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J70" s="1">
         <v>5</v>
@@ -3955,7 +3912,7 @@
         <v>1000000</v>
       </c>
       <c r="M70" s="1">
-        <f t="shared" si="6"/>
+        <f>F70*G70</f>
         <v>20000</v>
       </c>
       <c r="N70" s="1">
@@ -3967,7 +3924,7 @@
     </row>
     <row r="71" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C71" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D71" s="1">
         <v>1</v>
@@ -3979,14 +3936,14 @@
         <v>500</v>
       </c>
       <c r="G71" s="1">
-        <f t="shared" si="5"/>
+        <f>N71*O71</f>
         <v>40</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J71" s="1">
         <v>5</v>
@@ -3998,7 +3955,7 @@
         <v>6000000</v>
       </c>
       <c r="M71" s="1">
-        <f t="shared" si="6"/>
+        <f>F71*G71</f>
         <v>20000</v>
       </c>
       <c r="N71" s="1">
@@ -4010,7 +3967,7 @@
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C72" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D72" s="1">
         <v>1</v>
@@ -4022,14 +3979,13 @@
         <v>30000</v>
       </c>
       <c r="G72" s="1">
-        <f t="shared" si="5"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J72" s="1">
         <v>5</v>
@@ -4041,8 +3997,8 @@
         <v>1</v>
       </c>
       <c r="M72" s="1">
-        <f t="shared" si="6"/>
-        <v>150000</v>
+        <f>F72*G72</f>
+        <v>300000</v>
       </c>
       <c r="N72" s="1">
         <v>1</v>
@@ -4051,52 +4007,60 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C74" s="1">
-        <v>201</v>
-      </c>
-      <c r="D74" s="1">
-        <v>2</v>
-      </c>
-      <c r="E74" s="1">
-        <v>0</v>
-      </c>
-      <c r="F74" s="6">
-        <v>200</v>
-      </c>
-      <c r="G74" s="1">
-        <f t="shared" ref="G74:G81" si="7">N74*O74</f>
-        <v>300</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J74" s="1">
-        <v>5</v>
-      </c>
-      <c r="K74" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L74" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M74" s="1">
-        <f t="shared" ref="M74:M81" si="8">F74*G74</f>
-        <v>60000</v>
-      </c>
-      <c r="N74" s="1">
-        <v>1</v>
-      </c>
-      <c r="O74" s="1">
-        <v>300</v>
-      </c>
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C73" s="1">
+        <v>109</v>
+      </c>
+      <c r="D73" s="1">
+        <v>1</v>
+      </c>
+      <c r="E73" s="1">
+        <v>10</v>
+      </c>
+      <c r="F73" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G73" s="1">
+        <v>10</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J73" s="1">
+        <v>5</v>
+      </c>
+      <c r="K73" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L73" s="1">
+        <v>1</v>
+      </c>
+      <c r="M73" s="1">
+        <f>F73*G73</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="74" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1"/>
+      <c r="N74" s="1"/>
+      <c r="O74" s="1"/>
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C75" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D75" s="1">
         <v>2</v>
@@ -4108,38 +4072,38 @@
         <v>200</v>
       </c>
       <c r="G75" s="1">
-        <f t="shared" si="7"/>
-        <v>500</v>
+        <f>N75*O75</f>
+        <v>300</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J75" s="1">
         <v>5</v>
       </c>
       <c r="K75" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="L75" s="1">
         <v>1000</v>
       </c>
       <c r="M75" s="1">
-        <f t="shared" si="8"/>
-        <v>100000</v>
+        <f>F75*G75</f>
+        <v>60000</v>
       </c>
       <c r="N75" s="1">
         <v>1</v>
       </c>
       <c r="O75" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C76" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D76" s="1">
         <v>2</v>
@@ -4148,41 +4112,41 @@
         <v>0</v>
       </c>
       <c r="F76" s="6">
-        <v>2000</v>
+        <v>200</v>
       </c>
       <c r="G76" s="1">
-        <f t="shared" si="7"/>
-        <v>6</v>
+        <f>N76*O76</f>
+        <v>500</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J76" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K76" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="L76" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="M76" s="1">
-        <f t="shared" si="8"/>
-        <v>12000</v>
+        <f>F76*G76</f>
+        <v>100000</v>
       </c>
       <c r="N76" s="1">
         <v>1</v>
       </c>
       <c r="O76" s="1">
-        <v>6</v>
+        <v>500</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C77" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D77" s="1">
         <v>2</v>
@@ -4191,30 +4155,30 @@
         <v>0</v>
       </c>
       <c r="F77" s="6">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G77" s="1">
-        <f t="shared" si="7"/>
+        <f>N77*O77</f>
         <v>20</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J77" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K77" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="L77" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M77" s="1">
-        <f t="shared" si="8"/>
-        <v>20000</v>
+        <f>F77*G77</f>
+        <v>40000</v>
       </c>
       <c r="N77" s="1">
         <v>1</v>
@@ -4225,7 +4189,7 @@
     </row>
     <row r="78" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C78" s="1">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D78" s="1">
         <v>2</v>
@@ -4237,14 +4201,14 @@
         <v>30000</v>
       </c>
       <c r="G78" s="1">
-        <f t="shared" si="7"/>
+        <f>N78*O78</f>
         <v>8</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J78" s="1">
         <v>5</v>
@@ -4256,7 +4220,7 @@
         <v>1</v>
       </c>
       <c r="M78" s="1">
-        <f t="shared" si="8"/>
+        <f>F78*G78</f>
         <v>240000</v>
       </c>
       <c r="N78" s="1">
@@ -4268,7 +4232,7 @@
     </row>
     <row r="79" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C79" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D79" s="1">
         <v>2</v>
@@ -4280,14 +4244,14 @@
         <v>1000</v>
       </c>
       <c r="G79" s="1">
-        <f t="shared" si="7"/>
+        <f>N79*O79</f>
         <v>40</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J79" s="1">
         <v>5</v>
@@ -4299,7 +4263,7 @@
         <v>1000000</v>
       </c>
       <c r="M79" s="1">
-        <f t="shared" si="8"/>
+        <f>F79*G79</f>
         <v>40000</v>
       </c>
       <c r="N79" s="1">
@@ -4311,7 +4275,7 @@
     </row>
     <row r="80" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C80" s="1">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D80" s="1">
         <v>2</v>
@@ -4323,14 +4287,14 @@
         <v>1000</v>
       </c>
       <c r="G80" s="1">
-        <f t="shared" si="7"/>
+        <f>N80*O80</f>
         <v>40</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J80" s="1">
         <v>5</v>
@@ -4342,7 +4306,7 @@
         <v>6000000</v>
       </c>
       <c r="M80" s="1">
-        <f t="shared" si="8"/>
+        <f>F80*G80</f>
         <v>40000</v>
       </c>
       <c r="N80" s="1">
@@ -4354,7 +4318,7 @@
     </row>
     <row r="81" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C81" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D81" s="1">
         <v>2</v>
@@ -4366,14 +4330,13 @@
         <v>30000</v>
       </c>
       <c r="G81" s="1">
-        <f t="shared" si="7"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J81" s="1">
         <v>5</v>
@@ -4385,8 +4348,8 @@
         <v>1</v>
       </c>
       <c r="M81" s="1">
-        <f t="shared" si="8"/>
-        <v>150000</v>
+        <f>F81*G81</f>
+        <v>300000</v>
       </c>
       <c r="N81" s="1">
         <v>1</v>
@@ -4395,52 +4358,60 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C83" s="1">
-        <v>211</v>
-      </c>
-      <c r="D83" s="1">
-        <v>3</v>
-      </c>
-      <c r="E83" s="1">
-        <v>0</v>
-      </c>
-      <c r="F83" s="1">
-        <v>400</v>
-      </c>
-      <c r="G83" s="1">
-        <f t="shared" ref="G83:G90" si="9">N83*O83</f>
-        <v>300</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J83" s="1">
-        <v>5</v>
-      </c>
-      <c r="K83" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L83" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M83" s="1">
-        <f t="shared" ref="M83:M90" si="10">F83*G83</f>
-        <v>120000</v>
-      </c>
-      <c r="N83" s="1">
-        <v>1</v>
-      </c>
-      <c r="O83" s="1">
-        <v>300</v>
-      </c>
+    <row r="82" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C82" s="1">
+        <v>208</v>
+      </c>
+      <c r="D82" s="1">
+        <v>2</v>
+      </c>
+      <c r="E82" s="1">
+        <v>10</v>
+      </c>
+      <c r="F82" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G82" s="1">
+        <v>10</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J82" s="1">
+        <v>5</v>
+      </c>
+      <c r="K82" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L82" s="1">
+        <v>1</v>
+      </c>
+      <c r="M82" s="1">
+        <f>F82*G82</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="83" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="1"/>
+      <c r="M83" s="1"/>
+      <c r="N83" s="1"/>
+      <c r="O83" s="1"/>
     </row>
     <row r="84" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C84" s="1">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D84" s="1">
         <v>3</v>
@@ -4452,38 +4423,38 @@
         <v>400</v>
       </c>
       <c r="G84" s="1">
-        <f t="shared" si="9"/>
-        <v>500</v>
+        <f>N84*O84</f>
+        <v>300</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J84" s="1">
         <v>5</v>
       </c>
       <c r="K84" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="L84" s="1">
         <v>1000</v>
       </c>
       <c r="M84" s="1">
-        <f t="shared" si="10"/>
-        <v>200000</v>
+        <f>F84*G84</f>
+        <v>120000</v>
       </c>
       <c r="N84" s="1">
         <v>1</v>
       </c>
       <c r="O84" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="85" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C85" s="1">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D85" s="1">
         <v>3</v>
@@ -4492,41 +4463,41 @@
         <v>0</v>
       </c>
       <c r="F85" s="1">
-        <v>4000</v>
+        <v>400</v>
       </c>
       <c r="G85" s="1">
-        <f t="shared" si="9"/>
-        <v>6</v>
+        <f>N85*O85</f>
+        <v>500</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J85" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K85" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="L85" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="M85" s="1">
-        <f t="shared" si="10"/>
-        <v>24000</v>
+        <f>F85*G85</f>
+        <v>200000</v>
       </c>
       <c r="N85" s="1">
         <v>1</v>
       </c>
       <c r="O85" s="1">
-        <v>6</v>
+        <v>500</v>
       </c>
     </row>
     <row r="86" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C86" s="1">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D86" s="1">
         <v>3</v>
@@ -4535,30 +4506,30 @@
         <v>0</v>
       </c>
       <c r="F86" s="1">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="G86" s="1">
-        <f t="shared" si="9"/>
+        <f>N86*O86</f>
         <v>20</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J86" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K86" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="L86" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M86" s="1">
-        <f t="shared" si="10"/>
-        <v>40000</v>
+        <f>F86*G86</f>
+        <v>80000</v>
       </c>
       <c r="N86" s="1">
         <v>1</v>
@@ -4569,7 +4540,7 @@
     </row>
     <row r="87" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C87" s="1">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D87" s="1">
         <v>3</v>
@@ -4581,14 +4552,14 @@
         <v>45000</v>
       </c>
       <c r="G87" s="1">
-        <f t="shared" si="9"/>
+        <f>N87*O87</f>
         <v>8</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J87" s="1">
         <v>5</v>
@@ -4600,7 +4571,7 @@
         <v>1</v>
       </c>
       <c r="M87" s="1">
-        <f t="shared" si="10"/>
+        <f>F87*G87</f>
         <v>360000</v>
       </c>
       <c r="N87" s="1">
@@ -4612,7 +4583,7 @@
     </row>
     <row r="88" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C88" s="1">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D88" s="1">
         <v>3</v>
@@ -4624,14 +4595,14 @@
         <v>2000</v>
       </c>
       <c r="G88" s="1">
-        <f t="shared" si="9"/>
+        <f>N88*O88</f>
         <v>40</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J88" s="1">
         <v>5</v>
@@ -4643,7 +4614,7 @@
         <v>1000000</v>
       </c>
       <c r="M88" s="1">
-        <f t="shared" si="10"/>
+        <f>F88*G88</f>
         <v>80000</v>
       </c>
       <c r="N88" s="1">
@@ -4655,7 +4626,7 @@
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C89" s="1">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D89" s="1">
         <v>3</v>
@@ -4667,14 +4638,14 @@
         <v>2000</v>
       </c>
       <c r="G89" s="1">
-        <f t="shared" si="9"/>
+        <f>N89*O89</f>
         <v>40</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J89" s="1">
         <v>5</v>
@@ -4686,7 +4657,7 @@
         <v>6000000</v>
       </c>
       <c r="M89" s="1">
-        <f t="shared" si="10"/>
+        <f>F89*G89</f>
         <v>80000</v>
       </c>
       <c r="N89" s="1">
@@ -4698,7 +4669,7 @@
     </row>
     <row r="90" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C90" s="1">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D90" s="1">
         <v>3</v>
@@ -4710,14 +4681,13 @@
         <v>30000</v>
       </c>
       <c r="G90" s="1">
-        <f t="shared" si="9"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J90" s="1">
         <v>5</v>
@@ -4729,8 +4699,8 @@
         <v>1</v>
       </c>
       <c r="M90" s="1">
-        <f t="shared" si="10"/>
-        <v>150000</v>
+        <f>F90*G90</f>
+        <v>300000</v>
       </c>
       <c r="N90" s="1">
         <v>1</v>
@@ -4739,52 +4709,60 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C92" s="1">
-        <v>221</v>
-      </c>
-      <c r="D92" s="1">
-        <v>4</v>
-      </c>
-      <c r="E92" s="1">
-        <v>0</v>
-      </c>
-      <c r="F92" s="6">
-        <v>600</v>
-      </c>
-      <c r="G92" s="1">
-        <f t="shared" ref="G92:G99" si="11">N92*O92</f>
-        <v>300</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J92" s="1">
-        <v>5</v>
-      </c>
-      <c r="K92" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L92" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M92" s="1">
-        <f t="shared" ref="M92:M99" si="12">F92*G92</f>
-        <v>180000</v>
-      </c>
-      <c r="N92" s="1">
-        <v>1</v>
-      </c>
-      <c r="O92" s="1">
-        <v>300</v>
-      </c>
+    <row r="91" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C91" s="1">
+        <v>218</v>
+      </c>
+      <c r="D91" s="1">
+        <v>3</v>
+      </c>
+      <c r="E91" s="1">
+        <v>10</v>
+      </c>
+      <c r="F91" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G91" s="1">
+        <v>10</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J91" s="1">
+        <v>5</v>
+      </c>
+      <c r="K91" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L91" s="1">
+        <v>1</v>
+      </c>
+      <c r="M91" s="1">
+        <f>F91*G91</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="92" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="1"/>
+      <c r="M92" s="1"/>
+      <c r="N92" s="1"/>
+      <c r="O92" s="1"/>
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C93" s="1">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D93" s="1">
         <v>4</v>
@@ -4796,38 +4774,38 @@
         <v>600</v>
       </c>
       <c r="G93" s="1">
-        <f t="shared" si="11"/>
-        <v>500</v>
+        <f>N93*O93</f>
+        <v>300</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J93" s="1">
         <v>5</v>
       </c>
       <c r="K93" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="L93" s="1">
         <v>1000</v>
       </c>
       <c r="M93" s="1">
-        <f t="shared" si="12"/>
-        <v>300000</v>
+        <f>F93*G93</f>
+        <v>180000</v>
       </c>
       <c r="N93" s="1">
         <v>1</v>
       </c>
       <c r="O93" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C94" s="1">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D94" s="1">
         <v>4</v>
@@ -4836,41 +4814,41 @@
         <v>0</v>
       </c>
       <c r="F94" s="6">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="G94" s="1">
-        <f t="shared" si="11"/>
-        <v>6</v>
+        <f>N94*O94</f>
+        <v>500</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J94" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K94" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="L94" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="M94" s="1">
-        <f t="shared" si="12"/>
-        <v>36000</v>
+        <f>F94*G94</f>
+        <v>300000</v>
       </c>
       <c r="N94" s="1">
         <v>1</v>
       </c>
       <c r="O94" s="1">
-        <v>6</v>
+        <v>500</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C95" s="1">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D95" s="1">
         <v>4</v>
@@ -4879,30 +4857,30 @@
         <v>0</v>
       </c>
       <c r="F95" s="6">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="G95" s="1">
-        <f t="shared" si="11"/>
+        <f>N95*O95</f>
         <v>20</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J95" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K95" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="L95" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M95" s="1">
-        <f t="shared" si="12"/>
-        <v>60000</v>
+        <f>F95*G95</f>
+        <v>120000</v>
       </c>
       <c r="N95" s="1">
         <v>1</v>
@@ -4913,7 +4891,7 @@
     </row>
     <row r="96" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C96" s="1">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D96" s="1">
         <v>4</v>
@@ -4925,14 +4903,14 @@
         <v>60000</v>
       </c>
       <c r="G96" s="1">
-        <f t="shared" si="11"/>
+        <f>N96*O96</f>
         <v>8</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J96" s="1">
         <v>5</v>
@@ -4944,7 +4922,7 @@
         <v>1</v>
       </c>
       <c r="M96" s="1">
-        <f t="shared" si="12"/>
+        <f>F96*G96</f>
         <v>480000</v>
       </c>
       <c r="N96" s="1">
@@ -4956,7 +4934,7 @@
     </row>
     <row r="97" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C97" s="1">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D97" s="1">
         <v>4</v>
@@ -4968,14 +4946,14 @@
         <v>3000</v>
       </c>
       <c r="G97" s="1">
-        <f t="shared" si="11"/>
+        <f>N97*O97</f>
         <v>40</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J97" s="1">
         <v>5</v>
@@ -4987,7 +4965,7 @@
         <v>1000000</v>
       </c>
       <c r="M97" s="1">
-        <f t="shared" si="12"/>
+        <f>F97*G97</f>
         <v>120000</v>
       </c>
       <c r="N97" s="1">
@@ -4999,7 +4977,7 @@
     </row>
     <row r="98" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C98" s="1">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D98" s="1">
         <v>4</v>
@@ -5011,14 +4989,14 @@
         <v>3000</v>
       </c>
       <c r="G98" s="1">
-        <f t="shared" si="11"/>
+        <f>N98*O98</f>
         <v>40</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J98" s="1">
         <v>5</v>
@@ -5030,7 +5008,7 @@
         <v>6000000</v>
       </c>
       <c r="M98" s="1">
-        <f t="shared" si="12"/>
+        <f>F98*G98</f>
         <v>120000</v>
       </c>
       <c r="N98" s="1">
@@ -5042,7 +5020,7 @@
     </row>
     <row r="99" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C99" s="1">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D99" s="1">
         <v>4</v>
@@ -5054,14 +5032,13 @@
         <v>30000</v>
       </c>
       <c r="G99" s="1">
-        <f t="shared" si="11"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J99" s="1">
         <v>5</v>
@@ -5073,8 +5050,8 @@
         <v>1</v>
       </c>
       <c r="M99" s="1">
-        <f t="shared" si="12"/>
-        <v>150000</v>
+        <f>F99*G99</f>
+        <v>300000</v>
       </c>
       <c r="N99" s="1">
         <v>1</v>
@@ -5083,52 +5060,60 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C101" s="1">
-        <v>231</v>
-      </c>
-      <c r="D101" s="1">
-        <v>5</v>
-      </c>
-      <c r="E101" s="1">
-        <v>0</v>
-      </c>
-      <c r="F101" s="1">
-        <v>800</v>
-      </c>
-      <c r="G101" s="1">
-        <f t="shared" ref="G101:G108" si="13">N101*O101</f>
-        <v>1200</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J101" s="1">
-        <v>5</v>
-      </c>
-      <c r="K101" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L101" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M101" s="1">
-        <f t="shared" ref="M101:M108" si="14">F101*G101</f>
-        <v>960000</v>
-      </c>
-      <c r="N101" s="1">
+    <row r="100" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C100" s="1">
+        <v>228</v>
+      </c>
+      <c r="D100" s="1">
         <v>4</v>
       </c>
-      <c r="O101" s="1">
-        <v>300</v>
-      </c>
+      <c r="E100" s="1">
+        <v>10</v>
+      </c>
+      <c r="F100" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G100" s="1">
+        <v>10</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J100" s="1">
+        <v>5</v>
+      </c>
+      <c r="K100" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L100" s="1">
+        <v>1</v>
+      </c>
+      <c r="M100" s="1">
+        <f>F100*G100</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="101" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
+      <c r="K101" s="1"/>
+      <c r="L101" s="1"/>
+      <c r="M101" s="1"/>
+      <c r="N101" s="1"/>
+      <c r="O101" s="1"/>
     </row>
     <row r="102" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C102" s="1">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D102" s="1">
         <v>5</v>
@@ -5140,38 +5125,38 @@
         <v>800</v>
       </c>
       <c r="G102" s="1">
-        <f t="shared" si="13"/>
-        <v>2000</v>
+        <f>N102*O102</f>
+        <v>1200</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J102" s="1">
         <v>5</v>
       </c>
       <c r="K102" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="L102" s="1">
         <v>1000</v>
       </c>
       <c r="M102" s="1">
-        <f t="shared" si="14"/>
-        <v>1600000</v>
+        <f>F102*G102</f>
+        <v>960000</v>
       </c>
       <c r="N102" s="1">
         <v>4</v>
       </c>
       <c r="O102" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C103" s="1">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D103" s="1">
         <v>5</v>
@@ -5180,41 +5165,41 @@
         <v>0</v>
       </c>
       <c r="F103" s="1">
-        <v>8000</v>
+        <v>800</v>
       </c>
       <c r="G103" s="1">
-        <f t="shared" si="13"/>
-        <v>24</v>
+        <f>N103*O103</f>
+        <v>2000</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J103" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K103" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="L103" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="M103" s="1">
-        <f t="shared" si="14"/>
-        <v>192000</v>
+        <f>F103*G103</f>
+        <v>1600000</v>
       </c>
       <c r="N103" s="1">
         <v>4</v>
       </c>
       <c r="O103" s="1">
-        <v>6</v>
+        <v>500</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C104" s="1">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D104" s="1">
         <v>5</v>
@@ -5223,41 +5208,41 @@
         <v>0</v>
       </c>
       <c r="F104" s="1">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="G104" s="1">
-        <f t="shared" si="13"/>
-        <v>80</v>
+        <f>N104*O104</f>
+        <v>40</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J104" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K104" s="1">
-        <v>4012</v>
+        <v>4014</v>
       </c>
       <c r="L104" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M104" s="1">
-        <f t="shared" si="14"/>
+        <f>F104*G104</f>
         <v>320000</v>
       </c>
       <c r="N104" s="1">
         <v>4</v>
       </c>
       <c r="O104" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C105" s="1">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D105" s="1">
         <v>5</v>
@@ -5269,14 +5254,14 @@
         <v>75000</v>
       </c>
       <c r="G105" s="1">
-        <f t="shared" si="13"/>
+        <f>N105*O105</f>
         <v>32</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J105" s="1">
         <v>5</v>
@@ -5288,7 +5273,7 @@
         <v>1</v>
       </c>
       <c r="M105" s="1">
-        <f t="shared" si="14"/>
+        <f>F105*G105</f>
         <v>2400000</v>
       </c>
       <c r="N105" s="1">
@@ -5300,7 +5285,7 @@
     </row>
     <row r="106" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C106" s="1">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D106" s="1">
         <v>5</v>
@@ -5312,14 +5297,14 @@
         <v>4000</v>
       </c>
       <c r="G106" s="1">
-        <f t="shared" si="13"/>
+        <f>N106*O106</f>
         <v>160</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J106" s="1">
         <v>5</v>
@@ -5331,7 +5316,7 @@
         <v>1000000</v>
       </c>
       <c r="M106" s="1">
-        <f t="shared" si="14"/>
+        <f>F106*G106</f>
         <v>640000</v>
       </c>
       <c r="N106" s="1">
@@ -5343,7 +5328,7 @@
     </row>
     <row r="107" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C107" s="1">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D107" s="1">
         <v>5</v>
@@ -5355,14 +5340,14 @@
         <v>4000</v>
       </c>
       <c r="G107" s="1">
-        <f t="shared" si="13"/>
+        <f>N107*O107</f>
         <v>160</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J107" s="1">
         <v>5</v>
@@ -5374,7 +5359,7 @@
         <v>6000000</v>
       </c>
       <c r="M107" s="1">
-        <f t="shared" si="14"/>
+        <f>F107*G107</f>
         <v>640000</v>
       </c>
       <c r="N107" s="1">
@@ -5386,7 +5371,7 @@
     </row>
     <row r="108" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C108" s="1">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D108" s="1">
         <v>5</v>
@@ -5398,14 +5383,13 @@
         <v>30000</v>
       </c>
       <c r="G108" s="1">
-        <f t="shared" si="13"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J108" s="1">
         <v>5</v>
@@ -5417,8 +5401,8 @@
         <v>1</v>
       </c>
       <c r="M108" s="1">
-        <f t="shared" si="14"/>
-        <v>150000</v>
+        <f>F108*G108</f>
+        <v>300000</v>
       </c>
       <c r="N108" s="1">
         <v>1</v>
@@ -5427,81 +5411,94 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C110" s="1">
-        <v>999</v>
-      </c>
-      <c r="D110" s="1">
-        <v>0</v>
-      </c>
-      <c r="E110" s="1">
-        <v>0</v>
-      </c>
-      <c r="F110" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G110" s="1">
-        <v>50</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="J110" s="1">
-        <v>5</v>
-      </c>
-      <c r="K110" s="1">
-        <v>4006</v>
-      </c>
-      <c r="L110" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M110" s="1">
-        <f t="shared" ref="M110:M112" si="15">F110*G110</f>
-        <v>50000</v>
-      </c>
+    <row r="109" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C109" s="1">
+        <v>238</v>
+      </c>
+      <c r="D109" s="1">
+        <v>5</v>
+      </c>
+      <c r="E109" s="1">
+        <v>10</v>
+      </c>
+      <c r="F109" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G109" s="1">
+        <v>10</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J109" s="1">
+        <v>5</v>
+      </c>
+      <c r="K109" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L109" s="1">
+        <v>1</v>
+      </c>
+      <c r="M109" s="1">
+        <f>F109*G109</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="110" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1"/>
+      <c r="K110" s="1"/>
+      <c r="L110" s="1"/>
+      <c r="M110" s="1"/>
     </row>
     <row r="111" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C111" s="1">
+        <v>999</v>
+      </c>
+      <c r="D111" s="1">
+        <v>0</v>
+      </c>
+      <c r="E111" s="1">
+        <v>0</v>
+      </c>
+      <c r="F111" s="1">
         <v>1000</v>
       </c>
-      <c r="D111" s="1">
-        <v>0</v>
-      </c>
-      <c r="E111" s="1">
-        <v>0</v>
-      </c>
-      <c r="F111" s="1">
-        <v>2000</v>
-      </c>
       <c r="G111" s="1">
+        <v>50</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J111" s="1">
+        <v>5</v>
+      </c>
+      <c r="K111" s="1">
+        <v>4006</v>
+      </c>
+      <c r="L111" s="1">
         <v>1000</v>
       </c>
-      <c r="H111" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J111" s="1">
-        <v>5</v>
-      </c>
-      <c r="K111" s="1">
-        <v>4010</v>
-      </c>
-      <c r="L111" s="1">
-        <v>5</v>
-      </c>
       <c r="M111" s="1">
-        <f t="shared" si="15"/>
-        <v>2000000</v>
+        <f t="shared" ref="M111:M113" si="4">F111*G111</f>
+        <v>50000</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C112" s="1">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="D112" s="1">
         <v>0</v>
@@ -5513,25 +5510,61 @@
         <v>2000</v>
       </c>
       <c r="G112" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J112" s="1">
+        <v>5</v>
+      </c>
+      <c r="K112" s="1">
+        <v>4010</v>
+      </c>
+      <c r="L112" s="1">
+        <v>5</v>
+      </c>
+      <c r="M112" s="1">
+        <f t="shared" si="4"/>
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="113" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C113" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D113" s="1">
+        <v>0</v>
+      </c>
+      <c r="E113" s="1">
+        <v>0</v>
+      </c>
+      <c r="F113" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G113" s="1">
         <v>50</v>
       </c>
-      <c r="H112" s="1" t="s">
+      <c r="H113" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="I112" s="1" t="s">
+      <c r="I113" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J112" s="1">
-        <v>5</v>
-      </c>
-      <c r="K112" s="1">
+      <c r="J113" s="1">
+        <v>5</v>
+      </c>
+      <c r="K113" s="1">
         <v>4102</v>
       </c>
-      <c r="L112" s="1">
+      <c r="L113" s="1">
         <v>20</v>
       </c>
-      <c r="M112" s="1">
-        <f t="shared" si="15"/>
+      <c r="M113" s="1">
+        <f t="shared" si="4"/>
         <v>100000</v>
       </c>
     </row>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -3721,7 +3721,7 @@
         <v>100</v>
       </c>
       <c r="G66" s="1">
-        <f>N66*O66</f>
+        <f t="shared" ref="G66:G71" si="4">N66*O66</f>
         <v>300</v>
       </c>
       <c r="H66" s="1" t="s">
@@ -3740,7 +3740,7 @@
         <v>1000</v>
       </c>
       <c r="M66" s="1">
-        <f>F66*G66</f>
+        <f t="shared" ref="M66:M73" si="5">F66*G66</f>
         <v>30000</v>
       </c>
       <c r="N66" s="1">
@@ -3764,7 +3764,7 @@
         <v>100</v>
       </c>
       <c r="G67" s="1">
-        <f>N67*O67</f>
+        <f t="shared" si="4"/>
         <v>500</v>
       </c>
       <c r="H67" s="1" t="s">
@@ -3783,7 +3783,7 @@
         <v>1000</v>
       </c>
       <c r="M67" s="1">
-        <f>F67*G67</f>
+        <f t="shared" si="5"/>
         <v>50000</v>
       </c>
       <c r="N67" s="1">
@@ -3807,7 +3807,7 @@
         <v>1000</v>
       </c>
       <c r="G68" s="1">
-        <f>N68*O68</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="H68" s="1" t="s">
@@ -3826,7 +3826,7 @@
         <v>100</v>
       </c>
       <c r="M68" s="1">
-        <f>F68*G68</f>
+        <f t="shared" si="5"/>
         <v>20000</v>
       </c>
       <c r="N68" s="1">
@@ -3850,7 +3850,7 @@
         <v>15000</v>
       </c>
       <c r="G69" s="1">
-        <f>N69*O69</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="H69" s="1" t="s">
@@ -3869,7 +3869,7 @@
         <v>1</v>
       </c>
       <c r="M69" s="1">
-        <f>F69*G69</f>
+        <f t="shared" si="5"/>
         <v>120000</v>
       </c>
       <c r="N69" s="1">
@@ -3893,7 +3893,7 @@
         <v>500</v>
       </c>
       <c r="G70" s="1">
-        <f>N70*O70</f>
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="H70" s="1" t="s">
@@ -3912,7 +3912,7 @@
         <v>1000000</v>
       </c>
       <c r="M70" s="1">
-        <f>F70*G70</f>
+        <f t="shared" si="5"/>
         <v>20000</v>
       </c>
       <c r="N70" s="1">
@@ -3936,7 +3936,7 @@
         <v>500</v>
       </c>
       <c r="G71" s="1">
-        <f>N71*O71</f>
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="H71" s="1" t="s">
@@ -3955,7 +3955,7 @@
         <v>6000000</v>
       </c>
       <c r="M71" s="1">
-        <f>F71*G71</f>
+        <f t="shared" si="5"/>
         <v>20000</v>
       </c>
       <c r="N71" s="1">
@@ -3997,7 +3997,7 @@
         <v>1</v>
       </c>
       <c r="M72" s="1">
-        <f>F72*G72</f>
+        <f t="shared" si="5"/>
         <v>300000</v>
       </c>
       <c r="N72" s="1">
@@ -4039,7 +4039,7 @@
         <v>1</v>
       </c>
       <c r="M73" s="1">
-        <f>F73*G73</f>
+        <f t="shared" si="5"/>
         <v>300000</v>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
         <v>200</v>
       </c>
       <c r="G75" s="1">
-        <f>N75*O75</f>
+        <f t="shared" ref="G75:G80" si="6">N75*O75</f>
         <v>300</v>
       </c>
       <c r="H75" s="1" t="s">
@@ -4091,7 +4091,7 @@
         <v>1000</v>
       </c>
       <c r="M75" s="1">
-        <f>F75*G75</f>
+        <f t="shared" ref="M75:M82" si="7">F75*G75</f>
         <v>60000</v>
       </c>
       <c r="N75" s="1">
@@ -4115,7 +4115,7 @@
         <v>200</v>
       </c>
       <c r="G76" s="1">
-        <f>N76*O76</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="H76" s="1" t="s">
@@ -4134,7 +4134,7 @@
         <v>1000</v>
       </c>
       <c r="M76" s="1">
-        <f>F76*G76</f>
+        <f t="shared" si="7"/>
         <v>100000</v>
       </c>
       <c r="N76" s="1">
@@ -4158,7 +4158,7 @@
         <v>2000</v>
       </c>
       <c r="G77" s="1">
-        <f>N77*O77</f>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="H77" s="1" t="s">
@@ -4177,7 +4177,7 @@
         <v>100</v>
       </c>
       <c r="M77" s="1">
-        <f>F77*G77</f>
+        <f t="shared" si="7"/>
         <v>40000</v>
       </c>
       <c r="N77" s="1">
@@ -4201,7 +4201,7 @@
         <v>30000</v>
       </c>
       <c r="G78" s="1">
-        <f>N78*O78</f>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="H78" s="1" t="s">
@@ -4220,7 +4220,7 @@
         <v>1</v>
       </c>
       <c r="M78" s="1">
-        <f>F78*G78</f>
+        <f t="shared" si="7"/>
         <v>240000</v>
       </c>
       <c r="N78" s="1">
@@ -4244,7 +4244,7 @@
         <v>1000</v>
       </c>
       <c r="G79" s="1">
-        <f>N79*O79</f>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
       <c r="H79" s="1" t="s">
@@ -4263,7 +4263,7 @@
         <v>1000000</v>
       </c>
       <c r="M79" s="1">
-        <f>F79*G79</f>
+        <f t="shared" si="7"/>
         <v>40000</v>
       </c>
       <c r="N79" s="1">
@@ -4287,7 +4287,7 @@
         <v>1000</v>
       </c>
       <c r="G80" s="1">
-        <f>N80*O80</f>
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
       <c r="H80" s="1" t="s">
@@ -4306,7 +4306,7 @@
         <v>6000000</v>
       </c>
       <c r="M80" s="1">
-        <f>F80*G80</f>
+        <f t="shared" si="7"/>
         <v>40000</v>
       </c>
       <c r="N80" s="1">
@@ -4348,7 +4348,7 @@
         <v>1</v>
       </c>
       <c r="M81" s="1">
-        <f>F81*G81</f>
+        <f t="shared" si="7"/>
         <v>300000</v>
       </c>
       <c r="N81" s="1">
@@ -4390,7 +4390,7 @@
         <v>1</v>
       </c>
       <c r="M82" s="1">
-        <f>F82*G82</f>
+        <f t="shared" si="7"/>
         <v>300000</v>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
         <v>400</v>
       </c>
       <c r="G84" s="1">
-        <f>N84*O84</f>
+        <f t="shared" ref="G84:G89" si="8">N84*O84</f>
         <v>300</v>
       </c>
       <c r="H84" s="1" t="s">
@@ -4442,7 +4442,7 @@
         <v>1000</v>
       </c>
       <c r="M84" s="1">
-        <f>F84*G84</f>
+        <f t="shared" ref="M84:M91" si="9">F84*G84</f>
         <v>120000</v>
       </c>
       <c r="N84" s="1">
@@ -4466,7 +4466,7 @@
         <v>400</v>
       </c>
       <c r="G85" s="1">
-        <f>N85*O85</f>
+        <f t="shared" si="8"/>
         <v>500</v>
       </c>
       <c r="H85" s="1" t="s">
@@ -4485,7 +4485,7 @@
         <v>1000</v>
       </c>
       <c r="M85" s="1">
-        <f>F85*G85</f>
+        <f t="shared" si="9"/>
         <v>200000</v>
       </c>
       <c r="N85" s="1">
@@ -4509,7 +4509,7 @@
         <v>4000</v>
       </c>
       <c r="G86" s="1">
-        <f>N86*O86</f>
+        <f t="shared" si="8"/>
         <v>20</v>
       </c>
       <c r="H86" s="1" t="s">
@@ -4528,7 +4528,7 @@
         <v>100</v>
       </c>
       <c r="M86" s="1">
-        <f>F86*G86</f>
+        <f t="shared" si="9"/>
         <v>80000</v>
       </c>
       <c r="N86" s="1">
@@ -4552,7 +4552,7 @@
         <v>45000</v>
       </c>
       <c r="G87" s="1">
-        <f>N87*O87</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="H87" s="1" t="s">
@@ -4571,7 +4571,7 @@
         <v>1</v>
       </c>
       <c r="M87" s="1">
-        <f>F87*G87</f>
+        <f t="shared" si="9"/>
         <v>360000</v>
       </c>
       <c r="N87" s="1">
@@ -4595,7 +4595,7 @@
         <v>2000</v>
       </c>
       <c r="G88" s="1">
-        <f>N88*O88</f>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
       <c r="H88" s="1" t="s">
@@ -4614,7 +4614,7 @@
         <v>1000000</v>
       </c>
       <c r="M88" s="1">
-        <f>F88*G88</f>
+        <f t="shared" si="9"/>
         <v>80000</v>
       </c>
       <c r="N88" s="1">
@@ -4638,7 +4638,7 @@
         <v>2000</v>
       </c>
       <c r="G89" s="1">
-        <f>N89*O89</f>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
       <c r="H89" s="1" t="s">
@@ -4657,7 +4657,7 @@
         <v>6000000</v>
       </c>
       <c r="M89" s="1">
-        <f>F89*G89</f>
+        <f t="shared" si="9"/>
         <v>80000</v>
       </c>
       <c r="N89" s="1">
@@ -4699,7 +4699,7 @@
         <v>1</v>
       </c>
       <c r="M90" s="1">
-        <f>F90*G90</f>
+        <f t="shared" si="9"/>
         <v>300000</v>
       </c>
       <c r="N90" s="1">
@@ -4741,7 +4741,7 @@
         <v>1</v>
       </c>
       <c r="M91" s="1">
-        <f>F91*G91</f>
+        <f t="shared" si="9"/>
         <v>300000</v>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
         <v>600</v>
       </c>
       <c r="G93" s="1">
-        <f>N93*O93</f>
+        <f t="shared" ref="G93:G98" si="10">N93*O93</f>
         <v>300</v>
       </c>
       <c r="H93" s="1" t="s">
@@ -4793,7 +4793,7 @@
         <v>1000</v>
       </c>
       <c r="M93" s="1">
-        <f>F93*G93</f>
+        <f t="shared" ref="M93:M100" si="11">F93*G93</f>
         <v>180000</v>
       </c>
       <c r="N93" s="1">
@@ -4817,7 +4817,7 @@
         <v>600</v>
       </c>
       <c r="G94" s="1">
-        <f>N94*O94</f>
+        <f t="shared" si="10"/>
         <v>500</v>
       </c>
       <c r="H94" s="1" t="s">
@@ -4836,7 +4836,7 @@
         <v>1000</v>
       </c>
       <c r="M94" s="1">
-        <f>F94*G94</f>
+        <f t="shared" si="11"/>
         <v>300000</v>
       </c>
       <c r="N94" s="1">
@@ -4860,7 +4860,7 @@
         <v>6000</v>
       </c>
       <c r="G95" s="1">
-        <f>N95*O95</f>
+        <f t="shared" si="10"/>
         <v>20</v>
       </c>
       <c r="H95" s="1" t="s">
@@ -4879,7 +4879,7 @@
         <v>100</v>
       </c>
       <c r="M95" s="1">
-        <f>F95*G95</f>
+        <f t="shared" si="11"/>
         <v>120000</v>
       </c>
       <c r="N95" s="1">
@@ -4903,7 +4903,7 @@
         <v>60000</v>
       </c>
       <c r="G96" s="1">
-        <f>N96*O96</f>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
       <c r="H96" s="1" t="s">
@@ -4922,7 +4922,7 @@
         <v>1</v>
       </c>
       <c r="M96" s="1">
-        <f>F96*G96</f>
+        <f t="shared" si="11"/>
         <v>480000</v>
       </c>
       <c r="N96" s="1">
@@ -4946,7 +4946,7 @@
         <v>3000</v>
       </c>
       <c r="G97" s="1">
-        <f>N97*O97</f>
+        <f t="shared" si="10"/>
         <v>40</v>
       </c>
       <c r="H97" s="1" t="s">
@@ -4965,7 +4965,7 @@
         <v>1000000</v>
       </c>
       <c r="M97" s="1">
-        <f>F97*G97</f>
+        <f t="shared" si="11"/>
         <v>120000</v>
       </c>
       <c r="N97" s="1">
@@ -4989,7 +4989,7 @@
         <v>3000</v>
       </c>
       <c r="G98" s="1">
-        <f>N98*O98</f>
+        <f t="shared" si="10"/>
         <v>40</v>
       </c>
       <c r="H98" s="1" t="s">
@@ -5008,7 +5008,7 @@
         <v>6000000</v>
       </c>
       <c r="M98" s="1">
-        <f>F98*G98</f>
+        <f t="shared" si="11"/>
         <v>120000</v>
       </c>
       <c r="N98" s="1">
@@ -5050,7 +5050,7 @@
         <v>1</v>
       </c>
       <c r="M99" s="1">
-        <f>F99*G99</f>
+        <f t="shared" si="11"/>
         <v>300000</v>
       </c>
       <c r="N99" s="1">
@@ -5092,7 +5092,7 @@
         <v>1</v>
       </c>
       <c r="M100" s="1">
-        <f>F100*G100</f>
+        <f t="shared" si="11"/>
         <v>300000</v>
       </c>
     </row>
@@ -5125,7 +5125,7 @@
         <v>800</v>
       </c>
       <c r="G102" s="1">
-        <f>N102*O102</f>
+        <f t="shared" ref="G102:G107" si="12">N102*O102</f>
         <v>1200</v>
       </c>
       <c r="H102" s="1" t="s">
@@ -5144,7 +5144,7 @@
         <v>1000</v>
       </c>
       <c r="M102" s="1">
-        <f>F102*G102</f>
+        <f t="shared" ref="M102:M109" si="13">F102*G102</f>
         <v>960000</v>
       </c>
       <c r="N102" s="1">
@@ -5168,7 +5168,7 @@
         <v>800</v>
       </c>
       <c r="G103" s="1">
-        <f>N103*O103</f>
+        <f t="shared" si="12"/>
         <v>2000</v>
       </c>
       <c r="H103" s="1" t="s">
@@ -5187,7 +5187,7 @@
         <v>1000</v>
       </c>
       <c r="M103" s="1">
-        <f>F103*G103</f>
+        <f t="shared" si="13"/>
         <v>1600000</v>
       </c>
       <c r="N103" s="1">
@@ -5211,7 +5211,7 @@
         <v>8000</v>
       </c>
       <c r="G104" s="1">
-        <f>N104*O104</f>
+        <f t="shared" si="12"/>
         <v>40</v>
       </c>
       <c r="H104" s="1" t="s">
@@ -5230,7 +5230,7 @@
         <v>100</v>
       </c>
       <c r="M104" s="1">
-        <f>F104*G104</f>
+        <f t="shared" si="13"/>
         <v>320000</v>
       </c>
       <c r="N104" s="1">
@@ -5254,7 +5254,7 @@
         <v>75000</v>
       </c>
       <c r="G105" s="1">
-        <f>N105*O105</f>
+        <f t="shared" si="12"/>
         <v>32</v>
       </c>
       <c r="H105" s="1" t="s">
@@ -5273,7 +5273,7 @@
         <v>1</v>
       </c>
       <c r="M105" s="1">
-        <f>F105*G105</f>
+        <f t="shared" si="13"/>
         <v>2400000</v>
       </c>
       <c r="N105" s="1">
@@ -5297,7 +5297,7 @@
         <v>4000</v>
       </c>
       <c r="G106" s="1">
-        <f>N106*O106</f>
+        <f t="shared" si="12"/>
         <v>160</v>
       </c>
       <c r="H106" s="1" t="s">
@@ -5316,7 +5316,7 @@
         <v>1000000</v>
       </c>
       <c r="M106" s="1">
-        <f>F106*G106</f>
+        <f t="shared" si="13"/>
         <v>640000</v>
       </c>
       <c r="N106" s="1">
@@ -5340,7 +5340,7 @@
         <v>4000</v>
       </c>
       <c r="G107" s="1">
-        <f>N107*O107</f>
+        <f t="shared" si="12"/>
         <v>160</v>
       </c>
       <c r="H107" s="1" t="s">
@@ -5359,7 +5359,7 @@
         <v>6000000</v>
       </c>
       <c r="M107" s="1">
-        <f>F107*G107</f>
+        <f t="shared" si="13"/>
         <v>640000</v>
       </c>
       <c r="N107" s="1">
@@ -5401,7 +5401,7 @@
         <v>1</v>
       </c>
       <c r="M108" s="1">
-        <f>F108*G108</f>
+        <f t="shared" si="13"/>
         <v>300000</v>
       </c>
       <c r="N108" s="1">
@@ -5443,7 +5443,7 @@
         <v>1</v>
       </c>
       <c r="M109" s="1">
-        <f>F109*G109</f>
+        <f t="shared" si="13"/>
         <v>300000</v>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
         <v>1000</v>
       </c>
       <c r="M111" s="1">
-        <f t="shared" ref="M111:M113" si="4">F111*G111</f>
+        <f t="shared" ref="M111:M113" si="14">F111*G111</f>
         <v>50000</v>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
         <v>5</v>
       </c>
       <c r="M112" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>2000000</v>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
         <v>20</v>
       </c>
       <c r="M113" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="14"/>
         <v>100000</v>
       </c>
     </row>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="157">
   <si>
     <t>#</t>
   </si>
@@ -305,9 +305,6 @@
     <t>极法宝自选</t>
   </si>
   <si>
-    <t>5000</t>
-  </si>
-  <si>
     <t>兑换改造石</t>
   </si>
   <si>
@@ -350,66 +347,12 @@
     <t>开孔石</t>
   </si>
   <si>
-    <t>兑换攻击宝石</t>
+    <t>宝石集合包</t>
   </si>
   <si>
     <t>攻击宝石</t>
   </si>
   <si>
-    <t>兑换防御宝石</t>
-  </si>
-  <si>
-    <t>防御宝石</t>
-  </si>
-  <si>
-    <t>兑换生命宝石</t>
-  </si>
-  <si>
-    <t>生命宝石</t>
-  </si>
-  <si>
-    <t>兑换命中宝石</t>
-  </si>
-  <si>
-    <t>命中宝石</t>
-  </si>
-  <si>
-    <t>兑换闪避宝石</t>
-  </si>
-  <si>
-    <t>闪避宝石</t>
-  </si>
-  <si>
-    <t>兑换物理宝石</t>
-  </si>
-  <si>
-    <t>物理宝石</t>
-  </si>
-  <si>
-    <t>兑换魔法宝石</t>
-  </si>
-  <si>
-    <t>魔法宝石</t>
-  </si>
-  <si>
-    <t>兑换道术宝石</t>
-  </si>
-  <si>
-    <t>道术宝石</t>
-  </si>
-  <si>
-    <t>兑换增伤宝石</t>
-  </si>
-  <si>
-    <t>增伤宝石</t>
-  </si>
-  <si>
-    <t>兑换韧性宝石</t>
-  </si>
-  <si>
-    <t>韧性宝石</t>
-  </si>
-  <si>
     <t>兑换低级法宝自选*1</t>
   </si>
   <si>
@@ -434,6 +377,69 @@
     <t>11技能自选</t>
   </si>
   <si>
+    <t>金色魂心</t>
+  </si>
+  <si>
+    <t>暗金魂心</t>
+  </si>
+  <si>
+    <t>金色材料魂宠</t>
+  </si>
+  <si>
+    <t>炼神丹</t>
+  </si>
+  <si>
+    <t>炼神丹*500</t>
+  </si>
+  <si>
+    <t>不朽精华</t>
+  </si>
+  <si>
+    <t>不朽精华*1</t>
+  </si>
+  <si>
+    <t>混沌精华</t>
+  </si>
+  <si>
+    <t>混沌精华*1</t>
+  </si>
+  <si>
+    <t>仙鉴青龙</t>
+  </si>
+  <si>
+    <t>仙鉴青龙*1</t>
+  </si>
+  <si>
+    <t>仙鉴白虎</t>
+  </si>
+  <si>
+    <t>仙鉴白虎*1</t>
+  </si>
+  <si>
+    <t>仙鉴朱雀</t>
+  </si>
+  <si>
+    <t>仙鉴朱雀*1</t>
+  </si>
+  <si>
+    <t>仙鉴玄武</t>
+  </si>
+  <si>
+    <t>仙鉴玄武*1</t>
+  </si>
+  <si>
+    <t>仙鉴麒麟</t>
+  </si>
+  <si>
+    <t>仙鉴麒麟*1</t>
+  </si>
+  <si>
+    <t>兑换传奇精华</t>
+  </si>
+  <si>
+    <t>传奇精华</t>
+  </si>
+  <si>
     <t>兑换四格碎片*1000</t>
   </si>
   <si>
@@ -474,12 +480,6 @@
   </si>
   <si>
     <t>暗金精华</t>
-  </si>
-  <si>
-    <t>兑换传奇精华</t>
-  </si>
-  <si>
-    <t>传奇精华</t>
   </si>
   <si>
     <t>兑换书页1000个</t>
@@ -510,7 +510,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -537,11 +537,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1010,28 +1005,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1040,122 +1038,119 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1163,7 +1158,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
@@ -1514,7 +1508,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O113"/>
+  <dimension ref="A1:O122"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1640,11 +1634,11 @@
       <c r="E6" s="1">
         <v>0</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="1">
-        <v>268</v>
+        <v>888</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>14</v>
@@ -1663,7 +1657,7 @@
       </c>
       <c r="M6" s="1">
         <f t="shared" ref="M6:M14" si="0">F6*G6</f>
-        <v>80400</v>
+        <v>266400</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:13">
@@ -1676,11 +1670,11 @@
       <c r="E7" s="1">
         <v>0</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>268</v>
+        <v>888</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>16</v>
@@ -1699,7 +1693,7 @@
       </c>
       <c r="M7" s="1">
         <f t="shared" si="0"/>
-        <v>80400</v>
+        <v>266400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1712,11 +1706,11 @@
       <c r="E8" s="1">
         <v>0</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="1">
-        <v>268</v>
+        <v>888</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>18</v>
@@ -1735,7 +1729,7 @@
       </c>
       <c r="M8" s="1">
         <f t="shared" si="0"/>
-        <v>80400</v>
+        <v>266400</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:13">
@@ -1748,7 +1742,7 @@
       <c r="E9" s="1">
         <v>0</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>20</v>
       </c>
       <c r="G9" s="1">
@@ -1784,7 +1778,7 @@
       <c r="E10" s="1">
         <v>0</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="1">
@@ -1820,7 +1814,7 @@
       <c r="E11" s="1">
         <v>0</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="1">
@@ -1856,7 +1850,7 @@
       <c r="E12" s="1">
         <v>0</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="1">
@@ -1892,7 +1886,7 @@
       <c r="E13" s="1">
         <v>0</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="6" t="s">
         <v>20</v>
       </c>
       <c r="G13" s="1">
@@ -1928,7 +1922,7 @@
       <c r="E14" s="1">
         <v>0</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="6" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="1">
@@ -1964,7 +1958,7 @@
       <c r="E15" s="1">
         <v>0</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="6" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="1">
@@ -2000,7 +1994,7 @@
       <c r="E16" s="1">
         <v>0</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G16" s="1">
@@ -2036,7 +2030,7 @@
       <c r="E17" s="1">
         <v>0</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="1">
@@ -2072,7 +2066,7 @@
       <c r="E18" s="1">
         <v>0</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G18" s="1">
@@ -2108,7 +2102,7 @@
       <c r="E19" s="1">
         <v>0</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G19" s="1">
@@ -2144,7 +2138,7 @@
       <c r="E20" s="1">
         <v>0</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>13</v>
       </c>
       <c r="G20" s="1">
@@ -2180,7 +2174,7 @@
       <c r="E21" s="1">
         <v>0</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G21" s="1">
@@ -2216,7 +2210,7 @@
       <c r="E22" s="1">
         <v>0</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G22" s="1">
@@ -2252,7 +2246,7 @@
       <c r="E23" s="1">
         <v>0</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G23" s="1">
@@ -2288,7 +2282,7 @@
       <c r="E24" s="1">
         <v>0</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G24" s="1">
@@ -2540,7 +2534,7 @@
       <c r="E31" s="1">
         <v>0</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="6" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="1">
@@ -2576,7 +2570,7 @@
       <c r="E32" s="1">
         <v>0</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="6" t="s">
         <v>20</v>
       </c>
       <c r="G32" s="1">
@@ -2612,7 +2606,7 @@
       <c r="E33" s="1">
         <v>0</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="6" t="s">
         <v>71</v>
       </c>
       <c r="G33" s="1">
@@ -2648,7 +2642,7 @@
       <c r="E34" s="1">
         <v>0</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="6" t="s">
         <v>74</v>
       </c>
       <c r="G34" s="1">
@@ -2684,7 +2678,7 @@
       <c r="E35" s="1">
         <v>0</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G35" s="1">
@@ -2720,7 +2714,7 @@
       <c r="E36" s="1">
         <v>0</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="6" t="s">
         <v>80</v>
       </c>
       <c r="G36" s="1">
@@ -2756,11 +2750,11 @@
       <c r="E37" s="1">
         <v>0</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="6" t="s">
         <v>83</v>
       </c>
       <c r="G37" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>84</v>
@@ -2779,7 +2773,7 @@
       </c>
       <c r="M37" s="1">
         <f t="shared" si="1"/>
-        <v>1500000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:13">
@@ -2792,7 +2786,7 @@
       <c r="E38" s="1">
         <v>0</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="6" t="s">
         <v>86</v>
       </c>
       <c r="G38" s="1">
@@ -2814,7 +2808,7 @@
         <v>1</v>
       </c>
       <c r="M38" s="1">
-        <f t="shared" ref="M38:M43" si="2">F38*G38</f>
+        <f t="shared" ref="M38:M48" si="2">F38*G38</f>
         <v>800000</v>
       </c>
     </row>
@@ -2828,7 +2822,7 @@
       <c r="E39" s="1">
         <v>0</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="6" t="s">
         <v>89</v>
       </c>
       <c r="G39" s="1">
@@ -2864,17 +2858,17 @@
       <c r="E40" s="1">
         <v>0</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G40" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H40" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="G40" s="1">
-        <v>400</v>
-      </c>
-      <c r="H40" s="1" t="s">
+      <c r="I40" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="J40" s="1">
         <v>5</v>
@@ -2900,17 +2894,17 @@
       <c r="E41" s="1">
         <v>0</v>
       </c>
-      <c r="F41" s="7" t="s">
-        <v>92</v>
+      <c r="F41" s="1">
+        <v>1000</v>
       </c>
       <c r="G41" s="1">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="H41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="J41" s="1">
         <v>5</v>
@@ -2923,7 +2917,7 @@
       </c>
       <c r="M41" s="1">
         <f t="shared" si="2"/>
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:13">
@@ -2943,10 +2937,10 @@
         <v>200</v>
       </c>
       <c r="H42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="J42" s="1">
         <v>5</v>
@@ -2979,10 +2973,10 @@
         <v>50</v>
       </c>
       <c r="H43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I43" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="J43" s="1">
         <v>5</v>
@@ -3015,13 +3009,13 @@
         <v>40</v>
       </c>
       <c r="H44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I44" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="J44" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K44" s="1">
         <v>4020</v>
@@ -3030,7 +3024,7 @@
         <v>1</v>
       </c>
       <c r="M44" s="1">
-        <f t="shared" ref="M44:M57" si="3">F44*G44</f>
+        <f t="shared" si="2"/>
         <v>800000</v>
       </c>
     </row>
@@ -3051,10 +3045,10 @@
         <v>1</v>
       </c>
       <c r="H45" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="J45" s="1">
         <v>4</v>
@@ -3066,7 +3060,7 @@
         <v>1</v>
       </c>
       <c r="M45" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>388888</v>
       </c>
     </row>
@@ -3087,10 +3081,10 @@
         <v>2</v>
       </c>
       <c r="H46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="J46" s="1">
         <v>5</v>
@@ -3102,7 +3096,7 @@
         <v>1</v>
       </c>
       <c r="M46" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>600000</v>
       </c>
     </row>
@@ -3117,29 +3111,29 @@
         <v>4</v>
       </c>
       <c r="F47" s="1">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="G47" s="1">
         <v>200</v>
       </c>
       <c r="H47" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="I47" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="J47" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K47" s="4">
-        <v>60000001</v>
+        <v>36</v>
       </c>
       <c r="L47" s="1">
         <v>1</v>
       </c>
       <c r="M47" s="1">
-        <f t="shared" si="3"/>
-        <v>500000</v>
+        <f t="shared" si="2"/>
+        <v>2000000</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:13">
@@ -3150,500 +3144,499 @@
         <v>0</v>
       </c>
       <c r="E48" s="1">
+        <v>0</v>
+      </c>
+      <c r="F48" s="1">
+        <v>50000</v>
+      </c>
+      <c r="G48" s="1">
+        <v>50</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J48" s="1">
         <v>4</v>
       </c>
-      <c r="F48" s="1">
-        <v>2500</v>
-      </c>
-      <c r="G48" s="1">
-        <v>200</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="J48" s="1">
-        <v>5</v>
-      </c>
-      <c r="K48" s="4">
-        <v>60000002</v>
+      <c r="K48" s="1">
+        <v>24</v>
       </c>
       <c r="L48" s="1">
         <v>1</v>
       </c>
       <c r="M48" s="1">
-        <f t="shared" si="3"/>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="49" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C49" s="1">
-        <v>44</v>
-      </c>
-      <c r="D49" s="1">
-        <v>0</v>
-      </c>
-      <c r="E49" s="1">
-        <v>4</v>
-      </c>
-      <c r="F49" s="1">
-        <v>2500</v>
-      </c>
-      <c r="G49" s="1">
-        <v>200</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J49" s="1">
-        <v>5</v>
-      </c>
-      <c r="K49" s="4">
-        <v>60000003</v>
-      </c>
-      <c r="L49" s="1">
-        <v>1</v>
-      </c>
-      <c r="M49" s="1">
-        <f t="shared" si="3"/>
-        <v>500000</v>
-      </c>
+        <f t="shared" si="2"/>
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
     </row>
-    <row r="50" customFormat="1" customHeight="1" spans="3:15">
+    <row r="50" customFormat="1" customHeight="1" spans="1:15">
+      <c r="B50" s="1"/>
       <c r="C50" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F50" s="1">
-        <v>2500</v>
+        <v>100000</v>
       </c>
       <c r="G50" s="1">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J50" s="1">
         <v>5</v>
       </c>
-      <c r="K50" s="4">
-        <v>60000004</v>
+      <c r="K50" s="1">
+        <v>4034</v>
       </c>
       <c r="L50" s="1">
         <v>1</v>
       </c>
       <c r="M50" s="1">
-        <f t="shared" si="3"/>
-        <v>500000</v>
+        <f t="shared" ref="M50:M67" si="3">F50*G50</f>
+        <v>1000000</v>
       </c>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
     </row>
-    <row r="51" customFormat="1" customHeight="1" spans="3:15">
+    <row r="51" customFormat="1" customHeight="1" spans="1:15">
+      <c r="B51" s="1"/>
       <c r="C51" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F51" s="1">
-        <v>2500</v>
+        <v>150000</v>
       </c>
       <c r="G51" s="1">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J51" s="1">
         <v>5</v>
       </c>
-      <c r="K51" s="4">
-        <v>60000005</v>
+      <c r="K51" s="1">
+        <v>4112</v>
       </c>
       <c r="L51" s="1">
         <v>1</v>
       </c>
       <c r="M51" s="1">
         <f t="shared" si="3"/>
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
     </row>
-    <row r="52" customFormat="1" customHeight="1" spans="3:15">
+    <row r="52" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
       <c r="C52" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F52" s="1">
-        <v>2500</v>
+        <v>80000</v>
       </c>
       <c r="G52" s="1">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J52" s="1">
         <v>5</v>
       </c>
-      <c r="K52" s="4">
-        <v>60000006</v>
+      <c r="K52" s="1">
+        <v>4033</v>
       </c>
       <c r="L52" s="1">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="M52" s="1">
         <f t="shared" si="3"/>
-        <v>500000</v>
+        <v>1600000</v>
       </c>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
     </row>
-    <row r="53" customFormat="1" customHeight="1" spans="3:15">
+    <row r="53" customFormat="1" customHeight="1" spans="1:15">
+      <c r="B53" s="1"/>
       <c r="C53" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
+        <v>15</v>
+      </c>
+      <c r="F53" s="1">
+        <v>500000</v>
+      </c>
+      <c r="G53" s="1">
+        <v>5</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J53" s="1">
         <v>4</v>
       </c>
-      <c r="F53" s="1">
-        <v>2500</v>
-      </c>
-      <c r="G53" s="1">
-        <v>200</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J53" s="1">
-        <v>5</v>
-      </c>
-      <c r="K53" s="4">
-        <v>60000007</v>
+      <c r="K53" s="1">
+        <v>29</v>
       </c>
       <c r="L53" s="1">
         <v>1</v>
       </c>
       <c r="M53" s="1">
         <f t="shared" si="3"/>
-        <v>500000</v>
+        <v>2500000</v>
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
     </row>
-    <row r="54" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C54" s="1">
-        <v>49</v>
-      </c>
-      <c r="D54" s="1">
-        <v>0</v>
-      </c>
-      <c r="E54" s="1">
-        <v>4</v>
-      </c>
-      <c r="F54" s="1">
-        <v>2500</v>
-      </c>
-      <c r="G54" s="1">
-        <v>200</v>
-      </c>
-      <c r="H54" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="I54" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="J54" s="1">
-        <v>5</v>
-      </c>
-      <c r="K54" s="4">
-        <v>60000008</v>
-      </c>
-      <c r="L54" s="1">
-        <v>1</v>
-      </c>
-      <c r="M54" s="1">
-        <f t="shared" si="3"/>
-        <v>500000</v>
-      </c>
+    <row r="54" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
     </row>
-    <row r="55" customFormat="1" customHeight="1" spans="3:15">
+    <row r="55" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A55" s="1"/>
+      <c r="B55"/>
       <c r="C55" s="1">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F55" s="1">
-        <v>2500</v>
+        <v>800000</v>
       </c>
       <c r="G55" s="1">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="J55" s="1">
         <v>5</v>
       </c>
-      <c r="K55" s="4">
-        <v>60000009</v>
+      <c r="K55" s="1">
+        <v>4025</v>
       </c>
       <c r="L55" s="1">
         <v>1</v>
       </c>
       <c r="M55" s="1">
         <f t="shared" si="3"/>
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
     </row>
-    <row r="56" customFormat="1" customHeight="1" spans="3:15">
+    <row r="56" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A56" s="1"/>
+      <c r="B56"/>
       <c r="C56" s="1">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D56" s="1">
         <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F56" s="1">
-        <v>2500</v>
+        <v>1500000</v>
       </c>
       <c r="G56" s="1">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="J56" s="1">
         <v>5</v>
       </c>
-      <c r="K56" s="4">
-        <v>60000010</v>
+      <c r="K56" s="1">
+        <v>4041</v>
       </c>
       <c r="L56" s="1">
         <v>1</v>
       </c>
       <c r="M56" s="1">
         <f t="shared" si="3"/>
-        <v>500000</v>
+        <v>1500000</v>
       </c>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
     </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="B57"/>
       <c r="C57" s="1">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F57" s="1">
-        <v>50000</v>
+        <v>1000000</v>
       </c>
       <c r="G57" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="J57" s="1">
         <v>4</v>
       </c>
       <c r="K57" s="1">
-        <v>24</v>
+        <v>205</v>
       </c>
       <c r="L57" s="1">
         <v>1</v>
       </c>
       <c r="M57" s="1">
         <f t="shared" si="3"/>
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="58" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A58" s="1"/>
+      <c r="B58"/>
+      <c r="C58" s="1">
+        <v>51</v>
+      </c>
+      <c r="D58" s="1">
+        <v>0</v>
+      </c>
+      <c r="E58" s="1">
+        <v>20</v>
+      </c>
+      <c r="F58" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G58" s="1">
+        <v>20</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J58" s="1">
+        <v>5</v>
+      </c>
+      <c r="K58" s="1">
+        <v>4040</v>
+      </c>
+      <c r="L58" s="1">
+        <v>500</v>
+      </c>
+      <c r="M58" s="1">
+        <f t="shared" si="3"/>
+        <v>2000000</v>
+      </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A59"/>
+      <c r="B59"/>
       <c r="C59" s="1">
+        <v>52</v>
+      </c>
+      <c r="D59" s="1">
+        <v>0</v>
+      </c>
+      <c r="E59" s="1">
+        <v>15</v>
+      </c>
+      <c r="F59" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G59" s="1">
+        <v>200</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J59" s="1">
+        <v>5</v>
+      </c>
+      <c r="K59" s="1">
+        <v>4039</v>
+      </c>
+      <c r="L59" s="1">
+        <v>1</v>
+      </c>
+      <c r="M59" s="1">
+        <f t="shared" si="3"/>
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A60"/>
+      <c r="B60"/>
+      <c r="C60" s="1">
         <v>53</v>
       </c>
-      <c r="D59" s="1">
-        <v>0</v>
-      </c>
-      <c r="E59" s="1">
-        <v>0</v>
-      </c>
-      <c r="F59" s="1">
-        <v>100000</v>
-      </c>
-      <c r="G59" s="1">
-        <v>10</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J59" s="1">
-        <v>5</v>
-      </c>
-      <c r="K59" s="1">
-        <v>4034</v>
-      </c>
-      <c r="L59" s="1">
-        <v>1</v>
-      </c>
-      <c r="M59" s="1">
-        <f>F59*G59</f>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C60" s="1">
+      <c r="D60" s="1">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1">
+        <v>20</v>
+      </c>
+      <c r="F60" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G60" s="1">
+        <v>200</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J60" s="1">
+        <v>5</v>
+      </c>
+      <c r="K60" s="1">
+        <v>4038</v>
+      </c>
+      <c r="L60" s="1">
+        <v>1</v>
+      </c>
+      <c r="M60" s="1">
+        <f t="shared" si="3"/>
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A61"/>
+      <c r="B61"/>
+      <c r="C61" s="1">
         <v>54</v>
       </c>
-      <c r="D60" s="1">
-        <v>0</v>
-      </c>
-      <c r="E60" s="1">
-        <v>0</v>
-      </c>
-      <c r="F60" s="1">
-        <v>150000</v>
-      </c>
-      <c r="G60" s="1">
-        <v>2</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="J60" s="1">
-        <v>5</v>
-      </c>
-      <c r="K60" s="1">
-        <v>4112</v>
-      </c>
-      <c r="L60" s="1">
-        <v>1</v>
-      </c>
-      <c r="M60" s="1">
-        <f>F60*G60</f>
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C61" s="1">
+      <c r="D61" s="1">
+        <v>0</v>
+      </c>
+      <c r="E61" s="1">
+        <v>0</v>
+      </c>
+      <c r="F61" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G61" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J61" s="1">
+        <v>5</v>
+      </c>
+      <c r="K61" s="1">
+        <v>4022</v>
+      </c>
+      <c r="L61" s="1">
+        <v>100</v>
+      </c>
+      <c r="M61" s="1">
+        <f t="shared" si="3"/>
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A62"/>
+      <c r="B62"/>
+      <c r="C62" s="1">
         <v>55</v>
-      </c>
-      <c r="D61" s="1">
-        <v>0</v>
-      </c>
-      <c r="E61" s="1">
-        <v>10</v>
-      </c>
-      <c r="F61" s="1">
-        <v>100000</v>
-      </c>
-      <c r="G61" s="1">
-        <v>20</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="J61" s="1">
-        <v>5</v>
-      </c>
-      <c r="K61" s="1">
-        <v>4033</v>
-      </c>
-      <c r="L61" s="1">
-        <v>500</v>
-      </c>
-      <c r="M61" s="1">
-        <f>F61*G61</f>
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C62" s="1">
-        <v>56</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
@@ -3652,307 +3645,352 @@
         <v>15</v>
       </c>
       <c r="F62" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G62" s="1">
+        <v>10</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J62" s="1">
+        <v>11</v>
+      </c>
+      <c r="K62" s="1">
+        <v>1998001</v>
+      </c>
+      <c r="L62" s="1">
+        <v>1</v>
+      </c>
+      <c r="M62" s="1">
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
-      <c r="G62" s="1">
-        <v>3</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J62" s="1">
-        <v>4</v>
-      </c>
-      <c r="K62" s="1">
-        <v>29</v>
-      </c>
-      <c r="L62" s="1">
-        <v>1</v>
-      </c>
-      <c r="M62" s="1">
-        <f>F62*G62</f>
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="64" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-      <c r="M64" s="1"/>
+    </row>
+    <row r="63" customHeight="1" spans="1:15">
+      <c r="A63"/>
+      <c r="B63"/>
+      <c r="C63" s="1">
+        <v>56</v>
+      </c>
+      <c r="D63" s="1">
+        <v>0</v>
+      </c>
+      <c r="E63" s="1">
+        <v>15</v>
+      </c>
+      <c r="F63" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G63" s="1">
+        <v>10</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J63" s="1">
+        <v>11</v>
+      </c>
+      <c r="K63" s="1">
+        <v>1998002</v>
+      </c>
+      <c r="L63" s="1">
+        <v>1</v>
+      </c>
+      <c r="M63" s="1">
+        <f t="shared" si="3"/>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="64" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C64" s="1">
+        <v>57</v>
+      </c>
+      <c r="D64" s="1">
+        <v>0</v>
+      </c>
+      <c r="E64" s="1">
+        <v>15</v>
+      </c>
+      <c r="F64" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G64" s="1">
+        <v>10</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J64" s="1">
+        <v>11</v>
+      </c>
+      <c r="K64" s="1">
+        <v>1998003</v>
+      </c>
+      <c r="L64" s="1">
+        <v>1</v>
+      </c>
+      <c r="M64" s="1">
+        <f t="shared" si="3"/>
+        <v>1000000</v>
+      </c>
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
     </row>
-    <row r="65" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
-      <c r="L65" s="1"/>
-      <c r="M65" s="1"/>
+    <row r="65" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C65" s="1">
+        <v>58</v>
+      </c>
+      <c r="D65" s="1">
+        <v>0</v>
+      </c>
+      <c r="E65" s="1">
+        <v>15</v>
+      </c>
+      <c r="F65" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G65" s="1">
+        <v>10</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J65" s="1">
+        <v>11</v>
+      </c>
+      <c r="K65" s="1">
+        <v>1998004</v>
+      </c>
+      <c r="L65" s="1">
+        <v>1</v>
+      </c>
+      <c r="M65" s="1">
+        <f t="shared" si="3"/>
+        <v>1000000</v>
+      </c>
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
     </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="66" customFormat="1" customHeight="1" spans="1:15">
       <c r="C66" s="1">
+        <v>59</v>
+      </c>
+      <c r="D66" s="1">
+        <v>0</v>
+      </c>
+      <c r="E66" s="1">
+        <v>15</v>
+      </c>
+      <c r="F66" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G66" s="1">
+        <v>10</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J66" s="1">
+        <v>11</v>
+      </c>
+      <c r="K66" s="1">
+        <v>1998005</v>
+      </c>
+      <c r="L66" s="1">
+        <v>1</v>
+      </c>
+      <c r="M66" s="1">
+        <f t="shared" si="3"/>
+        <v>1000000</v>
+      </c>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
+    </row>
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A67"/>
+      <c r="B67"/>
+      <c r="C67" s="1">
+        <v>60</v>
+      </c>
+      <c r="D67" s="1">
+        <v>0</v>
+      </c>
+      <c r="E67" s="1">
+        <v>10</v>
+      </c>
+      <c r="F67" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G67" s="1">
+        <v>200</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J67" s="1">
+        <v>5</v>
+      </c>
+      <c r="K67" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L67" s="1">
+        <v>1</v>
+      </c>
+      <c r="M67" s="1">
+        <f t="shared" si="3"/>
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="68" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+    </row>
+    <row r="69" customFormat="1" customHeight="1" spans="1:15">
+      <c r="B69" s="1"/>
+      <c r="C69" s="1">
         <v>102</v>
       </c>
-      <c r="D66" s="1">
-        <v>1</v>
-      </c>
-      <c r="E66" s="1">
-        <v>0</v>
-      </c>
-      <c r="F66" s="1">
+      <c r="D69" s="1">
+        <v>1</v>
+      </c>
+      <c r="E69" s="1">
+        <v>0</v>
+      </c>
+      <c r="F69" s="1">
         <v>100</v>
       </c>
-      <c r="G66" s="1">
-        <f t="shared" ref="G66:G71" si="4">N66*O66</f>
+      <c r="G69" s="1">
+        <f t="shared" ref="G69:G74" si="4">N69*O73</f>
         <v>300</v>
       </c>
-      <c r="H66" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J66" s="1">
-        <v>5</v>
-      </c>
-      <c r="K66" s="1">
+      <c r="H69" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J69" s="1">
+        <v>5</v>
+      </c>
+      <c r="K69" s="1">
         <v>4007</v>
       </c>
-      <c r="L66" s="1">
+      <c r="L69" s="1">
         <v>1000</v>
       </c>
-      <c r="M66" s="1">
-        <f t="shared" ref="M66:M73" si="5">F66*G66</f>
+      <c r="M69" s="1">
+        <f t="shared" ref="M69:M76" si="5">F69*G69</f>
         <v>30000</v>
       </c>
-      <c r="N66" s="1">
-        <v>1</v>
-      </c>
-      <c r="O66" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C67" s="1">
+      <c r="N69" s="1">
+        <v>1</v>
+      </c>
+      <c r="O69" s="1"/>
+    </row>
+    <row r="70" customFormat="1" customHeight="1" spans="1:15">
+      <c r="B70" s="1"/>
+      <c r="C70" s="1">
         <v>103</v>
       </c>
-      <c r="D67" s="1">
-        <v>1</v>
-      </c>
-      <c r="E67" s="1">
-        <v>0</v>
-      </c>
-      <c r="F67" s="1">
+      <c r="D70" s="1">
+        <v>1</v>
+      </c>
+      <c r="E70" s="1">
+        <v>0</v>
+      </c>
+      <c r="F70" s="1">
         <v>100</v>
       </c>
-      <c r="G67" s="1">
+      <c r="G70" s="1">
         <f t="shared" si="4"/>
         <v>500</v>
       </c>
-      <c r="H67" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J67" s="1">
-        <v>5</v>
-      </c>
-      <c r="K67" s="1">
+      <c r="H70" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J70" s="1">
+        <v>5</v>
+      </c>
+      <c r="K70" s="1">
         <v>4101</v>
       </c>
-      <c r="L67" s="1">
+      <c r="L70" s="1">
         <v>1000</v>
       </c>
-      <c r="M67" s="1">
+      <c r="M70" s="1">
         <f t="shared" si="5"/>
         <v>50000</v>
       </c>
-      <c r="N67" s="1">
-        <v>1</v>
-      </c>
-      <c r="O67" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C68" s="1">
+      <c r="N70" s="1">
+        <v>1</v>
+      </c>
+      <c r="O70" s="1"/>
+    </row>
+    <row r="71" customFormat="1" customHeight="1" spans="1:15">
+      <c r="B71" s="1"/>
+      <c r="C71" s="1">
         <v>104</v>
       </c>
-      <c r="D68" s="1">
-        <v>1</v>
-      </c>
-      <c r="E68" s="1">
-        <v>0</v>
-      </c>
-      <c r="F68" s="1">
+      <c r="D71" s="1">
+        <v>1</v>
+      </c>
+      <c r="E71" s="1">
+        <v>0</v>
+      </c>
+      <c r="F71" s="1">
         <v>1000</v>
       </c>
-      <c r="G68" s="1">
+      <c r="G71" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="H68" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J68" s="1">
+      <c r="H71" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J71" s="1">
         <v>15</v>
       </c>
-      <c r="K68" s="1">
+      <c r="K71" s="1">
         <v>4014</v>
       </c>
-      <c r="L68" s="1">
+      <c r="L71" s="1">
         <v>100</v>
-      </c>
-      <c r="M68" s="1">
-        <f t="shared" si="5"/>
-        <v>20000</v>
-      </c>
-      <c r="N68" s="1">
-        <v>1</v>
-      </c>
-      <c r="O68" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C69" s="1">
-        <v>105</v>
-      </c>
-      <c r="D69" s="1">
-        <v>1</v>
-      </c>
-      <c r="E69" s="1">
-        <v>1</v>
-      </c>
-      <c r="F69" s="1">
-        <v>15000</v>
-      </c>
-      <c r="G69" s="1">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J69" s="1">
-        <v>5</v>
-      </c>
-      <c r="K69" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L69" s="1">
-        <v>1</v>
-      </c>
-      <c r="M69" s="1">
-        <f t="shared" si="5"/>
-        <v>120000</v>
-      </c>
-      <c r="N69" s="1">
-        <v>1</v>
-      </c>
-      <c r="O69" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C70" s="1">
-        <v>106</v>
-      </c>
-      <c r="D70" s="1">
-        <v>1</v>
-      </c>
-      <c r="E70" s="1">
-        <v>0</v>
-      </c>
-      <c r="F70" s="1">
-        <v>500</v>
-      </c>
-      <c r="G70" s="1">
-        <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J70" s="1">
-        <v>5</v>
-      </c>
-      <c r="K70" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L70" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M70" s="1">
-        <f t="shared" si="5"/>
-        <v>20000</v>
-      </c>
-      <c r="N70" s="1">
-        <v>1</v>
-      </c>
-      <c r="O70" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C71" s="1">
-        <v>107</v>
-      </c>
-      <c r="D71" s="1">
-        <v>1</v>
-      </c>
-      <c r="E71" s="1">
-        <v>0</v>
-      </c>
-      <c r="F71" s="1">
-        <v>500</v>
-      </c>
-      <c r="G71" s="1">
-        <f t="shared" si="4"/>
-        <v>40</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J71" s="1">
-        <v>5</v>
-      </c>
-      <c r="K71" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L71" s="1">
-        <v>6000000</v>
       </c>
       <c r="M71" s="1">
         <f t="shared" si="5"/>
@@ -3961,349 +3999,362 @@
       <c r="N71" s="1">
         <v>1</v>
       </c>
-      <c r="O71" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O71" s="1"/>
+    </row>
+    <row r="72" customFormat="1" customHeight="1" spans="1:15">
+      <c r="B72" s="1"/>
       <c r="C72" s="1">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D72" s="1">
         <v>1</v>
       </c>
       <c r="E72" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F72" s="1">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="G72" s="1">
-        <v>10</v>
+        <f t="shared" si="4"/>
+        <v>8</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="J72" s="1">
         <v>5</v>
       </c>
       <c r="K72" s="1">
-        <v>4026</v>
+        <v>4019</v>
       </c>
       <c r="L72" s="1">
         <v>1</v>
       </c>
       <c r="M72" s="1">
         <f t="shared" si="5"/>
-        <v>300000</v>
+        <v>120000</v>
       </c>
       <c r="N72" s="1">
         <v>1</v>
       </c>
-      <c r="O72" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="O72" s="1"/>
+    </row>
+    <row r="73" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
       <c r="C73" s="1">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D73" s="1">
         <v>1</v>
       </c>
       <c r="E73" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F73" s="1">
-        <v>30000</v>
+        <v>500</v>
       </c>
       <c r="G73" s="1">
-        <v>10</v>
+        <f t="shared" si="4"/>
+        <v>40</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J73" s="1">
         <v>5</v>
       </c>
       <c r="K73" s="1">
-        <v>4035</v>
+        <v>4001</v>
       </c>
       <c r="L73" s="1">
-        <v>1</v>
+        <v>1000000</v>
       </c>
       <c r="M73" s="1">
         <f t="shared" si="5"/>
+        <v>20000</v>
+      </c>
+      <c r="N73" s="1">
+        <v>1</v>
+      </c>
+      <c r="O73" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="74" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1">
+        <v>107</v>
+      </c>
+      <c r="D74" s="1">
+        <v>1</v>
+      </c>
+      <c r="E74" s="1">
+        <v>0</v>
+      </c>
+      <c r="F74" s="1">
+        <v>500</v>
+      </c>
+      <c r="G74" s="1">
+        <f t="shared" si="4"/>
+        <v>40</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J74" s="1">
+        <v>5</v>
+      </c>
+      <c r="K74" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L74" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M74" s="1">
+        <f t="shared" si="5"/>
+        <v>20000</v>
+      </c>
+      <c r="N74" s="1">
+        <v>1</v>
+      </c>
+      <c r="O74" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="75" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1">
+        <v>108</v>
+      </c>
+      <c r="D75" s="1">
+        <v>1</v>
+      </c>
+      <c r="E75" s="1">
+        <v>6</v>
+      </c>
+      <c r="F75" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G75" s="1">
+        <v>10</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J75" s="1">
+        <v>5</v>
+      </c>
+      <c r="K75" s="1">
+        <v>4026</v>
+      </c>
+      <c r="L75" s="1">
+        <v>1</v>
+      </c>
+      <c r="M75" s="1">
+        <f t="shared" si="5"/>
         <v>300000</v>
       </c>
-    </row>
-    <row r="74" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
-      <c r="L74" s="1"/>
-      <c r="M74" s="1"/>
-      <c r="N74" s="1"/>
-      <c r="O74" s="1"/>
-    </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C75" s="1">
+      <c r="N75" s="1">
+        <v>1</v>
+      </c>
+      <c r="O75" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1">
+        <v>109</v>
+      </c>
+      <c r="D76" s="1">
+        <v>1</v>
+      </c>
+      <c r="E76" s="1">
+        <v>10</v>
+      </c>
+      <c r="F76" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G76" s="1">
+        <v>10</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J76" s="1">
+        <v>5</v>
+      </c>
+      <c r="K76" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L76" s="1">
+        <v>1</v>
+      </c>
+      <c r="M76" s="1">
+        <f t="shared" si="5"/>
+        <v>300000</v>
+      </c>
+      <c r="N76" s="1"/>
+      <c r="O76" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A77" s="1"/>
+      <c r="B77"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+      <c r="O77" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="78" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C78" s="1">
         <v>201</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D78" s="1">
         <v>2</v>
       </c>
-      <c r="E75" s="1">
-        <v>0</v>
-      </c>
-      <c r="F75" s="6">
+      <c r="E78" s="1">
+        <v>0</v>
+      </c>
+      <c r="F78" s="5">
         <v>200</v>
       </c>
-      <c r="G75" s="1">
-        <f t="shared" ref="G75:G80" si="6">N75*O75</f>
+      <c r="G78" s="1">
+        <f t="shared" ref="G78:G83" si="6">N78*O82</f>
         <v>300</v>
       </c>
-      <c r="H75" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J75" s="1">
-        <v>5</v>
-      </c>
-      <c r="K75" s="1">
+      <c r="H78" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J78" s="1">
+        <v>5</v>
+      </c>
+      <c r="K78" s="1">
         <v>4007</v>
       </c>
-      <c r="L75" s="1">
+      <c r="L78" s="1">
         <v>1000</v>
       </c>
-      <c r="M75" s="1">
-        <f t="shared" ref="M75:M82" si="7">F75*G75</f>
+      <c r="M78" s="1">
+        <f t="shared" ref="M78:M85" si="7">F78*G78</f>
         <v>60000</v>
       </c>
-      <c r="N75" s="1">
-        <v>1</v>
-      </c>
-      <c r="O75" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C76" s="1">
+      <c r="N78" s="1">
+        <v>1</v>
+      </c>
+      <c r="O78" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C79" s="1">
         <v>202</v>
       </c>
-      <c r="D76" s="1">
+      <c r="D79" s="1">
         <v>2</v>
       </c>
-      <c r="E76" s="1">
-        <v>0</v>
-      </c>
-      <c r="F76" s="6">
+      <c r="E79" s="1">
+        <v>0</v>
+      </c>
+      <c r="F79" s="5">
         <v>200</v>
       </c>
-      <c r="G76" s="1">
+      <c r="G79" s="1">
         <f t="shared" si="6"/>
         <v>500</v>
       </c>
-      <c r="H76" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J76" s="1">
-        <v>5</v>
-      </c>
-      <c r="K76" s="1">
+      <c r="H79" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J79" s="1">
+        <v>5</v>
+      </c>
+      <c r="K79" s="1">
         <v>4101</v>
       </c>
-      <c r="L76" s="1">
+      <c r="L79" s="1">
         <v>1000</v>
       </c>
-      <c r="M76" s="1">
+      <c r="M79" s="1">
         <f t="shared" si="7"/>
         <v>100000</v>
       </c>
-      <c r="N76" s="1">
-        <v>1</v>
-      </c>
-      <c r="O76" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C77" s="1">
+      <c r="N79" s="1">
+        <v>1</v>
+      </c>
+      <c r="O79" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C80" s="1">
         <v>203</v>
       </c>
-      <c r="D77" s="1">
+      <c r="D80" s="1">
         <v>2</v>
       </c>
-      <c r="E77" s="1">
-        <v>0</v>
-      </c>
-      <c r="F77" s="6">
+      <c r="E80" s="1">
+        <v>0</v>
+      </c>
+      <c r="F80" s="5">
         <v>2000</v>
       </c>
-      <c r="G77" s="1">
+      <c r="G80" s="1">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="H77" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J77" s="1">
+      <c r="H80" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J80" s="1">
         <v>15</v>
       </c>
-      <c r="K77" s="1">
+      <c r="K80" s="1">
         <v>4014</v>
       </c>
-      <c r="L77" s="1">
+      <c r="L80" s="1">
         <v>100</v>
-      </c>
-      <c r="M77" s="1">
-        <f t="shared" si="7"/>
-        <v>40000</v>
-      </c>
-      <c r="N77" s="1">
-        <v>1</v>
-      </c>
-      <c r="O77" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C78" s="1">
-        <v>204</v>
-      </c>
-      <c r="D78" s="1">
-        <v>2</v>
-      </c>
-      <c r="E78" s="1">
-        <v>1</v>
-      </c>
-      <c r="F78" s="6">
-        <v>30000</v>
-      </c>
-      <c r="G78" s="1">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J78" s="1">
-        <v>5</v>
-      </c>
-      <c r="K78" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L78" s="1">
-        <v>1</v>
-      </c>
-      <c r="M78" s="1">
-        <f t="shared" si="7"/>
-        <v>240000</v>
-      </c>
-      <c r="N78" s="1">
-        <v>1</v>
-      </c>
-      <c r="O78" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C79" s="1">
-        <v>205</v>
-      </c>
-      <c r="D79" s="1">
-        <v>2</v>
-      </c>
-      <c r="E79" s="1">
-        <v>0</v>
-      </c>
-      <c r="F79" s="6">
-        <v>1000</v>
-      </c>
-      <c r="G79" s="1">
-        <f t="shared" si="6"/>
-        <v>40</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J79" s="1">
-        <v>5</v>
-      </c>
-      <c r="K79" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L79" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M79" s="1">
-        <f t="shared" si="7"/>
-        <v>40000</v>
-      </c>
-      <c r="N79" s="1">
-        <v>1</v>
-      </c>
-      <c r="O79" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="80" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C80" s="1">
-        <v>206</v>
-      </c>
-      <c r="D80" s="1">
-        <v>2</v>
-      </c>
-      <c r="E80" s="1">
-        <v>0</v>
-      </c>
-      <c r="F80" s="6">
-        <v>1000</v>
-      </c>
-      <c r="G80" s="1">
-        <f t="shared" si="6"/>
-        <v>40</v>
-      </c>
-      <c r="H80" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J80" s="1">
-        <v>5</v>
-      </c>
-      <c r="K80" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L80" s="1">
-        <v>6000000</v>
       </c>
       <c r="M80" s="1">
         <f t="shared" si="7"/>
@@ -4312,349 +4363,351 @@
       <c r="N80" s="1">
         <v>1</v>
       </c>
-      <c r="O80" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="81" s="1" customFormat="1" customHeight="1" spans="3:15">
+    </row>
+    <row r="81" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A81"/>
       <c r="C81" s="1">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D81" s="1">
         <v>2</v>
       </c>
       <c r="E81" s="1">
-        <v>6</v>
-      </c>
-      <c r="F81" s="1">
+        <v>1</v>
+      </c>
+      <c r="F81" s="5">
         <v>30000</v>
       </c>
       <c r="G81" s="1">
-        <v>10</v>
+        <f t="shared" si="6"/>
+        <v>8</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="J81" s="1">
         <v>5</v>
       </c>
       <c r="K81" s="1">
-        <v>4026</v>
+        <v>4019</v>
       </c>
       <c r="L81" s="1">
         <v>1</v>
       </c>
       <c r="M81" s="1">
         <f t="shared" si="7"/>
-        <v>300000</v>
+        <v>240000</v>
       </c>
       <c r="N81" s="1">
         <v>1</v>
       </c>
-      <c r="O81" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" s="1" customFormat="1" customHeight="1" spans="3:15">
+    </row>
+    <row r="82" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C82" s="1">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D82" s="1">
         <v>2</v>
       </c>
       <c r="E82" s="1">
-        <v>10</v>
-      </c>
-      <c r="F82" s="1">
-        <v>30000</v>
+        <v>0</v>
+      </c>
+      <c r="F82" s="5">
+        <v>1000</v>
       </c>
       <c r="G82" s="1">
-        <v>10</v>
+        <f t="shared" si="6"/>
+        <v>40</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J82" s="1">
         <v>5</v>
       </c>
       <c r="K82" s="1">
-        <v>4035</v>
+        <v>4001</v>
       </c>
       <c r="L82" s="1">
-        <v>1</v>
+        <v>1000000</v>
       </c>
       <c r="M82" s="1">
         <f t="shared" si="7"/>
+        <v>40000</v>
+      </c>
+      <c r="N82" s="1">
+        <v>1</v>
+      </c>
+      <c r="O82" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="83" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C83" s="1">
+        <v>206</v>
+      </c>
+      <c r="D83" s="1">
+        <v>2</v>
+      </c>
+      <c r="E83" s="1">
+        <v>0</v>
+      </c>
+      <c r="F83" s="5">
+        <v>1000</v>
+      </c>
+      <c r="G83" s="1">
+        <f t="shared" si="6"/>
+        <v>40</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J83" s="1">
+        <v>5</v>
+      </c>
+      <c r="K83" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L83" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M83" s="1">
+        <f t="shared" si="7"/>
+        <v>40000</v>
+      </c>
+      <c r="N83" s="1">
+        <v>1</v>
+      </c>
+      <c r="O83" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C84" s="1">
+        <v>207</v>
+      </c>
+      <c r="D84" s="1">
+        <v>2</v>
+      </c>
+      <c r="E84" s="1">
+        <v>6</v>
+      </c>
+      <c r="F84" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G84" s="1">
+        <v>10</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J84" s="1">
+        <v>5</v>
+      </c>
+      <c r="K84" s="1">
+        <v>4026</v>
+      </c>
+      <c r="L84" s="1">
+        <v>1</v>
+      </c>
+      <c r="M84" s="1">
+        <f t="shared" si="7"/>
         <v>300000</v>
       </c>
-    </row>
-    <row r="83" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-      <c r="K83" s="1"/>
-      <c r="L83" s="1"/>
-      <c r="M83" s="1"/>
-      <c r="N83" s="1"/>
-      <c r="O83" s="1"/>
-    </row>
-    <row r="84" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C84" s="1">
+      <c r="N84" s="1">
+        <v>1</v>
+      </c>
+      <c r="O84" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C85" s="1">
+        <v>208</v>
+      </c>
+      <c r="D85" s="1">
+        <v>2</v>
+      </c>
+      <c r="E85" s="1">
+        <v>10</v>
+      </c>
+      <c r="F85" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G85" s="1">
+        <v>10</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J85" s="1">
+        <v>5</v>
+      </c>
+      <c r="K85" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L85" s="1">
+        <v>1</v>
+      </c>
+      <c r="M85" s="1">
+        <f t="shared" si="7"/>
+        <v>300000</v>
+      </c>
+      <c r="O85" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A86" s="1"/>
+      <c r="B86"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+      <c r="M86" s="1"/>
+      <c r="N86" s="1"/>
+      <c r="O86" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="87" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C87" s="1">
         <v>211</v>
       </c>
-      <c r="D84" s="1">
+      <c r="D87" s="1">
         <v>3</v>
       </c>
-      <c r="E84" s="1">
-        <v>0</v>
-      </c>
-      <c r="F84" s="1">
+      <c r="E87" s="1">
+        <v>0</v>
+      </c>
+      <c r="F87" s="1">
         <v>400</v>
       </c>
-      <c r="G84" s="1">
-        <f t="shared" ref="G84:G89" si="8">N84*O84</f>
+      <c r="G87" s="1">
+        <f t="shared" ref="G87:G92" si="8">N87*O91</f>
         <v>300</v>
       </c>
-      <c r="H84" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J84" s="1">
-        <v>5</v>
-      </c>
-      <c r="K84" s="1">
+      <c r="H87" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J87" s="1">
+        <v>5</v>
+      </c>
+      <c r="K87" s="1">
         <v>4007</v>
       </c>
-      <c r="L84" s="1">
+      <c r="L87" s="1">
         <v>1000</v>
       </c>
-      <c r="M84" s="1">
-        <f t="shared" ref="M84:M91" si="9">F84*G84</f>
+      <c r="M87" s="1">
+        <f t="shared" ref="M87:M94" si="9">F87*G87</f>
         <v>120000</v>
       </c>
-      <c r="N84" s="1">
-        <v>1</v>
-      </c>
-      <c r="O84" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="85" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C85" s="1">
+      <c r="N87" s="1">
+        <v>1</v>
+      </c>
+      <c r="O87" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="88" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C88" s="1">
         <v>212</v>
       </c>
-      <c r="D85" s="1">
+      <c r="D88" s="1">
         <v>3</v>
       </c>
-      <c r="E85" s="1">
-        <v>0</v>
-      </c>
-      <c r="F85" s="1">
+      <c r="E88" s="1">
+        <v>0</v>
+      </c>
+      <c r="F88" s="1">
         <v>400</v>
       </c>
-      <c r="G85" s="1">
+      <c r="G88" s="1">
         <f t="shared" si="8"/>
         <v>500</v>
       </c>
-      <c r="H85" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J85" s="1">
-        <v>5</v>
-      </c>
-      <c r="K85" s="1">
+      <c r="H88" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J88" s="1">
+        <v>5</v>
+      </c>
+      <c r="K88" s="1">
         <v>4101</v>
       </c>
-      <c r="L85" s="1">
+      <c r="L88" s="1">
         <v>1000</v>
       </c>
-      <c r="M85" s="1">
+      <c r="M88" s="1">
         <f t="shared" si="9"/>
         <v>200000</v>
       </c>
-      <c r="N85" s="1">
-        <v>1</v>
-      </c>
-      <c r="O85" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="86" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C86" s="1">
+      <c r="N88" s="1">
+        <v>1</v>
+      </c>
+      <c r="O88" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C89" s="1">
         <v>213</v>
       </c>
-      <c r="D86" s="1">
+      <c r="D89" s="1">
         <v>3</v>
       </c>
-      <c r="E86" s="1">
-        <v>0</v>
-      </c>
-      <c r="F86" s="1">
+      <c r="E89" s="1">
+        <v>0</v>
+      </c>
+      <c r="F89" s="1">
         <v>4000</v>
       </c>
-      <c r="G86" s="1">
+      <c r="G89" s="1">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="H86" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J86" s="1">
+      <c r="H89" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J89" s="1">
         <v>15</v>
       </c>
-      <c r="K86" s="1">
+      <c r="K89" s="1">
         <v>4014</v>
       </c>
-      <c r="L86" s="1">
+      <c r="L89" s="1">
         <v>100</v>
-      </c>
-      <c r="M86" s="1">
-        <f t="shared" si="9"/>
-        <v>80000</v>
-      </c>
-      <c r="N86" s="1">
-        <v>1</v>
-      </c>
-      <c r="O86" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="87" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C87" s="1">
-        <v>214</v>
-      </c>
-      <c r="D87" s="1">
-        <v>3</v>
-      </c>
-      <c r="E87" s="1">
-        <v>1</v>
-      </c>
-      <c r="F87" s="1">
-        <v>45000</v>
-      </c>
-      <c r="G87" s="1">
-        <f t="shared" si="8"/>
-        <v>8</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J87" s="1">
-        <v>5</v>
-      </c>
-      <c r="K87" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L87" s="1">
-        <v>1</v>
-      </c>
-      <c r="M87" s="1">
-        <f t="shared" si="9"/>
-        <v>360000</v>
-      </c>
-      <c r="N87" s="1">
-        <v>1</v>
-      </c>
-      <c r="O87" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C88" s="1">
-        <v>215</v>
-      </c>
-      <c r="D88" s="1">
-        <v>3</v>
-      </c>
-      <c r="E88" s="1">
-        <v>0</v>
-      </c>
-      <c r="F88" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G88" s="1">
-        <f t="shared" si="8"/>
-        <v>40</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J88" s="1">
-        <v>5</v>
-      </c>
-      <c r="K88" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L88" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M88" s="1">
-        <f t="shared" si="9"/>
-        <v>80000</v>
-      </c>
-      <c r="N88" s="1">
-        <v>1</v>
-      </c>
-      <c r="O88" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="89" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C89" s="1">
-        <v>216</v>
-      </c>
-      <c r="D89" s="1">
-        <v>3</v>
-      </c>
-      <c r="E89" s="1">
-        <v>0</v>
-      </c>
-      <c r="F89" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G89" s="1">
-        <f t="shared" si="8"/>
-        <v>40</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J89" s="1">
-        <v>5</v>
-      </c>
-      <c r="K89" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L89" s="1">
-        <v>6000000</v>
       </c>
       <c r="M89" s="1">
         <f t="shared" si="9"/>
@@ -4663,349 +4716,351 @@
       <c r="N89" s="1">
         <v>1</v>
       </c>
-      <c r="O89" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="90" s="1" customFormat="1" customHeight="1" spans="3:15">
+    </row>
+    <row r="90" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A90"/>
       <c r="C90" s="1">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D90" s="1">
         <v>3</v>
       </c>
       <c r="E90" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F90" s="1">
-        <v>30000</v>
+        <v>45000</v>
       </c>
       <c r="G90" s="1">
-        <v>10</v>
+        <f t="shared" si="8"/>
+        <v>8</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="J90" s="1">
         <v>5</v>
       </c>
       <c r="K90" s="1">
-        <v>4026</v>
+        <v>4019</v>
       </c>
       <c r="L90" s="1">
         <v>1</v>
       </c>
       <c r="M90" s="1">
         <f t="shared" si="9"/>
-        <v>300000</v>
+        <v>360000</v>
       </c>
       <c r="N90" s="1">
         <v>1</v>
       </c>
-      <c r="O90" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91" s="1" customFormat="1" customHeight="1" spans="3:15">
+    </row>
+    <row r="91" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C91" s="1">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D91" s="1">
         <v>3</v>
       </c>
       <c r="E91" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F91" s="1">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="G91" s="1">
-        <v>10</v>
+        <f t="shared" si="8"/>
+        <v>40</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J91" s="1">
         <v>5</v>
       </c>
       <c r="K91" s="1">
-        <v>4035</v>
+        <v>4001</v>
       </c>
       <c r="L91" s="1">
-        <v>1</v>
+        <v>1000000</v>
       </c>
       <c r="M91" s="1">
         <f t="shared" si="9"/>
+        <v>80000</v>
+      </c>
+      <c r="N91" s="1">
+        <v>1</v>
+      </c>
+      <c r="O91" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="92" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C92" s="1">
+        <v>216</v>
+      </c>
+      <c r="D92" s="1">
+        <v>3</v>
+      </c>
+      <c r="E92" s="1">
+        <v>0</v>
+      </c>
+      <c r="F92" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G92" s="1">
+        <f t="shared" si="8"/>
+        <v>40</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J92" s="1">
+        <v>5</v>
+      </c>
+      <c r="K92" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L92" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M92" s="1">
+        <f t="shared" si="9"/>
+        <v>80000</v>
+      </c>
+      <c r="N92" s="1">
+        <v>1</v>
+      </c>
+      <c r="O92" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C93" s="1">
+        <v>217</v>
+      </c>
+      <c r="D93" s="1">
+        <v>3</v>
+      </c>
+      <c r="E93" s="1">
+        <v>6</v>
+      </c>
+      <c r="F93" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G93" s="1">
+        <v>10</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J93" s="1">
+        <v>5</v>
+      </c>
+      <c r="K93" s="1">
+        <v>4026</v>
+      </c>
+      <c r="L93" s="1">
+        <v>1</v>
+      </c>
+      <c r="M93" s="1">
+        <f t="shared" si="9"/>
         <v>300000</v>
       </c>
-    </row>
-    <row r="92" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1"/>
-      <c r="K92" s="1"/>
-      <c r="L92" s="1"/>
-      <c r="M92" s="1"/>
-      <c r="N92" s="1"/>
-      <c r="O92" s="1"/>
-    </row>
-    <row r="93" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C93" s="1">
+      <c r="N93" s="1">
+        <v>1</v>
+      </c>
+      <c r="O93" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C94" s="1">
+        <v>218</v>
+      </c>
+      <c r="D94" s="1">
+        <v>3</v>
+      </c>
+      <c r="E94" s="1">
+        <v>10</v>
+      </c>
+      <c r="F94" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G94" s="1">
+        <v>10</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J94" s="1">
+        <v>5</v>
+      </c>
+      <c r="K94" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L94" s="1">
+        <v>1</v>
+      </c>
+      <c r="M94" s="1">
+        <f t="shared" si="9"/>
+        <v>300000</v>
+      </c>
+      <c r="O94" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A95" s="1"/>
+      <c r="B95"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
+      <c r="K95" s="1"/>
+      <c r="L95" s="1"/>
+      <c r="M95" s="1"/>
+      <c r="N95" s="1"/>
+      <c r="O95" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="96" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C96" s="1">
         <v>221</v>
       </c>
-      <c r="D93" s="1">
+      <c r="D96" s="1">
         <v>4</v>
       </c>
-      <c r="E93" s="1">
-        <v>0</v>
-      </c>
-      <c r="F93" s="6">
+      <c r="E96" s="1">
+        <v>0</v>
+      </c>
+      <c r="F96" s="5">
         <v>600</v>
       </c>
-      <c r="G93" s="1">
-        <f t="shared" ref="G93:G98" si="10">N93*O93</f>
+      <c r="G96" s="1">
+        <f t="shared" ref="G96:G101" si="10">N96*O100</f>
         <v>300</v>
       </c>
-      <c r="H93" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J93" s="1">
-        <v>5</v>
-      </c>
-      <c r="K93" s="1">
+      <c r="H96" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J96" s="1">
+        <v>5</v>
+      </c>
+      <c r="K96" s="1">
         <v>4007</v>
       </c>
-      <c r="L93" s="1">
+      <c r="L96" s="1">
         <v>1000</v>
       </c>
-      <c r="M93" s="1">
-        <f t="shared" ref="M93:M100" si="11">F93*G93</f>
+      <c r="M96" s="1">
+        <f t="shared" ref="M96:M103" si="11">F96*G96</f>
         <v>180000</v>
       </c>
-      <c r="N93" s="1">
-        <v>1</v>
-      </c>
-      <c r="O93" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C94" s="1">
+      <c r="N96" s="1">
+        <v>1</v>
+      </c>
+      <c r="O96" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="97" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C97" s="1">
         <v>222</v>
       </c>
-      <c r="D94" s="1">
+      <c r="D97" s="1">
         <v>4</v>
       </c>
-      <c r="E94" s="1">
-        <v>0</v>
-      </c>
-      <c r="F94" s="6">
+      <c r="E97" s="1">
+        <v>0</v>
+      </c>
+      <c r="F97" s="5">
         <v>600</v>
       </c>
-      <c r="G94" s="1">
+      <c r="G97" s="1">
         <f t="shared" si="10"/>
         <v>500</v>
       </c>
-      <c r="H94" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J94" s="1">
-        <v>5</v>
-      </c>
-      <c r="K94" s="1">
+      <c r="H97" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J97" s="1">
+        <v>5</v>
+      </c>
+      <c r="K97" s="1">
         <v>4101</v>
       </c>
-      <c r="L94" s="1">
+      <c r="L97" s="1">
         <v>1000</v>
       </c>
-      <c r="M94" s="1">
+      <c r="M97" s="1">
         <f t="shared" si="11"/>
         <v>300000</v>
       </c>
-      <c r="N94" s="1">
-        <v>1</v>
-      </c>
-      <c r="O94" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="95" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C95" s="1">
+      <c r="N97" s="1">
+        <v>1</v>
+      </c>
+      <c r="O97" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C98" s="1">
         <v>223</v>
       </c>
-      <c r="D95" s="1">
+      <c r="D98" s="1">
         <v>4</v>
       </c>
-      <c r="E95" s="1">
-        <v>0</v>
-      </c>
-      <c r="F95" s="6">
+      <c r="E98" s="1">
+        <v>0</v>
+      </c>
+      <c r="F98" s="5">
         <v>6000</v>
       </c>
-      <c r="G95" s="1">
+      <c r="G98" s="1">
         <f t="shared" si="10"/>
         <v>20</v>
       </c>
-      <c r="H95" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J95" s="1">
+      <c r="H98" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J98" s="1">
         <v>15</v>
       </c>
-      <c r="K95" s="1">
+      <c r="K98" s="1">
         <v>4014</v>
       </c>
-      <c r="L95" s="1">
+      <c r="L98" s="1">
         <v>100</v>
-      </c>
-      <c r="M95" s="1">
-        <f t="shared" si="11"/>
-        <v>120000</v>
-      </c>
-      <c r="N95" s="1">
-        <v>1</v>
-      </c>
-      <c r="O95" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="96" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C96" s="1">
-        <v>224</v>
-      </c>
-      <c r="D96" s="1">
-        <v>4</v>
-      </c>
-      <c r="E96" s="1">
-        <v>1</v>
-      </c>
-      <c r="F96" s="6">
-        <v>60000</v>
-      </c>
-      <c r="G96" s="1">
-        <f t="shared" si="10"/>
-        <v>8</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J96" s="1">
-        <v>5</v>
-      </c>
-      <c r="K96" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L96" s="1">
-        <v>1</v>
-      </c>
-      <c r="M96" s="1">
-        <f t="shared" si="11"/>
-        <v>480000</v>
-      </c>
-      <c r="N96" s="1">
-        <v>1</v>
-      </c>
-      <c r="O96" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C97" s="1">
-        <v>225</v>
-      </c>
-      <c r="D97" s="1">
-        <v>4</v>
-      </c>
-      <c r="E97" s="1">
-        <v>0</v>
-      </c>
-      <c r="F97" s="6">
-        <v>3000</v>
-      </c>
-      <c r="G97" s="1">
-        <f t="shared" si="10"/>
-        <v>40</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J97" s="1">
-        <v>5</v>
-      </c>
-      <c r="K97" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L97" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M97" s="1">
-        <f t="shared" si="11"/>
-        <v>120000</v>
-      </c>
-      <c r="N97" s="1">
-        <v>1</v>
-      </c>
-      <c r="O97" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="98" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C98" s="1">
-        <v>226</v>
-      </c>
-      <c r="D98" s="1">
-        <v>4</v>
-      </c>
-      <c r="E98" s="1">
-        <v>0</v>
-      </c>
-      <c r="F98" s="6">
-        <v>3000</v>
-      </c>
-      <c r="G98" s="1">
-        <f t="shared" si="10"/>
-        <v>40</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J98" s="1">
-        <v>5</v>
-      </c>
-      <c r="K98" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L98" s="1">
-        <v>6000000</v>
       </c>
       <c r="M98" s="1">
         <f t="shared" si="11"/>
@@ -5014,559 +5069,734 @@
       <c r="N98" s="1">
         <v>1</v>
       </c>
-      <c r="O98" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="99" s="1" customFormat="1" customHeight="1" spans="3:15">
+    </row>
+    <row r="99" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A99"/>
       <c r="C99" s="1">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D99" s="1">
         <v>4</v>
       </c>
       <c r="E99" s="1">
-        <v>6</v>
-      </c>
-      <c r="F99" s="1">
-        <v>30000</v>
+        <v>1</v>
+      </c>
+      <c r="F99" s="5">
+        <v>60000</v>
       </c>
       <c r="G99" s="1">
-        <v>10</v>
+        <f t="shared" si="10"/>
+        <v>8</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="J99" s="1">
         <v>5</v>
       </c>
       <c r="K99" s="1">
-        <v>4026</v>
+        <v>4019</v>
       </c>
       <c r="L99" s="1">
         <v>1</v>
       </c>
       <c r="M99" s="1">
         <f t="shared" si="11"/>
-        <v>300000</v>
+        <v>480000</v>
       </c>
       <c r="N99" s="1">
         <v>1</v>
       </c>
-      <c r="O99" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="100" s="1" customFormat="1" customHeight="1" spans="3:15">
+    </row>
+    <row r="100" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C100" s="1">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D100" s="1">
         <v>4</v>
       </c>
       <c r="E100" s="1">
-        <v>10</v>
-      </c>
-      <c r="F100" s="1">
-        <v>30000</v>
+        <v>0</v>
+      </c>
+      <c r="F100" s="5">
+        <v>3000</v>
       </c>
       <c r="G100" s="1">
-        <v>10</v>
+        <f t="shared" si="10"/>
+        <v>40</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="J100" s="1">
         <v>5</v>
       </c>
       <c r="K100" s="1">
-        <v>4035</v>
+        <v>4001</v>
       </c>
       <c r="L100" s="1">
-        <v>1</v>
+        <v>1000000</v>
       </c>
       <c r="M100" s="1">
         <f t="shared" si="11"/>
+        <v>120000</v>
+      </c>
+      <c r="N100" s="1">
+        <v>1</v>
+      </c>
+      <c r="O100" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="101" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C101" s="1">
+        <v>226</v>
+      </c>
+      <c r="D101" s="1">
+        <v>4</v>
+      </c>
+      <c r="E101" s="1">
+        <v>0</v>
+      </c>
+      <c r="F101" s="5">
+        <v>3000</v>
+      </c>
+      <c r="G101" s="1">
+        <f t="shared" si="10"/>
+        <v>40</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J101" s="1">
+        <v>5</v>
+      </c>
+      <c r="K101" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L101" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M101" s="1">
+        <f t="shared" si="11"/>
+        <v>120000</v>
+      </c>
+      <c r="N101" s="1">
+        <v>1</v>
+      </c>
+      <c r="O101" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="102" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C102" s="1">
+        <v>227</v>
+      </c>
+      <c r="D102" s="1">
+        <v>4</v>
+      </c>
+      <c r="E102" s="1">
+        <v>6</v>
+      </c>
+      <c r="F102" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G102" s="1">
+        <v>10</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J102" s="1">
+        <v>5</v>
+      </c>
+      <c r="K102" s="1">
+        <v>4026</v>
+      </c>
+      <c r="L102" s="1">
+        <v>1</v>
+      </c>
+      <c r="M102" s="1">
+        <f t="shared" si="11"/>
         <v>300000</v>
       </c>
-    </row>
-    <row r="101" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
-      <c r="E101" s="1"/>
-      <c r="F101" s="1"/>
-      <c r="G101" s="1"/>
-      <c r="H101" s="1"/>
-      <c r="I101" s="1"/>
-      <c r="J101" s="1"/>
-      <c r="K101" s="1"/>
-      <c r="L101" s="1"/>
-      <c r="M101" s="1"/>
-      <c r="N101" s="1"/>
-      <c r="O101" s="1"/>
-    </row>
-    <row r="102" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C102" s="1">
+      <c r="N102" s="1">
+        <v>1</v>
+      </c>
+      <c r="O102" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C103" s="1">
+        <v>228</v>
+      </c>
+      <c r="D103" s="1">
+        <v>4</v>
+      </c>
+      <c r="E103" s="1">
+        <v>10</v>
+      </c>
+      <c r="F103" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G103" s="1">
+        <v>10</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J103" s="1">
+        <v>5</v>
+      </c>
+      <c r="K103" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L103" s="1">
+        <v>1</v>
+      </c>
+      <c r="M103" s="1">
+        <f t="shared" si="11"/>
+        <v>300000</v>
+      </c>
+      <c r="O103" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A104" s="1"/>
+      <c r="B104"/>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
+      <c r="K104" s="1"/>
+      <c r="L104" s="1"/>
+      <c r="M104" s="1"/>
+      <c r="N104" s="1"/>
+      <c r="O104" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="105" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C105" s="1">
         <v>231</v>
       </c>
-      <c r="D102" s="1">
-        <v>5</v>
-      </c>
-      <c r="E102" s="1">
-        <v>0</v>
-      </c>
-      <c r="F102" s="1">
+      <c r="D105" s="1">
+        <v>5</v>
+      </c>
+      <c r="E105" s="1">
+        <v>0</v>
+      </c>
+      <c r="F105" s="1">
         <v>800</v>
       </c>
-      <c r="G102" s="1">
-        <f t="shared" ref="G102:G107" si="12">N102*O102</f>
+      <c r="G105" s="1">
+        <f t="shared" ref="G105:G110" si="12">N105*O109</f>
         <v>1200</v>
       </c>
-      <c r="H102" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J102" s="1">
-        <v>5</v>
-      </c>
-      <c r="K102" s="1">
+      <c r="H105" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J105" s="1">
+        <v>5</v>
+      </c>
+      <c r="K105" s="1">
         <v>4007</v>
       </c>
-      <c r="L102" s="1">
+      <c r="L105" s="1">
         <v>1000</v>
       </c>
-      <c r="M102" s="1">
-        <f t="shared" ref="M102:M109" si="13">F102*G102</f>
+      <c r="M105" s="1">
+        <f t="shared" ref="M105:M112" si="13">F105*G105</f>
         <v>960000</v>
       </c>
-      <c r="N102" s="1">
+      <c r="N105" s="1">
         <v>4</v>
       </c>
-      <c r="O102" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="103" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C103" s="1">
+      <c r="O105" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="106" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C106" s="1">
         <v>232</v>
       </c>
-      <c r="D103" s="1">
-        <v>5</v>
-      </c>
-      <c r="E103" s="1">
-        <v>0</v>
-      </c>
-      <c r="F103" s="1">
+      <c r="D106" s="1">
+        <v>5</v>
+      </c>
+      <c r="E106" s="1">
+        <v>0</v>
+      </c>
+      <c r="F106" s="1">
         <v>800</v>
       </c>
-      <c r="G103" s="1">
+      <c r="G106" s="1">
         <f t="shared" si="12"/>
         <v>2000</v>
       </c>
-      <c r="H103" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I103" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J103" s="1">
-        <v>5</v>
-      </c>
-      <c r="K103" s="1">
+      <c r="H106" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J106" s="1">
+        <v>5</v>
+      </c>
+      <c r="K106" s="1">
         <v>4101</v>
       </c>
-      <c r="L103" s="1">
+      <c r="L106" s="1">
         <v>1000</v>
       </c>
-      <c r="M103" s="1">
+      <c r="M106" s="1">
         <f t="shared" si="13"/>
         <v>1600000</v>
       </c>
-      <c r="N103" s="1">
+      <c r="N106" s="1">
         <v>4</v>
       </c>
-      <c r="O103" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="104" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C104" s="1">
+      <c r="O106" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C107" s="1">
         <v>233</v>
       </c>
-      <c r="D104" s="1">
-        <v>5</v>
-      </c>
-      <c r="E104" s="1">
-        <v>0</v>
-      </c>
-      <c r="F104" s="1">
+      <c r="D107" s="1">
+        <v>5</v>
+      </c>
+      <c r="E107" s="1">
+        <v>0</v>
+      </c>
+      <c r="F107" s="1">
         <v>8000</v>
       </c>
-      <c r="G104" s="1">
+      <c r="G107" s="1">
         <f t="shared" si="12"/>
         <v>40</v>
       </c>
-      <c r="H104" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J104" s="1">
+      <c r="H107" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J107" s="1">
         <v>15</v>
       </c>
-      <c r="K104" s="1">
+      <c r="K107" s="1">
         <v>4014</v>
       </c>
-      <c r="L104" s="1">
+      <c r="L107" s="1">
         <v>100</v>
       </c>
-      <c r="M104" s="1">
+      <c r="M107" s="1">
         <f t="shared" si="13"/>
         <v>320000</v>
       </c>
-      <c r="N104" s="1">
+      <c r="N107" s="1">
         <v>4</v>
       </c>
-      <c r="O104" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="105" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C105" s="1">
+    </row>
+    <row r="108" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A108"/>
+      <c r="C108" s="1">
         <v>234</v>
       </c>
-      <c r="D105" s="1">
-        <v>5</v>
-      </c>
-      <c r="E105" s="1">
-        <v>1</v>
-      </c>
-      <c r="F105" s="1">
+      <c r="D108" s="1">
+        <v>5</v>
+      </c>
+      <c r="E108" s="1">
+        <v>1</v>
+      </c>
+      <c r="F108" s="1">
         <v>75000</v>
       </c>
-      <c r="G105" s="1">
+      <c r="G108" s="1">
         <f t="shared" si="12"/>
         <v>32</v>
       </c>
-      <c r="H105" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J105" s="1">
-        <v>5</v>
-      </c>
-      <c r="K105" s="1">
+      <c r="H108" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J108" s="1">
+        <v>5</v>
+      </c>
+      <c r="K108" s="1">
         <v>4019</v>
       </c>
-      <c r="L105" s="1">
-        <v>1</v>
-      </c>
-      <c r="M105" s="1">
+      <c r="L108" s="1">
+        <v>1</v>
+      </c>
+      <c r="M108" s="1">
         <f t="shared" si="13"/>
         <v>2400000</v>
       </c>
-      <c r="N105" s="1">
+      <c r="N108" s="1">
         <v>4</v>
       </c>
-      <c r="O105" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="106" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C106" s="1">
+    </row>
+    <row r="109" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C109" s="1">
         <v>235</v>
       </c>
-      <c r="D106" s="1">
-        <v>5</v>
-      </c>
-      <c r="E106" s="1">
-        <v>0</v>
-      </c>
-      <c r="F106" s="1">
+      <c r="D109" s="1">
+        <v>5</v>
+      </c>
+      <c r="E109" s="1">
+        <v>0</v>
+      </c>
+      <c r="F109" s="1">
         <v>4000</v>
       </c>
-      <c r="G106" s="1">
+      <c r="G109" s="1">
         <f t="shared" si="12"/>
         <v>160</v>
       </c>
-      <c r="H106" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J106" s="1">
-        <v>5</v>
-      </c>
-      <c r="K106" s="1">
+      <c r="H109" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J109" s="1">
+        <v>5</v>
+      </c>
+      <c r="K109" s="1">
         <v>4001</v>
       </c>
-      <c r="L106" s="1">
+      <c r="L109" s="1">
         <v>1000000</v>
       </c>
-      <c r="M106" s="1">
+      <c r="M109" s="1">
         <f t="shared" si="13"/>
         <v>640000</v>
       </c>
-      <c r="N106" s="1">
+      <c r="N109" s="1">
         <v>4</v>
       </c>
-      <c r="O106" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="107" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C107" s="1">
+      <c r="O109" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="110" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C110" s="1">
         <v>236</v>
       </c>
-      <c r="D107" s="1">
-        <v>5</v>
-      </c>
-      <c r="E107" s="1">
-        <v>0</v>
-      </c>
-      <c r="F107" s="1">
+      <c r="D110" s="1">
+        <v>5</v>
+      </c>
+      <c r="E110" s="1">
+        <v>0</v>
+      </c>
+      <c r="F110" s="1">
         <v>4000</v>
       </c>
-      <c r="G107" s="1">
+      <c r="G110" s="1">
         <f t="shared" si="12"/>
         <v>160</v>
       </c>
-      <c r="H107" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J107" s="1">
-        <v>5</v>
-      </c>
-      <c r="K107" s="1">
+      <c r="H110" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J110" s="1">
+        <v>5</v>
+      </c>
+      <c r="K110" s="1">
         <v>4002</v>
       </c>
-      <c r="L107" s="1">
+      <c r="L110" s="1">
         <v>6000000</v>
       </c>
-      <c r="M107" s="1">
+      <c r="M110" s="1">
         <f t="shared" si="13"/>
         <v>640000</v>
       </c>
-      <c r="N107" s="1">
+      <c r="N110" s="1">
         <v>4</v>
       </c>
-      <c r="O107" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="108" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C108" s="1">
+      <c r="O110" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="111" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C111" s="1">
         <v>237</v>
       </c>
-      <c r="D108" s="1">
-        <v>5</v>
-      </c>
-      <c r="E108" s="1">
+      <c r="D111" s="1">
+        <v>5</v>
+      </c>
+      <c r="E111" s="1">
         <v>6</v>
       </c>
-      <c r="F108" s="1">
+      <c r="F111" s="1">
         <v>30000</v>
       </c>
-      <c r="G108" s="1">
+      <c r="G111" s="1">
         <v>10</v>
       </c>
-      <c r="H108" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I108" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J108" s="1">
-        <v>5</v>
-      </c>
-      <c r="K108" s="1">
+      <c r="H111" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J111" s="1">
+        <v>5</v>
+      </c>
+      <c r="K111" s="1">
         <v>4026</v>
       </c>
-      <c r="L108" s="1">
-        <v>1</v>
-      </c>
-      <c r="M108" s="1">
+      <c r="L111" s="1">
+        <v>1</v>
+      </c>
+      <c r="M111" s="1">
         <f t="shared" si="13"/>
         <v>300000</v>
       </c>
-      <c r="N108" s="1">
-        <v>1</v>
-      </c>
-      <c r="O108" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="109" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C109" s="1">
+      <c r="N111" s="1">
+        <v>1</v>
+      </c>
+      <c r="O111" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C112" s="1">
         <v>238</v>
       </c>
-      <c r="D109" s="1">
-        <v>5</v>
-      </c>
-      <c r="E109" s="1">
+      <c r="D112" s="1">
+        <v>5</v>
+      </c>
+      <c r="E112" s="1">
         <v>10</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F112" s="1">
         <v>30000</v>
       </c>
-      <c r="G109" s="1">
+      <c r="G112" s="1">
         <v>10</v>
       </c>
-      <c r="H109" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J109" s="1">
-        <v>5</v>
-      </c>
-      <c r="K109" s="1">
+      <c r="H112" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J112" s="1">
+        <v>5</v>
+      </c>
+      <c r="K112" s="1">
         <v>4035</v>
       </c>
-      <c r="L109" s="1">
-        <v>1</v>
-      </c>
-      <c r="M109" s="1">
+      <c r="L112" s="1">
+        <v>1</v>
+      </c>
+      <c r="M112" s="1">
         <f t="shared" si="13"/>
         <v>300000</v>
       </c>
-    </row>
-    <row r="110" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
-      <c r="E110" s="1"/>
-      <c r="F110" s="1"/>
-      <c r="G110" s="1"/>
-      <c r="H110" s="1"/>
-      <c r="I110" s="1"/>
-      <c r="J110" s="1"/>
-      <c r="K110" s="1"/>
-      <c r="L110" s="1"/>
-      <c r="M110" s="1"/>
-    </row>
-    <row r="111" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C111" s="1">
+      <c r="O112" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A113" s="1"/>
+      <c r="B113"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1"/>
+      <c r="K113" s="1"/>
+      <c r="L113" s="1"/>
+      <c r="M113" s="1"/>
+      <c r="N113"/>
+      <c r="O113" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="114" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C114" s="1">
         <v>999</v>
       </c>
-      <c r="D111" s="1">
-        <v>0</v>
-      </c>
-      <c r="E111" s="1">
-        <v>0</v>
-      </c>
-      <c r="F111" s="1">
+      <c r="D114" s="1">
+        <v>0</v>
+      </c>
+      <c r="E114" s="1">
+        <v>0</v>
+      </c>
+      <c r="F114" s="1">
         <v>1000</v>
       </c>
-      <c r="G111" s="1">
+      <c r="G114" s="1">
         <v>50</v>
       </c>
-      <c r="H111" s="1" t="s">
+      <c r="H114" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="I111" s="1" t="s">
+      <c r="I114" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="J111" s="1">
-        <v>5</v>
-      </c>
-      <c r="K111" s="1">
+      <c r="J114" s="1">
+        <v>5</v>
+      </c>
+      <c r="K114" s="1">
         <v>4006</v>
       </c>
-      <c r="L111" s="1">
+      <c r="L114" s="1">
         <v>1000</v>
       </c>
-      <c r="M111" s="1">
-        <f t="shared" ref="M111:M113" si="14">F111*G111</f>
+      <c r="M114" s="1">
+        <f t="shared" ref="M114:M116" si="14">F114*G114</f>
         <v>50000</v>
       </c>
-    </row>
-    <row r="112" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C112" s="1">
+      <c r="O114" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="115" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C115" s="1">
         <v>1000</v>
       </c>
-      <c r="D112" s="1">
-        <v>0</v>
-      </c>
-      <c r="E112" s="1">
-        <v>0</v>
-      </c>
-      <c r="F112" s="1">
+      <c r="D115" s="1">
+        <v>0</v>
+      </c>
+      <c r="E115" s="1">
+        <v>0</v>
+      </c>
+      <c r="F115" s="1">
         <v>2000</v>
       </c>
-      <c r="G112" s="1">
+      <c r="G115" s="1">
         <v>1000</v>
       </c>
-      <c r="H112" s="1" t="s">
+      <c r="H115" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I112" s="1" t="s">
+      <c r="I115" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="J112" s="1">
-        <v>5</v>
-      </c>
-      <c r="K112" s="1">
+      <c r="J115" s="1">
+        <v>5</v>
+      </c>
+      <c r="K115" s="1">
         <v>4010</v>
       </c>
-      <c r="L112" s="1">
-        <v>5</v>
-      </c>
-      <c r="M112" s="1">
+      <c r="L115" s="1">
+        <v>5</v>
+      </c>
+      <c r="M115" s="1">
         <f t="shared" si="14"/>
         <v>2000000</v>
       </c>
-    </row>
-    <row r="113" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C113" s="1">
+      <c r="O115" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C116" s="1">
         <v>1001</v>
       </c>
-      <c r="D113" s="1">
-        <v>0</v>
-      </c>
-      <c r="E113" s="1">
-        <v>0</v>
-      </c>
-      <c r="F113" s="1">
+      <c r="D116" s="1">
+        <v>0</v>
+      </c>
+      <c r="E116" s="1">
+        <v>0</v>
+      </c>
+      <c r="F116" s="1">
         <v>2000</v>
       </c>
-      <c r="G113" s="1">
+      <c r="G116" s="1">
         <v>50</v>
       </c>
-      <c r="H113" s="1" t="s">
+      <c r="H116" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="I113" s="1" t="s">
+      <c r="I116" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J113" s="1">
-        <v>5</v>
-      </c>
-      <c r="K113" s="1">
+      <c r="J116" s="1">
+        <v>5</v>
+      </c>
+      <c r="K116" s="1">
         <v>4102</v>
       </c>
-      <c r="L113" s="1">
+      <c r="L116" s="1">
         <v>20</v>
       </c>
-      <c r="M113" s="1">
+      <c r="M116" s="1">
         <f t="shared" si="14"/>
         <v>100000</v>
       </c>
+    </row>
+    <row r="117" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A117"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
+      <c r="E117" s="1"/>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1"/>
+      <c r="K117" s="1"/>
+      <c r="L117" s="1"/>
+      <c r="M117" s="1"/>
+      <c r="N117" s="1"/>
+      <c r="O117"/>
+    </row>
+    <row r="122" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A122" s="1"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1"/>
+      <c r="K122" s="1"/>
+      <c r="L122" s="1"/>
+      <c r="M122" s="1"/>
+      <c r="N122" s="1"/>
+      <c r="O122" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="158">
   <si>
     <t>#</t>
   </si>
@@ -392,6 +392,12 @@
     <t>炼神丹*500</t>
   </si>
   <si>
+    <t>兑换传奇精华</t>
+  </si>
+  <si>
+    <t>传奇精华</t>
+  </si>
+  <si>
     <t>不朽精华</t>
   </si>
   <si>
@@ -404,6 +410,9 @@
     <t>混沌精华*1</t>
   </si>
   <si>
+    <t>宠物口粮*100</t>
+  </si>
+  <si>
     <t>仙鉴青龙</t>
   </si>
   <si>
@@ -432,12 +441,6 @@
   </si>
   <si>
     <t>仙鉴麒麟*1</t>
-  </si>
-  <si>
-    <t>兑换传奇精华</t>
-  </si>
-  <si>
-    <t>传奇精华</t>
   </si>
   <si>
     <t>兑换四格碎片*1000</t>
@@ -1508,7 +1511,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O122"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1638,7 +1641,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="1">
-        <v>888</v>
+        <v>388</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>14</v>
@@ -1657,7 +1660,7 @@
       </c>
       <c r="M6" s="1">
         <f t="shared" ref="M6:M14" si="0">F6*G6</f>
-        <v>266400</v>
+        <v>116400</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:13">
@@ -1674,7 +1677,7 @@
         <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>888</v>
+        <v>388</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>16</v>
@@ -1693,7 +1696,7 @@
       </c>
       <c r="M7" s="1">
         <f t="shared" si="0"/>
-        <v>266400</v>
+        <v>116400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1710,7 +1713,7 @@
         <v>13</v>
       </c>
       <c r="G8" s="1">
-        <v>888</v>
+        <v>388</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>18</v>
@@ -1729,7 +1732,7 @@
       </c>
       <c r="M8" s="1">
         <f t="shared" si="0"/>
-        <v>266400</v>
+        <v>116400</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:13">
@@ -3518,9 +3521,8 @@
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A59"/>
-      <c r="B59"/>
+    <row r="59" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A59" s="1"/>
       <c r="C59" s="1">
         <v>52</v>
       </c>
@@ -3528,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F59" s="1">
         <v>30000</v>
@@ -3546,15 +3548,17 @@
         <v>5</v>
       </c>
       <c r="K59" s="1">
-        <v>4039</v>
+        <v>4035</v>
       </c>
       <c r="L59" s="1">
         <v>1</v>
       </c>
       <c r="M59" s="1">
-        <f t="shared" si="3"/>
+        <f>F59*G59</f>
         <v>6000000</v>
       </c>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A60"/>
@@ -3566,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F60" s="1">
         <v>30000</v>
@@ -3584,13 +3588,13 @@
         <v>5</v>
       </c>
       <c r="K60" s="1">
-        <v>4038</v>
+        <v>4039</v>
       </c>
       <c r="L60" s="1">
         <v>1</v>
       </c>
       <c r="M60" s="1">
-        <f t="shared" si="3"/>
+        <f>F60*G60</f>
         <v>6000000</v>
       </c>
     </row>
@@ -3604,32 +3608,32 @@
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F61" s="1">
-        <v>1000</v>
+        <v>30000</v>
       </c>
       <c r="G61" s="1">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="J61" s="1">
         <v>5</v>
       </c>
       <c r="K61" s="1">
-        <v>4022</v>
+        <v>4038</v>
       </c>
       <c r="L61" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M61" s="1">
-        <f t="shared" si="3"/>
-        <v>3000000</v>
+        <f>F61*G61</f>
+        <v>6000000</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3642,35 +3646,35 @@
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F62" s="1">
-        <v>100000</v>
+        <v>1000</v>
       </c>
       <c r="G62" s="1">
-        <v>10</v>
+        <v>3000</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J62" s="1">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K62" s="1">
-        <v>1998001</v>
+        <v>4022</v>
       </c>
       <c r="L62" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M62" s="1">
-        <f t="shared" si="3"/>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="1:15">
+        <f>F62*G62</f>
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A63"/>
       <c r="B63"/>
       <c r="C63" s="1">
@@ -3689,26 +3693,28 @@
         <v>10</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J63" s="1">
         <v>11</v>
       </c>
       <c r="K63" s="1">
-        <v>1998002</v>
+        <v>1998001</v>
       </c>
       <c r="L63" s="1">
         <v>1</v>
       </c>
       <c r="M63" s="1">
-        <f t="shared" si="3"/>
+        <f>F63*G63</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="64" customFormat="1" customHeight="1" spans="1:15">
+    <row r="64" customHeight="1" spans="1:15">
+      <c r="A64"/>
+      <c r="B64"/>
       <c r="C64" s="1">
         <v>57</v>
       </c>
@@ -3725,26 +3731,24 @@
         <v>10</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J64" s="1">
         <v>11</v>
       </c>
       <c r="K64" s="1">
-        <v>1998003</v>
+        <v>1998002</v>
       </c>
       <c r="L64" s="1">
         <v>1</v>
       </c>
       <c r="M64" s="1">
-        <f t="shared" si="3"/>
+        <f>F64*G64</f>
         <v>1000000</v>
       </c>
-      <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="1:15">
       <c r="C65" s="1">
@@ -3763,22 +3767,22 @@
         <v>10</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J65" s="1">
         <v>11</v>
       </c>
       <c r="K65" s="1">
-        <v>1998004</v>
+        <v>1998003</v>
       </c>
       <c r="L65" s="1">
         <v>1</v>
       </c>
       <c r="M65" s="1">
-        <f t="shared" si="3"/>
+        <f>F65*G65</f>
         <v>1000000</v>
       </c>
       <c r="N65" s="1"/>
@@ -3801,30 +3805,28 @@
         <v>10</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J66" s="1">
         <v>11</v>
       </c>
       <c r="K66" s="1">
-        <v>1998005</v>
+        <v>1998004</v>
       </c>
       <c r="L66" s="1">
         <v>1</v>
       </c>
       <c r="M66" s="1">
-        <f t="shared" si="3"/>
+        <f>F66*G66</f>
         <v>1000000</v>
       </c>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
     </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A67"/>
-      <c r="B67"/>
+    <row r="67" customFormat="1" customHeight="1" spans="1:15">
       <c r="C67" s="1">
         <v>60</v>
       </c>
@@ -3832,95 +3834,59 @@
         <v>0</v>
       </c>
       <c r="E67" s="1">
+        <v>15</v>
+      </c>
+      <c r="F67" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G67" s="1">
         <v>10</v>
       </c>
-      <c r="F67" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G67" s="1">
-        <v>200</v>
-      </c>
       <c r="H67" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J67" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K67" s="1">
-        <v>4035</v>
+        <v>1998005</v>
       </c>
       <c r="L67" s="1">
         <v>1</v>
       </c>
       <c r="M67" s="1">
-        <f t="shared" si="3"/>
-        <v>6000000</v>
-      </c>
-    </row>
-    <row r="68" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
+        <f>F67*G67</f>
+        <v>1000000</v>
+      </c>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
+    </row>
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A68"/>
+      <c r="B68"/>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="1:15">
-      <c r="B69" s="1"/>
-      <c r="C69" s="1">
-        <v>102</v>
-      </c>
-      <c r="D69" s="1">
-        <v>1</v>
-      </c>
-      <c r="E69" s="1">
-        <v>0</v>
-      </c>
-      <c r="F69" s="1">
-        <v>100</v>
-      </c>
-      <c r="G69" s="1">
-        <f t="shared" ref="G69:G74" si="4">N69*O73</f>
-        <v>300</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J69" s="1">
-        <v>5</v>
-      </c>
-      <c r="K69" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L69" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M69" s="1">
-        <f t="shared" ref="M69:M76" si="5">F69*G69</f>
-        <v>30000</v>
-      </c>
-      <c r="N69" s="1">
-        <v>1</v>
-      </c>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
       <c r="O69" s="1"/>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="1:15">
       <c r="B70" s="1"/>
       <c r="C70" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D70" s="1">
         <v>1</v>
@@ -3932,27 +3898,27 @@
         <v>100</v>
       </c>
       <c r="G70" s="1">
-        <f t="shared" si="4"/>
-        <v>500</v>
+        <f t="shared" ref="G70:G75" si="4">N70*O74</f>
+        <v>300</v>
       </c>
       <c r="H70" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I70" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I70" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="J70" s="1">
         <v>5</v>
       </c>
       <c r="K70" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="L70" s="1">
         <v>1000</v>
       </c>
       <c r="M70" s="1">
-        <f t="shared" si="5"/>
-        <v>50000</v>
+        <f t="shared" ref="M70:M77" si="5">F70*G70</f>
+        <v>30000</v>
       </c>
       <c r="N70" s="1">
         <v>1</v>
@@ -3962,7 +3928,7 @@
     <row r="71" customFormat="1" customHeight="1" spans="1:15">
       <c r="B71" s="1"/>
       <c r="C71" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D71" s="1">
         <v>1</v>
@@ -3971,30 +3937,30 @@
         <v>0</v>
       </c>
       <c r="F71" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="G71" s="1">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="H71" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="I71" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="J71" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K71" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="L71" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="M71" s="1">
         <f t="shared" si="5"/>
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="N71" s="1">
         <v>1</v>
@@ -4004,39 +3970,39 @@
     <row r="72" customFormat="1" customHeight="1" spans="1:15">
       <c r="B72" s="1"/>
       <c r="C72" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D72" s="1">
         <v>1</v>
       </c>
       <c r="E72" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" s="1">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="G72" s="1">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H72" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I72" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="I72" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="J72" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K72" s="1">
-        <v>4019</v>
+        <v>4014</v>
       </c>
       <c r="L72" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M72" s="1">
         <f t="shared" si="5"/>
-        <v>120000</v>
+        <v>20000</v>
       </c>
       <c r="N72" s="1">
         <v>1</v>
@@ -4044,55 +4010,52 @@
       <c r="O72" s="1"/>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D73" s="1">
         <v>1</v>
       </c>
       <c r="E73" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="1">
-        <v>500</v>
+        <v>15000</v>
       </c>
       <c r="G73" s="1">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H73" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I73" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="I73" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="J73" s="1">
         <v>5</v>
       </c>
       <c r="K73" s="1">
-        <v>4001</v>
+        <v>4019</v>
       </c>
       <c r="L73" s="1">
-        <v>1000000</v>
+        <v>1</v>
       </c>
       <c r="M73" s="1">
         <f t="shared" si="5"/>
-        <v>20000</v>
+        <v>120000</v>
       </c>
       <c r="N73" s="1">
         <v>1</v>
       </c>
-      <c r="O73" s="1">
-        <v>300</v>
-      </c>
+      <c r="O73" s="1"/>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="1:15">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D74" s="1">
         <v>1</v>
@@ -4108,19 +4071,19 @@
         <v>40</v>
       </c>
       <c r="H74" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I74" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="J74" s="1">
         <v>5</v>
       </c>
       <c r="K74" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L74" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M74" s="1">
         <f t="shared" si="5"/>
@@ -4130,64 +4093,65 @@
         <v>1</v>
       </c>
       <c r="O74" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="1:15">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D75" s="1">
         <v>1</v>
       </c>
       <c r="E75" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F75" s="1">
-        <v>30000</v>
+        <v>500</v>
       </c>
       <c r="G75" s="1">
-        <v>10</v>
+        <f t="shared" si="4"/>
+        <v>40</v>
       </c>
       <c r="H75" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I75" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="I75" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="J75" s="1">
         <v>5</v>
       </c>
       <c r="K75" s="1">
-        <v>4026</v>
+        <v>4002</v>
       </c>
       <c r="L75" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M75" s="1">
         <f t="shared" si="5"/>
-        <v>300000</v>
+        <v>20000</v>
       </c>
       <c r="N75" s="1">
         <v>1</v>
       </c>
       <c r="O75" s="1">
-        <v>20</v>
+        <v>500</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="1:15">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D76" s="1">
         <v>1</v>
       </c>
       <c r="E76" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F76" s="1">
         <v>30000</v>
@@ -4196,16 +4160,16 @@
         <v>10</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="J76" s="1">
         <v>5</v>
       </c>
       <c r="K76" s="1">
-        <v>4035</v>
+        <v>4026</v>
       </c>
       <c r="L76" s="1">
         <v>1</v>
@@ -4214,76 +4178,77 @@
         <f t="shared" si="5"/>
         <v>300000</v>
       </c>
-      <c r="N76" s="1"/>
+      <c r="N76" s="1">
+        <v>1</v>
+      </c>
       <c r="O76" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" customFormat="1" customHeight="1" spans="1:15">
       <c r="A77" s="1"/>
-      <c r="B77"/>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
-      <c r="K77" s="1"/>
-      <c r="L77" s="1"/>
-      <c r="M77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1">
+        <v>109</v>
+      </c>
+      <c r="D77" s="1">
+        <v>1</v>
+      </c>
+      <c r="E77" s="1">
+        <v>10</v>
+      </c>
+      <c r="F77" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G77" s="1">
+        <v>10</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J77" s="1">
+        <v>5</v>
+      </c>
+      <c r="K77" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L77" s="1">
+        <v>1</v>
+      </c>
+      <c r="M77" s="1">
+        <f t="shared" si="5"/>
+        <v>300000</v>
+      </c>
       <c r="N77" s="1"/>
       <c r="O77" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C78" s="1">
-        <v>201</v>
-      </c>
-      <c r="D78" s="1">
-        <v>2</v>
-      </c>
-      <c r="E78" s="1">
-        <v>0</v>
-      </c>
-      <c r="F78" s="5">
-        <v>200</v>
-      </c>
-      <c r="G78" s="1">
-        <f t="shared" ref="G78:G83" si="6">N78*O82</f>
-        <v>300</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J78" s="1">
-        <v>5</v>
-      </c>
-      <c r="K78" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L78" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M78" s="1">
-        <f t="shared" ref="M78:M85" si="7">F78*G78</f>
-        <v>60000</v>
-      </c>
-      <c r="N78" s="1">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A78" s="1"/>
+      <c r="B78"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1"/>
+      <c r="N78" s="1"/>
       <c r="O78" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C79" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D79" s="1">
         <v>2</v>
@@ -4295,162 +4260,162 @@
         <v>200</v>
       </c>
       <c r="G79" s="1">
+        <f t="shared" ref="G79:G84" si="6">N79*O83</f>
+        <v>300</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J79" s="1">
+        <v>5</v>
+      </c>
+      <c r="K79" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L79" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M79" s="1">
+        <f t="shared" ref="M79:M86" si="7">F79*G79</f>
+        <v>60000</v>
+      </c>
+      <c r="N79" s="1">
+        <v>1</v>
+      </c>
+      <c r="O79" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="80" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C80" s="1">
+        <v>202</v>
+      </c>
+      <c r="D80" s="1">
+        <v>2</v>
+      </c>
+      <c r="E80" s="1">
+        <v>0</v>
+      </c>
+      <c r="F80" s="5">
+        <v>200</v>
+      </c>
+      <c r="G80" s="1">
         <f t="shared" si="6"/>
         <v>500</v>
       </c>
-      <c r="H79" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I79" s="1" t="s">
+      <c r="H80" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J79" s="1">
-        <v>5</v>
-      </c>
-      <c r="K79" s="1">
+      <c r="I80" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J80" s="1">
+        <v>5</v>
+      </c>
+      <c r="K80" s="1">
         <v>4101</v>
       </c>
-      <c r="L79" s="1">
+      <c r="L80" s="1">
         <v>1000</v>
       </c>
-      <c r="M79" s="1">
+      <c r="M80" s="1">
         <f t="shared" si="7"/>
         <v>100000</v>
       </c>
-      <c r="N79" s="1">
-        <v>1</v>
-      </c>
-      <c r="O79" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C80" s="1">
+      <c r="N80" s="1">
+        <v>1</v>
+      </c>
+      <c r="O80" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C81" s="1">
         <v>203</v>
       </c>
-      <c r="D80" s="1">
+      <c r="D81" s="1">
         <v>2</v>
       </c>
-      <c r="E80" s="1">
-        <v>0</v>
-      </c>
-      <c r="F80" s="5">
+      <c r="E81" s="1">
+        <v>0</v>
+      </c>
+      <c r="F81" s="5">
         <v>2000</v>
       </c>
-      <c r="G80" s="1">
+      <c r="G81" s="1">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="H80" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I80" s="1" t="s">
+      <c r="H81" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="J80" s="1">
+      <c r="I81" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J81" s="1">
         <v>15</v>
       </c>
-      <c r="K80" s="1">
+      <c r="K81" s="1">
         <v>4014</v>
       </c>
-      <c r="L80" s="1">
+      <c r="L81" s="1">
         <v>100</v>
       </c>
-      <c r="M80" s="1">
+      <c r="M81" s="1">
         <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="N80" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A81"/>
-      <c r="C81" s="1">
+      <c r="N81" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A82"/>
+      <c r="C82" s="1">
         <v>204</v>
       </c>
-      <c r="D81" s="1">
+      <c r="D82" s="1">
         <v>2</v>
       </c>
-      <c r="E81" s="1">
-        <v>1</v>
-      </c>
-      <c r="F81" s="5">
+      <c r="E82" s="1">
+        <v>1</v>
+      </c>
+      <c r="F82" s="5">
         <v>30000</v>
       </c>
-      <c r="G81" s="1">
+      <c r="G82" s="1">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="H81" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I81" s="1" t="s">
+      <c r="H82" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="J81" s="1">
-        <v>5</v>
-      </c>
-      <c r="K81" s="1">
+      <c r="I82" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J82" s="1">
+        <v>5</v>
+      </c>
+      <c r="K82" s="1">
         <v>4019</v>
       </c>
-      <c r="L81" s="1">
-        <v>1</v>
-      </c>
-      <c r="M81" s="1">
+      <c r="L82" s="1">
+        <v>1</v>
+      </c>
+      <c r="M82" s="1">
         <f t="shared" si="7"/>
         <v>240000</v>
       </c>
-      <c r="N81" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C82" s="1">
-        <v>205</v>
-      </c>
-      <c r="D82" s="1">
-        <v>2</v>
-      </c>
-      <c r="E82" s="1">
-        <v>0</v>
-      </c>
-      <c r="F82" s="5">
-        <v>1000</v>
-      </c>
-      <c r="G82" s="1">
-        <f t="shared" si="6"/>
-        <v>40</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J82" s="1">
-        <v>5</v>
-      </c>
-      <c r="K82" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L82" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M82" s="1">
-        <f t="shared" si="7"/>
-        <v>40000</v>
-      </c>
       <c r="N82" s="1">
         <v>1</v>
-      </c>
-      <c r="O82" s="1">
-        <v>300</v>
       </c>
     </row>
     <row r="83" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C83" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D83" s="1">
         <v>2</v>
@@ -4466,19 +4431,19 @@
         <v>40</v>
       </c>
       <c r="H83" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I83" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I83" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="J83" s="1">
         <v>5</v>
       </c>
       <c r="K83" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L83" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M83" s="1">
         <f t="shared" si="7"/>
@@ -4488,60 +4453,61 @@
         <v>1</v>
       </c>
       <c r="O83" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="84" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C84" s="1">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D84" s="1">
         <v>2</v>
       </c>
       <c r="E84" s="1">
-        <v>6</v>
-      </c>
-      <c r="F84" s="1">
-        <v>30000</v>
+        <v>0</v>
+      </c>
+      <c r="F84" s="5">
+        <v>1000</v>
       </c>
       <c r="G84" s="1">
-        <v>10</v>
+        <f t="shared" si="6"/>
+        <v>40</v>
       </c>
       <c r="H84" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I84" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="I84" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="J84" s="1">
         <v>5</v>
       </c>
       <c r="K84" s="1">
-        <v>4026</v>
+        <v>4002</v>
       </c>
       <c r="L84" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M84" s="1">
         <f t="shared" si="7"/>
-        <v>300000</v>
+        <v>40000</v>
       </c>
       <c r="N84" s="1">
         <v>1</v>
       </c>
       <c r="O84" s="1">
-        <v>20</v>
+        <v>500</v>
       </c>
     </row>
     <row r="85" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C85" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D85" s="1">
         <v>2</v>
       </c>
       <c r="E85" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F85" s="1">
         <v>30000</v>
@@ -4550,16 +4516,16 @@
         <v>10</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="J85" s="1">
         <v>5</v>
       </c>
       <c r="K85" s="1">
-        <v>4035</v>
+        <v>4026</v>
       </c>
       <c r="L85" s="1">
         <v>1</v>
@@ -4568,75 +4534,74 @@
         <f t="shared" si="7"/>
         <v>300000</v>
       </c>
+      <c r="N85" s="1">
+        <v>1</v>
+      </c>
       <c r="O85" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C86" s="1">
+        <v>208</v>
+      </c>
+      <c r="D86" s="1">
+        <v>2</v>
+      </c>
+      <c r="E86" s="1">
+        <v>10</v>
+      </c>
+      <c r="F86" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G86" s="1">
+        <v>10</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J86" s="1">
+        <v>5</v>
+      </c>
+      <c r="K86" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L86" s="1">
+        <v>1</v>
+      </c>
+      <c r="M86" s="1">
+        <f t="shared" si="7"/>
+        <v>300000</v>
+      </c>
+      <c r="O86" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="86" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A86" s="1"/>
-      <c r="B86"/>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
-      <c r="K86" s="1"/>
-      <c r="L86" s="1"/>
-      <c r="M86" s="1"/>
-      <c r="N86" s="1"/>
-      <c r="O86" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="87" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C87" s="1">
-        <v>211</v>
-      </c>
-      <c r="D87" s="1">
-        <v>3</v>
-      </c>
-      <c r="E87" s="1">
-        <v>0</v>
-      </c>
-      <c r="F87" s="1">
-        <v>400</v>
-      </c>
-      <c r="G87" s="1">
-        <f t="shared" ref="G87:G92" si="8">N87*O91</f>
-        <v>300</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J87" s="1">
-        <v>5</v>
-      </c>
-      <c r="K87" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L87" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M87" s="1">
-        <f t="shared" ref="M87:M94" si="9">F87*G87</f>
-        <v>120000</v>
-      </c>
-      <c r="N87" s="1">
-        <v>1</v>
-      </c>
+    <row r="87" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A87" s="1"/>
+      <c r="B87"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+      <c r="M87" s="1"/>
+      <c r="N87" s="1"/>
       <c r="O87" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="88" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C88" s="1">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D88" s="1">
         <v>3</v>
@@ -4648,162 +4613,162 @@
         <v>400</v>
       </c>
       <c r="G88" s="1">
+        <f t="shared" ref="G88:G93" si="8">N88*O92</f>
+        <v>300</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J88" s="1">
+        <v>5</v>
+      </c>
+      <c r="K88" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L88" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M88" s="1">
+        <f t="shared" ref="M88:M95" si="9">F88*G88</f>
+        <v>120000</v>
+      </c>
+      <c r="N88" s="1">
+        <v>1</v>
+      </c>
+      <c r="O88" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="89" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C89" s="1">
+        <v>212</v>
+      </c>
+      <c r="D89" s="1">
+        <v>3</v>
+      </c>
+      <c r="E89" s="1">
+        <v>0</v>
+      </c>
+      <c r="F89" s="1">
+        <v>400</v>
+      </c>
+      <c r="G89" s="1">
         <f t="shared" si="8"/>
         <v>500</v>
       </c>
-      <c r="H88" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I88" s="1" t="s">
+      <c r="H89" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J88" s="1">
-        <v>5</v>
-      </c>
-      <c r="K88" s="1">
+      <c r="I89" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J89" s="1">
+        <v>5</v>
+      </c>
+      <c r="K89" s="1">
         <v>4101</v>
       </c>
-      <c r="L88" s="1">
+      <c r="L89" s="1">
         <v>1000</v>
       </c>
-      <c r="M88" s="1">
+      <c r="M89" s="1">
         <f t="shared" si="9"/>
         <v>200000</v>
       </c>
-      <c r="N88" s="1">
-        <v>1</v>
-      </c>
-      <c r="O88" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="89" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C89" s="1">
+      <c r="N89" s="1">
+        <v>1</v>
+      </c>
+      <c r="O89" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C90" s="1">
         <v>213</v>
       </c>
-      <c r="D89" s="1">
+      <c r="D90" s="1">
         <v>3</v>
       </c>
-      <c r="E89" s="1">
-        <v>0</v>
-      </c>
-      <c r="F89" s="1">
+      <c r="E90" s="1">
+        <v>0</v>
+      </c>
+      <c r="F90" s="1">
         <v>4000</v>
       </c>
-      <c r="G89" s="1">
+      <c r="G90" s="1">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="H89" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I89" s="1" t="s">
+      <c r="H90" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="J89" s="1">
+      <c r="I90" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J90" s="1">
         <v>15</v>
       </c>
-      <c r="K89" s="1">
+      <c r="K90" s="1">
         <v>4014</v>
       </c>
-      <c r="L89" s="1">
+      <c r="L90" s="1">
         <v>100</v>
       </c>
-      <c r="M89" s="1">
+      <c r="M90" s="1">
         <f t="shared" si="9"/>
         <v>80000</v>
       </c>
-      <c r="N89" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A90"/>
-      <c r="C90" s="1">
+      <c r="N90" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A91"/>
+      <c r="C91" s="1">
         <v>214</v>
       </c>
-      <c r="D90" s="1">
+      <c r="D91" s="1">
         <v>3</v>
       </c>
-      <c r="E90" s="1">
-        <v>1</v>
-      </c>
-      <c r="F90" s="1">
+      <c r="E91" s="1">
+        <v>1</v>
+      </c>
+      <c r="F91" s="1">
         <v>45000</v>
       </c>
-      <c r="G90" s="1">
+      <c r="G91" s="1">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="H90" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I90" s="1" t="s">
+      <c r="H91" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="J90" s="1">
-        <v>5</v>
-      </c>
-      <c r="K90" s="1">
+      <c r="I91" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J91" s="1">
+        <v>5</v>
+      </c>
+      <c r="K91" s="1">
         <v>4019</v>
       </c>
-      <c r="L90" s="1">
-        <v>1</v>
-      </c>
-      <c r="M90" s="1">
+      <c r="L91" s="1">
+        <v>1</v>
+      </c>
+      <c r="M91" s="1">
         <f t="shared" si="9"/>
         <v>360000</v>
       </c>
-      <c r="N90" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C91" s="1">
-        <v>215</v>
-      </c>
-      <c r="D91" s="1">
-        <v>3</v>
-      </c>
-      <c r="E91" s="1">
-        <v>0</v>
-      </c>
-      <c r="F91" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G91" s="1">
-        <f t="shared" si="8"/>
-        <v>40</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J91" s="1">
-        <v>5</v>
-      </c>
-      <c r="K91" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L91" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M91" s="1">
-        <f t="shared" si="9"/>
-        <v>80000</v>
-      </c>
       <c r="N91" s="1">
         <v>1</v>
-      </c>
-      <c r="O91" s="1">
-        <v>300</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C92" s="1">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D92" s="1">
         <v>3</v>
@@ -4819,19 +4784,19 @@
         <v>40</v>
       </c>
       <c r="H92" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I92" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I92" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="J92" s="1">
         <v>5</v>
       </c>
       <c r="K92" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L92" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M92" s="1">
         <f t="shared" si="9"/>
@@ -4841,60 +4806,61 @@
         <v>1</v>
       </c>
       <c r="O92" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C93" s="1">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D93" s="1">
         <v>3</v>
       </c>
       <c r="E93" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F93" s="1">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="G93" s="1">
-        <v>10</v>
+        <f t="shared" si="8"/>
+        <v>40</v>
       </c>
       <c r="H93" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I93" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="I93" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="J93" s="1">
         <v>5</v>
       </c>
       <c r="K93" s="1">
-        <v>4026</v>
+        <v>4002</v>
       </c>
       <c r="L93" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M93" s="1">
         <f t="shared" si="9"/>
-        <v>300000</v>
+        <v>80000</v>
       </c>
       <c r="N93" s="1">
         <v>1</v>
       </c>
       <c r="O93" s="1">
-        <v>20</v>
+        <v>500</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C94" s="1">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D94" s="1">
         <v>3</v>
       </c>
       <c r="E94" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F94" s="1">
         <v>30000</v>
@@ -4903,16 +4869,16 @@
         <v>10</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="J94" s="1">
         <v>5</v>
       </c>
       <c r="K94" s="1">
-        <v>4035</v>
+        <v>4026</v>
       </c>
       <c r="L94" s="1">
         <v>1</v>
@@ -4921,75 +4887,74 @@
         <f t="shared" si="9"/>
         <v>300000</v>
       </c>
+      <c r="N94" s="1">
+        <v>1</v>
+      </c>
       <c r="O94" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="95" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C95" s="1">
+        <v>218</v>
+      </c>
+      <c r="D95" s="1">
+        <v>3</v>
+      </c>
+      <c r="E95" s="1">
+        <v>10</v>
+      </c>
+      <c r="F95" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G95" s="1">
+        <v>10</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J95" s="1">
+        <v>5</v>
+      </c>
+      <c r="K95" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L95" s="1">
+        <v>1</v>
+      </c>
+      <c r="M95" s="1">
+        <f t="shared" si="9"/>
+        <v>300000</v>
+      </c>
+      <c r="O95" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="95" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A95" s="1"/>
-      <c r="B95"/>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1"/>
-      <c r="K95" s="1"/>
-      <c r="L95" s="1"/>
-      <c r="M95" s="1"/>
-      <c r="N95" s="1"/>
-      <c r="O95" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="96" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C96" s="1">
-        <v>221</v>
-      </c>
-      <c r="D96" s="1">
-        <v>4</v>
-      </c>
-      <c r="E96" s="1">
-        <v>0</v>
-      </c>
-      <c r="F96" s="5">
-        <v>600</v>
-      </c>
-      <c r="G96" s="1">
-        <f t="shared" ref="G96:G101" si="10">N96*O100</f>
-        <v>300</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J96" s="1">
-        <v>5</v>
-      </c>
-      <c r="K96" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L96" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M96" s="1">
-        <f t="shared" ref="M96:M103" si="11">F96*G96</f>
-        <v>180000</v>
-      </c>
-      <c r="N96" s="1">
-        <v>1</v>
-      </c>
+    <row r="96" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A96" s="1"/>
+      <c r="B96"/>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1"/>
+      <c r="K96" s="1"/>
+      <c r="L96" s="1"/>
+      <c r="M96" s="1"/>
+      <c r="N96" s="1"/>
       <c r="O96" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C97" s="1">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D97" s="1">
         <v>4</v>
@@ -5001,162 +4966,162 @@
         <v>600</v>
       </c>
       <c r="G97" s="1">
+        <f t="shared" ref="G97:G102" si="10">N97*O101</f>
+        <v>300</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J97" s="1">
+        <v>5</v>
+      </c>
+      <c r="K97" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L97" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M97" s="1">
+        <f t="shared" ref="M97:M104" si="11">F97*G97</f>
+        <v>180000</v>
+      </c>
+      <c r="N97" s="1">
+        <v>1</v>
+      </c>
+      <c r="O97" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="98" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C98" s="1">
+        <v>222</v>
+      </c>
+      <c r="D98" s="1">
+        <v>4</v>
+      </c>
+      <c r="E98" s="1">
+        <v>0</v>
+      </c>
+      <c r="F98" s="5">
+        <v>600</v>
+      </c>
+      <c r="G98" s="1">
         <f t="shared" si="10"/>
         <v>500</v>
       </c>
-      <c r="H97" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I97" s="1" t="s">
+      <c r="H98" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J97" s="1">
-        <v>5</v>
-      </c>
-      <c r="K97" s="1">
+      <c r="I98" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J98" s="1">
+        <v>5</v>
+      </c>
+      <c r="K98" s="1">
         <v>4101</v>
       </c>
-      <c r="L97" s="1">
+      <c r="L98" s="1">
         <v>1000</v>
       </c>
-      <c r="M97" s="1">
+      <c r="M98" s="1">
         <f t="shared" si="11"/>
         <v>300000</v>
       </c>
-      <c r="N97" s="1">
-        <v>1</v>
-      </c>
-      <c r="O97" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C98" s="1">
+      <c r="N98" s="1">
+        <v>1</v>
+      </c>
+      <c r="O98" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C99" s="1">
         <v>223</v>
       </c>
-      <c r="D98" s="1">
+      <c r="D99" s="1">
         <v>4</v>
       </c>
-      <c r="E98" s="1">
-        <v>0</v>
-      </c>
-      <c r="F98" s="5">
+      <c r="E99" s="1">
+        <v>0</v>
+      </c>
+      <c r="F99" s="5">
         <v>6000</v>
       </c>
-      <c r="G98" s="1">
+      <c r="G99" s="1">
         <f t="shared" si="10"/>
         <v>20</v>
       </c>
-      <c r="H98" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I98" s="1" t="s">
+      <c r="H99" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="J98" s="1">
+      <c r="I99" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J99" s="1">
         <v>15</v>
       </c>
-      <c r="K98" s="1">
+      <c r="K99" s="1">
         <v>4014</v>
       </c>
-      <c r="L98" s="1">
+      <c r="L99" s="1">
         <v>100</v>
       </c>
-      <c r="M98" s="1">
+      <c r="M99" s="1">
         <f t="shared" si="11"/>
         <v>120000</v>
       </c>
-      <c r="N98" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A99"/>
-      <c r="C99" s="1">
+      <c r="N99" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A100"/>
+      <c r="C100" s="1">
         <v>224</v>
       </c>
-      <c r="D99" s="1">
+      <c r="D100" s="1">
         <v>4</v>
       </c>
-      <c r="E99" s="1">
-        <v>1</v>
-      </c>
-      <c r="F99" s="5">
+      <c r="E100" s="1">
+        <v>1</v>
+      </c>
+      <c r="F100" s="5">
         <v>60000</v>
       </c>
-      <c r="G99" s="1">
+      <c r="G100" s="1">
         <f t="shared" si="10"/>
         <v>8</v>
       </c>
-      <c r="H99" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I99" s="1" t="s">
+      <c r="H100" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="J99" s="1">
-        <v>5</v>
-      </c>
-      <c r="K99" s="1">
+      <c r="I100" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J100" s="1">
+        <v>5</v>
+      </c>
+      <c r="K100" s="1">
         <v>4019</v>
       </c>
-      <c r="L99" s="1">
-        <v>1</v>
-      </c>
-      <c r="M99" s="1">
+      <c r="L100" s="1">
+        <v>1</v>
+      </c>
+      <c r="M100" s="1">
         <f t="shared" si="11"/>
         <v>480000</v>
       </c>
-      <c r="N99" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C100" s="1">
-        <v>225</v>
-      </c>
-      <c r="D100" s="1">
-        <v>4</v>
-      </c>
-      <c r="E100" s="1">
-        <v>0</v>
-      </c>
-      <c r="F100" s="5">
-        <v>3000</v>
-      </c>
-      <c r="G100" s="1">
-        <f t="shared" si="10"/>
-        <v>40</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J100" s="1">
-        <v>5</v>
-      </c>
-      <c r="K100" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L100" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M100" s="1">
-        <f t="shared" si="11"/>
-        <v>120000</v>
-      </c>
       <c r="N100" s="1">
         <v>1</v>
-      </c>
-      <c r="O100" s="1">
-        <v>300</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C101" s="1">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D101" s="1">
         <v>4</v>
@@ -5172,19 +5137,19 @@
         <v>40</v>
       </c>
       <c r="H101" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I101" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I101" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="J101" s="1">
         <v>5</v>
       </c>
       <c r="K101" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L101" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M101" s="1">
         <f t="shared" si="11"/>
@@ -5194,60 +5159,61 @@
         <v>1</v>
       </c>
       <c r="O101" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C102" s="1">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D102" s="1">
         <v>4</v>
       </c>
       <c r="E102" s="1">
-        <v>6</v>
-      </c>
-      <c r="F102" s="1">
-        <v>30000</v>
+        <v>0</v>
+      </c>
+      <c r="F102" s="5">
+        <v>3000</v>
       </c>
       <c r="G102" s="1">
-        <v>10</v>
+        <f t="shared" si="10"/>
+        <v>40</v>
       </c>
       <c r="H102" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I102" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="I102" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="J102" s="1">
         <v>5</v>
       </c>
       <c r="K102" s="1">
-        <v>4026</v>
+        <v>4002</v>
       </c>
       <c r="L102" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M102" s="1">
         <f t="shared" si="11"/>
-        <v>300000</v>
+        <v>120000</v>
       </c>
       <c r="N102" s="1">
         <v>1</v>
       </c>
       <c r="O102" s="1">
-        <v>20</v>
+        <v>500</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C103" s="1">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D103" s="1">
         <v>4</v>
       </c>
       <c r="E103" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F103" s="1">
         <v>30000</v>
@@ -5256,16 +5222,16 @@
         <v>10</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="J103" s="1">
         <v>5</v>
       </c>
       <c r="K103" s="1">
-        <v>4035</v>
+        <v>4026</v>
       </c>
       <c r="L103" s="1">
         <v>1</v>
@@ -5274,75 +5240,74 @@
         <f t="shared" si="11"/>
         <v>300000</v>
       </c>
+      <c r="N103" s="1">
+        <v>1</v>
+      </c>
       <c r="O103" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="104" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C104" s="1">
+        <v>228</v>
+      </c>
+      <c r="D104" s="1">
+        <v>4</v>
+      </c>
+      <c r="E104" s="1">
+        <v>10</v>
+      </c>
+      <c r="F104" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G104" s="1">
+        <v>10</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J104" s="1">
+        <v>5</v>
+      </c>
+      <c r="K104" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L104" s="1">
+        <v>1</v>
+      </c>
+      <c r="M104" s="1">
+        <f t="shared" si="11"/>
+        <v>300000</v>
+      </c>
+      <c r="O104" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="104" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A104" s="1"/>
-      <c r="B104"/>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="1"/>
-      <c r="F104" s="1"/>
-      <c r="G104" s="1"/>
-      <c r="H104" s="1"/>
-      <c r="I104" s="1"/>
-      <c r="J104" s="1"/>
-      <c r="K104" s="1"/>
-      <c r="L104" s="1"/>
-      <c r="M104" s="1"/>
-      <c r="N104" s="1"/>
-      <c r="O104" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="105" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C105" s="1">
-        <v>231</v>
-      </c>
-      <c r="D105" s="1">
-        <v>5</v>
-      </c>
-      <c r="E105" s="1">
-        <v>0</v>
-      </c>
-      <c r="F105" s="1">
-        <v>800</v>
-      </c>
-      <c r="G105" s="1">
-        <f t="shared" ref="G105:G110" si="12">N105*O109</f>
-        <v>1200</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="J105" s="1">
-        <v>5</v>
-      </c>
-      <c r="K105" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L105" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M105" s="1">
-        <f t="shared" ref="M105:M112" si="13">F105*G105</f>
-        <v>960000</v>
-      </c>
-      <c r="N105" s="1">
-        <v>4</v>
-      </c>
+    <row r="105" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A105" s="1"/>
+      <c r="B105"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
+      <c r="K105" s="1"/>
+      <c r="L105" s="1"/>
+      <c r="M105" s="1"/>
+      <c r="N105" s="1"/>
       <c r="O105" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C106" s="1">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D106" s="1">
         <v>5</v>
@@ -5354,162 +5319,162 @@
         <v>800</v>
       </c>
       <c r="G106" s="1">
+        <f t="shared" ref="G106:G111" si="12">N106*O110</f>
+        <v>1200</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J106" s="1">
+        <v>5</v>
+      </c>
+      <c r="K106" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L106" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M106" s="1">
+        <f t="shared" ref="M106:M113" si="13">F106*G106</f>
+        <v>960000</v>
+      </c>
+      <c r="N106" s="1">
+        <v>4</v>
+      </c>
+      <c r="O106" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="107" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C107" s="1">
+        <v>232</v>
+      </c>
+      <c r="D107" s="1">
+        <v>5</v>
+      </c>
+      <c r="E107" s="1">
+        <v>0</v>
+      </c>
+      <c r="F107" s="1">
+        <v>800</v>
+      </c>
+      <c r="G107" s="1">
         <f t="shared" si="12"/>
         <v>2000</v>
       </c>
-      <c r="H106" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I106" s="1" t="s">
+      <c r="H107" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J106" s="1">
-        <v>5</v>
-      </c>
-      <c r="K106" s="1">
+      <c r="I107" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J107" s="1">
+        <v>5</v>
+      </c>
+      <c r="K107" s="1">
         <v>4101</v>
       </c>
-      <c r="L106" s="1">
+      <c r="L107" s="1">
         <v>1000</v>
       </c>
-      <c r="M106" s="1">
+      <c r="M107" s="1">
         <f t="shared" si="13"/>
         <v>1600000</v>
       </c>
-      <c r="N106" s="1">
+      <c r="N107" s="1">
         <v>4</v>
       </c>
-      <c r="O106" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="107" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C107" s="1">
+      <c r="O107" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C108" s="1">
         <v>233</v>
       </c>
-      <c r="D107" s="1">
-        <v>5</v>
-      </c>
-      <c r="E107" s="1">
-        <v>0</v>
-      </c>
-      <c r="F107" s="1">
+      <c r="D108" s="1">
+        <v>5</v>
+      </c>
+      <c r="E108" s="1">
+        <v>0</v>
+      </c>
+      <c r="F108" s="1">
         <v>8000</v>
       </c>
-      <c r="G107" s="1">
+      <c r="G108" s="1">
         <f t="shared" si="12"/>
         <v>40</v>
       </c>
-      <c r="H107" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I107" s="1" t="s">
+      <c r="H108" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="J107" s="1">
+      <c r="I108" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J108" s="1">
         <v>15</v>
       </c>
-      <c r="K107" s="1">
+      <c r="K108" s="1">
         <v>4014</v>
       </c>
-      <c r="L107" s="1">
+      <c r="L108" s="1">
         <v>100</v>
       </c>
-      <c r="M107" s="1">
+      <c r="M108" s="1">
         <f t="shared" si="13"/>
         <v>320000</v>
       </c>
-      <c r="N107" s="1">
+      <c r="N108" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="108" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A108"/>
-      <c r="C108" s="1">
+    <row r="109" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A109"/>
+      <c r="C109" s="1">
         <v>234</v>
       </c>
-      <c r="D108" s="1">
-        <v>5</v>
-      </c>
-      <c r="E108" s="1">
-        <v>1</v>
-      </c>
-      <c r="F108" s="1">
+      <c r="D109" s="1">
+        <v>5</v>
+      </c>
+      <c r="E109" s="1">
+        <v>1</v>
+      </c>
+      <c r="F109" s="1">
         <v>75000</v>
       </c>
-      <c r="G108" s="1">
+      <c r="G109" s="1">
         <f t="shared" si="12"/>
         <v>32</v>
       </c>
-      <c r="H108" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I108" s="1" t="s">
+      <c r="H109" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="J108" s="1">
-        <v>5</v>
-      </c>
-      <c r="K108" s="1">
+      <c r="I109" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="J109" s="1">
+        <v>5</v>
+      </c>
+      <c r="K109" s="1">
         <v>4019</v>
       </c>
-      <c r="L108" s="1">
-        <v>1</v>
-      </c>
-      <c r="M108" s="1">
+      <c r="L109" s="1">
+        <v>1</v>
+      </c>
+      <c r="M109" s="1">
         <f t="shared" si="13"/>
         <v>2400000</v>
       </c>
-      <c r="N108" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="109" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C109" s="1">
-        <v>235</v>
-      </c>
-      <c r="D109" s="1">
-        <v>5</v>
-      </c>
-      <c r="E109" s="1">
-        <v>0</v>
-      </c>
-      <c r="F109" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G109" s="1">
-        <f t="shared" si="12"/>
-        <v>160</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J109" s="1">
-        <v>5</v>
-      </c>
-      <c r="K109" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L109" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M109" s="1">
-        <f t="shared" si="13"/>
-        <v>640000</v>
-      </c>
       <c r="N109" s="1">
         <v>4</v>
       </c>
-      <c r="O109" s="1">
-        <v>300</v>
-      </c>
     </row>
     <row r="110" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C110" s="1">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D110" s="1">
         <v>5</v>
@@ -5525,19 +5490,19 @@
         <v>160</v>
       </c>
       <c r="H110" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I110" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I110" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="J110" s="1">
         <v>5</v>
       </c>
       <c r="K110" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L110" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M110" s="1">
         <f t="shared" si="13"/>
@@ -5547,60 +5512,61 @@
         <v>4</v>
       </c>
       <c r="O110" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="111" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C111" s="1">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D111" s="1">
         <v>5</v>
       </c>
       <c r="E111" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F111" s="1">
-        <v>30000</v>
+        <v>4000</v>
       </c>
       <c r="G111" s="1">
-        <v>10</v>
+        <f t="shared" si="12"/>
+        <v>160</v>
       </c>
       <c r="H111" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I111" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="I111" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="J111" s="1">
         <v>5</v>
       </c>
       <c r="K111" s="1">
-        <v>4026</v>
+        <v>4002</v>
       </c>
       <c r="L111" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M111" s="1">
         <f t="shared" si="13"/>
-        <v>300000</v>
+        <v>640000</v>
       </c>
       <c r="N111" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O111" s="1">
-        <v>10</v>
+        <v>500</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C112" s="1">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D112" s="1">
         <v>5</v>
       </c>
       <c r="E112" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F112" s="1">
         <v>30000</v>
@@ -5609,16 +5575,16 @@
         <v>10</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="J112" s="1">
         <v>5</v>
       </c>
       <c r="K112" s="1">
-        <v>4035</v>
+        <v>4026</v>
       </c>
       <c r="L112" s="1">
         <v>1</v>
@@ -5627,176 +5593,218 @@
         <f t="shared" si="13"/>
         <v>300000</v>
       </c>
+      <c r="N112" s="1">
+        <v>1</v>
+      </c>
       <c r="O112" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C113" s="1">
+        <v>238</v>
+      </c>
+      <c r="D113" s="1">
+        <v>5</v>
+      </c>
+      <c r="E113" s="1">
+        <v>10</v>
+      </c>
+      <c r="F113" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G113" s="1">
+        <v>10</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J113" s="1">
+        <v>5</v>
+      </c>
+      <c r="K113" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L113" s="1">
+        <v>1</v>
+      </c>
+      <c r="M113" s="1">
+        <f t="shared" si="13"/>
+        <v>300000</v>
+      </c>
+      <c r="O113" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="113" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A113" s="1"/>
-      <c r="B113"/>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
-      <c r="E113" s="1"/>
-      <c r="F113" s="1"/>
-      <c r="G113" s="1"/>
-      <c r="H113" s="1"/>
-      <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
-      <c r="K113" s="1"/>
-      <c r="L113" s="1"/>
-      <c r="M113" s="1"/>
-      <c r="N113"/>
-      <c r="O113" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="114" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C114" s="1">
-        <v>999</v>
-      </c>
-      <c r="D114" s="1">
-        <v>0</v>
-      </c>
-      <c r="E114" s="1">
-        <v>0</v>
-      </c>
-      <c r="F114" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G114" s="1">
-        <v>50</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="J114" s="1">
-        <v>5</v>
-      </c>
-      <c r="K114" s="1">
-        <v>4006</v>
-      </c>
-      <c r="L114" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M114" s="1">
-        <f t="shared" ref="M114:M116" si="14">F114*G114</f>
-        <v>50000</v>
-      </c>
+    <row r="114" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A114" s="1"/>
+      <c r="B114"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1"/>
+      <c r="F114" s="1"/>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1"/>
+      <c r="K114" s="1"/>
+      <c r="L114" s="1"/>
+      <c r="M114" s="1"/>
+      <c r="N114"/>
       <c r="O114" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C115" s="1">
+        <v>999</v>
+      </c>
+      <c r="D115" s="1">
+        <v>0</v>
+      </c>
+      <c r="E115" s="1">
+        <v>0</v>
+      </c>
+      <c r="F115" s="1">
         <v>1000</v>
       </c>
-      <c r="D115" s="1">
-        <v>0</v>
-      </c>
-      <c r="E115" s="1">
-        <v>0</v>
-      </c>
-      <c r="F115" s="1">
+      <c r="G115" s="1">
+        <v>50</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J115" s="1">
+        <v>5</v>
+      </c>
+      <c r="K115" s="1">
+        <v>4006</v>
+      </c>
+      <c r="L115" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M115" s="1">
+        <f t="shared" ref="M115:M117" si="14">F115*G115</f>
+        <v>50000</v>
+      </c>
+      <c r="O115" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="116" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C116" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D116" s="1">
+        <v>0</v>
+      </c>
+      <c r="E116" s="1">
+        <v>0</v>
+      </c>
+      <c r="F116" s="1">
         <v>2000</v>
       </c>
-      <c r="G115" s="1">
+      <c r="G116" s="1">
         <v>1000</v>
       </c>
-      <c r="H115" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="I115" s="1" t="s">
+      <c r="H116" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="J115" s="1">
-        <v>5</v>
-      </c>
-      <c r="K115" s="1">
+      <c r="I116" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="J116" s="1">
+        <v>5</v>
+      </c>
+      <c r="K116" s="1">
         <v>4010</v>
       </c>
-      <c r="L115" s="1">
-        <v>5</v>
-      </c>
-      <c r="M115" s="1">
+      <c r="L116" s="1">
+        <v>5</v>
+      </c>
+      <c r="M116" s="1">
         <f t="shared" si="14"/>
         <v>2000000</v>
       </c>
-      <c r="O115" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="116" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C116" s="1">
+      <c r="O116" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C117" s="1">
         <v>1001</v>
       </c>
-      <c r="D116" s="1">
-        <v>0</v>
-      </c>
-      <c r="E116" s="1">
-        <v>0</v>
-      </c>
-      <c r="F116" s="1">
+      <c r="D117" s="1">
+        <v>0</v>
+      </c>
+      <c r="E117" s="1">
+        <v>0</v>
+      </c>
+      <c r="F117" s="1">
         <v>2000</v>
       </c>
-      <c r="G116" s="1">
+      <c r="G117" s="1">
         <v>50</v>
       </c>
-      <c r="H116" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="I116" s="1" t="s">
+      <c r="H117" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J116" s="1">
-        <v>5</v>
-      </c>
-      <c r="K116" s="1">
+      <c r="I117" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J117" s="1">
+        <v>5</v>
+      </c>
+      <c r="K117" s="1">
         <v>4102</v>
       </c>
-      <c r="L116" s="1">
+      <c r="L117" s="1">
         <v>20</v>
       </c>
-      <c r="M116" s="1">
+      <c r="M117" s="1">
         <f t="shared" si="14"/>
         <v>100000</v>
       </c>
     </row>
-    <row r="117" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A117"/>
-      <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-      <c r="E117" s="1"/>
-      <c r="F117" s="1"/>
-      <c r="G117" s="1"/>
-      <c r="H117" s="1"/>
-      <c r="I117" s="1"/>
-      <c r="J117" s="1"/>
-      <c r="K117" s="1"/>
-      <c r="L117" s="1"/>
-      <c r="M117" s="1"/>
-      <c r="N117" s="1"/>
-      <c r="O117"/>
-    </row>
-    <row r="122" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A122" s="1"/>
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1"/>
-      <c r="G122" s="1"/>
-      <c r="H122" s="1"/>
-      <c r="I122" s="1"/>
-      <c r="J122" s="1"/>
-      <c r="K122" s="1"/>
-      <c r="L122" s="1"/>
-      <c r="M122" s="1"/>
-      <c r="N122" s="1"/>
-      <c r="O122" s="1"/>
+    <row r="118" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A118"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
+      <c r="E118" s="1"/>
+      <c r="F118" s="1"/>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1"/>
+      <c r="K118" s="1"/>
+      <c r="L118" s="1"/>
+      <c r="M118" s="1"/>
+      <c r="N118" s="1"/>
+      <c r="O118"/>
+    </row>
+    <row r="123" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A123" s="1"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
+      <c r="E123" s="1"/>
+      <c r="F123" s="1"/>
+      <c r="G123" s="1"/>
+      <c r="H123" s="1"/>
+      <c r="I123" s="1"/>
+      <c r="J123" s="1"/>
+      <c r="K123" s="1"/>
+      <c r="L123" s="1"/>
+      <c r="M123" s="1"/>
+      <c r="N123" s="1"/>
+      <c r="O123" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="158">
   <si>
     <t>#</t>
   </si>
@@ -1641,7 +1641,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="1">
-        <v>388</v>
+        <v>268</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>14</v>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="M6" s="1">
         <f t="shared" ref="M6:M14" si="0">F6*G6</f>
-        <v>116400</v>
+        <v>80400</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:13">
@@ -1677,7 +1677,7 @@
         <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>388</v>
+        <v>268</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>16</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="M7" s="1">
         <f t="shared" si="0"/>
-        <v>116400</v>
+        <v>80400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1713,7 +1713,7 @@
         <v>13</v>
       </c>
       <c r="G8" s="1">
-        <v>388</v>
+        <v>268</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>18</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="M8" s="1">
         <f t="shared" si="0"/>
-        <v>116400</v>
+        <v>80400</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:13">
@@ -3323,7 +3323,7 @@
         <v>500000</v>
       </c>
       <c r="G53" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>115</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="M53" s="1">
         <f t="shared" si="3"/>
-        <v>2500000</v>
+        <v>1500000</v>
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
@@ -3366,7 +3366,7 @@
     </row>
     <row r="55" customFormat="1" customHeight="1" spans="1:15">
       <c r="A55" s="1"/>
-      <c r="B55"/>
+      <c r="B55" s="1"/>
       <c r="C55" s="1">
         <v>48</v>
       </c>
@@ -3405,8 +3405,12 @@
       <c r="O55" s="1"/>
     </row>
     <row r="56" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A56" s="1"/>
-      <c r="B56"/>
+      <c r="A56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C56" s="1">
         <v>49</v>
       </c>
@@ -3445,7 +3449,12 @@
       <c r="O56" s="1"/>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="B57"/>
+      <c r="A57" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C57" s="1">
         <v>50</v>
       </c>
@@ -3483,7 +3492,7 @@
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="1:15">
       <c r="A58" s="1"/>
-      <c r="B58"/>
+      <c r="B58" s="1"/>
       <c r="C58" s="1">
         <v>51</v>
       </c>
@@ -3497,7 +3506,7 @@
         <v>100000</v>
       </c>
       <c r="G58" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>119</v>
@@ -3516,13 +3525,18 @@
       </c>
       <c r="M58" s="1">
         <f t="shared" si="3"/>
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
     </row>
     <row r="59" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A59" s="1"/>
+      <c r="A59" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C59" s="1">
         <v>52</v>
       </c>
@@ -3554,15 +3568,19 @@
         <v>1</v>
       </c>
       <c r="M59" s="1">
-        <f>F59*G59</f>
+        <f t="shared" si="3"/>
         <v>6000000</v>
       </c>
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A60"/>
-      <c r="B60"/>
+      <c r="A60" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C60" s="1">
         <v>53</v>
       </c>
@@ -3594,13 +3612,17 @@
         <v>1</v>
       </c>
       <c r="M60" s="1">
-        <f>F60*G60</f>
+        <f t="shared" si="3"/>
         <v>6000000</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A61"/>
-      <c r="B61"/>
+      <c r="A61" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C61" s="1">
         <v>54</v>
       </c>
@@ -3632,13 +3654,17 @@
         <v>1</v>
       </c>
       <c r="M61" s="1">
-        <f>F61*G61</f>
+        <f t="shared" si="3"/>
         <v>6000000</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A62"/>
-      <c r="B62"/>
+      <c r="A62" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C62" s="1">
         <v>55</v>
       </c>
@@ -3670,13 +3696,17 @@
         <v>100</v>
       </c>
       <c r="M62" s="1">
-        <f>F62*G62</f>
+        <f t="shared" si="3"/>
         <v>3000000</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A63"/>
-      <c r="B63"/>
+      <c r="A63" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C63" s="1">
         <v>56</v>
       </c>
@@ -3708,13 +3738,17 @@
         <v>1</v>
       </c>
       <c r="M63" s="1">
-        <f>F63*G63</f>
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:15">
-      <c r="A64"/>
-      <c r="B64"/>
+      <c r="A64" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C64" s="1">
         <v>57</v>
       </c>
@@ -3746,11 +3780,17 @@
         <v>1</v>
       </c>
       <c r="M64" s="1">
-        <f>F64*G64</f>
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
     </row>
     <row r="65" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A65" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C65" s="1">
         <v>58</v>
       </c>
@@ -3782,13 +3822,19 @@
         <v>1</v>
       </c>
       <c r="M65" s="1">
-        <f>F65*G65</f>
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A66" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C66" s="1">
         <v>59</v>
       </c>
@@ -3820,13 +3866,19 @@
         <v>1</v>
       </c>
       <c r="M66" s="1">
-        <f>F66*G66</f>
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
     </row>
     <row r="67" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A67" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C67" s="1">
         <v>60</v>
       </c>
@@ -3858,7 +3910,7 @@
         <v>1</v>
       </c>
       <c r="M67" s="1">
-        <f>F67*G67</f>
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
       <c r="N67" s="1"/>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -3042,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="1">
-        <v>388888</v>
+        <v>208888</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="M45" s="1">
         <f t="shared" si="2"/>
-        <v>388888</v>
+        <v>208888</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:13">

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="159">
   <si>
     <t>#</t>
   </si>
@@ -390,6 +390,9 @@
   </si>
   <si>
     <t>炼神丹*500</t>
+  </si>
+  <si>
+    <t>金色坐骑自选</t>
   </si>
   <si>
     <t>兑换传奇精华</t>
@@ -1511,7 +1514,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O123"/>
+  <dimension ref="A1:O124"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -3405,12 +3408,8 @@
       <c r="O55" s="1"/>
     </row>
     <row r="56" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A56" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
       <c r="C56" s="1">
         <v>49</v>
       </c>
@@ -3449,12 +3448,6 @@
       <c r="O56" s="1"/>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A57" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C57" s="1">
         <v>50</v>
       </c>
@@ -3530,13 +3523,7 @@
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
     </row>
-    <row r="59" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A59" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C59" s="1">
         <v>52</v>
       </c>
@@ -3547,34 +3534,32 @@
         <v>10</v>
       </c>
       <c r="F59" s="1">
-        <v>30000</v>
+        <v>1000000</v>
       </c>
       <c r="G59" s="1">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>121</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J59" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K59" s="1">
-        <v>4035</v>
+        <v>301</v>
       </c>
       <c r="L59" s="1">
         <v>1</v>
       </c>
       <c r="M59" s="1">
         <f t="shared" si="3"/>
-        <v>6000000</v>
-      </c>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
-    </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="1:15">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" customHeight="1" spans="1:15">
       <c r="A60" s="1" t="s">
         <v>0</v>
       </c>
@@ -3582,13 +3567,13 @@
         <v>0</v>
       </c>
       <c r="C60" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F60" s="1">
         <v>30000</v>
@@ -3597,24 +3582,26 @@
         <v>200</v>
       </c>
       <c r="H60" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I60" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="I60" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="J60" s="1">
         <v>5</v>
       </c>
       <c r="K60" s="1">
-        <v>4039</v>
+        <v>4035</v>
       </c>
       <c r="L60" s="1">
         <v>1</v>
       </c>
       <c r="M60" s="1">
-        <f t="shared" si="3"/>
+        <f>F60*G60</f>
         <v>6000000</v>
       </c>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A61" s="1" t="s">
@@ -3624,13 +3611,13 @@
         <v>0</v>
       </c>
       <c r="C61" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F61" s="1">
         <v>30000</v>
@@ -3639,22 +3626,22 @@
         <v>200</v>
       </c>
       <c r="H61" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I61" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="I61" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="J61" s="1">
         <v>5</v>
       </c>
       <c r="K61" s="1">
-        <v>4038</v>
+        <v>4039</v>
       </c>
       <c r="L61" s="1">
         <v>1</v>
       </c>
       <c r="M61" s="1">
-        <f t="shared" si="3"/>
+        <f>F61*G61</f>
         <v>6000000</v>
       </c>
     </row>
@@ -3666,22 +3653,22 @@
         <v>0</v>
       </c>
       <c r="C62" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F62" s="1">
-        <v>1000</v>
+        <v>30000</v>
       </c>
       <c r="G62" s="1">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>127</v>
@@ -3690,14 +3677,14 @@
         <v>5</v>
       </c>
       <c r="K62" s="1">
-        <v>4022</v>
+        <v>4038</v>
       </c>
       <c r="L62" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M62" s="1">
-        <f t="shared" si="3"/>
-        <v>3000000</v>
+        <f>F62*G62</f>
+        <v>6000000</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3708,49 +3695,49 @@
         <v>0</v>
       </c>
       <c r="C63" s="1">
+        <v>55</v>
+      </c>
+      <c r="D63" s="1">
+        <v>0</v>
+      </c>
+      <c r="E63" s="1">
+        <v>0</v>
+      </c>
+      <c r="F63" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G63" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J63" s="1">
+        <v>5</v>
+      </c>
+      <c r="K63" s="1">
+        <v>4022</v>
+      </c>
+      <c r="L63" s="1">
+        <v>100</v>
+      </c>
+      <c r="M63" s="1">
+        <f>F63*G63</f>
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A64" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C64" s="1">
         <v>56</v>
-      </c>
-      <c r="D63" s="1">
-        <v>0</v>
-      </c>
-      <c r="E63" s="1">
-        <v>15</v>
-      </c>
-      <c r="F63" s="1">
-        <v>100000</v>
-      </c>
-      <c r="G63" s="1">
-        <v>10</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="J63" s="1">
-        <v>11</v>
-      </c>
-      <c r="K63" s="1">
-        <v>1998001</v>
-      </c>
-      <c r="L63" s="1">
-        <v>1</v>
-      </c>
-      <c r="M63" s="1">
-        <f t="shared" si="3"/>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="1:15">
-      <c r="A64" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C64" s="1">
-        <v>57</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
@@ -3765,26 +3752,26 @@
         <v>10</v>
       </c>
       <c r="H64" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="J64" s="1">
         <v>11</v>
       </c>
       <c r="K64" s="1">
-        <v>1998002</v>
+        <v>1998001</v>
       </c>
       <c r="L64" s="1">
         <v>1</v>
       </c>
       <c r="M64" s="1">
-        <f t="shared" si="3"/>
+        <f>F64*G64</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="65" customFormat="1" customHeight="1" spans="1:15">
+    <row r="65" customHeight="1" spans="1:15">
       <c r="A65" s="1" t="s">
         <v>0</v>
       </c>
@@ -3792,7 +3779,7 @@
         <v>0</v>
       </c>
       <c r="C65" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
@@ -3807,26 +3794,24 @@
         <v>10</v>
       </c>
       <c r="H65" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I65" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="J65" s="1">
         <v>11</v>
       </c>
       <c r="K65" s="1">
-        <v>1998003</v>
+        <v>1998002</v>
       </c>
       <c r="L65" s="1">
         <v>1</v>
       </c>
       <c r="M65" s="1">
-        <f t="shared" si="3"/>
+        <f>F65*G65</f>
         <v>1000000</v>
       </c>
-      <c r="N65" s="1"/>
-      <c r="O65" s="1"/>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="1:15">
       <c r="A66" s="1" t="s">
@@ -3836,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="C66" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
@@ -3851,22 +3836,22 @@
         <v>10</v>
       </c>
       <c r="H66" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I66" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="J66" s="1">
         <v>11</v>
       </c>
       <c r="K66" s="1">
-        <v>1998004</v>
+        <v>1998003</v>
       </c>
       <c r="L66" s="1">
         <v>1</v>
       </c>
       <c r="M66" s="1">
-        <f t="shared" si="3"/>
+        <f>F66*G66</f>
         <v>1000000</v>
       </c>
       <c r="N66" s="1"/>
@@ -3880,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="C67" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
@@ -3895,92 +3880,94 @@
         <v>10</v>
       </c>
       <c r="H67" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I67" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="J67" s="1">
         <v>11</v>
       </c>
       <c r="K67" s="1">
-        <v>1998005</v>
+        <v>1998004</v>
       </c>
       <c r="L67" s="1">
         <v>1</v>
       </c>
       <c r="M67" s="1">
-        <f t="shared" si="3"/>
+        <f>F67*G67</f>
         <v>1000000</v>
       </c>
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
     </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A68"/>
-      <c r="B68"/>
-    </row>
-    <row r="69" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
+    <row r="68" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A68" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C68" s="1">
+        <v>60</v>
+      </c>
+      <c r="D68" s="1">
+        <v>0</v>
+      </c>
+      <c r="E68" s="1">
+        <v>15</v>
+      </c>
+      <c r="F68" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G68" s="1">
+        <v>10</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J68" s="1">
+        <v>11</v>
+      </c>
+      <c r="K68" s="1">
+        <v>1998005</v>
+      </c>
+      <c r="L68" s="1">
+        <v>1</v>
+      </c>
+      <c r="M68" s="1">
+        <f>F68*G68</f>
+        <v>1000000</v>
+      </c>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+    </row>
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A69"/>
+      <c r="B69"/>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="1:15">
-      <c r="B70" s="1"/>
-      <c r="C70" s="1">
-        <v>102</v>
-      </c>
-      <c r="D70" s="1">
-        <v>1</v>
-      </c>
-      <c r="E70" s="1">
-        <v>0</v>
-      </c>
-      <c r="F70" s="1">
-        <v>100</v>
-      </c>
-      <c r="G70" s="1">
-        <f t="shared" ref="G70:G75" si="4">N70*O74</f>
-        <v>300</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J70" s="1">
-        <v>5</v>
-      </c>
-      <c r="K70" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L70" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M70" s="1">
-        <f t="shared" ref="M70:M77" si="5">F70*G70</f>
-        <v>30000</v>
-      </c>
-      <c r="N70" s="1">
-        <v>1</v>
-      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
       <c r="O70" s="1"/>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="1:15">
       <c r="B71" s="1"/>
       <c r="C71" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D71" s="1">
         <v>1</v>
@@ -3992,27 +3979,27 @@
         <v>100</v>
       </c>
       <c r="G71" s="1">
-        <f t="shared" si="4"/>
-        <v>500</v>
+        <f t="shared" ref="G71:G76" si="4">N71*O75</f>
+        <v>300</v>
       </c>
       <c r="H71" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="I71" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="J71" s="1">
         <v>5</v>
       </c>
       <c r="K71" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="L71" s="1">
         <v>1000</v>
       </c>
       <c r="M71" s="1">
-        <f t="shared" si="5"/>
-        <v>50000</v>
+        <f t="shared" ref="M71:M78" si="5">F71*G71</f>
+        <v>30000</v>
       </c>
       <c r="N71" s="1">
         <v>1</v>
@@ -4022,7 +4009,7 @@
     <row r="72" customFormat="1" customHeight="1" spans="1:15">
       <c r="B72" s="1"/>
       <c r="C72" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D72" s="1">
         <v>1</v>
@@ -4031,30 +4018,30 @@
         <v>0</v>
       </c>
       <c r="F72" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="G72" s="1">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="H72" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I72" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="I72" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="J72" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K72" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="L72" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="M72" s="1">
         <f t="shared" si="5"/>
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="N72" s="1">
         <v>1</v>
@@ -4064,39 +4051,39 @@
     <row r="73" customFormat="1" customHeight="1" spans="1:15">
       <c r="B73" s="1"/>
       <c r="C73" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D73" s="1">
         <v>1</v>
       </c>
       <c r="E73" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" s="1">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="G73" s="1">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H73" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I73" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="I73" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="J73" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K73" s="1">
-        <v>4019</v>
+        <v>4014</v>
       </c>
       <c r="L73" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M73" s="1">
         <f t="shared" si="5"/>
-        <v>120000</v>
+        <v>20000</v>
       </c>
       <c r="N73" s="1">
         <v>1</v>
@@ -4104,55 +4091,52 @@
       <c r="O73" s="1"/>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D74" s="1">
         <v>1</v>
       </c>
       <c r="E74" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="1">
-        <v>500</v>
+        <v>15000</v>
       </c>
       <c r="G74" s="1">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H74" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I74" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="J74" s="1">
         <v>5</v>
       </c>
       <c r="K74" s="1">
-        <v>4001</v>
+        <v>4019</v>
       </c>
       <c r="L74" s="1">
-        <v>1000000</v>
+        <v>1</v>
       </c>
       <c r="M74" s="1">
         <f t="shared" si="5"/>
-        <v>20000</v>
+        <v>120000</v>
       </c>
       <c r="N74" s="1">
         <v>1</v>
       </c>
-      <c r="O74" s="1">
-        <v>300</v>
-      </c>
+      <c r="O74" s="1"/>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="1:15">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D75" s="1">
         <v>1</v>
@@ -4168,19 +4152,19 @@
         <v>40</v>
       </c>
       <c r="H75" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I75" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I75" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="J75" s="1">
         <v>5</v>
       </c>
       <c r="K75" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L75" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M75" s="1">
         <f t="shared" si="5"/>
@@ -4190,64 +4174,65 @@
         <v>1</v>
       </c>
       <c r="O75" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="1:15">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D76" s="1">
         <v>1</v>
       </c>
       <c r="E76" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F76" s="1">
-        <v>30000</v>
+        <v>500</v>
       </c>
       <c r="G76" s="1">
-        <v>10</v>
+        <f t="shared" si="4"/>
+        <v>40</v>
       </c>
       <c r="H76" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I76" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="I76" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="J76" s="1">
         <v>5</v>
       </c>
       <c r="K76" s="1">
-        <v>4026</v>
+        <v>4002</v>
       </c>
       <c r="L76" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M76" s="1">
         <f t="shared" si="5"/>
-        <v>300000</v>
+        <v>20000</v>
       </c>
       <c r="N76" s="1">
         <v>1</v>
       </c>
       <c r="O76" s="1">
-        <v>20</v>
+        <v>500</v>
       </c>
     </row>
     <row r="77" customFormat="1" customHeight="1" spans="1:15">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D77" s="1">
         <v>1</v>
       </c>
       <c r="E77" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F77" s="1">
         <v>30000</v>
@@ -4256,16 +4241,16 @@
         <v>10</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="J77" s="1">
         <v>5</v>
       </c>
       <c r="K77" s="1">
-        <v>4035</v>
+        <v>4026</v>
       </c>
       <c r="L77" s="1">
         <v>1</v>
@@ -4274,76 +4259,77 @@
         <f t="shared" si="5"/>
         <v>300000</v>
       </c>
-      <c r="N77" s="1"/>
+      <c r="N77" s="1">
+        <v>1</v>
+      </c>
       <c r="O77" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="1:15">
       <c r="A78" s="1"/>
-      <c r="B78"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-      <c r="K78" s="1"/>
-      <c r="L78" s="1"/>
-      <c r="M78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1">
+        <v>109</v>
+      </c>
+      <c r="D78" s="1">
+        <v>1</v>
+      </c>
+      <c r="E78" s="1">
+        <v>10</v>
+      </c>
+      <c r="F78" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G78" s="1">
+        <v>10</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J78" s="1">
+        <v>5</v>
+      </c>
+      <c r="K78" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L78" s="1">
+        <v>1</v>
+      </c>
+      <c r="M78" s="1">
+        <f t="shared" si="5"/>
+        <v>300000</v>
+      </c>
       <c r="N78" s="1"/>
       <c r="O78" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C79" s="1">
-        <v>201</v>
-      </c>
-      <c r="D79" s="1">
-        <v>2</v>
-      </c>
-      <c r="E79" s="1">
-        <v>0</v>
-      </c>
-      <c r="F79" s="5">
-        <v>200</v>
-      </c>
-      <c r="G79" s="1">
-        <f t="shared" ref="G79:G84" si="6">N79*O83</f>
-        <v>300</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J79" s="1">
-        <v>5</v>
-      </c>
-      <c r="K79" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L79" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M79" s="1">
-        <f t="shared" ref="M79:M86" si="7">F79*G79</f>
-        <v>60000</v>
-      </c>
-      <c r="N79" s="1">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A79" s="1"/>
+      <c r="B79"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="1"/>
+      <c r="M79" s="1"/>
+      <c r="N79" s="1"/>
       <c r="O79" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C80" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D80" s="1">
         <v>2</v>
@@ -4355,162 +4341,162 @@
         <v>200</v>
       </c>
       <c r="G80" s="1">
+        <f t="shared" ref="G80:G85" si="6">N80*O84</f>
+        <v>300</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J80" s="1">
+        <v>5</v>
+      </c>
+      <c r="K80" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L80" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M80" s="1">
+        <f t="shared" ref="M80:M87" si="7">F80*G80</f>
+        <v>60000</v>
+      </c>
+      <c r="N80" s="1">
+        <v>1</v>
+      </c>
+      <c r="O80" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="81" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C81" s="1">
+        <v>202</v>
+      </c>
+      <c r="D81" s="1">
+        <v>2</v>
+      </c>
+      <c r="E81" s="1">
+        <v>0</v>
+      </c>
+      <c r="F81" s="5">
+        <v>200</v>
+      </c>
+      <c r="G81" s="1">
         <f t="shared" si="6"/>
         <v>500</v>
       </c>
-      <c r="H80" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="I80" s="1" t="s">
+      <c r="H81" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="J80" s="1">
-        <v>5</v>
-      </c>
-      <c r="K80" s="1">
+      <c r="I81" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J81" s="1">
+        <v>5</v>
+      </c>
+      <c r="K81" s="1">
         <v>4101</v>
       </c>
-      <c r="L80" s="1">
+      <c r="L81" s="1">
         <v>1000</v>
       </c>
-      <c r="M80" s="1">
+      <c r="M81" s="1">
         <f t="shared" si="7"/>
         <v>100000</v>
       </c>
-      <c r="N80" s="1">
-        <v>1</v>
-      </c>
-      <c r="O80" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C81" s="1">
+      <c r="N81" s="1">
+        <v>1</v>
+      </c>
+      <c r="O81" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C82" s="1">
         <v>203</v>
       </c>
-      <c r="D81" s="1">
+      <c r="D82" s="1">
         <v>2</v>
       </c>
-      <c r="E81" s="1">
-        <v>0</v>
-      </c>
-      <c r="F81" s="5">
+      <c r="E82" s="1">
+        <v>0</v>
+      </c>
+      <c r="F82" s="5">
         <v>2000</v>
       </c>
-      <c r="G81" s="1">
+      <c r="G82" s="1">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="H81" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I81" s="1" t="s">
+      <c r="H82" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="J81" s="1">
+      <c r="I82" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J82" s="1">
         <v>15</v>
       </c>
-      <c r="K81" s="1">
+      <c r="K82" s="1">
         <v>4014</v>
       </c>
-      <c r="L81" s="1">
+      <c r="L82" s="1">
         <v>100</v>
       </c>
-      <c r="M81" s="1">
+      <c r="M82" s="1">
         <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="N81" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A82"/>
-      <c r="C82" s="1">
+      <c r="N82" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A83"/>
+      <c r="C83" s="1">
         <v>204</v>
       </c>
-      <c r="D82" s="1">
+      <c r="D83" s="1">
         <v>2</v>
       </c>
-      <c r="E82" s="1">
-        <v>1</v>
-      </c>
-      <c r="F82" s="5">
+      <c r="E83" s="1">
+        <v>1</v>
+      </c>
+      <c r="F83" s="5">
         <v>30000</v>
       </c>
-      <c r="G82" s="1">
+      <c r="G83" s="1">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="H82" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="I82" s="1" t="s">
+      <c r="H83" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="J82" s="1">
-        <v>5</v>
-      </c>
-      <c r="K82" s="1">
+      <c r="I83" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J83" s="1">
+        <v>5</v>
+      </c>
+      <c r="K83" s="1">
         <v>4019</v>
       </c>
-      <c r="L82" s="1">
-        <v>1</v>
-      </c>
-      <c r="M82" s="1">
+      <c r="L83" s="1">
+        <v>1</v>
+      </c>
+      <c r="M83" s="1">
         <f t="shared" si="7"/>
         <v>240000</v>
       </c>
-      <c r="N82" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C83" s="1">
-        <v>205</v>
-      </c>
-      <c r="D83" s="1">
-        <v>2</v>
-      </c>
-      <c r="E83" s="1">
-        <v>0</v>
-      </c>
-      <c r="F83" s="5">
-        <v>1000</v>
-      </c>
-      <c r="G83" s="1">
-        <f t="shared" si="6"/>
-        <v>40</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="J83" s="1">
-        <v>5</v>
-      </c>
-      <c r="K83" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L83" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M83" s="1">
-        <f t="shared" si="7"/>
-        <v>40000</v>
-      </c>
       <c r="N83" s="1">
         <v>1</v>
-      </c>
-      <c r="O83" s="1">
-        <v>300</v>
       </c>
     </row>
     <row r="84" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C84" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D84" s="1">
         <v>2</v>
@@ -4526,19 +4512,19 @@
         <v>40</v>
       </c>
       <c r="H84" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I84" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I84" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="J84" s="1">
         <v>5</v>
       </c>
       <c r="K84" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L84" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M84" s="1">
         <f t="shared" si="7"/>
@@ -4548,60 +4534,61 @@
         <v>1</v>
       </c>
       <c r="O84" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="85" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C85" s="1">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D85" s="1">
         <v>2</v>
       </c>
       <c r="E85" s="1">
-        <v>6</v>
-      </c>
-      <c r="F85" s="1">
-        <v>30000</v>
+        <v>0</v>
+      </c>
+      <c r="F85" s="5">
+        <v>1000</v>
       </c>
       <c r="G85" s="1">
-        <v>10</v>
+        <f t="shared" si="6"/>
+        <v>40</v>
       </c>
       <c r="H85" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I85" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="I85" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="J85" s="1">
         <v>5</v>
       </c>
       <c r="K85" s="1">
-        <v>4026</v>
+        <v>4002</v>
       </c>
       <c r="L85" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M85" s="1">
         <f t="shared" si="7"/>
-        <v>300000</v>
+        <v>40000</v>
       </c>
       <c r="N85" s="1">
         <v>1</v>
       </c>
       <c r="O85" s="1">
-        <v>20</v>
+        <v>500</v>
       </c>
     </row>
     <row r="86" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C86" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D86" s="1">
         <v>2</v>
       </c>
       <c r="E86" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F86" s="1">
         <v>30000</v>
@@ -4610,16 +4597,16 @@
         <v>10</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="J86" s="1">
         <v>5</v>
       </c>
       <c r="K86" s="1">
-        <v>4035</v>
+        <v>4026</v>
       </c>
       <c r="L86" s="1">
         <v>1</v>
@@ -4628,75 +4615,74 @@
         <f t="shared" si="7"/>
         <v>300000</v>
       </c>
+      <c r="N86" s="1">
+        <v>1</v>
+      </c>
       <c r="O86" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C87" s="1">
+        <v>208</v>
+      </c>
+      <c r="D87" s="1">
+        <v>2</v>
+      </c>
+      <c r="E87" s="1">
+        <v>10</v>
+      </c>
+      <c r="F87" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G87" s="1">
+        <v>10</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J87" s="1">
+        <v>5</v>
+      </c>
+      <c r="K87" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L87" s="1">
+        <v>1</v>
+      </c>
+      <c r="M87" s="1">
+        <f t="shared" si="7"/>
+        <v>300000</v>
+      </c>
+      <c r="O87" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="87" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A87" s="1"/>
-      <c r="B87"/>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1"/>
-      <c r="K87" s="1"/>
-      <c r="L87" s="1"/>
-      <c r="M87" s="1"/>
-      <c r="N87" s="1"/>
-      <c r="O87" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="88" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C88" s="1">
-        <v>211</v>
-      </c>
-      <c r="D88" s="1">
-        <v>3</v>
-      </c>
-      <c r="E88" s="1">
-        <v>0</v>
-      </c>
-      <c r="F88" s="1">
-        <v>400</v>
-      </c>
-      <c r="G88" s="1">
-        <f t="shared" ref="G88:G93" si="8">N88*O92</f>
-        <v>300</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J88" s="1">
-        <v>5</v>
-      </c>
-      <c r="K88" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L88" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M88" s="1">
-        <f t="shared" ref="M88:M95" si="9">F88*G88</f>
-        <v>120000</v>
-      </c>
-      <c r="N88" s="1">
-        <v>1</v>
-      </c>
+    <row r="88" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A88" s="1"/>
+      <c r="B88"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+      <c r="M88" s="1"/>
+      <c r="N88" s="1"/>
       <c r="O88" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C89" s="1">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D89" s="1">
         <v>3</v>
@@ -4708,162 +4694,162 @@
         <v>400</v>
       </c>
       <c r="G89" s="1">
+        <f t="shared" ref="G89:G94" si="8">N89*O93</f>
+        <v>300</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J89" s="1">
+        <v>5</v>
+      </c>
+      <c r="K89" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L89" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M89" s="1">
+        <f t="shared" ref="M89:M96" si="9">F89*G89</f>
+        <v>120000</v>
+      </c>
+      <c r="N89" s="1">
+        <v>1</v>
+      </c>
+      <c r="O89" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="90" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C90" s="1">
+        <v>212</v>
+      </c>
+      <c r="D90" s="1">
+        <v>3</v>
+      </c>
+      <c r="E90" s="1">
+        <v>0</v>
+      </c>
+      <c r="F90" s="1">
+        <v>400</v>
+      </c>
+      <c r="G90" s="1">
         <f t="shared" si="8"/>
         <v>500</v>
       </c>
-      <c r="H89" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="I89" s="1" t="s">
+      <c r="H90" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="J89" s="1">
-        <v>5</v>
-      </c>
-      <c r="K89" s="1">
+      <c r="I90" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J90" s="1">
+        <v>5</v>
+      </c>
+      <c r="K90" s="1">
         <v>4101</v>
       </c>
-      <c r="L89" s="1">
+      <c r="L90" s="1">
         <v>1000</v>
       </c>
-      <c r="M89" s="1">
+      <c r="M90" s="1">
         <f t="shared" si="9"/>
         <v>200000</v>
       </c>
-      <c r="N89" s="1">
-        <v>1</v>
-      </c>
-      <c r="O89" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C90" s="1">
+      <c r="N90" s="1">
+        <v>1</v>
+      </c>
+      <c r="O90" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C91" s="1">
         <v>213</v>
       </c>
-      <c r="D90" s="1">
+      <c r="D91" s="1">
         <v>3</v>
       </c>
-      <c r="E90" s="1">
-        <v>0</v>
-      </c>
-      <c r="F90" s="1">
+      <c r="E91" s="1">
+        <v>0</v>
+      </c>
+      <c r="F91" s="1">
         <v>4000</v>
       </c>
-      <c r="G90" s="1">
+      <c r="G91" s="1">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="H90" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I90" s="1" t="s">
+      <c r="H91" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="J90" s="1">
+      <c r="I91" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J91" s="1">
         <v>15</v>
       </c>
-      <c r="K90" s="1">
+      <c r="K91" s="1">
         <v>4014</v>
       </c>
-      <c r="L90" s="1">
+      <c r="L91" s="1">
         <v>100</v>
       </c>
-      <c r="M90" s="1">
+      <c r="M91" s="1">
         <f t="shared" si="9"/>
         <v>80000</v>
       </c>
-      <c r="N90" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A91"/>
-      <c r="C91" s="1">
+      <c r="N91" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A92"/>
+      <c r="C92" s="1">
         <v>214</v>
       </c>
-      <c r="D91" s="1">
+      <c r="D92" s="1">
         <v>3</v>
       </c>
-      <c r="E91" s="1">
-        <v>1</v>
-      </c>
-      <c r="F91" s="1">
+      <c r="E92" s="1">
+        <v>1</v>
+      </c>
+      <c r="F92" s="1">
         <v>45000</v>
       </c>
-      <c r="G91" s="1">
+      <c r="G92" s="1">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="H91" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="I91" s="1" t="s">
+      <c r="H92" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="J91" s="1">
-        <v>5</v>
-      </c>
-      <c r="K91" s="1">
+      <c r="I92" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J92" s="1">
+        <v>5</v>
+      </c>
+      <c r="K92" s="1">
         <v>4019</v>
       </c>
-      <c r="L91" s="1">
-        <v>1</v>
-      </c>
-      <c r="M91" s="1">
+      <c r="L92" s="1">
+        <v>1</v>
+      </c>
+      <c r="M92" s="1">
         <f t="shared" si="9"/>
         <v>360000</v>
       </c>
-      <c r="N91" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C92" s="1">
-        <v>215</v>
-      </c>
-      <c r="D92" s="1">
-        <v>3</v>
-      </c>
-      <c r="E92" s="1">
-        <v>0</v>
-      </c>
-      <c r="F92" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G92" s="1">
-        <f t="shared" si="8"/>
-        <v>40</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="J92" s="1">
-        <v>5</v>
-      </c>
-      <c r="K92" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L92" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M92" s="1">
-        <f t="shared" si="9"/>
-        <v>80000</v>
-      </c>
       <c r="N92" s="1">
         <v>1</v>
-      </c>
-      <c r="O92" s="1">
-        <v>300</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C93" s="1">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D93" s="1">
         <v>3</v>
@@ -4879,19 +4865,19 @@
         <v>40</v>
       </c>
       <c r="H93" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I93" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I93" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="J93" s="1">
         <v>5</v>
       </c>
       <c r="K93" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L93" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M93" s="1">
         <f t="shared" si="9"/>
@@ -4901,60 +4887,61 @@
         <v>1</v>
       </c>
       <c r="O93" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C94" s="1">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D94" s="1">
         <v>3</v>
       </c>
       <c r="E94" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F94" s="1">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="G94" s="1">
-        <v>10</v>
+        <f t="shared" si="8"/>
+        <v>40</v>
       </c>
       <c r="H94" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I94" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="I94" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="J94" s="1">
         <v>5</v>
       </c>
       <c r="K94" s="1">
-        <v>4026</v>
+        <v>4002</v>
       </c>
       <c r="L94" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M94" s="1">
         <f t="shared" si="9"/>
-        <v>300000</v>
+        <v>80000</v>
       </c>
       <c r="N94" s="1">
         <v>1</v>
       </c>
       <c r="O94" s="1">
-        <v>20</v>
+        <v>500</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C95" s="1">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D95" s="1">
         <v>3</v>
       </c>
       <c r="E95" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F95" s="1">
         <v>30000</v>
@@ -4963,16 +4950,16 @@
         <v>10</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="J95" s="1">
         <v>5</v>
       </c>
       <c r="K95" s="1">
-        <v>4035</v>
+        <v>4026</v>
       </c>
       <c r="L95" s="1">
         <v>1</v>
@@ -4981,75 +4968,74 @@
         <f t="shared" si="9"/>
         <v>300000</v>
       </c>
+      <c r="N95" s="1">
+        <v>1</v>
+      </c>
       <c r="O95" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="96" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C96" s="1">
+        <v>218</v>
+      </c>
+      <c r="D96" s="1">
+        <v>3</v>
+      </c>
+      <c r="E96" s="1">
+        <v>10</v>
+      </c>
+      <c r="F96" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G96" s="1">
+        <v>10</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J96" s="1">
+        <v>5</v>
+      </c>
+      <c r="K96" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L96" s="1">
+        <v>1</v>
+      </c>
+      <c r="M96" s="1">
+        <f t="shared" si="9"/>
+        <v>300000</v>
+      </c>
+      <c r="O96" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="96" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A96" s="1"/>
-      <c r="B96"/>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="1"/>
-      <c r="G96" s="1"/>
-      <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="1"/>
-      <c r="K96" s="1"/>
-      <c r="L96" s="1"/>
-      <c r="M96" s="1"/>
-      <c r="N96" s="1"/>
-      <c r="O96" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="97" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C97" s="1">
-        <v>221</v>
-      </c>
-      <c r="D97" s="1">
-        <v>4</v>
-      </c>
-      <c r="E97" s="1">
-        <v>0</v>
-      </c>
-      <c r="F97" s="5">
-        <v>600</v>
-      </c>
-      <c r="G97" s="1">
-        <f t="shared" ref="G97:G102" si="10">N97*O101</f>
-        <v>300</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J97" s="1">
-        <v>5</v>
-      </c>
-      <c r="K97" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L97" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M97" s="1">
-        <f t="shared" ref="M97:M104" si="11">F97*G97</f>
-        <v>180000</v>
-      </c>
-      <c r="N97" s="1">
-        <v>1</v>
-      </c>
+    <row r="97" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A97" s="1"/>
+      <c r="B97"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
+      <c r="K97" s="1"/>
+      <c r="L97" s="1"/>
+      <c r="M97" s="1"/>
+      <c r="N97" s="1"/>
       <c r="O97" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C98" s="1">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D98" s="1">
         <v>4</v>
@@ -5061,162 +5047,162 @@
         <v>600</v>
       </c>
       <c r="G98" s="1">
+        <f t="shared" ref="G98:G103" si="10">N98*O102</f>
+        <v>300</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J98" s="1">
+        <v>5</v>
+      </c>
+      <c r="K98" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L98" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M98" s="1">
+        <f t="shared" ref="M98:M105" si="11">F98*G98</f>
+        <v>180000</v>
+      </c>
+      <c r="N98" s="1">
+        <v>1</v>
+      </c>
+      <c r="O98" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="99" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C99" s="1">
+        <v>222</v>
+      </c>
+      <c r="D99" s="1">
+        <v>4</v>
+      </c>
+      <c r="E99" s="1">
+        <v>0</v>
+      </c>
+      <c r="F99" s="5">
+        <v>600</v>
+      </c>
+      <c r="G99" s="1">
         <f t="shared" si="10"/>
         <v>500</v>
       </c>
-      <c r="H98" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="I98" s="1" t="s">
+      <c r="H99" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="J98" s="1">
-        <v>5</v>
-      </c>
-      <c r="K98" s="1">
+      <c r="I99" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J99" s="1">
+        <v>5</v>
+      </c>
+      <c r="K99" s="1">
         <v>4101</v>
       </c>
-      <c r="L98" s="1">
+      <c r="L99" s="1">
         <v>1000</v>
       </c>
-      <c r="M98" s="1">
+      <c r="M99" s="1">
         <f t="shared" si="11"/>
         <v>300000</v>
       </c>
-      <c r="N98" s="1">
-        <v>1</v>
-      </c>
-      <c r="O98" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="99" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C99" s="1">
+      <c r="N99" s="1">
+        <v>1</v>
+      </c>
+      <c r="O99" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C100" s="1">
         <v>223</v>
       </c>
-      <c r="D99" s="1">
+      <c r="D100" s="1">
         <v>4</v>
       </c>
-      <c r="E99" s="1">
-        <v>0</v>
-      </c>
-      <c r="F99" s="5">
+      <c r="E100" s="1">
+        <v>0</v>
+      </c>
+      <c r="F100" s="5">
         <v>6000</v>
       </c>
-      <c r="G99" s="1">
+      <c r="G100" s="1">
         <f t="shared" si="10"/>
         <v>20</v>
       </c>
-      <c r="H99" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I99" s="1" t="s">
+      <c r="H100" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="J99" s="1">
+      <c r="I100" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J100" s="1">
         <v>15</v>
       </c>
-      <c r="K99" s="1">
+      <c r="K100" s="1">
         <v>4014</v>
       </c>
-      <c r="L99" s="1">
+      <c r="L100" s="1">
         <v>100</v>
       </c>
-      <c r="M99" s="1">
+      <c r="M100" s="1">
         <f t="shared" si="11"/>
         <v>120000</v>
       </c>
-      <c r="N99" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A100"/>
-      <c r="C100" s="1">
+      <c r="N100" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A101"/>
+      <c r="C101" s="1">
         <v>224</v>
       </c>
-      <c r="D100" s="1">
+      <c r="D101" s="1">
         <v>4</v>
       </c>
-      <c r="E100" s="1">
-        <v>1</v>
-      </c>
-      <c r="F100" s="5">
+      <c r="E101" s="1">
+        <v>1</v>
+      </c>
+      <c r="F101" s="5">
         <v>60000</v>
       </c>
-      <c r="G100" s="1">
+      <c r="G101" s="1">
         <f t="shared" si="10"/>
         <v>8</v>
       </c>
-      <c r="H100" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="I100" s="1" t="s">
+      <c r="H101" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="J100" s="1">
-        <v>5</v>
-      </c>
-      <c r="K100" s="1">
+      <c r="I101" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J101" s="1">
+        <v>5</v>
+      </c>
+      <c r="K101" s="1">
         <v>4019</v>
       </c>
-      <c r="L100" s="1">
-        <v>1</v>
-      </c>
-      <c r="M100" s="1">
+      <c r="L101" s="1">
+        <v>1</v>
+      </c>
+      <c r="M101" s="1">
         <f t="shared" si="11"/>
         <v>480000</v>
       </c>
-      <c r="N100" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C101" s="1">
-        <v>225</v>
-      </c>
-      <c r="D101" s="1">
-        <v>4</v>
-      </c>
-      <c r="E101" s="1">
-        <v>0</v>
-      </c>
-      <c r="F101" s="5">
-        <v>3000</v>
-      </c>
-      <c r="G101" s="1">
-        <f t="shared" si="10"/>
-        <v>40</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="J101" s="1">
-        <v>5</v>
-      </c>
-      <c r="K101" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L101" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M101" s="1">
-        <f t="shared" si="11"/>
-        <v>120000</v>
-      </c>
       <c r="N101" s="1">
         <v>1</v>
-      </c>
-      <c r="O101" s="1">
-        <v>300</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C102" s="1">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D102" s="1">
         <v>4</v>
@@ -5232,19 +5218,19 @@
         <v>40</v>
       </c>
       <c r="H102" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I102" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I102" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="J102" s="1">
         <v>5</v>
       </c>
       <c r="K102" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L102" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M102" s="1">
         <f t="shared" si="11"/>
@@ -5254,60 +5240,61 @@
         <v>1</v>
       </c>
       <c r="O102" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C103" s="1">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D103" s="1">
         <v>4</v>
       </c>
       <c r="E103" s="1">
-        <v>6</v>
-      </c>
-      <c r="F103" s="1">
-        <v>30000</v>
+        <v>0</v>
+      </c>
+      <c r="F103" s="5">
+        <v>3000</v>
       </c>
       <c r="G103" s="1">
-        <v>10</v>
+        <f t="shared" si="10"/>
+        <v>40</v>
       </c>
       <c r="H103" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I103" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="I103" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="J103" s="1">
         <v>5</v>
       </c>
       <c r="K103" s="1">
-        <v>4026</v>
+        <v>4002</v>
       </c>
       <c r="L103" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M103" s="1">
         <f t="shared" si="11"/>
-        <v>300000</v>
+        <v>120000</v>
       </c>
       <c r="N103" s="1">
         <v>1</v>
       </c>
       <c r="O103" s="1">
-        <v>20</v>
+        <v>500</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C104" s="1">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D104" s="1">
         <v>4</v>
       </c>
       <c r="E104" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F104" s="1">
         <v>30000</v>
@@ -5316,16 +5303,16 @@
         <v>10</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="J104" s="1">
         <v>5</v>
       </c>
       <c r="K104" s="1">
-        <v>4035</v>
+        <v>4026</v>
       </c>
       <c r="L104" s="1">
         <v>1</v>
@@ -5334,75 +5321,74 @@
         <f t="shared" si="11"/>
         <v>300000</v>
       </c>
+      <c r="N104" s="1">
+        <v>1</v>
+      </c>
       <c r="O104" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C105" s="1">
+        <v>228</v>
+      </c>
+      <c r="D105" s="1">
+        <v>4</v>
+      </c>
+      <c r="E105" s="1">
+        <v>10</v>
+      </c>
+      <c r="F105" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G105" s="1">
+        <v>10</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J105" s="1">
+        <v>5</v>
+      </c>
+      <c r="K105" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L105" s="1">
+        <v>1</v>
+      </c>
+      <c r="M105" s="1">
+        <f t="shared" si="11"/>
+        <v>300000</v>
+      </c>
+      <c r="O105" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="105" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A105" s="1"/>
-      <c r="B105"/>
-      <c r="C105" s="1"/>
-      <c r="D105" s="1"/>
-      <c r="E105" s="1"/>
-      <c r="F105" s="1"/>
-      <c r="G105" s="1"/>
-      <c r="H105" s="1"/>
-      <c r="I105" s="1"/>
-      <c r="J105" s="1"/>
-      <c r="K105" s="1"/>
-      <c r="L105" s="1"/>
-      <c r="M105" s="1"/>
-      <c r="N105" s="1"/>
-      <c r="O105" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="106" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C106" s="1">
-        <v>231</v>
-      </c>
-      <c r="D106" s="1">
-        <v>5</v>
-      </c>
-      <c r="E106" s="1">
-        <v>0</v>
-      </c>
-      <c r="F106" s="1">
-        <v>800</v>
-      </c>
-      <c r="G106" s="1">
-        <f t="shared" ref="G106:G111" si="12">N106*O110</f>
-        <v>1200</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J106" s="1">
-        <v>5</v>
-      </c>
-      <c r="K106" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L106" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M106" s="1">
-        <f t="shared" ref="M106:M113" si="13">F106*G106</f>
-        <v>960000</v>
-      </c>
-      <c r="N106" s="1">
-        <v>4</v>
-      </c>
+    <row r="106" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A106" s="1"/>
+      <c r="B106"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1"/>
+      <c r="K106" s="1"/>
+      <c r="L106" s="1"/>
+      <c r="M106" s="1"/>
+      <c r="N106" s="1"/>
       <c r="O106" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C107" s="1">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D107" s="1">
         <v>5</v>
@@ -5414,162 +5400,162 @@
         <v>800</v>
       </c>
       <c r="G107" s="1">
+        <f t="shared" ref="G107:G112" si="12">N107*O111</f>
+        <v>1200</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J107" s="1">
+        <v>5</v>
+      </c>
+      <c r="K107" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L107" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M107" s="1">
+        <f t="shared" ref="M107:M114" si="13">F107*G107</f>
+        <v>960000</v>
+      </c>
+      <c r="N107" s="1">
+        <v>4</v>
+      </c>
+      <c r="O107" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="108" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C108" s="1">
+        <v>232</v>
+      </c>
+      <c r="D108" s="1">
+        <v>5</v>
+      </c>
+      <c r="E108" s="1">
+        <v>0</v>
+      </c>
+      <c r="F108" s="1">
+        <v>800</v>
+      </c>
+      <c r="G108" s="1">
         <f t="shared" si="12"/>
         <v>2000</v>
       </c>
-      <c r="H107" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="I107" s="1" t="s">
+      <c r="H108" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="J107" s="1">
-        <v>5</v>
-      </c>
-      <c r="K107" s="1">
+      <c r="I108" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J108" s="1">
+        <v>5</v>
+      </c>
+      <c r="K108" s="1">
         <v>4101</v>
       </c>
-      <c r="L107" s="1">
+      <c r="L108" s="1">
         <v>1000</v>
       </c>
-      <c r="M107" s="1">
+      <c r="M108" s="1">
         <f t="shared" si="13"/>
         <v>1600000</v>
       </c>
-      <c r="N107" s="1">
+      <c r="N108" s="1">
         <v>4</v>
       </c>
-      <c r="O107" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="108" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C108" s="1">
+      <c r="O108" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C109" s="1">
         <v>233</v>
       </c>
-      <c r="D108" s="1">
-        <v>5</v>
-      </c>
-      <c r="E108" s="1">
-        <v>0</v>
-      </c>
-      <c r="F108" s="1">
+      <c r="D109" s="1">
+        <v>5</v>
+      </c>
+      <c r="E109" s="1">
+        <v>0</v>
+      </c>
+      <c r="F109" s="1">
         <v>8000</v>
       </c>
-      <c r="G108" s="1">
+      <c r="G109" s="1">
         <f t="shared" si="12"/>
         <v>40</v>
       </c>
-      <c r="H108" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I108" s="1" t="s">
+      <c r="H109" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="J108" s="1">
+      <c r="I109" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J109" s="1">
         <v>15</v>
       </c>
-      <c r="K108" s="1">
+      <c r="K109" s="1">
         <v>4014</v>
       </c>
-      <c r="L108" s="1">
+      <c r="L109" s="1">
         <v>100</v>
       </c>
-      <c r="M108" s="1">
+      <c r="M109" s="1">
         <f t="shared" si="13"/>
         <v>320000</v>
       </c>
-      <c r="N108" s="1">
+      <c r="N109" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="109" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A109"/>
-      <c r="C109" s="1">
+    <row r="110" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A110"/>
+      <c r="C110" s="1">
         <v>234</v>
       </c>
-      <c r="D109" s="1">
-        <v>5</v>
-      </c>
-      <c r="E109" s="1">
-        <v>1</v>
-      </c>
-      <c r="F109" s="1">
+      <c r="D110" s="1">
+        <v>5</v>
+      </c>
+      <c r="E110" s="1">
+        <v>1</v>
+      </c>
+      <c r="F110" s="1">
         <v>75000</v>
       </c>
-      <c r="G109" s="1">
+      <c r="G110" s="1">
         <f t="shared" si="12"/>
         <v>32</v>
       </c>
-      <c r="H109" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="I109" s="1" t="s">
+      <c r="H110" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="J109" s="1">
-        <v>5</v>
-      </c>
-      <c r="K109" s="1">
+      <c r="I110" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J110" s="1">
+        <v>5</v>
+      </c>
+      <c r="K110" s="1">
         <v>4019</v>
       </c>
-      <c r="L109" s="1">
-        <v>1</v>
-      </c>
-      <c r="M109" s="1">
+      <c r="L110" s="1">
+        <v>1</v>
+      </c>
+      <c r="M110" s="1">
         <f t="shared" si="13"/>
         <v>2400000</v>
       </c>
-      <c r="N109" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C110" s="1">
-        <v>235</v>
-      </c>
-      <c r="D110" s="1">
-        <v>5</v>
-      </c>
-      <c r="E110" s="1">
-        <v>0</v>
-      </c>
-      <c r="F110" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G110" s="1">
-        <f t="shared" si="12"/>
-        <v>160</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="J110" s="1">
-        <v>5</v>
-      </c>
-      <c r="K110" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L110" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M110" s="1">
-        <f t="shared" si="13"/>
-        <v>640000</v>
-      </c>
       <c r="N110" s="1">
         <v>4</v>
       </c>
-      <c r="O110" s="1">
-        <v>300</v>
-      </c>
     </row>
     <row r="111" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C111" s="1">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D111" s="1">
         <v>5</v>
@@ -5585,19 +5571,19 @@
         <v>160</v>
       </c>
       <c r="H111" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I111" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I111" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="J111" s="1">
         <v>5</v>
       </c>
       <c r="K111" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L111" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M111" s="1">
         <f t="shared" si="13"/>
@@ -5607,60 +5593,61 @@
         <v>4</v>
       </c>
       <c r="O111" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C112" s="1">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D112" s="1">
         <v>5</v>
       </c>
       <c r="E112" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F112" s="1">
-        <v>30000</v>
+        <v>4000</v>
       </c>
       <c r="G112" s="1">
-        <v>10</v>
+        <f t="shared" si="12"/>
+        <v>160</v>
       </c>
       <c r="H112" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I112" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="I112" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="J112" s="1">
         <v>5</v>
       </c>
       <c r="K112" s="1">
-        <v>4026</v>
+        <v>4002</v>
       </c>
       <c r="L112" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M112" s="1">
         <f t="shared" si="13"/>
-        <v>300000</v>
+        <v>640000</v>
       </c>
       <c r="N112" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O112" s="1">
-        <v>10</v>
+        <v>500</v>
       </c>
     </row>
     <row r="113" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C113" s="1">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D113" s="1">
         <v>5</v>
       </c>
       <c r="E113" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F113" s="1">
         <v>30000</v>
@@ -5669,16 +5656,16 @@
         <v>10</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="J113" s="1">
         <v>5</v>
       </c>
       <c r="K113" s="1">
-        <v>4035</v>
+        <v>4026</v>
       </c>
       <c r="L113" s="1">
         <v>1</v>
@@ -5687,176 +5674,218 @@
         <f t="shared" si="13"/>
         <v>300000</v>
       </c>
+      <c r="N113" s="1">
+        <v>1</v>
+      </c>
       <c r="O113" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C114" s="1">
+        <v>238</v>
+      </c>
+      <c r="D114" s="1">
+        <v>5</v>
+      </c>
+      <c r="E114" s="1">
+        <v>10</v>
+      </c>
+      <c r="F114" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G114" s="1">
+        <v>10</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J114" s="1">
+        <v>5</v>
+      </c>
+      <c r="K114" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L114" s="1">
+        <v>1</v>
+      </c>
+      <c r="M114" s="1">
+        <f t="shared" si="13"/>
+        <v>300000</v>
+      </c>
+      <c r="O114" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="114" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A114" s="1"/>
-      <c r="B114"/>
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
-      <c r="E114" s="1"/>
-      <c r="F114" s="1"/>
-      <c r="G114" s="1"/>
-      <c r="H114" s="1"/>
-      <c r="I114" s="1"/>
-      <c r="J114" s="1"/>
-      <c r="K114" s="1"/>
-      <c r="L114" s="1"/>
-      <c r="M114" s="1"/>
-      <c r="N114"/>
-      <c r="O114" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="115" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C115" s="1">
-        <v>999</v>
-      </c>
-      <c r="D115" s="1">
-        <v>0</v>
-      </c>
-      <c r="E115" s="1">
-        <v>0</v>
-      </c>
-      <c r="F115" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G115" s="1">
-        <v>50</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J115" s="1">
-        <v>5</v>
-      </c>
-      <c r="K115" s="1">
-        <v>4006</v>
-      </c>
-      <c r="L115" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M115" s="1">
-        <f t="shared" ref="M115:M117" si="14">F115*G115</f>
-        <v>50000</v>
-      </c>
+    <row r="115" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A115" s="1"/>
+      <c r="B115"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
+      <c r="E115" s="1"/>
+      <c r="F115" s="1"/>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1"/>
+      <c r="K115" s="1"/>
+      <c r="L115" s="1"/>
+      <c r="M115" s="1"/>
+      <c r="N115"/>
       <c r="O115" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C116" s="1">
+        <v>999</v>
+      </c>
+      <c r="D116" s="1">
+        <v>0</v>
+      </c>
+      <c r="E116" s="1">
+        <v>0</v>
+      </c>
+      <c r="F116" s="1">
         <v>1000</v>
       </c>
-      <c r="D116" s="1">
-        <v>0</v>
-      </c>
-      <c r="E116" s="1">
-        <v>0</v>
-      </c>
-      <c r="F116" s="1">
+      <c r="G116" s="1">
+        <v>50</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J116" s="1">
+        <v>5</v>
+      </c>
+      <c r="K116" s="1">
+        <v>4006</v>
+      </c>
+      <c r="L116" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M116" s="1">
+        <f t="shared" ref="M116:M118" si="14">F116*G116</f>
+        <v>50000</v>
+      </c>
+      <c r="O116" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="117" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C117" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D117" s="1">
+        <v>0</v>
+      </c>
+      <c r="E117" s="1">
+        <v>0</v>
+      </c>
+      <c r="F117" s="1">
         <v>2000</v>
       </c>
-      <c r="G116" s="1">
+      <c r="G117" s="1">
         <v>1000</v>
       </c>
-      <c r="H116" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="I116" s="1" t="s">
+      <c r="H117" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="J116" s="1">
-        <v>5</v>
-      </c>
-      <c r="K116" s="1">
+      <c r="I117" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J117" s="1">
+        <v>5</v>
+      </c>
+      <c r="K117" s="1">
         <v>4010</v>
       </c>
-      <c r="L116" s="1">
-        <v>5</v>
-      </c>
-      <c r="M116" s="1">
+      <c r="L117" s="1">
+        <v>5</v>
+      </c>
+      <c r="M117" s="1">
         <f t="shared" si="14"/>
         <v>2000000</v>
       </c>
-      <c r="O116" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="117" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C117" s="1">
+      <c r="O117" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C118" s="1">
         <v>1001</v>
       </c>
-      <c r="D117" s="1">
-        <v>0</v>
-      </c>
-      <c r="E117" s="1">
-        <v>0</v>
-      </c>
-      <c r="F117" s="1">
+      <c r="D118" s="1">
+        <v>0</v>
+      </c>
+      <c r="E118" s="1">
+        <v>0</v>
+      </c>
+      <c r="F118" s="1">
         <v>2000</v>
       </c>
-      <c r="G117" s="1">
+      <c r="G118" s="1">
         <v>50</v>
       </c>
-      <c r="H117" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="I117" s="1" t="s">
+      <c r="H118" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="J117" s="1">
-        <v>5</v>
-      </c>
-      <c r="K117" s="1">
+      <c r="I118" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J118" s="1">
+        <v>5</v>
+      </c>
+      <c r="K118" s="1">
         <v>4102</v>
       </c>
-      <c r="L117" s="1">
+      <c r="L118" s="1">
         <v>20</v>
       </c>
-      <c r="M117" s="1">
+      <c r="M118" s="1">
         <f t="shared" si="14"/>
         <v>100000</v>
       </c>
     </row>
-    <row r="118" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A118"/>
-      <c r="B118" s="1"/>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
-      <c r="E118" s="1"/>
-      <c r="F118" s="1"/>
-      <c r="G118" s="1"/>
-      <c r="H118" s="1"/>
-      <c r="I118" s="1"/>
-      <c r="J118" s="1"/>
-      <c r="K118" s="1"/>
-      <c r="L118" s="1"/>
-      <c r="M118" s="1"/>
-      <c r="N118" s="1"/>
-      <c r="O118"/>
-    </row>
-    <row r="123" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A123" s="1"/>
-      <c r="B123" s="1"/>
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
-      <c r="E123" s="1"/>
-      <c r="F123" s="1"/>
-      <c r="G123" s="1"/>
-      <c r="H123" s="1"/>
-      <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
-      <c r="K123" s="1"/>
-      <c r="L123" s="1"/>
-      <c r="M123" s="1"/>
-      <c r="N123" s="1"/>
-      <c r="O123" s="1"/>
+    <row r="119" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A119"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+      <c r="E119" s="1"/>
+      <c r="F119" s="1"/>
+      <c r="G119" s="1"/>
+      <c r="H119" s="1"/>
+      <c r="I119" s="1"/>
+      <c r="J119" s="1"/>
+      <c r="K119" s="1"/>
+      <c r="L119" s="1"/>
+      <c r="M119" s="1"/>
+      <c r="N119" s="1"/>
+      <c r="O119"/>
+    </row>
+    <row r="124" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A124" s="1"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
+      <c r="E124" s="1"/>
+      <c r="F124" s="1"/>
+      <c r="G124" s="1"/>
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+      <c r="J124" s="1"/>
+      <c r="K124" s="1"/>
+      <c r="L124" s="1"/>
+      <c r="M124" s="1"/>
+      <c r="N124" s="1"/>
+      <c r="O124" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="161">
   <si>
     <t>#</t>
   </si>
@@ -357,6 +357,12 @@
   </si>
   <si>
     <t>低级法宝自选</t>
+  </si>
+  <si>
+    <t>兑换坐骑兽粮*100</t>
+  </si>
+  <si>
+    <t>坐骑兽粮*100</t>
   </si>
   <si>
     <t>兑换时装精华</t>
@@ -1514,7 +1520,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O124"/>
+  <dimension ref="A1:O126"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -2814,7 +2820,7 @@
         <v>1</v>
       </c>
       <c r="M38" s="1">
-        <f t="shared" ref="M38:M48" si="2">F38*G38</f>
+        <f t="shared" ref="M38:M49" si="2">F38*G38</f>
         <v>800000</v>
       </c>
     </row>
@@ -2901,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G41" s="1">
         <v>2000</v>
@@ -2923,7 +2929,7 @@
       </c>
       <c r="M41" s="1">
         <f t="shared" si="2"/>
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:13">
@@ -3178,64 +3184,46 @@
         <v>2500000</v>
       </c>
     </row>
-    <row r="49" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-      <c r="O49" s="1"/>
-    </row>
-    <row r="50" customFormat="1" customHeight="1" spans="1:15">
-      <c r="B50" s="1"/>
-      <c r="C50" s="1">
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C49" s="1">
         <v>44</v>
       </c>
-      <c r="D50" s="1">
-        <v>0</v>
-      </c>
-      <c r="E50" s="1">
-        <v>0</v>
-      </c>
-      <c r="F50" s="1">
-        <v>100000</v>
-      </c>
-      <c r="G50" s="1">
+      <c r="D49" s="1">
+        <v>0</v>
+      </c>
+      <c r="E49" s="1">
         <v>10</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="F49" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G49" s="1">
+        <v>500</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="I50" s="1" t="s">
+      <c r="I49" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="J50" s="1">
-        <v>5</v>
-      </c>
-      <c r="K50" s="1">
-        <v>4034</v>
-      </c>
-      <c r="L50" s="1">
-        <v>1</v>
-      </c>
-      <c r="M50" s="1">
-        <f t="shared" ref="M50:M67" si="3">F50*G50</f>
-        <v>1000000</v>
-      </c>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
+      <c r="J49" s="1">
+        <v>5</v>
+      </c>
+      <c r="K49" s="1">
+        <v>4022</v>
+      </c>
+      <c r="L49" s="1">
+        <v>100</v>
+      </c>
+      <c r="M49" s="1">
+        <f t="shared" si="2"/>
+        <v>500000</v>
+      </c>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="1:15">
       <c r="B51" s="1"/>
       <c r="C51" s="1">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
@@ -3244,53 +3232,52 @@
         <v>0</v>
       </c>
       <c r="F51" s="1">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="G51" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>112</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J51" s="1">
         <v>5</v>
       </c>
       <c r="K51" s="1">
-        <v>4112</v>
+        <v>4034</v>
       </c>
       <c r="L51" s="1">
         <v>1</v>
       </c>
       <c r="M51" s="1">
-        <f t="shared" si="3"/>
-        <v>300000</v>
+        <f>F51*G51</f>
+        <v>1000000</v>
       </c>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F52" s="1">
-        <v>80000</v>
+        <v>150000</v>
       </c>
       <c r="G52" s="1">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>114</v>
@@ -3299,157 +3286,119 @@
         <v>5</v>
       </c>
       <c r="K52" s="1">
-        <v>4033</v>
+        <v>4112</v>
       </c>
       <c r="L52" s="1">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="M52" s="1">
-        <f t="shared" si="3"/>
-        <v>1600000</v>
+        <f>F52*G52</f>
+        <v>300000</v>
       </c>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F53" s="1">
-        <v>500000</v>
+        <v>80000</v>
       </c>
       <c r="G53" s="1">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>115</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J53" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K53" s="1">
-        <v>29</v>
+        <v>4033</v>
       </c>
       <c r="L53" s="1">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="M53" s="1">
-        <f t="shared" si="3"/>
-        <v>1500000</v>
+        <f>F53*G53</f>
+        <v>1600000</v>
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
     </row>
     <row r="54" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A54" s="1"/>
       <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
+      <c r="C54" s="1">
+        <v>53</v>
+      </c>
+      <c r="D54" s="1">
+        <v>0</v>
+      </c>
+      <c r="E54" s="1">
+        <v>15</v>
+      </c>
+      <c r="F54" s="1">
+        <v>500000</v>
+      </c>
+      <c r="G54" s="1">
+        <v>3</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J54" s="1">
+        <v>4</v>
+      </c>
+      <c r="K54" s="1">
+        <v>29</v>
+      </c>
+      <c r="L54" s="1">
+        <v>1</v>
+      </c>
+      <c r="M54" s="1">
+        <f>F54*G54</f>
+        <v>1500000</v>
+      </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
-    </row>
-    <row r="55" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1">
-        <v>48</v>
-      </c>
-      <c r="D55" s="1">
-        <v>0</v>
-      </c>
-      <c r="E55" s="1">
-        <v>10</v>
-      </c>
-      <c r="F55" s="1">
-        <v>800000</v>
-      </c>
-      <c r="G55" s="1">
-        <v>1</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="J55" s="1">
-        <v>5</v>
-      </c>
-      <c r="K55" s="1">
-        <v>4025</v>
-      </c>
-      <c r="L55" s="1">
-        <v>1</v>
-      </c>
-      <c r="M55" s="1">
-        <f t="shared" si="3"/>
-        <v>800000</v>
-      </c>
-      <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
     </row>
     <row r="56" customFormat="1" customHeight="1" spans="1:15">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
-      <c r="C56" s="1">
-        <v>49</v>
-      </c>
-      <c r="D56" s="1">
-        <v>0</v>
-      </c>
-      <c r="E56" s="1">
-        <v>15</v>
-      </c>
-      <c r="F56" s="1">
-        <v>1500000</v>
-      </c>
-      <c r="G56" s="1">
-        <v>1</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J56" s="1">
-        <v>5</v>
-      </c>
-      <c r="K56" s="1">
-        <v>4041</v>
-      </c>
-      <c r="L56" s="1">
-        <v>1</v>
-      </c>
-      <c r="M56" s="1">
-        <f t="shared" si="3"/>
-        <v>1500000</v>
-      </c>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
     </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="57" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
       <c r="C57" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
@@ -3458,7 +3407,7 @@
         <v>10</v>
       </c>
       <c r="F57" s="1">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
@@ -3470,62 +3419,64 @@
         <v>118</v>
       </c>
       <c r="J57" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K57" s="1">
-        <v>205</v>
+        <v>4025</v>
       </c>
       <c r="L57" s="1">
         <v>1</v>
       </c>
       <c r="M57" s="1">
-        <f t="shared" si="3"/>
-        <v>1000000</v>
-      </c>
+        <f t="shared" ref="M57:M70" si="3">F57*G57</f>
+        <v>800000</v>
+      </c>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="1:15">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F58" s="1">
-        <v>100000</v>
+        <v>1500000</v>
       </c>
       <c r="G58" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>119</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J58" s="1">
         <v>5</v>
       </c>
       <c r="K58" s="1">
-        <v>4040</v>
+        <v>4041</v>
       </c>
       <c r="L58" s="1">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="M58" s="1">
         <f t="shared" si="3"/>
-        <v>1000000</v>
+        <v>1500000</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C59" s="1">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
@@ -3540,16 +3491,16 @@
         <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J59" s="1">
         <v>4</v>
       </c>
       <c r="K59" s="1">
-        <v>301</v>
+        <v>205</v>
       </c>
       <c r="L59" s="1">
         <v>1</v>
@@ -3560,268 +3511,232 @@
       </c>
     </row>
     <row r="60" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A60" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
       <c r="C60" s="1">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
+        <v>20</v>
+      </c>
+      <c r="F60" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G60" s="1">
         <v>10</v>
       </c>
-      <c r="F60" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G60" s="1">
-        <v>200</v>
-      </c>
       <c r="H60" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I60" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="I60" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="J60" s="1">
         <v>5</v>
       </c>
       <c r="K60" s="1">
-        <v>4035</v>
+        <v>4040</v>
       </c>
       <c r="L60" s="1">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="M60" s="1">
-        <f>F60*G60</f>
-        <v>6000000</v>
+        <f t="shared" si="3"/>
+        <v>1000000</v>
       </c>
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A61" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C61" s="1">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F61" s="1">
-        <v>30000</v>
+        <v>1000000</v>
       </c>
       <c r="G61" s="1">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J61" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K61" s="1">
-        <v>4039</v>
+        <v>301</v>
       </c>
       <c r="L61" s="1">
         <v>1</v>
       </c>
       <c r="M61" s="1">
-        <f>F61*G61</f>
-        <v>6000000</v>
-      </c>
-    </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A62" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>0</v>
-      </c>
+        <f t="shared" si="3"/>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
       <c r="C62" s="1">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F62" s="1">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="G62" s="1">
         <v>200</v>
       </c>
       <c r="H62" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J62" s="1">
+        <v>5</v>
+      </c>
+      <c r="K62" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L62" s="1">
+        <v>1</v>
+      </c>
+      <c r="M62" s="1">
+        <f t="shared" si="3"/>
+        <v>4000000</v>
+      </c>
+      <c r="N62" s="1"/>
+      <c r="O62" s="1"/>
+    </row>
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C63" s="1">
+        <v>66</v>
+      </c>
+      <c r="D63" s="1">
+        <v>0</v>
+      </c>
+      <c r="E63" s="1">
+        <v>15</v>
+      </c>
+      <c r="F63" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G63" s="1">
+        <v>200</v>
+      </c>
+      <c r="H63" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="I62" s="1" t="s">
+      <c r="I63" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="J62" s="1">
-        <v>5</v>
-      </c>
-      <c r="K62" s="1">
+      <c r="J63" s="1">
+        <v>5</v>
+      </c>
+      <c r="K63" s="1">
+        <v>4039</v>
+      </c>
+      <c r="L63" s="1">
+        <v>1</v>
+      </c>
+      <c r="M63" s="1">
+        <f t="shared" si="3"/>
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C64" s="1">
+        <v>67</v>
+      </c>
+      <c r="D64" s="1">
+        <v>0</v>
+      </c>
+      <c r="E64" s="1">
+        <v>20</v>
+      </c>
+      <c r="F64" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G64" s="1">
+        <v>200</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J64" s="1">
+        <v>5</v>
+      </c>
+      <c r="K64" s="1">
         <v>4038</v>
       </c>
-      <c r="L62" s="1">
-        <v>1</v>
-      </c>
-      <c r="M62" s="1">
-        <f>F62*G62</f>
+      <c r="L64" s="1">
+        <v>1</v>
+      </c>
+      <c r="M64" s="1">
+        <f t="shared" si="3"/>
         <v>6000000</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A63" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C63" s="1">
-        <v>55</v>
-      </c>
-      <c r="D63" s="1">
-        <v>0</v>
-      </c>
-      <c r="E63" s="1">
-        <v>0</v>
-      </c>
-      <c r="F63" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G63" s="1">
-        <v>3000</v>
-      </c>
-      <c r="H63" s="1" t="s">
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C65" s="1">
+        <v>68</v>
+      </c>
+      <c r="D65" s="1">
+        <v>0</v>
+      </c>
+      <c r="E65" s="1">
+        <v>0</v>
+      </c>
+      <c r="F65" s="1">
+        <v>500</v>
+      </c>
+      <c r="G65" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H65" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I63" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J63" s="1">
-        <v>5</v>
-      </c>
-      <c r="K63" s="1">
+      <c r="I65" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J65" s="1">
+        <v>5</v>
+      </c>
+      <c r="K65" s="1">
         <v>4022</v>
       </c>
-      <c r="L63" s="1">
+      <c r="L65" s="1">
         <v>100</v>
       </c>
-      <c r="M63" s="1">
-        <f>F63*G63</f>
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="64" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A64" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C64" s="1">
-        <v>56</v>
-      </c>
-      <c r="D64" s="1">
-        <v>0</v>
-      </c>
-      <c r="E64" s="1">
-        <v>15</v>
-      </c>
-      <c r="F64" s="1">
-        <v>100000</v>
-      </c>
-      <c r="G64" s="1">
-        <v>10</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J64" s="1">
-        <v>11</v>
-      </c>
-      <c r="K64" s="1">
-        <v>1998001</v>
-      </c>
-      <c r="L64" s="1">
-        <v>1</v>
-      </c>
-      <c r="M64" s="1">
-        <f>F64*G64</f>
+      <c r="M65" s="1">
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="1:15">
-      <c r="A65" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C65" s="1">
-        <v>57</v>
-      </c>
-      <c r="D65" s="1">
-        <v>0</v>
-      </c>
-      <c r="E65" s="1">
-        <v>15</v>
-      </c>
-      <c r="F65" s="1">
-        <v>100000</v>
-      </c>
-      <c r="G65" s="1">
-        <v>10</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J65" s="1">
-        <v>11</v>
-      </c>
-      <c r="K65" s="1">
-        <v>1998002</v>
-      </c>
-      <c r="L65" s="1">
-        <v>1</v>
-      </c>
-      <c r="M65" s="1">
-        <f>F65*G65</f>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="66" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A66" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C66" s="1">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
@@ -3836,36 +3751,28 @@
         <v>10</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J66" s="1">
         <v>11</v>
       </c>
       <c r="K66" s="1">
-        <v>1998003</v>
+        <v>1998001</v>
       </c>
       <c r="L66" s="1">
         <v>1</v>
       </c>
       <c r="M66" s="1">
-        <f>F66*G66</f>
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-    </row>
-    <row r="67" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A67" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>0</v>
-      </c>
+    </row>
+    <row r="67" customHeight="1" spans="1:15">
       <c r="C67" s="1">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
@@ -3880,36 +3787,30 @@
         <v>10</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J67" s="1">
         <v>11</v>
       </c>
       <c r="K67" s="1">
-        <v>1998004</v>
+        <v>1998002</v>
       </c>
       <c r="L67" s="1">
         <v>1</v>
       </c>
       <c r="M67" s="1">
-        <f>F67*G67</f>
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
     </row>
     <row r="68" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A68" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
       <c r="C68" s="1">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
@@ -3924,134 +3825,130 @@
         <v>10</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J68" s="1">
         <v>11</v>
       </c>
       <c r="K68" s="1">
-        <v>1998005</v>
+        <v>1998003</v>
       </c>
       <c r="L68" s="1">
         <v>1</v>
       </c>
       <c r="M68" s="1">
-        <f>F68*G68</f>
+        <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
       <c r="N68" s="1"/>
       <c r="O68" s="1"/>
     </row>
-    <row r="69" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A69"/>
-      <c r="B69"/>
+    <row r="69" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1">
+        <v>72</v>
+      </c>
+      <c r="D69" s="1">
+        <v>0</v>
+      </c>
+      <c r="E69" s="1">
+        <v>15</v>
+      </c>
+      <c r="F69" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G69" s="1">
+        <v>10</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J69" s="1">
+        <v>11</v>
+      </c>
+      <c r="K69" s="1">
+        <v>1998004</v>
+      </c>
+      <c r="L69" s="1">
+        <v>1</v>
+      </c>
+      <c r="M69" s="1">
+        <f t="shared" si="3"/>
+        <v>1000000</v>
+      </c>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-      <c r="M70" s="1"/>
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1">
+        <v>73</v>
+      </c>
+      <c r="D70" s="1">
+        <v>0</v>
+      </c>
+      <c r="E70" s="1">
+        <v>15</v>
+      </c>
+      <c r="F70" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G70" s="1">
+        <v>10</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J70" s="1">
+        <v>11</v>
+      </c>
+      <c r="K70" s="1">
+        <v>1998005</v>
+      </c>
+      <c r="L70" s="1">
+        <v>1</v>
+      </c>
+      <c r="M70" s="1">
+        <f t="shared" si="3"/>
+        <v>1000000</v>
+      </c>
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
     </row>
-    <row r="71" customFormat="1" customHeight="1" spans="1:15">
-      <c r="B71" s="1"/>
-      <c r="C71" s="1">
-        <v>102</v>
-      </c>
-      <c r="D71" s="1">
-        <v>1</v>
-      </c>
-      <c r="E71" s="1">
-        <v>0</v>
-      </c>
-      <c r="F71" s="1">
-        <v>100</v>
-      </c>
-      <c r="G71" s="1">
-        <f t="shared" ref="G71:G76" si="4">N71*O75</f>
-        <v>300</v>
-      </c>
-      <c r="H71" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J71" s="1">
-        <v>5</v>
-      </c>
-      <c r="K71" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L71" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M71" s="1">
-        <f t="shared" ref="M71:M78" si="5">F71*G71</f>
-        <v>30000</v>
-      </c>
-      <c r="N71" s="1">
-        <v>1</v>
-      </c>
-      <c r="O71" s="1"/>
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A71"/>
+      <c r="B71"/>
     </row>
     <row r="72" customFormat="1" customHeight="1" spans="1:15">
-      <c r="B72" s="1"/>
-      <c r="C72" s="1">
-        <v>103</v>
-      </c>
-      <c r="D72" s="1">
-        <v>1</v>
-      </c>
-      <c r="E72" s="1">
-        <v>0</v>
-      </c>
-      <c r="F72" s="1">
-        <v>100</v>
-      </c>
-      <c r="G72" s="1">
-        <f t="shared" si="4"/>
-        <v>500</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J72" s="1">
-        <v>5</v>
-      </c>
-      <c r="K72" s="1">
-        <v>4101</v>
-      </c>
-      <c r="L72" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M72" s="1">
-        <f t="shared" si="5"/>
-        <v>50000</v>
-      </c>
-      <c r="N72" s="1">
-        <v>1</v>
-      </c>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+      <c r="N72" s="1"/>
       <c r="O72" s="1"/>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="1:15">
       <c r="B73" s="1"/>
       <c r="C73" s="1">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D73" s="1">
         <v>1</v>
@@ -4060,30 +3957,30 @@
         <v>0</v>
       </c>
       <c r="F73" s="1">
+        <v>100</v>
+      </c>
+      <c r="G73" s="1">
+        <f t="shared" ref="G73:G78" si="4">N73*O77</f>
+        <v>300</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J73" s="1">
+        <v>5</v>
+      </c>
+      <c r="K73" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L73" s="1">
         <v>1000</v>
       </c>
-      <c r="G73" s="1">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J73" s="1">
-        <v>15</v>
-      </c>
-      <c r="K73" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L73" s="1">
-        <v>100</v>
-      </c>
       <c r="M73" s="1">
-        <f t="shared" si="5"/>
-        <v>20000</v>
+        <f t="shared" ref="M73:M80" si="5">F73*G73</f>
+        <v>30000</v>
       </c>
       <c r="N73" s="1">
         <v>1</v>
@@ -4093,39 +3990,39 @@
     <row r="74" customFormat="1" customHeight="1" spans="1:15">
       <c r="B74" s="1"/>
       <c r="C74" s="1">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D74" s="1">
         <v>1</v>
       </c>
       <c r="E74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" s="1">
-        <v>15000</v>
+        <v>100</v>
       </c>
       <c r="G74" s="1">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>500</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J74" s="1">
         <v>5</v>
       </c>
       <c r="K74" s="1">
-        <v>4019</v>
+        <v>4101</v>
       </c>
       <c r="L74" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="M74" s="1">
         <f t="shared" si="5"/>
-        <v>120000</v>
+        <v>50000</v>
       </c>
       <c r="N74" s="1">
         <v>1</v>
@@ -4133,10 +4030,9 @@
       <c r="O74" s="1"/>
     </row>
     <row r="75" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D75" s="1">
         <v>1</v>
@@ -4145,26 +4041,26 @@
         <v>0</v>
       </c>
       <c r="F75" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G75" s="1">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J75" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K75" s="1">
-        <v>4001</v>
+        <v>4014</v>
       </c>
       <c r="L75" s="1">
-        <v>1000000</v>
+        <v>100</v>
       </c>
       <c r="M75" s="1">
         <f t="shared" si="5"/>
@@ -4173,358 +4069,362 @@
       <c r="N75" s="1">
         <v>1</v>
       </c>
-      <c r="O75" s="1">
-        <v>300</v>
-      </c>
+      <c r="O75" s="1"/>
     </row>
     <row r="76" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D76" s="1">
         <v>1</v>
       </c>
       <c r="E76" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="1">
-        <v>500</v>
+        <v>15000</v>
       </c>
       <c r="G76" s="1">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J76" s="1">
         <v>5</v>
       </c>
       <c r="K76" s="1">
-        <v>4002</v>
+        <v>4019</v>
       </c>
       <c r="L76" s="1">
-        <v>6000000</v>
+        <v>1</v>
       </c>
       <c r="M76" s="1">
         <f t="shared" si="5"/>
-        <v>20000</v>
+        <v>120000</v>
       </c>
       <c r="N76" s="1">
         <v>1</v>
       </c>
-      <c r="O76" s="1">
-        <v>500</v>
-      </c>
+      <c r="O76" s="1"/>
     </row>
     <row r="77" customFormat="1" customHeight="1" spans="1:15">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D77" s="1">
         <v>1</v>
       </c>
       <c r="E77" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F77" s="1">
-        <v>30000</v>
+        <v>500</v>
       </c>
       <c r="G77" s="1">
-        <v>10</v>
+        <f t="shared" si="4"/>
+        <v>40</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J77" s="1">
         <v>5</v>
       </c>
       <c r="K77" s="1">
-        <v>4026</v>
+        <v>4001</v>
       </c>
       <c r="L77" s="1">
-        <v>1</v>
+        <v>1000000</v>
       </c>
       <c r="M77" s="1">
         <f t="shared" si="5"/>
-        <v>300000</v>
+        <v>20000</v>
       </c>
       <c r="N77" s="1">
         <v>1</v>
       </c>
       <c r="O77" s="1">
-        <v>20</v>
+        <v>300</v>
       </c>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="1:15">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D78" s="1">
         <v>1</v>
       </c>
       <c r="E78" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F78" s="1">
-        <v>30000</v>
+        <v>500</v>
       </c>
       <c r="G78" s="1">
-        <v>10</v>
+        <f t="shared" si="4"/>
+        <v>40</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="J78" s="1">
         <v>5</v>
       </c>
       <c r="K78" s="1">
-        <v>4035</v>
+        <v>4002</v>
       </c>
       <c r="L78" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M78" s="1">
         <f t="shared" si="5"/>
-        <v>300000</v>
-      </c>
-      <c r="N78" s="1"/>
+        <v>20000</v>
+      </c>
+      <c r="N78" s="1">
+        <v>1</v>
+      </c>
       <c r="O78" s="1">
-        <v>8</v>
+        <v>500</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="1:15">
       <c r="A79" s="1"/>
-      <c r="B79"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
-      <c r="K79" s="1"/>
-      <c r="L79" s="1"/>
-      <c r="M79" s="1"/>
-      <c r="N79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1">
+        <v>108</v>
+      </c>
+      <c r="D79" s="1">
+        <v>1</v>
+      </c>
+      <c r="E79" s="1">
+        <v>6</v>
+      </c>
+      <c r="F79" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G79" s="1">
+        <v>10</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J79" s="1">
+        <v>5</v>
+      </c>
+      <c r="K79" s="1">
+        <v>4026</v>
+      </c>
+      <c r="L79" s="1">
+        <v>1</v>
+      </c>
+      <c r="M79" s="1">
+        <f t="shared" si="5"/>
+        <v>200000</v>
+      </c>
+      <c r="N79" s="1">
+        <v>1</v>
+      </c>
       <c r="O79" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1">
+        <v>109</v>
+      </c>
+      <c r="D80" s="1">
+        <v>1</v>
+      </c>
+      <c r="E80" s="1">
+        <v>10</v>
+      </c>
+      <c r="F80" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G80" s="1">
+        <v>10</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J80" s="1">
+        <v>5</v>
+      </c>
+      <c r="K80" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L80" s="1">
+        <v>1</v>
+      </c>
+      <c r="M80" s="1">
+        <f t="shared" si="5"/>
+        <v>200000</v>
+      </c>
+      <c r="N80" s="1"/>
+      <c r="O80" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A81" s="1"/>
+      <c r="B81"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1"/>
+      <c r="N81" s="1"/>
+      <c r="O81" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="80" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C80" s="1">
+    <row r="82" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C82" s="1">
         <v>201</v>
       </c>
-      <c r="D80" s="1">
+      <c r="D82" s="1">
         <v>2</v>
       </c>
-      <c r="E80" s="1">
-        <v>0</v>
-      </c>
-      <c r="F80" s="5">
+      <c r="E82" s="1">
+        <v>0</v>
+      </c>
+      <c r="F82" s="5">
         <v>200</v>
       </c>
-      <c r="G80" s="1">
-        <f t="shared" ref="G80:G85" si="6">N80*O84</f>
+      <c r="G82" s="1">
+        <f t="shared" ref="G82:G87" si="6">N82*O86</f>
         <v>300</v>
       </c>
-      <c r="H80" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J80" s="1">
-        <v>5</v>
-      </c>
-      <c r="K80" s="1">
+      <c r="H82" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J82" s="1">
+        <v>5</v>
+      </c>
+      <c r="K82" s="1">
         <v>4007</v>
       </c>
-      <c r="L80" s="1">
+      <c r="L82" s="1">
         <v>1000</v>
       </c>
-      <c r="M80" s="1">
-        <f t="shared" ref="M80:M87" si="7">F80*G80</f>
+      <c r="M82" s="1">
+        <f t="shared" ref="M82:M89" si="7">F82*G82</f>
         <v>60000</v>
       </c>
-      <c r="N80" s="1">
-        <v>1</v>
-      </c>
-      <c r="O80" s="1">
+      <c r="N82" s="1">
+        <v>1</v>
+      </c>
+      <c r="O82" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="81" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C81" s="1">
+    <row r="83" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C83" s="1">
         <v>202</v>
       </c>
-      <c r="D81" s="1">
+      <c r="D83" s="1">
         <v>2</v>
       </c>
-      <c r="E81" s="1">
-        <v>0</v>
-      </c>
-      <c r="F81" s="5">
+      <c r="E83" s="1">
+        <v>0</v>
+      </c>
+      <c r="F83" s="5">
         <v>200</v>
       </c>
-      <c r="G81" s="1">
+      <c r="G83" s="1">
         <f t="shared" si="6"/>
         <v>500</v>
       </c>
-      <c r="H81" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J81" s="1">
-        <v>5</v>
-      </c>
-      <c r="K81" s="1">
+      <c r="H83" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J83" s="1">
+        <v>5</v>
+      </c>
+      <c r="K83" s="1">
         <v>4101</v>
       </c>
-      <c r="L81" s="1">
+      <c r="L83" s="1">
         <v>1000</v>
       </c>
-      <c r="M81" s="1">
+      <c r="M83" s="1">
         <f t="shared" si="7"/>
         <v>100000</v>
       </c>
-      <c r="N81" s="1">
-        <v>1</v>
-      </c>
-      <c r="O81" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C82" s="1">
+      <c r="N83" s="1">
+        <v>1</v>
+      </c>
+      <c r="O83" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C84" s="1">
         <v>203</v>
       </c>
-      <c r="D82" s="1">
+      <c r="D84" s="1">
         <v>2</v>
       </c>
-      <c r="E82" s="1">
-        <v>0</v>
-      </c>
-      <c r="F82" s="5">
+      <c r="E84" s="1">
+        <v>0</v>
+      </c>
+      <c r="F84" s="5">
         <v>2000</v>
       </c>
-      <c r="G82" s="1">
+      <c r="G84" s="1">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="H82" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J82" s="1">
+      <c r="H84" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J84" s="1">
         <v>15</v>
       </c>
-      <c r="K82" s="1">
+      <c r="K84" s="1">
         <v>4014</v>
       </c>
-      <c r="L82" s="1">
+      <c r="L84" s="1">
         <v>100</v>
-      </c>
-      <c r="M82" s="1">
-        <f t="shared" si="7"/>
-        <v>40000</v>
-      </c>
-      <c r="N82" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A83"/>
-      <c r="C83" s="1">
-        <v>204</v>
-      </c>
-      <c r="D83" s="1">
-        <v>2</v>
-      </c>
-      <c r="E83" s="1">
-        <v>1</v>
-      </c>
-      <c r="F83" s="5">
-        <v>30000</v>
-      </c>
-      <c r="G83" s="1">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J83" s="1">
-        <v>5</v>
-      </c>
-      <c r="K83" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L83" s="1">
-        <v>1</v>
-      </c>
-      <c r="M83" s="1">
-        <f t="shared" si="7"/>
-        <v>240000</v>
-      </c>
-      <c r="N83" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C84" s="1">
-        <v>205</v>
-      </c>
-      <c r="D84" s="1">
-        <v>2</v>
-      </c>
-      <c r="E84" s="1">
-        <v>0</v>
-      </c>
-      <c r="F84" s="5">
-        <v>1000</v>
-      </c>
-      <c r="G84" s="1">
-        <f t="shared" si="6"/>
-        <v>40</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J84" s="1">
-        <v>5</v>
-      </c>
-      <c r="K84" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L84" s="1">
-        <v>1000000</v>
       </c>
       <c r="M84" s="1">
         <f t="shared" si="7"/>
@@ -4533,351 +4433,351 @@
       <c r="N84" s="1">
         <v>1</v>
       </c>
-      <c r="O84" s="1">
-        <v>300</v>
-      </c>
     </row>
     <row r="85" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A85"/>
       <c r="C85" s="1">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D85" s="1">
         <v>2</v>
       </c>
       <c r="E85" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="5">
-        <v>1000</v>
+        <v>30000</v>
       </c>
       <c r="G85" s="1">
         <f t="shared" si="6"/>
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J85" s="1">
         <v>5</v>
       </c>
       <c r="K85" s="1">
-        <v>4002</v>
+        <v>4019</v>
       </c>
       <c r="L85" s="1">
-        <v>6000000</v>
+        <v>1</v>
       </c>
       <c r="M85" s="1">
         <f t="shared" si="7"/>
-        <v>40000</v>
+        <v>240000</v>
       </c>
       <c r="N85" s="1">
         <v>1</v>
-      </c>
-      <c r="O85" s="1">
-        <v>500</v>
       </c>
     </row>
     <row r="86" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C86" s="1">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D86" s="1">
         <v>2</v>
       </c>
       <c r="E86" s="1">
-        <v>6</v>
-      </c>
-      <c r="F86" s="1">
-        <v>30000</v>
+        <v>0</v>
+      </c>
+      <c r="F86" s="5">
+        <v>1000</v>
       </c>
       <c r="G86" s="1">
-        <v>10</v>
+        <f t="shared" si="6"/>
+        <v>40</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J86" s="1">
         <v>5</v>
       </c>
       <c r="K86" s="1">
-        <v>4026</v>
+        <v>4001</v>
       </c>
       <c r="L86" s="1">
-        <v>1</v>
+        <v>1000000</v>
       </c>
       <c r="M86" s="1">
         <f t="shared" si="7"/>
-        <v>300000</v>
+        <v>40000</v>
       </c>
       <c r="N86" s="1">
         <v>1</v>
       </c>
       <c r="O86" s="1">
-        <v>20</v>
+        <v>300</v>
       </c>
     </row>
     <row r="87" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C87" s="1">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D87" s="1">
         <v>2</v>
       </c>
       <c r="E87" s="1">
-        <v>10</v>
-      </c>
-      <c r="F87" s="1">
-        <v>30000</v>
+        <v>0</v>
+      </c>
+      <c r="F87" s="5">
+        <v>1000</v>
       </c>
       <c r="G87" s="1">
-        <v>10</v>
+        <f t="shared" si="6"/>
+        <v>40</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="J87" s="1">
         <v>5</v>
       </c>
       <c r="K87" s="1">
-        <v>4035</v>
+        <v>4002</v>
       </c>
       <c r="L87" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M87" s="1">
         <f t="shared" si="7"/>
-        <v>300000</v>
+        <v>40000</v>
+      </c>
+      <c r="N87" s="1">
+        <v>1</v>
       </c>
       <c r="O87" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A88" s="1"/>
-      <c r="B88"/>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1"/>
-      <c r="K88" s="1"/>
-      <c r="L88" s="1"/>
-      <c r="M88" s="1"/>
-      <c r="N88" s="1"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="88" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C88" s="1">
+        <v>207</v>
+      </c>
+      <c r="D88" s="1">
+        <v>2</v>
+      </c>
+      <c r="E88" s="1">
+        <v>6</v>
+      </c>
+      <c r="F88" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G88" s="1">
+        <v>10</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J88" s="1">
+        <v>5</v>
+      </c>
+      <c r="K88" s="1">
+        <v>4026</v>
+      </c>
+      <c r="L88" s="1">
+        <v>1</v>
+      </c>
+      <c r="M88" s="1">
+        <f t="shared" si="7"/>
+        <v>200000</v>
+      </c>
+      <c r="N88" s="1">
+        <v>1</v>
+      </c>
       <c r="O88" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C89" s="1">
+        <v>208</v>
+      </c>
+      <c r="D89" s="1">
+        <v>2</v>
+      </c>
+      <c r="E89" s="1">
+        <v>10</v>
+      </c>
+      <c r="F89" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G89" s="1">
+        <v>10</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J89" s="1">
+        <v>5</v>
+      </c>
+      <c r="K89" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L89" s="1">
+        <v>1</v>
+      </c>
+      <c r="M89" s="1">
+        <f t="shared" si="7"/>
+        <v>200000</v>
+      </c>
+      <c r="O89" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A90" s="1"/>
+      <c r="B90"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+      <c r="K90" s="1"/>
+      <c r="L90" s="1"/>
+      <c r="M90" s="1"/>
+      <c r="N90" s="1"/>
+      <c r="O90" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="91" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C91" s="1">
         <v>211</v>
       </c>
-      <c r="D89" s="1">
+      <c r="D91" s="1">
         <v>3</v>
       </c>
-      <c r="E89" s="1">
-        <v>0</v>
-      </c>
-      <c r="F89" s="1">
+      <c r="E91" s="1">
+        <v>0</v>
+      </c>
+      <c r="F91" s="1">
         <v>400</v>
       </c>
-      <c r="G89" s="1">
-        <f t="shared" ref="G89:G94" si="8">N89*O93</f>
+      <c r="G91" s="1">
+        <f t="shared" ref="G91:G96" si="8">N91*O95</f>
         <v>300</v>
       </c>
-      <c r="H89" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J89" s="1">
-        <v>5</v>
-      </c>
-      <c r="K89" s="1">
+      <c r="H91" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J91" s="1">
+        <v>5</v>
+      </c>
+      <c r="K91" s="1">
         <v>4007</v>
       </c>
-      <c r="L89" s="1">
+      <c r="L91" s="1">
         <v>1000</v>
       </c>
-      <c r="M89" s="1">
-        <f t="shared" ref="M89:M96" si="9">F89*G89</f>
+      <c r="M91" s="1">
+        <f t="shared" ref="M91:M98" si="9">F91*G91</f>
         <v>120000</v>
       </c>
-      <c r="N89" s="1">
-        <v>1</v>
-      </c>
-      <c r="O89" s="1">
+      <c r="N91" s="1">
+        <v>1</v>
+      </c>
+      <c r="O91" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="90" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C90" s="1">
+    <row r="92" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C92" s="1">
         <v>212</v>
       </c>
-      <c r="D90" s="1">
+      <c r="D92" s="1">
         <v>3</v>
       </c>
-      <c r="E90" s="1">
-        <v>0</v>
-      </c>
-      <c r="F90" s="1">
+      <c r="E92" s="1">
+        <v>0</v>
+      </c>
+      <c r="F92" s="1">
         <v>400</v>
       </c>
-      <c r="G90" s="1">
+      <c r="G92" s="1">
         <f t="shared" si="8"/>
         <v>500</v>
       </c>
-      <c r="H90" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J90" s="1">
-        <v>5</v>
-      </c>
-      <c r="K90" s="1">
+      <c r="H92" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J92" s="1">
+        <v>5</v>
+      </c>
+      <c r="K92" s="1">
         <v>4101</v>
       </c>
-      <c r="L90" s="1">
+      <c r="L92" s="1">
         <v>1000</v>
       </c>
-      <c r="M90" s="1">
+      <c r="M92" s="1">
         <f t="shared" si="9"/>
         <v>200000</v>
       </c>
-      <c r="N90" s="1">
-        <v>1</v>
-      </c>
-      <c r="O90" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C91" s="1">
+      <c r="N92" s="1">
+        <v>1</v>
+      </c>
+      <c r="O92" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C93" s="1">
         <v>213</v>
       </c>
-      <c r="D91" s="1">
+      <c r="D93" s="1">
         <v>3</v>
       </c>
-      <c r="E91" s="1">
-        <v>0</v>
-      </c>
-      <c r="F91" s="1">
+      <c r="E93" s="1">
+        <v>0</v>
+      </c>
+      <c r="F93" s="1">
         <v>4000</v>
       </c>
-      <c r="G91" s="1">
+      <c r="G93" s="1">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="H91" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J91" s="1">
+      <c r="H93" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J93" s="1">
         <v>15</v>
       </c>
-      <c r="K91" s="1">
+      <c r="K93" s="1">
         <v>4014</v>
       </c>
-      <c r="L91" s="1">
+      <c r="L93" s="1">
         <v>100</v>
-      </c>
-      <c r="M91" s="1">
-        <f t="shared" si="9"/>
-        <v>80000</v>
-      </c>
-      <c r="N91" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A92"/>
-      <c r="C92" s="1">
-        <v>214</v>
-      </c>
-      <c r="D92" s="1">
-        <v>3</v>
-      </c>
-      <c r="E92" s="1">
-        <v>1</v>
-      </c>
-      <c r="F92" s="1">
-        <v>45000</v>
-      </c>
-      <c r="G92" s="1">
-        <f t="shared" si="8"/>
-        <v>8</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J92" s="1">
-        <v>5</v>
-      </c>
-      <c r="K92" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L92" s="1">
-        <v>1</v>
-      </c>
-      <c r="M92" s="1">
-        <f t="shared" si="9"/>
-        <v>360000</v>
-      </c>
-      <c r="N92" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C93" s="1">
-        <v>215</v>
-      </c>
-      <c r="D93" s="1">
-        <v>3</v>
-      </c>
-      <c r="E93" s="1">
-        <v>0</v>
-      </c>
-      <c r="F93" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G93" s="1">
-        <f t="shared" si="8"/>
-        <v>40</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J93" s="1">
-        <v>5</v>
-      </c>
-      <c r="K93" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L93" s="1">
-        <v>1000000</v>
       </c>
       <c r="M93" s="1">
         <f t="shared" si="9"/>
@@ -4886,351 +4786,351 @@
       <c r="N93" s="1">
         <v>1</v>
       </c>
-      <c r="O93" s="1">
-        <v>300</v>
-      </c>
     </row>
     <row r="94" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A94"/>
       <c r="C94" s="1">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D94" s="1">
         <v>3</v>
       </c>
       <c r="E94" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="1">
-        <v>2000</v>
+        <v>45000</v>
       </c>
       <c r="G94" s="1">
         <f t="shared" si="8"/>
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J94" s="1">
         <v>5</v>
       </c>
       <c r="K94" s="1">
-        <v>4002</v>
+        <v>4019</v>
       </c>
       <c r="L94" s="1">
-        <v>6000000</v>
+        <v>1</v>
       </c>
       <c r="M94" s="1">
         <f t="shared" si="9"/>
-        <v>80000</v>
+        <v>360000</v>
       </c>
       <c r="N94" s="1">
         <v>1</v>
-      </c>
-      <c r="O94" s="1">
-        <v>500</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C95" s="1">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D95" s="1">
         <v>3</v>
       </c>
       <c r="E95" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F95" s="1">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="G95" s="1">
-        <v>10</v>
+        <f t="shared" si="8"/>
+        <v>40</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J95" s="1">
         <v>5</v>
       </c>
       <c r="K95" s="1">
-        <v>4026</v>
+        <v>4001</v>
       </c>
       <c r="L95" s="1">
-        <v>1</v>
+        <v>1000000</v>
       </c>
       <c r="M95" s="1">
         <f t="shared" si="9"/>
-        <v>300000</v>
+        <v>80000</v>
       </c>
       <c r="N95" s="1">
         <v>1</v>
       </c>
       <c r="O95" s="1">
-        <v>20</v>
+        <v>300</v>
       </c>
     </row>
     <row r="96" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C96" s="1">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D96" s="1">
         <v>3</v>
       </c>
       <c r="E96" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F96" s="1">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="G96" s="1">
-        <v>10</v>
+        <f t="shared" si="8"/>
+        <v>40</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="J96" s="1">
         <v>5</v>
       </c>
       <c r="K96" s="1">
-        <v>4035</v>
+        <v>4002</v>
       </c>
       <c r="L96" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M96" s="1">
         <f t="shared" si="9"/>
+        <v>80000</v>
+      </c>
+      <c r="N96" s="1">
+        <v>1</v>
+      </c>
+      <c r="O96" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="97" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C97" s="1">
+        <v>217</v>
+      </c>
+      <c r="D97" s="1">
+        <v>3</v>
+      </c>
+      <c r="E97" s="1">
+        <v>6</v>
+      </c>
+      <c r="F97" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G97" s="1">
+        <v>10</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J97" s="1">
+        <v>5</v>
+      </c>
+      <c r="K97" s="1">
+        <v>4026</v>
+      </c>
+      <c r="L97" s="1">
+        <v>1</v>
+      </c>
+      <c r="M97" s="1">
+        <f t="shared" si="9"/>
         <v>300000</v>
       </c>
-      <c r="O96" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A97" s="1"/>
-      <c r="B97"/>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="1"/>
-      <c r="G97" s="1"/>
-      <c r="H97" s="1"/>
-      <c r="I97" s="1"/>
-      <c r="J97" s="1"/>
-      <c r="K97" s="1"/>
-      <c r="L97" s="1"/>
-      <c r="M97" s="1"/>
-      <c r="N97" s="1"/>
+      <c r="N97" s="1">
+        <v>1</v>
+      </c>
       <c r="O97" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C98" s="1">
+        <v>218</v>
+      </c>
+      <c r="D98" s="1">
+        <v>3</v>
+      </c>
+      <c r="E98" s="1">
+        <v>10</v>
+      </c>
+      <c r="F98" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G98" s="1">
+        <v>10</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J98" s="1">
+        <v>5</v>
+      </c>
+      <c r="K98" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L98" s="1">
+        <v>1</v>
+      </c>
+      <c r="M98" s="1">
+        <f t="shared" si="9"/>
+        <v>200000</v>
+      </c>
+      <c r="O98" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A99" s="1"/>
+      <c r="B99"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1"/>
+      <c r="K99" s="1"/>
+      <c r="L99" s="1"/>
+      <c r="M99" s="1"/>
+      <c r="N99" s="1"/>
+      <c r="O99" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="100" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C100" s="1">
         <v>221</v>
       </c>
-      <c r="D98" s="1">
+      <c r="D100" s="1">
         <v>4</v>
       </c>
-      <c r="E98" s="1">
-        <v>0</v>
-      </c>
-      <c r="F98" s="5">
+      <c r="E100" s="1">
+        <v>0</v>
+      </c>
+      <c r="F100" s="5">
         <v>600</v>
       </c>
-      <c r="G98" s="1">
-        <f t="shared" ref="G98:G103" si="10">N98*O102</f>
+      <c r="G100" s="1">
+        <f t="shared" ref="G100:G105" si="10">N100*O104</f>
         <v>300</v>
       </c>
-      <c r="H98" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J98" s="1">
-        <v>5</v>
-      </c>
-      <c r="K98" s="1">
+      <c r="H100" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J100" s="1">
+        <v>5</v>
+      </c>
+      <c r="K100" s="1">
         <v>4007</v>
       </c>
-      <c r="L98" s="1">
+      <c r="L100" s="1">
         <v>1000</v>
       </c>
-      <c r="M98" s="1">
-        <f t="shared" ref="M98:M105" si="11">F98*G98</f>
+      <c r="M100" s="1">
+        <f t="shared" ref="M100:M107" si="11">F100*G100</f>
         <v>180000</v>
       </c>
-      <c r="N98" s="1">
-        <v>1</v>
-      </c>
-      <c r="O98" s="1">
+      <c r="N100" s="1">
+        <v>1</v>
+      </c>
+      <c r="O100" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="99" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C99" s="1">
+    <row r="101" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C101" s="1">
         <v>222</v>
       </c>
-      <c r="D99" s="1">
+      <c r="D101" s="1">
         <v>4</v>
       </c>
-      <c r="E99" s="1">
-        <v>0</v>
-      </c>
-      <c r="F99" s="5">
+      <c r="E101" s="1">
+        <v>0</v>
+      </c>
+      <c r="F101" s="5">
         <v>600</v>
       </c>
-      <c r="G99" s="1">
+      <c r="G101" s="1">
         <f t="shared" si="10"/>
         <v>500</v>
       </c>
-      <c r="H99" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J99" s="1">
-        <v>5</v>
-      </c>
-      <c r="K99" s="1">
+      <c r="H101" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J101" s="1">
+        <v>5</v>
+      </c>
+      <c r="K101" s="1">
         <v>4101</v>
       </c>
-      <c r="L99" s="1">
+      <c r="L101" s="1">
         <v>1000</v>
       </c>
-      <c r="M99" s="1">
+      <c r="M101" s="1">
         <f t="shared" si="11"/>
         <v>300000</v>
       </c>
-      <c r="N99" s="1">
-        <v>1</v>
-      </c>
-      <c r="O99" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="100" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C100" s="1">
+      <c r="N101" s="1">
+        <v>1</v>
+      </c>
+      <c r="O101" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C102" s="1">
         <v>223</v>
       </c>
-      <c r="D100" s="1">
+      <c r="D102" s="1">
         <v>4</v>
       </c>
-      <c r="E100" s="1">
-        <v>0</v>
-      </c>
-      <c r="F100" s="5">
+      <c r="E102" s="1">
+        <v>0</v>
+      </c>
+      <c r="F102" s="5">
         <v>6000</v>
       </c>
-      <c r="G100" s="1">
+      <c r="G102" s="1">
         <f t="shared" si="10"/>
         <v>20</v>
       </c>
-      <c r="H100" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J100" s="1">
+      <c r="H102" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J102" s="1">
         <v>15</v>
       </c>
-      <c r="K100" s="1">
+      <c r="K102" s="1">
         <v>4014</v>
       </c>
-      <c r="L100" s="1">
+      <c r="L102" s="1">
         <v>100</v>
-      </c>
-      <c r="M100" s="1">
-        <f t="shared" si="11"/>
-        <v>120000</v>
-      </c>
-      <c r="N100" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A101"/>
-      <c r="C101" s="1">
-        <v>224</v>
-      </c>
-      <c r="D101" s="1">
-        <v>4</v>
-      </c>
-      <c r="E101" s="1">
-        <v>1</v>
-      </c>
-      <c r="F101" s="5">
-        <v>60000</v>
-      </c>
-      <c r="G101" s="1">
-        <f t="shared" si="10"/>
-        <v>8</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J101" s="1">
-        <v>5</v>
-      </c>
-      <c r="K101" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L101" s="1">
-        <v>1</v>
-      </c>
-      <c r="M101" s="1">
-        <f t="shared" si="11"/>
-        <v>480000</v>
-      </c>
-      <c r="N101" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C102" s="1">
-        <v>225</v>
-      </c>
-      <c r="D102" s="1">
-        <v>4</v>
-      </c>
-      <c r="E102" s="1">
-        <v>0</v>
-      </c>
-      <c r="F102" s="5">
-        <v>3000</v>
-      </c>
-      <c r="G102" s="1">
-        <f t="shared" si="10"/>
-        <v>40</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J102" s="1">
-        <v>5</v>
-      </c>
-      <c r="K102" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L102" s="1">
-        <v>1000000</v>
       </c>
       <c r="M102" s="1">
         <f t="shared" si="11"/>
@@ -5239,653 +5139,734 @@
       <c r="N102" s="1">
         <v>1</v>
       </c>
-      <c r="O102" s="1">
-        <v>300</v>
-      </c>
     </row>
     <row r="103" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A103"/>
       <c r="C103" s="1">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D103" s="1">
         <v>4</v>
       </c>
       <c r="E103" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="5">
-        <v>3000</v>
+        <v>60000</v>
       </c>
       <c r="G103" s="1">
         <f t="shared" si="10"/>
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J103" s="1">
         <v>5</v>
       </c>
       <c r="K103" s="1">
-        <v>4002</v>
+        <v>4019</v>
       </c>
       <c r="L103" s="1">
-        <v>6000000</v>
+        <v>1</v>
       </c>
       <c r="M103" s="1">
         <f t="shared" si="11"/>
-        <v>120000</v>
+        <v>480000</v>
       </c>
       <c r="N103" s="1">
         <v>1</v>
-      </c>
-      <c r="O103" s="1">
-        <v>500</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C104" s="1">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D104" s="1">
         <v>4</v>
       </c>
       <c r="E104" s="1">
-        <v>6</v>
-      </c>
-      <c r="F104" s="1">
-        <v>30000</v>
+        <v>0</v>
+      </c>
+      <c r="F104" s="5">
+        <v>3000</v>
       </c>
       <c r="G104" s="1">
-        <v>10</v>
+        <f t="shared" si="10"/>
+        <v>40</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J104" s="1">
         <v>5</v>
       </c>
       <c r="K104" s="1">
-        <v>4026</v>
+        <v>4001</v>
       </c>
       <c r="L104" s="1">
-        <v>1</v>
+        <v>1000000</v>
       </c>
       <c r="M104" s="1">
         <f t="shared" si="11"/>
-        <v>300000</v>
+        <v>120000</v>
       </c>
       <c r="N104" s="1">
         <v>1</v>
       </c>
       <c r="O104" s="1">
-        <v>20</v>
+        <v>300</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C105" s="1">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D105" s="1">
         <v>4</v>
       </c>
       <c r="E105" s="1">
-        <v>10</v>
-      </c>
-      <c r="F105" s="1">
-        <v>30000</v>
+        <v>0</v>
+      </c>
+      <c r="F105" s="5">
+        <v>3000</v>
       </c>
       <c r="G105" s="1">
-        <v>10</v>
+        <f t="shared" si="10"/>
+        <v>40</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="J105" s="1">
         <v>5</v>
       </c>
       <c r="K105" s="1">
-        <v>4035</v>
+        <v>4002</v>
       </c>
       <c r="L105" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M105" s="1">
         <f t="shared" si="11"/>
-        <v>300000</v>
+        <v>120000</v>
+      </c>
+      <c r="N105" s="1">
+        <v>1</v>
       </c>
       <c r="O105" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="106" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A106" s="1"/>
-      <c r="B106"/>
-      <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
-      <c r="E106" s="1"/>
-      <c r="F106" s="1"/>
-      <c r="G106" s="1"/>
-      <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
-      <c r="J106" s="1"/>
-      <c r="K106" s="1"/>
-      <c r="L106" s="1"/>
-      <c r="M106" s="1"/>
-      <c r="N106" s="1"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="106" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C106" s="1">
+        <v>227</v>
+      </c>
+      <c r="D106" s="1">
+        <v>4</v>
+      </c>
+      <c r="E106" s="1">
+        <v>6</v>
+      </c>
+      <c r="F106" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G106" s="1">
+        <v>10</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J106" s="1">
+        <v>5</v>
+      </c>
+      <c r="K106" s="1">
+        <v>4026</v>
+      </c>
+      <c r="L106" s="1">
+        <v>1</v>
+      </c>
+      <c r="M106" s="1">
+        <f t="shared" si="11"/>
+        <v>200000</v>
+      </c>
+      <c r="N106" s="1">
+        <v>1</v>
+      </c>
       <c r="O106" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C107" s="1">
+        <v>228</v>
+      </c>
+      <c r="D107" s="1">
+        <v>4</v>
+      </c>
+      <c r="E107" s="1">
+        <v>10</v>
+      </c>
+      <c r="F107" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G107" s="1">
+        <v>10</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J107" s="1">
+        <v>5</v>
+      </c>
+      <c r="K107" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L107" s="1">
+        <v>1</v>
+      </c>
+      <c r="M107" s="1">
+        <f t="shared" si="11"/>
+        <v>200000</v>
+      </c>
+      <c r="O107" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A108" s="1"/>
+      <c r="B108"/>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
+      <c r="E108" s="1"/>
+      <c r="F108" s="1"/>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1"/>
+      <c r="K108" s="1"/>
+      <c r="L108" s="1"/>
+      <c r="M108" s="1"/>
+      <c r="N108" s="1"/>
+      <c r="O108" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="109" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C109" s="1">
         <v>231</v>
       </c>
-      <c r="D107" s="1">
-        <v>5</v>
-      </c>
-      <c r="E107" s="1">
-        <v>0</v>
-      </c>
-      <c r="F107" s="1">
+      <c r="D109" s="1">
+        <v>5</v>
+      </c>
+      <c r="E109" s="1">
+        <v>0</v>
+      </c>
+      <c r="F109" s="1">
         <v>800</v>
       </c>
-      <c r="G107" s="1">
-        <f t="shared" ref="G107:G112" si="12">N107*O111</f>
+      <c r="G109" s="1">
+        <f t="shared" ref="G109:G114" si="12">N109*O113</f>
         <v>1200</v>
       </c>
-      <c r="H107" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J107" s="1">
-        <v>5</v>
-      </c>
-      <c r="K107" s="1">
+      <c r="H109" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J109" s="1">
+        <v>5</v>
+      </c>
+      <c r="K109" s="1">
         <v>4007</v>
       </c>
-      <c r="L107" s="1">
+      <c r="L109" s="1">
         <v>1000</v>
       </c>
-      <c r="M107" s="1">
-        <f t="shared" ref="M107:M114" si="13">F107*G107</f>
+      <c r="M109" s="1">
+        <f t="shared" ref="M109:M116" si="13">F109*G109</f>
         <v>960000</v>
       </c>
-      <c r="N107" s="1">
+      <c r="N109" s="1">
         <v>4</v>
       </c>
-      <c r="O107" s="1">
+      <c r="O109" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="108" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C108" s="1">
+    <row r="110" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C110" s="1">
         <v>232</v>
       </c>
-      <c r="D108" s="1">
-        <v>5</v>
-      </c>
-      <c r="E108" s="1">
-        <v>0</v>
-      </c>
-      <c r="F108" s="1">
+      <c r="D110" s="1">
+        <v>5</v>
+      </c>
+      <c r="E110" s="1">
+        <v>0</v>
+      </c>
+      <c r="F110" s="1">
         <v>800</v>
       </c>
-      <c r="G108" s="1">
+      <c r="G110" s="1">
         <f t="shared" si="12"/>
         <v>2000</v>
       </c>
-      <c r="H108" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I108" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J108" s="1">
-        <v>5</v>
-      </c>
-      <c r="K108" s="1">
+      <c r="H110" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J110" s="1">
+        <v>5</v>
+      </c>
+      <c r="K110" s="1">
         <v>4101</v>
       </c>
-      <c r="L108" s="1">
+      <c r="L110" s="1">
         <v>1000</v>
       </c>
-      <c r="M108" s="1">
+      <c r="M110" s="1">
         <f t="shared" si="13"/>
         <v>1600000</v>
       </c>
-      <c r="N108" s="1">
+      <c r="N110" s="1">
         <v>4</v>
       </c>
-      <c r="O108" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="109" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C109" s="1">
+      <c r="O110" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C111" s="1">
         <v>233</v>
       </c>
-      <c r="D109" s="1">
-        <v>5</v>
-      </c>
-      <c r="E109" s="1">
-        <v>0</v>
-      </c>
-      <c r="F109" s="1">
+      <c r="D111" s="1">
+        <v>5</v>
+      </c>
+      <c r="E111" s="1">
+        <v>0</v>
+      </c>
+      <c r="F111" s="1">
         <v>8000</v>
       </c>
-      <c r="G109" s="1">
+      <c r="G111" s="1">
         <f t="shared" si="12"/>
         <v>40</v>
       </c>
-      <c r="H109" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J109" s="1">
+      <c r="H111" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J111" s="1">
         <v>15</v>
       </c>
-      <c r="K109" s="1">
+      <c r="K111" s="1">
         <v>4014</v>
       </c>
-      <c r="L109" s="1">
+      <c r="L111" s="1">
         <v>100</v>
       </c>
-      <c r="M109" s="1">
+      <c r="M111" s="1">
         <f t="shared" si="13"/>
         <v>320000</v>
       </c>
-      <c r="N109" s="1">
+      <c r="N111" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="110" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A110"/>
-      <c r="C110" s="1">
+    <row r="112" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A112"/>
+      <c r="C112" s="1">
         <v>234</v>
       </c>
-      <c r="D110" s="1">
-        <v>5</v>
-      </c>
-      <c r="E110" s="1">
-        <v>1</v>
-      </c>
-      <c r="F110" s="1">
+      <c r="D112" s="1">
+        <v>5</v>
+      </c>
+      <c r="E112" s="1">
+        <v>1</v>
+      </c>
+      <c r="F112" s="1">
         <v>75000</v>
       </c>
-      <c r="G110" s="1">
+      <c r="G112" s="1">
         <f t="shared" si="12"/>
         <v>32</v>
       </c>
-      <c r="H110" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J110" s="1">
-        <v>5</v>
-      </c>
-      <c r="K110" s="1">
+      <c r="H112" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J112" s="1">
+        <v>5</v>
+      </c>
+      <c r="K112" s="1">
         <v>4019</v>
       </c>
-      <c r="L110" s="1">
-        <v>1</v>
-      </c>
-      <c r="M110" s="1">
+      <c r="L112" s="1">
+        <v>1</v>
+      </c>
+      <c r="M112" s="1">
         <f t="shared" si="13"/>
         <v>2400000</v>
       </c>
-      <c r="N110" s="1">
+      <c r="N112" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="111" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C111" s="1">
+    <row r="113" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C113" s="1">
         <v>235</v>
       </c>
-      <c r="D111" s="1">
-        <v>5</v>
-      </c>
-      <c r="E111" s="1">
-        <v>0</v>
-      </c>
-      <c r="F111" s="1">
+      <c r="D113" s="1">
+        <v>5</v>
+      </c>
+      <c r="E113" s="1">
+        <v>0</v>
+      </c>
+      <c r="F113" s="1">
         <v>4000</v>
       </c>
-      <c r="G111" s="1">
+      <c r="G113" s="1">
         <f t="shared" si="12"/>
         <v>160</v>
       </c>
-      <c r="H111" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J111" s="1">
-        <v>5</v>
-      </c>
-      <c r="K111" s="1">
+      <c r="H113" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J113" s="1">
+        <v>5</v>
+      </c>
+      <c r="K113" s="1">
         <v>4001</v>
       </c>
-      <c r="L111" s="1">
+      <c r="L113" s="1">
         <v>1000000</v>
       </c>
-      <c r="M111" s="1">
+      <c r="M113" s="1">
         <f t="shared" si="13"/>
         <v>640000</v>
       </c>
-      <c r="N111" s="1">
+      <c r="N113" s="1">
         <v>4</v>
       </c>
-      <c r="O111" s="1">
+      <c r="O113" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="112" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C112" s="1">
+    <row r="114" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C114" s="1">
         <v>236</v>
       </c>
-      <c r="D112" s="1">
-        <v>5</v>
-      </c>
-      <c r="E112" s="1">
-        <v>0</v>
-      </c>
-      <c r="F112" s="1">
+      <c r="D114" s="1">
+        <v>5</v>
+      </c>
+      <c r="E114" s="1">
+        <v>0</v>
+      </c>
+      <c r="F114" s="1">
         <v>4000</v>
       </c>
-      <c r="G112" s="1">
+      <c r="G114" s="1">
         <f t="shared" si="12"/>
         <v>160</v>
       </c>
-      <c r="H112" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="I112" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J112" s="1">
-        <v>5</v>
-      </c>
-      <c r="K112" s="1">
+      <c r="H114" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J114" s="1">
+        <v>5</v>
+      </c>
+      <c r="K114" s="1">
         <v>4002</v>
       </c>
-      <c r="L112" s="1">
+      <c r="L114" s="1">
         <v>6000000</v>
       </c>
-      <c r="M112" s="1">
+      <c r="M114" s="1">
         <f t="shared" si="13"/>
         <v>640000</v>
       </c>
-      <c r="N112" s="1">
+      <c r="N114" s="1">
         <v>4</v>
       </c>
-      <c r="O112" s="1">
+      <c r="O114" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="113" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C113" s="1">
+    <row r="115" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C115" s="1">
         <v>237</v>
       </c>
-      <c r="D113" s="1">
-        <v>5</v>
-      </c>
-      <c r="E113" s="1">
+      <c r="D115" s="1">
+        <v>5</v>
+      </c>
+      <c r="E115" s="1">
         <v>6</v>
       </c>
-      <c r="F113" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G113" s="1">
+      <c r="F115" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G115" s="1">
         <v>10</v>
       </c>
-      <c r="H113" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="J113" s="1">
-        <v>5</v>
-      </c>
-      <c r="K113" s="1">
+      <c r="H115" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J115" s="1">
+        <v>5</v>
+      </c>
+      <c r="K115" s="1">
         <v>4026</v>
       </c>
-      <c r="L113" s="1">
-        <v>1</v>
-      </c>
-      <c r="M113" s="1">
+      <c r="L115" s="1">
+        <v>1</v>
+      </c>
+      <c r="M115" s="1">
         <f t="shared" si="13"/>
-        <v>300000</v>
-      </c>
-      <c r="N113" s="1">
-        <v>1</v>
-      </c>
-      <c r="O113" s="1">
+        <v>200000</v>
+      </c>
+      <c r="N115" s="1">
+        <v>1</v>
+      </c>
+      <c r="O115" s="1">
         <v>10</v>
-      </c>
-    </row>
-    <row r="114" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C114" s="1">
-        <v>238</v>
-      </c>
-      <c r="D114" s="1">
-        <v>5</v>
-      </c>
-      <c r="E114" s="1">
-        <v>10</v>
-      </c>
-      <c r="F114" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G114" s="1">
-        <v>10</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J114" s="1">
-        <v>5</v>
-      </c>
-      <c r="K114" s="1">
-        <v>4035</v>
-      </c>
-      <c r="L114" s="1">
-        <v>1</v>
-      </c>
-      <c r="M114" s="1">
-        <f t="shared" si="13"/>
-        <v>300000</v>
-      </c>
-      <c r="O114" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="115" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A115" s="1"/>
-      <c r="B115"/>
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
-      <c r="E115" s="1"/>
-      <c r="F115" s="1"/>
-      <c r="G115" s="1"/>
-      <c r="H115" s="1"/>
-      <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
-      <c r="K115" s="1"/>
-      <c r="L115" s="1"/>
-      <c r="M115" s="1"/>
-      <c r="N115"/>
-      <c r="O115" s="1">
-        <v>40</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C116" s="1">
+        <v>238</v>
+      </c>
+      <c r="D116" s="1">
+        <v>5</v>
+      </c>
+      <c r="E116" s="1">
+        <v>10</v>
+      </c>
+      <c r="F116" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G116" s="1">
+        <v>10</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J116" s="1">
+        <v>5</v>
+      </c>
+      <c r="K116" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L116" s="1">
+        <v>1</v>
+      </c>
+      <c r="M116" s="1">
+        <f t="shared" si="13"/>
+        <v>200000</v>
+      </c>
+      <c r="O116" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A117" s="1"/>
+      <c r="B117"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
+      <c r="E117" s="1"/>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1"/>
+      <c r="K117" s="1"/>
+      <c r="L117" s="1"/>
+      <c r="M117" s="1"/>
+      <c r="N117"/>
+      <c r="O117" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="118" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C118" s="1">
         <v>999</v>
       </c>
-      <c r="D116" s="1">
-        <v>0</v>
-      </c>
-      <c r="E116" s="1">
-        <v>0</v>
-      </c>
-      <c r="F116" s="1">
+      <c r="D118" s="1">
+        <v>0</v>
+      </c>
+      <c r="E118" s="1">
+        <v>0</v>
+      </c>
+      <c r="F118" s="1">
         <v>1000</v>
       </c>
-      <c r="G116" s="1">
+      <c r="G118" s="1">
         <v>50</v>
       </c>
-      <c r="H116" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J116" s="1">
-        <v>5</v>
-      </c>
-      <c r="K116" s="1">
+      <c r="H118" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J118" s="1">
+        <v>5</v>
+      </c>
+      <c r="K118" s="1">
         <v>4006</v>
       </c>
-      <c r="L116" s="1">
+      <c r="L118" s="1">
         <v>1000</v>
       </c>
-      <c r="M116" s="1">
-        <f t="shared" ref="M116:M118" si="14">F116*G116</f>
+      <c r="M118" s="1">
+        <f t="shared" ref="M118:M120" si="14">F118*G118</f>
         <v>50000</v>
       </c>
-      <c r="O116" s="1">
+      <c r="O118" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="117" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C117" s="1">
+    <row r="119" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C119" s="1">
         <v>1000</v>
       </c>
-      <c r="D117" s="1">
-        <v>0</v>
-      </c>
-      <c r="E117" s="1">
-        <v>0</v>
-      </c>
-      <c r="F117" s="1">
+      <c r="D119" s="1">
+        <v>0</v>
+      </c>
+      <c r="E119" s="1">
+        <v>0</v>
+      </c>
+      <c r="F119" s="1">
         <v>2000</v>
       </c>
-      <c r="G117" s="1">
+      <c r="G119" s="1">
         <v>1000</v>
       </c>
-      <c r="H117" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="I117" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J117" s="1">
-        <v>5</v>
-      </c>
-      <c r="K117" s="1">
+      <c r="H119" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J119" s="1">
+        <v>5</v>
+      </c>
+      <c r="K119" s="1">
         <v>4010</v>
       </c>
-      <c r="L117" s="1">
-        <v>5</v>
-      </c>
-      <c r="M117" s="1">
+      <c r="L119" s="1">
+        <v>5</v>
+      </c>
+      <c r="M119" s="1">
         <f t="shared" si="14"/>
         <v>2000000</v>
       </c>
-      <c r="O117" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="118" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C118" s="1">
+      <c r="O119" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C120" s="1">
         <v>1001</v>
       </c>
-      <c r="D118" s="1">
-        <v>0</v>
-      </c>
-      <c r="E118" s="1">
-        <v>0</v>
-      </c>
-      <c r="F118" s="1">
+      <c r="D120" s="1">
+        <v>0</v>
+      </c>
+      <c r="E120" s="1">
+        <v>0</v>
+      </c>
+      <c r="F120" s="1">
         <v>2000</v>
       </c>
-      <c r="G118" s="1">
+      <c r="G120" s="1">
         <v>50</v>
       </c>
-      <c r="H118" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="I118" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J118" s="1">
-        <v>5</v>
-      </c>
-      <c r="K118" s="1">
+      <c r="H120" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J120" s="1">
+        <v>5</v>
+      </c>
+      <c r="K120" s="1">
         <v>4102</v>
       </c>
-      <c r="L118" s="1">
+      <c r="L120" s="1">
         <v>20</v>
       </c>
-      <c r="M118" s="1">
+      <c r="M120" s="1">
         <f t="shared" si="14"/>
         <v>100000</v>
       </c>
     </row>
-    <row r="119" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A119"/>
-      <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
-      <c r="E119" s="1"/>
-      <c r="F119" s="1"/>
-      <c r="G119" s="1"/>
-      <c r="H119" s="1"/>
-      <c r="I119" s="1"/>
-      <c r="J119" s="1"/>
-      <c r="K119" s="1"/>
-      <c r="L119" s="1"/>
-      <c r="M119" s="1"/>
-      <c r="N119" s="1"/>
-      <c r="O119"/>
-    </row>
-    <row r="124" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A124" s="1"/>
-      <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
-      <c r="E124" s="1"/>
-      <c r="F124" s="1"/>
-      <c r="G124" s="1"/>
-      <c r="H124" s="1"/>
-      <c r="I124" s="1"/>
-      <c r="J124" s="1"/>
-      <c r="K124" s="1"/>
-      <c r="L124" s="1"/>
-      <c r="M124" s="1"/>
-      <c r="N124" s="1"/>
-      <c r="O124" s="1"/>
+    <row r="121" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A121"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
+      <c r="E121" s="1"/>
+      <c r="F121" s="1"/>
+      <c r="G121" s="1"/>
+      <c r="H121" s="1"/>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1"/>
+      <c r="K121" s="1"/>
+      <c r="L121" s="1"/>
+      <c r="M121" s="1"/>
+      <c r="N121" s="1"/>
+      <c r="O121"/>
+    </row>
+    <row r="126" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A126" s="1"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
+      <c r="E126" s="1"/>
+      <c r="F126" s="1"/>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1"/>
+      <c r="K126" s="1"/>
+      <c r="L126" s="1"/>
+      <c r="M126" s="1"/>
+      <c r="N126" s="1"/>
+      <c r="O126" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="159">
   <si>
     <t>#</t>
   </si>
@@ -287,16 +287,10 @@
     <t>魂骨自选</t>
   </si>
   <si>
-    <t>400000</t>
-  </si>
-  <si>
     <t>兑换极矿工礼包*1</t>
   </si>
   <si>
     <t>极矿工礼包</t>
-  </si>
-  <si>
-    <t>500000</t>
   </si>
   <si>
     <t>兑换极法宝自选*1</t>
@@ -2798,17 +2792,17 @@
       <c r="E38" s="1">
         <v>0</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>86</v>
+      <c r="F38" s="1">
+        <v>150000</v>
       </c>
       <c r="G38" s="1">
         <v>2</v>
       </c>
       <c r="H38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="J38" s="1">
         <v>4</v>
@@ -2821,7 +2815,7 @@
       </c>
       <c r="M38" s="1">
         <f t="shared" ref="M38:M49" si="2">F38*G38</f>
-        <v>800000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:13">
@@ -2834,17 +2828,17 @@
       <c r="E39" s="1">
         <v>0</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="1">
+        <v>300000</v>
+      </c>
+      <c r="G39" s="1">
+        <v>1</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="G39" s="1">
-        <v>1</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="J39" s="1">
         <v>4</v>
@@ -2857,7 +2851,7 @@
       </c>
       <c r="M39" s="1">
         <f t="shared" si="2"/>
-        <v>500000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:13">
@@ -2877,10 +2871,10 @@
         <v>2000</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J40" s="1">
         <v>5</v>
@@ -2913,10 +2907,10 @@
         <v>2000</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J41" s="1">
         <v>5</v>
@@ -2949,10 +2943,10 @@
         <v>200</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J42" s="1">
         <v>5</v>
@@ -2985,10 +2979,10 @@
         <v>50</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J43" s="1">
         <v>5</v>
@@ -3021,10 +3015,10 @@
         <v>40</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J44" s="1">
         <v>15</v>
@@ -3057,10 +3051,10 @@
         <v>1</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J45" s="1">
         <v>4</v>
@@ -3093,10 +3087,10 @@
         <v>2</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J46" s="1">
         <v>5</v>
@@ -3129,10 +3123,10 @@
         <v>200</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J47" s="1">
         <v>4</v>
@@ -3165,10 +3159,10 @@
         <v>50</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J48" s="1">
         <v>4</v>
@@ -3201,10 +3195,10 @@
         <v>500</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J49" s="1">
         <v>5</v>
@@ -3238,10 +3232,10 @@
         <v>10</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J51" s="1">
         <v>5</v>
@@ -3277,10 +3271,10 @@
         <v>2</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J52" s="1">
         <v>5</v>
@@ -3317,10 +3311,10 @@
         <v>20</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J53" s="1">
         <v>5</v>
@@ -3356,10 +3350,10 @@
         <v>3</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J54" s="1">
         <v>4</v>
@@ -3413,10 +3407,10 @@
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J57" s="1">
         <v>5</v>
@@ -3453,10 +3447,10 @@
         <v>1</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J58" s="1">
         <v>5</v>
@@ -3491,10 +3485,10 @@
         <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J59" s="1">
         <v>4</v>
@@ -3529,10 +3523,10 @@
         <v>10</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J60" s="1">
         <v>5</v>
@@ -3567,10 +3561,10 @@
         <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J61" s="1">
         <v>4</v>
@@ -3605,10 +3599,10 @@
         <v>200</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J62" s="1">
         <v>5</v>
@@ -3643,10 +3637,10 @@
         <v>200</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J63" s="1">
         <v>5</v>
@@ -3679,10 +3673,10 @@
         <v>200</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J64" s="1">
         <v>5</v>
@@ -3715,10 +3709,10 @@
         <v>2000</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J65" s="1">
         <v>5</v>
@@ -3751,10 +3745,10 @@
         <v>10</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J66" s="1">
         <v>11</v>
@@ -3787,10 +3781,10 @@
         <v>10</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J67" s="1">
         <v>11</v>
@@ -3825,10 +3819,10 @@
         <v>10</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J68" s="1">
         <v>11</v>
@@ -3865,10 +3859,10 @@
         <v>10</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J69" s="1">
         <v>11</v>
@@ -3905,10 +3899,10 @@
         <v>10</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J70" s="1">
         <v>11</v>
@@ -3964,10 +3958,10 @@
         <v>300</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J73" s="1">
         <v>5</v>
@@ -4006,10 +4000,10 @@
         <v>500</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J74" s="1">
         <v>5</v>
@@ -4048,10 +4042,10 @@
         <v>20</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J75" s="1">
         <v>15</v>
@@ -4090,10 +4084,10 @@
         <v>8</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J76" s="1">
         <v>5</v>
@@ -4133,10 +4127,10 @@
         <v>40</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J77" s="1">
         <v>5</v>
@@ -4178,10 +4172,10 @@
         <v>40</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J78" s="1">
         <v>5</v>
@@ -4222,10 +4216,10 @@
         <v>10</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J79" s="1">
         <v>5</v>
@@ -4266,10 +4260,10 @@
         <v>10</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J80" s="1">
         <v>5</v>
@@ -4326,10 +4320,10 @@
         <v>300</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J82" s="1">
         <v>5</v>
@@ -4369,10 +4363,10 @@
         <v>500</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J83" s="1">
         <v>5</v>
@@ -4412,10 +4406,10 @@
         <v>20</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J84" s="1">
         <v>15</v>
@@ -4453,10 +4447,10 @@
         <v>8</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J85" s="1">
         <v>5</v>
@@ -4493,10 +4487,10 @@
         <v>40</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J86" s="1">
         <v>5</v>
@@ -4536,10 +4530,10 @@
         <v>40</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J87" s="1">
         <v>5</v>
@@ -4578,10 +4572,10 @@
         <v>10</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J88" s="1">
         <v>5</v>
@@ -4620,10 +4614,10 @@
         <v>10</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J89" s="1">
         <v>5</v>
@@ -4679,10 +4673,10 @@
         <v>300</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J91" s="1">
         <v>5</v>
@@ -4722,10 +4716,10 @@
         <v>500</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J92" s="1">
         <v>5</v>
@@ -4765,10 +4759,10 @@
         <v>20</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J93" s="1">
         <v>15</v>
@@ -4806,10 +4800,10 @@
         <v>8</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J94" s="1">
         <v>5</v>
@@ -4846,10 +4840,10 @@
         <v>40</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J95" s="1">
         <v>5</v>
@@ -4889,10 +4883,10 @@
         <v>40</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J96" s="1">
         <v>5</v>
@@ -4931,10 +4925,10 @@
         <v>10</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J97" s="1">
         <v>5</v>
@@ -4973,10 +4967,10 @@
         <v>10</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J98" s="1">
         <v>5</v>
@@ -5032,10 +5026,10 @@
         <v>300</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J100" s="1">
         <v>5</v>
@@ -5075,10 +5069,10 @@
         <v>500</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J101" s="1">
         <v>5</v>
@@ -5118,10 +5112,10 @@
         <v>20</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J102" s="1">
         <v>15</v>
@@ -5159,10 +5153,10 @@
         <v>8</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J103" s="1">
         <v>5</v>
@@ -5199,10 +5193,10 @@
         <v>40</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J104" s="1">
         <v>5</v>
@@ -5242,10 +5236,10 @@
         <v>40</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J105" s="1">
         <v>5</v>
@@ -5284,10 +5278,10 @@
         <v>10</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J106" s="1">
         <v>5</v>
@@ -5326,10 +5320,10 @@
         <v>10</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J107" s="1">
         <v>5</v>
@@ -5385,10 +5379,10 @@
         <v>1200</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J109" s="1">
         <v>5</v>
@@ -5428,10 +5422,10 @@
         <v>2000</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J110" s="1">
         <v>5</v>
@@ -5471,10 +5465,10 @@
         <v>40</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J111" s="1">
         <v>15</v>
@@ -5512,10 +5506,10 @@
         <v>32</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J112" s="1">
         <v>5</v>
@@ -5552,10 +5546,10 @@
         <v>160</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J113" s="1">
         <v>5</v>
@@ -5595,10 +5589,10 @@
         <v>160</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J114" s="1">
         <v>5</v>
@@ -5637,10 +5631,10 @@
         <v>10</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J115" s="1">
         <v>5</v>
@@ -5679,10 +5673,10 @@
         <v>10</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J116" s="1">
         <v>5</v>
@@ -5737,10 +5731,10 @@
         <v>50</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J118" s="1">
         <v>5</v>
@@ -5776,10 +5770,10 @@
         <v>1000</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J119" s="1">
         <v>5</v>
@@ -5815,10 +5809,10 @@
         <v>50</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J120" s="1">
         <v>5</v>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -3204,7 +3204,7 @@
         <v>5</v>
       </c>
       <c r="K49" s="1">
-        <v>4022</v>
+        <v>4051</v>
       </c>
       <c r="L49" s="1">
         <v>100</v>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -278,7 +278,7 @@
     <t>法宝自选</t>
   </si>
   <si>
-    <t>300000</t>
+    <t>150000</t>
   </si>
   <si>
     <t>兑换魂骨自选*1</t>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="M37" s="1">
         <f t="shared" si="1"/>
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:13">
@@ -5764,7 +5764,7 @@
         <v>0</v>
       </c>
       <c r="F119" s="1">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G119" s="1">
         <v>1000</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="M119" s="1">
         <f t="shared" si="14"/>
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="O119" s="1">
         <v>5</v>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="161">
   <si>
     <t>#</t>
   </si>
@@ -411,6 +411,12 @@
   </si>
   <si>
     <t>混沌精华*1</t>
+  </si>
+  <si>
+    <t>虚无精华</t>
+  </si>
+  <si>
+    <t>虚无精华*1</t>
   </si>
   <si>
     <t>宠物口粮*100</t>
@@ -1514,7 +1520,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O126"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -3081,10 +3087,10 @@
         <v>4</v>
       </c>
       <c r="F46" s="1">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="G46" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>102</v>
@@ -3422,7 +3428,7 @@
         <v>1</v>
       </c>
       <c r="M57" s="1">
-        <f t="shared" ref="M57:M70" si="3">F57*G57</f>
+        <f t="shared" ref="M57:M71" si="3">F57*G57</f>
         <v>800000</v>
       </c>
       <c r="N57" s="1"/>
@@ -3700,32 +3706,32 @@
         <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F65" s="1">
-        <v>500</v>
+        <v>50000</v>
       </c>
       <c r="G65" s="1">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J65" s="1">
         <v>5</v>
       </c>
       <c r="K65" s="1">
-        <v>4022</v>
+        <v>4046</v>
       </c>
       <c r="L65" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M65" s="1">
         <f t="shared" si="3"/>
-        <v>1000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3736,35 +3742,35 @@
         <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F66" s="1">
-        <v>100000</v>
+        <v>500</v>
       </c>
       <c r="G66" s="1">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>130</v>
       </c>
       <c r="J66" s="1">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K66" s="1">
-        <v>1998001</v>
+        <v>4022</v>
       </c>
       <c r="L66" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M66" s="1">
         <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="1:15">
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C67" s="1">
         <v>70</v>
       </c>
@@ -3790,7 +3796,7 @@
         <v>11</v>
       </c>
       <c r="K67" s="1">
-        <v>1998002</v>
+        <v>1998001</v>
       </c>
       <c r="L67" s="1">
         <v>1</v>
@@ -3800,9 +3806,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="68" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
+    <row r="68" customHeight="1" spans="1:15">
       <c r="C68" s="1">
         <v>71</v>
       </c>
@@ -3828,7 +3832,7 @@
         <v>11</v>
       </c>
       <c r="K68" s="1">
-        <v>1998003</v>
+        <v>1998002</v>
       </c>
       <c r="L68" s="1">
         <v>1</v>
@@ -3837,8 +3841,6 @@
         <f t="shared" si="3"/>
         <v>1000000</v>
       </c>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
     </row>
     <row r="69" customFormat="1" customHeight="1" spans="1:15">
       <c r="A69" s="1"/>
@@ -3868,7 +3870,7 @@
         <v>11</v>
       </c>
       <c r="K69" s="1">
-        <v>1998004</v>
+        <v>1998003</v>
       </c>
       <c r="L69" s="1">
         <v>1</v>
@@ -3908,7 +3910,7 @@
         <v>11</v>
       </c>
       <c r="K70" s="1">
-        <v>1998005</v>
+        <v>1998004</v>
       </c>
       <c r="L70" s="1">
         <v>1</v>
@@ -3920,71 +3922,69 @@
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
     </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A71"/>
-      <c r="B71"/>
-    </row>
-    <row r="72" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
-      <c r="L72" s="1"/>
-      <c r="M72" s="1"/>
-      <c r="N72" s="1"/>
-      <c r="O72" s="1"/>
+    <row r="71" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1">
+        <v>74</v>
+      </c>
+      <c r="D71" s="1">
+        <v>0</v>
+      </c>
+      <c r="E71" s="1">
+        <v>15</v>
+      </c>
+      <c r="F71" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G71" s="1">
+        <v>10</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J71" s="1">
+        <v>11</v>
+      </c>
+      <c r="K71" s="1">
+        <v>1998005</v>
+      </c>
+      <c r="L71" s="1">
+        <v>1</v>
+      </c>
+      <c r="M71" s="1">
+        <f t="shared" si="3"/>
+        <v>1000000</v>
+      </c>
+      <c r="N71" s="1"/>
+      <c r="O71" s="1"/>
+    </row>
+    <row r="72" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A72"/>
+      <c r="B72"/>
     </row>
     <row r="73" customFormat="1" customHeight="1" spans="1:15">
-      <c r="B73" s="1"/>
-      <c r="C73" s="1">
-        <v>102</v>
-      </c>
-      <c r="D73" s="1">
-        <v>1</v>
-      </c>
-      <c r="E73" s="1">
-        <v>0</v>
-      </c>
-      <c r="F73" s="1">
-        <v>100</v>
-      </c>
-      <c r="G73" s="1">
-        <f t="shared" ref="G73:G78" si="4">N73*O77</f>
-        <v>300</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J73" s="1">
-        <v>5</v>
-      </c>
-      <c r="K73" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L73" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M73" s="1">
-        <f t="shared" ref="M73:M80" si="5">F73*G73</f>
-        <v>30000</v>
-      </c>
-      <c r="N73" s="1">
-        <v>1</v>
-      </c>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1"/>
+      <c r="N73" s="1"/>
       <c r="O73" s="1"/>
     </row>
     <row r="74" customFormat="1" customHeight="1" spans="1:15">
       <c r="B74" s="1"/>
       <c r="C74" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D74" s="1">
         <v>1</v>
@@ -3996,8 +3996,8 @@
         <v>100</v>
       </c>
       <c r="G74" s="1">
-        <f t="shared" si="4"/>
-        <v>500</v>
+        <f t="shared" ref="G74:G79" si="4">N74*O78</f>
+        <v>300</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>141</v>
@@ -4009,14 +4009,14 @@
         <v>5</v>
       </c>
       <c r="K74" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="L74" s="1">
         <v>1000</v>
       </c>
       <c r="M74" s="1">
-        <f t="shared" si="5"/>
-        <v>50000</v>
+        <f t="shared" ref="M74:M81" si="5">F74*G74</f>
+        <v>30000</v>
       </c>
       <c r="N74" s="1">
         <v>1</v>
@@ -4026,7 +4026,7 @@
     <row r="75" customFormat="1" customHeight="1" spans="1:15">
       <c r="B75" s="1"/>
       <c r="C75" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D75" s="1">
         <v>1</v>
@@ -4035,11 +4035,11 @@
         <v>0</v>
       </c>
       <c r="F75" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="G75" s="1">
         <f t="shared" si="4"/>
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>143</v>
@@ -4048,17 +4048,17 @@
         <v>144</v>
       </c>
       <c r="J75" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K75" s="1">
-        <v>4014</v>
+        <v>4101</v>
       </c>
       <c r="L75" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="M75" s="1">
         <f t="shared" si="5"/>
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="N75" s="1">
         <v>1</v>
@@ -4068,20 +4068,20 @@
     <row r="76" customFormat="1" customHeight="1" spans="1:15">
       <c r="B76" s="1"/>
       <c r="C76" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D76" s="1">
         <v>1</v>
       </c>
       <c r="E76" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" s="1">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="G76" s="1">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>145</v>
@@ -4090,17 +4090,17 @@
         <v>146</v>
       </c>
       <c r="J76" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K76" s="1">
-        <v>4019</v>
+        <v>4014</v>
       </c>
       <c r="L76" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M76" s="1">
         <f t="shared" si="5"/>
-        <v>120000</v>
+        <v>20000</v>
       </c>
       <c r="N76" s="1">
         <v>1</v>
@@ -4108,23 +4108,22 @@
       <c r="O76" s="1"/>
     </row>
     <row r="77" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D77" s="1">
         <v>1</v>
       </c>
       <c r="E77" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="1">
-        <v>500</v>
+        <v>15000</v>
       </c>
       <c r="G77" s="1">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>147</v>
@@ -4136,27 +4135,25 @@
         <v>5</v>
       </c>
       <c r="K77" s="1">
-        <v>4001</v>
+        <v>4019</v>
       </c>
       <c r="L77" s="1">
-        <v>1000000</v>
+        <v>1</v>
       </c>
       <c r="M77" s="1">
         <f t="shared" si="5"/>
-        <v>20000</v>
+        <v>120000</v>
       </c>
       <c r="N77" s="1">
         <v>1</v>
       </c>
-      <c r="O77" s="1">
-        <v>300</v>
-      </c>
+      <c r="O77" s="1"/>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="1:15">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D78" s="1">
         <v>1</v>
@@ -4181,10 +4178,10 @@
         <v>5</v>
       </c>
       <c r="K78" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L78" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M78" s="1">
         <f t="shared" si="5"/>
@@ -4194,26 +4191,27 @@
         <v>1</v>
       </c>
       <c r="O78" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="1:15">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D79" s="1">
         <v>1</v>
       </c>
       <c r="E79" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F79" s="1">
-        <v>20000</v>
+        <v>500</v>
       </c>
       <c r="G79" s="1">
-        <v>10</v>
+        <f t="shared" si="4"/>
+        <v>40</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>151</v>
@@ -4225,33 +4223,33 @@
         <v>5</v>
       </c>
       <c r="K79" s="1">
-        <v>4026</v>
+        <v>4002</v>
       </c>
       <c r="L79" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M79" s="1">
         <f t="shared" si="5"/>
-        <v>200000</v>
+        <v>20000</v>
       </c>
       <c r="N79" s="1">
         <v>1</v>
       </c>
       <c r="O79" s="1">
-        <v>20</v>
+        <v>500</v>
       </c>
     </row>
     <row r="80" customFormat="1" customHeight="1" spans="1:15">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D80" s="1">
         <v>1</v>
       </c>
       <c r="E80" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F80" s="1">
         <v>20000</v>
@@ -4260,16 +4258,16 @@
         <v>10</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="J80" s="1">
         <v>5</v>
       </c>
       <c r="K80" s="1">
-        <v>4035</v>
+        <v>4026</v>
       </c>
       <c r="L80" s="1">
         <v>1</v>
@@ -4278,76 +4276,77 @@
         <f t="shared" si="5"/>
         <v>200000</v>
       </c>
-      <c r="N80" s="1"/>
+      <c r="N80" s="1">
+        <v>1</v>
+      </c>
       <c r="O80" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" customFormat="1" customHeight="1" spans="1:15">
       <c r="A81" s="1"/>
-      <c r="B81"/>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
-      <c r="K81" s="1"/>
-      <c r="L81" s="1"/>
-      <c r="M81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1">
+        <v>109</v>
+      </c>
+      <c r="D81" s="1">
+        <v>1</v>
+      </c>
+      <c r="E81" s="1">
+        <v>10</v>
+      </c>
+      <c r="F81" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G81" s="1">
+        <v>10</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J81" s="1">
+        <v>5</v>
+      </c>
+      <c r="K81" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L81" s="1">
+        <v>1</v>
+      </c>
+      <c r="M81" s="1">
+        <f t="shared" si="5"/>
+        <v>200000</v>
+      </c>
       <c r="N81" s="1"/>
       <c r="O81" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="82" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C82" s="1">
-        <v>201</v>
-      </c>
-      <c r="D82" s="1">
-        <v>2</v>
-      </c>
-      <c r="E82" s="1">
-        <v>0</v>
-      </c>
-      <c r="F82" s="5">
-        <v>200</v>
-      </c>
-      <c r="G82" s="1">
-        <f t="shared" ref="G82:G87" si="6">N82*O86</f>
-        <v>300</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J82" s="1">
-        <v>5</v>
-      </c>
-      <c r="K82" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L82" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M82" s="1">
-        <f t="shared" ref="M82:M89" si="7">F82*G82</f>
-        <v>60000</v>
-      </c>
-      <c r="N82" s="1">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A82" s="1"/>
+      <c r="B82"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1"/>
+      <c r="N82" s="1"/>
       <c r="O82" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="83" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C83" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D83" s="1">
         <v>2</v>
@@ -4359,162 +4358,162 @@
         <v>200</v>
       </c>
       <c r="G83" s="1">
+        <f t="shared" ref="G83:G88" si="6">N83*O87</f>
+        <v>300</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J83" s="1">
+        <v>5</v>
+      </c>
+      <c r="K83" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L83" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M83" s="1">
+        <f t="shared" ref="M83:M90" si="7">F83*G83</f>
+        <v>60000</v>
+      </c>
+      <c r="N83" s="1">
+        <v>1</v>
+      </c>
+      <c r="O83" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C84" s="1">
+        <v>202</v>
+      </c>
+      <c r="D84" s="1">
+        <v>2</v>
+      </c>
+      <c r="E84" s="1">
+        <v>0</v>
+      </c>
+      <c r="F84" s="5">
+        <v>200</v>
+      </c>
+      <c r="G84" s="1">
         <f t="shared" si="6"/>
         <v>500</v>
       </c>
-      <c r="H83" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J83" s="1">
-        <v>5</v>
-      </c>
-      <c r="K83" s="1">
+      <c r="H84" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J84" s="1">
+        <v>5</v>
+      </c>
+      <c r="K84" s="1">
         <v>4101</v>
       </c>
-      <c r="L83" s="1">
+      <c r="L84" s="1">
         <v>1000</v>
       </c>
-      <c r="M83" s="1">
+      <c r="M84" s="1">
         <f t="shared" si="7"/>
         <v>100000</v>
       </c>
-      <c r="N83" s="1">
-        <v>1</v>
-      </c>
-      <c r="O83" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C84" s="1">
+      <c r="N84" s="1">
+        <v>1</v>
+      </c>
+      <c r="O84" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C85" s="1">
         <v>203</v>
       </c>
-      <c r="D84" s="1">
+      <c r="D85" s="1">
         <v>2</v>
       </c>
-      <c r="E84" s="1">
-        <v>0</v>
-      </c>
-      <c r="F84" s="5">
+      <c r="E85" s="1">
+        <v>0</v>
+      </c>
+      <c r="F85" s="5">
         <v>2000</v>
       </c>
-      <c r="G84" s="1">
+      <c r="G85" s="1">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="H84" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J84" s="1">
+      <c r="H85" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J85" s="1">
         <v>15</v>
       </c>
-      <c r="K84" s="1">
+      <c r="K85" s="1">
         <v>4014</v>
       </c>
-      <c r="L84" s="1">
+      <c r="L85" s="1">
         <v>100</v>
       </c>
-      <c r="M84" s="1">
+      <c r="M85" s="1">
         <f t="shared" si="7"/>
         <v>40000</v>
       </c>
-      <c r="N84" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A85"/>
-      <c r="C85" s="1">
+      <c r="N85" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A86"/>
+      <c r="C86" s="1">
         <v>204</v>
       </c>
-      <c r="D85" s="1">
+      <c r="D86" s="1">
         <v>2</v>
       </c>
-      <c r="E85" s="1">
-        <v>1</v>
-      </c>
-      <c r="F85" s="5">
+      <c r="E86" s="1">
+        <v>1</v>
+      </c>
+      <c r="F86" s="5">
         <v>30000</v>
       </c>
-      <c r="G85" s="1">
+      <c r="G86" s="1">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
-      <c r="H85" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J85" s="1">
-        <v>5</v>
-      </c>
-      <c r="K85" s="1">
+      <c r="H86" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J86" s="1">
+        <v>5</v>
+      </c>
+      <c r="K86" s="1">
         <v>4019</v>
       </c>
-      <c r="L85" s="1">
-        <v>1</v>
-      </c>
-      <c r="M85" s="1">
+      <c r="L86" s="1">
+        <v>1</v>
+      </c>
+      <c r="M86" s="1">
         <f t="shared" si="7"/>
         <v>240000</v>
       </c>
-      <c r="N85" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C86" s="1">
-        <v>205</v>
-      </c>
-      <c r="D86" s="1">
-        <v>2</v>
-      </c>
-      <c r="E86" s="1">
-        <v>0</v>
-      </c>
-      <c r="F86" s="5">
-        <v>1000</v>
-      </c>
-      <c r="G86" s="1">
-        <f t="shared" si="6"/>
-        <v>40</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J86" s="1">
-        <v>5</v>
-      </c>
-      <c r="K86" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L86" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M86" s="1">
-        <f t="shared" si="7"/>
-        <v>40000</v>
-      </c>
       <c r="N86" s="1">
         <v>1</v>
-      </c>
-      <c r="O86" s="1">
-        <v>300</v>
       </c>
     </row>
     <row r="87" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C87" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D87" s="1">
         <v>2</v>
@@ -4539,10 +4538,10 @@
         <v>5</v>
       </c>
       <c r="K87" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L87" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M87" s="1">
         <f t="shared" si="7"/>
@@ -4552,24 +4551,25 @@
         <v>1</v>
       </c>
       <c r="O87" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="88" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C88" s="1">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D88" s="1">
         <v>2</v>
       </c>
       <c r="E88" s="1">
-        <v>6</v>
-      </c>
-      <c r="F88" s="1">
-        <v>20000</v>
+        <v>0</v>
+      </c>
+      <c r="F88" s="5">
+        <v>1000</v>
       </c>
       <c r="G88" s="1">
-        <v>10</v>
+        <f t="shared" si="6"/>
+        <v>40</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>151</v>
@@ -4581,31 +4581,31 @@
         <v>5</v>
       </c>
       <c r="K88" s="1">
-        <v>4026</v>
+        <v>4002</v>
       </c>
       <c r="L88" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M88" s="1">
         <f t="shared" si="7"/>
-        <v>200000</v>
+        <v>40000</v>
       </c>
       <c r="N88" s="1">
         <v>1</v>
       </c>
       <c r="O88" s="1">
-        <v>20</v>
+        <v>500</v>
       </c>
     </row>
     <row r="89" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C89" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D89" s="1">
         <v>2</v>
       </c>
       <c r="E89" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F89" s="1">
         <v>20000</v>
@@ -4614,16 +4614,16 @@
         <v>10</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="J89" s="1">
         <v>5</v>
       </c>
       <c r="K89" s="1">
-        <v>4035</v>
+        <v>4026</v>
       </c>
       <c r="L89" s="1">
         <v>1</v>
@@ -4632,75 +4632,74 @@
         <f t="shared" si="7"/>
         <v>200000</v>
       </c>
+      <c r="N89" s="1">
+        <v>1</v>
+      </c>
       <c r="O89" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C90" s="1">
+        <v>208</v>
+      </c>
+      <c r="D90" s="1">
+        <v>2</v>
+      </c>
+      <c r="E90" s="1">
+        <v>10</v>
+      </c>
+      <c r="F90" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G90" s="1">
+        <v>10</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J90" s="1">
+        <v>5</v>
+      </c>
+      <c r="K90" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L90" s="1">
+        <v>1</v>
+      </c>
+      <c r="M90" s="1">
+        <f t="shared" si="7"/>
+        <v>200000</v>
+      </c>
+      <c r="O90" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="90" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A90" s="1"/>
-      <c r="B90"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
-      <c r="K90" s="1"/>
-      <c r="L90" s="1"/>
-      <c r="M90" s="1"/>
-      <c r="N90" s="1"/>
-      <c r="O90" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="91" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C91" s="1">
-        <v>211</v>
-      </c>
-      <c r="D91" s="1">
-        <v>3</v>
-      </c>
-      <c r="E91" s="1">
-        <v>0</v>
-      </c>
-      <c r="F91" s="1">
-        <v>400</v>
-      </c>
-      <c r="G91" s="1">
-        <f t="shared" ref="G91:G96" si="8">N91*O95</f>
-        <v>300</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J91" s="1">
-        <v>5</v>
-      </c>
-      <c r="K91" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L91" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M91" s="1">
-        <f t="shared" ref="M91:M98" si="9">F91*G91</f>
-        <v>120000</v>
-      </c>
-      <c r="N91" s="1">
-        <v>1</v>
-      </c>
+    <row r="91" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A91" s="1"/>
+      <c r="B91"/>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="1"/>
+      <c r="M91" s="1"/>
+      <c r="N91" s="1"/>
       <c r="O91" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C92" s="1">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D92" s="1">
         <v>3</v>
@@ -4712,162 +4711,162 @@
         <v>400</v>
       </c>
       <c r="G92" s="1">
+        <f t="shared" ref="G92:G97" si="8">N92*O96</f>
+        <v>300</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J92" s="1">
+        <v>5</v>
+      </c>
+      <c r="K92" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L92" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M92" s="1">
+        <f t="shared" ref="M92:M99" si="9">F92*G92</f>
+        <v>120000</v>
+      </c>
+      <c r="N92" s="1">
+        <v>1</v>
+      </c>
+      <c r="O92" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C93" s="1">
+        <v>212</v>
+      </c>
+      <c r="D93" s="1">
+        <v>3</v>
+      </c>
+      <c r="E93" s="1">
+        <v>0</v>
+      </c>
+      <c r="F93" s="1">
+        <v>400</v>
+      </c>
+      <c r="G93" s="1">
         <f t="shared" si="8"/>
         <v>500</v>
       </c>
-      <c r="H92" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J92" s="1">
-        <v>5</v>
-      </c>
-      <c r="K92" s="1">
+      <c r="H93" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J93" s="1">
+        <v>5</v>
+      </c>
+      <c r="K93" s="1">
         <v>4101</v>
       </c>
-      <c r="L92" s="1">
+      <c r="L93" s="1">
         <v>1000</v>
       </c>
-      <c r="M92" s="1">
+      <c r="M93" s="1">
         <f t="shared" si="9"/>
         <v>200000</v>
       </c>
-      <c r="N92" s="1">
-        <v>1</v>
-      </c>
-      <c r="O92" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="93" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C93" s="1">
+      <c r="N93" s="1">
+        <v>1</v>
+      </c>
+      <c r="O93" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C94" s="1">
         <v>213</v>
       </c>
-      <c r="D93" s="1">
+      <c r="D94" s="1">
         <v>3</v>
       </c>
-      <c r="E93" s="1">
-        <v>0</v>
-      </c>
-      <c r="F93" s="1">
+      <c r="E94" s="1">
+        <v>0</v>
+      </c>
+      <c r="F94" s="1">
         <v>4000</v>
       </c>
-      <c r="G93" s="1">
+      <c r="G94" s="1">
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="H93" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J93" s="1">
+      <c r="H94" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J94" s="1">
         <v>15</v>
       </c>
-      <c r="K93" s="1">
+      <c r="K94" s="1">
         <v>4014</v>
       </c>
-      <c r="L93" s="1">
+      <c r="L94" s="1">
         <v>100</v>
       </c>
-      <c r="M93" s="1">
+      <c r="M94" s="1">
         <f t="shared" si="9"/>
         <v>80000</v>
       </c>
-      <c r="N93" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A94"/>
-      <c r="C94" s="1">
+      <c r="N94" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A95"/>
+      <c r="C95" s="1">
         <v>214</v>
       </c>
-      <c r="D94" s="1">
+      <c r="D95" s="1">
         <v>3</v>
       </c>
-      <c r="E94" s="1">
-        <v>1</v>
-      </c>
-      <c r="F94" s="1">
+      <c r="E95" s="1">
+        <v>1</v>
+      </c>
+      <c r="F95" s="1">
         <v>45000</v>
       </c>
-      <c r="G94" s="1">
+      <c r="G95" s="1">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="H94" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J94" s="1">
-        <v>5</v>
-      </c>
-      <c r="K94" s="1">
+      <c r="H95" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J95" s="1">
+        <v>5</v>
+      </c>
+      <c r="K95" s="1">
         <v>4019</v>
       </c>
-      <c r="L94" s="1">
-        <v>1</v>
-      </c>
-      <c r="M94" s="1">
+      <c r="L95" s="1">
+        <v>1</v>
+      </c>
+      <c r="M95" s="1">
         <f t="shared" si="9"/>
         <v>360000</v>
       </c>
-      <c r="N94" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C95" s="1">
-        <v>215</v>
-      </c>
-      <c r="D95" s="1">
-        <v>3</v>
-      </c>
-      <c r="E95" s="1">
-        <v>0</v>
-      </c>
-      <c r="F95" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G95" s="1">
-        <f t="shared" si="8"/>
-        <v>40</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J95" s="1">
-        <v>5</v>
-      </c>
-      <c r="K95" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L95" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M95" s="1">
-        <f t="shared" si="9"/>
-        <v>80000</v>
-      </c>
       <c r="N95" s="1">
         <v>1</v>
-      </c>
-      <c r="O95" s="1">
-        <v>300</v>
       </c>
     </row>
     <row r="96" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C96" s="1">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D96" s="1">
         <v>3</v>
@@ -4892,10 +4891,10 @@
         <v>5</v>
       </c>
       <c r="K96" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L96" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M96" s="1">
         <f t="shared" si="9"/>
@@ -4905,24 +4904,25 @@
         <v>1</v>
       </c>
       <c r="O96" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C97" s="1">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D97" s="1">
         <v>3</v>
       </c>
       <c r="E97" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F97" s="1">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="G97" s="1">
-        <v>10</v>
+        <f t="shared" si="8"/>
+        <v>40</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>151</v>
@@ -4934,126 +4934,125 @@
         <v>5</v>
       </c>
       <c r="K97" s="1">
-        <v>4026</v>
+        <v>4002</v>
       </c>
       <c r="L97" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M97" s="1">
         <f t="shared" si="9"/>
-        <v>300000</v>
+        <v>80000</v>
       </c>
       <c r="N97" s="1">
         <v>1</v>
       </c>
       <c r="O97" s="1">
-        <v>20</v>
+        <v>500</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C98" s="1">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D98" s="1">
         <v>3</v>
       </c>
       <c r="E98" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F98" s="1">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="G98" s="1">
         <v>10</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="J98" s="1">
         <v>5</v>
       </c>
       <c r="K98" s="1">
-        <v>4035</v>
+        <v>4026</v>
       </c>
       <c r="L98" s="1">
         <v>1</v>
       </c>
       <c r="M98" s="1">
         <f t="shared" si="9"/>
+        <v>300000</v>
+      </c>
+      <c r="N98" s="1">
+        <v>1</v>
+      </c>
+      <c r="O98" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C99" s="1">
+        <v>218</v>
+      </c>
+      <c r="D99" s="1">
+        <v>3</v>
+      </c>
+      <c r="E99" s="1">
+        <v>10</v>
+      </c>
+      <c r="F99" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G99" s="1">
+        <v>10</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J99" s="1">
+        <v>5</v>
+      </c>
+      <c r="K99" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L99" s="1">
+        <v>1</v>
+      </c>
+      <c r="M99" s="1">
+        <f t="shared" si="9"/>
         <v>200000</v>
       </c>
-      <c r="O98" s="1">
+      <c r="O99" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="99" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A99" s="1"/>
-      <c r="B99"/>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
-      <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
-      <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="1"/>
-      <c r="K99" s="1"/>
-      <c r="L99" s="1"/>
-      <c r="M99" s="1"/>
-      <c r="N99" s="1"/>
-      <c r="O99" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="100" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C100" s="1">
-        <v>221</v>
-      </c>
-      <c r="D100" s="1">
-        <v>4</v>
-      </c>
-      <c r="E100" s="1">
-        <v>0</v>
-      </c>
-      <c r="F100" s="5">
-        <v>600</v>
-      </c>
-      <c r="G100" s="1">
-        <f t="shared" ref="G100:G105" si="10">N100*O104</f>
-        <v>300</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J100" s="1">
-        <v>5</v>
-      </c>
-      <c r="K100" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L100" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M100" s="1">
-        <f t="shared" ref="M100:M107" si="11">F100*G100</f>
-        <v>180000</v>
-      </c>
-      <c r="N100" s="1">
-        <v>1</v>
-      </c>
+    <row r="100" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A100" s="1"/>
+      <c r="B100"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
+      <c r="K100" s="1"/>
+      <c r="L100" s="1"/>
+      <c r="M100" s="1"/>
+      <c r="N100" s="1"/>
       <c r="O100" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C101" s="1">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D101" s="1">
         <v>4</v>
@@ -5065,162 +5064,162 @@
         <v>600</v>
       </c>
       <c r="G101" s="1">
+        <f t="shared" ref="G101:G106" si="10">N101*O105</f>
+        <v>300</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J101" s="1">
+        <v>5</v>
+      </c>
+      <c r="K101" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L101" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M101" s="1">
+        <f t="shared" ref="M101:M108" si="11">F101*G101</f>
+        <v>180000</v>
+      </c>
+      <c r="N101" s="1">
+        <v>1</v>
+      </c>
+      <c r="O101" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="102" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C102" s="1">
+        <v>222</v>
+      </c>
+      <c r="D102" s="1">
+        <v>4</v>
+      </c>
+      <c r="E102" s="1">
+        <v>0</v>
+      </c>
+      <c r="F102" s="5">
+        <v>600</v>
+      </c>
+      <c r="G102" s="1">
         <f t="shared" si="10"/>
         <v>500</v>
       </c>
-      <c r="H101" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J101" s="1">
-        <v>5</v>
-      </c>
-      <c r="K101" s="1">
+      <c r="H102" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J102" s="1">
+        <v>5</v>
+      </c>
+      <c r="K102" s="1">
         <v>4101</v>
       </c>
-      <c r="L101" s="1">
+      <c r="L102" s="1">
         <v>1000</v>
       </c>
-      <c r="M101" s="1">
+      <c r="M102" s="1">
         <f t="shared" si="11"/>
         <v>300000</v>
       </c>
-      <c r="N101" s="1">
-        <v>1</v>
-      </c>
-      <c r="O101" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C102" s="1">
+      <c r="N102" s="1">
+        <v>1</v>
+      </c>
+      <c r="O102" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C103" s="1">
         <v>223</v>
       </c>
-      <c r="D102" s="1">
+      <c r="D103" s="1">
         <v>4</v>
       </c>
-      <c r="E102" s="1">
-        <v>0</v>
-      </c>
-      <c r="F102" s="5">
+      <c r="E103" s="1">
+        <v>0</v>
+      </c>
+      <c r="F103" s="5">
         <v>6000</v>
       </c>
-      <c r="G102" s="1">
+      <c r="G103" s="1">
         <f t="shared" si="10"/>
         <v>20</v>
       </c>
-      <c r="H102" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J102" s="1">
+      <c r="H103" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J103" s="1">
         <v>15</v>
       </c>
-      <c r="K102" s="1">
+      <c r="K103" s="1">
         <v>4014</v>
       </c>
-      <c r="L102" s="1">
+      <c r="L103" s="1">
         <v>100</v>
       </c>
-      <c r="M102" s="1">
+      <c r="M103" s="1">
         <f t="shared" si="11"/>
         <v>120000</v>
       </c>
-      <c r="N102" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A103"/>
-      <c r="C103" s="1">
+      <c r="N103" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A104"/>
+      <c r="C104" s="1">
         <v>224</v>
       </c>
-      <c r="D103" s="1">
+      <c r="D104" s="1">
         <v>4</v>
       </c>
-      <c r="E103" s="1">
-        <v>1</v>
-      </c>
-      <c r="F103" s="5">
+      <c r="E104" s="1">
+        <v>1</v>
+      </c>
+      <c r="F104" s="5">
         <v>60000</v>
       </c>
-      <c r="G103" s="1">
+      <c r="G104" s="1">
         <f t="shared" si="10"/>
         <v>8</v>
       </c>
-      <c r="H103" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I103" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J103" s="1">
-        <v>5</v>
-      </c>
-      <c r="K103" s="1">
+      <c r="H104" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J104" s="1">
+        <v>5</v>
+      </c>
+      <c r="K104" s="1">
         <v>4019</v>
       </c>
-      <c r="L103" s="1">
-        <v>1</v>
-      </c>
-      <c r="M103" s="1">
+      <c r="L104" s="1">
+        <v>1</v>
+      </c>
+      <c r="M104" s="1">
         <f t="shared" si="11"/>
         <v>480000</v>
       </c>
-      <c r="N103" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C104" s="1">
-        <v>225</v>
-      </c>
-      <c r="D104" s="1">
-        <v>4</v>
-      </c>
-      <c r="E104" s="1">
-        <v>0</v>
-      </c>
-      <c r="F104" s="5">
-        <v>3000</v>
-      </c>
-      <c r="G104" s="1">
-        <f t="shared" si="10"/>
-        <v>40</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J104" s="1">
-        <v>5</v>
-      </c>
-      <c r="K104" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L104" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M104" s="1">
-        <f t="shared" si="11"/>
-        <v>120000</v>
-      </c>
       <c r="N104" s="1">
         <v>1</v>
-      </c>
-      <c r="O104" s="1">
-        <v>300</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C105" s="1">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D105" s="1">
         <v>4</v>
@@ -5245,10 +5244,10 @@
         <v>5</v>
       </c>
       <c r="K105" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L105" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M105" s="1">
         <f t="shared" si="11"/>
@@ -5258,24 +5257,25 @@
         <v>1</v>
       </c>
       <c r="O105" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C106" s="1">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D106" s="1">
         <v>4</v>
       </c>
       <c r="E106" s="1">
-        <v>6</v>
-      </c>
-      <c r="F106" s="1">
-        <v>20000</v>
+        <v>0</v>
+      </c>
+      <c r="F106" s="5">
+        <v>3000</v>
       </c>
       <c r="G106" s="1">
-        <v>10</v>
+        <f t="shared" si="10"/>
+        <v>40</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>151</v>
@@ -5287,31 +5287,31 @@
         <v>5</v>
       </c>
       <c r="K106" s="1">
-        <v>4026</v>
+        <v>4002</v>
       </c>
       <c r="L106" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M106" s="1">
         <f t="shared" si="11"/>
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="N106" s="1">
         <v>1</v>
       </c>
       <c r="O106" s="1">
-        <v>20</v>
+        <v>500</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C107" s="1">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D107" s="1">
         <v>4</v>
       </c>
       <c r="E107" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F107" s="1">
         <v>20000</v>
@@ -5320,16 +5320,16 @@
         <v>10</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="J107" s="1">
         <v>5</v>
       </c>
       <c r="K107" s="1">
-        <v>4035</v>
+        <v>4026</v>
       </c>
       <c r="L107" s="1">
         <v>1</v>
@@ -5338,75 +5338,74 @@
         <f t="shared" si="11"/>
         <v>200000</v>
       </c>
+      <c r="N107" s="1">
+        <v>1</v>
+      </c>
       <c r="O107" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C108" s="1">
+        <v>228</v>
+      </c>
+      <c r="D108" s="1">
+        <v>4</v>
+      </c>
+      <c r="E108" s="1">
+        <v>10</v>
+      </c>
+      <c r="F108" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G108" s="1">
+        <v>10</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J108" s="1">
+        <v>5</v>
+      </c>
+      <c r="K108" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L108" s="1">
+        <v>1</v>
+      </c>
+      <c r="M108" s="1">
+        <f t="shared" si="11"/>
+        <v>200000</v>
+      </c>
+      <c r="O108" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="108" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A108" s="1"/>
-      <c r="B108"/>
-      <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
-      <c r="E108" s="1"/>
-      <c r="F108" s="1"/>
-      <c r="G108" s="1"/>
-      <c r="H108" s="1"/>
-      <c r="I108" s="1"/>
-      <c r="J108" s="1"/>
-      <c r="K108" s="1"/>
-      <c r="L108" s="1"/>
-      <c r="M108" s="1"/>
-      <c r="N108" s="1"/>
-      <c r="O108" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="109" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C109" s="1">
-        <v>231</v>
-      </c>
-      <c r="D109" s="1">
-        <v>5</v>
-      </c>
-      <c r="E109" s="1">
-        <v>0</v>
-      </c>
-      <c r="F109" s="1">
-        <v>800</v>
-      </c>
-      <c r="G109" s="1">
-        <f t="shared" ref="G109:G114" si="12">N109*O113</f>
-        <v>1200</v>
-      </c>
-      <c r="H109" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J109" s="1">
-        <v>5</v>
-      </c>
-      <c r="K109" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L109" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M109" s="1">
-        <f t="shared" ref="M109:M116" si="13">F109*G109</f>
-        <v>960000</v>
-      </c>
-      <c r="N109" s="1">
-        <v>4</v>
-      </c>
+    <row r="109" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A109" s="1"/>
+      <c r="B109"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1"/>
+      <c r="K109" s="1"/>
+      <c r="L109" s="1"/>
+      <c r="M109" s="1"/>
+      <c r="N109" s="1"/>
       <c r="O109" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C110" s="1">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D110" s="1">
         <v>5</v>
@@ -5418,162 +5417,162 @@
         <v>800</v>
       </c>
       <c r="G110" s="1">
+        <f t="shared" ref="G110:G115" si="12">N110*O114</f>
+        <v>1200</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J110" s="1">
+        <v>5</v>
+      </c>
+      <c r="K110" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L110" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M110" s="1">
+        <f t="shared" ref="M110:M117" si="13">F110*G110</f>
+        <v>960000</v>
+      </c>
+      <c r="N110" s="1">
+        <v>4</v>
+      </c>
+      <c r="O110" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="111" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C111" s="1">
+        <v>232</v>
+      </c>
+      <c r="D111" s="1">
+        <v>5</v>
+      </c>
+      <c r="E111" s="1">
+        <v>0</v>
+      </c>
+      <c r="F111" s="1">
+        <v>800</v>
+      </c>
+      <c r="G111" s="1">
         <f t="shared" si="12"/>
         <v>2000</v>
       </c>
-      <c r="H110" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J110" s="1">
-        <v>5</v>
-      </c>
-      <c r="K110" s="1">
+      <c r="H111" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J111" s="1">
+        <v>5</v>
+      </c>
+      <c r="K111" s="1">
         <v>4101</v>
       </c>
-      <c r="L110" s="1">
+      <c r="L111" s="1">
         <v>1000</v>
       </c>
-      <c r="M110" s="1">
+      <c r="M111" s="1">
         <f t="shared" si="13"/>
         <v>1600000</v>
       </c>
-      <c r="N110" s="1">
+      <c r="N111" s="1">
         <v>4</v>
       </c>
-      <c r="O110" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="111" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C111" s="1">
+      <c r="O111" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C112" s="1">
         <v>233</v>
       </c>
-      <c r="D111" s="1">
-        <v>5</v>
-      </c>
-      <c r="E111" s="1">
-        <v>0</v>
-      </c>
-      <c r="F111" s="1">
+      <c r="D112" s="1">
+        <v>5</v>
+      </c>
+      <c r="E112" s="1">
+        <v>0</v>
+      </c>
+      <c r="F112" s="1">
         <v>8000</v>
       </c>
-      <c r="G111" s="1">
+      <c r="G112" s="1">
         <f t="shared" si="12"/>
         <v>40</v>
       </c>
-      <c r="H111" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J111" s="1">
+      <c r="H112" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J112" s="1">
         <v>15</v>
       </c>
-      <c r="K111" s="1">
+      <c r="K112" s="1">
         <v>4014</v>
       </c>
-      <c r="L111" s="1">
+      <c r="L112" s="1">
         <v>100</v>
       </c>
-      <c r="M111" s="1">
+      <c r="M112" s="1">
         <f t="shared" si="13"/>
         <v>320000</v>
       </c>
-      <c r="N111" s="1">
+      <c r="N112" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="112" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A112"/>
-      <c r="C112" s="1">
+    <row r="113" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A113"/>
+      <c r="C113" s="1">
         <v>234</v>
       </c>
-      <c r="D112" s="1">
-        <v>5</v>
-      </c>
-      <c r="E112" s="1">
-        <v>1</v>
-      </c>
-      <c r="F112" s="1">
+      <c r="D113" s="1">
+        <v>5</v>
+      </c>
+      <c r="E113" s="1">
+        <v>1</v>
+      </c>
+      <c r="F113" s="1">
         <v>75000</v>
       </c>
-      <c r="G112" s="1">
+      <c r="G113" s="1">
         <f t="shared" si="12"/>
         <v>32</v>
       </c>
-      <c r="H112" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I112" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J112" s="1">
-        <v>5</v>
-      </c>
-      <c r="K112" s="1">
+      <c r="H113" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J113" s="1">
+        <v>5</v>
+      </c>
+      <c r="K113" s="1">
         <v>4019</v>
       </c>
-      <c r="L112" s="1">
-        <v>1</v>
-      </c>
-      <c r="M112" s="1">
+      <c r="L113" s="1">
+        <v>1</v>
+      </c>
+      <c r="M113" s="1">
         <f t="shared" si="13"/>
         <v>2400000</v>
       </c>
-      <c r="N112" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="113" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C113" s="1">
-        <v>235</v>
-      </c>
-      <c r="D113" s="1">
-        <v>5</v>
-      </c>
-      <c r="E113" s="1">
-        <v>0</v>
-      </c>
-      <c r="F113" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G113" s="1">
-        <f t="shared" si="12"/>
-        <v>160</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J113" s="1">
-        <v>5</v>
-      </c>
-      <c r="K113" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L113" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M113" s="1">
-        <f t="shared" si="13"/>
-        <v>640000</v>
-      </c>
       <c r="N113" s="1">
         <v>4</v>
       </c>
-      <c r="O113" s="1">
-        <v>300</v>
-      </c>
     </row>
     <row r="114" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C114" s="1">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D114" s="1">
         <v>5</v>
@@ -5598,10 +5597,10 @@
         <v>5</v>
       </c>
       <c r="K114" s="1">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="L114" s="1">
-        <v>6000000</v>
+        <v>1000000</v>
       </c>
       <c r="M114" s="1">
         <f t="shared" si="13"/>
@@ -5611,24 +5610,25 @@
         <v>4</v>
       </c>
       <c r="O114" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C115" s="1">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D115" s="1">
         <v>5</v>
       </c>
       <c r="E115" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F115" s="1">
-        <v>20000</v>
+        <v>4000</v>
       </c>
       <c r="G115" s="1">
-        <v>10</v>
+        <f t="shared" si="12"/>
+        <v>160</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>151</v>
@@ -5640,31 +5640,31 @@
         <v>5</v>
       </c>
       <c r="K115" s="1">
-        <v>4026</v>
+        <v>4002</v>
       </c>
       <c r="L115" s="1">
-        <v>1</v>
+        <v>6000000</v>
       </c>
       <c r="M115" s="1">
         <f t="shared" si="13"/>
-        <v>200000</v>
+        <v>640000</v>
       </c>
       <c r="N115" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O115" s="1">
-        <v>10</v>
+        <v>500</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C116" s="1">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D116" s="1">
         <v>5</v>
       </c>
       <c r="E116" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F116" s="1">
         <v>20000</v>
@@ -5673,16 +5673,16 @@
         <v>10</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="J116" s="1">
         <v>5</v>
       </c>
       <c r="K116" s="1">
-        <v>4035</v>
+        <v>4026</v>
       </c>
       <c r="L116" s="1">
         <v>1</v>
@@ -5691,71 +5691,74 @@
         <f t="shared" si="13"/>
         <v>200000</v>
       </c>
+      <c r="N116" s="1">
+        <v>1</v>
+      </c>
       <c r="O116" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C117" s="1">
+        <v>238</v>
+      </c>
+      <c r="D117" s="1">
+        <v>5</v>
+      </c>
+      <c r="E117" s="1">
+        <v>10</v>
+      </c>
+      <c r="F117" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G117" s="1">
+        <v>10</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J117" s="1">
+        <v>5</v>
+      </c>
+      <c r="K117" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L117" s="1">
+        <v>1</v>
+      </c>
+      <c r="M117" s="1">
+        <f t="shared" si="13"/>
+        <v>200000</v>
+      </c>
+      <c r="O117" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="117" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A117" s="1"/>
-      <c r="B117"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-      <c r="E117" s="1"/>
-      <c r="F117" s="1"/>
-      <c r="G117" s="1"/>
-      <c r="H117" s="1"/>
-      <c r="I117" s="1"/>
-      <c r="J117" s="1"/>
-      <c r="K117" s="1"/>
-      <c r="L117" s="1"/>
-      <c r="M117" s="1"/>
-      <c r="N117"/>
-      <c r="O117" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="118" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C118" s="1">
-        <v>999</v>
-      </c>
-      <c r="D118" s="1">
-        <v>0</v>
-      </c>
-      <c r="E118" s="1">
-        <v>0</v>
-      </c>
-      <c r="F118" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G118" s="1">
-        <v>50</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="I118" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J118" s="1">
-        <v>5</v>
-      </c>
-      <c r="K118" s="1">
-        <v>4006</v>
-      </c>
-      <c r="L118" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M118" s="1">
-        <f t="shared" ref="M118:M120" si="14">F118*G118</f>
-        <v>50000</v>
-      </c>
+    <row r="118" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A118" s="1"/>
+      <c r="B118"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
+      <c r="E118" s="1"/>
+      <c r="F118" s="1"/>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1"/>
+      <c r="K118" s="1"/>
+      <c r="L118" s="1"/>
+      <c r="M118" s="1"/>
+      <c r="N118"/>
       <c r="O118" s="1">
         <v>40</v>
       </c>
     </row>
     <row r="119" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C119" s="1">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D119" s="1">
         <v>0</v>
@@ -5767,7 +5770,7 @@
         <v>1000</v>
       </c>
       <c r="G119" s="1">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>155</v>
@@ -5779,88 +5782,127 @@
         <v>5</v>
       </c>
       <c r="K119" s="1">
+        <v>4006</v>
+      </c>
+      <c r="L119" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M119" s="1">
+        <f t="shared" ref="M119:M121" si="14">F119*G119</f>
+        <v>50000</v>
+      </c>
+      <c r="O119" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="120" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C120" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D120" s="1">
+        <v>0</v>
+      </c>
+      <c r="E120" s="1">
+        <v>0</v>
+      </c>
+      <c r="F120" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G120" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J120" s="1">
+        <v>5</v>
+      </c>
+      <c r="K120" s="1">
         <v>4010</v>
       </c>
-      <c r="L119" s="1">
-        <v>5</v>
-      </c>
-      <c r="M119" s="1">
+      <c r="L120" s="1">
+        <v>5</v>
+      </c>
+      <c r="M120" s="1">
         <f t="shared" si="14"/>
         <v>1000000</v>
       </c>
-      <c r="O119" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="120" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C120" s="1">
+      <c r="O120" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C121" s="1">
         <v>1001</v>
       </c>
-      <c r="D120" s="1">
-        <v>0</v>
-      </c>
-      <c r="E120" s="1">
-        <v>0</v>
-      </c>
-      <c r="F120" s="1">
+      <c r="D121" s="1">
+        <v>0</v>
+      </c>
+      <c r="E121" s="1">
+        <v>0</v>
+      </c>
+      <c r="F121" s="1">
         <v>2000</v>
       </c>
-      <c r="G120" s="1">
+      <c r="G121" s="1">
         <v>50</v>
       </c>
-      <c r="H120" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="I120" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J120" s="1">
-        <v>5</v>
-      </c>
-      <c r="K120" s="1">
+      <c r="H121" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J121" s="1">
+        <v>5</v>
+      </c>
+      <c r="K121" s="1">
         <v>4102</v>
       </c>
-      <c r="L120" s="1">
+      <c r="L121" s="1">
         <v>20</v>
       </c>
-      <c r="M120" s="1">
+      <c r="M121" s="1">
         <f t="shared" si="14"/>
         <v>100000</v>
       </c>
     </row>
-    <row r="121" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A121"/>
-      <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
-      <c r="D121" s="1"/>
-      <c r="E121" s="1"/>
-      <c r="F121" s="1"/>
-      <c r="G121" s="1"/>
-      <c r="H121" s="1"/>
-      <c r="I121" s="1"/>
-      <c r="J121" s="1"/>
-      <c r="K121" s="1"/>
-      <c r="L121" s="1"/>
-      <c r="M121" s="1"/>
-      <c r="N121" s="1"/>
-      <c r="O121"/>
-    </row>
-    <row r="126" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A126" s="1"/>
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
-      <c r="F126" s="1"/>
-      <c r="G126" s="1"/>
-      <c r="H126" s="1"/>
-      <c r="I126" s="1"/>
-      <c r="J126" s="1"/>
-      <c r="K126" s="1"/>
-      <c r="L126" s="1"/>
-      <c r="M126" s="1"/>
-      <c r="N126" s="1"/>
-      <c r="O126" s="1"/>
+    <row r="122" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A122"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1"/>
+      <c r="K122" s="1"/>
+      <c r="L122" s="1"/>
+      <c r="M122" s="1"/>
+      <c r="N122" s="1"/>
+      <c r="O122"/>
+    </row>
+    <row r="127" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A127" s="1"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="D127" s="1"/>
+      <c r="E127" s="1"/>
+      <c r="F127" s="1"/>
+      <c r="G127" s="1"/>
+      <c r="H127" s="1"/>
+      <c r="I127" s="1"/>
+      <c r="J127" s="1"/>
+      <c r="K127" s="1"/>
+      <c r="L127" s="1"/>
+      <c r="M127" s="1"/>
+      <c r="N127" s="1"/>
+      <c r="O127" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -4481,8 +4481,8 @@
       <c r="E86" s="1">
         <v>1</v>
       </c>
-      <c r="F86" s="5">
-        <v>30000</v>
+      <c r="F86" s="1">
+        <v>15000</v>
       </c>
       <c r="G86" s="1">
         <f t="shared" si="6"/>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="M86" s="1">
         <f t="shared" si="7"/>
-        <v>240000</v>
+        <v>120000</v>
       </c>
       <c r="N86" s="1">
         <v>1</v>
@@ -5187,8 +5187,8 @@
       <c r="E104" s="1">
         <v>1</v>
       </c>
-      <c r="F104" s="5">
-        <v>60000</v>
+      <c r="F104" s="1">
+        <v>15000</v>
       </c>
       <c r="G104" s="1">
         <f t="shared" si="10"/>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="M104" s="1">
         <f t="shared" si="11"/>
-        <v>480000</v>
+        <v>120000</v>
       </c>
       <c r="N104" s="1">
         <v>1</v>
@@ -5541,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="1">
-        <v>75000</v>
+        <v>15000</v>
       </c>
       <c r="G113" s="1">
         <f t="shared" si="12"/>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="M113" s="1">
         <f t="shared" si="13"/>
-        <v>2400000</v>
+        <v>480000</v>
       </c>
       <c r="N113" s="1">
         <v>4</v>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="165">
   <si>
     <t>#</t>
   </si>
@@ -305,106 +310,133 @@
     <t>改造石</t>
   </si>
   <si>
+    <t>兑换遗物粉尘*10</t>
+  </si>
+  <si>
+    <t>遗物粉尘</t>
+  </si>
+  <si>
+    <t>兑换天赋秘籍*1</t>
+  </si>
+  <si>
+    <t>天赋秘籍</t>
+  </si>
+  <si>
+    <t>兑换开孔石</t>
+  </si>
+  <si>
+    <t>开孔石</t>
+  </si>
+  <si>
+    <t>宝石集合包</t>
+  </si>
+  <si>
+    <t>兑换低级法宝自选*1</t>
+  </si>
+  <si>
+    <t>低级法宝自选</t>
+  </si>
+  <si>
+    <t>极宝石集合包</t>
+  </si>
+  <si>
+    <t>兑换时装精华</t>
+  </si>
+  <si>
+    <t>时装精华</t>
+  </si>
+  <si>
+    <t>超级书页</t>
+  </si>
+  <si>
+    <t>行气丹*500</t>
+  </si>
+  <si>
+    <t>行气丹</t>
+  </si>
+  <si>
+    <t>炼神丹*500</t>
+  </si>
+  <si>
+    <t>炼魂丹*500</t>
+  </si>
+  <si>
+    <t>11技能自选</t>
+  </si>
+  <si>
+    <t>兑换红宠自选</t>
+  </si>
+  <si>
+    <t>红宠自选</t>
+  </si>
+  <si>
+    <t>金色材料魂宠</t>
+  </si>
+  <si>
+    <t>金色40宠物</t>
+  </si>
+  <si>
+    <t>金色魂心</t>
+  </si>
+  <si>
+    <t>暗金魂心</t>
+  </si>
+  <si>
+    <t>金色50坐骑</t>
+  </si>
+  <si>
+    <t>金色50坐骑自选</t>
+  </si>
+  <si>
+    <t>金色兽魂</t>
+  </si>
+  <si>
     <t>兑换宠物口粮*100</t>
   </si>
   <si>
-    <t>宠物口粮</t>
+    <t>宠物口粮*100</t>
+  </si>
+  <si>
+    <t>兑换坐骑兽粮*100</t>
+  </si>
+  <si>
+    <t>坐骑兽粮*100</t>
+  </si>
+  <si>
+    <t>粉色50坐骑</t>
+  </si>
+  <si>
+    <t>暗金50坐骑</t>
+  </si>
+  <si>
+    <t>兑换传奇精华</t>
+  </si>
+  <si>
+    <t>传奇精华</t>
+  </si>
+  <si>
+    <t>不朽精华</t>
+  </si>
+  <si>
+    <t>不朽精华*1</t>
   </si>
   <si>
     <t>兑换红装精华*1</t>
   </si>
   <si>
-    <t>红装精华</t>
-  </si>
-  <si>
-    <t>兑换遗物粉尘*10</t>
-  </si>
-  <si>
-    <t>遗物粉尘</t>
-  </si>
-  <si>
-    <t>兑换天赋秘籍*1</t>
-  </si>
-  <si>
-    <t>天赋秘籍</t>
-  </si>
-  <si>
-    <t>兑换红宠自选</t>
-  </si>
-  <si>
-    <t>红宠自选</t>
-  </si>
-  <si>
-    <t>兑换开孔石</t>
-  </si>
-  <si>
-    <t>开孔石</t>
-  </si>
-  <si>
-    <t>宝石集合包</t>
-  </si>
-  <si>
-    <t>攻击宝石</t>
-  </si>
-  <si>
-    <t>兑换低级法宝自选*1</t>
-  </si>
-  <si>
-    <t>低级法宝自选</t>
-  </si>
-  <si>
-    <t>兑换坐骑兽粮*100</t>
-  </si>
-  <si>
-    <t>坐骑兽粮*100</t>
-  </si>
-  <si>
-    <t>兑换时装精华</t>
-  </si>
-  <si>
-    <t>时装精华</t>
-  </si>
-  <si>
-    <t>超级书页</t>
-  </si>
-  <si>
-    <t>行气丹*500</t>
-  </si>
-  <si>
-    <t>行气丹</t>
-  </si>
-  <si>
-    <t>11技能自选</t>
-  </si>
-  <si>
-    <t>金色魂心</t>
-  </si>
-  <si>
-    <t>暗金魂心</t>
-  </si>
-  <si>
-    <t>金色材料魂宠</t>
-  </si>
-  <si>
-    <t>炼神丹</t>
-  </si>
-  <si>
-    <t>炼神丹*500</t>
-  </si>
-  <si>
-    <t>金色坐骑自选</t>
-  </si>
-  <si>
-    <t>兑换传奇精华</t>
-  </si>
-  <si>
-    <t>传奇精华</t>
-  </si>
-  <si>
-    <t>不朽精华</t>
-  </si>
-  <si>
-    <t>不朽精华*1</t>
+    <t>红装精华*1</t>
+  </si>
+  <si>
+    <t>兑换金装精华*1</t>
+  </si>
+  <si>
+    <t>金装精华*1</t>
+  </si>
+  <si>
+    <t>兑换暗金精华*1</t>
+  </si>
+  <si>
+    <t>暗金精华*1</t>
   </si>
   <si>
     <t>混沌精华</t>
@@ -419,9 +451,6 @@
     <t>虚无精华*1</t>
   </si>
   <si>
-    <t>宠物口粮*100</t>
-  </si>
-  <si>
     <t>仙鉴青龙</t>
   </si>
   <si>
@@ -470,12 +499,6 @@
     <t>经验丹</t>
   </si>
   <si>
-    <t>兑换金装精华*1</t>
-  </si>
-  <si>
-    <t>金装精华</t>
-  </si>
-  <si>
     <t>兑换魂环碎片*100w</t>
   </si>
   <si>
@@ -486,12 +509,6 @@
   </si>
   <si>
     <t>精炼石</t>
-  </si>
-  <si>
-    <t>兑换暗金精华*1</t>
-  </si>
-  <si>
-    <t>暗金精华</t>
   </si>
   <si>
     <t>兑换书页1000个</t>
@@ -1520,7 +1537,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O122"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1650,7 +1667,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="1">
-        <v>268</v>
+        <v>888</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>14</v>
@@ -1669,7 +1686,7 @@
       </c>
       <c r="M6" s="1">
         <f t="shared" ref="M6:M14" si="0">F6*G6</f>
-        <v>80400</v>
+        <v>266400</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:13">
@@ -1686,7 +1703,7 @@
         <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>268</v>
+        <v>888</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>16</v>
@@ -1705,7 +1722,7 @@
       </c>
       <c r="M7" s="1">
         <f t="shared" si="0"/>
-        <v>80400</v>
+        <v>266400</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1722,7 +1739,7 @@
         <v>13</v>
       </c>
       <c r="G8" s="1">
-        <v>268</v>
+        <v>888</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>18</v>
@@ -1741,7 +1758,7 @@
       </c>
       <c r="M8" s="1">
         <f t="shared" si="0"/>
-        <v>80400</v>
+        <v>266400</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:13">
@@ -2608,7 +2625,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="3:13">
+    <row r="33" customHeight="1" spans="2:15">
       <c r="C33" s="1">
         <v>28</v>
       </c>
@@ -2644,7 +2661,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="3:13">
+    <row r="34" customHeight="1" spans="2:15">
       <c r="C34" s="1">
         <v>29</v>
       </c>
@@ -2680,7 +2697,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="3:13">
+    <row r="35" customHeight="1" spans="2:15">
       <c r="C35" s="1">
         <v>30</v>
       </c>
@@ -2716,7 +2733,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="3:13">
+    <row r="36" customHeight="1" spans="2:15">
       <c r="C36" s="1">
         <v>31</v>
       </c>
@@ -2752,7 +2769,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="3:13">
+    <row r="37" customHeight="1" spans="2:15">
       <c r="C37" s="1">
         <v>32</v>
       </c>
@@ -2766,7 +2783,7 @@
         <v>83</v>
       </c>
       <c r="G37" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>84</v>
@@ -2785,10 +2802,10 @@
       </c>
       <c r="M37" s="1">
         <f t="shared" si="1"/>
-        <v>1500000</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:13">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="2:15">
       <c r="C38" s="1">
         <v>33</v>
       </c>
@@ -2802,7 +2819,7 @@
         <v>150000</v>
       </c>
       <c r="G38" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>86</v>
@@ -2820,11 +2837,11 @@
         <v>1</v>
       </c>
       <c r="M38" s="1">
-        <f t="shared" ref="M38:M49" si="2">F38*G38</f>
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:13">
+        <f>F38*G38</f>
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="2:15">
       <c r="C39" s="1">
         <v>34</v>
       </c>
@@ -2838,7 +2855,7 @@
         <v>300000</v>
       </c>
       <c r="G39" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>88</v>
@@ -2856,11 +2873,11 @@
         <v>1</v>
       </c>
       <c r="M39" s="1">
-        <f t="shared" si="2"/>
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:13">
+        <f>F39*G39</f>
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="2:15">
       <c r="C40" s="1">
         <v>35</v>
       </c>
@@ -2874,7 +2891,7 @@
         <v>1000</v>
       </c>
       <c r="G40" s="1">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>90</v>
@@ -2892,11 +2909,11 @@
         <v>1</v>
       </c>
       <c r="M40" s="1">
-        <f t="shared" si="2"/>
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:13">
+        <f>F40*G40</f>
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="2:15">
       <c r="C41" s="1">
         <v>36</v>
       </c>
@@ -2907,10 +2924,10 @@
         <v>0</v>
       </c>
       <c r="F41" s="1">
-        <v>500</v>
+        <v>20000</v>
       </c>
       <c r="G41" s="1">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>92</v>
@@ -2922,17 +2939,17 @@
         <v>5</v>
       </c>
       <c r="K41" s="1">
-        <v>4022</v>
+        <v>4018</v>
       </c>
       <c r="L41" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="M41" s="1">
-        <f t="shared" si="2"/>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:13">
+        <f>F41*G41</f>
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="2:15">
       <c r="C42" s="1">
         <v>37</v>
       </c>
@@ -2943,10 +2960,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="1">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="G42" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>94</v>
@@ -2955,34 +2972,34 @@
         <v>95</v>
       </c>
       <c r="J42" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K42" s="1">
-        <v>4011</v>
+        <v>4020</v>
       </c>
       <c r="L42" s="1">
         <v>1</v>
       </c>
       <c r="M42" s="1">
-        <f t="shared" si="2"/>
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:13">
+        <f>F42*G42</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="2:15">
       <c r="C43" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F43" s="1">
-        <v>20000</v>
+        <v>200000</v>
       </c>
       <c r="G43" s="1">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>96</v>
@@ -2994,91 +3011,91 @@
         <v>5</v>
       </c>
       <c r="K43" s="1">
-        <v>4018</v>
+        <v>4027</v>
       </c>
       <c r="L43" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M43" s="1">
-        <f t="shared" si="2"/>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:13">
+        <f>F43*G43</f>
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="2:15">
       <c r="C44" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="G44" s="1">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>98</v>
       </c>
       <c r="I44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J44" s="1">
+        <v>4</v>
+      </c>
+      <c r="K44" s="4">
+        <v>36</v>
+      </c>
+      <c r="L44" s="1">
+        <v>1</v>
+      </c>
+      <c r="M44" s="1">
+        <f>F44*G44</f>
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="2:15">
+      <c r="C45" s="1">
+        <v>41</v>
+      </c>
+      <c r="D45" s="1">
+        <v>0</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0</v>
+      </c>
+      <c r="F45" s="1">
+        <v>50000</v>
+      </c>
+      <c r="G45" s="1">
+        <v>100</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="J44" s="1">
-        <v>15</v>
-      </c>
-      <c r="K44" s="1">
-        <v>4020</v>
-      </c>
-      <c r="L44" s="1">
-        <v>1</v>
-      </c>
-      <c r="M44" s="1">
-        <f t="shared" si="2"/>
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C45" s="1">
-        <v>40</v>
-      </c>
-      <c r="D45" s="1">
-        <v>0</v>
-      </c>
-      <c r="E45" s="1">
-        <v>0</v>
-      </c>
-      <c r="F45" s="1">
-        <v>208888</v>
-      </c>
-      <c r="G45" s="1">
-        <v>1</v>
-      </c>
-      <c r="H45" s="1" t="s">
+      <c r="I45" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="J45" s="1">
         <v>4</v>
       </c>
       <c r="K45" s="1">
-        <v>204</v>
+        <v>24</v>
       </c>
       <c r="L45" s="1">
         <v>1</v>
       </c>
       <c r="M45" s="1">
-        <f t="shared" si="2"/>
-        <v>208888</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:13">
+        <f>F45*G45</f>
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="2:15">
       <c r="C46" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
@@ -3087,318 +3104,359 @@
         <v>4</v>
       </c>
       <c r="F46" s="1">
-        <v>200000</v>
+        <v>15000</v>
       </c>
       <c r="G46" s="1">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="H46" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J46" s="1">
+        <v>4</v>
+      </c>
+      <c r="K46" s="4">
+        <v>54</v>
+      </c>
+      <c r="L46" s="1">
+        <v>1</v>
+      </c>
+      <c r="M46" s="1">
+        <f>F46*G46</f>
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" customHeight="1" spans="2:15">
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="2:15">
+      <c r="B48" s="1"/>
+      <c r="C48" s="1">
+        <v>50</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0</v>
+      </c>
+      <c r="F48" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G48" s="1">
+        <v>20</v>
+      </c>
+      <c r="H48" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="I48" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="J46" s="1">
+      <c r="J48" s="1">
         <v>5</v>
       </c>
-      <c r="K46" s="1">
-        <v>4027</v>
-      </c>
-      <c r="L46" s="1">
-        <v>1</v>
-      </c>
-      <c r="M46" s="1">
-        <f t="shared" si="2"/>
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:13">
-      <c r="C47" s="1">
-        <v>42</v>
-      </c>
-      <c r="D47" s="1">
-        <v>0</v>
-      </c>
-      <c r="E47" s="1">
-        <v>4</v>
-      </c>
-      <c r="F47" s="1">
-        <v>10000</v>
-      </c>
-      <c r="G47" s="1">
-        <v>200</v>
-      </c>
-      <c r="H47" s="1" t="s">
+      <c r="K48" s="1">
+        <v>4034</v>
+      </c>
+      <c r="L48" s="1">
+        <v>1</v>
+      </c>
+      <c r="M48" s="1">
+        <f t="shared" ref="M48:M52" si="2">F48*G48</f>
+        <v>2000000</v>
+      </c>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="1:15">
+      <c r="B49" s="1"/>
+      <c r="C49" s="1">
+        <v>51</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0</v>
+      </c>
+      <c r="F49" s="1">
+        <v>150000</v>
+      </c>
+      <c r="G49" s="1">
+        <v>5</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I47" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="J47" s="1">
-        <v>4</v>
-      </c>
-      <c r="K47" s="4">
-        <v>36</v>
-      </c>
-      <c r="L47" s="1">
-        <v>1</v>
-      </c>
-      <c r="M47" s="1">
-        <f t="shared" si="2"/>
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:13">
-      <c r="C48" s="1">
-        <v>43</v>
-      </c>
-      <c r="D48" s="1">
-        <v>0</v>
-      </c>
-      <c r="E48" s="1">
-        <v>0</v>
-      </c>
-      <c r="F48" s="1">
-        <v>50000</v>
-      </c>
-      <c r="G48" s="1">
-        <v>50</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J48" s="1">
-        <v>4</v>
-      </c>
-      <c r="K48" s="1">
-        <v>24</v>
-      </c>
-      <c r="L48" s="1">
-        <v>1</v>
-      </c>
-      <c r="M48" s="1">
-        <f t="shared" si="2"/>
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C49" s="1">
-        <v>44</v>
-      </c>
-      <c r="D49" s="1">
-        <v>0</v>
-      </c>
-      <c r="E49" s="1">
-        <v>10</v>
-      </c>
-      <c r="F49" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G49" s="1">
-        <v>500</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="I49" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="J49" s="1">
         <v>5</v>
       </c>
       <c r="K49" s="1">
-        <v>4051</v>
+        <v>4112</v>
       </c>
       <c r="L49" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M49" s="1">
         <f t="shared" si="2"/>
-        <v>500000</v>
-      </c>
+        <v>750000</v>
+      </c>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1">
+        <v>52</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0</v>
+      </c>
+      <c r="E50" s="1">
+        <v>10</v>
+      </c>
+      <c r="F50" s="1">
+        <v>80000</v>
+      </c>
+      <c r="G50" s="1">
+        <v>40</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J50" s="1">
+        <v>5</v>
+      </c>
+      <c r="K50" s="1">
+        <v>4033</v>
+      </c>
+      <c r="L50" s="1">
+        <v>500</v>
+      </c>
+      <c r="M50" s="1">
+        <f t="shared" si="2"/>
+        <v>3200000</v>
+      </c>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
     </row>
     <row r="51" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F51" s="1">
         <v>100000</v>
       </c>
       <c r="G51" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="J51" s="1">
         <v>5</v>
       </c>
       <c r="K51" s="1">
-        <v>4034</v>
+        <v>4040</v>
       </c>
       <c r="L51" s="1">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="M51" s="1">
-        <f>F51*G51</f>
-        <v>1000000</v>
+        <f t="shared" si="2"/>
+        <v>4000000</v>
       </c>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
     </row>
     <row r="52" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F52" s="1">
         <v>150000</v>
       </c>
       <c r="G52" s="1">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J52" s="1">
         <v>5</v>
       </c>
       <c r="K52" s="1">
-        <v>4112</v>
+        <v>4050</v>
       </c>
       <c r="L52" s="1">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="M52" s="1">
-        <f>F52*G52</f>
-        <v>300000</v>
+        <f t="shared" si="2"/>
+        <v>6000000</v>
       </c>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
     </row>
     <row r="53" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
       </c>
       <c r="E53" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F53" s="1">
-        <v>80000</v>
+        <v>500000</v>
       </c>
       <c r="G53" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="J53" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K53" s="1">
-        <v>4033</v>
+        <v>29</v>
       </c>
       <c r="L53" s="1">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="M53" s="1">
-        <f>F53*G53</f>
-        <v>1600000</v>
+        <f t="shared" ref="M53:M57" si="3">F53*G53</f>
+        <v>3000000</v>
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
     </row>
-    <row r="54" customFormat="1" customHeight="1" spans="1:15">
-      <c r="B54" s="1"/>
-      <c r="C54" s="1">
-        <v>53</v>
-      </c>
-      <c r="D54" s="1">
-        <v>0</v>
-      </c>
-      <c r="E54" s="1">
-        <v>15</v>
-      </c>
-      <c r="F54" s="1">
-        <v>500000</v>
-      </c>
-      <c r="G54" s="1">
-        <v>3</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="J54" s="1">
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C55" s="1">
+        <v>60</v>
+      </c>
+      <c r="D55" s="1">
+        <v>0</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0</v>
+      </c>
+      <c r="F55" s="1">
+        <v>208888</v>
+      </c>
+      <c r="G55" s="1">
+        <v>2</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J55" s="1">
         <v>4</v>
       </c>
-      <c r="K54" s="1">
-        <v>29</v>
-      </c>
-      <c r="L54" s="1">
-        <v>1</v>
-      </c>
-      <c r="M54" s="1">
-        <f>F54*G54</f>
-        <v>1500000</v>
-      </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-    </row>
-    <row r="56" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-    </row>
-    <row r="57" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
+      <c r="K55" s="1">
+        <v>204</v>
+      </c>
+      <c r="L55" s="1">
+        <v>1</v>
+      </c>
+      <c r="M55" s="1">
+        <f t="shared" si="3"/>
+        <v>417776</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C56" s="1">
+        <v>61</v>
+      </c>
+      <c r="D56" s="1">
+        <v>0</v>
+      </c>
+      <c r="E56" s="1">
+        <v>10</v>
+      </c>
+      <c r="F56" s="1">
+        <v>800000</v>
+      </c>
+      <c r="G56" s="1">
+        <v>2</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J56" s="1">
+        <v>4</v>
+      </c>
+      <c r="K56" s="1">
+        <v>205</v>
+      </c>
+      <c r="L56" s="1">
+        <v>1</v>
+      </c>
+      <c r="M56" s="1">
+        <f t="shared" si="3"/>
+        <v>1600000</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C57" s="1">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
@@ -3407,152 +3465,150 @@
         <v>10</v>
       </c>
       <c r="F57" s="1">
-        <v>800000</v>
+        <v>1000000</v>
       </c>
       <c r="G57" s="1">
         <v>1</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="J57" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K57" s="1">
-        <v>4025</v>
+        <v>207</v>
       </c>
       <c r="L57" s="1">
         <v>1</v>
       </c>
       <c r="M57" s="1">
-        <f t="shared" ref="M57:M71" si="3">F57*G57</f>
-        <v>800000</v>
-      </c>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
+        <f t="shared" si="3"/>
+        <v>1000000</v>
+      </c>
     </row>
     <row r="58" customFormat="1" customHeight="1" spans="1:15">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D58" s="1">
         <v>0</v>
       </c>
       <c r="E58" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F58" s="1">
-        <v>1500000</v>
+        <v>800000</v>
       </c>
       <c r="G58" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J58" s="1">
         <v>5</v>
       </c>
       <c r="K58" s="1">
-        <v>4041</v>
+        <v>4025</v>
       </c>
       <c r="L58" s="1">
         <v>1</v>
       </c>
       <c r="M58" s="1">
-        <f t="shared" si="3"/>
-        <v>1500000</v>
+        <f>F58*G58</f>
+        <v>2400000</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="1:15">
+    <row r="59" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
       <c r="C59" s="1">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
       </c>
       <c r="E59" s="1">
+        <v>15</v>
+      </c>
+      <c r="F59" s="1">
+        <v>1500000</v>
+      </c>
+      <c r="G59" s="1">
+        <v>2</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J59" s="1">
+        <v>5</v>
+      </c>
+      <c r="K59" s="1">
+        <v>4041</v>
+      </c>
+      <c r="L59" s="1">
+        <v>1</v>
+      </c>
+      <c r="M59" s="1">
+        <f>F59*G59</f>
+        <v>3000000</v>
+      </c>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
+    </row>
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C60" s="1">
+        <v>65</v>
+      </c>
+      <c r="D60" s="1">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1">
         <v>10</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F60" s="1">
         <v>1000000</v>
       </c>
-      <c r="G59" s="1">
-        <v>1</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="J59" s="1">
+      <c r="G60" s="1">
+        <v>1</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J60" s="1">
         <v>4</v>
       </c>
-      <c r="K59" s="1">
-        <v>205</v>
-      </c>
-      <c r="L59" s="1">
-        <v>1</v>
-      </c>
-      <c r="M59" s="1">
-        <f t="shared" si="3"/>
+      <c r="K60" s="1">
+        <v>302</v>
+      </c>
+      <c r="L60" s="1">
+        <v>1</v>
+      </c>
+      <c r="M60" s="1">
+        <f t="shared" ref="M60:M65" si="4">F60*G60</f>
         <v>1000000</v>
       </c>
-    </row>
-    <row r="60" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1">
-        <v>63</v>
-      </c>
-      <c r="D60" s="1">
-        <v>0</v>
-      </c>
-      <c r="E60" s="1">
-        <v>20</v>
-      </c>
-      <c r="F60" s="1">
-        <v>100000</v>
-      </c>
-      <c r="G60" s="1">
-        <v>10</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="J60" s="1">
-        <v>5</v>
-      </c>
-      <c r="K60" s="1">
-        <v>4040</v>
-      </c>
-      <c r="L60" s="1">
-        <v>500</v>
-      </c>
-      <c r="M60" s="1">
-        <f t="shared" si="3"/>
-        <v>1000000</v>
-      </c>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C61" s="1">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
@@ -3561,254 +3617,235 @@
         <v>10</v>
       </c>
       <c r="F61" s="1">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="G61" s="1">
         <v>1</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="J61" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K61" s="1">
-        <v>301</v>
+        <v>4052</v>
       </c>
       <c r="L61" s="1">
         <v>1</v>
       </c>
       <c r="M61" s="1">
-        <f t="shared" si="3"/>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="62" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
+        <f t="shared" si="4"/>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C62" s="1">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F62" s="1">
-        <v>20000</v>
+        <v>500</v>
       </c>
       <c r="G62" s="1">
-        <v>200</v>
+        <v>10000</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J62" s="1">
         <v>5</v>
       </c>
       <c r="K62" s="1">
-        <v>4035</v>
+        <v>4022</v>
       </c>
       <c r="L62" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M62" s="1">
-        <f t="shared" si="3"/>
-        <v>4000000</v>
-      </c>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
+        <f t="shared" si="4"/>
+        <v>5000000</v>
+      </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C63" s="1">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F63" s="1">
-        <v>30000</v>
+        <v>1000</v>
       </c>
       <c r="G63" s="1">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J63" s="1">
         <v>5</v>
       </c>
       <c r="K63" s="1">
-        <v>4039</v>
+        <v>4051</v>
       </c>
       <c r="L63" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M63" s="1">
-        <f t="shared" si="3"/>
-        <v>6000000</v>
+        <f t="shared" si="4"/>
+        <v>2000000</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C64" s="1">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F64" s="1">
-        <v>30000</v>
+        <v>3000000</v>
       </c>
       <c r="G64" s="1">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J64" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K64" s="1">
-        <v>4038</v>
+        <v>211</v>
       </c>
       <c r="L64" s="1">
         <v>1</v>
       </c>
       <c r="M64" s="1">
-        <f t="shared" si="3"/>
-        <v>6000000</v>
+        <f t="shared" si="4"/>
+        <v>3000000</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C65" s="1">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F65" s="1">
-        <v>50000</v>
+        <v>3000000</v>
       </c>
       <c r="G65" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="J65" s="1">
+        <v>4</v>
+      </c>
+      <c r="K65" s="1">
+        <v>303</v>
+      </c>
+      <c r="L65" s="1">
+        <v>1</v>
+      </c>
+      <c r="M65" s="1">
+        <f t="shared" si="4"/>
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="66" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
+    </row>
+    <row r="67" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1">
+        <v>71</v>
+      </c>
+      <c r="D67" s="1">
+        <v>0</v>
+      </c>
+      <c r="E67" s="1">
+        <v>10</v>
+      </c>
+      <c r="F67" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G67" s="1">
+        <v>450</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J67" s="1">
         <v>5</v>
       </c>
-      <c r="K65" s="1">
-        <v>4046</v>
-      </c>
-      <c r="L65" s="1">
-        <v>1</v>
-      </c>
-      <c r="M65" s="1">
-        <f t="shared" si="3"/>
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C66" s="1">
-        <v>69</v>
-      </c>
-      <c r="D66" s="1">
-        <v>0</v>
-      </c>
-      <c r="E66" s="1">
-        <v>0</v>
-      </c>
-      <c r="F66" s="1">
-        <v>500</v>
-      </c>
-      <c r="G66" s="1">
-        <v>2000</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J66" s="1">
-        <v>5</v>
-      </c>
-      <c r="K66" s="1">
-        <v>4022</v>
-      </c>
-      <c r="L66" s="1">
-        <v>100</v>
-      </c>
-      <c r="M66" s="1">
-        <f t="shared" si="3"/>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C67" s="1">
-        <v>70</v>
-      </c>
-      <c r="D67" s="1">
-        <v>0</v>
-      </c>
-      <c r="E67" s="1">
-        <v>15</v>
-      </c>
-      <c r="F67" s="1">
-        <v>100000</v>
-      </c>
-      <c r="G67" s="1">
-        <v>10</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J67" s="1">
-        <v>11</v>
-      </c>
       <c r="K67" s="1">
-        <v>1998001</v>
+        <v>4035</v>
       </c>
       <c r="L67" s="1">
         <v>1</v>
       </c>
       <c r="M67" s="1">
-        <f t="shared" si="3"/>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="1:15">
+        <f>F67*G67</f>
+        <v>9000000</v>
+      </c>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
+    </row>
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C68" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
@@ -3817,517 +3854,421 @@
         <v>15</v>
       </c>
       <c r="F68" s="1">
-        <v>100000</v>
+        <v>30000</v>
       </c>
       <c r="G68" s="1">
-        <v>10</v>
+        <v>450</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J68" s="1">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K68" s="1">
-        <v>1998002</v>
+        <v>4039</v>
       </c>
       <c r="L68" s="1">
         <v>1</v>
       </c>
       <c r="M68" s="1">
-        <f t="shared" si="3"/>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="69" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
+        <f>F68*G68</f>
+        <v>13500000</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="1:15">
       <c r="C69" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
       </c>
       <c r="E69" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F69" s="1">
-        <v>100000</v>
+        <v>3000</v>
       </c>
       <c r="G69" s="1">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="J69" s="1">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K69" s="1">
-        <v>1998003</v>
+        <v>4011</v>
       </c>
       <c r="L69" s="1">
         <v>1</v>
       </c>
       <c r="M69" s="1">
-        <f t="shared" si="3"/>
-        <v>1000000</v>
-      </c>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
+        <f>F69*G69</f>
+        <v>3000000</v>
+      </c>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F70" s="1">
-        <v>100000</v>
+        <v>15000</v>
       </c>
       <c r="G70" s="1">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="J70" s="1">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K70" s="1">
-        <v>1998004</v>
+        <v>4019</v>
       </c>
       <c r="L70" s="1">
         <v>1</v>
       </c>
       <c r="M70" s="1">
-        <f t="shared" si="3"/>
-        <v>1000000</v>
-      </c>
-      <c r="N70" s="1"/>
+        <f>F70*G70</f>
+        <v>7500000</v>
+      </c>
+      <c r="N70" s="1">
+        <v>1</v>
+      </c>
       <c r="O70" s="1"/>
     </row>
     <row r="71" customFormat="1" customHeight="1" spans="1:15">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
       </c>
       <c r="E71" s="1">
+        <v>6</v>
+      </c>
+      <c r="F71" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G71" s="1">
+        <v>300</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J71" s="1">
+        <v>5</v>
+      </c>
+      <c r="K71" s="1">
+        <v>4026</v>
+      </c>
+      <c r="L71" s="1">
+        <v>1</v>
+      </c>
+      <c r="M71" s="1">
+        <f>F71*G71</f>
+        <v>6000000</v>
+      </c>
+      <c r="N71" s="1">
+        <v>1</v>
+      </c>
+      <c r="O71" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C72" s="1">
+        <v>76</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0</v>
+      </c>
+      <c r="E72" s="1">
+        <v>20</v>
+      </c>
+      <c r="F72" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G72" s="1">
+        <v>200</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J72" s="1">
+        <v>5</v>
+      </c>
+      <c r="K72" s="1">
+        <v>4038</v>
+      </c>
+      <c r="L72" s="1">
+        <v>1</v>
+      </c>
+      <c r="M72" s="1">
+        <f>F72*G72</f>
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C73" s="1">
+        <v>77</v>
+      </c>
+      <c r="D73" s="1">
+        <v>0</v>
+      </c>
+      <c r="E73" s="1">
+        <v>20</v>
+      </c>
+      <c r="F73" s="1">
+        <v>50000</v>
+      </c>
+      <c r="G73" s="1">
+        <v>100</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J73" s="1">
+        <v>5</v>
+      </c>
+      <c r="K73" s="1">
+        <v>4046</v>
+      </c>
+      <c r="L73" s="1">
+        <v>1</v>
+      </c>
+      <c r="M73" s="1">
+        <f>F73*G73</f>
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C76" s="1">
+        <v>80</v>
+      </c>
+      <c r="D76" s="1">
+        <v>0</v>
+      </c>
+      <c r="E76" s="1">
         <v>15</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F76" s="1">
         <v>100000</v>
       </c>
-      <c r="G71" s="1">
+      <c r="G76" s="1">
         <v>10</v>
       </c>
-      <c r="H71" s="1" t="s">
+      <c r="H76" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="I71" s="1" t="s">
+      <c r="I76" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="J71" s="1">
+      <c r="J76" s="1">
         <v>11</v>
       </c>
-      <c r="K71" s="1">
-        <v>1998005</v>
-      </c>
-      <c r="L71" s="1">
-        <v>1</v>
-      </c>
-      <c r="M71" s="1">
-        <f t="shared" si="3"/>
+      <c r="K76" s="1">
+        <v>1998001</v>
+      </c>
+      <c r="L76" s="1">
+        <v>1</v>
+      </c>
+      <c r="M76" s="1">
+        <f>F76*G76</f>
         <v>1000000</v>
       </c>
-      <c r="N71" s="1"/>
-      <c r="O71" s="1"/>
-    </row>
-    <row r="72" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A72"/>
-      <c r="B72"/>
-    </row>
-    <row r="73" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
-      <c r="L73" s="1"/>
-      <c r="M73" s="1"/>
-      <c r="N73" s="1"/>
-      <c r="O73" s="1"/>
-    </row>
-    <row r="74" customFormat="1" customHeight="1" spans="1:15">
-      <c r="B74" s="1"/>
-      <c r="C74" s="1">
-        <v>102</v>
-      </c>
-      <c r="D74" s="1">
-        <v>1</v>
-      </c>
-      <c r="E74" s="1">
-        <v>0</v>
-      </c>
-      <c r="F74" s="1">
-        <v>100</v>
-      </c>
-      <c r="G74" s="1">
-        <f t="shared" ref="G74:G79" si="4">N74*O78</f>
-        <v>300</v>
-      </c>
-      <c r="H74" s="1" t="s">
+    </row>
+    <row r="77" customHeight="1" spans="1:15">
+      <c r="C77" s="1">
+        <v>81</v>
+      </c>
+      <c r="D77" s="1">
+        <v>0</v>
+      </c>
+      <c r="E77" s="1">
+        <v>15</v>
+      </c>
+      <c r="F77" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G77" s="1">
+        <v>10</v>
+      </c>
+      <c r="H77" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="I74" s="1" t="s">
+      <c r="I77" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="J74" s="1">
-        <v>5</v>
-      </c>
-      <c r="K74" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L74" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M74" s="1">
-        <f t="shared" ref="M74:M81" si="5">F74*G74</f>
-        <v>30000</v>
-      </c>
-      <c r="N74" s="1">
-        <v>1</v>
-      </c>
-      <c r="O74" s="1"/>
-    </row>
-    <row r="75" customFormat="1" customHeight="1" spans="1:15">
-      <c r="B75" s="1"/>
-      <c r="C75" s="1">
-        <v>103</v>
-      </c>
-      <c r="D75" s="1">
-        <v>1</v>
-      </c>
-      <c r="E75" s="1">
-        <v>0</v>
-      </c>
-      <c r="F75" s="1">
-        <v>100</v>
-      </c>
-      <c r="G75" s="1">
-        <f t="shared" si="4"/>
-        <v>500</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J75" s="1">
-        <v>5</v>
-      </c>
-      <c r="K75" s="1">
-        <v>4101</v>
-      </c>
-      <c r="L75" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M75" s="1">
-        <f t="shared" si="5"/>
-        <v>50000</v>
-      </c>
-      <c r="N75" s="1">
-        <v>1</v>
-      </c>
-      <c r="O75" s="1"/>
-    </row>
-    <row r="76" customFormat="1" customHeight="1" spans="1:15">
-      <c r="B76" s="1"/>
-      <c r="C76" s="1">
-        <v>104</v>
-      </c>
-      <c r="D76" s="1">
-        <v>1</v>
-      </c>
-      <c r="E76" s="1">
-        <v>0</v>
-      </c>
-      <c r="F76" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G76" s="1">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J76" s="1">
-        <v>15</v>
-      </c>
-      <c r="K76" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L76" s="1">
-        <v>100</v>
-      </c>
-      <c r="M76" s="1">
-        <f t="shared" si="5"/>
-        <v>20000</v>
-      </c>
-      <c r="N76" s="1">
-        <v>1</v>
-      </c>
-      <c r="O76" s="1"/>
-    </row>
-    <row r="77" customFormat="1" customHeight="1" spans="1:15">
-      <c r="B77" s="1"/>
-      <c r="C77" s="1">
-        <v>105</v>
-      </c>
-      <c r="D77" s="1">
-        <v>1</v>
-      </c>
-      <c r="E77" s="1">
-        <v>1</v>
-      </c>
-      <c r="F77" s="1">
-        <v>15000</v>
-      </c>
-      <c r="G77" s="1">
-        <f t="shared" si="4"/>
-        <v>8</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="J77" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K77" s="1">
-        <v>4019</v>
+        <v>1998002</v>
       </c>
       <c r="L77" s="1">
         <v>1</v>
       </c>
       <c r="M77" s="1">
-        <f t="shared" si="5"/>
-        <v>120000</v>
-      </c>
-      <c r="N77" s="1">
-        <v>1</v>
-      </c>
-      <c r="O77" s="1"/>
+        <f>F77*G77</f>
+        <v>1000000</v>
+      </c>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="1:15">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="D78" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F78" s="1">
-        <v>500</v>
+        <v>100000</v>
       </c>
       <c r="G78" s="1">
-        <f t="shared" si="4"/>
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="J78" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K78" s="1">
-        <v>4001</v>
+        <v>1998003</v>
       </c>
       <c r="L78" s="1">
+        <v>1</v>
+      </c>
+      <c r="M78" s="1">
+        <f>F78*G78</f>
         <v>1000000</v>
       </c>
-      <c r="M78" s="1">
-        <f t="shared" si="5"/>
-        <v>20000</v>
-      </c>
-      <c r="N78" s="1">
-        <v>1</v>
-      </c>
-      <c r="O78" s="1">
-        <v>300</v>
-      </c>
+      <c r="N78" s="1"/>
+      <c r="O78" s="1"/>
     </row>
     <row r="79" customFormat="1" customHeight="1" spans="1:15">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D79" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F79" s="1">
-        <v>500</v>
+        <v>100000</v>
       </c>
       <c r="G79" s="1">
-        <f t="shared" si="4"/>
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="J79" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K79" s="1">
-        <v>4002</v>
+        <v>1998004</v>
       </c>
       <c r="L79" s="1">
-        <v>6000000</v>
+        <v>1</v>
       </c>
       <c r="M79" s="1">
-        <f t="shared" si="5"/>
-        <v>20000</v>
-      </c>
-      <c r="N79" s="1">
-        <v>1</v>
-      </c>
-      <c r="O79" s="1">
-        <v>500</v>
-      </c>
+        <f>F79*G79</f>
+        <v>1000000</v>
+      </c>
+      <c r="N79" s="1"/>
+      <c r="O79" s="1"/>
     </row>
     <row r="80" customFormat="1" customHeight="1" spans="1:15">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="D80" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" s="1">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F80" s="1">
-        <v>20000</v>
+        <v>100000</v>
       </c>
       <c r="G80" s="1">
         <v>10</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="J80" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K80" s="1">
-        <v>4026</v>
+        <v>1998005</v>
       </c>
       <c r="L80" s="1">
         <v>1</v>
       </c>
       <c r="M80" s="1">
-        <f t="shared" si="5"/>
-        <v>200000</v>
-      </c>
-      <c r="N80" s="1">
-        <v>1</v>
-      </c>
-      <c r="O80" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="81" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1">
-        <v>109</v>
-      </c>
-      <c r="D81" s="1">
-        <v>1</v>
-      </c>
-      <c r="E81" s="1">
-        <v>10</v>
-      </c>
-      <c r="F81" s="1">
-        <v>20000</v>
-      </c>
-      <c r="G81" s="1">
-        <v>10</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J81" s="1">
-        <v>5</v>
-      </c>
-      <c r="K81" s="1">
-        <v>4035</v>
-      </c>
-      <c r="L81" s="1">
-        <v>1</v>
-      </c>
-      <c r="M81" s="1">
-        <f t="shared" si="5"/>
-        <v>200000</v>
-      </c>
-      <c r="N81" s="1"/>
-      <c r="O81" s="1">
-        <v>8</v>
-      </c>
+        <f>F80*G80</f>
+        <v>1000000</v>
+      </c>
+      <c r="N80" s="1"/>
+      <c r="O80" s="1"/>
+    </row>
+    <row r="81" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A81"/>
+      <c r="B81"/>
     </row>
     <row r="82" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A82" s="1"/>
-      <c r="B82"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -4340,32 +4281,31 @@
       <c r="L82" s="1"/>
       <c r="M82" s="1"/>
       <c r="N82" s="1"/>
-      <c r="O82" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="83" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O82" s="1"/>
+    </row>
+    <row r="83" customFormat="1" customHeight="1" spans="1:15">
+      <c r="B83" s="1"/>
       <c r="C83" s="1">
-        <v>201</v>
+        <v>102</v>
       </c>
       <c r="D83" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="1">
         <v>0</v>
       </c>
-      <c r="F83" s="5">
-        <v>200</v>
+      <c r="F83" s="1">
+        <v>100</v>
       </c>
       <c r="G83" s="1">
-        <f t="shared" ref="G83:G88" si="6">N83*O87</f>
+        <f t="shared" ref="G83:G87" si="5">N83*O83</f>
         <v>300</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="J83" s="1">
         <v>5</v>
@@ -4377,844 +4317,802 @@
         <v>1000</v>
       </c>
       <c r="M83" s="1">
-        <f t="shared" ref="M83:M90" si="7">F83*G83</f>
+        <f>F83*G83</f>
+        <v>30000</v>
+      </c>
+      <c r="N83" s="1">
+        <v>1</v>
+      </c>
+      <c r="O83" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="84" customFormat="1" customHeight="1" spans="1:15">
+      <c r="B84" s="1"/>
+      <c r="C84" s="1">
+        <v>103</v>
+      </c>
+      <c r="D84" s="1">
+        <v>1</v>
+      </c>
+      <c r="E84" s="1">
+        <v>0</v>
+      </c>
+      <c r="F84" s="1">
+        <v>100</v>
+      </c>
+      <c r="G84" s="1">
+        <f t="shared" si="5"/>
+        <v>500</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J84" s="1">
+        <v>5</v>
+      </c>
+      <c r="K84" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L84" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M84" s="1">
+        <f>F84*G84</f>
+        <v>50000</v>
+      </c>
+      <c r="N84" s="1">
+        <v>1</v>
+      </c>
+      <c r="O84" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="85" customFormat="1" customHeight="1" spans="1:15">
+      <c r="B85" s="1"/>
+      <c r="C85" s="1">
+        <v>104</v>
+      </c>
+      <c r="D85" s="1">
+        <v>1</v>
+      </c>
+      <c r="E85" s="1">
+        <v>0</v>
+      </c>
+      <c r="F85" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G85" s="1">
+        <f t="shared" si="5"/>
+        <v>40</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J85" s="1">
+        <v>15</v>
+      </c>
+      <c r="K85" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L85" s="1">
+        <v>100</v>
+      </c>
+      <c r="M85" s="1">
+        <f>F85*G85</f>
+        <v>40000</v>
+      </c>
+      <c r="N85" s="1">
+        <v>1</v>
+      </c>
+      <c r="O85" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="86" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1">
+        <v>106</v>
+      </c>
+      <c r="D86" s="1">
+        <v>1</v>
+      </c>
+      <c r="E86" s="1">
+        <v>0</v>
+      </c>
+      <c r="F86" s="1">
+        <v>500</v>
+      </c>
+      <c r="G86" s="1">
+        <f t="shared" si="5"/>
+        <v>40</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J86" s="1">
+        <v>5</v>
+      </c>
+      <c r="K86" s="1">
+        <v>4001</v>
+      </c>
+      <c r="L86" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="M86" s="1">
+        <f>F86*G86</f>
+        <v>20000</v>
+      </c>
+      <c r="N86" s="1">
+        <v>1</v>
+      </c>
+      <c r="O86" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="87" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1">
+        <v>107</v>
+      </c>
+      <c r="D87" s="1">
+        <v>1</v>
+      </c>
+      <c r="E87" s="1">
+        <v>0</v>
+      </c>
+      <c r="F87" s="1">
+        <v>500</v>
+      </c>
+      <c r="G87" s="1">
+        <f t="shared" si="5"/>
+        <v>40</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J87" s="1">
+        <v>5</v>
+      </c>
+      <c r="K87" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L87" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M87" s="1">
+        <f>F87*G87</f>
+        <v>20000</v>
+      </c>
+      <c r="N87" s="1">
+        <v>1</v>
+      </c>
+      <c r="O87" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="89" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A89" s="1"/>
+      <c r="B89"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
+      <c r="K89" s="1"/>
+      <c r="L89" s="1"/>
+      <c r="M89" s="1"/>
+      <c r="N89" s="1"/>
+      <c r="O89" s="1"/>
+    </row>
+    <row r="90" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C90" s="1">
+        <v>201</v>
+      </c>
+      <c r="D90" s="1">
+        <v>2</v>
+      </c>
+      <c r="E90" s="1">
+        <v>0</v>
+      </c>
+      <c r="F90" s="5">
+        <v>200</v>
+      </c>
+      <c r="G90" s="1">
+        <f t="shared" ref="G90:G94" si="6">N90*O90</f>
+        <v>300</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J90" s="1">
+        <v>5</v>
+      </c>
+      <c r="K90" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L90" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M90" s="1">
+        <f>F90*G90</f>
         <v>60000</v>
       </c>
-      <c r="N83" s="1">
-        <v>1</v>
-      </c>
-      <c r="O83" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="84" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C84" s="1">
+      <c r="N90" s="1">
+        <v>1</v>
+      </c>
+      <c r="O90" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="91" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C91" s="1">
         <v>202</v>
       </c>
-      <c r="D84" s="1">
+      <c r="D91" s="1">
         <v>2</v>
       </c>
-      <c r="E84" s="1">
-        <v>0</v>
-      </c>
-      <c r="F84" s="5">
+      <c r="E91" s="1">
+        <v>0</v>
+      </c>
+      <c r="F91" s="5">
         <v>200</v>
       </c>
-      <c r="G84" s="1">
+      <c r="G91" s="1">
         <f t="shared" si="6"/>
         <v>500</v>
       </c>
-      <c r="H84" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J84" s="1">
+      <c r="H91" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J91" s="1">
         <v>5</v>
       </c>
-      <c r="K84" s="1">
+      <c r="K91" s="1">
         <v>4101</v>
       </c>
-      <c r="L84" s="1">
+      <c r="L91" s="1">
         <v>1000</v>
       </c>
-      <c r="M84" s="1">
-        <f t="shared" si="7"/>
+      <c r="M91" s="1">
+        <f>F91*G91</f>
         <v>100000</v>
       </c>
-      <c r="N84" s="1">
-        <v>1</v>
-      </c>
-      <c r="O84" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="85" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C85" s="1">
+      <c r="N91" s="1">
+        <v>1</v>
+      </c>
+      <c r="O91" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="92" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C92" s="1">
         <v>203</v>
       </c>
-      <c r="D85" s="1">
+      <c r="D92" s="1">
         <v>2</v>
       </c>
-      <c r="E85" s="1">
-        <v>0</v>
-      </c>
-      <c r="F85" s="5">
+      <c r="E92" s="1">
+        <v>0</v>
+      </c>
+      <c r="F92" s="5">
         <v>2000</v>
       </c>
-      <c r="G85" s="1">
-        <f t="shared" si="6"/>
-        <v>20</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J85" s="1">
-        <v>15</v>
-      </c>
-      <c r="K85" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L85" s="1">
-        <v>100</v>
-      </c>
-      <c r="M85" s="1">
-        <f t="shared" si="7"/>
-        <v>40000</v>
-      </c>
-      <c r="N85" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A86"/>
-      <c r="C86" s="1">
-        <v>204</v>
-      </c>
-      <c r="D86" s="1">
-        <v>2</v>
-      </c>
-      <c r="E86" s="1">
-        <v>1</v>
-      </c>
-      <c r="F86" s="1">
-        <v>15000</v>
-      </c>
-      <c r="G86" s="1">
-        <f t="shared" si="6"/>
-        <v>8</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I86" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J86" s="1">
-        <v>5</v>
-      </c>
-      <c r="K86" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L86" s="1">
-        <v>1</v>
-      </c>
-      <c r="M86" s="1">
-        <f t="shared" si="7"/>
-        <v>120000</v>
-      </c>
-      <c r="N86" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C87" s="1">
-        <v>205</v>
-      </c>
-      <c r="D87" s="1">
-        <v>2</v>
-      </c>
-      <c r="E87" s="1">
-        <v>0</v>
-      </c>
-      <c r="F87" s="5">
-        <v>1000</v>
-      </c>
-      <c r="G87" s="1">
+      <c r="G92" s="1">
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="H87" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J87" s="1">
-        <v>5</v>
-      </c>
-      <c r="K87" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L87" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M87" s="1">
-        <f t="shared" si="7"/>
-        <v>40000</v>
-      </c>
-      <c r="N87" s="1">
-        <v>1</v>
-      </c>
-      <c r="O87" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="88" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C88" s="1">
-        <v>206</v>
-      </c>
-      <c r="D88" s="1">
+      <c r="H92" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J92" s="1">
+        <v>15</v>
+      </c>
+      <c r="K92" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L92" s="1">
+        <v>100</v>
+      </c>
+      <c r="M92" s="1">
+        <f>F92*G92</f>
+        <v>80000</v>
+      </c>
+      <c r="N92" s="1">
+        <v>1</v>
+      </c>
+      <c r="O92" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="93" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C93" s="1">
+        <v>205</v>
+      </c>
+      <c r="D93" s="1">
         <v>2</v>
       </c>
-      <c r="E88" s="1">
-        <v>0</v>
-      </c>
-      <c r="F88" s="5">
+      <c r="E93" s="1">
+        <v>0</v>
+      </c>
+      <c r="F93" s="5">
         <v>1000</v>
       </c>
-      <c r="G88" s="1">
+      <c r="G93" s="1">
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="H88" s="1" t="s">
+      <c r="H93" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J93" s="1">
+        <v>5</v>
+      </c>
+      <c r="K93" s="1">
+        <v>4001</v>
+      </c>
+      <c r="L93" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="M93" s="1">
+        <f>F93*G93</f>
+        <v>40000</v>
+      </c>
+      <c r="N93" s="1">
+        <v>1</v>
+      </c>
+      <c r="O93" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="94" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C94" s="1">
+        <v>206</v>
+      </c>
+      <c r="D94" s="1">
+        <v>2</v>
+      </c>
+      <c r="E94" s="1">
+        <v>0</v>
+      </c>
+      <c r="F94" s="5">
+        <v>1000</v>
+      </c>
+      <c r="G94" s="1">
+        <f t="shared" si="6"/>
+        <v>40</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J94" s="1">
+        <v>5</v>
+      </c>
+      <c r="K94" s="1">
+        <v>4002</v>
+      </c>
+      <c r="L94" s="1">
+        <v>6000000</v>
+      </c>
+      <c r="M94" s="1">
+        <f>F94*G94</f>
+        <v>40000</v>
+      </c>
+      <c r="N94" s="1">
+        <v>1</v>
+      </c>
+      <c r="O94" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A95" s="1"/>
+      <c r="B95"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
+      <c r="K95" s="1"/>
+      <c r="L95" s="1"/>
+      <c r="M95" s="1"/>
+      <c r="N95" s="1"/>
+      <c r="O95" s="1"/>
+    </row>
+    <row r="96" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C96" s="1">
+        <v>211</v>
+      </c>
+      <c r="D96" s="1">
+        <v>3</v>
+      </c>
+      <c r="E96" s="1">
+        <v>0</v>
+      </c>
+      <c r="F96" s="1">
+        <v>400</v>
+      </c>
+      <c r="G96" s="1">
+        <f t="shared" ref="G96:G100" si="7">N96*O96</f>
+        <v>300</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J96" s="1">
+        <v>5</v>
+      </c>
+      <c r="K96" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L96" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M96" s="1">
+        <f>F96*G96</f>
+        <v>120000</v>
+      </c>
+      <c r="N96" s="1">
+        <v>1</v>
+      </c>
+      <c r="O96" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="97" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C97" s="1">
+        <v>212</v>
+      </c>
+      <c r="D97" s="1">
+        <v>3</v>
+      </c>
+      <c r="E97" s="1">
+        <v>0</v>
+      </c>
+      <c r="F97" s="1">
+        <v>400</v>
+      </c>
+      <c r="G97" s="1">
+        <f t="shared" si="7"/>
+        <v>500</v>
+      </c>
+      <c r="H97" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="I88" s="1" t="s">
+      <c r="I97" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="J88" s="1">
+      <c r="J97" s="1">
         <v>5</v>
       </c>
-      <c r="K88" s="1">
+      <c r="K97" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L97" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M97" s="1">
+        <f>F97*G97</f>
+        <v>200000</v>
+      </c>
+      <c r="N97" s="1">
+        <v>1</v>
+      </c>
+      <c r="O97" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="98" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C98" s="1">
+        <v>213</v>
+      </c>
+      <c r="D98" s="1">
+        <v>3</v>
+      </c>
+      <c r="E98" s="1">
+        <v>0</v>
+      </c>
+      <c r="F98" s="1">
+        <v>4000</v>
+      </c>
+      <c r="G98" s="1">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J98" s="1">
+        <v>15</v>
+      </c>
+      <c r="K98" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L98" s="1">
+        <v>100</v>
+      </c>
+      <c r="M98" s="1">
+        <f>F98*G98</f>
+        <v>160000</v>
+      </c>
+      <c r="N98" s="1">
+        <v>1</v>
+      </c>
+      <c r="O98" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="99" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C99" s="1">
+        <v>215</v>
+      </c>
+      <c r="D99" s="1">
+        <v>3</v>
+      </c>
+      <c r="E99" s="1">
+        <v>0</v>
+      </c>
+      <c r="F99" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G99" s="1">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J99" s="1">
+        <v>5</v>
+      </c>
+      <c r="K99" s="1">
+        <v>4001</v>
+      </c>
+      <c r="L99" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="M99" s="1">
+        <f>F99*G99</f>
+        <v>80000</v>
+      </c>
+      <c r="N99" s="1">
+        <v>1</v>
+      </c>
+      <c r="O99" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="100" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C100" s="1">
+        <v>216</v>
+      </c>
+      <c r="D100" s="1">
+        <v>3</v>
+      </c>
+      <c r="E100" s="1">
+        <v>0</v>
+      </c>
+      <c r="F100" s="1">
+        <v>2000</v>
+      </c>
+      <c r="G100" s="1">
+        <f t="shared" si="7"/>
+        <v>40</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J100" s="1">
+        <v>5</v>
+      </c>
+      <c r="K100" s="1">
         <v>4002</v>
       </c>
-      <c r="L88" s="1">
+      <c r="L100" s="1">
         <v>6000000</v>
       </c>
-      <c r="M88" s="1">
-        <f t="shared" si="7"/>
-        <v>40000</v>
-      </c>
-      <c r="N88" s="1">
-        <v>1</v>
-      </c>
-      <c r="O88" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="89" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C89" s="1">
-        <v>207</v>
-      </c>
-      <c r="D89" s="1">
-        <v>2</v>
-      </c>
-      <c r="E89" s="1">
-        <v>6</v>
-      </c>
-      <c r="F89" s="1">
-        <v>20000</v>
-      </c>
-      <c r="G89" s="1">
-        <v>10</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J89" s="1">
+      <c r="M100" s="1">
+        <f>F100*G100</f>
+        <v>80000</v>
+      </c>
+      <c r="N100" s="1">
+        <v>1</v>
+      </c>
+      <c r="O100" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="101" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A101" s="1"/>
+      <c r="B101"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
+      <c r="K101" s="1"/>
+      <c r="L101" s="1"/>
+      <c r="M101" s="1"/>
+      <c r="N101" s="1"/>
+      <c r="O101" s="1"/>
+    </row>
+    <row r="102" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C102" s="1">
+        <v>221</v>
+      </c>
+      <c r="D102" s="1">
+        <v>4</v>
+      </c>
+      <c r="E102" s="1">
+        <v>0</v>
+      </c>
+      <c r="F102" s="5">
+        <v>600</v>
+      </c>
+      <c r="G102" s="1">
+        <f t="shared" ref="G102:G106" si="8">N102*O102</f>
+        <v>300</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="J102" s="1">
         <v>5</v>
       </c>
-      <c r="K89" s="1">
-        <v>4026</v>
-      </c>
-      <c r="L89" s="1">
-        <v>1</v>
-      </c>
-      <c r="M89" s="1">
-        <f t="shared" si="7"/>
-        <v>200000</v>
-      </c>
-      <c r="N89" s="1">
-        <v>1</v>
-      </c>
-      <c r="O89" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="90" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C90" s="1">
-        <v>208</v>
-      </c>
-      <c r="D90" s="1">
-        <v>2</v>
-      </c>
-      <c r="E90" s="1">
-        <v>10</v>
-      </c>
-      <c r="F90" s="1">
-        <v>20000</v>
-      </c>
-      <c r="G90" s="1">
-        <v>10</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J90" s="1">
-        <v>5</v>
-      </c>
-      <c r="K90" s="1">
-        <v>4035</v>
-      </c>
-      <c r="L90" s="1">
-        <v>1</v>
-      </c>
-      <c r="M90" s="1">
-        <f t="shared" si="7"/>
-        <v>200000</v>
-      </c>
-      <c r="O90" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="91" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A91" s="1"/>
-      <c r="B91"/>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
-      <c r="K91" s="1"/>
-      <c r="L91" s="1"/>
-      <c r="M91" s="1"/>
-      <c r="N91" s="1"/>
-      <c r="O91" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="92" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C92" s="1">
-        <v>211</v>
-      </c>
-      <c r="D92" s="1">
-        <v>3</v>
-      </c>
-      <c r="E92" s="1">
-        <v>0</v>
-      </c>
-      <c r="F92" s="1">
-        <v>400</v>
-      </c>
-      <c r="G92" s="1">
-        <f t="shared" ref="G92:G97" si="8">N92*O96</f>
+      <c r="K102" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L102" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M102" s="1">
+        <f>F102*G102</f>
+        <v>180000</v>
+      </c>
+      <c r="N102" s="1">
+        <v>1</v>
+      </c>
+      <c r="O102" s="1">
         <v>300</v>
       </c>
-      <c r="H92" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J92" s="1">
-        <v>5</v>
-      </c>
-      <c r="K92" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L92" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M92" s="1">
-        <f t="shared" ref="M92:M99" si="9">F92*G92</f>
-        <v>120000</v>
-      </c>
-      <c r="N92" s="1">
-        <v>1</v>
-      </c>
-      <c r="O92" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="93" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C93" s="1">
-        <v>212</v>
-      </c>
-      <c r="D93" s="1">
-        <v>3</v>
-      </c>
-      <c r="E93" s="1">
-        <v>0</v>
-      </c>
-      <c r="F93" s="1">
-        <v>400</v>
-      </c>
-      <c r="G93" s="1">
+    </row>
+    <row r="103" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C103" s="1">
+        <v>222</v>
+      </c>
+      <c r="D103" s="1">
+        <v>4</v>
+      </c>
+      <c r="E103" s="1">
+        <v>0</v>
+      </c>
+      <c r="F103" s="5">
+        <v>600</v>
+      </c>
+      <c r="G103" s="1">
         <f t="shared" si="8"/>
         <v>500</v>
       </c>
-      <c r="H93" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J93" s="1">
+      <c r="H103" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J103" s="1">
         <v>5</v>
       </c>
-      <c r="K93" s="1">
+      <c r="K103" s="1">
         <v>4101</v>
       </c>
-      <c r="L93" s="1">
+      <c r="L103" s="1">
         <v>1000</v>
       </c>
-      <c r="M93" s="1">
-        <f t="shared" si="9"/>
-        <v>200000</v>
-      </c>
-      <c r="N93" s="1">
-        <v>1</v>
-      </c>
-      <c r="O93" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C94" s="1">
-        <v>213</v>
-      </c>
-      <c r="D94" s="1">
-        <v>3</v>
-      </c>
-      <c r="E94" s="1">
-        <v>0</v>
-      </c>
-      <c r="F94" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G94" s="1">
-        <f t="shared" si="8"/>
-        <v>20</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J94" s="1">
-        <v>15</v>
-      </c>
-      <c r="K94" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L94" s="1">
-        <v>100</v>
-      </c>
-      <c r="M94" s="1">
-        <f t="shared" si="9"/>
-        <v>80000</v>
-      </c>
-      <c r="N94" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A95"/>
-      <c r="C95" s="1">
-        <v>214</v>
-      </c>
-      <c r="D95" s="1">
-        <v>3</v>
-      </c>
-      <c r="E95" s="1">
-        <v>1</v>
-      </c>
-      <c r="F95" s="1">
-        <v>45000</v>
-      </c>
-      <c r="G95" s="1">
-        <f t="shared" si="8"/>
-        <v>8</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J95" s="1">
-        <v>5</v>
-      </c>
-      <c r="K95" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L95" s="1">
-        <v>1</v>
-      </c>
-      <c r="M95" s="1">
-        <f t="shared" si="9"/>
-        <v>360000</v>
-      </c>
-      <c r="N95" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C96" s="1">
-        <v>215</v>
-      </c>
-      <c r="D96" s="1">
-        <v>3</v>
-      </c>
-      <c r="E96" s="1">
-        <v>0</v>
-      </c>
-      <c r="F96" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G96" s="1">
+      <c r="M103" s="1">
+        <f>F103*G103</f>
+        <v>300000</v>
+      </c>
+      <c r="N103" s="1">
+        <v>1</v>
+      </c>
+      <c r="O103" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="104" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C104" s="1">
+        <v>223</v>
+      </c>
+      <c r="D104" s="1">
+        <v>4</v>
+      </c>
+      <c r="E104" s="1">
+        <v>0</v>
+      </c>
+      <c r="F104" s="5">
+        <v>6000</v>
+      </c>
+      <c r="G104" s="1">
         <f t="shared" si="8"/>
         <v>40</v>
       </c>
-      <c r="H96" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J96" s="1">
-        <v>5</v>
-      </c>
-      <c r="K96" s="1">
-        <v>4001</v>
-      </c>
-      <c r="L96" s="1">
-        <v>1000000</v>
-      </c>
-      <c r="M96" s="1">
-        <f t="shared" si="9"/>
-        <v>80000</v>
-      </c>
-      <c r="N96" s="1">
-        <v>1</v>
-      </c>
-      <c r="O96" s="1">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="97" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C97" s="1">
-        <v>216</v>
-      </c>
-      <c r="D97" s="1">
-        <v>3</v>
-      </c>
-      <c r="E97" s="1">
-        <v>0</v>
-      </c>
-      <c r="F97" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G97" s="1">
-        <f t="shared" si="8"/>
+      <c r="H104" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J104" s="1">
+        <v>15</v>
+      </c>
+      <c r="K104" s="1">
+        <v>4014</v>
+      </c>
+      <c r="L104" s="1">
+        <v>100</v>
+      </c>
+      <c r="M104" s="1">
+        <f>F104*G104</f>
+        <v>240000</v>
+      </c>
+      <c r="N104" s="1">
+        <v>1</v>
+      </c>
+      <c r="O104" s="1">
         <v>40</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="J97" s="1">
-        <v>5</v>
-      </c>
-      <c r="K97" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L97" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M97" s="1">
-        <f t="shared" si="9"/>
-        <v>80000</v>
-      </c>
-      <c r="N97" s="1">
-        <v>1</v>
-      </c>
-      <c r="O97" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="98" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C98" s="1">
-        <v>217</v>
-      </c>
-      <c r="D98" s="1">
-        <v>3</v>
-      </c>
-      <c r="E98" s="1">
-        <v>6</v>
-      </c>
-      <c r="F98" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G98" s="1">
-        <v>10</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J98" s="1">
-        <v>5</v>
-      </c>
-      <c r="K98" s="1">
-        <v>4026</v>
-      </c>
-      <c r="L98" s="1">
-        <v>1</v>
-      </c>
-      <c r="M98" s="1">
-        <f t="shared" si="9"/>
-        <v>300000</v>
-      </c>
-      <c r="N98" s="1">
-        <v>1</v>
-      </c>
-      <c r="O98" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="99" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C99" s="1">
-        <v>218</v>
-      </c>
-      <c r="D99" s="1">
-        <v>3</v>
-      </c>
-      <c r="E99" s="1">
-        <v>10</v>
-      </c>
-      <c r="F99" s="1">
-        <v>20000</v>
-      </c>
-      <c r="G99" s="1">
-        <v>10</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J99" s="1">
-        <v>5</v>
-      </c>
-      <c r="K99" s="1">
-        <v>4035</v>
-      </c>
-      <c r="L99" s="1">
-        <v>1</v>
-      </c>
-      <c r="M99" s="1">
-        <f t="shared" si="9"/>
-        <v>200000</v>
-      </c>
-      <c r="O99" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="100" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A100" s="1"/>
-      <c r="B100"/>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
-      <c r="E100" s="1"/>
-      <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="1"/>
-      <c r="K100" s="1"/>
-      <c r="L100" s="1"/>
-      <c r="M100" s="1"/>
-      <c r="N100" s="1"/>
-      <c r="O100" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="101" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C101" s="1">
-        <v>221</v>
-      </c>
-      <c r="D101" s="1">
-        <v>4</v>
-      </c>
-      <c r="E101" s="1">
-        <v>0</v>
-      </c>
-      <c r="F101" s="5">
-        <v>600</v>
-      </c>
-      <c r="G101" s="1">
-        <f t="shared" ref="G101:G106" si="10">N101*O105</f>
-        <v>300</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J101" s="1">
-        <v>5</v>
-      </c>
-      <c r="K101" s="1">
-        <v>4007</v>
-      </c>
-      <c r="L101" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M101" s="1">
-        <f t="shared" ref="M101:M108" si="11">F101*G101</f>
-        <v>180000</v>
-      </c>
-      <c r="N101" s="1">
-        <v>1</v>
-      </c>
-      <c r="O101" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="102" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C102" s="1">
-        <v>222</v>
-      </c>
-      <c r="D102" s="1">
-        <v>4</v>
-      </c>
-      <c r="E102" s="1">
-        <v>0</v>
-      </c>
-      <c r="F102" s="5">
-        <v>600</v>
-      </c>
-      <c r="G102" s="1">
-        <f t="shared" si="10"/>
-        <v>500</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J102" s="1">
-        <v>5</v>
-      </c>
-      <c r="K102" s="1">
-        <v>4101</v>
-      </c>
-      <c r="L102" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M102" s="1">
-        <f t="shared" si="11"/>
-        <v>300000</v>
-      </c>
-      <c r="N102" s="1">
-        <v>1</v>
-      </c>
-      <c r="O102" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="103" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C103" s="1">
-        <v>223</v>
-      </c>
-      <c r="D103" s="1">
-        <v>4</v>
-      </c>
-      <c r="E103" s="1">
-        <v>0</v>
-      </c>
-      <c r="F103" s="5">
-        <v>6000</v>
-      </c>
-      <c r="G103" s="1">
-        <f t="shared" si="10"/>
-        <v>20</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I103" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J103" s="1">
-        <v>15</v>
-      </c>
-      <c r="K103" s="1">
-        <v>4014</v>
-      </c>
-      <c r="L103" s="1">
-        <v>100</v>
-      </c>
-      <c r="M103" s="1">
-        <f t="shared" si="11"/>
-        <v>120000</v>
-      </c>
-      <c r="N103" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A104"/>
-      <c r="C104" s="1">
-        <v>224</v>
-      </c>
-      <c r="D104" s="1">
-        <v>4</v>
-      </c>
-      <c r="E104" s="1">
-        <v>1</v>
-      </c>
-      <c r="F104" s="1">
-        <v>15000</v>
-      </c>
-      <c r="G104" s="1">
-        <f t="shared" si="10"/>
-        <v>8</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J104" s="1">
-        <v>5</v>
-      </c>
-      <c r="K104" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L104" s="1">
-        <v>1</v>
-      </c>
-      <c r="M104" s="1">
-        <f t="shared" si="11"/>
-        <v>120000</v>
-      </c>
-      <c r="N104" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -5231,14 +5129,14 @@
         <v>3000</v>
       </c>
       <c r="G105" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="J105" s="1">
         <v>5</v>
@@ -5250,14 +5148,14 @@
         <v>1000000</v>
       </c>
       <c r="M105" s="1">
-        <f t="shared" si="11"/>
+        <f>F105*G105</f>
         <v>120000</v>
       </c>
       <c r="N105" s="1">
         <v>1</v>
       </c>
       <c r="O105" s="1">
-        <v>300</v>
+        <v>40</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -5274,14 +5172,14 @@
         <v>3000</v>
       </c>
       <c r="G106" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J106" s="1">
         <v>5</v>
@@ -5293,119 +5191,122 @@
         <v>6000000</v>
       </c>
       <c r="M106" s="1">
-        <f t="shared" si="11"/>
+        <f>F106*G106</f>
         <v>120000</v>
       </c>
       <c r="N106" s="1">
         <v>1</v>
       </c>
       <c r="O106" s="1">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="107" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C107" s="1">
-        <v>227</v>
-      </c>
-      <c r="D107" s="1">
-        <v>4</v>
-      </c>
-      <c r="E107" s="1">
-        <v>6</v>
-      </c>
-      <c r="F107" s="1">
-        <v>20000</v>
-      </c>
-      <c r="G107" s="1">
-        <v>10</v>
-      </c>
-      <c r="H107" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J107" s="1">
-        <v>5</v>
-      </c>
-      <c r="K107" s="1">
-        <v>4026</v>
-      </c>
-      <c r="L107" s="1">
-        <v>1</v>
-      </c>
-      <c r="M107" s="1">
-        <f t="shared" si="11"/>
-        <v>200000</v>
-      </c>
-      <c r="N107" s="1">
-        <v>1</v>
-      </c>
-      <c r="O107" s="1">
-        <v>20</v>
-      </c>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="107" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A107" s="1"/>
+      <c r="B107"/>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
+      <c r="E107" s="1"/>
+      <c r="F107" s="1"/>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1"/>
+      <c r="K107" s="1"/>
+      <c r="L107" s="1"/>
+      <c r="M107" s="1"/>
+      <c r="N107" s="1"/>
+      <c r="O107" s="1"/>
     </row>
     <row r="108" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C108" s="1">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D108" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E108" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F108" s="1">
-        <v>20000</v>
+        <v>800</v>
       </c>
       <c r="G108" s="1">
-        <v>10</v>
+        <f t="shared" ref="G108:G112" si="9">N108*O108</f>
+        <v>1200</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="J108" s="1">
         <v>5</v>
       </c>
       <c r="K108" s="1">
-        <v>4035</v>
+        <v>4007</v>
       </c>
       <c r="L108" s="1">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="M108" s="1">
-        <f t="shared" si="11"/>
-        <v>200000</v>
+        <f>F108*G108</f>
+        <v>960000</v>
+      </c>
+      <c r="N108" s="1">
+        <v>4</v>
       </c>
       <c r="O108" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="109" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A109" s="1"/>
-      <c r="B109"/>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
-      <c r="E109" s="1"/>
-      <c r="F109" s="1"/>
-      <c r="G109" s="1"/>
-      <c r="H109" s="1"/>
-      <c r="I109" s="1"/>
-      <c r="J109" s="1"/>
-      <c r="K109" s="1"/>
-      <c r="L109" s="1"/>
-      <c r="M109" s="1"/>
-      <c r="N109" s="1"/>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="109" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C109" s="1">
+        <v>232</v>
+      </c>
+      <c r="D109" s="1">
+        <v>5</v>
+      </c>
+      <c r="E109" s="1">
+        <v>0</v>
+      </c>
+      <c r="F109" s="1">
+        <v>800</v>
+      </c>
+      <c r="G109" s="1">
+        <f t="shared" si="9"/>
+        <v>2000</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J109" s="1">
+        <v>5</v>
+      </c>
+      <c r="K109" s="1">
+        <v>4101</v>
+      </c>
+      <c r="L109" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M109" s="1">
+        <f>F109*G109</f>
+        <v>1600000</v>
+      </c>
+      <c r="N109" s="1">
+        <v>4</v>
+      </c>
       <c r="O109" s="1">
-        <v>40</v>
+        <v>500</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C110" s="1">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D110" s="1">
         <v>5</v>
@@ -5414,30 +5315,30 @@
         <v>0</v>
       </c>
       <c r="F110" s="1">
-        <v>800</v>
+        <v>8000</v>
       </c>
       <c r="G110" s="1">
-        <f t="shared" ref="G110:G115" si="12">N110*O114</f>
-        <v>1200</v>
+        <f t="shared" si="9"/>
+        <v>160</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="J110" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K110" s="1">
-        <v>4007</v>
+        <v>4014</v>
       </c>
       <c r="L110" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="M110" s="1">
-        <f t="shared" ref="M110:M117" si="13">F110*G110</f>
-        <v>960000</v>
+        <f>F110*G110</f>
+        <v>1280000</v>
       </c>
       <c r="N110" s="1">
         <v>4</v>
@@ -5448,7 +5349,7 @@
     </row>
     <row r="111" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C111" s="1">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D111" s="1">
         <v>5</v>
@@ -5457,41 +5358,41 @@
         <v>0</v>
       </c>
       <c r="F111" s="1">
-        <v>800</v>
+        <v>4000</v>
       </c>
       <c r="G111" s="1">
-        <f t="shared" si="12"/>
-        <v>2000</v>
+        <f t="shared" si="9"/>
+        <v>160</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="J111" s="1">
         <v>5</v>
       </c>
       <c r="K111" s="1">
-        <v>4101</v>
+        <v>4001</v>
       </c>
       <c r="L111" s="1">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
       <c r="M111" s="1">
-        <f t="shared" si="13"/>
-        <v>1600000</v>
+        <f>F111*G111</f>
+        <v>640000</v>
       </c>
       <c r="N111" s="1">
         <v>4</v>
       </c>
       <c r="O111" s="1">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C112" s="1">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D112" s="1">
         <v>5</v>
@@ -5500,378 +5401,188 @@
         <v>0</v>
       </c>
       <c r="F112" s="1">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="G112" s="1">
-        <f t="shared" si="12"/>
-        <v>40</v>
+        <f t="shared" si="9"/>
+        <v>160</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="J112" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K112" s="1">
-        <v>4014</v>
+        <v>4002</v>
       </c>
       <c r="L112" s="1">
-        <v>100</v>
+        <v>6000000</v>
       </c>
       <c r="M112" s="1">
-        <f t="shared" si="13"/>
-        <v>320000</v>
+        <f>F112*G112</f>
+        <v>640000</v>
       </c>
       <c r="N112" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="113" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A113"/>
-      <c r="C113" s="1">
-        <v>234</v>
-      </c>
-      <c r="D113" s="1">
-        <v>5</v>
-      </c>
-      <c r="E113" s="1">
-        <v>1</v>
-      </c>
-      <c r="F113" s="1">
-        <v>15000</v>
-      </c>
-      <c r="G113" s="1">
-        <f t="shared" si="12"/>
-        <v>32</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="J113" s="1">
-        <v>5</v>
-      </c>
-      <c r="K113" s="1">
-        <v>4019</v>
-      </c>
-      <c r="L113" s="1">
-        <v>1</v>
-      </c>
-      <c r="M113" s="1">
-        <f t="shared" si="13"/>
-        <v>480000</v>
-      </c>
-      <c r="N113" s="1">
-        <v>4</v>
-      </c>
+      <c r="O112" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="113" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A113" s="1"/>
+      <c r="B113"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1"/>
+      <c r="K113" s="1"/>
+      <c r="L113" s="1"/>
+      <c r="M113" s="1"/>
+      <c r="N113"/>
+      <c r="O113" s="1"/>
     </row>
     <row r="114" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C114" s="1">
-        <v>235</v>
+        <v>999</v>
       </c>
       <c r="D114" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E114" s="1">
         <v>0</v>
       </c>
       <c r="F114" s="1">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="G114" s="1">
-        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I114" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="J114" s="1">
         <v>5</v>
       </c>
       <c r="K114" s="1">
-        <v>4001</v>
+        <v>4006</v>
       </c>
       <c r="L114" s="1">
-        <v>1000000</v>
+        <v>1000</v>
       </c>
       <c r="M114" s="1">
-        <f t="shared" si="13"/>
-        <v>640000</v>
-      </c>
-      <c r="N114" s="1">
-        <v>4</v>
+        <f t="shared" ref="M114:M116" si="10">F114*G114</f>
+        <v>100000</v>
       </c>
       <c r="O114" s="1">
-        <v>300</v>
+        <v>40</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C115" s="1">
-        <v>236</v>
+        <v>1000</v>
       </c>
       <c r="D115" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E115" s="1">
         <v>0</v>
       </c>
       <c r="F115" s="1">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="G115" s="1">
-        <f t="shared" si="12"/>
-        <v>160</v>
+        <v>2000</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="J115" s="1">
         <v>5</v>
       </c>
       <c r="K115" s="1">
-        <v>4002</v>
+        <v>4010</v>
       </c>
       <c r="L115" s="1">
-        <v>6000000</v>
+        <v>5</v>
       </c>
       <c r="M115" s="1">
-        <f t="shared" si="13"/>
-        <v>640000</v>
-      </c>
-      <c r="N115" s="1">
-        <v>4</v>
+        <f t="shared" si="10"/>
+        <v>2000000</v>
       </c>
       <c r="O115" s="1">
-        <v>500</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C116" s="1">
-        <v>237</v>
+        <v>1001</v>
       </c>
       <c r="D116" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E116" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F116" s="1">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="G116" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="J116" s="1">
         <v>5</v>
       </c>
       <c r="K116" s="1">
-        <v>4026</v>
+        <v>4102</v>
       </c>
       <c r="L116" s="1">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M116" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>200000</v>
       </c>
-      <c r="N116" s="1">
-        <v>1</v>
-      </c>
-      <c r="O116" s="1">
-        <v>10</v>
-      </c>
     </row>
     <row r="117" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C117" s="1">
-        <v>238</v>
-      </c>
-      <c r="D117" s="1">
-        <v>5</v>
-      </c>
-      <c r="E117" s="1">
-        <v>10</v>
-      </c>
-      <c r="F117" s="1">
-        <v>20000</v>
-      </c>
-      <c r="G117" s="1">
-        <v>10</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I117" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="J117" s="1">
-        <v>5</v>
-      </c>
-      <c r="K117" s="1">
-        <v>4035</v>
-      </c>
-      <c r="L117" s="1">
-        <v>1</v>
-      </c>
-      <c r="M117" s="1">
-        <f t="shared" si="13"/>
-        <v>200000</v>
-      </c>
-      <c r="O117" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="118" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A118" s="1"/>
-      <c r="B118"/>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
-      <c r="E118" s="1"/>
-      <c r="F118" s="1"/>
-      <c r="G118" s="1"/>
-      <c r="H118" s="1"/>
-      <c r="I118" s="1"/>
-      <c r="J118" s="1"/>
-      <c r="K118" s="1"/>
-      <c r="L118" s="1"/>
-      <c r="M118" s="1"/>
-      <c r="N118"/>
-      <c r="O118" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="119" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C119" s="1">
-        <v>999</v>
-      </c>
-      <c r="D119" s="1">
-        <v>0</v>
-      </c>
-      <c r="E119" s="1">
-        <v>0</v>
-      </c>
-      <c r="F119" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G119" s="1">
-        <v>50</v>
-      </c>
-      <c r="H119" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="I119" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J119" s="1">
-        <v>5</v>
-      </c>
-      <c r="K119" s="1">
-        <v>4006</v>
-      </c>
-      <c r="L119" s="1">
-        <v>1000</v>
-      </c>
-      <c r="M119" s="1">
-        <f t="shared" ref="M119:M121" si="14">F119*G119</f>
-        <v>50000</v>
-      </c>
-      <c r="O119" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="120" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C120" s="1">
-        <v>1000</v>
-      </c>
-      <c r="D120" s="1">
-        <v>0</v>
-      </c>
-      <c r="E120" s="1">
-        <v>0</v>
-      </c>
-      <c r="F120" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G120" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H120" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="I120" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J120" s="1">
-        <v>5</v>
-      </c>
-      <c r="K120" s="1">
-        <v>4010</v>
-      </c>
-      <c r="L120" s="1">
-        <v>5</v>
-      </c>
-      <c r="M120" s="1">
-        <f t="shared" si="14"/>
-        <v>1000000</v>
-      </c>
-      <c r="O120" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="121" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C121" s="1">
-        <v>1001</v>
-      </c>
-      <c r="D121" s="1">
-        <v>0</v>
-      </c>
-      <c r="E121" s="1">
-        <v>0</v>
-      </c>
-      <c r="F121" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G121" s="1">
-        <v>50</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="I121" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="J121" s="1">
-        <v>5</v>
-      </c>
-      <c r="K121" s="1">
-        <v>4102</v>
-      </c>
-      <c r="L121" s="1">
-        <v>20</v>
-      </c>
-      <c r="M121" s="1">
-        <f t="shared" si="14"/>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="122" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A122"/>
+      <c r="A117"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
+      <c r="E117" s="1"/>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1"/>
+      <c r="K117" s="1"/>
+      <c r="L117" s="1"/>
+      <c r="M117" s="1"/>
+      <c r="N117" s="1"/>
+      <c r="O117"/>
+    </row>
+    <row r="122" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
@@ -5885,24 +5596,7 @@
       <c r="L122" s="1"/>
       <c r="M122" s="1"/>
       <c r="N122" s="1"/>
-      <c r="O122"/>
-    </row>
-    <row r="127" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A127" s="1"/>
-      <c r="B127" s="1"/>
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
-      <c r="E127" s="1"/>
-      <c r="F127" s="1"/>
-      <c r="G127" s="1"/>
-      <c r="H127" s="1"/>
-      <c r="I127" s="1"/>
-      <c r="J127" s="1"/>
-      <c r="K127" s="1"/>
-      <c r="L127" s="1"/>
-      <c r="M127" s="1"/>
-      <c r="N127" s="1"/>
-      <c r="O127" s="1"/>
+      <c r="O122" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="163">
   <si>
     <t>#</t>
   </si>
@@ -380,12 +380,6 @@
   </si>
   <si>
     <t>暗金魂心</t>
-  </si>
-  <si>
-    <t>金色50坐骑</t>
-  </si>
-  <si>
-    <t>金色50坐骑自选</t>
   </si>
   <si>
     <t>金色兽魂</t>
@@ -1537,7 +1531,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O122"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -2009,7 +2003,7 @@
         <v>1</v>
       </c>
       <c r="M15" s="1">
-        <f t="shared" ref="M15:M37" si="1">F15*G15</f>
+        <f t="shared" ref="M15:M46" si="1">F15*G15</f>
         <v>100000</v>
       </c>
     </row>
@@ -2837,7 +2831,7 @@
         <v>1</v>
       </c>
       <c r="M38" s="1">
-        <f>F38*G38</f>
+        <f t="shared" si="1"/>
         <v>600000</v>
       </c>
     </row>
@@ -2873,7 +2867,7 @@
         <v>1</v>
       </c>
       <c r="M39" s="1">
-        <f>F39*G39</f>
+        <f t="shared" si="1"/>
         <v>600000</v>
       </c>
     </row>
@@ -2909,7 +2903,7 @@
         <v>1</v>
       </c>
       <c r="M40" s="1">
-        <f>F40*G40</f>
+        <f t="shared" si="1"/>
         <v>5000000</v>
       </c>
     </row>
@@ -2945,7 +2939,7 @@
         <v>10</v>
       </c>
       <c r="M41" s="1">
-        <f>F41*G41</f>
+        <f t="shared" si="1"/>
         <v>2000000</v>
       </c>
     </row>
@@ -2981,7 +2975,7 @@
         <v>1</v>
       </c>
       <c r="M42" s="1">
-        <f>F42*G42</f>
+        <f t="shared" si="1"/>
         <v>1000000</v>
       </c>
     </row>
@@ -3017,7 +3011,7 @@
         <v>1</v>
       </c>
       <c r="M43" s="1">
-        <f>F43*G43</f>
+        <f t="shared" si="1"/>
         <v>2000000</v>
       </c>
     </row>
@@ -3053,7 +3047,7 @@
         <v>1</v>
       </c>
       <c r="M44" s="1">
-        <f>F44*G44</f>
+        <f t="shared" si="1"/>
         <v>2000000</v>
       </c>
     </row>
@@ -3089,7 +3083,7 @@
         <v>1</v>
       </c>
       <c r="M45" s="1">
-        <f>F45*G45</f>
+        <f t="shared" si="1"/>
         <v>5000000</v>
       </c>
     </row>
@@ -3125,7 +3119,7 @@
         <v>1</v>
       </c>
       <c r="M46" s="1">
-        <f>F46*G46</f>
+        <f t="shared" si="1"/>
         <v>3000000</v>
       </c>
     </row>
@@ -3376,7 +3370,7 @@
         <v>1</v>
       </c>
       <c r="M53" s="1">
-        <f t="shared" ref="M53:M57" si="3">F53*G53</f>
+        <f t="shared" ref="M53:M59" si="3">F53*G53</f>
         <v>3000000</v>
       </c>
       <c r="N53" s="1"/>
@@ -3524,7 +3518,7 @@
         <v>1</v>
       </c>
       <c r="M58" s="1">
-        <f>F58*G58</f>
+        <f t="shared" si="3"/>
         <v>2400000</v>
       </c>
       <c r="N58" s="1"/>
@@ -3564,7 +3558,7 @@
         <v>1</v>
       </c>
       <c r="M59" s="1">
-        <f>F59*G59</f>
+        <f t="shared" si="3"/>
         <v>3000000</v>
       </c>
       <c r="N59" s="1"/>
@@ -3581,7 +3575,7 @@
         <v>10</v>
       </c>
       <c r="F60" s="1">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="G60" s="1">
         <v>1</v>
@@ -3590,20 +3584,20 @@
         <v>116</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J60" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K60" s="1">
-        <v>302</v>
+        <v>4052</v>
       </c>
       <c r="L60" s="1">
         <v>1</v>
       </c>
       <c r="M60" s="1">
-        <f t="shared" ref="M60:M65" si="4">F60*G60</f>
-        <v>1000000</v>
+        <f>F60*G60</f>
+        <v>500000</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3614,16 +3608,16 @@
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F61" s="1">
-        <v>500000</v>
+        <v>500</v>
       </c>
       <c r="G61" s="1">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>118</v>
@@ -3632,14 +3626,14 @@
         <v>5</v>
       </c>
       <c r="K61" s="1">
-        <v>4052</v>
+        <v>4022</v>
       </c>
       <c r="L61" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M61" s="1">
-        <f t="shared" si="4"/>
-        <v>500000</v>
+        <f>F61*G61</f>
+        <v>5000000</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3650,13 +3644,13 @@
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F62" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G62" s="1">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>119</v>
@@ -3668,14 +3662,14 @@
         <v>5</v>
       </c>
       <c r="K62" s="1">
-        <v>4022</v>
+        <v>4051</v>
       </c>
       <c r="L62" s="1">
         <v>100</v>
       </c>
       <c r="M62" s="1">
-        <f t="shared" si="4"/>
-        <v>5000000</v>
+        <f>F62*G62</f>
+        <v>2000000</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3686,32 +3680,32 @@
         <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F63" s="1">
-        <v>1000</v>
+        <v>3000000</v>
       </c>
       <c r="G63" s="1">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>121</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J63" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K63" s="1">
-        <v>4051</v>
+        <v>211</v>
       </c>
       <c r="L63" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="M63" s="1">
-        <f t="shared" si="4"/>
-        <v>2000000</v>
+        <f>F63*G63</f>
+        <v>3000000</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3731,92 +3725,94 @@
         <v>1</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J64" s="1">
         <v>4</v>
       </c>
       <c r="K64" s="1">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="L64" s="1">
         <v>1</v>
       </c>
       <c r="M64" s="1">
-        <f t="shared" si="4"/>
+        <f>F64*G64</f>
         <v>3000000</v>
       </c>
     </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C65" s="1">
-        <v>70</v>
-      </c>
-      <c r="D65" s="1">
-        <v>0</v>
-      </c>
-      <c r="E65" s="1">
-        <v>15</v>
-      </c>
-      <c r="F65" s="1">
-        <v>3000000</v>
-      </c>
-      <c r="G65" s="1">
-        <v>1</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="J65" s="1">
-        <v>4</v>
-      </c>
-      <c r="K65" s="1">
-        <v>303</v>
-      </c>
-      <c r="L65" s="1">
-        <v>1</v>
-      </c>
-      <c r="M65" s="1">
-        <f t="shared" si="4"/>
-        <v>3000000</v>
-      </c>
+    <row r="65" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
     </row>
     <row r="66" customFormat="1" customHeight="1" spans="1:15">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
+      <c r="C66" s="1">
+        <v>71</v>
+      </c>
+      <c r="D66" s="1">
+        <v>0</v>
+      </c>
+      <c r="E66" s="1">
+        <v>10</v>
+      </c>
+      <c r="F66" s="1">
+        <v>20000</v>
+      </c>
+      <c r="G66" s="1">
+        <v>450</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J66" s="1">
+        <v>5</v>
+      </c>
+      <c r="K66" s="1">
+        <v>4035</v>
+      </c>
+      <c r="L66" s="1">
+        <v>1</v>
+      </c>
+      <c r="M66" s="1">
+        <f t="shared" ref="M66:M72" si="4">F66*G66</f>
+        <v>9000000</v>
+      </c>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
     </row>
-    <row r="67" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C67" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
       </c>
       <c r="E67" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F67" s="1">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="G67" s="1">
         <v>450</v>
@@ -3831,33 +3827,31 @@
         <v>5</v>
       </c>
       <c r="K67" s="1">
-        <v>4035</v>
+        <v>4039</v>
       </c>
       <c r="L67" s="1">
         <v>1</v>
       </c>
       <c r="M67" s="1">
-        <f>F67*G67</f>
-        <v>9000000</v>
-      </c>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
-    </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="1:15">
+        <f t="shared" si="4"/>
+        <v>13500000</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="1:15">
       <c r="C68" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F68" s="1">
-        <v>30000</v>
+        <v>3000</v>
       </c>
       <c r="G68" s="1">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>127</v>
@@ -3869,31 +3863,32 @@
         <v>5</v>
       </c>
       <c r="K68" s="1">
-        <v>4039</v>
+        <v>4011</v>
       </c>
       <c r="L68" s="1">
         <v>1</v>
       </c>
       <c r="M68" s="1">
-        <f>F68*G68</f>
-        <v>13500000</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="1:15">
+        <f t="shared" si="4"/>
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="69" customFormat="1" customHeight="1" spans="1:15">
+      <c r="B69" s="1"/>
       <c r="C69" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
       </c>
       <c r="E69" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="1">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="G69" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>129</v>
@@ -3905,32 +3900,37 @@
         <v>5</v>
       </c>
       <c r="K69" s="1">
-        <v>4011</v>
+        <v>4019</v>
       </c>
       <c r="L69" s="1">
         <v>1</v>
       </c>
       <c r="M69" s="1">
-        <f>F69*G69</f>
-        <v>3000000</v>
-      </c>
+        <f t="shared" si="4"/>
+        <v>7500000</v>
+      </c>
+      <c r="N69" s="1">
+        <v>1</v>
+      </c>
+      <c r="O69" s="1"/>
     </row>
     <row r="70" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F70" s="1">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="G70" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>131</v>
@@ -3942,37 +3942,37 @@
         <v>5</v>
       </c>
       <c r="K70" s="1">
-        <v>4019</v>
+        <v>4026</v>
       </c>
       <c r="L70" s="1">
         <v>1</v>
       </c>
       <c r="M70" s="1">
-        <f>F70*G70</f>
-        <v>7500000</v>
+        <f t="shared" si="4"/>
+        <v>6000000</v>
       </c>
       <c r="N70" s="1">
         <v>1</v>
       </c>
-      <c r="O70" s="1"/>
-    </row>
-    <row r="71" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
+      <c r="O70" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C71" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F71" s="1">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="G71" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>133</v>
@@ -3984,25 +3984,19 @@
         <v>5</v>
       </c>
       <c r="K71" s="1">
-        <v>4026</v>
+        <v>4038</v>
       </c>
       <c r="L71" s="1">
         <v>1</v>
       </c>
       <c r="M71" s="1">
-        <f>F71*G71</f>
+        <f t="shared" si="4"/>
         <v>6000000</v>
-      </c>
-      <c r="N71" s="1">
-        <v>1</v>
-      </c>
-      <c r="O71" s="1">
-        <v>20</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C72" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
@@ -4011,10 +4005,10 @@
         <v>20</v>
       </c>
       <c r="F72" s="1">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="G72" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>135</v>
@@ -4026,55 +4020,55 @@
         <v>5</v>
       </c>
       <c r="K72" s="1">
-        <v>4038</v>
+        <v>4046</v>
       </c>
       <c r="L72" s="1">
         <v>1</v>
       </c>
       <c r="M72" s="1">
-        <f>F72*G72</f>
-        <v>6000000</v>
-      </c>
-    </row>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C73" s="1">
-        <v>77</v>
-      </c>
-      <c r="D73" s="1">
-        <v>0</v>
-      </c>
-      <c r="E73" s="1">
-        <v>20</v>
-      </c>
-      <c r="F73" s="1">
-        <v>50000</v>
-      </c>
-      <c r="G73" s="1">
-        <v>100</v>
-      </c>
-      <c r="H73" s="1" t="s">
+        <f t="shared" si="4"/>
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C75" s="1">
+        <v>80</v>
+      </c>
+      <c r="D75" s="1">
+        <v>0</v>
+      </c>
+      <c r="E75" s="1">
+        <v>15</v>
+      </c>
+      <c r="F75" s="1">
+        <v>100000</v>
+      </c>
+      <c r="G75" s="1">
+        <v>10</v>
+      </c>
+      <c r="H75" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="I73" s="1" t="s">
+      <c r="I75" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="J73" s="1">
-        <v>5</v>
-      </c>
-      <c r="K73" s="1">
-        <v>4046</v>
-      </c>
-      <c r="L73" s="1">
-        <v>1</v>
-      </c>
-      <c r="M73" s="1">
-        <f>F73*G73</f>
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="J75" s="1">
+        <v>11</v>
+      </c>
+      <c r="K75" s="1">
+        <v>1998001</v>
+      </c>
+      <c r="L75" s="1">
+        <v>1</v>
+      </c>
+      <c r="M75" s="1">
+        <f>F75*G75</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="1:15">
       <c r="C76" s="1">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
@@ -4098,7 +4092,7 @@
         <v>11</v>
       </c>
       <c r="K76" s="1">
-        <v>1998001</v>
+        <v>1998002</v>
       </c>
       <c r="L76" s="1">
         <v>1</v>
@@ -4108,9 +4102,11 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="1:15">
+    <row r="77" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
       <c r="C77" s="1">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
@@ -4134,7 +4130,7 @@
         <v>11</v>
       </c>
       <c r="K77" s="1">
-        <v>1998002</v>
+        <v>1998003</v>
       </c>
       <c r="L77" s="1">
         <v>1</v>
@@ -4143,12 +4139,14 @@
         <f>F77*G77</f>
         <v>1000000</v>
       </c>
+      <c r="N77" s="1"/>
+      <c r="O77" s="1"/>
     </row>
     <row r="78" customFormat="1" customHeight="1" spans="1:15">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
@@ -4172,7 +4170,7 @@
         <v>11</v>
       </c>
       <c r="K78" s="1">
-        <v>1998003</v>
+        <v>1998004</v>
       </c>
       <c r="L78" s="1">
         <v>1</v>
@@ -4188,7 +4186,7 @@
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D79" s="1">
         <v>0</v>
@@ -4212,7 +4210,7 @@
         <v>11</v>
       </c>
       <c r="K79" s="1">
-        <v>1998004</v>
+        <v>1998005</v>
       </c>
       <c r="L79" s="1">
         <v>1</v>
@@ -4224,69 +4222,73 @@
       <c r="N79" s="1"/>
       <c r="O79" s="1"/>
     </row>
-    <row r="80" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A80" s="1"/>
-      <c r="B80" s="1"/>
-      <c r="C80" s="1">
-        <v>84</v>
-      </c>
-      <c r="D80" s="1">
-        <v>0</v>
-      </c>
-      <c r="E80" s="1">
-        <v>15</v>
-      </c>
-      <c r="F80" s="1">
-        <v>100000</v>
-      </c>
-      <c r="G80" s="1">
-        <v>10</v>
-      </c>
-      <c r="H80" s="1" t="s">
+    <row r="80" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A80"/>
+      <c r="B80"/>
+    </row>
+    <row r="81" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1"/>
+      <c r="N81" s="1"/>
+      <c r="O81" s="1"/>
+    </row>
+    <row r="82" customFormat="1" customHeight="1" spans="1:15">
+      <c r="B82" s="1"/>
+      <c r="C82" s="1">
+        <v>102</v>
+      </c>
+      <c r="D82" s="1">
+        <v>1</v>
+      </c>
+      <c r="E82" s="1">
+        <v>0</v>
+      </c>
+      <c r="F82" s="1">
+        <v>100</v>
+      </c>
+      <c r="G82" s="1">
+        <f t="shared" ref="G82:G86" si="5">N82*O82</f>
+        <v>300</v>
+      </c>
+      <c r="H82" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="I80" s="1" t="s">
+      <c r="I82" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="J80" s="1">
-        <v>11</v>
-      </c>
-      <c r="K80" s="1">
-        <v>1998005</v>
-      </c>
-      <c r="L80" s="1">
-        <v>1</v>
-      </c>
-      <c r="M80" s="1">
-        <f>F80*G80</f>
-        <v>1000000</v>
-      </c>
-      <c r="N80" s="1"/>
-      <c r="O80" s="1"/>
-    </row>
-    <row r="81" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A81"/>
-      <c r="B81"/>
-    </row>
-    <row r="82" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
-      <c r="L82" s="1"/>
-      <c r="M82" s="1"/>
-      <c r="N82" s="1"/>
-      <c r="O82" s="1"/>
+      <c r="J82" s="1">
+        <v>5</v>
+      </c>
+      <c r="K82" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L82" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M82" s="1">
+        <f>F82*G82</f>
+        <v>30000</v>
+      </c>
+      <c r="N82" s="1">
+        <v>1</v>
+      </c>
+      <c r="O82" s="1">
+        <v>300</v>
+      </c>
     </row>
     <row r="83" customFormat="1" customHeight="1" spans="1:15">
       <c r="B83" s="1"/>
       <c r="C83" s="1">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D83" s="1">
         <v>1</v>
@@ -4298,8 +4300,8 @@
         <v>100</v>
       </c>
       <c r="G83" s="1">
-        <f t="shared" ref="G83:G87" si="5">N83*O83</f>
-        <v>300</v>
+        <f t="shared" si="5"/>
+        <v>500</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>149</v>
@@ -4311,26 +4313,26 @@
         <v>5</v>
       </c>
       <c r="K83" s="1">
-        <v>4007</v>
+        <v>4101</v>
       </c>
       <c r="L83" s="1">
         <v>1000</v>
       </c>
       <c r="M83" s="1">
         <f>F83*G83</f>
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="N83" s="1">
         <v>1</v>
       </c>
       <c r="O83" s="1">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="84" customFormat="1" customHeight="1" spans="1:15">
       <c r="B84" s="1"/>
       <c r="C84" s="1">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D84" s="1">
         <v>1</v>
@@ -4339,11 +4341,11 @@
         <v>0</v>
       </c>
       <c r="F84" s="1">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G84" s="1">
         <f t="shared" si="5"/>
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>151</v>
@@ -4352,29 +4354,30 @@
         <v>152</v>
       </c>
       <c r="J84" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K84" s="1">
-        <v>4101</v>
+        <v>4014</v>
       </c>
       <c r="L84" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="M84" s="1">
         <f>F84*G84</f>
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="N84" s="1">
         <v>1</v>
       </c>
       <c r="O84" s="1">
-        <v>500</v>
+        <v>40</v>
       </c>
     </row>
     <row r="85" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D85" s="1">
         <v>1</v>
@@ -4383,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G85" s="1">
         <f t="shared" si="5"/>
@@ -4396,17 +4399,17 @@
         <v>154</v>
       </c>
       <c r="J85" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K85" s="1">
-        <v>4014</v>
+        <v>4001</v>
       </c>
       <c r="L85" s="1">
-        <v>100</v>
+        <v>1000000</v>
       </c>
       <c r="M85" s="1">
         <f>F85*G85</f>
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="N85" s="1">
         <v>1</v>
@@ -4419,7 +4422,7 @@
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D86" s="1">
         <v>1</v>
@@ -4444,10 +4447,10 @@
         <v>5</v>
       </c>
       <c r="K86" s="1">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="L86" s="1">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="M86" s="1">
         <f>F86*G86</f>
@@ -4460,71 +4463,69 @@
         <v>40</v>
       </c>
     </row>
-    <row r="87" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1">
-        <v>107</v>
-      </c>
-      <c r="D87" s="1">
-        <v>1</v>
-      </c>
-      <c r="E87" s="1">
-        <v>0</v>
-      </c>
-      <c r="F87" s="1">
-        <v>500</v>
-      </c>
-      <c r="G87" s="1">
-        <f t="shared" si="5"/>
-        <v>40</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J87" s="1">
-        <v>5</v>
-      </c>
-      <c r="K87" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L87" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M87" s="1">
-        <f>F87*G87</f>
-        <v>20000</v>
-      </c>
-      <c r="N87" s="1">
-        <v>1</v>
-      </c>
-      <c r="O87" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="89" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A89" s="1"/>
-      <c r="B89"/>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="1"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="1"/>
-      <c r="K89" s="1"/>
-      <c r="L89" s="1"/>
-      <c r="M89" s="1"/>
-      <c r="N89" s="1"/>
-      <c r="O89" s="1"/>
+    <row r="88" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A88" s="1"/>
+      <c r="B88"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+      <c r="M88" s="1"/>
+      <c r="N88" s="1"/>
+      <c r="O88" s="1"/>
+    </row>
+    <row r="89" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C89" s="1">
+        <v>201</v>
+      </c>
+      <c r="D89" s="1">
+        <v>2</v>
+      </c>
+      <c r="E89" s="1">
+        <v>0</v>
+      </c>
+      <c r="F89" s="5">
+        <v>200</v>
+      </c>
+      <c r="G89" s="1">
+        <f t="shared" ref="G89:G93" si="6">N89*O89</f>
+        <v>300</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J89" s="1">
+        <v>5</v>
+      </c>
+      <c r="K89" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L89" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M89" s="1">
+        <f>F89*G89</f>
+        <v>60000</v>
+      </c>
+      <c r="N89" s="1">
+        <v>1</v>
+      </c>
+      <c r="O89" s="1">
+        <v>300</v>
+      </c>
     </row>
     <row r="90" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C90" s="1">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D90" s="1">
         <v>2</v>
@@ -4536,8 +4537,8 @@
         <v>200</v>
       </c>
       <c r="G90" s="1">
-        <f t="shared" ref="G90:G94" si="6">N90*O90</f>
-        <v>300</v>
+        <f t="shared" si="6"/>
+        <v>500</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>149</v>
@@ -4549,25 +4550,25 @@
         <v>5</v>
       </c>
       <c r="K90" s="1">
-        <v>4007</v>
+        <v>4101</v>
       </c>
       <c r="L90" s="1">
         <v>1000</v>
       </c>
       <c r="M90" s="1">
         <f>F90*G90</f>
-        <v>60000</v>
+        <v>100000</v>
       </c>
       <c r="N90" s="1">
         <v>1</v>
       </c>
       <c r="O90" s="1">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="91" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C91" s="1">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D91" s="1">
         <v>2</v>
@@ -4576,11 +4577,11 @@
         <v>0</v>
       </c>
       <c r="F91" s="5">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="G91" s="1">
         <f t="shared" si="6"/>
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>151</v>
@@ -4589,28 +4590,28 @@
         <v>152</v>
       </c>
       <c r="J91" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K91" s="1">
-        <v>4101</v>
+        <v>4014</v>
       </c>
       <c r="L91" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="M91" s="1">
         <f>F91*G91</f>
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="N91" s="1">
         <v>1</v>
       </c>
       <c r="O91" s="1">
-        <v>500</v>
+        <v>40</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C92" s="1">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D92" s="1">
         <v>2</v>
@@ -4619,7 +4620,7 @@
         <v>0</v>
       </c>
       <c r="F92" s="5">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G92" s="1">
         <f t="shared" si="6"/>
@@ -4632,17 +4633,17 @@
         <v>154</v>
       </c>
       <c r="J92" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K92" s="1">
-        <v>4014</v>
+        <v>4001</v>
       </c>
       <c r="L92" s="1">
-        <v>100</v>
+        <v>1000000</v>
       </c>
       <c r="M92" s="1">
         <f>F92*G92</f>
-        <v>80000</v>
+        <v>40000</v>
       </c>
       <c r="N92" s="1">
         <v>1</v>
@@ -4653,7 +4654,7 @@
     </row>
     <row r="93" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C93" s="1">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D93" s="1">
         <v>2</v>
@@ -4678,10 +4679,10 @@
         <v>5</v>
       </c>
       <c r="K93" s="1">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="L93" s="1">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="M93" s="1">
         <f>F93*G93</f>
@@ -4694,69 +4695,69 @@
         <v>40</v>
       </c>
     </row>
-    <row r="94" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C94" s="1">
-        <v>206</v>
-      </c>
-      <c r="D94" s="1">
-        <v>2</v>
-      </c>
-      <c r="E94" s="1">
-        <v>0</v>
-      </c>
-      <c r="F94" s="5">
+    <row r="94" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A94" s="1"/>
+      <c r="B94"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
+      <c r="K94" s="1"/>
+      <c r="L94" s="1"/>
+      <c r="M94" s="1"/>
+      <c r="N94" s="1"/>
+      <c r="O94" s="1"/>
+    </row>
+    <row r="95" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C95" s="1">
+        <v>211</v>
+      </c>
+      <c r="D95" s="1">
+        <v>3</v>
+      </c>
+      <c r="E95" s="1">
+        <v>0</v>
+      </c>
+      <c r="F95" s="1">
+        <v>400</v>
+      </c>
+      <c r="G95" s="1">
+        <f t="shared" ref="G95:G99" si="7">N95*O95</f>
+        <v>300</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J95" s="1">
+        <v>5</v>
+      </c>
+      <c r="K95" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L95" s="1">
         <v>1000</v>
       </c>
-      <c r="G94" s="1">
-        <f t="shared" si="6"/>
-        <v>40</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J94" s="1">
-        <v>5</v>
-      </c>
-      <c r="K94" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L94" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M94" s="1">
-        <f>F94*G94</f>
-        <v>40000</v>
-      </c>
-      <c r="N94" s="1">
-        <v>1</v>
-      </c>
-      <c r="O94" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="95" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A95" s="1"/>
-      <c r="B95"/>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1"/>
-      <c r="K95" s="1"/>
-      <c r="L95" s="1"/>
-      <c r="M95" s="1"/>
-      <c r="N95" s="1"/>
-      <c r="O95" s="1"/>
+      <c r="M95" s="1">
+        <f>F95*G95</f>
+        <v>120000</v>
+      </c>
+      <c r="N95" s="1">
+        <v>1</v>
+      </c>
+      <c r="O95" s="1">
+        <v>300</v>
+      </c>
     </row>
     <row r="96" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C96" s="1">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D96" s="1">
         <v>3</v>
@@ -4768,8 +4769,8 @@
         <v>400</v>
       </c>
       <c r="G96" s="1">
-        <f t="shared" ref="G96:G100" si="7">N96*O96</f>
-        <v>300</v>
+        <f t="shared" si="7"/>
+        <v>500</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>149</v>
@@ -4781,25 +4782,25 @@
         <v>5</v>
       </c>
       <c r="K96" s="1">
-        <v>4007</v>
+        <v>4101</v>
       </c>
       <c r="L96" s="1">
         <v>1000</v>
       </c>
       <c r="M96" s="1">
         <f>F96*G96</f>
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="N96" s="1">
         <v>1</v>
       </c>
       <c r="O96" s="1">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C97" s="1">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D97" s="1">
         <v>3</v>
@@ -4808,11 +4809,11 @@
         <v>0</v>
       </c>
       <c r="F97" s="1">
-        <v>400</v>
+        <v>4000</v>
       </c>
       <c r="G97" s="1">
         <f t="shared" si="7"/>
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>151</v>
@@ -4821,28 +4822,28 @@
         <v>152</v>
       </c>
       <c r="J97" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K97" s="1">
-        <v>4101</v>
+        <v>4014</v>
       </c>
       <c r="L97" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="M97" s="1">
         <f>F97*G97</f>
-        <v>200000</v>
+        <v>160000</v>
       </c>
       <c r="N97" s="1">
         <v>1</v>
       </c>
       <c r="O97" s="1">
-        <v>500</v>
+        <v>40</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C98" s="1">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D98" s="1">
         <v>3</v>
@@ -4851,7 +4852,7 @@
         <v>0</v>
       </c>
       <c r="F98" s="1">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G98" s="1">
         <f t="shared" si="7"/>
@@ -4864,17 +4865,17 @@
         <v>154</v>
       </c>
       <c r="J98" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K98" s="1">
-        <v>4014</v>
+        <v>4001</v>
       </c>
       <c r="L98" s="1">
-        <v>100</v>
+        <v>1000000</v>
       </c>
       <c r="M98" s="1">
         <f>F98*G98</f>
-        <v>160000</v>
+        <v>80000</v>
       </c>
       <c r="N98" s="1">
         <v>1</v>
@@ -4885,7 +4886,7 @@
     </row>
     <row r="99" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C99" s="1">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D99" s="1">
         <v>3</v>
@@ -4910,10 +4911,10 @@
         <v>5</v>
       </c>
       <c r="K99" s="1">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="L99" s="1">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="M99" s="1">
         <f>F99*G99</f>
@@ -4926,69 +4927,69 @@
         <v>40</v>
       </c>
     </row>
-    <row r="100" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C100" s="1">
-        <v>216</v>
-      </c>
-      <c r="D100" s="1">
-        <v>3</v>
-      </c>
-      <c r="E100" s="1">
-        <v>0</v>
-      </c>
-      <c r="F100" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G100" s="1">
-        <f t="shared" si="7"/>
-        <v>40</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J100" s="1">
-        <v>5</v>
-      </c>
-      <c r="K100" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L100" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M100" s="1">
-        <f>F100*G100</f>
-        <v>80000</v>
-      </c>
-      <c r="N100" s="1">
-        <v>1</v>
-      </c>
-      <c r="O100" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="101" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A101" s="1"/>
-      <c r="B101"/>
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
-      <c r="E101" s="1"/>
-      <c r="F101" s="1"/>
-      <c r="G101" s="1"/>
-      <c r="H101" s="1"/>
-      <c r="I101" s="1"/>
-      <c r="J101" s="1"/>
-      <c r="K101" s="1"/>
-      <c r="L101" s="1"/>
-      <c r="M101" s="1"/>
-      <c r="N101" s="1"/>
-      <c r="O101" s="1"/>
+    <row r="100" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A100" s="1"/>
+      <c r="B100"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
+      <c r="K100" s="1"/>
+      <c r="L100" s="1"/>
+      <c r="M100" s="1"/>
+      <c r="N100" s="1"/>
+      <c r="O100" s="1"/>
+    </row>
+    <row r="101" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C101" s="1">
+        <v>221</v>
+      </c>
+      <c r="D101" s="1">
+        <v>4</v>
+      </c>
+      <c r="E101" s="1">
+        <v>0</v>
+      </c>
+      <c r="F101" s="5">
+        <v>600</v>
+      </c>
+      <c r="G101" s="1">
+        <f t="shared" ref="G101:G105" si="8">N101*O101</f>
+        <v>300</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J101" s="1">
+        <v>5</v>
+      </c>
+      <c r="K101" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L101" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M101" s="1">
+        <f>F101*G101</f>
+        <v>180000</v>
+      </c>
+      <c r="N101" s="1">
+        <v>1</v>
+      </c>
+      <c r="O101" s="1">
+        <v>300</v>
+      </c>
     </row>
     <row r="102" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C102" s="1">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D102" s="1">
         <v>4</v>
@@ -5000,8 +5001,8 @@
         <v>600</v>
       </c>
       <c r="G102" s="1">
-        <f t="shared" ref="G102:G106" si="8">N102*O102</f>
-        <v>300</v>
+        <f t="shared" si="8"/>
+        <v>500</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>149</v>
@@ -5013,25 +5014,25 @@
         <v>5</v>
       </c>
       <c r="K102" s="1">
-        <v>4007</v>
+        <v>4101</v>
       </c>
       <c r="L102" s="1">
         <v>1000</v>
       </c>
       <c r="M102" s="1">
         <f>F102*G102</f>
-        <v>180000</v>
+        <v>300000</v>
       </c>
       <c r="N102" s="1">
         <v>1</v>
       </c>
       <c r="O102" s="1">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C103" s="1">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D103" s="1">
         <v>4</v>
@@ -5040,11 +5041,11 @@
         <v>0</v>
       </c>
       <c r="F103" s="5">
-        <v>600</v>
+        <v>6000</v>
       </c>
       <c r="G103" s="1">
         <f t="shared" si="8"/>
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>151</v>
@@ -5053,28 +5054,28 @@
         <v>152</v>
       </c>
       <c r="J103" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K103" s="1">
-        <v>4101</v>
+        <v>4014</v>
       </c>
       <c r="L103" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="M103" s="1">
         <f>F103*G103</f>
-        <v>300000</v>
+        <v>240000</v>
       </c>
       <c r="N103" s="1">
         <v>1</v>
       </c>
       <c r="O103" s="1">
-        <v>500</v>
+        <v>40</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C104" s="1">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D104" s="1">
         <v>4</v>
@@ -5083,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="F104" s="5">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="G104" s="1">
         <f t="shared" si="8"/>
@@ -5096,17 +5097,17 @@
         <v>154</v>
       </c>
       <c r="J104" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K104" s="1">
-        <v>4014</v>
+        <v>4001</v>
       </c>
       <c r="L104" s="1">
-        <v>100</v>
+        <v>1000000</v>
       </c>
       <c r="M104" s="1">
         <f>F104*G104</f>
-        <v>240000</v>
+        <v>120000</v>
       </c>
       <c r="N104" s="1">
         <v>1</v>
@@ -5117,7 +5118,7 @@
     </row>
     <row r="105" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C105" s="1">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D105" s="1">
         <v>4</v>
@@ -5142,10 +5143,10 @@
         <v>5</v>
       </c>
       <c r="K105" s="1">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="L105" s="1">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="M105" s="1">
         <f>F105*G105</f>
@@ -5158,69 +5159,69 @@
         <v>40</v>
       </c>
     </row>
-    <row r="106" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C106" s="1">
-        <v>226</v>
-      </c>
-      <c r="D106" s="1">
+    <row r="106" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A106" s="1"/>
+      <c r="B106"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1"/>
+      <c r="K106" s="1"/>
+      <c r="L106" s="1"/>
+      <c r="M106" s="1"/>
+      <c r="N106" s="1"/>
+      <c r="O106" s="1"/>
+    </row>
+    <row r="107" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C107" s="1">
+        <v>231</v>
+      </c>
+      <c r="D107" s="1">
+        <v>5</v>
+      </c>
+      <c r="E107" s="1">
+        <v>0</v>
+      </c>
+      <c r="F107" s="1">
+        <v>800</v>
+      </c>
+      <c r="G107" s="1">
+        <f t="shared" ref="G107:G111" si="9">N107*O107</f>
+        <v>1200</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J107" s="1">
+        <v>5</v>
+      </c>
+      <c r="K107" s="1">
+        <v>4007</v>
+      </c>
+      <c r="L107" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M107" s="1">
+        <f>F107*G107</f>
+        <v>960000</v>
+      </c>
+      <c r="N107" s="1">
         <v>4</v>
       </c>
-      <c r="E106" s="1">
-        <v>0</v>
-      </c>
-      <c r="F106" s="5">
-        <v>3000</v>
-      </c>
-      <c r="G106" s="1">
-        <f t="shared" si="8"/>
-        <v>40</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="J106" s="1">
-        <v>5</v>
-      </c>
-      <c r="K106" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L106" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M106" s="1">
-        <f>F106*G106</f>
-        <v>120000</v>
-      </c>
-      <c r="N106" s="1">
-        <v>1</v>
-      </c>
-      <c r="O106" s="1">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="107" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A107" s="1"/>
-      <c r="B107"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
-      <c r="G107" s="1"/>
-      <c r="H107" s="1"/>
-      <c r="I107" s="1"/>
-      <c r="J107" s="1"/>
-      <c r="K107" s="1"/>
-      <c r="L107" s="1"/>
-      <c r="M107" s="1"/>
-      <c r="N107" s="1"/>
-      <c r="O107" s="1"/>
+      <c r="O107" s="1">
+        <v>300</v>
+      </c>
     </row>
     <row r="108" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C108" s="1">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D108" s="1">
         <v>5</v>
@@ -5232,8 +5233,8 @@
         <v>800</v>
       </c>
       <c r="G108" s="1">
-        <f t="shared" ref="G108:G112" si="9">N108*O108</f>
-        <v>1200</v>
+        <f t="shared" si="9"/>
+        <v>2000</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>149</v>
@@ -5245,25 +5246,25 @@
         <v>5</v>
       </c>
       <c r="K108" s="1">
-        <v>4007</v>
+        <v>4101</v>
       </c>
       <c r="L108" s="1">
         <v>1000</v>
       </c>
       <c r="M108" s="1">
         <f>F108*G108</f>
-        <v>960000</v>
+        <v>1600000</v>
       </c>
       <c r="N108" s="1">
         <v>4</v>
       </c>
       <c r="O108" s="1">
-        <v>300</v>
+        <v>500</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C109" s="1">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D109" s="1">
         <v>5</v>
@@ -5272,11 +5273,11 @@
         <v>0</v>
       </c>
       <c r="F109" s="1">
-        <v>800</v>
+        <v>8000</v>
       </c>
       <c r="G109" s="1">
         <f t="shared" si="9"/>
-        <v>2000</v>
+        <v>160</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>151</v>
@@ -5285,28 +5286,28 @@
         <v>152</v>
       </c>
       <c r="J109" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K109" s="1">
-        <v>4101</v>
+        <v>4014</v>
       </c>
       <c r="L109" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="M109" s="1">
         <f>F109*G109</f>
-        <v>1600000</v>
+        <v>1280000</v>
       </c>
       <c r="N109" s="1">
         <v>4</v>
       </c>
       <c r="O109" s="1">
-        <v>500</v>
+        <v>40</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C110" s="1">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D110" s="1">
         <v>5</v>
@@ -5315,7 +5316,7 @@
         <v>0</v>
       </c>
       <c r="F110" s="1">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="G110" s="1">
         <f t="shared" si="9"/>
@@ -5328,17 +5329,17 @@
         <v>154</v>
       </c>
       <c r="J110" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K110" s="1">
-        <v>4014</v>
+        <v>4001</v>
       </c>
       <c r="L110" s="1">
-        <v>100</v>
+        <v>1000000</v>
       </c>
       <c r="M110" s="1">
         <f>F110*G110</f>
-        <v>1280000</v>
+        <v>640000</v>
       </c>
       <c r="N110" s="1">
         <v>4</v>
@@ -5349,7 +5350,7 @@
     </row>
     <row r="111" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C111" s="1">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D111" s="1">
         <v>5</v>
@@ -5374,10 +5375,10 @@
         <v>5</v>
       </c>
       <c r="K111" s="1">
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="L111" s="1">
-        <v>1000000</v>
+        <v>6000000</v>
       </c>
       <c r="M111" s="1">
         <f>F111*G111</f>
@@ -5390,69 +5391,65 @@
         <v>40</v>
       </c>
     </row>
-    <row r="112" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C112" s="1">
-        <v>236</v>
-      </c>
-      <c r="D112" s="1">
-        <v>5</v>
-      </c>
-      <c r="E112" s="1">
-        <v>0</v>
-      </c>
-      <c r="F112" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G112" s="1">
-        <f t="shared" si="9"/>
-        <v>160</v>
-      </c>
-      <c r="H112" s="1" t="s">
+    <row r="112" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A112" s="1"/>
+      <c r="B112"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1"/>
+      <c r="K112" s="1"/>
+      <c r="L112" s="1"/>
+      <c r="M112" s="1"/>
+      <c r="N112"/>
+      <c r="O112" s="1"/>
+    </row>
+    <row r="113" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="C113" s="1">
+        <v>999</v>
+      </c>
+      <c r="D113" s="1">
+        <v>0</v>
+      </c>
+      <c r="E113" s="1">
+        <v>0</v>
+      </c>
+      <c r="F113" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G113" s="1">
+        <v>100</v>
+      </c>
+      <c r="H113" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="I112" s="1" t="s">
+      <c r="I113" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="J112" s="1">
-        <v>5</v>
-      </c>
-      <c r="K112" s="1">
-        <v>4002</v>
-      </c>
-      <c r="L112" s="1">
-        <v>6000000</v>
-      </c>
-      <c r="M112" s="1">
-        <f>F112*G112</f>
-        <v>640000</v>
-      </c>
-      <c r="N112" s="1">
-        <v>4</v>
-      </c>
-      <c r="O112" s="1">
+      <c r="J113" s="1">
+        <v>5</v>
+      </c>
+      <c r="K113" s="1">
+        <v>4006</v>
+      </c>
+      <c r="L113" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M113" s="1">
+        <f t="shared" ref="M113:M115" si="10">F113*G113</f>
+        <v>100000</v>
+      </c>
+      <c r="O113" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="113" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A113" s="1"/>
-      <c r="B113"/>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
-      <c r="E113" s="1"/>
-      <c r="F113" s="1"/>
-      <c r="G113" s="1"/>
-      <c r="H113" s="1"/>
-      <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
-      <c r="K113" s="1"/>
-      <c r="L113" s="1"/>
-      <c r="M113" s="1"/>
-      <c r="N113"/>
-      <c r="O113" s="1"/>
     </row>
     <row r="114" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C114" s="1">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="D114" s="1">
         <v>0</v>
@@ -5464,7 +5461,7 @@
         <v>1000</v>
       </c>
       <c r="G114" s="1">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>159</v>
@@ -5476,22 +5473,22 @@
         <v>5</v>
       </c>
       <c r="K114" s="1">
-        <v>4006</v>
+        <v>4010</v>
       </c>
       <c r="L114" s="1">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="M114" s="1">
-        <f t="shared" ref="M114:M116" si="10">F114*G114</f>
-        <v>100000</v>
+        <f t="shared" si="10"/>
+        <v>2000000</v>
       </c>
       <c r="O114" s="1">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C115" s="1">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D115" s="1">
         <v>0</v>
@@ -5500,10 +5497,10 @@
         <v>0</v>
       </c>
       <c r="F115" s="1">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G115" s="1">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>161</v>
@@ -5515,88 +5512,49 @@
         <v>5</v>
       </c>
       <c r="K115" s="1">
-        <v>4010</v>
+        <v>4102</v>
       </c>
       <c r="L115" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="M115" s="1">
         <f t="shared" si="10"/>
-        <v>2000000</v>
-      </c>
-      <c r="O115" s="1">
-        <v>5</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="C116" s="1">
-        <v>1001</v>
-      </c>
-      <c r="D116" s="1">
-        <v>0</v>
-      </c>
-      <c r="E116" s="1">
-        <v>0</v>
-      </c>
-      <c r="F116" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G116" s="1">
-        <v>100</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="J116" s="1">
-        <v>5</v>
-      </c>
-      <c r="K116" s="1">
-        <v>4102</v>
-      </c>
-      <c r="L116" s="1">
-        <v>20</v>
-      </c>
-      <c r="M116" s="1">
-        <f t="shared" si="10"/>
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="117" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A117"/>
-      <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-      <c r="E117" s="1"/>
-      <c r="F117" s="1"/>
-      <c r="G117" s="1"/>
-      <c r="H117" s="1"/>
-      <c r="I117" s="1"/>
-      <c r="J117" s="1"/>
-      <c r="K117" s="1"/>
-      <c r="L117" s="1"/>
-      <c r="M117" s="1"/>
-      <c r="N117" s="1"/>
-      <c r="O117"/>
-    </row>
-    <row r="122" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A122" s="1"/>
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1"/>
-      <c r="G122" s="1"/>
-      <c r="H122" s="1"/>
-      <c r="I122" s="1"/>
-      <c r="J122" s="1"/>
-      <c r="K122" s="1"/>
-      <c r="L122" s="1"/>
-      <c r="M122" s="1"/>
-      <c r="N122" s="1"/>
-      <c r="O122" s="1"/>
+      <c r="A116"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
+      <c r="E116" s="1"/>
+      <c r="F116" s="1"/>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1"/>
+      <c r="I116" s="1"/>
+      <c r="J116" s="1"/>
+      <c r="K116" s="1"/>
+      <c r="L116" s="1"/>
+      <c r="M116" s="1"/>
+      <c r="N116" s="1"/>
+      <c r="O116"/>
+    </row>
+    <row r="121" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A121" s="1"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
+      <c r="E121" s="1"/>
+      <c r="F121" s="1"/>
+      <c r="G121" s="1"/>
+      <c r="H121" s="1"/>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1"/>
+      <c r="K121" s="1"/>
+      <c r="L121" s="1"/>
+      <c r="M121" s="1"/>
+      <c r="N121" s="1"/>
+      <c r="O121" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -397,7 +397,7 @@
     <t>坐骑兽粮*100</t>
   </si>
   <si>
-    <t>粉色50坐骑</t>
+    <t>粉色50仙宠</t>
   </si>
   <si>
     <t>暗金50坐骑</t>
@@ -3370,7 +3370,7 @@
         <v>1</v>
       </c>
       <c r="M53" s="1">
-        <f t="shared" ref="M53:M59" si="3">F53*G53</f>
+        <f t="shared" ref="M53:M64" si="3">F53*G53</f>
         <v>3000000</v>
       </c>
       <c r="N53" s="1"/>
@@ -3596,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="M60" s="1">
-        <f>F60*G60</f>
+        <f t="shared" si="3"/>
         <v>500000</v>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
         <v>100</v>
       </c>
       <c r="M61" s="1">
-        <f>F61*G61</f>
+        <f t="shared" si="3"/>
         <v>5000000</v>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
         <v>100</v>
       </c>
       <c r="M62" s="1">
-        <f>F62*G62</f>
+        <f t="shared" si="3"/>
         <v>2000000</v>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
         <v>1</v>
       </c>
       <c r="M63" s="1">
-        <f>F63*G63</f>
+        <f t="shared" si="3"/>
         <v>3000000</v>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
         <v>1</v>
       </c>
       <c r="M64" s="1">
-        <f>F64*G64</f>
+        <f t="shared" si="3"/>
         <v>3000000</v>
       </c>
     </row>

--- a/Excel/FestiveConfig.xlsx
+++ b/Excel/FestiveConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="163">
   <si>
     <t>#</t>
   </si>
@@ -1661,7 +1661,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="1">
-        <v>888</v>
+        <v>666</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>14</v>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M6" s="1">
         <f t="shared" ref="M6:M14" si="0">F6*G6</f>
-        <v>266400</v>
+        <v>199800</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:13">
@@ -1697,7 +1697,7 @@
         <v>13</v>
       </c>
       <c r="G7" s="1">
-        <v>888</v>
+        <v>666</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>16</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="M7" s="1">
         <f t="shared" si="0"/>
-        <v>266400</v>
+        <v>199800</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1733,7 +1733,7 @@
         <v>13</v>
       </c>
       <c r="G8" s="1">
-        <v>888</v>
+        <v>666</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>18</v>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="M8" s="1">
         <f t="shared" si="0"/>
-        <v>266400</v>
+        <v>199800</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:13">
@@ -2777,7 +2777,7 @@
         <v>83</v>
       </c>
       <c r="G37" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>84</v>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="M37" s="1">
         <f t="shared" si="1"/>
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="2:15">
@@ -3154,7 +3154,7 @@
         <v>100000</v>
       </c>
       <c r="G48" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>102</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="M48" s="1">
         <f t="shared" ref="M48:M52" si="2">F48*G48</f>
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
@@ -3352,7 +3352,7 @@
         <v>500000</v>
       </c>
       <c r="G53" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>109</v>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="M53" s="1">
         <f t="shared" ref="M53:M64" si="3">F53*G53</f>
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
@@ -3540,7 +3540,7 @@
         <v>1500000</v>
       </c>
       <c r="G59" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>115</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="M59" s="1">
         <f t="shared" si="3"/>
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
@@ -3673,6 +3673,12 @@
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A63" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C63" s="1">
         <v>68</v>
       </c>
@@ -3709,6 +3715,12 @@
       </c>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A64" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C64" s="1">
         <v>69</v>
       </c>
